--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,20 +476,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="83" customWidth="1" min="3" max="3"/>
+    <col width="103" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="220" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="273" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,11 +556,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2403</v>
+        <v>2.354</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>机构研报显示，8月电子布经销商7628价格已卖到15元/米，9月又上涨10-20%；当前电子布厂家7628电子布价格为11-12元/米，涨价已连续三个月加速。</t>
+          <t>机构研报指出，随着电子布、铜箔及CCL价格持续上行，PCB厂商已陆续启动重新报价。相较上游材料，板厂涨价存在一定时滞，Q3有望成为产品价格、产能利用率与订单结构共同改善的起涨点。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -577,14 +577,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20.57</v>
+        <v>22.63</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10</v>
+        <v>10.0146</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>5天3板</t>
+          <t>6天4板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -605,11 +605,11 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.2403</v>
+        <v>2.354</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>机构研报显示，8月电子布经销商7628价格已卖到15元/米，9月又上涨10-20%；当前电子布厂家7628电子布价格为11-12元/米，涨价已连续三个月加速。</t>
+          <t>机构研报指出，随着电子布、铜箔及CCL价格持续上行，PCB厂商已陆续启动重新报价。相较上游材料，板厂涨价存在一定时滞，Q3有望成为产品价格、产能利用率与订单结构共同改善的起涨点。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -617,24 +617,28 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh605258</t>
+          <t>sh605058</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>协和电子</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>34.77</v>
+        <v>36.64</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.9968</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+        <v>9.997</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司主要从事印制电路板的研发、生产、销售以及SMT业务，PCB产品主要应用在汽车电子和高频通讯领域。</t>
+          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -650,11 +654,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2403</v>
+        <v>2.354</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>机构研报显示，8月电子布经销商7628价格已卖到15元/米，9月又上涨10-20%；当前电子布厂家7628电子布价格为11-12元/米，涨价已连续三个月加速。</t>
+          <t>机构研报指出，随着电子布、铜箔及CCL价格持续上行，PCB厂商已陆续启动重新报价。相较上游材料，板厂涨价存在一定时滞，Q3有望成为产品价格、产能利用率与订单结构共同改善的起涨点。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -662,25 +666,24 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz002848</t>
+          <t>sz002579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>高斯贝尔</t>
+          <t>中京电子</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15.24</v>
+        <v>18.79</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.0361</v>
+        <v>10.0117</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PCB|公司覆铜板产品是高频高速信号传输特性的PCB基板材料。公司高速板覆铜板产品可以应用于服务器及光模块。
-</t>
+          <t>PCB|公司主营业务为印制电路板(PCB)的研发、生产、销售与服务，已获得AI PC的小批量订单。公司PCB产品可广泛应用于航天军工。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -696,11 +699,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.2403</v>
+        <v>2.354</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>机构研报显示，8月电子布经销商7628价格已卖到15元/米，9月又上涨10-20%；当前电子布厂家7628电子布价格为11-12元/米，涨价已连续三个月加速。</t>
+          <t>机构研报指出，随着电子布、铜箔及CCL价格持续上行，PCB厂商已陆续启动重新报价。相较上游材料，板厂涨价存在一定时滞，Q3有望成为产品价格、产能利用率与订单结构共同改善的起涨点。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -708,24 +711,24 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh605058</t>
+          <t>sz300903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>科翔股份</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>33.31</v>
+        <v>108.3</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.0066</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
+          <t>PCB|公司具备为客户提供“PCB+元器件+解决方案”的一站式服务能力，可以提供双层板、多层板、高密度互连（HDI）板、厚铜板、高频/高速板、金属基板、陶瓷基板、IC载板、软硬结合板等PCB产品。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -741,11 +744,11 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2403</v>
+        <v>2.354</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>机构研报显示，8月电子布经销商7628价格已卖到15元/米，9月又上涨10-20%；当前电子布厂家7628电子布价格为11-12元/米，涨价已连续三个月加速。</t>
+          <t>机构研报指出，随着电子布、铜箔及CCL价格持续上行，PCB厂商已陆续启动重新报价。相较上游材料，板厂涨价存在一定时滞，Q3有望成为产品价格、产能利用率与订单结构共同改善的起涨点。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -753,29 +756,29 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh603936</t>
+          <t>sz001212</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>博敏电子</t>
+          <t>中旗新材</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20.88</v>
+        <v>35.02</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.0105</v>
+        <v>9.987400000000001</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司PCB事业群战略性聚焦“电源/储能、数据通信、汽车电子、智能终端”四大领域，以“陶瓷基板、特色产品、数连产品”树差异，将PCB业务内核持续向高质量、高价值领域延伸，打造持续增长三级火箭，实现产品结构升级及优质客户渗透。</t>
+          <t>硅微粉|中旗新材在互动平台回答投资者提问时表示，公司硅微粉产品尚未向覆铜板企业实现供货，公司正在积极开展市场拓展工作，努力推动硅微粉业务向覆铜板企业供货的发展。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>硅微粉</t>
         </is>
       </c>
     </row>
@@ -786,11 +789,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.2403</v>
+        <v>2.354</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>机构研报显示，8月电子布经销商7628价格已卖到15元/米，9月又上涨10-20%；当前电子布厂家7628电子布价格为11-12元/米，涨价已连续三个月加速。</t>
+          <t>机构研报指出，随着电子布、铜箔及CCL价格持续上行，PCB厂商已陆续启动重新报价。相较上游材料，板厂涨价存在一定时滞，Q3有望成为产品价格、产能利用率与订单结构共同改善的起涨点。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -798,30 +801,30 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz002815</t>
+          <t>sz002141</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>崇达技术</t>
+          <t>贤丰控股</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20.08</v>
+        <v>6.97</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.0274</v>
+        <v>9.9369</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>PCB+服务器|1.主营业务为印制电路板的生产和销售；主要产品为小批量印制电路板,产品类型覆盖HDI板、背板、厚铜板等。
-2.公司服务器产品客户是中兴通讯、新华三、云尖等，产品包括服务器主板和AI服务器。</t>
+          <t>PCB|公司旗下高硕航宇与上下游协同运作构建起了完整覆铜板产业链，主要产品包括常规FR-4/CEM-3系列覆铜板、无铅无卤FR-4系列覆铜板等，具备60万余张/月覆铜板产能。
+2026年7月15日公告，子公司贤丰东莞与广东盈硕签署协议，共同出资设立贤丰盈硕科技有限公司，注册资本1.18亿元。贤丰东莞以货币出资6018万元，持股51%；广东盈硕以货币及实物出资5782万元，持股49%。合资公司主要业务为消费领域PCB的研发、生产和销售。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>PCB, 服务器</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
@@ -832,11 +835,11 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.2403</v>
+        <v>2.354</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>机构研报显示，8月电子布经销商7628价格已卖到15元/米，9月又上涨10-20%；当前电子布厂家7628电子布价格为11-12元/米，涨价已连续三个月加速。</t>
+          <t>机构研报指出，随着电子布、铜箔及CCL价格持续上行，PCB厂商已陆续启动重新报价。相较上游材料，板厂涨价存在一定时滞，Q3有望成为产品价格、产能利用率与订单结构共同改善的起涨点。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -844,29 +847,30 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz001232</t>
+          <t>sh600186</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>嘉立创</t>
+          <t>莲花控股</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>182.48</v>
+        <v>13.18</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.0006</v>
+        <v>10.0167</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司聚焦于服务PCB样板、小批量板制造需求，同时也具备PCB中大批量板的生产能力。</t>
+          <t>ABF膜+算力租赁|1.4月9日，深圳联合产权交易所一则成交公示，莲花控股的全资子公司杭州莲花科创以约1.03亿元拿下深圳纽菲斯51%股权。纽菲斯的主营方向，是ABF膜，高端芯片封装载板用增层胶膜。
+2.2023年9月，新华三集团与公司举行战略合作签约仪式，携手莲花健康共建国内领先、国际一流的智能算力中心，满足通用大模型、自动驾驶、机器人、元宇宙、游戏、传媒等应用行业在内的算力需求。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>ABF膜, 算力租赁</t>
         </is>
       </c>
     </row>
@@ -877,11 +881,11 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.2403</v>
+        <v>2.354</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>机构研报显示，8月电子布经销商7628价格已卖到15元/米，9月又上涨10-20%；当前电子布厂家7628电子布价格为11-12元/米，涨价已连续三个月加速。</t>
+          <t>机构研报指出，随着电子布、铜箔及CCL价格持续上行，PCB厂商已陆续启动重新报价。相较上游材料，板厂涨价存在一定时滞，Q3有望成为产品价格、产能利用率与订单结构共同改善的起涨点。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -889,48 +893,48 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh603386</t>
+          <t>sz301132</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>骏亚科技</t>
+          <t>满坤科技</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>16.46</v>
+        <v>58.37</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.0267</v>
+        <v>20.0041</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司主营业务为印制电路板（PCB）的研发、生产和销售，在人形机器人领域，公司成功导入国内头部客户并开始批量供货。</t>
+          <t>PCB+汽车|公司具备PCB全制程生产能力和全方位服务体系，主要产品为单/双面、多层印制电路板，以刚性板为主。公司HDI起步产品LED显示、触控模组等已经可以满足10层二阶产品的批量生产。汽车电子领域是公司市场战略布局的重点领域，产品覆盖传统汽车（燃油车）主要零部件和新能源汽车电池核心部件领域。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>PCB, 汽车</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-1.9352</v>
+        <v>2.2833</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash模型正式发布。该模型具备原生多模态视觉理解能力，能力上限更高、推理速度更快、吞吐更大、可扩展到更大参数模型。</t>
+          <t>Anthropic首席执行官达里奥·阿莫代伊在博客中表示，AI行业需放缓新模型开发速度，要留足时间完成模型与人类目标对齐及安全防护。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -943,14 +947,14 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>23.51</v>
+        <v>25.86</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.014</v>
+        <v>9.995700000000001</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -967,1416 +971,2148 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-1.9352</v>
+        <v>2.2833</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash模型正式发布。该模型具备原生多模态视觉理解能力，能力上限更高、推理速度更快、吞吐更大、可扩展到更大参数模型。</t>
+          <t>Anthropic首席执行官达里奥·阿莫代伊在博客中表示，AI行业需放缓新模型开发速度，要留足时间完成模型与人类目标对齐及安全防护。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh605069</t>
+          <t>sz002212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>正和生态</t>
+          <t>天融信</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10.0478</v>
+        <v>9.955400000000001</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>AI智能体|公司专门设立了“数字科技”业务版块，以数值溯源模型为核心，融合AI大模型技术，聚焦“数智生态、智慧体验空间”两大产品方向。其中“数智生态”将智慧监测、智能设备、智慧水务大模型应用在在生态、水务垂直领域场景，提供生态水务智能体及运维一体化解决方案。</t>
+          <t>网络安全+AI|1.公司作为中国领先的网络安全、大数据与云服务提供商，为政府、金融、运营商、能源、卫生、教育、交通、制造等各行业客户提供网络安全产品、大数据产品和云服务。
+2.2024年11月26日公司在互动平台表示，AI Agent（智能体）是公司天问大模型关键技术之一，具备自然语言处理、风险预测、情报抽取等核心能力，应用于安全知识问答、日志分析、告警研判等安全运营场景。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>AI智能体</t>
+          <t>网络安全, AI</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-1.9352</v>
+        <v>2.2833</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash模型正式发布。该模型具备原生多模态视觉理解能力，能力上限更高、推理速度更快、吞吐更大、可扩展到更大参数模型。</t>
+          <t>Anthropic首席执行官达里奥·阿莫代伊在博客中表示，AI行业需放缓新模型开发速度，要留足时间完成模型与人类目标对齐及安全防护。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh600410</t>
+          <t>sh688004</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>华胜天成</t>
+          <t>博汇科技</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>15.42</v>
+        <v>22.82</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>9.9857</v>
+        <v>19.979</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>华为算力+AI应用|1.公司与华为深度合作人工智能算力中心解决方案，携手鲲鹏、昇腾助力人工智能领域发展，共同参与多个省市智算中心规划建设项目。
-2.公司打造了AI驱动的企业投标系统投标大王，通过引入大模型技术和Multi-Agent架构，形成高效的模型交互策略，实现了招标文件智能解读、资源精准匹配、风险科学评估和标书全面审核等关键功能。</t>
+          <t>股权转让+网络安全|1.博汇科技公告称，公司控股股东、实控人及其一致行动人孙传明、郭忠武、博聚睿智，股东数码视讯、郑金福、王荣芳、陈恒拟通过协议转让方式，向投资者深圳市明心泓智科技合伙企业合计转让公司1169.56万股，占公司股本总额的14.6%。
+2.公司通过综合运用人工智能深度学习算法，对各类媒体内容进行多维度分析，精准识别敏感、违规内容，实现对广播电视、IPTV/OTT、互联网站、微信、微博、各类短视频、自媒体等传播媒介播放的视听内容进行监管，实现对媒体中敏感、有害、违规内容的自动化、智能化分析研判，提高媒体内容监管的智能化水平。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>华为算力, AI应用</t>
+          <t>股权转让, 网络安全</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-1.9352</v>
+        <v>2.2833</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash模型正式发布。该模型具备原生多模态视觉理解能力，能力上限更高、推理速度更快、吞吐更大、可扩展到更大参数模型。</t>
+          <t>Anthropic首席执行官达里奥·阿莫代伊在博客中表示，AI行业需放缓新模型开发速度，要留足时间完成模型与人类目标对齐及安全防护。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603466</t>
+          <t>sz000839</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">风语筑  </t>
+          <t>国安股份</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>13.27</v>
+        <v>3.11</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.0332</v>
+        <v>9.894</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>机器人+AI应用|1.公司设立“具身智能研究院”，与松延机器人签署战略合作，并积极与头部AI硬件厂商对接，面向文化场馆、文旅街区等新文旅场景提供“场景策划—内容生成—算法部署—硬件集成—持续运营”一体化具身智能解决方案。
-2.公司将致力于加速虚拟现实（VR）和混合现实（MR）技术与人工智能生成内容（AIGC）技术的结合，推动交互式数字内容、VR/MR与AIGC技术在文化、博物馆和旅游等不同领域的应用。</t>
+          <t>网络安全+AI|1.公司旗下子公司鸿联九五为企业提供一站式的审核服务体系。公司内容审核业务包括文本审核、图片审核、视频审核、音频审核、人工智能审核。
+2.下属鸿联九五已有自研AI智能体在特定场景中进行应用。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>机器人, AI应用</t>
+          <t>网络安全, AI</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-1.9352</v>
+        <v>2.2833</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek V4.1 Flash模型正式发布。该模型具备原生多模态视觉理解能力，能力上限更高、推理速度更快、吞吐更大、可扩展到更大参数模型。</t>
+          <t>Anthropic首席执行官达里奥·阿莫代伊在博客中表示，AI行业需放缓新模型开发速度，要留足时间完成模型与人类目标对齐及安全防护。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh600088</t>
+          <t>sh688244</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>中视传媒</t>
+          <t>永信至诚</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>13.4</v>
+        <v>16.44</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.0164</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>网络安全+AI|在人工智能领域，公司网络靶场系列产品和“数字风洞”产品体系均是人工智能安全测试评估的基础设施平台，具备对人工智能相关产品和风险进行安全测试评估的能力。</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>网络安全, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1.9599</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>中信证券研报称，新重磅药物/新分子/新技术对于工艺开发和试验设计能力的要求提高，中国CDMO行业有望凭借在全球生物医药创新技术领域早期管线的不断积累，进入由“工程师红利”+“引领创新红利”双核驱动时代。</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>sh603439</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>三力制药</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>9.9681</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>创新药|公司联合控股子公司云南无敌与贵阳工业发展基金等专业投资机构设立黔力生物医药基金，基金总规模5亿元，将重点关注生物科技与健康管理赛道的股权投资项目，该基金通过"产业洞察+资本赋能"双驱动模式，截止2024年年报，已储备十多个创新药标的，其中已有多个产品进入III期临床试验阶段。</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>1.9599</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>中信证券研报称，新重磅药物/新分子/新技术对于工艺开发和试验设计能力的要求提高，中国CDMO行业有望凭借在全球生物医药创新技术领域早期管线的不断积累，进入由“工程师红利”+“引领创新红利”双核驱动时代。</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>sh600488</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>10.0935</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>卤米松|旗下津药和平持有"尤乐宁"，且具备卤米松原料药生产资质，形成原料药+制剂一体化。</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>卤米松</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1.9599</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>中信证券研报称，新重磅药物/新分子/新技术对于工艺开发和试验设计能力的要求提高，中国CDMO行业有望凭借在全球生物医药创新技术领域早期管线的不断积累，进入由“工程师红利”+“引领创新红利”双核驱动时代。</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>sz301520</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>CXO|公司是一家同时提供药学研究和临床研究服务的综合型CRO企业，通过合同形式为医药企业和其他医药研发机构提供专业化医药研发外包服务。</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>CXO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>1.9599</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>中信证券研报称，新重磅药物/新分子/新技术对于工艺开发和试验设计能力的要求提高，中国CDMO行业有望凭借在全球生物医药创新技术领域早期管线的不断积累，进入由“工程师红利”+“引领创新红利”双核驱动时代。</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>sh688137</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>近岸蛋白</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>CXO|公司CRO服务业务主要分为定制化技术服务和技术包转让，主要为生物领域相关科研院所、药企及疫苗生产企业提供研究用重组蛋白、抗体及mRNA等相关定制化服务，同时也可提供重组蛋白质大规模生产工艺开发及技术转移服务。</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>CXO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1.9599</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>中信证券研报称，新重磅药物/新分子/新技术对于工艺开发和试验设计能力的要求提高，中国CDMO行业有望凭借在全球生物医药创新技术领域早期管线的不断积累，进入由“工程师红利”+“引领创新红利”双核驱动时代。</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>sz002172</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>澳洋健康</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>10.0877</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>医疗服务|公司的医疗服务业务已形成医、康、养护联动发展模式，形成以澳洋医院总院为支撑，澳洋医院三兴分院、顺康医院、港城康复医院、优居壹佰护理院、张家港澳洋护理院联动发展。</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>医疗服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>新能源汽车</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>上交所停复牌信息显示，广汽集团因重要事项未公告，9月14日全天停牌。广汽集团港股早盘竞价大幅高开8.64%。</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>sz000980</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>众泰汽车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>9.905700000000001</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5天4板</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>汽车整车|公司是国内较早进入新能源汽车领域的车企，已具备新能源汽车完整的整车设计、试制、试验和零部件开发能力。</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>汽车整车</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>新能源汽车</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>上交所停复牌信息显示，广汽集团因重要事项未公告，9月14日全天停牌。广汽集团港股早盘竞价大幅高开8.64%。</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>sz000981</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>山子高科</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>10.0386</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>哪吒汽车重整|9月11日，合众新能源（哪吒汽车母公司）破产重整案第四次债权人会议以线上形式召开，《重整计划（草案）》显示，浙江太乙圣莲企业管理合伙企业（有限合伙）拟出资30亿元入主，“太乙圣莲”注册成立于2026年4月，由浙江山子控股有限公司和浙江山子玉虚科技有限公司两家公司合伙组建，前者实控人为深交所上市公司山子高科董事长叶骥，后者实控人为山子高科董办负责人虞舒心。</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>哪吒汽车重整</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>新能源汽车</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>上交所停复牌信息显示，广汽集团因重要事项未公告，9月14日全天停牌。广汽集团港股早盘竞价大幅高开8.64%。</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>sz002232</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>启明信息</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>10.0072</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>汽车零部件+AI|1.中国第一汽车集团旗下直接控股的上市公司，为整车企业提供前装导航、行驶记录仪、国六法规监控模块等智能网联终端产品的定制开发、生产及售后服务。
+2.公司基于云原生的MLOps敏捷AI平台，帮助数据科学家和开发人员快速准备、构建、训练和部署高质量的AI模型。</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>汽车零部件, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>新能源汽车</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>上交所停复牌信息显示，广汽集团因重要事项未公告，9月14日全天停牌。广汽集团港股早盘竞价大幅高开8.64%。</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>sz000572</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>海马汽车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>9.8985</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>汽车整车|地处海南省海口市，主营汽车制造及服务。</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>汽车整车</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>新能源汽车</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>上交所停复牌信息显示，广汽集团因重要事项未公告，9月14日全天停牌。广汽集团港股早盘竞价大幅高开8.64%。</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>sz000868</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>安凯客车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>10.1408</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>客车整车|公司是国内较早研发和批量生产运营新能源客车的整车企业，已形成集10-12米纯电动公交客车，12米纯电动旅游和通勤客车、12米增程式电动公交客车、10-12米油电混合动力城市客车于一体的产品平台。</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>客车整车</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0.7676999999999999</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>中国电信研究院行业与企业战略研究所所长饶少阳称，从算力需求来看，智能体的爆发将带动我国算力需求持续高速增长，预计未来2～3年，我国算力需求平均每年将增长近10倍。</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>sh605069</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>正和生态</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>AI应用|公司专门设立了“数字科技”业务版块，以数值溯源模型为核心，融合AI大模型技术，聚焦“数智生态、智慧体验空间”两大产品方向。其中“数智生态”将智慧监测、智能设备、智慧水务大模型应用在在生态、水务垂直领域场景，提供生态水务智能体及运维一体化解决方案。</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>0.7676999999999999</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>中国电信研究院行业与企业战略研究所所长饶少阳称，从算力需求来看，智能体的爆发将带动我国算力需求持续高速增长，预计未来2～3年，我国算力需求平均每年将增长近10倍。</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>sh600088</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>中视传媒</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>AI+影视|1.公司在内容创制过程中，探索应用AI技术进行辅助，提升制作的效率与品质。
 2.中央电视台旗下上市公司。公司所从事的业务有影视业务，既影视拍摄、电视节目制作；广告业务，代理各类广告；旅游业务，无锡及南海影视基地开发。</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>AI, 影视</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>-1.9352</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek V4.1 Flash模型正式发布。该模型具备原生多模态视觉理解能力，能力上限更高、推理速度更快、吞吐更大、可扩展到更大参数模型。</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>sz002242</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>九阳股份</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>10.0565</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>类脑人工智能|深思考人工智能是一家专注于类脑人工智能与深度学习核心科技的AI公司，公司最为突出的技术是“多模态深度语义理解技术”，可同时理解文本、视觉图像背后的语义，主要面向场景为智慧医疗大健康和智能汽车。公司于2019年9月23日在互动平台确认，目前持有深思考8.77%，目前位列第二大股东。</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>类脑人工智能</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>-0.7159000000000001</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>东方证券表示，算力用电的长期天花板可能高于当前市场预期，电力保障能力正成为算力时代的核心竞争变量，算电协同有望驱动电力资产价值重估。</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>sz000993</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>闽东电力</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>13.88</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>9.9842</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>电力|公司致力于清洁能源、新能源等领域的发展。发电业务是公司业务的核心业务，主要包括水力发电和风力发电。是电力产业链的发电环节，相对电网企业，处于弱势地位，由于水电、风电生产均属清洁能源，电调顺序靠前，与火电相比，来自电网的竞争压力相对较小。公司目前是宁德市唯一以经营清洁能源发电为主营业务的国有控股上市公司。</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>-0.7159000000000001</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>东方证券表示，算力用电的长期天花板可能高于当前市场预期，电力保障能力正成为算力时代的核心竞争变量，算电协同有望驱动电力资产价值重估。</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>sh605011</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>杭州热电</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>19.03</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>电力|公司的最终控制人为杭州市人民政府。公司是一家主营工业园区热电联产、集中供热的节能环保型企业。公司提供的主要产品是蒸汽与电力。</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>-0.7159000000000001</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>东方证券表示，算力用电的长期天花板可能高于当前市场预期，电力保障能力正成为算力时代的核心竞争变量，算电协同有望驱动电力资产价值重估。</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>sh603693</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>江苏新能</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>9.9656</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>绿电|公司的主营业务为新能源发电项目的投资开发、建设运营及电力销售，目前主要包括风能发电、生物质能发电和光伏发电三个板块。</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>绿电</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>-0.7159000000000001</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>东方证券表示，算力用电的长期天花板可能高于当前市场预期，电力保障能力正成为算力时代的核心竞争变量，算电协同有望驱动电力资产价值重估。</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>sz002218</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>拓日新能</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>9.975100000000001</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>绿电+太空光伏|1.公司具备超过十年的光伏电站开发、设计、建设和运营等一体化能力，自持光伏电站与同行企业相比的成本优势主要源于公司在光伏电站和EPC承建中实现超70%的原材料自产自供，其中包括太阳能电池产品（硅片、电池片）、光伏组件核心辅材（光伏玻璃、光伏胶膜、光伏接线盒）以及光伏支架等，从而形成了公司承建光伏电站独特的优势。
-2.公司于2015年参与了东方红卫星“开拓一号”单晶硅太阳电池项目，具备成熟的卫星用光伏组件生产制造能力。</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>绿电, 太空光伏</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>-0.7553</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>机构研报指出，基本面上，军工2026年中报显示主机厂经营性现金流大幅改善，下半年集中交付推进下有望迎来结构性业绩兑现。</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>sz002560</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>通达股份</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>电线电缆+军工|1.1.公司从事的主要业务包括电线电缆生产、销售及航空零部件加工两大板块。
-2.公司全资子公司成都航飞主要从事飞机结构零部件的高端精密加工制造服务，产品包括机体钛合金、铝合金框、梁、肋、接头等数控加工件，钣金成型模具、复合材料成型模具，产品覆盖多款主要军用机型以及中国商飞C919等民用机型。</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>电线电缆, 军工</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>-0.7553</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>机构研报指出，基本面上，军工2026年中报显示主机厂经营性现金流大幅改善，下半年集中交付推进下有望迎来结构性业绩兑现。</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>sz300563</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>神宇股份</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>27.92</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>19.9828</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>军工+铜连接|1.公司是专业从事射频同轴电缆的研发、生产和销售的高新技术企业，主要产品包括军标系列射频同轴电缆等多种系列产品，公司已经与多家军工企业建立长期战略合作关系，共同研发航天、电子等军用射频同轴电缆。
-2.公司生产的DAC铜连接线缆可大量用于AI伺服器内部数据的传输。</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>军工, 铜连接</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>-0.7553</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>机构研报指出，基本面上，军工2026年中报显示主机厂经营性现金流大幅改善，下半年集中交付推进下有望迎来结构性业绩兑现。</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>sh600967</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>内蒙一机</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>9.985300000000001</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>军工+机器人|1.中国兵器工业集团旗下上市公司，主要生产履带、轮式、火炮三大系列产品，形成了轮履结合、车炮结合、轻重结合、内外贸结合的研制生产格局。
-2.公司在机器人领域承担了国家多项攻关项目和重点研发项目，已经开展了多型产品的研制。目前公司研制的两栖无人查险机器人系列产品是公司承担的国家应急管理部揭榜攻关项目，目前已完成研制，正在试验中。</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>军工, 机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>-0.7553</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>机构研报指出，基本面上，军工2026年中报显示主机厂经营性现金流大幅改善，下半年集中交付推进下有望迎来结构性业绩兑现。</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>sz002519</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>银河电子</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>9.930300000000001</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>军工+商业航天|1.公司军品智能机电业务由同智机电开展运营，主要业务是为满足我国国防建设需要，为不同行业的特定客户提供特种车辆的智能供配电管理系统、智能电源管理系统、环境控制系统、健康管理系统等。
-2.参股格思航天作为卫星ODM厂商承接量产卫星设计制造与卫星核心组部件研发业务，拥有完善的卫星设计与制造条件保障资源。</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>军工, 商业航天</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>MLCC</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>1.4749</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>MLCC龙头村田制作所日前正式发布官方通知，宣布在2026会计年度启动产品线优化，将停产部分MLCC产品并扩充其他产能。</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>sz002585</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>双星新材</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>10.0552</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>MLCC离型膜|公司的MLCC离型膜产品涵盖中高低端产品，2026年MLCC项目5亿平米全面建成并投产。</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>MLCC离型膜</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>MLCC</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>1.4749</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>MLCC龙头村田制作所日前正式发布官方通知，宣布在2026会计年度启动产品线优化，将停产部分MLCC产品并扩充其他产能。</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>sz000636</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>风华高科</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>55.99</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>MLCC|公司系国内MLCC龙头生产商，拥有完整的从材料、工艺到产品大规模研发制造的产品链。</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>MLCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>光纤光缆</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>0.5819000000000001</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>康宁在宣布向Zayo供应数据中心互联光纤的长期协议后，紧接着与Verizon签下了一份价值数十亿美元的供应协议，将在2032年前提供超过8000万英里高密度光纤。</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>sh603938</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>三孚股份</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>49.56</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>10.0111</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>二氯二氢硅+光纤|1.公司电子特气产品为电子级二氯二氢硅、电子级三氯氢硅、电子级四氯化硅，下游主要应用于先进晶圆加工，存储芯片制造，硅外延片制造，已实现向部分国内龙头存储厂商、逻辑芯片Fab厂商批量稳定供应。
-2.公司高纯四氯化硅产品下游主要用于生产光纤预制棒及人造石英，主要客户有：中天科技、长飞光纤光缆等。</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>二氯二氢硅, 光纤</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.5819000000000001</v>
+        <v>0.7676999999999999</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>康宁在宣布向Zayo供应数据中心互联光纤的长期协议后，紧接着与Verizon签下了一份价值数十亿美元的供应协议，将在2032年前提供超过8000万英里高密度光纤。</t>
+          <t>中国电信研究院行业与企业战略研究所所长饶少阳称，从算力需求来看，智能体的爆发将带动我国算力需求持续高速增长，预计未来2～3年，我国算力需求平均每年将增长近10倍。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh600184</t>
+          <t>sh605168</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>光电股份</t>
+          <t xml:space="preserve">三人行  </t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>19.98</v>
+        <v>50.11</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10.022</v>
+        <v>10.011</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>GP材料+光纤皮料管|1.子公司新华光自主研发的光通信核心材料GP，突破了批量生产工艺，已经送样给光通信领域多家企业测试使用。
-2.子公司新华光研发生产的光纤皮料管，在产品质量与核心性能方面满足客户要求，实现批量生产。</t>
+          <t>AI应用+算力租赁|1.在AI营销领域的应用方面，公司持续迭代优化营销领域多模态AI产品，成功构建 “一个”AI全链路营销智能体，逐步实现从策略生成、内容创作、智能投放到效果归因的全链路营销自动化闭环。
+2.公司设立子公司青海三人行绿能智算科技有限公司，从事算力租赁、算力解决方案服务等综合性算力服务业务。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>GP材料, 光纤皮料管</t>
+          <t>AI应用, 算力租赁</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-0.5483</v>
+        <v>0.7676999999999999</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>第27届光博会将于9月9日-9月11日在深圳召开，本届展会聚焦算力集群规模扩张驱动的光互联架构升级，NPO、CPO与OCS等颠覆性架构的工程化进展成为核心看点。</t>
+          <t>中国电信研究院行业与企业战略研究所所长饶少阳称，从算力需求来看，智能体的爆发将带动我国算力需求持续高速增长，预计未来2～3年，我国算力需求平均每年将增长近10倍。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz002161</t>
+          <t>sh600228</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>远 望 谷</t>
+          <t>返利科技</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>9.9863</v>
+        <v>9.9895</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>并购重组+光通信|远望谷公告称，公司与深圳光泰通信设备有限公司及其股东签订股权投资意向书，拟收购光泰通信100%股权。标的公司主要业务包括为客户提供光通信器件与模块的自动化耦合设备和测试仪表、自动化测试解决方案。</t>
+          <t>AI+电商|公司基于人工智能技术开发了电商导购APP“如意”，可通过AI对话的交互方式为用户提供购物问答、建议清单、全网比价、评价提炼、评测聚合等网购服务。“如意”APP已获发第四批生成式人工智能（大模型）备案号告知书。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 光通信</t>
+          <t>AI, 电商</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-0.5483</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>第27届光博会将于9月9日-9月11日在深圳召开，本届展会聚焦算力集群规模扩张驱动的光互联架构升级，NPO、CPO与OCS等颠覆性架构的工程化进展成为核心看点。</t>
+          <t>随着算力芯片出货量提升、算力集群规模化部署，先进制程、先进封装带来的增量需求，持续向上游设备材料环节传导。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz002902</t>
+          <t>sh688835</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>铭普光磁</t>
+          <t>高凯技术</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30.86</v>
+        <v>324.41</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.0178</v>
+        <v>20.0007</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>光模块+储能|1.铭普光磁在互动平台表示，公司持续开展光模块产品的研发与迭代，目前200G及以下速率光模块正常供货。800G LPO（线性驱动可插拔光模块）方案的ODM定制开发，已实现小批量出货，但整体订单量较小，产生的利润不足以实质性影响公司的整体业绩方向。
-2.2022年5月31日公司在互动平台表示，公司目前生产的用于光伏领域的主要有光伏逆变器用电抗器、高频变压器和电感器，及通信局站用光伏供电系统。</t>
+          <t>半导体设备|公司是国内极少数已批量应用于7nm及以下制程的设备零部件供应商，如某系列刻蚀设备，最高可应用于5nm制程工艺，多款产品为解决半导体设备流体控制领域的“卡脖子”难题提供了有力支撑。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>光模块, 储能</t>
+          <t>半导体设备</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-1.6418</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>中信证券研报称，玻璃基板有望成为解决当前先进封装大尺寸化、高密高速升级、产出效率等瓶颈的重要工艺，有望进入加速成熟阶段。</t>
+          <t>随着算力芯片出货量提升、算力集群规模化部署，先进制程、先进封装带来的增量需求，持续向上游设备材料环节传导。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh600876</t>
+          <t>sz002346</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>凯盛新能</t>
+          <t>柘中股份</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>19.82</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.987400000000001</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.988900000000001</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板|公司是国内最早开始研发并商业化生产超薄浮法玻璃产品的企业，在十余年的超薄玻璃基板生产经营中积累了丰富的知识体系与工艺经验。</t>
+          <t>电网设备+半导体|1.公司主营的成套输配电设备属通用配电设备，是数据中心建设中比较重要的基础设备。
+2.公司参股瀚天天成，后者是全球领先的宽禁带半导体(第三代半导体)外延晶片提供商，于2024年6月7日终止科创板IPO。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>电网设备, 半导体</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-1.6418</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>中信证券研报称，玻璃基板有望成为解决当前先进封装大尺寸化、高密高速升级、产出效率等瓶颈的重要工艺，有望进入加速成熟阶段。</t>
+          <t>随着算力芯片出货量提升、算力集群规模化部署，先进制程、先进封装带来的增量需求，持续向上游设备材料环节传导。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh600207</t>
+          <t>sz002918</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>安彩高科</t>
+          <t>蒙娜丽莎</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>4.94</v>
+        <v>11.7</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.0223</v>
+        <v>9.962400000000001</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板|公司打破日本旭硝子的技术垄断，自研生产出了3mm、4mm光热超白浮法玻璃基板，全光谱透过率达到91%以上，同时积极布局光热玻璃基板企业认证， 目前已获得国内外多家企业认可。</t>
+          <t>陶瓷基板|旗下珠海晶瓷电子科技有限公司经营范围包括半导体分立器件制造、半导体器件专用设备制造、特种陶瓷制品制造等，拥有“一种陶瓷基板钻孔加工方法”的专利。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>陶瓷基板</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
+          <t>液冷IDC</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>0.6329</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>浙商证券研报指出，第三季度是液冷行业从试点走向批量交付、业绩集中兑现的关键拐点，以英伟达VR200机柜规模化出货为核心驱动。</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz002790</t>
+          <t>sh603090</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>瑞尔特</t>
+          <t>宏盛股份</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>9.31</v>
+        <v>36.55</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.0473</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>9.991</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>卫浴产品|公司致力于节约全球水资源的卫浴产品的研发、生产与销售，产品涵盖节水型冲水组件、智能座便器、静音缓降盖板、隐藏式水箱、挂式水箱等。</t>
+          <t>液冷|公司掌握液冷散热技术，能够为多种场景提供解决方案，同时，公司与苏州和信精密科技股份有限公司合资成立了无锡和宏智散热科技有限公司，和信精密是行业内领先的数据中心设备供应商，双方通过设立合资公司的形式，拓展数据中心环境温度控制业务。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>卫浴产品</t>
+          <t>液冷</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
+          <t>液冷IDC</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>0.6329</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>浙商证券研报指出，第三季度是液冷行业从试点走向批量交付、业绩集中兑现的关键拐点，以英伟达VR200机柜规模化出货为核心驱动。</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>sh603400</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">华之杰  </t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="H33" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>sh603421</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>鼎信通讯</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>10.0137</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>半导体+电网设备|1.鼎信通讯在互动平台表示，公司芯片开发采用平头哥的CK802 32位内核架构，平头哥与公司签订有全面技术授权协议。
-2.公司的主营业务为低压用电系统产品的研发、生产、销售及服务，主要产品包括低压电力线载波通信模块（含芯片）产品、采集终端设备、智能电能表和配电终端等，主要应用于国家智能电网的用电信息采集系统和配网自动化系统。</t>
+          <t>机器人+液冷|1.旗下苏州康阳机器人有限公司已设立完成并取得营业执照，持续围绕“电驱、电控、电池管理”开展技术创新和产品布局，实现公司在具身智能机器人领域的产业化布局。
+2.公司的电子水泵产品广泛应用于储能、电动汽车及数据中心液冷系统，通过精准流量控制与高可靠性设计，保障系统稳定高效运行。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>半导体, 电网设备</t>
+          <t>机器人, 液冷</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
+          <t>液冷IDC</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>0.6329</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>浙商证券研报指出，第三季度是液冷行业从试点走向批量交付、业绩集中兑现的关键拐点，以英伟达VR200机柜规模化出货为核心驱动。</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>sz002897</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>意华股份</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>71.39</v>
+      </c>
+      <c r="H34" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>sz000980</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>众泰汽车</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>9.8446</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>汽车整车|公司是国内较早进入新能源汽车领域的车企，已具备新能源汽车完整的整车设计、试制、试验和零部件开发能力。</t>
+          <t>光通信+液冷|1.公司是国内少数具备高速连接器量产能力的企业之一，以SFP、SFP+光电连接器为代表产品，与华为、中兴等优质客户建立长期合作关系，已开发800G高速连接器进入小批量试用阶段；子公司武汉意谷光电布局光模块，覆盖速率范围1G-400Gbps，800G正在设计开发。
+2.公司在研的液冷产品，主要用于对连接器和光模块信号传递接触面进行散热处理。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>汽车整车</t>
+          <t>光通信, 液冷</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr"/>
+          <t>超硬材料</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>3.5621</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>机构研报指出，金刚石铜凭借热导率、成本与热膨胀匹配三重优势有望率先实现规模化应用。</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz002201</t>
+          <t>sh605580</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>九鼎新材</t>
+          <t>恒盛能源</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>11.09</v>
+        <v>23.6</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.0198</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0233</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>玻纤|作为全球最大的玻纤制砂轮增强片供应商、国家航空航天特种玻纤布定点企业，公司一直承载着为运载火箭和航天飞船提供特种材料的使命。</t>
+          <t>电力+金刚石|1.公司主营业务为蒸汽的生产和供应、电力的生产和销售，是以煤炭和生物质作为燃料，通过热电联产方式生产蒸汽和电力。
+2.公司旗下桦茂科技专注于MPCVD（微波等离子体化学气相沉积）法生长金刚石技术的研发与产业化，已形成覆盖CVD设备制造、金刚石生长及加工的全产业链布局，成为行业少数具备规模化生产高品质单晶与多晶金刚石能力的企业。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>玻纤</t>
+          <t>电力, 金刚石</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr"/>
+          <t>超硬材料</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>3.5621</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>机构研报指出，金刚石铜凭借热导率、成本与热膨胀匹配三重优势有望率先实现规模化应用。</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh605088</t>
+          <t>sh600172</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>冠盛股份</t>
+          <t>黄河旋风</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>22.48</v>
+        <v>16.53</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.980399999999999</v>
+        <v>9.98</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>机器人+固态电池|冠盛股份发布投资者关系活动记录表公告称，冠盛东驰团队目前正与机器人领域的相关企业进行了初步业务洽谈对接。机器人和低空飞行器均为固态电池重要的应用场景，目前公司动力电池仍处于小试研发阶段，未来公司会积极布局并及时公告进展。</t>
+          <t>金刚石散热|从许昌市工业和信息化局获悉，河南黄河旋风股份有限公司自主研发的“金刚石—碳化硅复合材料”项目取得重大阶段性成果，核心性能指标达到国际先进水平，成功破解了长期困扰半导体产业的热膨胀失配难题，为我国高端半导体散热技术自主可控提供了关键支撑。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>机器人, 固态电池</t>
+          <t>金刚石散热</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
+          <t>MLCC</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>3.3986</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>村田正式公告停产部分MLCC料号，向客户发布"产品线优化"通知，宣布在2026会计年度启动部分 MLCC 产品停产与产能调整，同时扩充其他产能。</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh601199</t>
+          <t>sz002585</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>江南水务</t>
+          <t>双星新材</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>6.47</v>
+        <v>10.96</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.034</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+        <v>10.0402</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>水务|公司从事的主要业务为自来水业务、工程业务和污水处理业务。</t>
+          <t>MLCC离型膜|公司的MLCC离型膜产品涵盖中高低端产品，2026年MLCC项目5亿平米全面建成并投产。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>MLCC离型膜</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
+          <t>MLCC</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>3.3986</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>村田正式公告停产部分MLCC料号，向客户发布"产品线优化"通知，宣布在2026会计年度启动部分 MLCC 产品停产与产能调整，同时扩充其他产能。</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>sz002669</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>康达新材</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H38" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>sh603336</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>宏辉果蔬</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>10.0327</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>果蔬+创新药|1.公司是一家集果蔬产品的种植管理、采后收购、产地预冷、冷冻仓储、预选分级、加工包装、冷链配送于一体的专业生鲜产品服务商。
-2.2026年4月28日公告，公司拟使用自有及自筹资金约7亿元收购江西施美药业股份有限公司41.128%股份。施美药业是一家致力于复方降压、降脂、降糖药和心脑血管药的现代化高科技创新型制药企业，已建成成熟的生产与经营体系，主营产品涵盖化学原料药及片剂、胶囊等主流制剂。</t>
+          <t>PCB+MLCC|1.子公司康成达创（上海）新材料有限公司主要就电子级双马来酰亚胺树脂应用于高速覆铜板、BT载板等领域开展技术测试、中试生产等相关工作。
+2.公司参股企业成都铭瓷主要产品系列包括片式多层陶瓷电容器、钽电容器等。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>果蔬, 创新药</t>
+          <t>PCB, MLCC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
+          <t>烟草</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>2026年7月28日国家烟草专卖局发布《加热卷烟》强制性国标征求意见稿，意见反馈截止9月26日。标准对烟碱释放、烟具安全、防护机制设立强制指标。</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh603136</t>
+          <t>sh603020</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">天目湖  </t>
+          <t>爱普股份</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>10.58</v>
+        <v>11.17</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>9.979200000000001</v>
+        <v>10.0493</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>旅游|主要从事旅游景区的开发管理和经营。公司经营旅行社/景区/酒店/温泉等多种业态形成一站式目的地，全面满足游客的“体验型旅行”需求。</t>
+          <t>烟草香精|公司系国内香料香精行业龙头，产品广泛应用于食品、饮料、卷烟、日化等多个领域。公司于2019年6月在互动平台确认，公司有生产销售烟草用香精。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>旅游</t>
+          <t>烟草香精</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
+          <t>烟草</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>2026年7月28日国家烟草专卖局发布《加热卷烟》强制性国标征求意见稿，意见反馈截止9月26日。标准对烟碱释放、烟具安全、防护机制设立强制指标。</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh600237</t>
+          <t>sz000812</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>铜峰电子</t>
+          <t>陕西金叶</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>9.220000000000001</v>
+        <v>4.14</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10.0239</v>
+        <v>10.1064</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>薄膜电容器|公司主营业务为薄膜电容器及其薄膜材料的研发、生产和销售，具备行业特有的电容器用聚丙烯光膜—金属化薄膜—薄膜电容器上下游一体化产业链，产品涵盖聚丙烯薄膜、聚酯薄膜、金属化薄膜、电容器等众多品种。</t>
+          <t>烟草|主营涵盖烟草配套产业、教育产业、房地产业。烟草配套产业主要产品为烟标、烟用丝束、咀棒的生产销售；教育产业主要业务为高等学历教育及其他教育教学，互联网智慧校园和教育投资业务。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>薄膜电容器</t>
+          <t>烟草</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>0.6314</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>此次光博会，“1.6T”已完全站上了“C位”，成为几乎从模块到引擎、芯片，再到解调器、光纤、材料、测试设备等产业链各个环节的“必展亮点”。</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh603439</t>
+          <t>sh600330</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>三力制药</t>
+          <t>天通股份</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>12.54</v>
+        <v>30.23</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10</v>
+        <v>10.0073</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司联合控股子公司云南无敌与贵阳工业发展基金等专业投资机构设立黔力生物医药基金，基金总规模5亿元，将重点关注生物科技与健康管理赛道的股权投资项目，该基金通过"产业洞察+资本赋能"双驱动模式，截止2024年年报，已储备十多个创新药标的，其中已有多个产品进入III期临床试验阶段。</t>
+          <t>铌酸锂单晶材料|2023年6月9日公司在互动平台表示，国内多家厂商已经发布数通800G薄膜铌酸锂方案的光模块，公司生产的铌酸锂单晶材料是薄膜铌酸锂调制器的上游关键原材料。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>铌酸锂单晶材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>0.6314</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>此次光博会，“1.6T”已完全站上了“C位”，成为几乎从模块到引擎、芯片，再到解调器、光纤、材料、测试设备等产业链各个环节的“必展亮点”。</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>sz002976</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>瑞玛精密</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>10.0086</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>汽车+光通信|1.1.公司在汽车电子领域的布局主要是自动驾驶系统及智能座舱系统。
+2.公司借助通信领域（诺基亚、爱立信）、电子电气领域（施耐德）等战略性国际客户资源，逐步切入移动通信、光通信散热与热管理业务。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>汽车, 光通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>9月11日国常会提出，进一步完善算力基础设施，构建多层次网络化算力体系，加快绿电直连、源网荷储等项目落地。</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>sz000993</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>闽东电力</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>10.0144</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>绿电|公司致力于清洁能源、新能源等领域的发展。发电业务是公司业务的核心业务，主要包括水力发电和风力发电。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>绿电</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>9月11日国常会提出，进一步完善算力基础设施，构建多层次网络化算力体系，加快绿电直连、源网荷储等项目落地。</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>sz001896</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>豫能控股</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>9.9915</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>电力+算力|1.公司是河南省内唯一省级资本控股的电力上市公司，从事的主要业务包括，火电项目的投资管理、能源销售、新能源项目投资建设等。
+2.豫能控股早间公告，公司正在筹划参股投资公司控股股东河南投资集团下属控股企业先天算力（河南）科技有限公司，并联合河南投资集团以先天算力为收购主体，收购郑州合盈数据有限责任公司控股权相关事项。此次参股投资事项尚处筹划阶段，存在较大不确定性。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>电力, 算力</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>旅游酒店</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>-1.2153</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>广西壮族自治区人民政府办公厅关于印发《旅游强区建设“十五五”规划》。到2030年，旅游强区建设取得显著进展，旅游消费水平有效提升，稳步推进从观光旅游目的地向休闲度假目的地转型升级。</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>sz000978</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>桂林旅游</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>10.0304</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>6天5板</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>旅游+AI|1.主营业务包括:游船客运、景区旅游业务、酒店、公路旅行客运、出租车业务等。
+2.子公司一城游公司旗下“桂林一城游”平台接入DeepSeek大模型，推出“桂林旅游AI小助手”，开启“智能+文旅”深度融合的全新阶段。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>旅游, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>旅游酒店</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>-1.2153</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>广西壮族自治区人民政府办公厅关于印发《旅游强区建设“十五五”规划》。到2030年，旅游强区建设取得显著进展，旅游消费水平有效提升，稳步推进从观光旅游目的地向休闲度假目的地转型升级。</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>sh600697</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>欧亚集团</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>10.0452</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>零售+旅游|1.公司为商贸企业，全渠道营销，以实体零售经营为主，覆盖现代百货、商业综合体、商超连锁等业态模式，形成了不同发展阶段的门店梯次。
+2.长春欧亚神龙湾旅游有限责任公司是公司控股子公司长春欧亚卖场有限责任公司参股的联营企业，其经营范围为：旅游项目及旅游纪念品和旅游环保产品的开发；旅游基础设施建设和经营。</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>零售, 旅游</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>玻璃基板</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>华泰证券研报称，大尺寸、高密度封装升级为玻璃基板打开新应用空间，量产能力将决定产业化节奏。</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>sh600876</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>凯盛新能</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>玻璃基板|公司是国内最早开始研发并商业化生产超薄浮法玻璃产品的企业，在十余年的超薄玻璃基板生产经营中积累了丰富的知识体系与工艺经验。</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>玻璃基板</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>0.7957000000000001</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>9月12日，柳州优必选万台级工业人形机器人超级智慧工厂投产仪式举行，“用机器人造机器人”的智造模式在柳州实现量产。</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>sh603626</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>科森科技</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>9.9779</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>机器人+固态电池|1.公司不生产机器人产品，公司为某品牌家用机器人提供相关结构件。
+2.公司持有固态电池生产、研发企业清陶能源部分股权，同时作为清陶能源供应商，公司为清陶能源及其控制的公司提供电池周边结构件产品。此外，公司与清陶成立合资公司科森清陶，以科森清陶为载体，在固态电池等领域开展相关业务合作。</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 固态电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>sz300430</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>*ST益通</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司在脑机接口业务方向布局主要分为非侵入式和侵入式，在非侵入式方面，主要致力于将脑机接口技术与龙之杰现有康复产品进行融合，实现现有康复产品的功能升级；在侵入式方面，正在积极推进脑连科技脑连科技与大兴医药基地管委会联合成立的“脑机接口植入式生物实验室”项目落地。</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>sz002560</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>通达股份</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>10.0291</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>电网设备+军工|1.1.公司从事的主要业务包括电线电缆生产、销售及航空零部件加工两大板块。
+2.公司全资子公司成都航飞主要从事飞机结构零部件的高端精密加工制造服务，产品包括机体钛合金、铝合金框、梁、肋、接头等数控加工件，钣金成型模具、复合材料成型模具，产品覆盖多款主要军用机型以及中国商飞C919等民用机型。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>电网设备, 军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>sh603657</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>春光科技</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>9.986000000000001</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>家电|公司主营业务为吸尘器零件、橡塑软管、塑料制品、小家电的研发、制造和销售及自营进出口业务。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>家电</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>sh601123</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>马矿股份</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>10.0262</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>次新+铁矿|公司是一家长期从事铁矿资源开发及综合利用的企业，主营铁矿石的采选、综合利用及铁精粉、钼精矿销售，石灰石的开采和销售。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>次新, 铁矿</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sh601567</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>三星电气</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>10.0155</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>智能电网|公司主营业务为电能计量及信息采集产品、配电设备的研发、生产和销售。公司主要产品均面向电力系统用户销售，消费群体包括国家电网公司、南方电网公司等电力系统用户。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>sh603285</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>键邦股份</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>9.994400000000001</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>赛克产品|公司赛克产品行业领先，2026年1月，旗下艾伦塔斯集团在铜陵计划扩产年产16 万吨绝缘材料项目，一期投产后可形成13 万吨绝缘材料的生产能力。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>赛克产品</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sz000962</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>东方钽业</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>10.002</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>钽电容器|公司主导产品电容器级钽粉国际市场占有率25%以上、钽电容器阳极引线用钽丝国际市场占有率35%以上。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>钽电容器</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>sh600802</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>9.9437</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>水泥|公司是福建地区产能规模最大的水泥制造企业，也是福建省水泥行业唯一的一家上市公司。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>水泥</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>sh601086</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>国芳集团</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>10.0306</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>零售|公司从事以百货业为主，超市、电器为辅的连锁零售业务，是甘肃省内最大的连锁零售企业。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>零售</t>
         </is>
       </c>
     </row>
@@ -2391,7 +3127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2422,12 +3158,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sz002790</t>
+          <t>sz000993</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>瑞尔特</t>
+          <t>闽东电力</t>
         </is>
       </c>
     </row>
@@ -2437,12 +3173,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz000993</t>
+          <t>sz000823</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>闽东电力</t>
+          <t>超声电子</t>
         </is>
       </c>
     </row>
@@ -2452,27 +3188,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh603421</t>
+          <t>sz002912</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>鼎信通讯</t>
+          <t>中新赛克</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002201</t>
+          <t>sh600876</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>九鼎新材</t>
+          <t>凯盛新能</t>
         </is>
       </c>
     </row>
@@ -2482,12 +3218,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz000823</t>
+          <t>sz000980</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>众泰汽车</t>
         </is>
       </c>
     </row>
@@ -2497,12 +3233,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz002912</t>
+          <t>sh600088</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>中视传媒</t>
         </is>
       </c>
     </row>
@@ -2512,12 +3248,72 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh600876</t>
+          <t>sh605058</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>凯盛新能</t>
+          <t>澳弘电子</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>sh605069</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>正和生态</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>sh603439</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>三力制药</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>sz002560</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>通达股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>sz002585</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>双星新材</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,20 +476,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="104" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="206" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="247" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,2233 +552,3608 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.3831</v>
+        <v>2.7686</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>记者了解到，9月20日，上纬新材旗下消费级具身智能品牌启元机器人将在上海举办新品发布会。期间，启元Q1、启元T1两款机器人将正式亮相。</t>
+          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh603626</t>
+          <t>sz002453</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>科森科技</t>
+          <t>华软科技</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>21.29</v>
+        <v>5.34</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.0258</v>
+        <v>10.1031</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>机器人+消费电子|1.公司不生产机器人产品，公司为某品牌家用机器人提供相关结构件。
-2.公司消费电子产品包括智能手机、笔记本电脑、平板电脑的外壳、中框、中板、按键、标志、转轴（铰链）等。</t>
+          <t>光刻胶基材|关于公司相关的光刻胶基材产品业务，目前正处于客户接洽阶段，已有少量试订单。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>机器人, 消费电子</t>
+          <t>光刻胶基材</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.3831</v>
+        <v>2.7686</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>记者了解到，9月20日，上纬新材旗下消费级具身智能品牌启元机器人将在上海举办新品发布会。期间，启元Q1、启元T1两款机器人将正式亮相。</t>
+          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh605288</t>
+          <t>sh603353</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>凯迪股份</t>
+          <t>和顺石油</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>67.25</v>
+        <v>48.55</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.993499999999999</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+        <v>9.9909</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司主要产品为线性驱动系统，可以应用在机器人上。</t>
+          <t>石油+先进封装|1.公司是湖南省第一家获国家商务部批准取得成品油批发资质的民营石油企业，主营成品油批发零售，业务涵盖成品油采购、仓储、物流、批发、零售环节，在成品油流通领域形成完整产业链。
+2.2025年11月16日晚公告，公司拟以现金收购及增资方式取得上海奎芯集成电路设计有限公司不低于34%股权并通过表决权委托合计控制其51%表决权，交易完成后奎芯科技将纳入合并报表，布局高速接口IP及Chiplet解决方案。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>石油, 先进封装</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.3831</v>
+        <v>2.7686</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>记者了解到，9月20日，上纬新材旗下消费级具身智能品牌启元机器人将在上海举办新品发布会。期间，启元Q1、启元T1两款机器人将正式亮相。</t>
+          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh605088</t>
+          <t>sh603120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>冠盛股份</t>
+          <t>肯特催化</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>24.17</v>
+        <v>59.21</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.0137</v>
+        <v>9.994400000000001</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>机器人+固态电池|冠盛股份发布投资者关系活动记录表公告称，冠盛东驰团队目前正与机器人领域的相关企业进行了初步业务洽谈对接。机器人和低空飞行器均为固态电池重要的应用场景，目前公司动力电池仍处于小试研发阶段，未来公司会积极布局并及时公告进展。</t>
+          <t>光刻胶显影液|公司的电子级季铵碱可应用于光刻胶显影液等湿电子化学品。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>机器人, 固态电池</t>
+          <t>光刻胶显影液</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.3831</v>
+        <v>2.7686</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>记者了解到，9月20日，上纬新材旗下消费级具身智能品牌启元机器人将在上海举办新品发布会。期间，启元Q1、启元T1两款机器人将正式亮相。</t>
+          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh600699</t>
+          <t>sh603068</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>均胜电子</t>
+          <t>博通集成</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>19.87</v>
+        <v>39.81</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.0221</v>
+        <v>10.0028</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>机器人+智能驾驶|1.公司定位“汽车+机器人Tier1”，全面布局人形机器人领域，向包括全球车企在内的具身智能机器人相关公司提供软硬件及解决方案。
-2.公司与大唐集团旗下的辰芯科技签署战略合作协议，联手发力汽车智能车联技术，打造新一代TBOX和V2X车用电子产品。</t>
+          <t>端侧AI芯片|公司依托在AI无线通信的经验和技术积累，将研发资源拓展至端侧AI算力。公司发布的BK7259作为AIoT算力标杆，率先集成ARM Ethos-U65 microNPU的Wi-Fi 6 MCU，为边缘智能应用注入超强算力与卓越能效。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>机器人, 智能驾驶</t>
+          <t>端侧AI芯片</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.3831</v>
+        <v>2.7686</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>记者了解到，9月20日，上纬新材旗下消费级具身智能品牌启元机器人将在上海举办新品发布会。期间，启元Q1、启元T1两款机器人将正式亮相。</t>
+          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh603009</t>
+          <t>sh603316</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>北特科技</t>
+          <t>诚邦股份</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>47.37</v>
+        <v>16.69</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.0093</v>
+        <v>10.0198</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">机器人|2024年10月14日公告，公司当日与江苏昆山经济技术开发区管理委员会签订投资协议。公司拟在江苏昆山经济技术开发区总投资18.5亿元，规划用地约140亩，建设行星滚柱丝杠研发生产基地项目。公司将切入到机器人相关领域，此次投资建设行星滚柱丝杠研发生产基地项目，可将公司布局的机器人相关技术和产品落地并实现商业化、规模化生产，为公司未来发展奠定坚实基础。 </t>
+          <t>存储芯片|公司旗下芯存科技主要从事半导体存储器的研发设计、封装测试、生产和销售，已量产并销售的主要产品为移动存储（包括TFCARD、USB模块等）、固态硬盘（包括SATASSD、PCIESSD、PSSD）等。芯存科技整合了包括芯源科技在内的相关业务资源，致力于构筑芯片封测、存储模组产品研发生产一体化的经营模式，布局嵌入式存储、内存条等产品，打造完善的闪存存储产品矩阵，在存储介质特性研究、固件算法开发、存储芯片封测、测试研发等方面打造综合竞争力。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>存储芯片</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.3831</v>
+        <v>2.7686</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>记者了解到，9月20日，上纬新材旗下消费级具身智能品牌启元机器人将在上海举办新品发布会。期间，启元Q1、启元T1两款机器人将正式亮相。</t>
+          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh603960</t>
+          <t>sz002185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>克来机电</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>17</v>
+        <v>18.03</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.0324</v>
+        <v>10.0061</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>机器人+光通信|1.公司是柔性自动化装备与工业机器人系统应用供应商，致力于现代机电智能装备、工业机器人系统集成的研究、开发、制造。公司的产品可分为柔性自动化生产线与工业机器人系统应用两大类。
-2.在光通信领域，公司成功开发了光纤收发器柔性自动化装配测试单元，已供货至全球光通讯器件著名生产商Finisar。</t>
+          <t>先进封装|公司的主营业务为集成电路封装测试，产品主要有DIP/SDIP、SOT、SOP、SSOP、TSSOP/ETSSOP、QFP/LQFP/TQFP、QFN/DFN、BGA/LGA、FC、MCM（MCP）、SiP、WLP、TSV、Bumping、MEMS、Fan-Out等多个系列。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>机器人, 光通信</t>
+          <t>先进封装</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.6026</v>
+        <v>2.7686</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>近日中央网信办、农业农村部、工业和信息化部联合印发《数字乡村高质量发展行动计划（2026—2030年）》，其中提到，强化农业科技创新。加强智慧农业创新载体建设。</t>
+          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh600371</t>
+          <t>sh601026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>万向德农</t>
+          <t>道生天合</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15.64</v>
+        <v>15.95</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.985900000000001</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>农业种植|公司从事的主要业务为玉米杂交种子研发、生产、销售，主营包括但不限于“京科968”、“德单系列”等玉米杂交种的生产与销售。</t>
+          <t>半导体材料+次新|参股上海道宜半导体材料有限公司主营业务为环氧塑封材料（EMC），该产品属于半导体传统封装环节的常规材料。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>半导体材料, 次新</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1.6026</v>
+        <v>2.7686</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>近日中央网信办、农业农村部、工业和信息化部联合印发《数字乡村高质量发展行动计划（2026—2030年）》，其中提到，强化农业科技创新。加强智慧农业创新载体建设。</t>
+          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh600127</t>
+          <t>sz001399</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>惠科股份</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>13.02</v>
+        <v>23.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9.966200000000001</v>
+        <v>10.019</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>大米|公司是我国粮食系统的第一家上市公司，是首批农业产业化国家重点龙头企业，国家水稻工程优质米示范基地。公司以优质粮油、新型健康食品和药品开发、生产、销售为发展方向，坚持农、工、科、贸一体化的现代农业产业化经营模式，主要产品有大米、面粉、面条、植物油、米粉、牛奶、糖果、果冻、药品等。</t>
+          <t>先进封装|2026年7月17日公告，公司与杭绍临空经济一体化发展示范区绍兴片区管理委员会就开展惠科先进封装及测试项目签署《先进封装及测试项目合作协议》，出资40亿元设立全资子公司浙江惠芯先进半导体有限公司（暂定名）作为项目实施主体。项目分二期建设，其中项目一期计划建设12寸混合芯片先进封装及测试，全部达产后，达到2000万颗/月产能，预计项目建设周期不超过三年。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>大米</t>
+          <t>先进封装</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1.6026</v>
+        <v>2.7686</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>近日中央网信办、农业农村部、工业和信息化部联合印发《数字乡村高质量发展行动计划（2026—2030年）》，其中提到，强化农业科技创新。加强智慧农业创新载体建设。</t>
+          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh600354</t>
+          <t>sh601133</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>敦煌种业</t>
+          <t>柏诚股份</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>9.75</v>
+        <v>26</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.0451</v>
+        <v>9.9831</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>种业|公司目前主要从事各类农作物种子的研发、生产、加工、销售和脱水菜、番茄粉、番茄酱、啤酒花制品的加工、销售以及棉花及其副产品的收购、加工、仓储、贸易。</t>
+          <t>洁净室系统集成|公司主要专注于为高科技产业的建厂、技改等项目提供专业的洁净室系统集成整体解决方案，覆盖半导体及泛半导体、新型显示、生命科学、食品药品大健康等国家重点产业。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>种业</t>
+          <t>洁净室系统集成</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1.6026</v>
+        <v>2.7686</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>近日中央网信办、农业农村部、工业和信息化部联合印发《数字乡村高质量发展行动计划（2026—2030年）》，其中提到，强化农业科技创新。加强智慧农业创新载体建设。</t>
+          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz002321</t>
+          <t>sz002971</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>华英农业</t>
+          <t>和远气体</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2.18</v>
+        <v>42.68</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10.101</v>
+        <v>10</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>鸭/鸡养殖|主营业务为种鸭/鸡养殖、孵化、禽苗销售、饲料生产、商品鸭/鸡屠宰加工、冻品销售、熟食、羽绒及羽绒制品生产和销售。</t>
+          <t>电子特气|公司电子特气产品涵盖了硅基、氟基、氨基、氯基、碳基五大系列，主要产品有电子级三氟化氮、六氟化钨、三氯氢硅、二氯二氢硅、四氯化硅、正硅酸乙酯、硅烷、乙硅烷，电子级超纯氨、电子级氯化氢、电子级氯气、电子级甲烷、电子级一氧化碳、高纯羰基硫等，产品广泛应用于集成电路、显示面板、LED、光伏、光纤、动力电池、人工智能等新兴产业。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>鸭/鸡养殖</t>
+          <t>电子特气</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.4524</v>
+        <v>2.7686</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>广汽集团公告，筹划发行股份购买一汽股份持有的某整车合资公司部分股权。</t>
+          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz000980</t>
+          <t>sz301583</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>托伦斯</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2.37</v>
+        <v>142.56</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.2326</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8天5板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>汽车整车|公司是国内较早进入新能源汽车领域的车企，已具备新能源汽车完整的整车设计、试制、试验和零部件开发能力。</t>
+          <t>次新+半导体设备|托伦斯是国内领先的精密金属零部件综合服务商，专注于半导体设备关键工艺零部件的研发、生产和销售，产品覆盖薄膜沉积、刻蚀设备等核心半导体设备，包括腔体、内衬、加热器、匀气盘、静电卡盘基体等关键零部件。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>汽车整车</t>
+          <t>次新, 半导体设备</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.4524</v>
+        <v>2.7686</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>广汽集团公告，筹划发行股份购买一汽股份持有的某整车合资公司部分股权。</t>
+          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz000868</t>
+          <t>sh603375</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>安凯客车</t>
+          <t xml:space="preserve">盛景微  </t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4.06</v>
+        <v>51.69</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.0271</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.0021</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>客车整车|公司是国内较早研发和批量生产运营新能源客车的整车企业，已形成集10-12米纯电动公交客车，12米纯电动旅游和通勤客车、12米增程式电动公交客车、10-12米油电混合动力城市客车于一体的产品平台。</t>
+          <t>民爆+芯片|公司是一家具备高性能、超低功耗芯片设计能力的电子器件提供商，主要产品为工业安全领域的电子控制模块。公司销售的产品包括电子控制模块、起爆控制器、放大器等。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>客车整车</t>
+          <t>民爆, 芯片</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.4524</v>
+        <v>2.5704</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>广汽集团公告，筹划发行股份购买一汽股份持有的某整车合资公司部分股权。</t>
+          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz000981</t>
+          <t>sz002161</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>山子高科</t>
+          <t>远 望 谷</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3.01</v>
+        <v>7.25</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>9.854000000000001</v>
+        <v>10.0152</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>6天3板</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>哪吒汽车重整概念|9月11日，合众新能源（哪吒汽车母公司）破产重整案第四次债权人会议以线上形式召开，《重整计划（草案）》显示，浙江太乙圣莲企业管理合伙企业（有限合伙）拟出资30亿元入主，“太乙圣莲”注册成立于2026年4月，由浙江山子控股有限公司和浙江山子玉虚科技有限公司两家公司合伙组建，前者实控人为深交所上市公司山子高科董事长叶骥，后者实控人为山子高科董办负责人虞舒心。</t>
+          <t>光通信测试|远望谷公告称，公司与深圳光泰通信设备有限公司及其股东签订股权投资意向书，拟收购光泰通信100%股权。标的公司主要业务包括为客户提供光通信器件与模块的自动化耦合设备和测试仪表、自动化测试解决方案。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>哪吒汽车重整概念</t>
+          <t>光通信测试</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.4524</v>
+        <v>2.5704</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>广汽集团公告，筹划发行股份购买一汽股份持有的某整车合资公司部分股权。</t>
+          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh600609</t>
+          <t>sh603725</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>金杯汽车</t>
+          <t>天安新材</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>3.58</v>
+        <v>11.75</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.1538</v>
+        <v>10.0187</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>汽车+机器人|1.公司核心产品汽车座椅、汽车内饰， 对于传统车和新能源车均可配套。
-2.公司与自变量机器人科技（深圳）有限公司设立金智变量机器人科技（沈阳）有限公司，主要业务为机器人销售、数据类业务等。</t>
+          <t>光通信+机器人|1.2026年6月，公司官网披露，完成对烁光精密参股。烁光精密主要产品包括2D垂直/倾斜孔阵列、多通道V槽阵列、三维光波导，为光互连与集成封装提供超精密定位解决方案。
+2.公司在电子皮肤相关领域仍处于技术探索和研究阶段。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>汽车, 机器人</t>
+          <t>光通信, 机器人</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.3942</v>
+        <v>2.5704</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>中信证券预计，较为紧缺的重掺硅片下半年有望继续涨，相关公司可能在9月到10月调涨明年长协价格。这意味着涨价周期至少持续到2027年。</t>
+          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz003026</t>
+          <t>sz001229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>中晶科技</t>
+          <t>魅视科技</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>37</v>
+        <v>39.99</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>9.988099999999999</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.0138</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>半导体硅材料|公司是专业的高品质半导体硅材料制造商，主要产品为半导体硅片及半导体硅棒，主要应用于半导体分立器件。</t>
+          <t>AI应用+磷化铟|1.目前公司已经在视听产品中应用人工智能相关功能，如融入到业务流程的坐席人脸登录、现场恢复、坐席引导、语音指挥、隔空指挥、视频分析、数据AI识别采集等。
+2.2026年8月5日公告，公司已成立全资子公司珠海明曜新材料科技有限公司作为实施主体，注册资本1000万元，拟开展磷化铟半导体材料产业化项目的前期准备工作。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>半导体硅材料</t>
+          <t>AI应用, 磷化铟</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.3942</v>
+        <v>2.5704</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>中信证券预计，较为紧缺的重掺硅片下半年有望继续涨，相关公司可能在9月到10月调涨明年长协价格。这意味着涨价周期至少持续到2027年。</t>
+          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz002655</t>
+          <t>sh603118</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>共达电声</t>
+          <t>共进股份</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>40.77</v>
+        <v>18.43</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.0108</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0299</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>消费电子+半导体|1.公司是专业的电声元器件及电声组件制造商和服务商、电声技术解决方案提供商，主营业务为微型电声元器件及电声组件的研发、生产和销售。
-2.2026年8月17日晚发布对外投资暨关联交易公告，公司拟以自有资金2000万元参与对合肥硅臻芯片的增资。九天睿芯科技有限公司以 MPM(Memory-Processor-Model)共生设计为核心方法论，致力于推动模型、处理器、存储及系统软件的联合创新。</t>
+          <t>交换机|据2025年9月26日互动易，公司交换机已覆盖100G、400G、800G数据中心产品，800G型号按订单生产并供货国内交换机品牌商。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>消费电子, 半导体</t>
+          <t>交换机</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-0.3942</v>
+        <v>2.5704</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>中信证券预计，较为紧缺的重掺硅片下半年有望继续涨，相关公司可能在9月到10月调涨明年长协价格。这意味着涨价周期至少持续到2027年。</t>
+          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz000920</t>
+          <t>sz301689</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>沃顿科技</t>
+          <t>电科思仪</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>12.63</v>
+        <v>63</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.0174</v>
+        <v>20</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>超纯水系列膜|公司超纯水系列膜产品已在多家大型半导体企业实现稳定应用。</t>
+          <t>次新+光模块测试|2026年9月9日根据公司官微透露，公司携1.6T/3.2T高速光芯片/光模块综合测试、波长扫描测试系统、光通信激光特性测试、高速光芯片/光器件测试诊断、光纤接续等五大自研核心解决方案集中亮相2026年中国国际光电博览会。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>超纯水系列膜</t>
+          <t>次新, 光模块测试</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-0.3942</v>
+        <v>2.5704</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>中信证券预计，较为紧缺的重掺硅片下半年有望继续涨，相关公司可能在9月到10月调涨明年长协价格。这意味着涨价周期至少持续到2027年。</t>
+          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz002453</t>
+          <t>sz002980</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>华软科技</t>
+          <t>华盛昌</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4.85</v>
+        <v>128.03</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.9773</v>
+        <v>10.0009</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>光刻胶基材|关于公司相关的光刻胶基材产品业务，目前正处于客户接洽阶段，已有少量试订单。</t>
+          <t>光芯片测试|2026年2月27日公告，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。同时，公司控股股东袁剑敏拟向伽蓝特创始股东余新文协议转让公司5%股份，协议转让事项以目标公司收购事项完成为实施的前提条件。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域，本次股权收购为公司产业布局横向延伸。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>光刻胶基材</t>
+          <t>光芯片测试</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>烟草</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2.0476</v>
+        <v>1.5433</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2026年德国多特蒙德国际烟草展于9 月 15 日 - 17 日在多特蒙德会展中心盛大启幕。</t>
+          <t>近期机构研报指出，轻工出口链韧性仍强，低估值高分红内需龙头具备防御价值；新消费标的随新品周期启动和团队改革，基本面修复弹性值得关注。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz002836</t>
+          <t>sh600448</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>新宏泽</t>
+          <t>华纺股份</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>10.84</v>
+        <v>3.54</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.0508</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+        <v>9.937899999999999</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>烟标|公司系专业烟标印刷服务供应商，主营业务为烟标的设计、生产及销售。</t>
+          <t>印染加工|公司以印染加工为主业，形成包含纺纱、服装、家纺成品、纺织贸易、品牌开发、“B2B”平台、金融投资及热电等业务的多元化发展模式。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>烟标</t>
+          <t>印染加工</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>烟草</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2.0476</v>
+        <v>1.5433</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2026年德国多特蒙德国际烟草展于9 月 15 日 - 17 日在多特蒙德会展中心盛大启幕。</t>
+          <t>近期机构研报指出，轻工出口链韧性仍强，低估值高分红内需龙头具备防御价值；新消费标的随新品周期启动和团队改革，基本面修复弹性值得关注。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh600356</t>
+          <t>sh600630</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>恒丰纸业</t>
+          <t>龙头股份</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>10.19</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.0432</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+        <v>9.946899999999999</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>卷烟纸|公司主导产品为卷烟纸、滤嘴棒纸、铝箔衬纸和水松纸等，是国内卷烟辅料生产基地，五大卷烟辅料供应商之一。</t>
+          <t>上海本地+纺织|1.东方国际（集团）有限公司控股子公司上海纺织集团旗下上市公司。公司以品牌经营和国际贸易为主营业务。
+2.自主品牌业务包括以三枪、ELSMORR、鹅牌、菊花、海螺、民光、皇后、凤凰、钟牌414等品牌为主的针织、服饰、家纺类产品的经营。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>卷烟纸</t>
+          <t>上海本地, 纺织</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>烟草</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2.0476</v>
+        <v>1.5433</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2026年德国多特蒙德国际烟草展于9 月 15 日 - 17 日在多特蒙德会展中心盛大启幕。</t>
+          <t>近期机构研报指出，轻工出口链韧性仍强，低估值高分红内需龙头具备防御价值；新消费标的随新品周期启动和团队改革，基本面修复弹性值得关注。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz300741</t>
+          <t>sz003041</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>华宝股份</t>
+          <t>真爱美家</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>27.17</v>
+        <v>42.02</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>20.0088</v>
+        <v>10</v>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>烟草香精|国内烟草香精龙头，国内最大香精上市公司。公司在烟草用香精领域主要客户为云南、上海等19个省的省级中烟工业公司，食品用香精领域主要客户有蒙牛、光明、伊利、百事等。旗下拥有“喜登”、“华宝”、“孔雀”、“天宏”、“华芳”、“澳华达”、“琥珀”等一系列知名品牌。</t>
+          <t>家用纺织品|公司主要从事以毛毯为主的家用纺织品的研发、设计、生产与销售，主要产品为毛毯及床上用品（套件、被芯、枕芯等）。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>烟草香精</t>
+          <t>家用纺织品</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.9138999999999999</v>
+        <v>1.5433</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>据报道，今年以来，我国创新药出海步伐再提速，对外授权交易总额突破1200亿美元，同比增长36%。</t>
+          <t>近期机构研报指出，轻工出口链韧性仍强，低估值高分红内需龙头具备防御价值；新消费标的随新品周期启动和团队改革，基本面修复弹性值得关注。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz300434</t>
+          <t>sh603001</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>金石亚药</t>
+          <t>奥康国际</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>12.49</v>
+        <v>10.43</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>19.9808</v>
+        <v>10.0211</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司持有杭州领业医药32.4304%的股权。杭州领业医药以核心技术为驱动，解决临床未满足需求为目标，深耕皮肤科学领域，开发创新药、仿制药和皮肤健康产品，做皮肤健康的守护者。</t>
+          <t>鞋类|主要从事皮鞋及皮具产品的研发、生产、零售及分销业务,产品种类主要有商务正装鞋、休闲鞋、运动鞋等鞋类产品以及皮具配套产品。公司实施以“奥康”品牌为主, “康龙”、 “斯凯奇”等品牌为辅的多品牌运营策略。主品牌“奥康”在男鞋领域具有较强的市场竞争力。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>鞋类</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.9138999999999999</v>
+        <v>1.5433</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>据报道，今年以来，我国创新药出海步伐再提速，对外授权交易总额突破1200亿美元，同比增长36%。</t>
+          <t>近期机构研报指出，轻工出口链韧性仍强，低估值高分红内需龙头具备防御价值；新消费标的随新品周期启动和团队改革，基本面修复弹性值得关注。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh600721</t>
+          <t>sz001238</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>浙江正特</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>11.87</v>
+        <v>26.31</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10.0093</v>
+        <v>9.9916</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>CXO|公司主营业务为药物发现、研究、技术服务，提供从药物发现、CMC、临床CRO、药品注册、CMO/API供应等新药开发全流程的服务及一体化的解决方案。</t>
+          <t>遮阳制品|公司现拥有遮阳制品、户外休闲家具两大产品系列，其中遮阳制品主要包括星空篷、遮阳篷和遮阳伞，户外休闲家具主要包括户外家具、储物用品、宠物屋。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>CXO</t>
+          <t>遮阳制品</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.9138999999999999</v>
+        <v>1.5433</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>据报道，今年以来，我国创新药出海步伐再提速，对外授权交易总额突破1200亿美元，同比增长36%。</t>
+          <t>近期机构研报指出，轻工出口链韧性仍强，低估值高分红内需龙头具备防御价值；新消费标的随新品周期启动和团队改革，基本面修复弹性值得关注。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz000504</t>
+          <t>sz002029</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>南华生物</t>
+          <t>七 匹 狼</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.0363</v>
+        <v>10.0244</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>细胞治疗|公司是目前国内一家国资控股的干细胞、免疫细胞及组织工程产业主板上市公司，“生物医药”板块业务包括干细胞储存服务、化妆品的生产和销售、医疗器械设备及耗材的代理和销售。</t>
+          <t>纺织+参股宇树|1.主要从事“七匹狼”品牌男装的设计、生产和销售,主要产品包括衬衫、西服、裤装、茄克衫、针织衫等。
+2.公司母公司间接持有摩尔线程和宇树科技的部分股权。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>细胞治疗</t>
+          <t>纺织, 参股宇树</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>次新股</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-1.5875</v>
+        <v>5.9091</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2026年以来，AI服务器带动的PCB高多层化使电子布（玻纤布）从周期品变成紧缺品：风向标品种7628厚布出厂价由2026年初约4.6元/米涨至9月的11—12元/米。</t>
+          <t>C沈鼓早盘一度跌近30%，随后持续拉升，一度翻红，带动整个次新板块情绪。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sh605058</t>
+          <t>sh603248</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>锡华科技</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>48.76</v>
+        <v>24.57</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>9.9932</v>
+        <v>9.982099999999999</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5天5板</t>
+          <t>4天4板</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
+          <t>次新+风电|公司主要从事大型高端装备专用部件的研发、制造与销售，产品结构以风电齿轮箱专用部件为主、注塑机厚大专用部件为辅，是全球行业领先、质量可靠、技术卓越的大型高端装备专用部件制造商。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>次新, 风电</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>次新股</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-1.5875</v>
+        <v>5.9091</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2026年以来，AI服务器带动的PCB高多层化使电子布（玻纤布）从周期品变成紧缺品：风向标品种7628厚布出厂价由2026年初约4.6元/米涨至9月的11—12元/米。</t>
+          <t>C沈鼓早盘一度跌近30%，随后持续拉升，一度翻红，带动整个次新板块情绪。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sz003001</t>
+          <t>sz001233</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>中岩大地</t>
+          <t>海安集团</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>20.32</v>
+        <v>45.58</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10.0162</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.990300000000001</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>PCB钻针|中岩大地公告称，公司拟通过现金收购及增资方式取得深圳市鑫寰宇精工科技有限公司60%股权。标的公司是国内专注于PCB精密钻针及铣刀的专精特新企业，核心产品覆盖PCB及FPC钻针、涂层钻针、金刚石刀具及铣刀等。</t>
+          <t>次新+福建+轮胎|公司的主营业务包括巨型全钢工程机械子午线轮胎的研发、生产与销售，以及矿用轮胎运营管理业务，现已具备全系列型号全钢巨胎（轮辋直径49英寸及以上）的生产技术和量产能力，为国内外上百个矿山提供了全钢巨胎产品或服务。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>PCB钻针</t>
+          <t>次新, 福建, 轮胎</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>次新股</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-1.5875</v>
+        <v>5.9091</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2026年以来，AI服务器带动的PCB高多层化使电子布（玻纤布）从周期品变成紧缺品：风向标品种7628厚布出厂价由2026年初约4.6元/米涨至9月的11—12元/米。</t>
+          <t>C沈鼓早盘一度跌近30%，随后持续拉升，一度翻红，带动整个次新板块情绪。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz001365</t>
+          <t>sh603402</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>天海电子</t>
+          <t>陕西旅游</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>37.51</v>
+        <v>64.19</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10</v>
+        <v>10.0086</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>PCB+机器人|1.公司涉及PCB的产品有电器盒、智能电器盒等汽车电子产品，相关工艺分为精密连接器制造、电子组装等。
-2.公司现有产品涵盖人形机器人线束。</t>
+          <t>次新+旅游|公司依托华清宫、华山等国家5A级景区，为游客提供高品质的旅游产品及服务体验。在旅游演艺业务方面，公司打造了中国首部大型实景历史舞剧《长恨歌》、大型实景影画《12·12西安事变》、大型红色实景演艺《泰山烽火》等优质旅游演艺作品。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>PCB, 机器人</t>
+          <t>次新, 旅游</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>次新股</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.3081</v>
+        <v>5.9091</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>DataEye数据显示，2026年国内AI短剧市场规模有望突破400亿元，同比增长138%。</t>
+          <t>C沈鼓早盘一度跌近30%，随后持续拉升，一度翻红，带动整个次新板块情绪。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh603230</t>
+          <t>sh601123</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>马矿股份</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>12.25</v>
+        <v>17.78</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>9.9641</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0248</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>出版传媒|公司的最终控制人为内蒙古自治区人民政府。公司主营业务是出版物的批发、零售；文体用品零售；音像制品发行</t>
+          <t>次新+福建+铁矿石|公司是一家长期从事铁矿资源开发及综合利用的企业，主营铁矿石的采选、综合利用及铁精粉、钼精矿销售，石灰石的开采和销售。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>出版传媒</t>
+          <t>次新, 福建, 铁矿石</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>次新股</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1.3081</v>
+        <v>5.9091</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>DataEye数据显示，2026年国内AI短剧市场规模有望突破400亿元，同比增长138%。</t>
+          <t>C沈鼓早盘一度跌近30%，随后持续拉升，一度翻红，带动整个次新板块情绪。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh605577</t>
+          <t>920298.BJ</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>腾信精密</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>15</v>
+        <v>90.48</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.970700000000001</v>
+        <v>30</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧+出版传媒|1.公司首部AI漫剧《穿越1988》完成170集制作上线，全网播放量突破1.2亿，红果热度值超4000万。
-2.公司地处哈尔滨，是我国东北地区出版发行行业的领先企业之一，公司拥有出版物“编、印、发”完整的产业链。</t>
+          <t>北交所次新|腾信精密定位于“全球精密零部件及组件制造专家”，专注高附加值精密零部件的研发设计、制造与销售，以高精度及高温合金复杂结构机加工、激光熔覆、柔性自动化技术为核心竞争力。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧, 出版传媒</t>
+          <t>北交所次新</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.3244</v>
+        <v>1.7548</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>中欧陆家嘴国际金融研究院9月15日发布2026全球资产管理中心评价指数报告。报告显示，上海以87.05分升至第三，首次进入全球前三，并成为亚洲排名最高的资产管理中心。</t>
+          <t>特斯拉相关团队已于9月16日落地宁波，并于9月17日开启新一轮针对旗下机器人业务的量产审厂工作。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh600822</t>
+          <t>sh603626</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>上海物贸</t>
+          <t>科森科技</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>23.42</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>9.9648</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
+        <v>10.0047</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>上海+物流|目前公司主要在上海地区从事汽车贸易（包括新车、二手车交易、维修等）、化工等生产资料的批发与零售业务、有色金属交易及仓储物流业务。</t>
+          <t>机器人+折叠屏|1.公司不生产机器人产品，公司为某品牌家用机器人提供相关结构件。
+2.公司生产的折叠屏手机铰链已量产。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>上海, 物流</t>
+          <t>机器人, 折叠屏</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.3244</v>
+        <v>1.7548</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>中欧陆家嘴国际金融研究院9月15日发布2026全球资产管理中心评价指数报告。报告显示，上海以87.05分升至第三，首次进入全球前三，并成为亚洲排名最高的资产管理中心。</t>
+          <t>特斯拉相关团队已于9月16日落地宁波，并于9月17日开启新一轮针对旗下机器人业务的量产审厂工作。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh600630</t>
+          <t>sz000910</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>龙头股份</t>
+          <t>大亚圣象</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>7.54</v>
+        <v>5.69</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.073</v>
+        <v>10.058</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>上海+纺织|1.东方国际（集团）有限公司控股子公司上海纺织集团旗下上市公司。公司以品牌经营和国际贸易为主营业务。
-2.公司旗下“三枪”品牌获2022年度上海首发经济引领性本土品牌。</t>
+          <t>参股七腾机器人|公司以自有资金1,500万元人民币认购嘉兴翼龙股权投资合伙企业 （有限合伙）28.30189%的份额，该基金以股权投资的方式投资七腾机器人有限公司。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>上海, 纺织</t>
+          <t>参股七腾机器人</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-0.2598</v>
+        <v>1.7548</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>近日，德国联邦内阁批准《海上风电法》修正案草案，该法案将提交联邦议会审议，计划于2027年1月1日正式生效。改革方案将差价合约机制引入德国海上风电框架，并计划将项目标准运营期限由25年延长至35年。</t>
+          <t>特斯拉相关团队已于9月16日落地宁波，并于9月17日开启新一轮针对旗下机器人业务的量产审厂工作。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh603248</t>
+          <t>sz002965</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>锡华科技</t>
+          <t>祥鑫科技</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>22.34</v>
+        <v>31.11</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>9.995099999999999</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.0071</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>风电|公司主要从事大型高端装备专用部件的研发、制造与销售，产品结构以风电齿轮箱专用部件为主、注塑机厚大专用部件为辅，是全球行业领先、质量可靠、技术卓越的大型高端装备专用部件制造商。</t>
+          <t>机器人+液冷|1.公司已为优必选和库卡供应金属结构件相关产品。在工业机器人领域，公司旗下的东莞市荣升自动化系统有限公司拥有生产电池托盘相关产品的柔性化产线、焊接机器人工作站及其他非标金属结构件产品。
+2.公司的埋管式水冷板、水冷散热器、新能源散热器、剖沟散热器等产品可应用于GPU冷却、服务器冷却和IDC数据中心以及汽车领域。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>机器人, 液冷</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-0.2598</v>
+        <v>1.7548</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>近日，德国联邦内阁批准《海上风电法》修正案草案，该法案将提交联邦议会审议，计划于2027年1月1日正式生效。改革方案将差价合约机制引入德国海上风电框架，并计划将项目标准运营期限由25年延长至35年。</t>
+          <t>特斯拉相关团队已于9月16日落地宁波，并于9月17日开启新一轮针对旗下机器人业务的量产审厂工作。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh601218</t>
+          <t>sz000410</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>沈阳机床</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5.74</v>
+        <v>5.57</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>9.9617</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>10.0791</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>风电|公司是一家专注于研发、制造和销售大型风力发电机组用零部件的龙头企业，主要生产750KW-12MW风力发电机组用轮毂、底座、轴、轴承座等系列产品。</t>
+          <t>工业母机+机器人|1.公司主营业务包括产品研发、机床制造、销售服务、行业解决方案、机床零部件配套等，可面向机械制造核心领域提供量大面广的通用型机床。
+2.子公司沈阳优尼斯智能装备有限公司经营范围包括机器人产品的技术开发、制造。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>工业母机, 机器人</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-0.5262</v>
+        <v>1.7548</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>中金公司研报称，“锁订单”、“锁物料”成为第27届光博会调研关键词，2027年需求确定性进一步提高。结合展会调研，部分高速光芯片企业订单排期已延伸至2028年及以后，光模块订单能见度覆盖2027年及以后。</t>
+          <t>特斯拉相关团队已于9月16日落地宁波，并于9月17日开启新一轮针对旗下机器人业务的量产审厂工作。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh600641</t>
+          <t>sh600577</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>先导基电</t>
+          <t>精达股份</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>36.8</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.0149</v>
+        <v>9.962200000000001</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>磷化铟|2026年7月1日公告，公司正在筹划对广东先导微电子科技有限公司增资以实现对其控制的相关事项。公司拟与清远先导特种材料有限公司、先导微电子签署《投资协议》，以增资形式对先导微电子进行投资，取得标的公司50%以上的股权。先导微电子主营砷化镓、磷化铟衬底晶圆制造，是国内少数实现4-6英寸磷化铟抛光片量产的企业，也是AI高速光模块、CPO（光电共封装）技术的上游核心材料供应商。</t>
+          <t>机器人+高速线|1.公司有部分产品应用于机器人伺服电机。
+2.子公司恒丰特导生产的高速线主要用于数据中心、5G信号基站等高速信息传输领域。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>磷化铟</t>
+          <t>机器人, 高速线</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.5262</v>
+        <v>2.307</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>中金公司研报称，“锁订单”、“锁物料”成为第27届光博会调研关键词，2027年需求确定性进一步提高。结合展会调研，部分高速光芯片企业订单排期已延伸至2028年及以后，光模块订单能见度覆盖2027年及以后。</t>
+          <t>《半导体存储介质块擦除技术指引》《电子产品回收过程中的信息清除管理指引》《移动智能终端信息清除技术指引》等3项网络安全标准实践指南正式向社会发布。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sz002796</t>
+          <t>sh603138</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>世嘉科技</t>
+          <t>海量数据</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>32.54</v>
+        <v>15.57</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.0068</v>
+        <v>10.0353</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>光模块|2026年3月27日公告，公司拟以1.3亿元收购金帝联合控股集团有限公司持有的光彩芯辰(浙江)科技有限公司6.9365%股权。交易完成后，公司对光彩芯辰的持股比例将由20%增至26.9365%。标的公司是一家专注于光通信领域传输和接入技术的高新技术企业，专业从事以光模块、AOC、AEC等为主的光通信产品的研发、生产及销售，产品矩阵覆盖100G至800G、1.6T系列光模块产品。</t>
+          <t>数据安全|数据库是公司的核心业务，主要针对客户的实际需求，在满足性能、安全、连续性的前提下，提供最优的数据库资产配置。公司高度重视自主创新，专注做好数据库，相继研发并推出了一系列高性能、高可用、高安全的数据库产品。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>光模块</t>
+          <t>数据安全</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
+        <v>2.307</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>《半导体存储介质块擦除技术指引》《电子产品回收过程中的信息清除管理指引》《移动智能终端信息清除技术指引》等3项网络安全标准实践指南正式向社会发布。</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh603838</t>
+          <t>sh688292</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST四通 </t>
+          <t>浩瀚深度</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>13.53</v>
+        <v>23.02</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10</v>
+        <v>20.0209</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">AI+网络安全|1.公司目前人工智能技术主要应用在网络可视化与智能化中的互联网流量识别、数据提取与分析领域。
+2.公司聚焦于互联网流量的智能化管控和数据应用领域，致力于为电信运营商等各类客户提供全方位、高性能、跨平台的网络智能化及信息安全防护解决方案，为各层级网络的高效、稳定、安全运行提供保障。
+</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>AI, 网络安全</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
+        <v>2.307</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>《半导体存储介质块擦除技术指引》《电子产品回收过程中的信息清除管理指引》《移动智能终端信息清除技术指引》等3项网络安全标准实践指南正式向社会发布。</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz002528</t>
+          <t>sh603232</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>*ST英飞</t>
+          <t>格尔软件</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>7.18</v>
+        <v>16.31</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>9.9541</v>
+        <v>9.979799999999999</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 英飞拓推出5G多功能智慧灯杆，支持节能照明、视频监控、新能源充电、公共WIFI、环境监测、信息发布、应急报警、5G微基站等模块，实现多种类型的感知数据采集、分析、仿真预测，提升城市综合治理。</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t>AI+网络安全|1.公司的AI赋能旨在深化AI与密码学、安全、产品三大核心业务的融合,明确推动AI应用从工具引入向范式变革演进,实现“AI赋能效率、创新驱动升级”双重目标。
+2.公司自成立以来一直专注于信息安全行业PKI领域，主要从事以公钥基础设施PKI为核心的商用密码软件产品的研发、生产和销售及服务业务，为用户提供基于PKI的信息安全系列产品、安全服务和信息安全整体解决方案。</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>AI, 网络安全</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
+          <t>网络安全</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>2.307</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>《半导体存储介质块擦除技术指引》《电子产品回收过程中的信息清除管理指引》《移动智能终端信息清除技术指引》等3项网络安全标准实践指南正式向社会发布。</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sz001216</t>
+          <t>sh688175</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>高凌信息</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>19.88</v>
+        <v>21.74</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10.0166</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>19.9779</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>MLCC|子公司氧化锆粉体纯度最高可达99.995%，产品可适配新能源研磨、齿科陶瓷、MLCC等不同领域使用需求。</t>
+          <t>AI+网络安全|公司已规划研发反诈智能体，主要用于网络内容安全方面的应用。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>MLCC</t>
+          <t>AI, 网络安全</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1.9628</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>TrendForce集邦咨询估算，2026年全球数据中心电力需求容量将达161GW，年增约31%，主要增长来源为AI Server，预估占整体需求容量达33.4%。</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sz002285</t>
+          <t>sz002300</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>世联行</t>
+          <t>太阳电缆</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>2.63</v>
+        <v>8.67</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10.0418</v>
+        <v>10.0254</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>房地产|公司专注房地产服务业，凭借对行业发展的理解和客户需求的认知，叠加了金融、资管、互联网+（电商）等创新服务。</t>
+          <t>电线电缆|公司是福建省最大的综合性电线电缆生产基地，通过旗下全资子公司太阳海缆建设海底电缆生产基地。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>电线电缆</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1.9628</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>TrendForce集邦咨询估算，2026年全球数据中心电力需求容量将达161GW，年增约31%，主要增长来源为AI Server，预估占整体需求容量达33.4%。</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh605162</t>
+          <t>sz002298</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">新中港  </t>
+          <t>中电鑫龙</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>12.2</v>
+        <v>9</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10.009</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>10.0244</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>电力|公司采用热电联产的方式进行热力产品和电力产品的生产及供应。公司的热力业务主要面向工业用户供应所生产的蒸汽，主要满足工业园区内的造纸、印染、医药、化工、食品等150余家工业企业的热需求。</t>
+          <t>数据中心+电网设备|1.公司与HUAWEI公司签订了战略合作协议，双方在智慧城市、大数据中心等领域进行合作，双方积极推动智慧城市、大数据中心等项目落地。
+2.公司致力于新型储能产品制造和储能系统集成、测试，光伏电站和储能电站项目开发、建设、运维，园区级和企业级能碳管理软件平台和节能降碳解决方案等三大业务板块。公司产品可用于电网的发电端、输电端，配电端及用电端。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>数据中心, 电网设备</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>1.9628</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>TrendForce集邦咨询估算，2026年全球数据中心电力需求容量将达161GW，年增约31%，主要增长来源为AI Server，预估占整体需求容量达33.4%。</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sz301390</t>
+          <t>sz002471</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>经纬股份</t>
+          <t>中超控股</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>45</v>
+        <v>5.96</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>20</v>
+        <v>9.963099999999999</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>控股股东变更|经纬股份公告称，公司实控人叶肖华及其一致行动人、员工持股平台、持股5%以上股东炬华科技及其一致行动人炬华联昕、股东吴仁德与中软国际(西安)智能科技签署《股份转让协议》，拟以53元/股协议转让合计1780.62万股(占总股本29.68%)，转让价款合计9.44亿元。完成后，中软国际(西安)智能科技将成为公司控股股东。</t>
+          <t>机器人+电力电缆|1.中超控股公告称，公司近日与合肥市智能机器人研究院签订《战略合作协议》，双方将在智能机器人技术合作与产业化应用、航空航天领域高温合金铸造轻量化技术、智能机器人用电线电缆技术开发与应用等方面展开合作。
+2.公司是国内综合线缆供应商，主要产品涵盖从超高压到低压的各类电力电缆、导线及民用电缆。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>控股股东变更</t>
+          <t>机器人, 电力电缆</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
+          <t>智能电网</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1.9628</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>TrendForce集邦咨询估算，2026年全球数据中心电力需求容量将达161GW，年增约31%，主要增长来源为AI Server，预估占整体需求容量达33.4%。</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sh600293</t>
+          <t>sh603016</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t xml:space="preserve">新宏泰  </t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>3.4</v>
+        <v>30.48</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>10.0324</v>
+        <v>9.9964</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板|公司深耕玻璃产业40余载，较早致力于玻璃产品的研发、制造和销售，已形成完整的产业链和产业集群，公司将向超薄玻璃、超白玻璃、超强玻璃等平板玻璃，光伏背板、光伏盖板等光伏玻璃，盖板玻璃、基板玻璃等电子玻璃延伸和拓展。</t>
+          <t>电网设备|公司主营业务为断路器关键部件，低压断路器及刀熔开关的研发，生产与销售，公司实控人为无锡市人民政府国有资产监督管理委员会。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>电网设备</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+          <t>房地产概念</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>“十五五”时期将推动住房公积金高质量发展。将扩大住房公积金制度覆盖面，支持个体工商户、非全日制从业人员以及其他灵活就业人员自愿缴存住房公积金，进一步增强公积金制度的普惠性。</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sh600448</t>
+          <t>sz002285</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>华纺股份</t>
+          <t>世联行</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>3.22</v>
+        <v>2.89</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>9.897599999999999</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+        <v>9.885899999999999</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>纺织服装|公司以印染加工为主业，形成包含纺纱、服装、家纺成品、纺织贸易、品牌开发、“B2B”平台、金融投资及热电等业务的多元化发展模式。</t>
+          <t>房地产|公司专注房地产服务业，凭借对行业发展的理解和客户需求的认知，叠加了金融、资管、互联网+（电商）等创新服务。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>纺织服装</t>
+          <t>房地产</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
+          <t>房地产概念</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>“十五五”时期将推动住房公积金高质量发展。将扩大住房公积金制度覆盖面，支持个体工商户、非全日制从业人员以及其他灵活就业人员自愿缴存住房公积金，进一步增强公积金制度的普惠性。</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz002339</t>
+          <t>sh600606</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>积成电子</t>
+          <t>绿地控股</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>8.23</v>
+        <v>1.45</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10.0267</v>
+        <v>9.8485</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>电网设备|公司在电力自动化领域产品线覆盖了电力系统发、输、变、配、用、调度各环节，是国内少数几家能够提供电力自动化整体解决方案的厂家之一。</t>
+          <t>房地产|公司是一家总部位于中国上海的跨国经营企业，同时也是中国首家以房地产为主业并跻身《财富》世界500强的综合性企业集团。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>房地产</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
+          <t>房地产概念</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>“十五五”时期将推动住房公积金高质量发展。将扩大住房公积金制度覆盖面，支持个体工商户、非全日制从业人员以及其他灵活就业人员自愿缴存住房公积金，进一步增强公积金制度的普惠性。</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh600593</t>
+          <t>sz000002</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>大连圣亚</t>
+          <t>万  科Ａ</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>43.31</v>
+        <v>3.32</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>10.0076</v>
+        <v>9.9338</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>旅游+冰雪产业|公司正在经营的哈尔滨景区包括哈尔滨极地公园海洋馆、哈尔滨极地公园极地馆、哈尔滨极地公园恐龙馆、哈尔滨极地公园北极熊体验馆、哈尔滨极地公园淘学企鹅馆。</t>
+          <t>房地产|本集团的主营业务包括房地产开发和物业服务，本集团将自身定位进一步迭代升级为“城乡建设与生活服务商”。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>旅游, 冰雪产业</t>
+          <t>房地产</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
+          <t>商业零售</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1.8073</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>国家统计局发布数据显示，1—8月份，社会消费品零售总额327569亿元，同比增长1.1%。其中，除汽车以外的消费品零售额301764亿元，增长2.7%。</t>
+        </is>
+      </c>
       <c r="D47" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sz002640</t>
+          <t>sh605188</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>跨境通</t>
+          <t>国光连锁</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>3.77</v>
+        <v>13.12</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>9.9125</v>
+        <v>9.9749</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>跨境电商|公司主营业务包括跨境出口电商业务、跨境进口电商业务两大类，跨境通助力中国优质产品通过电商渠道输出到海外市场，同时将海外的优质产品进口到中国市场。</t>
+          <t>零售|公司自设立以来主要从事连锁超市、百货商场的运营业务。公司立足于江西省内，多年来通过深耕本地市场、持续推进门店升级转型，成为以生鲜、食品为核心品类的零售企业。公司是江西省商贸流通行业首家上市企业，江西本土领先的连锁经营企业。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>跨境电商</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr"/>
+          <t>商业零售</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>1.8073</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>国家统计局发布数据显示，1—8月份，社会消费品零售总额327569亿元，同比增长1.1%。其中，除汽车以外的消费品零售额301764亿元，增长2.7%。</t>
+        </is>
+      </c>
       <c r="D48" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sh600929</t>
+          <t>sh600838</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>雪天盐业</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>5.94</v>
+        <v>8.59</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>10</v>
+        <v>9.9872</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>并购重组|雪天盐业公告称，公司拟通过发行股份及支付现金方式购买河北坤天新能源股份有限公司100%股份并募集配套资金，预计构成重大资产重组。</t>
+          <t>零售|公司控股股东为上海九百（集团）有限公司。目前已经发展成为涉及洗涤化工产品生产销售及洗染服务、酒类产品批发等多种业态的综合性企业。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
+          <t>商业零售</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1.8073</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>国家统计局发布数据显示，1—8月份，社会消费品零售总额327569亿元，同比增长1.1%。其中，除汽车以外的消费品零售额301764亿元，增长2.7%。</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh600792</t>
+          <t>sh601086</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>云煤能源</t>
+          <t>国芳集团</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>5.34</v>
+        <v>16.06</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10.1031</v>
+        <v>10</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>煤炭|云南省最大的焦化企业，主要产品有冶金焦炭、焦油、粗苯、煤气、甲醇、硫酸铵、硫磺等产品。</t>
+          <t>零售|公司从事以百货业为主，超市、电器为辅的连锁零售业务，是甘肃省内最大的连锁零售企业。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>1.6795</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>浙商证券最新研报显示，随着PCB上游材料价格持续上涨，涨价开始向部分PCB品类传导，涨价效果自2026年第三季度起将逐步体现。</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh601872</t>
+          <t>sz002134</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>招商轮船</t>
+          <t>天津普林</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>21.85</v>
+        <v>27.1</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>10.0201</v>
+        <v>9.9838</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>油运|公司主要从事国际原油运输、国际干散货运输业务，并通过持股50%的CLNG公司（另一持股50%的股东为中远海能下属的大连中远海运油品运输有限公司）投资经营国际LNG运输业务。</t>
+          <t>PCB|公司主要从事印制电路板（PCB）的研发、生产及销售，产品类型覆盖单双面板、多层板、高多层板、HDI、高频高速板及厚铜板等，专注于中小批量、高多层、厚铜板、光电板和HDI领域的PCB领先企业。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>油运</t>
+          <t>PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>1.6795</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>浙商证券最新研报显示，随着PCB上游材料价格持续上涨，涨价开始向部分PCB品类传导，涨价效果自2026年第三季度起将逐步体现。</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>sz001212</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>中旗新材</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>9.991300000000001</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>PCB|公司的超细硅晶材料可应用于涂料、覆铜板、电工绝缘料、液晶显示玻璃等。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>1.6795</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>浙商证券最新研报显示，随着PCB上游材料价格持续上涨，涨价开始向部分PCB品类传导，涨价效果自2026年第三季度起将逐步体现。</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>sz000509</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>华塑控股</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>9.9125</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>PCB|子公司宏创智能研发投产多工位粗精磨一体机MF6000E，该设备加工生产的钻针可用于加工高频高速PCB板。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>诺和诺德与Anthropic宣布达成合作，双方将利用Anthropic的人工智能（AI）模型及Claude Science支持药物发现与研发。</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sz000504</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>南华生物</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>细胞治疗|公司是目前国内一家国资控股的干细胞、免疫细胞及组织工程产业主板上市公司，“生物医药”板块业务包括干细胞储存服务、化妆品的生产和销售、医疗器械设备及耗材的代理和销售。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>细胞治疗</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>诺和诺德与Anthropic宣布达成合作，双方将利用Anthropic的人工智能（AI）模型及Claude Science支持药物发现与研发。</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>sh603122</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>合富中国</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>医疗流通+海峡两岸|1.公司系医疗流通领域的渠道商，具备与境内外试剂耗材和医疗设备原厂、各大代理商及医疗机构长期互惠、合作共赢的核心竞争力。
+2.公司为唯一一家海峡两岸市场“双上市”的医疗企业，其母公司合富医疗控股在台湾上市，公司实际控制人为台湾企业家王琼芝，在两岸医疗流通领域有深度合作。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>医疗流通, 海峡两岸</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>诺和诺德与Anthropic宣布达成合作，双方将利用Anthropic的人工智能（AI）模型及Claude Science支持药物发现与研发。</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sz002589</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>瑞康医药</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>10.101</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>创新药|公司与广东药科大学相关医学专家合作，共同合作研发治疗非酒精性肝脂肪变中医新药FTZ浓缩丸，2024年内已进入临床二期阶段。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>0.7743</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>华泰证券指出，黄酒行业量价逻辑有望迎来重构，量上由江浙沪渗透提升走向全国拓展，价上龙头合力推进高端化。</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>sh601579</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">会稽山  </t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>10.0168</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>8天4板</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>黄酒|公司主要从事黄酒的生产、销售和研发等业务，公司及下属子公司主要拥有“会稽山”、“西塘”、“乌毡帽”、“唐宋”等主品牌。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>黄酒</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>0.7743</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>华泰证券指出，黄酒行业量价逻辑有望迎来重构，量上由江浙沪渗透提升走向全国拓展，价上龙头合力推进高端化。</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>sh600127</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>9.9846</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>农业种植+食品饮料|公司是我国粮食系统的第一家上市公司，是首批农业产业化国家重点龙头企业，国家水稻工程优质米示范基地。公司以优质粮油、新型健康食品和药品开发、生产、销售为发展方向，坚持农、工、科、贸一体化的现代农业产业化经营模式，主要产品有大米、面粉、面条、植物油、米粉、牛奶、糖果、果冻、药品等。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>农业种植, 食品饮料</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>0.7743</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>华泰证券指出，黄酒行业量价逻辑有望迎来重构，量上由江浙沪渗透提升走向全国拓展，价上龙头合力推进高端化。</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>sz001211</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>双枪科技</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>9.987300000000001</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料+餐厨具|1.子公司极野食品主要销售以食材笋和调味笋为主的笋产品。
+2.公司是一家领先的日用餐厨具供应商，拥有筷子、砧板、勺铲、签类和其他餐厨具5个大类，超过1000种单品。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料, 餐厨具</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>文化传媒</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>方正证券研报指出，AI正从单点工具应用逐步向内容生产、分发及商业化等产业链环节渗透，互联网传媒行业进入生产方式与商业模式加速重构阶段。</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>sh603230</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>内蒙新华</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>10.0408</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>出版传媒|公司的最终控制人为内蒙古自治区人民政府。公司主营业务是出版物的批发、零售；文体用品零售；音像制品发行</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>出版传媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>文化传媒</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>方正证券研报指出，AI正从单点工具应用逐步向内容生产、分发及商业化等产业链环节渗透，互联网传媒行业进入生产方式与商业模式加速重构阶段。</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>sh600640</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>国脉文化</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>10.0365</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI短剧+机器人|1.公司构建了包含AI创意与文本创作、视觉概念及分镜设计、图像到视频转换、语音合成以及AI音乐创作全流程的AI短剧创作工作流，实现AIGC赋能内容生产。围绕文化、经典、文旅方向，成功打造“AIGC微短剧”系列内容。
+2.公司与宇树科技的合作属于小范围个别产品的合作，面向会展等应用场景的探索。
+</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>AI短剧, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>文化传媒</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>方正证券研报指出，AI正从单点工具应用逐步向内容生产、分发及商业化等产业链环节渗透，互联网传媒行业进入生产方式与商业模式加速重构阶段。</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>sh601811</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>9.968399999999999</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>出版传媒|公司是我国第一家按照上市公众公司标准规范设立的大型股份制出版发行企业。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>出版传媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>算力工程</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>2.1637</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>AI算力租赁商Nebius拟于10月1日起上调部分GPU算力价格，涨幅约20%。</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>sz002713</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>东易日盛</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>9.969799999999999</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁|公司于2025年3月18日披露重整投资协议暨预重整进展，公司与北京华著签订了《重整投资协议》，交易完成后，北京华著预计对公司的持股比例为15.77%，成为公司控股股东。北京华著为AIDC（智算中心）综合服务商。在协议中，北京华著明确表示将向上市公司捐赠智算中心等资产，帮助上市公司转型智算领域。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>算力工程</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>2.1637</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>AI算力租赁商Nebius拟于10月1日起上调部分GPU算力价格，涨幅约20%。</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>sz002849</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>威星智能</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>10.0162</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>投资智算中心|2023年7月24日公告，近日，公司与贵安管委会、摩尔线程签署《贵安智算中心项目投资合作协议》，三方拟在贵安新区建立智算中心，在3D图形渲染和视觉设计、高性能科学计算、HDV高速视频解编码、AI训练和推理等应用领域构建深度合作关系。</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>投资智算中心</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>大金融</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>今年以来，A股IPO市场持续放量，券商IPO承销金额已超过2025年全年，投行业务竞争格局出现新变化。</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>sh600621</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>华鑫股份</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>9.984400000000001</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>券商|公司以证券业务为主，以部分持有型物业经营业务为辅。公司通过全资子公司华鑫证券开展证券业务</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>大金融</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>今年以来，A股IPO市场持续放量，券商IPO承销金额已超过2025年全年，投行业务竞争格局出现新变化。</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>sz000532</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>华金资本</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>10.017</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>多元金融|公司全力打造股权投资、资产管理、实体产业三大业务体系，构建了“创投+实业”双轮驱动的产业新格局。</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>sh603272</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST联翔 </t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>10.0326</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 联翔股份公告称，公司控股股东卜晓华与金美含签署股份转让协议，拟以20.36元/股的价格协议转让5,181,400股无限售流通股，占公司总股本的5%，转让总价款约为1.05亿元。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>sz001216</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>华瓷股份</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>10.0101</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>MLCC上游粉体|子公司氧化锆粉体纯度最高可达99.995%，产品可适配新能源研磨、齿科陶瓷、MLCC等不同领域使用需求。</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>MLCC上游粉体</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>sz301390</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>经纬股份</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>控股股东变更|经纬股份公告称，公司实控人叶肖华及其一致行动人、员工持股平台、持股5%以上股东炬华科技及其一致行动人炬华联昕、股东吴仁德与中软国际(西安)智能科技签署《股份转让协议》，拟以53元/股协议转让合计1780.62万股(占总股本29.68%)，转让价款合计9.44亿元。完成后，中软国际(西安)智能科技将成为公司控股股东。</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>控股股东变更</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>sz002836</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>新宏泽</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>9.963099999999999</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>烟标|公司系专业烟标印刷服务供应商，主营业务为烟标的设计、生产及销售。</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>烟标</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>sz001376</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>百通能源</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>9.991300000000001</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>铝业公司完成注册|境外全资子公司百通图达（安哥拉）铝业有限公司已完成注册。该公司经营范围为铝业相关产品及服务的生产、加工、销售、进口和出口。</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>铝业公司完成注册</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>sh603686</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福龙马  </t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>10.0284</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>与华为云合作自驾|福龙马公告称，公司与华为云计算技术有限公司签署环卫自动驾驶技术开发合同，合同总金额2亿元(含税)，有效期3年。双方将基于公司业务需求，针对3吨级和6吨级车型平台、清扫和洗扫业务场景，由华为云计算为公司独家研发和部署“福龙马环卫自动驾驶系统”。</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>与华为云合作自驾</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>sz001317</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>三羊马</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>10.0101</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>物流+谐音“羊”|公司是一家主要通过公铁联运方式为汽车行业和啤酒、饮料、洗涤用品等非汽车行业提供综合服务的第三方物流企业，建成以重庆为龙头，以柳州、西安、兰州、乌鲁木齐等为支点，串联“一带一路”沿线节点城市，横贯中西部地区，联系亚欧大陆的流通大通道。</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>物流, 谐音“羊”</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>sh600343</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>航天动力</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>军工+商业航天|公司是航天六院唯一的资产证券化平台。航天六院是我国液体火箭发动机研制中心和专业抓总单位，承担着为我国运载火箭和导弹武器提供液体火箭发动机的重任。</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>军工, 商业航天</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>sz002623</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>亚玛顿</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>9.9762</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>光伏+玻璃基板|1.国内光伏镀膜玻璃、大尺寸超薄光伏玻璃产品的先行及引领者，在行业内率先开发了更加轻量化、薄型化的1.6mm的光伏玻璃、BIPV美学、彩色镀膜玻璃、玻璃扩散板、一体化AG玻璃等具有核心竞争力的产品。
+2.2023年9月16日公司在官微透露，超高清玻璃基板产业项目占地800亩，由常州亚玛顿股份有限公司建设，主要建设年产5800万平方米的超高清玻璃基板生产基地。生产的超高清玻璃基板厚度为0.55毫米至1.1毫米，广泛应用于超高清电视、智能手机、电脑等智能电子产品显示屏制造。</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>光伏, 玻璃基板</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>sh600847</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>万里股份</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>10.0395</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>铅酸蓄电池|公司是中国铅酸蓄电池行业首家上市公司，以生产“万里”牌各型铅酸蓄电池闻名于世，被誉为“中国蓄能专家”。</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>铅酸蓄电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>sz002005</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>德豪润达</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>9.917400000000001</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>LED|小家电及LED双主营业务。是国内拥有包括LED芯片、LED封装、LED应用产品(照明和显示)、照明品牌及渠道在内的LED全产业链布局的极少数企业之一。</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>sz001332</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锡装股份</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>10.0114</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>核电+光伏|1.公司向全球知名核电企业法马通销售金属压力容器，该等产品用于红沿河核电站、防城港核电站、阳江核电站等国内外多个大型核能发电项目。
+2.公司已经与多家大型多晶硅企业建立了良好的合作关系，获得了高端换热器产品及关键反应器产品的订单。</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>核电, 光伏</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>sh600719</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>大连热电</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>10.0654</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>热电|公司是大连地区供热、供电联产龙头企业，装机容量10万千瓦，年上网电量1.53亿千瓦时，供热面积达1839万平方米，主要产品有电力和热力两大类，共有电力、工业蒸汽、高温水和供暖四个品种。</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>热电</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>sh600881</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>亚泰集团</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>10.2857</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>中药+水泥|1.公司生产范围涵盖现代中药、中药饮片、化药、生物制品、医疗器械和保健食品等，形成了以“参一胶囊”单体抗癌中药、“消栓通络胶囊”“丹黄祛瘀胶囊”等国家中药保护品种为主的中成药，以亚泰大连水产维生素AD滴剂、维生素D2为主的系列维生素，以及“亚泰康派”品牌系列保健食品等特色化的产品群。
+2.公司建材产业拥有集“石灰石、熟料、水泥、混凝土、预制构件、骨料”业务于一体的绿色建材产业链。</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>中药, 水泥</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>sh600261</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>阳光照明</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>10.0313</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>节能灯|公司是中国最大的节能灯生产和出口基地之一，国家级高新技术企业。主要生产紧凑型节能荧光灯、电子节能灯、直管型荧光灯、T5大功率节能荧光灯及配套灯具、CCFL荧光屏背景光源及各类台灯系列。</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>节能灯</t>
         </is>
       </c>
     </row>
@@ -2793,7 +4168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2820,31 +4195,31 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sh605058</t>
+          <t>sh603248</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>锡华科技</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz003026</t>
+          <t>sz001216</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>中晶科技</t>
+          <t>华瓷股份</t>
         </is>
       </c>
     </row>
@@ -2854,12 +4229,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh603248</t>
+          <t>sh603230</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>锡华科技</t>
+          <t>内蒙新华</t>
         </is>
       </c>
     </row>
@@ -2869,12 +4244,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz001216</t>
+          <t>sz002285</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>世联行</t>
         </is>
       </c>
     </row>
@@ -2884,12 +4259,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh600371</t>
+          <t>sh603626</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>万向德农</t>
+          <t>科森科技</t>
         </is>
       </c>
     </row>
@@ -2899,12 +4274,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz003001</t>
+          <t>sz002453</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>中岩大地</t>
+          <t>华软科技</t>
         </is>
       </c>
     </row>
@@ -2914,12 +4289,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sz002655</t>
+          <t>sh600448</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>共达电声</t>
+          <t>华纺股份</t>
         </is>
       </c>
     </row>
@@ -2929,12 +4304,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sz002285</t>
+          <t>sz301390</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>世联行</t>
+          <t>经纬股份</t>
         </is>
       </c>
     </row>
@@ -2944,12 +4319,57 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sh603230</t>
+          <t>sz000504</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>南华生物</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>sz002836</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>新宏泽</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>sh600630</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>龙头股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>sh600127</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金健米业</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,20 +476,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="97" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="247" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="293" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,2120 +552,2133 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.7686</v>
+        <v>4.1012</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz002453</t>
+          <t>sz000504</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>华软科技</t>
+          <t>南华生物</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5.34</v>
+        <v>11.01</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.1031</v>
+        <v>9.99</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>光刻胶基材|关于公司相关的光刻胶基材产品业务，目前正处于客户接洽阶段，已有少量试订单。</t>
+          <t>医药+“华”字辈|公司是目前国内一家国资控股的干细胞、免疫细胞及组织工程产业主板上市公司，“生物医药”板块业务包括干细胞储存服务、化妆品的生产和销售、医疗器械设备及耗材的代理和销售。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>光刻胶基材</t>
+          <t>医药, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.7686</v>
+        <v>4.1012</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh603353</t>
+          <t>sz002589</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>和顺石油</t>
+          <t>瑞康医药</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>48.55</v>
+        <v>3.6</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.9909</v>
+        <v>10.0917</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>石油+先进封装|1.公司是湖南省第一家获国家商务部批准取得成品油批发资质的民营石油企业，主营成品油批发零售，业务涵盖成品油采购、仓储、物流、批发、零售环节，在成品油流通领域形成完整产业链。
-2.2025年11月16日晚公告，公司拟以现金收购及增资方式取得上海奎芯集成电路设计有限公司不低于34%股权并通过表决权委托合计控制其51%表决权，交易完成后奎芯科技将纳入合并报表，布局高速接口IP及Chiplet解决方案。</t>
+          <t>创新药|公司与广东药科大学相关医学专家合作，共同合作研发治疗非酒精性肝脂肪变中医新药FTZ浓缩丸，2024年内已进入临床二期阶段。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>石油, 先进封装</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.7686</v>
+        <v>4.1012</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh603120</t>
+          <t>sh600721</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>肯特催化</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>59.21</v>
+        <v>13.15</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.994400000000001</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
+        <v>10.0418</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>光刻胶显影液|公司的电子级季铵碱可应用于光刻胶显影液等湿电子化学品。</t>
+          <t>CXO|公司主营业务为药物发现、研究、技术服务，提供从药物发现、CMC、临床CRO、药品注册、CMO/API供应等新药开发全流程的服务及一体化的解决方案。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>光刻胶显影液</t>
+          <t>CXO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.7686</v>
+        <v>4.1012</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh603068</t>
+          <t>sz000756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>博通集成</t>
+          <t>新华制药</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>39.81</v>
+        <v>14.67</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.0028</v>
+        <v>9.969999999999999</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>端侧AI芯片|公司依托在AI无线通信的经验和技术积累，将研发资源拓展至端侧AI算力。公司发布的BK7259作为AIoT算力标杆，率先集成ARM Ethos-U65 microNPU的Wi-Fi 6 MCU，为边缘智能应用注入超强算力与卓越能效。</t>
+          <t>医药+“华”字辈|公司围绕心脑血管类、解热镇痛类、消化系统类、抗代谢类、神经系统、精麻药品等方向开展研发工作，包括创新药物和仿制药。进入研发管线的药物有100多个。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>端侧AI芯片</t>
+          <t>医药, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2.7686</v>
+        <v>4.1012</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh603316</t>
+          <t>sh600664</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>诚邦股份</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>16.69</v>
+        <v>8.25</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.0198</v>
+        <v>10</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>存储芯片|公司旗下芯存科技主要从事半导体存储器的研发设计、封装测试、生产和销售，已量产并销售的主要产品为移动存储（包括TFCARD、USB模块等）、固态硬盘（包括SATASSD、PCIESSD、PSSD）等。芯存科技整合了包括芯源科技在内的相关业务资源，致力于构筑芯片封测、存储模组产品研发生产一体化的经营模式，布局嵌入式存储、内存条等产品，打造完善的闪存存储产品矩阵，在存储介质特性研究、固件算法开发、存储芯片封测、测试研发等方面打造综合竞争力。</t>
+          <t>创新药|在创新药研发领域，公司制定了研发的短中长期规划，涉及心血管、代谢、呼吸、抗感染和抗肿瘤等领域，积极探索产品研发新路径，全面丰富公司产品线。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>存储芯片</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.7686</v>
+        <v>4.1012</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz002185</t>
+          <t>sh688315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>诺禾致源</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>18.03</v>
+        <v>18.18</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.0061</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>先进封装|公司的主营业务为集成电路封装测试，产品主要有DIP/SDIP、SOT、SOP、SSOP、TSSOP/ETSSOP、QFP/LQFP/TQFP、QFN/DFN、BGA/LGA、FC、MCM（MCP）、SiP、WLP、TSV、Bumping、MEMS、Fan-Out等多个系列。</t>
+          <t>AI制药|公司开发了基于GBLUP、BA、BB、BC、RRBLUP、SVR、DNNGP、BRR、BL等九种模型的育种值预测体系、建设了基于KNN、随机森林、分类回归树、PLS、SVM、朴素贝叶斯等五种机器学习算法的精准品种鉴定架构。这些举措构建了坚实的技术框架，扩展了分子育种的发展空间。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>先进封装</t>
+          <t>AI制药</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.7686</v>
+        <v>4.1012</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh601026</t>
+          <t>sh600613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>道生天合</t>
+          <t>神奇制药</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15.95</v>
+        <v>9.25</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10</v>
+        <v>9.988099999999999</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>半导体材料+次新|参股上海道宜半导体材料有限公司主营业务为环氧塑封材料（EMC），该产品属于半导体传统封装环节的常规材料。</t>
+          <t>医药|公司的主营业务为药品的研发、生产与销售，产品涉及抗肿瘤、感冒止咳、心脑血管、风湿骨病、抗真菌、补益安神及妇科等治疗领域。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>半导体材料, 次新</t>
+          <t>医药</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.7686</v>
+        <v>4.1012</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz001399</t>
+          <t>sz002349</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>惠科股份</t>
+          <t>精华制药</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>23.17</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.019</v>
+        <v>9.9747</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>先进封装|2026年7月17日公告，公司与杭绍临空经济一体化发展示范区绍兴片区管理委员会就开展惠科先进封装及测试项目签署《先进封装及测试项目合作协议》，出资40亿元设立全资子公司浙江惠芯先进半导体有限公司（暂定名）作为项目实施主体。项目分二期建设，其中项目一期计划建设12寸混合芯片先进封装及测试，全部达产后，达到2000万颗/月产能，预计项目建设周期不超过三年。</t>
+          <t>医药+“华”字辈|公司正成为国家在原料药、医药中间体和西药与中成药制剂生产销售和研发方面的主力企业，中药产品主要有传统名牌中药季德胜牌季德胜蛇药片、南通牌王氏保赤丸、宁宁牌正柴胡饮颗粒、汉方传奇的大柴胡颗粒，以及国家中药保护品种固本咳喘片、晕可平糖浆、金荞麦片等。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>先进封装</t>
+          <t>医药, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.7686</v>
+        <v>4.1012</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh601133</t>
+          <t>sz300642</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>柏诚股份</t>
+          <t>透景生命</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>26</v>
+        <v>20.35</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>9.9831</v>
+        <v>19.9882</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>洁净室系统集成|公司主要专注于为高科技产业的建厂、技改等项目提供专业的洁净室系统集成整体解决方案，覆盖半导体及泛半导体、新型显示、生命科学、食品药品大健康等国家重点产业。</t>
+          <t>医药|公司主要从事自主品牌体外诊断产品的研发、生产与销售，产品主要涉及肿瘤全程检测、自身免疫、心血管疾病、病原体感染及生殖健康等为主要应用方向的多系列产品。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>洁净室系统集成</t>
+          <t>医药</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2.7686</v>
+        <v>4.1012</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz002971</t>
+          <t>sh600812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>和远气体</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>42.68</v>
+        <v>5.08</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10</v>
+        <v>9.9567</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>电子特气|公司电子特气产品涵盖了硅基、氟基、氨基、氯基、碳基五大系列，主要产品有电子级三氟化氮、六氟化钨、三氯氢硅、二氯二氢硅、四氯化硅、正硅酸乙酯、硅烷、乙硅烷，电子级超纯氨、电子级氯化氢、电子级氯气、电子级甲烷、电子级一氧化碳、高纯羰基硫等，产品广泛应用于集成电路、显示面板、LED、光伏、光纤、动力电池、人工智能等新兴产业。</t>
+          <t>创新药+“华”字辈|公司是我国最早进入生物制药领域的制药企业之一，拥有微生物药物国家工程研究中心、抗体药物研制国家重点实验室、抗生素酶催化与结晶技术国家地方联合工程实验室三个国家级研发平台，以基因重组抗狂犬抗体为代表的生物技术药物技术水平处于国内行业领先地位。2022年1月自主研发的国家一类新药奥木替韦单抗获批上市，填补了我国狂犬病毒单抗市场的空白。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>电子特气</t>
+          <t>创新药, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2.7686</v>
+        <v>4.1012</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz301583</t>
+          <t>920478.BJ</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>托伦斯</t>
+          <t>峆一药业</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>142.56</v>
+        <v>12.38</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>20</v>
+        <v>29.9056</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>次新+半导体设备|托伦斯是国内领先的精密金属零部件综合服务商，专注于半导体设备关键工艺零部件的研发、生产和销售，产品覆盖薄膜沉积、刻蚀设备等核心半导体设备，包括腔体、内衬、加热器、匀气盘、静电卡盘基体等关键零部件。</t>
+          <t>AI制药|旗下上海安睿鸿生物医药科技有限公司经营范围包含：人工智能通用应用系统、人工智能基础软件开发、人工智能基础资源与技术平台等。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>次新, 半导体设备</t>
+          <t>AI制药</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.7686</v>
+        <v>4.1012</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>据报道，业内人士16日透露，有韩国半导体制造设备关键零部件的交货周期已延长了一倍以上。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603375</t>
+          <t>sh600587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">盛景微  </t>
+          <t>新华医疗</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>51.69</v>
+        <v>13.4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.0021</v>
+        <v>10.0164</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>民爆+芯片|公司是一家具备高性能、超低功耗芯片设计能力的电子器件提供商，主要产品为工业安全领域的电子控制模块。公司销售的产品包括电子控制模块、起爆控制器、放大器等。</t>
+          <t>医药+“华”字辈|公司以医疗器械及装备、制药装备、医疗服务为主要业务板块。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>民爆, 芯片</t>
+          <t>医药, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2.5704</v>
+        <v>4.1012</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz002161</t>
+          <t>sz002022</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>远 望 谷</t>
+          <t>科华生物</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>7.25</v>
+        <v>6.17</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.0152</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6天3板</t>
-        </is>
-      </c>
+        <v>9.982199999999999</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>光通信测试|远望谷公告称，公司与深圳光泰通信设备有限公司及其股东签订股权投资意向书，拟收购光泰通信100%股权。标的公司主要业务包括为客户提供光通信器件与模块的自动化耦合设备和测试仪表、自动化测试解决方案。</t>
+          <t>医药+“华”字辈|公司是国内首家在深圳证券交易所中小板上市的诊断用品专业公司，融产品研发、生产、销售于一体，拥有医疗诊断领域完整产业链。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>光通信测试</t>
+          <t>医药, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2.5704</v>
+        <v>4.1012</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh603725</t>
+          <t>sz002907</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>天安新材</t>
+          <t>华森制药</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>11.75</v>
+        <v>15.25</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.0187</v>
+        <v>10.0289</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>光通信+机器人|1.2026年6月，公司官网披露，完成对烁光精密参股。烁光精密主要产品包括2D垂直/倾斜孔阵列、多通道V槽阵列、三维光波导，为光互连与集成封装提供超精密定位解决方案。
-2.公司在电子皮肤相关领域仍处于技术探索和研究阶段。</t>
+          <t>医药+“华”字辈|公司专注于肿瘤、肿瘤免疫以及自勉性疾病领域的小分子药物开发，已具备从靶点发现至早期临床开发的创新药研发能力，在研管线潜在适应症覆盖肿瘤免疫以及肺癌、乳腺癌、结直肠癌、胰腺癌等多种实体瘤。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>光通信, 机器人</t>
+          <t>医药, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2.5704</v>
+        <v>4.1012</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz001229</t>
+          <t>sh688026</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>魅视科技</t>
+          <t>洁特生物</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>39.99</v>
+        <v>25.22</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.0138</v>
+        <v>19.981</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>AI应用+磷化铟|1.目前公司已经在视听产品中应用人工智能相关功能，如融入到业务流程的坐席人脸登录、现场恢复、坐席引导、语音指挥、隔空指挥、视频分析、数据AI识别采集等。
-2.2026年8月5日公告，公司已成立全资子公司珠海明曜新材料科技有限公司作为实施主体，注册资本1000万元，拟开展磷化铟半导体材料产业化项目的前期准备工作。</t>
+          <t>医疗器械+半导体|1.公司是主要从事细胞培养类及与之相关的液体处理类生物实验室一次性塑料耗材研发、生产和销售的高新技术企业，主要产品包括生物培养和液体处理两大类生物实验室一次性塑料耗材，并配有少量试剂、小型实验仪器等，涉及逾千种产品。
+2.公司的过滤产品除了生物过滤以外，其在半导体生产封测、水污染治理等领域内也有着广阔的市场空间，正尝试拓展过滤产品在半导体生产以及水污染治理中的应用。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>AI应用, 磷化铟</t>
+          <t>医疗器械, 半导体</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.5704</v>
+        <v>4.1012</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh603118</t>
+          <t>sz002622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>共进股份</t>
+          <t>皓宸医疗</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>18.43</v>
+        <v>2.72</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.0299</v>
+        <v>10.1215</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>交换机|据2025年9月26日互动易，公司交换机已覆盖100G、400G、800G数据中心产品，800G型号按订单生产并供货国内交换机品牌商。</t>
+          <t>口腔医疗|公司购买德伦医疗51.00%股权。德伦医疗是一家以口腔医疗服务连锁经营为核心，专注于口腔疾病的诊断、治疗以及口腔保健、修复服务等口腔医疗服务的企业。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>交换机</t>
+          <t>口腔医疗</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2.5704</v>
+        <v>4.1012</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz301689</t>
+          <t>sz002900</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>电科思仪</t>
+          <t>哈三联</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>63</v>
+        <v>13.04</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>20</v>
+        <v>10.0422</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>次新+光模块测试|2026年9月9日根据公司官微透露，公司携1.6T/3.2T高速光芯片/光模块综合测试、波长扫描测试系统、光通信激光特性测试、高速光芯片/光器件测试诊断、光纤接续等五大自研核心解决方案集中亮相2026年中国国际光电博览会。</t>
+          <t>创新药|2025年5月14日公司在调研中表示，公司以临床需求为导向,围绕自身研发管线与前沿科学,持续在神经系统、慢病、肿瘤等领域加大投入,致力于通过研发创新,攻克关键药物技术,不断推出临床迫切需要的高品质新产品,进一步巩固公司在核心治疗领域的优势地位。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>次新, 光模块测试</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2.5704</v>
+        <v>4.1012</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz002980</t>
+          <t>sz000566</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>华盛昌</t>
+          <t>海南海药</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>128.03</v>
+        <v>5.07</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10.0009</v>
+        <v>9.978299999999999</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>光芯片测试|2026年2月27日公告，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。同时，公司控股股东袁剑敏拟向伽蓝特创始股东余新文协议转让公司5%股份，协议转让事项以目标公司收购事项完成为实施的前提条件。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域，本次股权收购为公司产业布局横向延伸。</t>
+          <t>创新药|公司主要产品包括以下系列，分别为抗生素系列、胃肠道用药系列、抗肿瘤药系列、与制剂配套的原料药和中间体系列及其他产品。公司的创新药项目：抗癫痫1类创新药派恩加滨片已完成Ⅰ期临床试验，已启动派恩加滨片Ⅱa期临床研究。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>光芯片测试</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>纺织服装</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.5433</v>
+        <v>4.1012</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>近期机构研报指出，轻工出口链韧性仍强，低估值高分红内需龙头具备防御价值；新消费标的随新品周期启动和团队改革，基本面修复弹性值得关注。</t>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh600448</t>
+          <t>sz300110</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>华纺股份</t>
+          <t>华仁药业</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>3.54</v>
+        <v>3.29</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.937899999999999</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>20.073</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>印染加工|公司以印染加工为主业，形成包含纺纱、服装、家纺成品、纺织贸易、品牌开发、“B2B”平台、金融投资及热电等业务的多元化发展模式。</t>
+          <t>医药+“华”字辈|公司是一家集研发、生产、销售为一体的，以精麻科、呼吸科、肾科、治疗性大容量制剂、医疗器械等产品为主线，以基础输液、大健康产品为两翼，原料药、制剂、医药包材、医疗器械等板块全面协同发展的国有控股医药健康产业集团。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>印染加工</t>
+          <t>医药, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>4.1012</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>sh688137</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>近岸蛋白</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>118.84</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>20.004</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI制药|公司创新性地将AI工具与自主研发的机器学习系统深度融合，提高了研发创新的效率，广泛应用于酶、抗体等蛋白质的创新设计、改造和表达，以及抗体亲和力和稳定性改造噬菌体库等技术领域。 </t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>AI制药</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>4.1012</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>9月18日，工信部等十部门联合印发《医药工业发展“十五五”规划》。规划提出，加快人工智能、量子计算、超级计算、计算医学等新技术赋能药物研发。</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>sz002755</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>奥赛康</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>9.982299999999999</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>创新药|公司是一家创新与研发驱动的医药制造企业，公司药物治疗领域主要覆盖消化、抗肿瘤、抗感染、慢性病四大领域，业务涵盖原料药及制剂的研发、生产、销售，在中国医药细分市场具有较高的品牌影响力。</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1.1888</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>据瑞银最新估算，2026年全球AI资本支出总额将达9980亿美元，较2025年的5060亿美元几乎翻倍。这一预测的大幅上修，主要源于内存价格的快速攀升。</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>sz002453</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>华软科技</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>9.9251</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>光刻胶+“华”字辈|关于公司相关的光刻胶基材产品业务，目前正处于客户接洽阶段，已有少量试订单。</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>光刻胶, “华”字辈</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>1.1888</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>据瑞银最新估算，2026年全球AI资本支出总额将达9980亿美元，较2025年的5060亿美元几乎翻倍。这一预测的大幅上修，主要源于内存价格的快速攀升。</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>sh603316</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>诚邦股份</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>10.006</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>存储芯片|公司旗下芯存科技主要从事半导体存储器的研发设计、封装测试、生产和销售，已量产并销售的主要产品为移动存储（包括TFCARD、USB模块等）、固态硬盘（包括SATASSD、PCIESSD、PSSD）等。芯存科技整合了包括芯源科技在内的相关业务资源，致力于构筑芯片封测、存储模组产品研发生产一体化的经营模式，布局嵌入式存储、内存条等产品，打造完善的闪存存储产品矩阵，在存储介质特性研究、固件算法开发、存储芯片封测、测试研发等方面打造综合竞争力。</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>存储芯片</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1.1888</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>据瑞银最新估算，2026年全球AI资本支出总额将达9980亿美元，较2025年的5060亿美元几乎翻倍。这一预测的大幅上修，主要源于内存价格的快速攀升。</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>sh603068</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>博通集成</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>9.997499999999999</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>端侧AI芯片|公司依托在AI无线通信的经验和技术积累，将研发资源拓展至端侧AI算力。公司发布的BK7259作为AIoT算力标杆，率先集成ARM Ethos-U65 microNPU的Wi-Fi 6 MCU，为边缘智能应用注入超强算力与卓越能效。</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>端侧AI芯片</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>1.1888</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>据瑞银最新估算，2026年全球AI资本支出总额将达9980亿美元，较2025年的5060亿美元几乎翻倍。这一预测的大幅上修，主要源于内存价格的快速攀升。</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>sz002388</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>新亚制程</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>9.958500000000001</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>锂电池+半导体|1.杉杉新材料为新亚新能源的控股子公司、公司的间接控股公司。杉杉新材料具有较好的市场竞争力和盈利能力，现有电解液产能3万吨、六氟磷酸锂产能2000吨，在建电解液产能3万吨、六氟磷酸锂产能4000吨。
+2.公司的底部填充胶COO602系列用于BGA、CSP和Flip chip底部填充制程，不仅可以助力电子产品的抗跌落性，还具有一定的导热的可靠性，在产品封装解决方案中起到非常重要的作用。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>锂电池, 半导体</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1.1888</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>据瑞银最新估算，2026年全球AI资本支出总额将达9980亿美元，较2025年的5060亿美元几乎翻倍。这一预测的大幅上修，主要源于内存价格的快速攀升。</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>sz002869</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>金溢科技</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>10.0065</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">功率半导体|参股11.25%的深圳镓华微电子主营业务包括硅衬底GaN功率芯片等，其器件技术性能指标国内外领先。
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>功率半导体</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>1.1888</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>据瑞银最新估算，2026年全球AI资本支出总额将达9980亿美元，较2025年的5060亿美元几乎翻倍。这一预测的大幅上修，主要源于内存价格的快速攀升。</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>sh603663</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>三祥新材</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>10.0022</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>锆+半导体材料|1.电熔氧化锆龙头企业，拥有普通电熔氧化锆、高纯电熔氧化锆、稳定电熔氧化锆、特种电熔氧化锆等系列产品，产品广泛应用于耐火耐磨材料、陶瓷色釉料、锆基刹车片、电子、机械、钢铁、化工等领域。
+2.公司产出的锆铪产品均为4N级以上产品，已将部分产品向下游半导体领域客户送样。</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>锆, 半导体材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1.1888</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>据瑞银最新估算，2026年全球AI资本支出总额将达9980亿美元，较2025年的5060亿美元几乎翻倍。这一预测的大幅上修，主要源于内存价格的快速攀升。</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>sz300691</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>联合光电</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>机器人+光刻机|1.公司研制机器人产品有智能消杀机器人、智能服务机器人、安保巡逻机器人等。
+2.公司具备生产制造光刻机镜头的技术和能力，公司的光刻机镜头技术为自主研发。</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 光刻机</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>1.1888</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>据瑞银最新估算，2026年全球AI资本支出总额将达9980亿美元，较2025年的5060亿美元几乎翻倍。这一预测的大幅上修，主要源于内存价格的快速攀升。</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>920427.BJ</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>华维设计</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>29.9176</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>半导体+“华”字辈|2025年1月7日公告，公司拟以6300万元价格收购廖红伟持有的九江正启微电子有限公司51%股权。九江正启主要为集成电路设计企业提供集成电路封装与测试服务，并收取封装和测试服务加工费，标的公司拥有独栋标准化厂房及1万多平方米的无尘车间，可实现磨片、划片、上片、打线、电镀、塑封、切筋、打标、测试、编带等集成电路封装测试工艺流程。</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>半导体, “华”字辈</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>房地产概念</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>3.4147</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高。</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>sz002285</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>世联行</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>10.0346</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>房地产|公司专注房地产服务业，凭借对行业发展的理解和客户需求的认知，叠加了金融、资管、互联网+（电商）等创新服务。</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>房地产概念</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>3.4147</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高。</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>sh600606</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>绿地控股</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>10.3448</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>房地产|公司是一家总部位于中国上海的跨国经营企业，同时也是中国首家以房地产为主业并跻身《财富》世界500强的综合性企业集团。</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>房地产概念</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>3.4147</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高。</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>sh600743</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>9.905700000000001</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>房地产+“华”字辈|2025年4月，公司完成了重大资产重组，已将持有的房地产开发业务相关资产及负债转让至公司控股股东华远集团，实现了从重资产开发商向轻资产服务商的价值重构。</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>房地产, “华”字辈</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>房地产概念</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>3.4147</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高。</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>sz000020</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>深华发Ａ</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>10.0309</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>房地产+“华”字辈|公司在深圳市福田区华强北商圈及光明新区公明街道均拥有数万平方米的大型物业。</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>房地产, “华”字辈</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>房地产概念</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>3.4147</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高。</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>sz000560</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>我爱我家</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>房地产|地产平台运营商，基于二十余年的锐意进取，以专业、安全、高效的运营管理体系为支撑，为客户提供高品质、一站式的居住全生命周期综合服务。</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>房地产概念</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>3.4147</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高。</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>sh600325</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>华发股份</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>10.0806</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>房地产+“华”字辈|公司主营业务为房地产开发与经营，拥有房地产一级开发资质。</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>房地产, “华”字辈</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>房地产概念</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>3.4147</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高。</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>sz000402</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>金 融 街</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>9.9206</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>房地产|公司是一家以商务地产为主业的大型国有控股公司，拥有北京西城区金融街规划区商业地产独家开发权。</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>纺织服装</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>1.5433</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>近期机构研报指出，轻工出口链韧性仍强，低估值高分红内需龙头具备防御价值；新消费标的随新品周期启动和团队改革，基本面修复弹性值得关注。</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="B38" s="2" t="n">
+        <v>2.2801</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>据中国纺织品进出口商会消息，1-7月，我国家用纺织品累计出口196.4亿美元，同比增长3.7%。</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>sh600630</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>龙头股份</t>
         </is>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>9.946899999999999</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="G38" s="2" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>10.0121</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>上海本地+纺织|1.东方国际（集团）有限公司控股子公司上海纺织集团旗下上市公司。公司以品牌经营和国际贸易为主营业务。
 2.自主品牌业务包括以三枪、ELSMORR、鹅牌、菊花、海螺、民光、皇后、凤凰、钟牌414等品牌为主的针织、服饰、家纺类产品的经营。</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>上海本地, 纺织</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>纺织服装</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>1.5433</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>近期机构研报指出，轻工出口链韧性仍强，低估值高分红内需龙头具备防御价值；新消费标的随新品周期启动和团队改革，基本面修复弹性值得关注。</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>sz003041</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>真爱美家</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>42.02</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>家用纺织品|公司主要从事以毛毯为主的家用纺织品的研发、设计、生产与销售，主要产品为毛毯及床上用品（套件、被芯、枕芯等）。</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>家用纺织品</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>纺织服装</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>1.5433</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>近期机构研报指出，轻工出口链韧性仍强，低估值高分红内需龙头具备防御价值；新消费标的随新品周期启动和团队改革，基本面修复弹性值得关注。</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>sh603001</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>奥康国际</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>10.0211</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>鞋类|主要从事皮鞋及皮具产品的研发、生产、零售及分销业务,产品种类主要有商务正装鞋、休闲鞋、运动鞋等鞋类产品以及皮具配套产品。公司实施以“奥康”品牌为主, “康龙”、 “斯凯奇”等品牌为辅的多品牌运营策略。主品牌“奥康”在男鞋领域具有较强的市场竞争力。</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>鞋类</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>纺织服装</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>1.5433</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>近期机构研报指出，轻工出口链韧性仍强，低估值高分红内需龙头具备防御价值；新消费标的随新品周期启动和团队改革，基本面修复弹性值得关注。</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>sz001238</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>浙江正特</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>26.31</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>9.9916</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>遮阳制品|公司现拥有遮阳制品、户外休闲家具两大产品系列，其中遮阳制品主要包括星空篷、遮阳篷和遮阳伞，户外休闲家具主要包括户外家具、储物用品、宠物屋。</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>遮阳制品</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>纺织服装</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>1.5433</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>近期机构研报指出，轻工出口链韧性仍强，低估值高分红内需龙头具备防御价值；新消费标的随新品周期启动和团队改革，基本面修复弹性值得关注。</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>sz002029</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>七 匹 狼</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>10.0244</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>纺织+参股宇树|1.主要从事“七匹狼”品牌男装的设计、生产和销售,主要产品包括衬衫、西服、裤装、茄克衫、针织衫等。
-2.公司母公司间接持有摩尔线程和宇树科技的部分股权。</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>纺织, 参股宇树</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>次新股</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>5.9091</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>C沈鼓早盘一度跌近30%，随后持续拉升，一度翻红，带动整个次新板块情绪。</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>sh603248</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>锡华科技</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>24.57</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>9.982099999999999</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>次新+风电|公司主要从事大型高端装备专用部件的研发、制造与销售，产品结构以风电齿轮箱专用部件为主、注塑机厚大专用部件为辅，是全球行业领先、质量可靠、技术卓越的大型高端装备专用部件制造商。</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>次新, 风电</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>次新股</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>5.9091</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>C沈鼓早盘一度跌近30%，随后持续拉升，一度翻红，带动整个次新板块情绪。</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>sz001233</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>海安集团</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>45.58</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>9.990300000000001</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>次新+福建+轮胎|公司的主营业务包括巨型全钢工程机械子午线轮胎的研发、生产与销售，以及矿用轮胎运营管理业务，现已具备全系列型号全钢巨胎（轮辋直径49英寸及以上）的生产技术和量产能力，为国内外上百个矿山提供了全钢巨胎产品或服务。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>次新, 福建, 轮胎</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>次新股</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>5.9091</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>C沈鼓早盘一度跌近30%，随后持续拉升，一度翻红，带动整个次新板块情绪。</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>sh603402</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>陕西旅游</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>64.19</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>10.0086</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>次新+旅游|公司依托华清宫、华山等国家5A级景区，为游客提供高品质的旅游产品及服务体验。在旅游演艺业务方面，公司打造了中国首部大型实景历史舞剧《长恨歌》、大型实景影画《12·12西安事变》、大型红色实景演艺《泰山烽火》等优质旅游演艺作品。</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>次新, 旅游</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>次新股</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>5.9091</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>C沈鼓早盘一度跌近30%，随后持续拉升，一度翻红，带动整个次新板块情绪。</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>sh601123</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>马矿股份</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>17.78</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>10.0248</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>次新+福建+铁矿石|公司是一家长期从事铁矿资源开发及综合利用的企业，主营铁矿石的采选、综合利用及铁精粉、钼精矿销售，石灰石的开采和销售。</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>次新, 福建, 铁矿石</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>次新股</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>5.9091</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>C沈鼓早盘一度跌近30%，随后持续拉升，一度翻红，带动整个次新板块情绪。</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>920298.BJ</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>腾信精密</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>90.48</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>北交所次新|腾信精密定位于“全球精密零部件及组件制造专家”，专注高附加值精密零部件的研发设计、制造与销售，以高精度及高温合金复杂结构机加工、激光熔覆、柔性自动化技术为核心竞争力。</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>北交所次新</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>机器人概念</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>1.7548</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉相关团队已于9月16日落地宁波，并于9月17日开启新一轮针对旗下机器人业务的量产审厂工作。</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>sh603626</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>科森科技</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>10.0047</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>机器人+折叠屏|1.公司不生产机器人产品，公司为某品牌家用机器人提供相关结构件。
-2.公司生产的折叠屏手机铰链已量产。</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>机器人, 折叠屏</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>机器人概念</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>1.7548</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉相关团队已于9月16日落地宁波，并于9月17日开启新一轮针对旗下机器人业务的量产审厂工作。</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>sz000910</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>大亚圣象</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>10.058</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>参股七腾机器人|公司以自有资金1,500万元人民币认购嘉兴翼龙股权投资合伙企业 （有限合伙）28.30189%的份额，该基金以股权投资的方式投资七腾机器人有限公司。</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>参股七腾机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>机器人概念</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>1.7548</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉相关团队已于9月16日落地宁波，并于9月17日开启新一轮针对旗下机器人业务的量产审厂工作。</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>sz002965</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>祥鑫科技</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>10.0071</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>机器人+液冷|1.公司已为优必选和库卡供应金属结构件相关产品。在工业机器人领域，公司旗下的东莞市荣升自动化系统有限公司拥有生产电池托盘相关产品的柔性化产线、焊接机器人工作站及其他非标金属结构件产品。
-2.公司的埋管式水冷板、水冷散热器、新能源散热器、剖沟散热器等产品可应用于GPU冷却、服务器冷却和IDC数据中心以及汽车领域。</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>机器人, 液冷</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>机器人概念</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>1.7548</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉相关团队已于9月16日落地宁波，并于9月17日开启新一轮针对旗下机器人业务的量产审厂工作。</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>sz000410</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>沈阳机床</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>10.0791</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>工业母机+机器人|1.公司主营业务包括产品研发、机床制造、销售服务、行业解决方案、机床零部件配套等，可面向机械制造核心领域提供量大面广的通用型机床。
-2.子公司沈阳优尼斯智能装备有限公司经营范围包括机器人产品的技术开发、制造。</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>工业母机, 机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>机器人概念</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>1.7548</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉相关团队已于9月16日落地宁波，并于9月17日开启新一轮针对旗下机器人业务的量产审厂工作。</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>sh600577</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>精达股份</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>9.962200000000001</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>机器人+高速线|1.公司有部分产品应用于机器人伺服电机。
-2.子公司恒丰特导生产的高速线主要用于数据中心、5G信号基站等高速信息传输领域。</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>机器人, 高速线</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>网络安全</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>2.307</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>《半导体存储介质块擦除技术指引》《电子产品回收过程中的信息清除管理指引》《移动智能终端信息清除技术指引》等3项网络安全标准实践指南正式向社会发布。</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>sh603138</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>海量数据</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>10.0353</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>数据安全|数据库是公司的核心业务，主要针对客户的实际需求，在满足性能、安全、连续性的前提下，提供最优的数据库资产配置。公司高度重视自主创新，专注做好数据库，相继研发并推出了一系列高性能、高可用、高安全的数据库产品。</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>数据安全</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>网络安全</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>2.307</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>《半导体存储介质块擦除技术指引》《电子产品回收过程中的信息清除管理指引》《移动智能终端信息清除技术指引》等3项网络安全标准实践指南正式向社会发布。</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>sh688292</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>浩瀚深度</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>23.02</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>20.0209</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI+网络安全|1.公司目前人工智能技术主要应用在网络可视化与智能化中的互联网流量识别、数据提取与分析领域。
-2.公司聚焦于互联网流量的智能化管控和数据应用领域，致力于为电信运营商等各类客户提供全方位、高性能、跨平台的网络智能化及信息安全防护解决方案，为各层级网络的高效、稳定、安全运行提供保障。
-</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>AI, 网络安全</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>网络安全</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>2.307</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>《半导体存储介质块擦除技术指引》《电子产品回收过程中的信息清除管理指引》《移动智能终端信息清除技术指引》等3项网络安全标准实践指南正式向社会发布。</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>sh603232</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>格尔软件</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>9.979799999999999</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>AI+网络安全|1.公司的AI赋能旨在深化AI与密码学、安全、产品三大核心业务的融合,明确推动AI应用从工具引入向范式变革演进,实现“AI赋能效率、创新驱动升级”双重目标。
-2.公司自成立以来一直专注于信息安全行业PKI领域，主要从事以公钥基础设施PKI为核心的商用密码软件产品的研发、生产和销售及服务业务，为用户提供基于PKI的信息安全系列产品、安全服务和信息安全整体解决方案。</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>AI, 网络安全</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>2.307</v>
+        <v>2.2801</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>《半导体存储介质块擦除技术指引》《电子产品回收过程中的信息清除管理指引》《移动智能终端信息清除技术指引》等3项网络安全标准实践指南正式向社会发布。</t>
+          <t>据中国纺织品进出口商会消息，1-7月，我国家用纺织品累计出口196.4亿美元，同比增长3.7%。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh688175</t>
+          <t>sh600448</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>高凌信息</t>
+          <t>华纺股份</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>21.74</v>
+        <v>3.89</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>19.9779</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
+        <v>9.887</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>AI+网络安全|公司已规划研发反诈智能体，主要用于网络内容安全方面的应用。</t>
+          <t>纺织+“华”字辈|公司以印染加工为主业，形成包含纺纱、服装、家纺成品、纺织贸易、品牌开发、“B2B”平台、金融投资及热电等业务的多元化发展模式。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>AI, 网络安全</t>
+          <t>纺织, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1.9628</v>
+        <v>2.2801</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>TrendForce集邦咨询估算，2026年全球数据中心电力需求容量将达161GW，年增约31%，主要增长来源为AI Server，预估占整体需求容量达33.4%。</t>
+          <t>据中国纺织品进出口商会消息，1-7月，我国家用纺织品累计出口196.4亿美元，同比增长3.7%。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sz002300</t>
+          <t>sh603001</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>太阳电缆</t>
+          <t>奥康国际</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>8.67</v>
+        <v>11.47</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10.0254</v>
+        <v>9.9712</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>电线电缆|公司是福建省最大的综合性电线电缆生产基地，通过旗下全资子公司太阳海缆建设海底电缆生产基地。</t>
+          <t>纺织服装|主要从事皮鞋及皮具产品的研发、生产、零售及分销业务,产品种类主要有商务正装鞋、休闲鞋、运动鞋等鞋类产品以及皮具配套产品。公司实施以“奥康”品牌为主, “康龙”、 “斯凯奇”等品牌为辅的多品牌运营策略。主品牌“奥康”在男鞋领域具有较强的市场竞争力。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>电线电缆</t>
+          <t>纺织服装</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1.9628</v>
+        <v>2.2801</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>TrendForce集邦咨询估算，2026年全球数据中心电力需求容量将达161GW，年增约31%，主要增长来源为AI Server，预估占整体需求容量达33.4%。</t>
+          <t>据中国纺织品进出口商会消息，1-7月，我国家用纺织品累计出口196.4亿美元，同比增长3.7%。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sz002298</t>
+          <t>sz001234</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>中电鑫龙</t>
+          <t>泰慕士</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>9</v>
+        <v>26.59</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10.0244</v>
+        <v>10.0124</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>数据中心+电网设备|1.公司与HUAWEI公司签订了战略合作协议，双方在智慧城市、大数据中心等领域进行合作，双方积极推动智慧城市、大数据中心等项目落地。
-2.公司致力于新型储能产品制造和储能系统集成、测试，光伏电站和储能电站项目开发、建设、运维，园区级和企业级能碳管理软件平台和节能降碳解决方案等三大业务板块。公司产品可用于电网的发电端、输电端，配电端及用电端。</t>
+          <t>纺织服装|公司主营业务为针织面料与针织服装的研发、生产和销售，主要产品可以分为运动服装、休闲服装及儿童服装。公司已与森马服饰旗下童装品牌巴拉巴拉建立了战略合作关系并为其提供贴牌加工服务。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>数据中心, 电网设备</t>
+          <t>纺织服装</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>1.9628</v>
+        <v>2.2801</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>TrendForce集邦咨询估算，2026年全球数据中心电力需求容量将达161GW，年增约31%，主要增长来源为AI Server，预估占整体需求容量达33.4%。</t>
+          <t>据中国纺织品进出口商会消息，1-7月，我国家用纺织品累计出口196.4亿美元，同比增长3.7%。</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sz002471</t>
+          <t>sz002042</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>中超控股</t>
+          <t>华孚时尚</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>5.96</v>
+        <v>4.22</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>9.963099999999999</v>
+        <v>9.895800000000001</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>机器人+电力电缆|1.中超控股公告称，公司近日与合肥市智能机器人研究院签订《战略合作协议》，双方将在智能机器人技术合作与产业化应用、航空航天领域高温合金铸造轻量化技术、智能机器人用电线电缆技术开发与应用等方面展开合作。
-2.公司是国内综合线缆供应商，主要产品涵盖从超高压到低压的各类电力电缆、导线及民用电缆。</t>
+          <t>纺织+“华”字辈|公司是全球最大的色纺纱供应商和制造商之一，主营中高档色纺纱线，配套提供高档新型的坯纱、染色纱，同时提供流行趋势、原料与产品认证、技术咨询等增值服务。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>机器人, 电力电缆</t>
+          <t>纺织, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>1.9628</v>
+        <v>1.8023</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>TrendForce集邦咨询估算，2026年全球数据中心电力需求容量将达161GW，年增约31%，主要增长来源为AI Server，预估占整体需求容量达33.4%。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性。</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sh603016</t>
+          <t>sh603230</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">新宏泰  </t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>30.48</v>
+        <v>14.83</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>9.9964</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+        <v>10.0148</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>电网设备|公司主营业务为断路器关键部件，低压断路器及刀熔开关的研发，生产与销售，公司实控人为无锡市人民政府国有资产监督管理委员会。</t>
+          <t>传媒+“华”字辈|公司的最终控制人为内蒙古自治区人民政府。公司主营业务是出版物的批发、零售；文体用品零售；音像制品发行</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>传媒, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1.854</v>
+        <v>1.8023</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>“十五五”时期将推动住房公积金高质量发展。将扩大住房公积金制度覆盖面，支持个体工商户、非全日制从业人员以及其他灵活就业人员自愿缴存住房公积金，进一步增强公积金制度的普惠性。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性。</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz002285</t>
+          <t>sh601811</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>世联行</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>2.89</v>
+        <v>15.29</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>9.885899999999999</v>
+        <v>10</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>房地产|公司专注房地产服务业，凭借对行业发展的理解和客户需求的认知，叠加了金融、资管、互联网+（电商）等创新服务。</t>
+          <t>传媒|公司是我国第一家按照上市公众公司标准规范设立的大型股份制出版发行企业。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>传媒</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>1.854</v>
+        <v>1.8023</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>“十五五”时期将推动住房公积金高质量发展。将扩大住房公积金制度覆盖面，支持个体工商户、非全日制从业人员以及其他灵活就业人员自愿缴存住房公积金，进一步增强公积金制度的普惠性。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性。</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sh600606</t>
+          <t>sz000607</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>绿地控股</t>
+          <t>华媒控股</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>1.45</v>
+        <v>4.53</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>9.8485</v>
+        <v>9.951500000000001</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>房地产|公司是一家总部位于中国上海的跨国经营企业，同时也是中国首家以房地产为主业并跻身《财富》世界500强的综合性企业集团。</t>
+          <t>传媒+AI+“华”字辈|1.公司主要从事广告策划发布、报刊发行与印刷、教育等业务，涵盖平面媒体、网络媒体、移动新媒体、户外 媒体包括地铁媒体的广告承揽发布、企事业单位宣传公关的全案策划和实施。
+2.公司控股子公司中教未来的业务板块之一是IT教育。旗下部分幼儿园引进AI智能机器人，培养人机协同的兴趣和科学探索精神，以便适应AI智能对孩子学习的辅助作用。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>传媒, AI, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>1.854</v>
+        <v>1.8023</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>“十五五”时期将推动住房公积金高质量发展。将扩大住房公积金制度覆盖面，支持个体工商户、非全日制从业人员以及其他灵活就业人员自愿缴存住房公积金，进一步增强公积金制度的普惠性。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性。</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sz000002</t>
+          <t>sh600825</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>3.32</v>
+        <v>5.84</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>9.9338</v>
+        <v>9.981199999999999</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>房地产|本集团的主营业务包括房地产开发和物业服务，本集团将自身定位进一步迭代升级为“城乡建设与生活服务商”。</t>
+          <t>并购重组+传媒|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>并购重组, 传媒</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>商业零售</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>1.8073</v>
+        <v>1.8023</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>国家统计局发布数据显示，1—8月份，社会消费品零售总额327569亿元，同比增长1.1%。其中，除汽车以外的消费品零售额301764亿元，增长2.7%。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性。</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sh605188</t>
+          <t>sh603258</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>国光连锁</t>
+          <t>电魂网络</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>13.12</v>
+        <v>14.19</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>9.9749</v>
+        <v>10</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>零售|公司自设立以来主要从事连锁超市、百货商场的运营业务。公司立足于江西省内，多年来通过深耕本地市场、持续推进门店升级转型，成为以生鲜、食品为核心品类的零售企业。公司是江西省商贸流通行业首家上市企业，江西本土领先的连锁经营企业。</t>
+          <t>游戏|公司为一家拥有自主研发能力、运营能力的专业化网络游戏公司，致力于自主研发运营精品化的网络游戏。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>游戏</t>
         </is>
       </c>
     </row>
@@ -2676,36 +2689,40 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1.8073</v>
+        <v>2.9204</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>国家统计局发布数据显示，1—8月份，社会消费品零售总额327569亿元，同比增长1.1%。其中，除汽车以外的消费品零售额301764亿元，增长2.7%。</t>
+          <t>商务部消费促进司负责人解读2026年1月至8月我国消费市场情况时表示，1月至8月，社会消费商品和服务零售总额同比增长2.5%，消费市场稳中提质，消费结构持续优化。</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sh600838</t>
+          <t>sh601086</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>国芳集团</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>8.59</v>
+        <v>17.67</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>9.9872</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+        <v>10.0249</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>零售|公司控股股东为上海九百（集团）有限公司。目前已经发展成为涉及洗涤化工产品生产销售及洗染服务、酒类产品批发等多种业态的综合性企业。</t>
+          <t>零售|公司从事以百货业为主，超市、电器为辅的连锁零售业务，是甘肃省内最大的连锁零售企业。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2721,528 +2738,523 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>1.8073</v>
+        <v>2.9204</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>国家统计局发布数据显示，1—8月份，社会消费品零售总额327569亿元，同比增长1.1%。其中，除汽车以外的消费品零售额301764亿元，增长2.7%。</t>
+          <t>商务部消费促进司负责人解读2026年1月至8月我国消费市场情况时表示，1月至8月，社会消费商品和服务零售总额同比增长2.5%，消费市场稳中提质，消费结构持续优化。</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh601086</t>
+          <t>sh600785</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>新华百货</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>16.06</v>
+        <v>11.35</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10</v>
+        <v>9.980600000000001</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>零售|公司从事以百货业为主，超市、电器为辅的连锁零售业务，是甘肃省内最大的连锁零售企业。</t>
+          <t>零售+“华”字辈|公司是宁夏乃至西北地区较大的商业零售企业，主要从事商业零售、物流和商业物业出租业务，零售业务主要涉及百货商场、综合购物中心、超市连锁、电器及通信连锁。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>零售, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>商业零售</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>1.6795</v>
+        <v>2.9204</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>浙商证券最新研报显示，随着PCB上游材料价格持续上涨，涨价开始向部分PCB品类传导，涨价效果自2026年第三季度起将逐步体现。</t>
+          <t>商务部消费促进司负责人解读2026年1月至8月我国消费市场情况时表示，1月至8月，社会消费商品和服务零售总额同比增长2.5%，消费市场稳中提质，消费结构持续优化。</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sz002134</t>
+          <t>sh600857</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>天津普林</t>
+          <t>宁波中百</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>27.1</v>
+        <v>23.41</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>9.9838</v>
+        <v>10.0094</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司主要从事印制电路板（PCB）的研发、生产及销售，产品类型覆盖单双面板、多层板、高多层板、HDI、高频高速板及厚铜板等，专注于中小批量、高多层、厚铜板、光电板和HDI领域的PCB领先企业。</t>
+          <t>零售|公司主要从事商业零售业务，宁波地区为公司商业零售业务的主导区域。作为宁波本土的商业零售品牌“宁波二百”，具有悠久的历史和较高的知名度。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>商业零售</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>1.6795</v>
+        <v>2.9204</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>浙商证券最新研报显示，随着PCB上游材料价格持续上涨，涨价开始向部分PCB品类传导，涨价效果自2026年第三季度起将逐步体现。</t>
+          <t>商务部消费促进司负责人解读2026年1月至8月我国消费市场情况时表示，1月至8月，社会消费商品和服务零售总额同比增长2.5%，消费市场稳中提质，消费结构持续优化。</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz001212</t>
+          <t>sh600712</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>中旗新材</t>
+          <t>南宁百货</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>37.98</v>
+        <v>5.89</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>9.991300000000001</v>
+        <v>10.0935</v>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司的超细硅晶材料可应用于涂料、覆铜板、电工绝缘料、液晶显示玻璃等。</t>
+          <t>零售|公司主要从事商业零售业务，地处广西南宁市，南宁市是华南经济圈、西南经济圈和中国—东盟经济圈的交汇点。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>1.6795</v>
+        <v>2.6123</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>浙商证券最新研报显示，随着PCB上游材料价格持续上涨，涨价开始向部分PCB品类传导，涨价效果自2026年第三季度起将逐步体现。</t>
+          <t>风险咨询公司Verisk Maplecroft近期发布的一份报告中表示，极端天气灾害将加剧亚洲的粮食安全风险。</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sz000509</t>
+          <t>sh600127</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>华塑控股</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>3.77</v>
+        <v>15.75</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>9.9125</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+        <v>9.986000000000001</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>PCB|子公司宏创智能研发投产多工位粗精磨一体机MF6000E，该设备加工生产的钻针可用于加工高频高速PCB板。</t>
+          <t>大米|公司是我国粮食系统的第一家上市公司，是首批农业产业化国家重点龙头企业，国家水稻工程优质米示范基地。公司以优质粮油、新型健康食品和药品开发、生产、销售为发展方向，坚持农、工、科、贸一体化的现代农业产业化经营模式，主要产品有大米、面粉、面条、植物油、米粉、牛奶、糖果、果冻、药品等。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>大米</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>1.386</v>
+        <v>2.6123</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>诺和诺德与Anthropic宣布达成合作，双方将利用Anthropic的人工智能（AI）模型及Claude Science支持药物发现与研发。</t>
+          <t>风险咨询公司Verisk Maplecroft近期发布的一份报告中表示，极端天气灾害将加剧亚洲的粮食安全风险。</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sz000504</t>
+          <t>sz002321</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>南华生物</t>
+          <t>华英农业</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>10.01</v>
+        <v>2.3</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>10</v>
+        <v>10.0478</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>细胞治疗|公司是目前国内一家国资控股的干细胞、免疫细胞及组织工程产业主板上市公司，“生物医药”板块业务包括干细胞储存服务、化妆品的生产和销售、医疗器械设备及耗材的代理和销售。</t>
+          <t>养殖+“华”字辈|主营业务为种鸭/鸡养殖、孵化、禽苗销售、饲料生产、商品鸭/鸡屠宰加工、冻品销售、熟食、羽绒及羽绒制品生产和销售。</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>细胞治疗</t>
+          <t>养殖, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>1.386</v>
+        <v>2.6123</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>诺和诺德与Anthropic宣布达成合作，双方将利用Anthropic的人工智能（AI）模型及Claude Science支持药物发现与研发。</t>
+          <t>风险咨询公司Verisk Maplecroft近期发布的一份报告中表示，极端天气灾害将加剧亚洲的粮食安全风险。</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sh603122</t>
+          <t>sh603151</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>合富中国</t>
+          <t>邦基科技</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>13.64</v>
+        <v>18.35</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>10.012</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>医疗流通+海峡两岸|1.公司系医疗流通领域的渠道商，具备与境内外试剂耗材和医疗设备原厂、各大代理商及医疗机构长期互惠、合作共赢的核心竞争力。
-2.公司为唯一一家海峡两岸市场“双上市”的医疗企业，其母公司合富医疗控股在台湾上市，公司实际控制人为台湾企业家王琼芝，在两岸医疗流通领域有深度合作。</t>
+          <t>饲料|公司是一家为现代化养殖场提供专业化产品的饲料生产企业，专注于动物生命与动物营养研究，涉足猪料、蛋禽预混料、肉类反刍饲料、兽药销售等产业，主要产品包括猪预混料、猪浓缩料、猪配合料等。</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>医疗流通, 海峡两岸</t>
+          <t>饲料</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>1.386</v>
+        <v>2.6123</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>诺和诺德与Anthropic宣布达成合作，双方将利用Anthropic的人工智能（AI）模型及Claude Science支持药物发现与研发。</t>
+          <t>风险咨询公司Verisk Maplecroft近期发布的一份报告中表示，极端天气灾害将加剧亚洲的粮食安全风险。</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sz002589</t>
+          <t>sz001201</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>瑞康医药</t>
+          <t>东瑞股份</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>3.27</v>
+        <v>16.08</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>10.101</v>
+        <v>9.9863</v>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司与广东药科大学相关医学专家合作，共同合作研发治疗非酒精性肝脂肪变中医新药FTZ浓缩丸，2024年内已进入临床二期阶段。</t>
+          <t>猪肉|公司主营业务为生猪的养殖和销售，主要产品为商品猪、仔猪、种猪等。此外，公司自行生产生猪养殖所需的饲料，并有部分饲料对外销售。</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>猪肉</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>0.7743</v>
+        <v>1.6203</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>华泰证券指出，黄酒行业量价逻辑有望迎来重构，量上由江浙沪渗透提升走向全国拓展，价上龙头合力推进高端化。</t>
+          <t>无人机视频显示，特斯拉Optimus在美国得州的专用生产线建设主结构可能接近完工，钢结构、混凝土浇筑等施工正同步推进。该生产线计划2027年计划投产，年产能目标在1000万台。</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>sh601579</t>
+          <t>sz000910</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">会稽山  </t>
+          <t>大亚圣象</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>32.84</v>
+        <v>6.26</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>10.0168</v>
+        <v>10.0176</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>8天4板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>黄酒|公司主要从事黄酒的生产、销售和研发等业务，公司及下属子公司主要拥有“会稽山”、“西塘”、“乌毡帽”、“唐宋”等主品牌。</t>
+          <t>机器人|公司以自有资金1,500万元人民币认购嘉兴翼龙股权投资合伙企业 （有限合伙）28.30189%的份额，该基金以股权投资的方式投资七腾机器人有限公司。</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>黄酒</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>0.7743</v>
+        <v>1.6203</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>华泰证券指出，黄酒行业量价逻辑有望迎来重构，量上由江浙沪渗透提升走向全国拓展，价上龙头合力推进高端化。</t>
+          <t>无人机视频显示，特斯拉Optimus在美国得州的专用生产线建设主结构可能接近完工，钢结构、混凝土浇筑等施工正同步推进。该生产线计划2027年计划投产，年产能目标在1000万台。</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sh600127</t>
+          <t>sh605566</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>福莱蒽特</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>14.32</v>
+        <v>30.44</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>9.9846</v>
+        <v>10.0108</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>农业种植+食品饮料|公司是我国粮食系统的第一家上市公司，是首批农业产业化国家重点龙头企业，国家水稻工程优质米示范基地。公司以优质粮油、新型健康食品和药品开发、生产、销售为发展方向，坚持农、工、科、贸一体化的现代农业产业化经营模式，主要产品有大米、面粉、面条、植物油、米粉、牛奶、糖果、果冻、药品等。</t>
+          <t>机器人+算力|1.公司通过参股双曲线智能（杭州）有限公司布局柔性触觉传感相关业务，合作方钛深科技具备柔性触觉传感核心技术。
+2.2026年5月21日公告，公司召开第三届董事会第五次会议，审议通过了《关于购买资产的议案》。根据公司发展需要，公司拟采购IT设备及服务器，并签署相关采购合同，采购合同总金额预计不超过人民币8.5亿元。</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>农业种植, 食品饮料</t>
+          <t>机器人, 算力</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>0.7743</v>
+        <v>1.6203</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>华泰证券指出，黄酒行业量价逻辑有望迎来重构，量上由江浙沪渗透提升走向全国拓展，价上龙头合力推进高端化。</t>
+          <t>无人机视频显示，特斯拉Optimus在美国得州的专用生产线建设主结构可能接近完工，钢结构、混凝土浇筑等施工正同步推进。该生产线计划2027年计划投产，年产能目标在1000万台。</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sz001211</t>
+          <t>sh600503</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>双枪科技</t>
+          <t>华丽家族</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>25.88</v>
+        <v>2.43</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>9.987300000000001</v>
+        <v>9.954800000000001</v>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>食品饮料+餐厨具|1.子公司极野食品主要销售以食材笋和调味笋为主的笋产品。
-2.公司是一家领先的日用餐厨具供应商，拥有筷子、砧板、勺铲、签类和其他餐厨具5个大类，超过1000种单品。</t>
+          <t>机器人+“华”字辈|持有南江机器人50.82%的股权，是全产业链机器人公司；主要产品为面向智能制造和智能物流的智能移动机器人IAGV和智能搬运几期二年ICARRIER系列机器人。</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>食品饮料, 餐厨具</t>
+          <t>机器人, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>0.6956</v>
+        <v>1.6203</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>方正证券研报指出，AI正从单点工具应用逐步向内容生产、分发及商业化等产业链环节渗透，互联网传媒行业进入生产方式与商业模式加速重构阶段。</t>
+          <t>无人机视频显示，特斯拉Optimus在美国得州的专用生产线建设主结构可能接近完工，钢结构、混凝土浇筑等施工正同步推进。该生产线计划2027年计划投产，年产能目标在1000万台。</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>sh603230</t>
+          <t>sh603319</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>美湖股份</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>13.48</v>
+        <v>32.18</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>10.0408</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.0171</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>出版传媒|公司的最终控制人为内蒙古自治区人民政府。公司主营业务是出版物的批发、零售；文体用品零售；音像制品发行</t>
+          <t>机器人|2025年3月23日公告，公司拟与重庆市沙坪坝区招商投资促进中心签订《项目合作协议书》，计划总投资约7亿元建设美湖智造西部生产研发基地项目，主要开展可变排量泵、电子泵、谐波减速器、关节模组四大类产品的研发及生产。</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>出版传媒</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>养老</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>0.6956</v>
+        <v>3.1766</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>方正证券研报指出，AI正从单点工具应用逐步向内容生产、分发及商业化等产业链环节渗透，互联网传媒行业进入生产方式与商业模式加速重构阶段。</t>
+          <t>9月18日国常会指出，要全面客观认识人口老龄化带来的影响，深入实施积极应对人口老龄化国家战略，推动老龄事业全面发展进步。</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
@@ -3250,46 +3262,44 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>sh600640</t>
+          <t>sz002614</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>国脉文化</t>
+          <t>奥佳华</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>12.06</v>
+        <v>6.25</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>10.0365</v>
+        <v>10.0352</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI短剧+机器人|1.公司构建了包含AI创意与文本创作、视觉概念及分镜设计、图像到视频转换、语音合成以及AI音乐创作全流程的AI短剧创作工作流，实现AIGC赋能内容生产。围绕文化、经典、文旅方向，成功打造“AIGC微短剧”系列内容。
-2.公司与宇树科技的合作属于小范围个别产品的合作，面向会展等应用场景的探索。
-</t>
+          <t>养老+“华”字辈|国内按摩器具行业产业链最完整并在全球具有影响力的龙头民企，公司已形成高端、中端、低端三个市场全面发力的布局。</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>AI短剧, 机器人</t>
+          <t>养老, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>养老</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>0.6956</v>
+        <v>3.1766</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>方正证券研报指出，AI正从单点工具应用逐步向内容生产、分发及商业化等产业链环节渗透，互联网传媒行业进入生产方式与商业模式加速重构阶段。</t>
+          <t>9月18日国常会指出，要全面客观认识人口老龄化带来的影响，深入实施积极应对人口老龄化国家战略，推动老龄事业全面发展进步。</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -3297,863 +3307,2057 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sz002172</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>澳洋健康</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>13.9</v>
+        <v>5.81</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>9.968399999999999</v>
+        <v>10.0379</v>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>出版传媒|公司是我国第一家按照上市公众公司标准规范设立的大型股份制出版发行企业。</t>
+          <t xml:space="preserve">养老+谐音“羊”|子公司张家港澳洋护理院经营范围包含老年人养护服务。
+</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>出版传媒</t>
+          <t>养老, 谐音“羊”</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>养老</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>2.1637</v>
+        <v>3.1766</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>AI算力租赁商Nebius拟于10月1日起上调部分GPU算力价格，涨幅约20%。</t>
+          <t>9月18日国常会指出，要全面客观认识人口老龄化带来的影响，深入实施积极应对人口老龄化国家战略，推动老龄事业全面发展进步。</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>sz002713</t>
+          <t>sz002178</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>东易日盛</t>
+          <t>延华智能</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>10.92</v>
+        <v>5.08</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>9.969799999999999</v>
+        <v>9.9567</v>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司于2025年3月18日披露重整投资协议暨预重整进展，公司与北京华著签订了《重整投资协议》，交易完成后，北京华著预计对公司的持股比例为15.77%，成为公司控股股东。北京华著为AIDC（智算中心）综合服务商。在协议中，北京华著明确表示将向上市公司捐赠智算中心等资产，帮助上市公司转型智算领域。</t>
+          <t>养老+AI医疗|1.公司智慧医疗与大健康业务为诊所、门诊部、药店、养老机构等提供标准化解决方案，为居民提供健康管理的服务平台，打造多学科中心垂直叠加医疗及康养综合体，为医患提供便捷的诊疗与康复环境。
+2.在智慧医疗领域，公司研究开发了HIS系统、智能化电子病历系统、基于微服务的医院信息化集成平台，基于AI的临床辅助诊断系统、全流程医疗质量管理系统、智能决策分析系统、智能导诊系统、城市智慧救护车云服务平台、医疗质量信息管理平台、医院总值班信息系统平台、医护一体化平台等。</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>养老, AI医疗</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>电子烟</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>2.1637</v>
+        <v>1.907</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>AI算力租赁商Nebius拟于10月1日起上调部分GPU算力价格，涨幅约20%。</t>
+          <t>国家烟草专卖局发布《加热卷烟》强制性国家标准征求意见稿，机构认为随着新规落地，国内HNB即将从规则制定进入产品上市阶段。</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>sz002849</t>
+          <t>sz002303</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>威星智能</t>
+          <t>美盈森</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>20.32</v>
+        <v>6.27</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>10.0162</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>投资智算中心|2023年7月24日公告，近日，公司与贵安管委会、摩尔线程签署《贵安智算中心项目投资合作协议》，三方拟在贵安新区建立智算中心，在3D图形渲染和视觉设计、高性能科学计算、HDV高速视频解编码、AI训练和推理等应用领域构建深度合作关系。</t>
+          <t>电子烟|公司全资子公司东莞美盈森顺利通过电子香烟制造商吉瑞科技验厂、打样测试、综合评估的审核程序，取得其包装供应资质，为其电子烟产品提供一体化包装服务。</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>投资智算中心</t>
+          <t>电子烟</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>大金融</t>
+          <t>电子烟</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>0.764</v>
+        <v>1.907</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>今年以来，A股IPO市场持续放量，券商IPO承销金额已超过2025年全年，投行业务竞争格局出现新变化。</t>
+          <t>国家烟草专卖局发布《加热卷烟》强制性国家标准征求意见稿，机构认为随着新规落地，国内HNB即将从规则制定进入产品上市阶段。</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>sh600621</t>
+          <t>sh603020</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>华鑫股份</t>
+          <t>爱普股份</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>14.1</v>
+        <v>12.57</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>9.984400000000001</v>
+        <v>9.973799999999999</v>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>券商|公司以证券业务为主，以部分持有型物业经营业务为辅。公司通过全资子公司华鑫证券开展证券业务</t>
+          <t>烟草香精|公司设有烟草香精事业部，向多家国内知名烟草企业提供烟用香精产品。</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>烟草香精</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>大金融</t>
+          <t>电子烟</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>0.764</v>
+        <v>1.907</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>今年以来，A股IPO市场持续放量，券商IPO承销金额已超过2025年全年，投行业务竞争格局出现新变化。</t>
+          <t>国家烟草专卖局发布《加热卷烟》强制性国家标准征求意见稿，机构认为随着新规落地，国内HNB即将从规则制定进入产品上市阶段。</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>sz000532</t>
+          <t>sz000829</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>华金资本</t>
+          <t>天音控股</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>12.96</v>
+        <v>9.77</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>10.017</v>
+        <v>10.0225</v>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>多元金融|公司全力打造股权投资、资产管理、实体产业三大业务体系，构建了“创投+实业”双轮驱动的产业新格局。</t>
+          <t>电子烟|公司已经与电子烟头部品牌（铂德和小野）签订了战略合作伙伴，并成为电子烟品牌商铂德和小野的唯一国代，进行全渠道销售，负责开拓品牌商产品市场，逐步提高品牌产品的市场占有率。</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电子烟</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>军工</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
+        <v>1.607</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>多家券商研报判断，2025至2027年行业向好趋势确定性较强。随着"十五五"装备目录逐步明确，规模化订单下达渐行渐近。</t>
+        </is>
+      </c>
       <c r="D66" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>sh603272</t>
+          <t>sz002724</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST联翔 </t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>16.89</v>
+        <v>7.84</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>10.0326</v>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
+        <v>9.9579</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 联翔股份公告称，公司控股股东卜晓华与金美含签署股份转让协议，拟以20.36元/股的价格协议转让5,181,400股无限售流通股，占公司总股本的5%，转让总价款约为1.05亿元。</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr"/>
+          <t>军工+谐音“羊”|公司是武器装备科研生产三级保密资格单位，设有专门的军品事业部负责军品的销售。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>军工, 谐音“羊”</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr"/>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>1.607</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>多家券商研报判断，2025至2027年行业向好趋势确定性较强。随着"十五五"装备目录逐步明确，规模化订单下达渐行渐近。</t>
+        </is>
+      </c>
       <c r="D67" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>sz001216</t>
+          <t>sh600992</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>贵绳股份</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>21.87</v>
+        <v>10.57</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>10.0101</v>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>9.989599999999999</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>MLCC上游粉体|子公司氧化锆粉体纯度最高可达99.995%，产品可适配新能源研磨、齿科陶瓷、MLCC等不同领域使用需求。</t>
+          <t>军工|公司是我国钢丝、钢丝绳生产最大专业企业之一，年生产能力近40万吨，应用客户涵盖海洋工程、航空航天、重大水利工程、煤炭、有色金属等领域。公司通过了国军标第三方认证审核并获得证书和武器装备科研单位三级保密资格认证。</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>MLCC上游粉体</t>
+          <t>军工</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr"/>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>1.607</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>多家券商研报判断，2025至2027年行业向好趋势确定性较强。随着"十五五"装备目录逐步明确，规模化订单下达渐行渐近。</t>
+        </is>
+      </c>
       <c r="D68" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>sz301390</t>
+          <t>sz002246</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>经纬股份</t>
+          <t>北化股份</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>54</v>
+        <v>26.27</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0084</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>控股股东变更|经纬股份公告称，公司实控人叶肖华及其一致行动人、员工持股平台、持股5%以上股东炬华科技及其一致行动人炬华联昕、股东吴仁德与中软国际(西安)智能科技签署《股份转让协议》，拟以53元/股协议转让合计1780.62万股(占总股本29.68%)，转让价款合计9.44亿元。完成后，中软国际(西安)智能科技将成为公司控股股东。</t>
+          <t>军工+硝化棉|1.中国兵器工业集团旗下上市公司，下属子公司新华化工是我国唯一的“核化生”三防器材科研、生产单位，专业生产军用核生化防护装备。
+2.公司是全球生产规模最大的硝化棉生产企业，产销量连续多年排在世界首位，是世界硝化棉行业协会三家执委单位之一，是国内、国际硝化棉行业的领先企业。</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>控股股东变更</t>
+          <t>军工, 硝化棉</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr"/>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>1.4986</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
+        </is>
+      </c>
       <c r="D69" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>sz002836</t>
+          <t>sh603042</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>新宏泽</t>
+          <t>华脉科技</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>11.92</v>
+        <v>19.03</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>9.963099999999999</v>
+        <v>10</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>烟标|公司系专业烟标印刷服务供应商，主营业务为烟标的设计、生产及销售。</t>
+          <t>光纤+“华”字辈|公司是一家信息通信网络基础设施解决方案提供商，主要产品包括光纤、光缆、光器件及光配线设施全场景有线传输链路解决方案及系列产品。</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>烟标</t>
+          <t>光纤, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr"/>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>1.4986</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
+        </is>
+      </c>
       <c r="D70" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>sz001376</t>
+          <t>sz002792</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>百通能源</t>
+          <t>通宇通讯</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>12.66</v>
+        <v>34.54</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>9.991300000000001</v>
+        <v>10</v>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>铝业公司完成注册|境外全资子公司百通图达（安哥拉）铝业有限公司已完成注册。该公司经营范围为铝业相关产品及服务的生产、加工、销售、进口和出口。</t>
+          <t>光模块+6G|1.间接参股25.58%的深圳光为致力于各类光模块研发，目前已成功研发出了包括100G CFP2、400G QSFP-DD等系列在内的多个光模块产品类型。
+2.佳贤通信是基于英伟达CUDA Aerial开源生态平台开展6GAI-RAN基站技术研发工作，未与英伟达签署任何研发合作协议或战略合作框架协议，与英伟达之间不存在任何形式的研发合作、联合开发关系。相关产品目前仍处前期研发阶段，未实现商业化应用，未对佳贤通信经营业绩产生影响。公司拟以3亿元购买佳贤通信25%股权，交易完成后不纳入合并报表范围，采用权益法核算。</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>铝业公司完成注册</t>
+          <t>光模块, 6G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr"/>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>1.4986</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月17日，英伟达CEO黄仁勋在苏格兰参加AI活动时表示，英伟达预计2027年芯片销量将达到当前年度水平的约两倍。</t>
+        </is>
+      </c>
       <c r="D71" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>sh603686</t>
+          <t>sh688112</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">福龙马  </t>
+          <t>鼎阳科技</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>15.47</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>10.0284</v>
+        <v>20.0026</v>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>与华为云合作自驾|福龙马公告称，公司与华为云计算技术有限公司签署环卫自动驾驶技术开发合同，合同总金额2亿元(含税)，有效期3年。双方将基于公司业务需求，针对3吨级和6吨级车型平台、清扫和洗扫业务场景，由华为云计算为公司独家研发和部署“福龙马环卫自动驾驶系统”。</t>
+          <t>光模块设备|公司有多种产品可以用于光模块的研发和生产测试环节，包括但不限于电源、源表、台式万用表等。</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>与华为云合作自驾</t>
+          <t>光模块设备</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr"/>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>1.0499</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。</t>
+        </is>
+      </c>
       <c r="D72" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>sz001317</t>
+          <t>sh603175</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>三羊马</t>
+          <t>超颖电子</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>54.51</v>
+        <v>110.17</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>10.0101</v>
+        <v>10.005</v>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>物流+谐音“羊”|公司是一家主要通过公铁联运方式为汽车行业和啤酒、饮料、洗涤用品等非汽车行业提供综合服务的第三方物流企业，建成以重庆为龙头，以柳州、西安、兰州、乌鲁木齐等为支点，串联“一带一路”沿线节点城市，横贯中西部地区，联系亚欧大陆的流通大通道。</t>
+          <t>PCB+存储芯片|1.公司主营业务是印制电路板的研发、生产和销售，拥有HDI板、厚铜板、金属基板、高频板、高速板等特殊材料、特殊工艺产品的生产能力，产品广泛应用于汽车电子、显示、储存、消费电子、通信等领域，并积极布局AR/VR、航天卫星等领域。
+2.在储存领域，公司产品主要应用于机械硬盘、固态硬盘、内存条等，与全球机械硬盘制造商龙头希捷、西部数据及全球知名固态硬盘制造商海力士等建立了稳定合作。</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>物流, 谐音“羊”</t>
+          <t>PCB, 存储芯片</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>1.0499</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。</t>
+        </is>
+      </c>
       <c r="D73" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>sh600343</t>
+          <t>sz001389</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>航天动力</t>
+          <t>广合科技</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>21.67</v>
+        <v>185.93</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>10</v>
+        <v>9.998200000000001</v>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>军工+商业航天|公司是航天六院唯一的资产证券化平台。航天六院是我国液体火箭发动机研制中心和专业抓总单位，承担着为我国运载火箭和导弹武器提供液体火箭发动机的重任。</t>
+          <t>PCB|公司主营业务是印制电路板的研发、生产和销售。在下游应用和技术能力方面具有代表性产品有高性能计算服务器板、AI运算服务器板、高性能存储服务器板等。</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>军工, 商业航天</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr"/>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>1.0499</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。</t>
+        </is>
+      </c>
       <c r="D74" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>sz002623</t>
+          <t>sz002080</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>亚玛顿</t>
+          <t>中材科技</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>18.52</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>9.9762</v>
+        <v>9.996700000000001</v>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>光伏+玻璃基板|1.国内光伏镀膜玻璃、大尺寸超薄光伏玻璃产品的先行及引领者，在行业内率先开发了更加轻量化、薄型化的1.6mm的光伏玻璃、BIPV美学、彩色镀膜玻璃、玻璃扩散板、一体化AG玻璃等具有核心竞争力的产品。
-2.2023年9月16日公司在官微透露，超高清玻璃基板产业项目占地800亩，由常州亚玛顿股份有限公司建设，主要建设年产5800万平方米的超高清玻璃基板生产基地。生产的超高清玻璃基板厚度为0.55毫米至1.1毫米，广泛应用于超高清电视、智能手机、电脑等智能电子产品显示屏制造。</t>
+          <t>PCB+风电|1.公司自主研发的应用于高端PCB的第一代低介电产品获得国内知名客户“PCB多元化项目技术突破奖”，已量产量供。
+2.公司旗下中材叶片是专业的风电叶片设计、研发、制造和服务提供商，拥有31-147米全系列超过150款产品型号，覆盖陆上和海上各种不同风况1.0MW-20MW+机组平台。</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>光伏, 玻璃基板</t>
+          <t>PCB, 风电</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr"/>
+          <t>电梯</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>2.5193</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>住房和城乡建设部城市管理监督局局长‌张强在国新办新闻发布会上表示，“十五五”时期，更新和加装住宅电梯57.5万台。</t>
+        </is>
+      </c>
       <c r="D75" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>sh600847</t>
+          <t>sz002367</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>万里股份</t>
+          <t>康力电梯</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>13.92</v>
+        <v>6.28</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>10.0395</v>
+        <v>9.9825</v>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>铅酸蓄电池|公司是中国铅酸蓄电池行业首家上市公司，以生产“万里”牌各型铅酸蓄电池闻名于世，被誉为“中国蓄能专家”。</t>
+          <t>电梯+机器人|1.国内电梯综合制造商。主要从事电梯、自动扶梯、自动人行道及成套配件的产品研产销及整机产品的安装和维保业务。
+2.子公司康力优蓝已量产多款机器人，如教育陪伴类机器人U03S、HELLO KITTY，商用服务机器人U05，烹饪机器人爱乐优08等。</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>铅酸蓄电池</t>
+          <t>电梯, 机器人</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
+          <t>电梯</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>2.5193</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>住房和城乡建设部城市管理监督局局长‌张强在国新办新闻发布会上表示，“十五五”时期，更新和加装住宅电梯57.5万台。</t>
+        </is>
+      </c>
       <c r="D76" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>sz002005</t>
+          <t>sh600894</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>德豪润达</t>
+          <t>广日股份</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>2.66</v>
+        <v>7.92</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>9.917400000000001</v>
+        <v>10</v>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>LED|小家电及LED双主营业务。是国内拥有包括LED芯片、LED封装、LED应用产品(照明和显示)、照明品牌及渠道在内的LED全产业链布局的极少数企业之一。</t>
+          <t>电梯+机器人|1.公司的业务范围包括研发、设计、生产、安装、维修及保养电梯、自动扶梯、自动人行道等设备。
+2.子公司松兴电气长期专注焊接技术，集弧焊、电阻焊、激光、机器人系统集成等产品技术为一体，研发生产和销售喷涂机器人本体及喷涂自动化生产线。</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>电梯, 机器人</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr"/>
+          <t>发电机概念</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>2.0224</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>中信建投研报称，2026Q2全球燃机订单约38GW，创单季度历史新高，美国贡献接近一半。</t>
+        </is>
+      </c>
       <c r="D77" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>sz001332</t>
+          <t>sh603819</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>锡装股份</t>
+          <t>神力股份</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>28.9</v>
+        <v>17.33</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>10.0114</v>
+        <v>10.0317</v>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>核电+光伏|1.公司向全球知名核电企业法马通销售金属压力容器，该等产品用于红沿河核电站、防城港核电站、阳江核电站等国内外多个大型核能发电项目。
-2.公司已经与多家大型多晶硅企业建立了良好的合作关系，获得了高端换热器产品及关键反应器产品的订单。</t>
+          <t>发电机|公司主营业务为大中型电机(包括电动机和发电机)定子、转子冲片和铁芯的研发及生产，可应用于不同种类和型号的电机，包括柴油发电机等，服务范围涉及柴油发电等专用电机配套领域。终端产品应用领域包括不限于船用，汽车，应急发电等，可应用于医院、数据中心等需要应急发电的行业。</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>核电, 光伏</t>
+          <t>发电机</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr"/>
+          <t>发电机概念</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>2.0224</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>中信建投研报称，2026Q2全球燃机订单约38GW，创单季度历史新高，美国贡献接近一半。</t>
+        </is>
+      </c>
       <c r="D78" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>sh600719</t>
+          <t>sh600218</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>大连热电</t>
+          <t>全柴动力</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>8.42</v>
+        <v>8.27</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>10.0654</v>
+        <v>9.9734</v>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>热电|公司是大连地区供热、供电联产龙头企业，装机容量10万千瓦，年上网电量1.53亿千瓦时，供热面积达1839万平方米，主要产品有电力和热力两大类，共有电力、工业蒸汽、高温水和供暖四个品种。</t>
+          <t>发电机|公司部分产品可用于发电机组等特定的作业场景。</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>热电</t>
+          <t>发电机</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr"/>
+          <t>3D打印</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>2.0092</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>美国劳伦斯利弗莫尔国家实验室研究人员开发出一种利用摄像头和人工智能（AI）检测3D打印质量的系统，在打印过程中，3D打印机可逐层“检查”自己制造的零部件，并及时发现断丝、尺寸异常等细微缺陷。</t>
+        </is>
+      </c>
       <c r="D79" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>sh600881</t>
+          <t>sz300829</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>亚泰集团</t>
+          <t>金丹科技</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>1.93</v>
+        <v>25.72</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>10.2857</v>
+        <v>20.0187</v>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>中药+水泥|1.公司生产范围涵盖现代中药、中药饮片、化药、生物制品、医疗器械和保健食品等，形成了以“参一胶囊”单体抗癌中药、“消栓通络胶囊”“丹黄祛瘀胶囊”等国家中药保护品种为主的中成药，以亚泰大连水产维生素AD滴剂、维生素D2为主的系列维生素，以及“亚泰康派”品牌系列保健食品等特色化的产品群。
-2.公司建材产业拥有集“石灰石、熟料、水泥、混凝土、预制构件、骨料”业务于一体的绿色建材产业链。</t>
+          <t>3D打印|公司产品聚乳酸（PLA）是以乳酸为原料生产的一种环保绿色的新型生物基可降解材料，已可以应用于吸管、餐具、膜袋类包装材料、纤维、织物、3D打印材料等产品和领域。</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>中药, 水泥</t>
+          <t>3D打印</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr"/>
+          <t>3D打印</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>2.0092</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>美国劳伦斯利弗莫尔国家实验室研究人员开发出一种利用摄像头和人工智能（AI）检测3D打印质量的系统，在打印过程中，3D打印机可逐层“检查”自己制造的零部件，并及时发现断丝、尺寸异常等细微缺陷。</t>
+        </is>
+      </c>
       <c r="D80" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>sh600261</t>
+          <t>sh603958</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>阳光照明</t>
+          <t>哈森股份</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>3.51</v>
+        <v>18.37</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>10.0313</v>
+        <v>10</v>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>节能灯|公司是中国最大的节能灯生产和出口基地之一，国家级高新技术企业。主要生产紧凑型节能荧光灯、电子节能灯、直管型荧光灯、T5大功率节能荧光灯及配套灯具、CCFL荧光屏背景光源及各类台灯系列。</t>
+          <t>机器人+3D打印|1.参股中科中成供应链（成都）有限公司主要从事机器人零部件、产品等采购、销售业务及相关技术服务等。
+2.公司旗下哈森唯特使用NPA技术（等离子体雾化技术）、TPR技术（钛粒径重构技术）生产的钛合金粉产品已中试成功，该产品可应用于3D打印和MIM（金属粉末注射成型）行业。</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>节能灯</t>
+          <t>机器人, 3D打印</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>MLCC</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>1.887</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>MLCC被业内称为“电子工业大米”，AI拉动高容量型号缺货疯涨，部分现货暴涨数倍。进入6月，现货市场进入“一天一价、甚至一小时一价”的火热状态，部分热门型号短短一个月涨幅达7-8倍。</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>sz001216</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>华瓷股份</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>10.0137</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>5天5板</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>MLCC+“华”字辈|子公司氧化锆粉体纯度最高可达99.995%，产品可适配新能源研磨、齿科陶瓷、MLCC等不同领域使用需求。</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, “华”字辈</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>MLCC</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>1.887</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>MLCC被业内称为“电子工业大米”，AI拉动高容量型号缺货疯涨，部分现货暴涨数倍。进入6月，现货市场进入“一天一价、甚至一小时一价”的火热状态，部分热门型号短短一个月涨幅达7-8倍。</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>sz002585</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>双星新材</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>10.0433</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>MLCC离型膜|公司的MLCC离型膜产品涵盖中高低端产品，2026年MLCC项目5亿平米全面建成并投产。</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>MLCC离型膜</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>大金融</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>1.1268</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>近日，中国证券业协会发布了证券公司2026年上半年度经营数据。传统业务与转型业务同步回暖。</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>sz000532</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>华金资本</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>10.0309</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>多元金融+“华”字辈|公司全力打造股权投资、资产管理、实体产业三大业务体系，构建了“创投+实业”双轮驱动的产业新格局。</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>多元金融, “华”字辈</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>大金融</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>1.1268</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>近日，中国证券业协会发布了证券公司2026年上半年度经营数据。传统业务与转型业务同步回暖。</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>sh603093</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>南华期货</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>9.984299999999999</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>期货+“华”字辈|公司成立于1996年，主要从事商品期货经纪、金融期货经纪业务，是中国金融期货交易所首批全面结算会员单位。</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>期货, “华”字辈</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>旅游酒店</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>2.4635</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>同程旅行报告显示，近期国内热门城市机票预订热度同比增长超40%。报告还显示，酒店5天以上长住订单占比较去年同期提升约7个百分点。</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>sh600593</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>大连圣亚</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>10.0113</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>旅游+冰雪产业|公司正在经营的哈尔滨景区包括哈尔滨极地公园海洋馆、哈尔滨极地公园极地馆、哈尔滨极地公园恐龙馆、哈尔滨极地公园北极熊体验馆、哈尔滨极地公园淘学企鹅馆。</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>旅游, 冰雪产业</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>1.1852</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>sz002667</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>*ST威领</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>9.979799999999999</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>*ST威领公告称，公司收到西藏山南锑金资源有限公司出具的要约收购报告书摘要。山南锑金拟向全体股东发出部分要约，收购股份数量为7817.745万股，要约价格为18元/股，占公司总股本的30%。本次要约收购所需资金总额预计不超过14.07亿元，收购人已存入履约保证金7.04亿元。要约收购完成后，山南锑金将最多持有公司30%股份，取得公司控制权。</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>sh601579</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">会稽山  </t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>9.9878</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>12天6板</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>黄酒|公司主要从事黄酒的生产、销售和研发等业务，公司及下属子公司主要拥有“会稽山”、“西塘”、“乌毡帽”、“唐宋”等主品牌。</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>黄酒</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>sh601123</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>马矿股份</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>10.0112</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>次新+福建+铁矿|公司是一家长期从事铁矿资源开发及综合利用的企业，主营铁矿石的采选、综合利用及铁精粉、钼精矿销售，石灰石的开采和销售。</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>次新, 福建, 铁矿</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr"/>
+      <c r="D89" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>sz001376</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>百通能源</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>10.0316</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>境外铝业公司注册|境外全资子公司百通图达（安哥拉）铝业有限公司已完成注册。该公司经营范围为铝业相关产品及服务的生产、加工、销售、进口和出口。</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>境外铝业公司注册</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>sz001317</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>三羊马</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>9.998200000000001</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>物流+谐音“羊”|公司是一家主要通过公铁联运方式为汽车行业和啤酒、饮料、洗涤用品等非汽车行业提供综合服务的第三方物流企业，建成以重庆为龙头，以柳州、西安、兰州、乌鲁木齐等为支点，串联“一带一路”沿线节点城市，横贯中西部地区，联系亚欧大陆的流通大通道。</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>物流, 谐音“羊”</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>sz002963</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>豪尔赛</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>10.0195</v>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>液冷+固态电池|1.参股的新疆华奕新能源科技股份有限公司是专业从事蒸发冷却空调设备的研发、设计、生产、销售、安装、及售后服务，已有数据中心液冷业务布局。
+2.公司参股投资的蜂巢能源科技有限公司成功研发出国内首批20Ah级硫系全固态原型电芯。该电芯的能量密度达350~400Wh/kg，并通过针刺、200℃热箱等实验测试。</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>液冷, 固态电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>sh600301</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>华锡有色</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>9.993399999999999</v>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>实控人变更|华锡有色公告称，公司间接控股股东广西关键金属集团及其股东北部湾港集团、关键金属股权基金与中国五矿签署《合作框架协议》，中国五矿拟以现金或现金与非现金资产组合的方式对广西关键金属集团进行增资，取得广西关键金属集团51%股权，并在交易后实际控制广西关键金属集团。本次交易完成后，公司控股股东仍为广西华锡集团股份有限公司，间接控股股东将由北部湾港集团和广西关键金属集团调整为广西关键金属集团，实际控制人将由广西壮族自治区人民政府国有资产监督管理委员会变更为中国五矿，中国五矿通过广西关键金属集团间接持有华锡有色的权益将超过华锡有色已发行股份的30%，从而触发全面要约收购义务。</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>实控人变更</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>sh600281</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>华阳新材</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>9.9338</v>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>稀土+“华”字辈|子公司太原华盛丰贵金属材料有限公司经营范围包含铂、钯、铑、银、镍贵金属系列催化剂、催化网及稀土高磁性材料的回收利用、加工、研究、生产、销售及技术服务。</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>稀土, “华”字辈</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>sh603580</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>艾艾精工</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>9.9954</v>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>股权转让|艾艾精工公告称，公司控股股东及实际控制人涂木林、蔡瑞美筹划的控制权变更事项取得进展。蔡瑞美与上海誉升同风金属材料科技有限公司签署股份转让协议，拟以27.62元/股转让3918.89万股(占总股本29.99%)，总价款10.82亿元。同时，以本次股份转让为前提，上海誉升拟以部分要约收购方式增持1308.04万股(占总股本10.01%)，要约价27.62元/股。</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>sz002084</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>海鸥住工</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>10.0719</v>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>实控人变更|2026年8月21日公告，公司控股股东中馀投资与博泰车联签署股份转让协议，拟转让1.29亿股(占总股本20%)；另与福清曜鸿签署协议，拟转让3236.74万股(占总股本5.01%)。完成后，公司控股股东将变更为博泰车联，实控人变更为应臻恺。</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>实控人变更</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr"/>
+      <c r="D96" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>sz002860</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>星帅尔</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>9.988</v>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>汽车零部件|公司产品已覆盖新能源汽车驱动电机、新能源汽车空调压缩机电机、新能源汽车空调压缩机接线端子等系列产品。</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>汽车零部件</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>sz001373</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>翔腾新材</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>10.0034</v>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>偏光片|公司主要从事新型显示领域各类薄膜器件的研发、生产、精密加工和销售，产品包括各类规格的偏光片、光学膜片和功能性胶粘材料，均是新型显示领域的关键组件，已经广泛应用于液晶电视、显示器、笔记本电脑、平板电脑、手机、穿戴设备、车载显示、工业控制及公共显示等各类光电显示产品中。</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>偏光片</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>sh688121</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST卓然 </t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司是大型炼油化工专用装备模块化、集成化制造的提供商，专业为石油化工、炼油、天然气化工等领域的客户提供设计、制造、安装和服务一体化的解决方案。</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr"/>
+      <c r="D99" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>sh600714</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>金瑞矿业</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>锶+玻璃基板|公司主营碳酸锶系列产品是国内能应用于液晶玻璃基板的主要锶盐产品。</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>锶, 玻璃基板</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>sz000995</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>皇台酒业</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>9.963099999999999</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>白酒|西北风格的名优白酒。葡萄酒产品依靠河西走廊得天独厚的地理优势，酒体品质达到了国际标准。</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>白酒</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr"/>
+      <c r="D101" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>sh603395</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">红四方  </t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>10.0078</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>化肥|公司隶属于中盐集团，是专业从事复合肥和氮肥产品研发、生产、销售和服务的化肥生产企业，为中盐集团农肥业务板块的运营主体，入选国务院国资委“双百企业”名单。公司已形成以复合肥产品为主，并向上游氮肥产业延伸的完整的研发、生产、销售和农化服务体系。</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>化肥</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr"/>
+      <c r="D102" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>sh605196</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>华通线缆</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>10.0095</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>电线电缆+“华”字辈|公司主要从事电线电缆的研发、生产与销售业务，主导产品包括以进户线为代表的中低压电力电缆，及以潜油泵电缆为代表的电气装备用电缆，广泛应用于电力输配、采矿/油/气等行业，并已获得美国UL、欧盟CE等国际认证，中国CRCC、CCC等国内认证，是我国在电线电缆国际认证，尤其是美国UL认证领域具有数量领先优势的企业之一。</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>电线电缆, “华”字辈</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr"/>
+      <c r="D103" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>sh603289</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>泰瑞机器</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>10.0524</v>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>注塑机|公司是塑料注射成型设备的制造商和方案解决服务商，专业从事注塑机的研发、设计、生产、销售和服务。</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>注塑机</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr"/>
+      <c r="D104" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>sz002259</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>升达林业</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>9.9757</v>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>天然气|公司自2013年切入清洁能源行业以来，通过并购、自建等方式快速布局清洁能源业务板块，现已拥有多家涉及LNG业务的子公司，其主要经营业务为液化天然气的生产和销售、城镇燃气、加气站等，现已初步形成“液化天然气生产与销售-天然气管道-液化天然气运输-城镇燃气（管道输配）-加气站与调峰站”的产业链格局。公司目前的业绩主要来源于液化天然气销售业务。</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>天然气</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr"/>
+      <c r="D105" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>sh603636</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>南威软件</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>9.969799999999999</v>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁+AI应用|1.公司于2024年4月获得北京市发展和改革委员会批准，建设2300PFlops算力的“北京七星园数字经济产业智算中心”，用于服务企业人工智能发展、政府公共算力及企业算力需求。
+2.公司已发布AI智能体服务平台“白泽启元”、政务公文写作与协同平台“白泽文墨”、智能体客服平台“白泽对话管理”以及智能体BI产品“白泽云图”等白泽系列四款大模型智能体产品。</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁, AI应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr"/>
+      <c r="D106" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>sz002795</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>永和智控</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>9.9863</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>医疗器械|子公司成都永和成医疗科技有限公司主营业务为医疗器械研发、租赁及销售。</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>医疗器械</t>
         </is>
       </c>
     </row>
@@ -4168,7 +5372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4195,16 +5399,16 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sh603248</t>
+          <t>sz001216</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>锡华科技</t>
+          <t>华瓷股份</t>
         </is>
       </c>
     </row>
@@ -4214,27 +5418,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz001216</t>
+          <t>sh603230</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>内蒙新华</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh603230</t>
+          <t>sz002285</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>世联行</t>
         </is>
       </c>
     </row>
@@ -4244,72 +5448,72 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002285</t>
+          <t>sz002453</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>世联行</t>
+          <t>华软科技</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh603626</t>
+          <t>sh600448</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>科森科技</t>
+          <t>华纺股份</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz002453</t>
+          <t>sz000504</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>华软科技</t>
+          <t>南华生物</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh600448</t>
+          <t>sh600630</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>华纺股份</t>
+          <t>龙头股份</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sz301390</t>
+          <t>sh600127</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>经纬股份</t>
+          <t>金健米业</t>
         </is>
       </c>
     </row>
@@ -4319,12 +5523,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sz000504</t>
+          <t>sz000910</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>南华生物</t>
+          <t>大亚圣象</t>
         </is>
       </c>
     </row>
@@ -4334,12 +5538,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sz002836</t>
+          <t>sh601579</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>新宏泽</t>
+          <t xml:space="preserve">会稽山  </t>
         </is>
       </c>
     </row>
@@ -4349,12 +5553,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>sh600630</t>
+          <t>sh601123</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>龙头股份</t>
+          <t>马矿股份</t>
         </is>
       </c>
     </row>
@@ -4364,12 +5568,147 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>sh600127</t>
+          <t>sh601086</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>国芳集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>sz001317</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>三羊马</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>sh601811</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>sz002589</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>瑞康医药</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>sz001376</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>百通能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>sh600606</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>绿地控股</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>sh603001</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>奥康国际</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>sz000532</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>华金资本</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>sh603316</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>诚邦股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>sh603068</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>博通集成</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,20 +476,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="92" customWidth="1" min="3" max="3"/>
+    <col width="131" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="286" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="422" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,275 +552,279 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.1663</v>
+        <v>1.8411</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Meta旗下AI智能体Muse走红，提振市场对服务器CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%；AMD市值首次突破1万亿美元。</t>
+          <t>9月22日，江西省宏瑞兴科技股份有限公司发布调价通知，将覆铜板产品出厂价格上调10%，这是继中国巨石9月对电子布厚布、薄布分别提价15%和20%之后的又一轮材料涨价。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh600641</t>
+          <t>sh605058</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>先导基电</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>43.74</v>
+        <v>58.6</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.0101</v>
+        <v>10.0056</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>9天7板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>磷化铟|2026年7月1日公告，公司正在筹划对广东先导微电子科技有限公司增资以实现对其控制的相关事项。公司拟与清远先导特种材料有限公司、先导微电子签署《投资协议》，以增资形式对先导微电子进行投资，取得标的公司50%以上的股权。先导微电子主营砷化镓、磷化铟衬底晶圆制造，是国内少数实现4-6英寸磷化铟抛光片量产的企业，也是AI高速光模块、CPO（光电共封装）技术的上游核心材料供应商。</t>
+          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>磷化铟</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1663</v>
+        <v>1.8411</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Meta旗下AI智能体Muse走红，提振市场对服务器CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%；AMD市值首次突破1万亿美元。</t>
+          <t>9月22日，江西省宏瑞兴科技股份有限公司发布调价通知，将覆铜板产品出厂价格上调10%，这是继中国巨石9月对电子布厚布、薄布分别提价15%和20%之后的又一轮材料涨价。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz002290</t>
+          <t>sz000910</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>禾盛新材</t>
+          <t>大亚圣象</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>77.84999999999999</v>
+        <v>7.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.0042</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+        <v>10.0145</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>CPU|‌‌禾盛新材在持有熠知电子17.0491%股权，熠知电子核心业务是研发基于ARMCPU与自研NPU的异构计算芯片，提供覆盖云端服务器、边缘设备和终端嵌入式的全栈智能计算方案。</t>
+          <t>PCB|公司研发生产的超薄PCB纤维板主要用途电子线路垫板。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.1663</v>
+        <v>1.8411</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Meta旗下AI智能体Muse走红，提振市场对服务器CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%；AMD市值首次突破1万亿美元。</t>
+          <t>9月22日，江西省宏瑞兴科技股份有限公司发布调价通知，将覆铜板产品出厂价格上调10%，这是继中国巨石9月对电子布厚布、薄布分别提价15%和20%之后的又一轮材料涨价。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh600770</t>
+          <t>sh603328</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>综艺股份</t>
+          <t>依顿电子</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6.63</v>
+        <v>15.2</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.950199999999999</v>
+        <v>9.9855</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>CPU|公司旗下的集成电路设计企业主要有天一集成和神州龙芯。 神州龙芯是‌中国首家从事自主可控高端通用CPU研发及产业化的企业‌，起源于2002年成立北京神州龙芯集成电路设计有限公司。</t>
+          <t>PCB|公司专注于高精度、高密度双层及多层印制电路板的研发、生产和销售业务，作为首批进入国际大厂汽车PCB核心供应链的PCB厂商，公司PCB产品供货覆盖传统汽车零部件。
+2026年8月6日公告，公司拟使用自有资金及自筹资金投资建设高端印制电路板智能制造项目，计划总投资29.79亿元。投资项目主要围绕市场高端印制电路板需求，建设高端高速高多层PCB智能制造项目。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.1663</v>
+        <v>1.8411</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Meta旗下AI智能体Muse走红，提振市场对服务器CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%；AMD市值首次突破1万亿美元。</t>
+          <t>9月22日，江西省宏瑞兴科技股份有限公司发布调价通知，将覆铜板产品出厂价格上调10%，这是继中国巨石9月对电子布厚布、薄布分别提价15%和20%之后的又一轮材料涨价。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh603221</t>
+          <t>sz301150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>爱丽家居</t>
+          <t>中一科技</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>33.55</v>
+        <v>49.2</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>存储测试设备|爱丽家居公告称，公司拟筹划以自有和自筹现金方式收购不低于武汉欧康诺电子科技股份有限公司（简称“欧康诺”或“目标公司”）股权总数的77.08%的股权，欧康诺100%股权的整体估值不超过人民币6.5亿元；收购完成后，欧康诺将成为公司控股子公司。本次交易构成关联交易，预计不构成重大资产重组。目标公司专注于存储测试设备及测试服务领域。</t>
+          <t>PCB铜箔|在电子电路铜箔方面，公司产品规格覆盖8μm到210μm，并逐步向高端电子电路铜箔领域延伸，已经实现HDI用铜箔、RTF等产品批量销售，HVLP产品通过多家客户验证。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>存储测试设备</t>
+          <t>PCB铜箔</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.1663</v>
+        <v>1.8411</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Meta旗下AI智能体Muse走红，提振市场对服务器CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%；AMD市值首次突破1万亿美元。</t>
+          <t>9月22日，江西省宏瑞兴科技股份有限公司发布调价通知，将覆铜板产品出厂价格上调10%，这是继中国巨石9月对电子布厚布、薄布分别提价15%和20%之后的又一轮材料涨价。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh603216</t>
+          <t>sz002909</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>梦天家居</t>
+          <t>集泰股份</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>22.75</v>
+        <v>7.54</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.0097</v>
+        <v>10.073</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>家居+半导体|1.公司主要从事木门、墙板、柜类等定制化木质家具的设计、研发、生产和销售，为客户提供家居的整体空间解决方案。
-2.参股凌芯微通过创新整合极薄工艺、厚膜工艺、晶圆级封装三大核心制程，构建“CP测试-化镀-减薄-蚀刻-背金-晶圆级封装”一体化服务能力，覆盖功率器件中后段全流程制造需求，可高效支撑新能源汽车、工业控制、AI服务器、光伏储能等高端场景。</t>
+          <t>PCB|公司PCB三防漆涵盖有机硅、UV等多个系列，主要用于PCB电路板及电子元器件表面防护，可应用于智能设备、汽车电子、消费电子、工业控制、通信设备等场景。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>家居, 半导体</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.1663</v>
+        <v>1.8411</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Meta旗下AI智能体Muse走红，提振市场对服务器CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%；AMD市值首次突破1万亿美元。</t>
+          <t>9月22日，江西省宏瑞兴科技股份有限公司发布调价通知，将覆铜板产品出厂价格上调10%，这是继中国巨石9月对电子布厚布、薄布分别提价15%和20%之后的又一轮材料涨价。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh605178</t>
+          <t>sh603124</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>时空科技</t>
+          <t>江南新材</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>74.79000000000001</v>
+        <v>145</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.0015</v>
+        <v>9.9985</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>存储芯片测试|2025年10月9日公告，公司正在筹划以发行股份及支付现金的方式购买深圳市嘉合劲威电子科技有限公司的控股权，同时拟发行股份募集配套资金。本次交易预计构成重大资产重组。嘉合劲威业务核心围绕存储产品及相关应用展开，现已形成固件算法开发、存储芯片测试、集成封装设计、存储产品定制等核心竞争力，其存储芯片产品广泛应用于移动智能终端、PC、行业终端、数据中心等多个信息技术领域。</t>
+          <t>PCB材料|公司核心产品包括铜球系列、氧化铜粉系列及高精密铜基散热片系列三大产品类别，应用于PCB镀铜制程，下游客户覆盖大多数境内外一线PCB制造企业，包括鹏鼎控股、东山精密、健鼎科技、深南电路、瀚宇博德、景旺电子、志超科技、奥士康、胜宏科技、崇达技术、定颖电子、博敏电子等。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>存储芯片测试</t>
+          <t>PCB材料</t>
         </is>
       </c>
     </row>
@@ -831,41 +835,41 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.1663</v>
+        <v>0.782</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Meta旗下AI智能体Muse走红，提振市场对服务器CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%；AMD市值首次突破1万亿美元。</t>
+          <t>Muse爆火，提振市场对CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz001268</t>
+          <t>sh603396</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>联合精密</t>
+          <t>金辰股份</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>26.57</v>
+        <v>32.4</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.0207</v>
+        <v>10.017</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>机器人+光刻机|公司在建工程包括年产3万吨空调压宿机零部件、汽车零部件、机器人零部件、光刻机零部件铸件项目。</t>
+          <t>半导体设备|2026年8月25日公告，公司拟与江苏南通苏锡通科技产业园区管理委员会签订投资协议，投资设立“半导体装备研发及制造项目”，项目投资总额约10亿元。公司拟设立全资子公司辰光微电半导体设备(南通)有限公司作为项目公司，注册资本1000万元，持股比例100%。项目将建设现代化厂房和高标准洁净室，搭建以TGV玻璃基封装为代表的半导体设备生产试验线，推动超快激光诱导改质设备等半导体专用设备的研发与制造验证。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>机器人, 光刻机</t>
+          <t>半导体设备</t>
         </is>
       </c>
     </row>
@@ -876,42 +880,41 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.1663</v>
+        <v>0.782</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Meta旗下AI智能体Muse走红，提振市场对服务器CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%；AMD市值首次突破1万亿美元。</t>
+          <t>Muse爆火，提振市场对CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz301234</t>
+          <t>sz002119</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>五洲医疗</t>
+          <t>康强电子</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>139.74</v>
+        <v>26.92</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>20</v>
+        <v>10.0123</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>半导体+股权转让|1.五洲医疗公告称，公司拟通过发行股份及支付现金方式购买旋智电子科技(上海)有限公司100%股权，并募集配套资金。标的公司专注于高集成度电机控制芯片的研发、设计及销售，产品应用于智能装备、白色家电、工业控制及汽车电子等领域。本次交易完成后，上市公司将切入电机控制芯片领域，寻求第二增长曲线。
-2.五洲医疗公告称，公司股东黄凡及其一致行动人邹爱英、项炳义、张洪瑜及其一致行动人张樑、陈晓如、周乐翔与嘉兴汇芯企业管理合伙企业(有限合伙)签署股份转让协议，合计转让802.88万股(占公司总股本11.81%)，转让价格为48.53元/股，总价款3.9亿元。</t>
+          <t>封装材料|公司是一家专业从事各类半导体封装材料引线框架、键合丝等半导体封装材料的开发、生产、销售的高新技术企业，主要产品引线框架和键合丝国内市场规模处于领先地位，产品覆盖国内知名的半导体后封装企业。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>半导体, 股权转让</t>
+          <t>封装材料</t>
         </is>
       </c>
     </row>
@@ -922,41 +925,41 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.1663</v>
+        <v>0.782</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Meta旗下AI智能体Muse走红，提振市场对服务器CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%；AMD市值首次突破1万亿美元。</t>
+          <t>Muse爆火，提振市场对CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh603903</t>
+          <t>sz002989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>中持股份</t>
+          <t>中天精装</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>15.27</v>
+        <v>27.96</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.0144</v>
+        <v>9.992099999999999</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>半导体设备|2026年7月24日公告，公司拟与控股股东芯长征的全资子公司阅芯电子共同投资设立合资公司，注册资本1亿元，公司持股51%，阅芯电子持股49%。合资公司主要开展半导体设备业务，聚焦半导体先进封装领域缺陷量测设备的研发。</t>
+          <t>载板|公司间接参股科睿斯半导体主营业务为FCBGA（ABF)高端载板的生产和销售，产品主要应用于CPU、GPU、AI及车载等高算力芯片的封装。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>半导体设备</t>
+          <t>载板</t>
         </is>
       </c>
     </row>
@@ -967,41 +970,42 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.1663</v>
+        <v>0.782</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Meta旗下AI智能体Muse走红，提振市场对服务器CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%；AMD市值首次突破1万亿美元。</t>
+          <t>Muse爆火，提振市场对CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>920526.BJ</t>
+          <t>sh603991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>凯华材料</t>
+          <t>领先股份</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>26.14</v>
+        <v>185.57</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>29.9851</v>
+        <v>10</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>半导体+“华”字辈|公司主要从事电子元器件封装材料的研发、生产与销售，主营产品中的环氧塑封料是半导体封装工艺中的主要封装材料之一。</t>
+          <t xml:space="preserve">半导体设备|子公司苏州桔云主要从事半导体专用设备的研发、生产和销售，主要产品包括清洗设备、腐蚀设备、涂胶显影设备、去胶设备、烘箱设备、分片设备等，产品线较为丰富。苏州桔云专注于后道先进封装领域设备的研发，并逐步向前道拓展，围绕清洗设备、烘箱设备等持续深耕细作，形成自身独特的产品及技术优势，并凭借其较高的性价比优势和定制化、快速响应的客户服务优势不断扩大市场份额。
+</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>半导体, “华”字辈</t>
+          <t>半导体设备</t>
         </is>
       </c>
     </row>
@@ -1012,937 +1016,930 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.1663</v>
+        <v>0.782</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Meta旗下AI智能体Muse走红，提振市场对服务器CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%；AMD市值首次突破1万亿美元。</t>
+          <t>Muse爆火，提振市场对CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz300324</t>
+          <t>sh688512</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>旋极信息</t>
+          <t>慧智微-U</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4.14</v>
+        <v>17.32</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>20</v>
+        <v>20.0277</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>算力芯片|2025年6月30日盘后公告，公司参股公司浙江曲速完成对赌约定，浙江曲速已开发出新产品“TGU01芯片"，新产品为AI大模型推理芯片，搭载该芯片的板卡及服务器(名称为Bumblebee)已上市销售。2023年公司使用3亿元购买浙江曲速13.23%股权。</t>
+          <t xml:space="preserve">射频前端芯片|公司是一家为智能手机、物联网等领域提供射频前端的芯片设计公司，主营业务为射频前端芯片及模组的研发、设计和销售。公司具备全套射频前端芯片设计能力和集成化模组研发能力，技术体系以功率放大器（PA）的设计能力为核心，兼具低噪声放大器（LNA）、射频开关（Switch）、集成无源器件滤波器（IPD Filter）等射频器件的设计能力，产品系列覆盖的通信频段需求包括2G、3G、4G、3GHz以下的5G重耕频段、3GHz~6GHz 的5G新频段等，可为客户提供无线通信射频前端发射模组、接收模组等。2021年公司在智能手机领域5G L-PAMiF出货量为1132.33万颗，同口径下市占率估算约为1.96%，在国产厂商中排名第二。公司的射频前端模组已经在三星全球畅销系列A22 5G手机和OPPO、vivo、荣耀等智能手机机型中实现大规模量产，并进入闻泰科技、华勤通讯和龙旗科技等一线移动终端设备ODM厂商，拥有较为优质的客户结构。
+</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>算力芯片</t>
+          <t>射频前端芯片</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.3265</v>
+        <v>-0.8371999999999999</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>日前算力租赁厂商Nebius宣布GPU云服务价格上调17%至21%。渤海证券研报称，当前围绕Token的调用、分发与结算，一套新的价值体系正在加速形成，并成为人工智能产业可能变现的重要路径，持续看好AI时代“词元经济”发展浪潮下算力租赁等AI云计算服务环节。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603230</t>
+          <t>sh603636</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>南威软件</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>16.31</v>
+        <v>8.81</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9.979799999999999</v>
+        <v>9.987500000000001</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5天5板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>传媒+“华”字辈|公司的最终控制人为内蒙古自治区人民政府。公司主营业务是出版物的批发、零售；文体用品零售；音像制品发行</t>
+          <t>算力|1.公司于2024年4月获得北京市发展和改革委员会批准，建设2300PFlops算力的“北京七星园数字经济产业智算中心”，用于服务企业人工智能发展、政府公共算力及企业算力需求。
+2.公司已发布AI智能体服务平台“白泽启元”、政务公文写作与协同平台“白泽文墨”、智能体客服平台“白泽对话管理”以及智能体BI产品“白泽云图”等白泽系列四款大模型智能体产品。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>传媒, “华”字辈</t>
+          <t>算力</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2.3265</v>
+        <v>-0.8371999999999999</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>日前算力租赁厂商Nebius宣布GPU云服务价格上调17%至21%。渤海证券研报称，当前围绕Token的调用、分发与结算，一套新的价值体系正在加速形成，并成为人工智能产业可能变现的重要路径，持续看好AI时代“词元经济”发展浪潮下算力租赁等AI云计算服务环节。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sz002238</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>天威视讯</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>16.82</v>
+        <v>7.66</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.0065</v>
+        <v>10.0575</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>并购重组+传媒|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
+          <t xml:space="preserve">算力工程|公司初步形成位于深圳市福田区、南山区、龙华区以及深汕合作区的3000个5-8KW 机柜规模的数据中心布局，正在加紧推进系统调试、检测、认证、以及销售运维团队招选等正式投产前相关运营准备工作，未来将结合自身经营状况和行业发展状况来评估包括算力服务在内的增值业务的必要性、可行性和经济效益，再研究是否推出相应的数据中心增值服务业务。
+</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 传媒</t>
+          <t>算力工程</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2.3265</v>
+        <v>-0.8371999999999999</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>日前算力租赁厂商Nebius宣布GPU云服务价格上调17%至21%。渤海证券研报称，当前围绕Token的调用、分发与结算，一套新的价值体系正在加速形成，并成为人工智能产业可能变现的重要路径，持续看好AI时代“词元经济”发展浪潮下算力租赁等AI云计算服务环节。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz000607</t>
+          <t>sz002849</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>华媒控股</t>
+          <t>威星智能</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>4.98</v>
+        <v>23</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9.9338</v>
+        <v>9.995200000000001</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>传媒+AI+“华”字辈|1.公司主要从事广告策划发布、报刊发行与印刷、教育等业务，涵盖平面媒体、网络媒体、移动新媒体、户外 媒体包括地铁媒体的广告承揽发布、企事业单位宣传公关的全案策划和实施。
-2.公司控股子公司中教未来的业务板块之一是IT教育。旗下部分幼儿园引进AI智能机器人，培养人机协同的兴趣和科学探索精神，以便适应AI智能对孩子学习的辅助作用。</t>
+          <t>算力|2023年7月24日公告，近日，公司与贵安管委会、摩尔线程签署《贵安智算中心项目投资合作协议》，三方拟在贵安新区建立智算中心，在3D图形渲染和视觉设计、高性能科学计算、HDV高速视频解编码、AI训练和推理等应用领域构建深度合作关系。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>传媒, AI, “华”字辈</t>
+          <t>算力</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>算力工程</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2.3265</v>
+        <v>-0.8371999999999999</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>日前算力租赁厂商Nebius宣布GPU云服务价格上调17%至21%。渤海证券研报称，当前围绕Token的调用、分发与结算，一套新的价值体系正在加速形成，并成为人工智能产业可能变现的重要路径，持续看好AI时代“词元经济”发展浪潮下算力租赁等AI云计算服务环节。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sh603803</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6.42</v>
+        <v>12.87</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>9.9315</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>并购重组+传媒|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
+          <t>算力交换机|1.在高端光模块领域，公司联营企业易锐光电是中国少数产业链上下游关键层面具备完整核心技术和解决方案的高科技企业，新一代基于自主知识产权的25G/100G/超100G集成光收发芯片的光通信模块及光组件，用于电信网络城域网和大型数据中心网络。
+2.2022年，公司自主研发的100%国产化工业以太网交换机在电力DCS系统实现应用。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 传媒</t>
+          <t>算力交换机</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>科学仪器</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.3265</v>
+        <v>5.038200000000001</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>华泰证券研报指出，随着数据中心网络向800G、1.6T演进，高速连接器、线缆及高端PCB对信号完整性与良率管控的要求持续提高，带动VNA测试需求增长；同时测试向更高频率、更多端口及自动化方向升级，有望推动VNA量价齐升。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh603598</t>
+          <t>sh688628</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>引力传媒</t>
+          <t xml:space="preserve">优利德  </t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>18.96</v>
+        <v>114.44</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.976799999999999</v>
+        <v>19.9958</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>传媒+AI|1.公司是一家以内容创意与科技创新驱动的卓越数字商业服务公司。
-2.公司已推出自有营销电商行业模型并推出三大智能体（Agent）-感知智能体、决策智能体、内容智能体，用以增强营销决策、创意素材、视频混剪等环节内容产出的精准性与稳定性。</t>
+          <t>PCB检测|公司致力于测试测量仪器仪表的研发、生产和销售，涉及电子电工、测试仪器、温度及环境、电力及高压、测绘测量等产品线，是行业内产品系列较为丰富和齐全的企业。测试仪器产品包括实验系统综合测试平台、示波器、信号发生器、频谱分析仪、电源负载和电子元器件测试仪等产品。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>传媒, AI</t>
+          <t>PCB检测</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>科学仪器</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2.3265</v>
+        <v>5.038200000000001</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>华泰证券研报指出，随着数据中心网络向800G、1.6T演进，高速连接器、线缆及高端PCB对信号完整性与良率管控的要求持续提高，带动VNA测试需求增长；同时测试向更高频率、更多端口及自动化方向升级，有望推动VNA量价齐升。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz002238</t>
+          <t>sz002819</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>天威视讯</t>
+          <t>东方中科</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>6.96</v>
+        <v>24.24</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.9526</v>
+        <v>9.981900000000001</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>传媒+数据中心|1.公司是深圳地区最主要的电视服务提供商，主要向用户提供有线数字业务（包括基本收视、增值业务）、互联网宽带接入服务、视频购物服务和政企项目服务。
-2.公司初步形成位于深圳市福田区、南山区、龙华区以及深汕合作区的3000个5-8KW 机柜规模的数据中心布局。</t>
+          <t xml:space="preserve">测试测量仪器|公司定位为电子测试测量领域领先的综合服务商，专注于为客户提供包括仪器销售、租赁、系统集成，主要产品包括示波器、数据记录仪、频谱分析仪、光谱仪、质谱仪、色谱仪等。
+</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>传媒, 数据中心</t>
+          <t>测试测量仪器</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>科学仪器</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2.3265</v>
+        <v>5.038200000000001</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>华泰证券研报指出，随着数据中心网络向800G、1.6T演进，高速连接器、线缆及高端PCB对信号完整性与良率管控的要求持续提高，带动VNA测试需求增长；同时测试向更高频率、更多端口及自动化方向升级，有望推动VNA量价齐升。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh601949</t>
+          <t>sh688337</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>中国出版</t>
+          <t>普源精电</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>6.62</v>
+        <v>57.18</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.966800000000001</v>
+        <v>20</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>AI+传媒|1.公司推动“文化+科技”业态创新，中华古籍大模型建设初步完成，东方“多AI平台协同工作流”提升视频生产效率。
-2.公司是以图书、报纸、期刊等出版物出版为主业，是集出版、发行、物资供应、印刷等业务于一体的大型出版企业，拥有丰富的作者、译者、内容资源。</t>
+          <t xml:space="preserve">科学仪器|2023年9月17日公告，公司首次正式公开发布13GHz带宽的DS80000系列数字示波器。该新产品通过自研核心技术平台，首次实现国产数字示波器产品带宽达到13GHz，具备国内行业技术领先优势和核心技术壁垒。
+</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>AI, 传媒</t>
+          <t>科学仪器</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>科学仪器</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.3989</v>
+        <v>5.038200000000001</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Meta在9月初推出的消费级AI智能体Muse，据当地媒体援引Sensor Tower数据，自从上周登顶后，Muse已连续三天位居美国iPhone免费应用下载榜首。</t>
+          <t>华泰证券研报指出，随着数据中心网络向800G、1.6T演进，高速连接器、线缆及高端PCB对信号完整性与良率管控的要求持续提高，带动VNA测试需求增长；同时测试向更高频率、更多端口及自动化方向升级，有望推动VNA量价齐升。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz002301</t>
+          <t>sh688056</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>齐心集团</t>
+          <t>莱伯泰科</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>9.27</v>
+        <v>52.92</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.964399999999999</v>
+        <v>20</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>AI应用|公司云视频业务通过“云+端+SDK/API”解决方案覆盖多终端、多平台、多场景，融合AI人工智能技术和音视频算法，研发升级智能云视频灵犀算法和夜莺AI音频算法，为组织数字化升级提供云视频服务。</t>
+          <t>实验分析仪器|公司是一家专业从事实验分析仪器研发、生产和销售、提供洁净环保型实验室解决方案以及实验室耗材和相关服务的高新技术企业，致力于研发全自动实验检测平台，联接包括样品采集与处理、自动化进样、分析检测、智能数据分析在内的全检测流程，覆盖并联通实验分析的各个环节，为环境监测、食品检测、医疗制药、地质勘测等领域的用户提供自动化、系统化的实验分析检测整体解决方案。公司是全球范围内能将多种类和多功能的样品前处理技术与全自动分析实验分析检测平台组合成全自动实验分析仪器系统的主要实验分析仪器供应商之一。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>实验分析仪器</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.3989</v>
+        <v>0.05810000000000001</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Meta在9月初推出的消费级AI智能体Muse，据当地媒体援引Sensor Tower数据，自从上周登顶后，Muse已连续三天位居美国iPhone免费应用下载榜首。</t>
+          <t>消息面上，网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高；截至9月19日，9月上海二手房累计成交15597套，同比上涨28%。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz000676</t>
+          <t>sh600743</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>智度股份</t>
+          <t>华远控股</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>7.45</v>
+        <v>2.82</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.0443</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+        <v>10.1562</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>AI应用|公司的AI技术主要是AI算法，如公司海外子公司SPE，是以算法和大数据技术为驱动的第三方搜索流量入口公司，通过大数据和算法对发行渠道和产品用户进行多维度分析，从而以低成本获取高质量的用户，同时为用户提供搜索入口服务，并将搜索请求分发给合作的互联网企业，从而获得可观的商业变现收入。</t>
+          <t>房地产+并购重组|2025年4月，公司完成了重大资产重组，已将持有的房地产开发业务相关资产及负债转让至公司控股股东华远集团，实现了从重资产开发商向轻资产服务商的价值重构。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>房地产, 并购重组</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.3989</v>
+        <v>0.05810000000000001</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Meta在9月初推出的消费级AI智能体Muse，据当地媒体援引Sensor Tower数据，自从上周登顶后，Muse已连续三天位居美国iPhone免费应用下载榜首。</t>
+          <t>消息面上，网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高；截至9月19日，9月上海二手房累计成交15597套，同比上涨28%。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh605398</t>
+          <t>sz000560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>新炬网络</t>
+          <t>我爱我家</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>23.63</v>
+        <v>3.86</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.0093</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+        <v>9.971499999999999</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>AI应用|公司自主研发的低代码开发平台可开放企业现有数字化运维/运营基础能力，实现敏捷业务创新，并面向运维、运营人员提供个性场景快速构建能力。</t>
+          <t>地产中介|地产平台运营商，基于二十余年的锐意进取，以专业、安全、高效的运营管理体系为支撑，为客户提供高品质、一站式的居住全生命周期综合服务。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>地产中介</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.3989</v>
+        <v>0.05810000000000001</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Meta在9月初推出的消费级AI智能体Muse，据当地媒体援引Sensor Tower数据，自从上周登顶后，Muse已连续三天位居美国iPhone免费应用下载榜首。</t>
+          <t>消息面上，网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高；截至9月19日，9月上海二手房累计成交15597套，同比上涨28%。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz002757</t>
+          <t>sh600503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>南兴股份</t>
+          <t>华丽家族</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>19.86</v>
+        <v>2.94</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.0277</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
+        <v>10.1124</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>算力+AI智能体|1.公司子公司唯一网络业务范围包括：云数据中心、网络安全、云专线、公有云、私有云、混合云等服务，唯一网络与阿里云、华为云、腾讯云、天翼云、金山云等均有业务合作关系。
-2.公司与微软合作的小鹭AIGC智能助手已经上线，能为行业客户提供AIGC应用产品和解决方案,可满足客户对智能化的问题解答、协同办公和信息查询等需求。</t>
+          <t>房地产开发|公司是一家以房地产开发为主营业务，以改善型产品为主的中小型房地产企业，房地产开发业务主要分布在上海、苏州和遵义三地，打造了上海檀宫、华丽家族浦东花园、华丽家族古北花园等精品楼盘。截至2024年12月31日，公司土地储备面积约6.5万平方米，包含苏州项目待开发土地面积约2.32万平方米、遵义项目待开发土地面积约4.18万平方米。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>算力, AI智能体</t>
+          <t>房地产开发</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1.3989</v>
+        <v>0.05810000000000001</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Meta在9月初推出的消费级AI智能体Muse，据当地媒体援引Sensor Tower数据，自从上周登顶后，Muse已连续三天位居美国iPhone免费应用下载榜首。</t>
+          <t>消息面上，网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高；截至9月19日，9月上海二手房累计成交15597套，同比上涨28%。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sz002912</t>
+          <t>sh600605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>汇通能源</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>26.38</v>
+        <v>31.61</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10.0083</v>
+        <v>9.9861</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>AI+网络安全|公司推出的小赛安全智脑产品，支持多模型底座，基于智能体、RAG等技术，包含渗透测试智能体、事件调查智能体、代码安全审计智能体，也配备了敏感数据识别、智能解码、安全知识问答等多种智能体应用，全方位满足安全运维场景下的各类用户需求，为企业数据与网络安全保驾护航。</t>
+          <t>房屋租赁|公司的主营业务为房屋租赁，物业服务及房地产开发与销售等。公司房产管理团队负责公司房产招商租赁及运营管理，同时对公司持有的空置房产，厂房等重新规划和定位，因地制宜地提出经营方案。公司房产租赁项目主要集中在上海中心城区，出租建筑面积过万平方米的行政区域有静安区，闵行，虹口，浦东新区及宝山区。此外，公司也积极在尝试通过承租获取房产使用权和收益权。公司房产管理团队同时对出租房产提供物业服务，同时负责运营郑州“百年德化·风情购物公园”项目。公司住宅地产开发业务实施聚焦和城市深耕战略，在江西市场，以南昌为根据地，快速建立住宅开发的操盘能力，通过项目的成功树立品牌。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>AI, 网络安全</t>
+          <t>房屋租赁</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>建材</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1.3989</v>
+        <v>0.1403</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Meta在9月初推出的消费级AI智能体Muse，据当地媒体援引Sensor Tower数据，自从上周登顶后，Muse已连续三天位居美国iPhone免费应用下载榜首。</t>
+          <t>住建部表示，“十五五”时期提升人民群众居住水平关键是建设好房子。将层高标准从原来的2.8米提高到3米；为解决老年群体上下楼的问题，新标准提出4楼及以上住宅都要加装电梯。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sh603039</t>
+          <t>sh600293</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>泛微网络</t>
+          <t>三峡新材</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>39.7</v>
+        <v>3.7</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.0028</v>
+        <v>10.119</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>AI智能体|泛微数智大脑Xiaoe.AI为组织每个用户提供了一位7*24工作的智能助理。有了Xiaoe.AI的支撑，办理事务无需摸索与学习多个系统，也不用填写大量的、重复的表单和信息，只要对着手机喊话就完成工作，让组织的业务运营更加敏捷。</t>
+          <t>玻璃|中部最大、全国十强的玻璃生产企业，主营业务为平板玻璃及玻璃深加工和移动互联网终端产品销售及服务行业，已有浮法玻璃生产线五条，日熔化玻璃液3700吨，产能达到2460万重箱，有玻璃精深加工线五条，年玻璃精深加工500万平米。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>AI智能体</t>
+          <t>玻璃</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>建材</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.7672</v>
+        <v>0.1403</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>美股“癌症疫苗”牛股莫德纳周一收涨12.27%，接近回到8月19日发布“癌症疫苗”结果后创出的年内高点。</t>
+          <t>住建部表示，“十五五”时期提升人民群众居住水平关键是建设好房子。将层高标准从原来的2.8米提高到3米；为解决老年群体上下楼的问题，新标准提出4楼及以上住宅都要加装电梯。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz000504</t>
+          <t>sh600802</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>南华生物</t>
+          <t>福建水泥</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>12.11</v>
+        <v>6.02</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>9.9909</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>10.0548</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>医药+“华”字辈|公司是目前国内一家国资控股的干细胞、免疫细胞及组织工程产业主板上市公司，“生物医药”板块业务包括干细胞储存服务、化妆品的生产和销售、医疗器械设备及耗材的代理和销售。</t>
+          <t>水泥|公司主要从事水泥及熟料的生产及销售，拥有7条新型干法熟料水泥生产线，具备年产熟料784.3万吨、水泥1164万吨。公司是福建地区产能规模最大的水泥制造企业，也是福建省水泥行业唯一的一家上市公司。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>医药, “华”字辈</t>
+          <t>水泥</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>建材</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.7672</v>
+        <v>0.1403</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>美股“癌症疫苗”牛股莫德纳周一收涨12.27%，接近回到8月19日发布“癌症疫苗”结果后创出的年内高点。</t>
+          <t>住建部表示，“十五五”时期提升人民群众居住水平关键是建设好房子。将层高标准从原来的2.8米提高到3米；为解决老年群体上下楼的问题，新标准提出4楼及以上住宅都要加装电梯。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh600721</t>
+          <t>sz002541</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>鸿路钢构</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>14.47</v>
+        <v>19.69</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10.038</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>CXO|公司主营业务为药物发现、研究、技术服务，提供从药物发现、CMC、临床CRO、药品注册、CMO/API供应等新药开发全流程的服务及一体化的解决方案。</t>
+          <t>建材|国内钢结构品种最齐全的制造企业，主营业务主要有钢结构制造销售、新型建材产品生产销售、钢结构工程专业承包、智能立体车库生产销售及钢结构装配式建筑总承包等五大类业务。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>CXO</t>
+          <t>建材</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.7672</v>
+        <v>-0.0221</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>美股“癌症疫苗”牛股莫德纳周一收涨12.27%，接近回到8月19日发布“癌症疫苗”结果后创出的年内高点。</t>
+          <t>无人机视频显示，特斯拉Optimus在美国得州的专用生产线建设主结构可能接近完工，钢结构、混凝土浇筑等施工正同步推进。该生产线计划2027年计划投产，年产能目标在1000万台。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sh600664</t>
+          <t>sz002614</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>奥佳华</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>9.08</v>
+        <v>7.57</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10.0606</v>
+        <v>10.0291</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>创新药|在创新药研发领域，公司制定了研发的短中长期规划，涉及心血管、代谢、呼吸、抗感染和抗肿瘤等领域，积极探索产品研发新路径，全面丰富公司产品线。</t>
+          <t>机器人|公司AI按摩机器人2.0（OG-8598Plus），已实现服务功能与产品有机结合，运用人脸识别、疲感侦测、“千人千方”智能AI算法、云端个人健康数据库、新一代4D无刷变频温感机芯等新技术构建围绕用户健康的检测-分析-调理闭环服务系统，关注每一位用户的健康状态，为用户远程推送“量身定制”的专属按摩解决方案，构建家庭健康管理服务生态。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.7672</v>
+        <v>-0.0221</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>美股“癌症疫苗”牛股莫德纳周一收涨12.27%，接近回到8月19日发布“癌症疫苗”结果后创出的年内高点。</t>
+          <t>无人机视频显示，特斯拉Optimus在美国得州的专用生产线建设主结构可能接近完工，钢结构、混凝土浇筑等施工正同步推进。该生产线计划2027年计划投产，年产能目标在1000万台。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz000756</t>
+          <t>sh603949</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>新华制药</t>
+          <t>雪龙集团</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>16.14</v>
+        <v>15.36</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.0204</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0287</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>医药+“华”字辈|公司围绕心脑血管类、解热镇痛类、消化系统类、抗代谢类、神经系统、精麻药品等方向开展研发工作，包括创新药物和仿制药。进入研发管线的药物有100多个。</t>
+          <t>机器人|公司作为有限合伙人通过深创投中小企业发展基金（新疆）有限合伙企业间接持股杭州宇树科技有限公司。目前，深创投中小企业发展基金（新疆）有限合伙企业对杭州宇树科技有限公司的持股比例为1.3546%；公司对深创投中小企业发展基金（新疆）有限合伙企业的持股比例为0.7239%。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>医药, “华”字辈</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.7672</v>
+        <v>-0.0221</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>美股“癌症疫苗”牛股莫德纳周一收涨12.27%，接近回到8月19日发布“癌症疫苗”结果后创出的年内高点。</t>
+          <t>无人机视频显示，特斯拉Optimus在美国得州的专用生产线建设主结构可能接近完工，钢结构、混凝土浇筑等施工正同步推进。该生产线计划2027年计划投产，年产能目标在1000万台。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz300110</t>
+          <t>sh603373</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>华仁药业</t>
+          <t>安邦护卫</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>3.95</v>
+        <v>47.96</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>20.0608</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>医药+“华”字辈|公司是一家集研发、生产、销售为一体的，以精麻科、呼吸科、肾科、治疗性大容量制剂、医疗器械等产品为主线，以基础输液、大健康产品为两翼，原料药、制剂、医药包材、医疗器械等板块全面协同发展的国有控股医药健康产业集团。</t>
+          <t>机器人|温州安邦护卫联合温州理工学院科研团队打造了“智能安防中枢平台”，创新性地应用四足机器人技术，引入了安防巡逻机器人用于库房管理，进一步提升库房管理的智能化水平。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>医药, “华”字辈</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.7672</v>
+        <v>0.3387</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>美股“癌症疫苗”牛股莫德纳周一收涨12.27%，接近回到8月19日发布“癌症疫苗”结果后创出的年内高点。</t>
+          <t>苹果首款折叠屏iPhone Duo有望推动折叠手机走向主流，并预计苹果未来将进一步扩充该产品线，推出更大屏幕的iPhone Duo Max。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh600479</t>
+          <t>sz002426</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>千金药业</t>
+          <t>胜利精密</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>13.57</v>
+        <v>2.96</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>9.967600000000001</v>
+        <v>10.0372</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>医药|公司主要从事中成药、化学药和女性卫生用品的研制、生产和销售以及药品的批发和零售业务，已初步构建了包括医药制造、医药流通和中药种植在内的医药全产业链业务架构。“千金”为妇科中成药领域首个中国驰名商标，主要产品有妇科千金片（胶囊）、补血益母丸（颗粒）、椿乳凝胶、妇科断红饮胶囊等11个独家品种。</t>
+          <t>消费电子|公司精密结构模组业务主要涉及精密金属结构件、塑胶结构件和盖板玻璃等产品的生产加工，广泛应用于电视、笔记本、手机、车载视窗，以及手表、手环等可穿戴智能终端产品上。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>消费电子</t>
         </is>
       </c>
     </row>
@@ -1953,45 +1950,42 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.5216000000000001</v>
+        <v>0.3387</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2026年9月22日机构研报，MetaMuse引爆端侧场景，与自有AI眼镜结合实现”用户触达——生活场景落地”的完整闭环。</t>
+          <t>苹果首款折叠屏iPhone Duo有望推动折叠手机走向主流，并预计苹果未来将进一步扩充该产品线，推出更大屏幕的iPhone Duo Max。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh603068</t>
+          <t>sz002635</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>博通集成</t>
+          <t>安洁科技</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>48.17</v>
+        <v>16.79</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.0023</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.0262</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>端侧AI芯片|公司依托在AI无线通信的经验和技术积累，将研发资源拓展至端侧AI算力。公司发布的BK7259作为AIoT算力标杆，率先集成ARM Ethos-U65 microNPU的Wi-Fi 6 MCU，为边缘智能应用注入超强算力与卓越能效。</t>
+          <t>消费电子|1.公司已有折叠屏相关技术储备，且已为多个品牌客户的多款折叠产品提供相关精密结构件和精密功能件。
+2.安洁科技公告称，公司全资子公司威斯东山拟以现金方式收购苏州志烽密姆粉末冶金有限公司51%股权，基础对价为2.04亿元，或有对价上限不超过5100万元，合计不超过2.55亿元。本次交易完成后，苏州志烽将成为公司控股子公司，纳入合并报表范围。苏州志烽以金属粉末注射成型（MIM）为核心工艺，主要为光通信互联、新能源汽车、高端医疗等领域配套产品，主要产品包括光模块芯片基座等。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>端侧AI芯片</t>
+          <t>消费电子</t>
         </is>
       </c>
     </row>
@@ -2002,36 +1996,36 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.5216000000000001</v>
+        <v>0.3387</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2026年9月22日机构研报，MetaMuse引爆端侧场景，与自有AI眼镜结合实现”用户触达——生活场景落地”的完整闭环。</t>
+          <t>苹果首款折叠屏iPhone Duo有望推动折叠手机走向主流，并预计苹果未来将进一步扩充该产品线，推出更大屏幕的iPhone Duo Max。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh605218</t>
+          <t>sz002937</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>伟时电子</t>
+          <t>兴瑞科技</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>15.94</v>
+        <v>30.13</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10.0069</v>
+        <v>10.0037</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>消费电子|公司主要从事背光显示模组、液晶显示模组、触控装饰面板、显示组件、智能显示等产品研发、生产、销售，公司产品主要应用于中高端汽车、手机、平板电脑、数码相机、小型游戏机、工控显示、智能家居、VR等领域。</t>
+          <t>消费电子|公司以模具技术和智能制造为核心，通过与客户同步设计，采用精密注塑／冲压和自动化组装等先进技术，为智能终端，汽车电子，消费电子等领域中高端客户提供定制化整体解决方案，为客户提供电子连接器、结构件、塑料外壳外壳、镶嵌注塑件等精密电子零部件产品及模具产品。智能终端领域主要客户为ARRIS、TECHNICOLOR、HUMAX、SAGEMCOM、仁宝电脑、金宝电子、富士康等；消费电子领域主要客户为柯尼卡美能达、SONY、SAMSUNG、LG、ABB等。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2043,174 +2037,174 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.5216000000000001</v>
+        <v>-0.0145</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026年9月22日机构研报，MetaMuse引爆端侧场景，与自有AI眼镜结合实现”用户触达——生活场景落地”的完整闭环。</t>
+          <t>消息面上，华源证券最新研报指出，创新药行业多维向好，CRO需求逐步复苏。中国创新药审批与支付双端政策环境改善，临床CRO需求延续复苏态势，市场有望持续扩容。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz002313</t>
+          <t>sh688656</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>日海智能</t>
+          <t xml:space="preserve">浩欧博  </t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>141.04</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10.0592</v>
+        <v>20.0034</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>算力模组|公司有智能模组产品，部分产品可以提供10-15TOPS左右的算力，满足智能终端对于中低算力边缘计算的需求。</t>
+          <t>体外诊断试剂|公司专业从事体外诊断试剂的研发、生产和销售，专注于过敏性疾病和自身免疫性疾病的检测，所生产的检测试剂应用于过敏性疾病和自身免疫性疾病的临床辅助诊断，产品在全国各级医疗机构得到广泛使用。公司过敏产品已扩展到多个系列，覆盖69种IgE过敏原及80种食物特异性IgG过敏原，可检测的IgE过敏原数量国内领先。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>算力模组</t>
+          <t>体外诊断试剂</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.5216000000000001</v>
+        <v>-0.0145</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2026年9月22日机构研报，MetaMuse引爆端侧场景，与自有AI眼镜结合实现”用户触达——生活场景落地”的完整闭环。</t>
+          <t>消息面上，华源证券最新研报指出，创新药行业多维向好，CRO需求逐步复苏。中国创新药审批与支付双端政策环境改善，临床CRO需求延续复苏态势，市场有望持续扩容。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh688781</t>
+          <t>sh603222</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>视涯科技-UW</t>
+          <t>济民健康</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>51.95</v>
+        <v>8.94</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>20.0046</v>
+        <v>9.963099999999999</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>次新+消费电子|视涯科技为全球硅基OLED核心厂商，公司核心产品为硅基OLED微型显示屏，并为客户提供包括战略产品开发、光学系统和XR整体解决方案等增值服务。</t>
+          <t>医药|公司系浙江省医药行业重点骨干企业，产业已覆盖大输液、医疗器械、血液透析、体外诊断试剂、综合医疗服务等5大领域，初步构建形成“一主两翼”发展格局。主导产品“双管双阀非PVC软袋”大输液在华东、华南地区市场占有率达30%以上，国外销售东南亚、非洲、南美等30多个国家和地区。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>次新, 消费电子</t>
+          <t>医药</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.2183</v>
+        <v>-2.5779</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。</t>
+          <t>国家版权局印发《版权工作“十五五”规划》，其中提出2030年版权质权融资登记金额目标为120亿元。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh605058</t>
+          <t>sh601811</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>53.27</v>
+        <v>18.5</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.9938</v>
+        <v>9.988099999999999</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8天6板</t>
+          <t>4天4板</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
+          <t>传媒+并购|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>传媒, 并购</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.2183</v>
+        <v>-2.5779</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。</t>
+          <t>国家版权局印发《版权工作“十五五”规划》，其中提出2030年版权质权融资登记金额目标为120亿元。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz000910</t>
+          <t>sh600825</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>大亚圣象</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>6.89</v>
+        <v>7.06</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.0639</v>
+        <v>9.9688</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -2219,628 +2213,590 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>PCB+机器人|1.公司研发生产的超薄PCB纤维板主要用途电子线路垫板。
-2.公司以自有资金1,500万元人民币认购嘉兴翼龙股权投资合伙企业 （有限合伙）28.30189%的份额，该基金以股权投资的方式投资七腾机器人有限公司。</t>
+          <t>传媒+并购|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>PCB, 机器人</t>
+          <t>传媒, 并购</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.2183</v>
+        <v>-0.8027</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。</t>
+          <t>华泰证券研报判断，黄酒行业的量价逻辑有望迎来重构。从量的弹性看，消费场景稳步升级，先由江浙沪渗透率提升，后到全国市场的稳步拓展；从价的维度看，在行业竞争格局优化背景下，龙头企业合力培育品牌，稳步推动高端化进程。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sh605258</t>
+          <t>sz002286</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>协和电子</t>
+          <t>保龄宝</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>42.16</v>
+        <v>8.75</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>9.9922</v>
+        <v>10.0629</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司主要从事印制电路板的研发、生产、销售以及SMT业务，PCB产品主要应用在汽车电子和高频通讯领域。</t>
+          <t>功能糖|公司主要产品完整覆盖高、中、低全品类功能糖产品，形成了完整的淀粉—淀粉糖—益生元—膳食纤维—功能糖醇及新糖源—益生元终端的金字塔式产品结构，可提供全品类的功能性低聚糖、功能性膳食纤维、功能性糖醇及新糖源等综合性应用解决方案、产品和服务。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>功能糖</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>农业种植</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.2183</v>
+        <v>-1.3155</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。</t>
+          <t>近日农业农村部召开全国“三秋”农业生产工作视频会议，会议强调，要紧盯不放抓好秋管秋收，密切关注超强厄尔尼诺气候影响，细化气象灾害和病虫草害应急预案，扎实推进高标准农田建设。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sz002141</t>
+          <t>sh600371</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>贤丰控股</t>
+          <t>万向德农</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>7.43</v>
+        <v>17.28</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10.0741</v>
+        <v>9.993599999999999</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司旗下高硕航宇与上下游协同运作构建起了完整覆铜板产业链，主要产品包括常规FR-4/CEM-3系列覆铜板、无铅无卤FR-4系列覆铜板等，具备60万余张/月覆铜板产能。
-2026年7月15日公告，子公司贤丰东莞与广东盈硕签署协议，共同出资设立贤丰盈硕科技有限公司，注册资本1.18亿元。贤丰东莞以货币出资6018万元，持股51%；广东盈硕以货币及实物出资5782万元，持股49%。合资公司主要业务为消费领域PCB的研发、生产和销售。</t>
+          <t>玉米种子|公司从事的主要业务为玉米杂交种子研发、生产、销售，主营包括但不限于“京科968”、“德单系列”等玉米杂交种的生产与销售。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>玉米种子</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>电子烟</t>
+          <t>量子科技</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1.2542</v>
+        <v>0.5506</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>7月28日，由国家烟草专卖局组织起草的《加热卷烟》强制性国家标准和《加热卷烟常规分析用吸烟机定义和标准条件》等3项配套方法国家标准征求意见稿发布，征求意见周期为即日起至9月26日。</t>
+          <t>美股量子计算概念股IonQ盘后涨超5%，公司展示业界首个端到端实时量子纠错解码器。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sz002303</t>
+          <t>sz002935</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>美盈森</t>
+          <t>天奥电子</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>6.9</v>
+        <v>17.52</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10.0478</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>9.981199999999999</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>电子烟包装|公司全资子公司东莞美盈森顺利通过电子香烟制造商吉瑞科技验厂、打样测试、综合评估的审核程序，取得其包装供应资质，为其电子烟产品提供一体化包装服务。</t>
+          <t>量子|量子科技方面公司涉及的主要是量子精密测量领域。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>电子烟包装</t>
+          <t>量子</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>电子烟</t>
+          <t>玻璃基板</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1.2542</v>
+        <v>1.895</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>7月28日，由国家烟草专卖局组织起草的《加热卷烟》强制性国家标准和《加热卷烟常规分析用吸烟机定义和标准条件》等3项配套方法国家标准征求意见稿发布，征求意见周期为即日起至9月26日。</t>
+          <t>京东方董事长陈炎顺在2026年京东方全球创新伙伴大会上宣布，未来五年公司研发投入将超800亿元，采购支出超8000亿元，明确未来一年内将敲定玻璃基钙钛矿器件与玻璃基封装载板两条量产线的投资计划。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh603020</t>
+          <t>sh603773</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>爱普股份</t>
+          <t>沃格光电</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>13.83</v>
+        <v>102.5</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10.0239</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0021</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>烟草香精|公司设有烟草香精事业部，向多家国内知名烟草企业提供烟用香精产品。</t>
+          <t>玻璃基板|公司具备的玻璃基微米级巨量互通技术（TGV技术），可应用于 2.5D/3D封装的垂直封装载板，终端应用场景包括大型AI算力服务器（CPU/GPU）、数据中心、自动驾驶、光通信、CPO光模块、射频（含手机）、5G/6G通信基站、MEMS（微型传感器）等高性能计算或高性能信号传输应用场景。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>烟草香精</t>
+          <t>玻璃基板</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>1.0256</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>日前算力租赁厂商Nebius宣布GPU云服务价格上调17%至21%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sh603636</t>
+          <t>sz001234</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>南威软件</t>
+          <t>泰慕士</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>8.01</v>
+        <v>32.18</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10.0275</v>
+        <v>10.0171</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>算力租赁+AI智能体|1.公司于2024年4月获得北京市发展和改革委员会批准，建设2300PFlops算力的“北京七星园数字经济产业智算中心”，用于服务企业人工智能发展、政府公共算力及企业算力需求。
-2.公司已发布AI智能体服务平台“白泽启元”、政务公文写作与协同平台“白泽文墨”、智能体客服平台“白泽对话管理”以及智能体BI产品“白泽云图”等白泽系列四款大模型智能体产品。</t>
+          <t>纺织|公司主营业务为针织面料和针织服装的研发、生产和销售，主要为迪卡侬、森马服饰、蕉内、Quiksilver、佐丹奴、全棉时代、曼妮芬、安踏、波司登等知名服装品牌提供贴牌加工服务。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>算力租赁, AI智能体</t>
+          <t>纺织</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>1.0256</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>日前算力租赁厂商Nebius宣布GPU云服务价格上调17%至21%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz002467</t>
+          <t>sh600418</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>二六三</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>5.09</v>
+        <v>23.45</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>9.9352</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+        <v>9.990599999999999</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>AI智能体+算力调度|1.公司在WebRTC、QoS、实时音视频等核心技术基础上，深度融合AI与大模型能力，打造智能通信中枢。通过自研AICC人工智能客户联络中心，实现企业邮箱、视频直播等场景的端到端智能化交互。同时，研发投入持续向AI驱动的云通信解决方案倾斜，构建跨网络动态负载均衡与智能运维体系，支撑亿级并发场景下的服务稳定性。
-2.公司的二六三海外算力调度平台是一个覆盖日本、新加坡、西欧、美国的算力智能调度网络平台，通过对数据的使用时间、属性、用量、时效、各地计算成本，通过AI和SDN的结合实现智能调度，使得计算的效率和成本最优。</t>
+          <t>汽车|公司是一家集全系列商用车、乘用车及动力总成等研产销和服务于一体,“先进节能汽车、新能源汽车、智能网联汽车”并举的综合型汽车企业集团。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>AI智能体, 算力调度</t>
+          <t>汽车</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>养老</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>0.8075000000000001</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>9月18日国常会指出，要全面客观认识人口老龄化带来的影响，深入实施积极应对人口老龄化国家战略，推动老龄事业全面发展进步。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz002614</t>
+          <t>sz000850</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>华茂股份</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>6.88</v>
+        <v>4.65</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.9291</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>养老+“华”字辈|国内按摩器具行业产业链最完整并在全球具有影响力的龙头民企。MEDISANA是奥佳华集团旗下五大自主品牌之一。产品系列主要有保健按摩、家用医疗（血压计、血糖仪、血氧计等）及移动保健产品。</t>
+          <t>棉花|公司专注于棉、毛、麻、丝和人造纤维的纯、混纺纱线及其织物、针织品、服装、印染加工；纺织设备及配件、家用纺织品销售；投资管理。公司产品包括纱线系列产品，坯布面料系列产品、色织面料系列产品和功能性产业用布等。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>养老, “华”字辈</t>
+          <t>棉花</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>养老</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>0.8075000000000001</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>9月18日国常会指出，要全面客观认识人口老龄化带来的影响，深入实施积极应对人口老龄化国家战略，推动老龄事业全面发展进步。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz002178</t>
+          <t>sh600653</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>延华智能</t>
+          <t>申华控股</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>5.59</v>
+        <v>1.87</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10.0394</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>养老+AI医疗|1.公司智慧医疗与大健康业务为诊所、门诊部、药店、养老机构等提供标准化解决方案，为居民提供健康管理的服务平台，打造多学科中心垂直叠加医疗及康养综合体，为医患提供便捷的诊疗与康复环境。
-2.在智慧医疗领域，公司研究开发了HIS系统、智能化电子病历系统、基于微服务的医院信息化集成平台，基于AI的临床辅助诊断系统、全流程医疗质量管理系统、智能决策分析系统、智能导诊系统、城市智慧救护车云服务平台、医疗质量信息管理平台、医院总值班信息系统平台、医护一体化平台等。</t>
+          <t>汽车销售|公司汽车消费服务类业务可细分为三个部分，汽车销售服务业务、汽车文化产业园、汽车租赁业务等。公司主营华晨旗下的中华、金杯、华颂等汽车品牌销售，且通过2017年对申华晨宝的收购，实现了宝马等中高端汽车品牌补充，公司现有渭南汽博园和开封汽博园两个汽车文化产业项目。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>养老, AI医疗</t>
+          <t>汽车销售</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>0.1871</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高；截至9月19日，9月上海二手房累计成交15597套，同比上涨28%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh600743</t>
+          <t>sh600230</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>华远控股</t>
+          <t>沧州大化</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>2.56</v>
+        <v>14.82</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>9.8712</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0223</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>房地产+“华”字辈|2025年4月，公司完成了重大资产重组，已将持有的房地产开发业务相关资产及负债转让至公司控股股东华远集团，实现了从重资产开发商向轻资产服务商的价值重构。</t>
+          <t>化工|公司是我国首家规模生产TDI的公司，拥有年产15万吨TDI、10万吨PC、及配套的16万吨烧碱、造气原料气、20万吨双酚A等相关产品链相衔接、上下游原料相配套的生产规模。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>房地产, “华”字辈</t>
+          <t>化工</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>0.1871</v>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高；截至9月19日，9月上海二手房累计成交15597套，同比上涨28%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sz000560</t>
+          <t>sh603937</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>丽岛新材</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>3.51</v>
+        <v>12.97</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>10.0313</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0085</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>房地产|地产平台运营商，基于二十余年的锐意进取，以专业、安全、高效的运营管理体系为支撑，为客户提供高品质、一站式的居住全生命周期综合服务。</t>
+          <t>锂电池|子公司安徽丽岛的主要产品为铝板带箔材料，产品可广泛应用于建筑材料、食品包装、电子电器、新能源电池、储能等市场领域。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>锂电池</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>0.1187</v>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>从消息人士处获悉，小鹏机器人已完成供应链审厂及核心零部件定点，量产进程进一步推进。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sh600503</t>
+          <t>sz002633</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>华丽家族</t>
+          <t>申科股份</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2.67</v>
+        <v>15.87</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>9.8765</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.979200000000001</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>机器人+“华”字辈|持有南江机器人50.82%的股权，是全产业链机器人公司；主要产品为面向智能制造和智能物流的智能移动机器人IAGV和智能搬运几期二年ICARRIER系列机器人。</t>
+          <t>轴承|公司主导产品为厚壁滑动轴承，主要配套于汽轮机、燃气轮机、水轮机、发动机、电动机、鼓风机、水泵、压缩机、风机等各类旋转机械。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>机器人, “华”字辈</t>
+          <t>轴承</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>0.1187</v>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>从消息人士处获悉，小鹏机器人已完成供应链审厂及核心零部件定点，量产进程进一步推进。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sz002768</t>
+          <t>sh600843</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>国恩股份</t>
+          <t>上工申贝</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>74.86</v>
+        <v>7.61</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10.0073</v>
+        <v>9.9711</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>PEEK材料|公司已完成PEEK材料生产技术与核心工艺的开发，计划通过浙江国恩化学建设2条PEEK聚合生产线，实现1,000 吨/年的PEEK材料生产能力，拓展公司高性能工程塑料产品在航空航天、医疗、新能源汽车、人形机器人等领域的应用。</t>
+          <t>低空|1.2024年3月4日互动，碳纤维轻型运动飞机项目是公司参股的上海飞人科技涉及投资的项目之一。该项目消化吸收国外的飞机制造技术、进行民航的TC/VTC认证、零部件国产化的供应商认证。
+2.公司已经成长为一家占据全球缝制技术制高点并为客户量身定制工业4.0应用解决方案的专业设备供应商，主要产品有机器人焊接、组装生产线，程控机械加工流水线等。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>PEEK材料</t>
+          <t>低空</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>-0.2901</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sz002082</t>
+          <t>sh603067</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>ST万邦</t>
+          <t>振华股份</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>11.12</v>
+        <v>39.86</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>9.9901</v>
+        <v>9.989000000000001</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST股 | 在研发端，公司探索人工智能在创新药设计、筛选、实验设计等环节的应用，目前全球首个治疗胃轻瘫的中药1.1类新药“理中消痞颗粒”正在开展临床研究。 </t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
+          <t>燃气轮机|公司金属铬产品在高温合金、铜基、铝基特种合金、高端焊接材料、溅射靶材等领域广泛应用，高温合金是燃气轮机的主要材料，单质铬的添加量在15%~20%之间。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>燃气轮机</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2855,37 +2811,33 @@
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz001216</t>
+          <t>sz002638</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>勤上股份</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>26.47</v>
+        <v>4.74</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>10.0166</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>6天6板</t>
-        </is>
-      </c>
+        <v>9.976799999999999</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>MLCC+“华”字辈|子公司氧化锆粉体纯度最高可达99.995%，产品可适配新能源研磨、齿科陶瓷、MLCC等不同领域使用需求。</t>
+          <t>LED|公司半导体照明主要产品包括LED户外照明、LED景观照明、LED室内照明和LED显示屏等。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>MLCC, “华”字辈</t>
+          <t>LED</t>
         </is>
       </c>
     </row>
@@ -2902,609 +2854,33 @@
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sz001317</t>
+          <t>sz300931</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>三羊马</t>
+          <t>通用电梯</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>65.95999999999999</v>
+        <v>19.21</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>10.0067</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>19.9875</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>物流+“羊”|公司是一家主要通过公铁联运方式为汽车行业和啤酒、饮料、洗涤用品等非汽车行业提供综合服务的第三方物流企业，建成以重庆为龙头，以柳州、西安、兰州、乌鲁木齐等为支点，串联“一带一路”沿线节点城市，横贯中西部地区，联系亚欧大陆的流通大通道。</t>
+          <t>电梯|公司主要从事电梯、自动扶梯、自动人行道的产品研发、设计、制造、销售、安装、改造及维保业务，是一家为各类建筑的电梯提供系统性的解决方案及全面的更新改造方案的科技创新型企业，产品线覆盖乘客电梯、观光电梯、医用电梯、家用电梯、载货电梯、汽车电梯、既有建筑加装电梯、自动扶梯、自动人行道等各系列电梯。公司承接了一系列政府机构、企事业单位、机场高铁站、大型地产项目及地标性建筑的电梯项目，代表性项目包括刚果(布)奥隆博国际机场、乌鲁木齐高铁站北广场项目、长沙通程逸城大酒店、新疆克拉玛依市行政综合楼、重庆北温泉9号、银川滨河新区景城安置区等。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>物流, “羊”</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr"/>
-      <c r="D53" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>sz001234</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>泰慕士</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>10.0038</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>纺织服装|公司主营业务为针织面料与针织服装的研发、生产和销售，主要产品可以分为运动服装、休闲服装及儿童服装。公司已与森马服饰旗下童装品牌巴拉巴拉建立了战略合作关系并为其提供贴牌加工服务。</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>纺织服装</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>sh603580</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>艾艾精工</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>78.68000000000001</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>9.995800000000001</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>股权转让|艾艾精工公告称，公司控股股东及实际控制人涂木林、蔡瑞美筹划的控制权变更事项取得进展。蔡瑞美与上海誉升同风金属材料科技有限公司签署股份转让协议，拟以27.62元/股转让3918.89万股(占总股本29.99%)，总价款10.82亿元。同时，以本次股份转让为前提，上海誉升拟以部分要约收购方式增持1308.04万股(占总股本10.01%)，要约价27.62元/股。</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>股权转让</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>sz002259</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>升达林业</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>9.9558</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>天然气|公司自2013年切入清洁能源行业以来，通过并购、自建等方式快速布局清洁能源业务板块，现已拥有多家涉及LNG业务的子公司，其主要经营业务为液化天然气的生产和销售、城镇燃气、加气站等，现已初步形成“液化天然气生产与销售-天然气管道-液化天然气运输-城镇燃气（管道输配）-加气站与调峰站”的产业链格局。公司目前的业绩主要来源于液化天然气销售业务。</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>天然气</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>sz002564</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>天沃科技</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>10.101</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>上海微电子概念|公司与上海微电子均为上海国资委下属公司。上海电气控股在2022年承诺推动旗下资产整合，明确表示将利用天沃科技作为资本运作平台，注入集团资产以解决同业竞争问题。公司作为上海电气系最小市值的上市公司，被市场视为潜在标的。</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>上海微电子概念</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>sz001322</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>箭牌家居</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>9.968399999999999</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>家居|公司是一家集研发、生产、销售与服务于一体的大型现代化制造企业，生产产品品类范围覆盖卫生陶瓷、龙头五金、浴室家具、瓷砖、浴缸浴房、定制橱衣柜等全系列家居产品。</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>家居</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>sh605179</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>一鸣食品</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>9.9963</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>乳业|公司主要从事新鲜乳品与烘焙食品的研发、生产、销售及连锁经营业务。</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>乳业</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr"/>
-      <c r="D59" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>sh600815</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>厦工股份</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>9.973799999999999</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>福建+工程机械|公司核心竞争力包含装载机、挖掘机、道路机械、叉车等工程机械整机产品与核心零部件的研发、制造和营销服务能力。</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>福建, 工程机械</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>sh600403</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>大有能源</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>9.9855</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>煤炭|公司的主要产品为长焰煤、焦煤、贫煤、洗精煤、气煤。截止2024年末，公司煤炭资源量11.23亿吨，可采储量6.02亿吨，证实储量2.6亿吨。</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>sz002672</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>东江环保</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>10.1093</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>环保|子公司雄风环保已形成对含有有色金属的废料、废渣等废弃资源及其他物料回收再利用的成熟生产工艺，其可综合利用的有色金属物料包括锌冶炼、铅冶炼、铜冶炼、钢铁冶炼企业及其它有色金属回收行业二次资源。</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>环保</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>sz001260</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>坤泰股份</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>9.978299999999999</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>汽车零部件|公司的内饰产品主要包括三大类，汽车簇绒地毯、汽车针刺地毯、汽车脚垫，公司和众多新能源车企有业务往来。</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>汽车零部件</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr"/>
-      <c r="D63" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>sz001266</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>宏英智能</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>37.75</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>9.994200000000001</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>商业航天+液冷|1.公司智能电控产品已经批量应用于航天配套的相关领域。
-2.公司的液冷储能相关产品已实现批量应用，在数据中心应用场景下采用全浸没式液冷储能技术。</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>商业航天, 液冷</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>sz000595</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>新能股份</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>9.962400000000001</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>绿电|旗下宁夏电投新能源主营光伏发电、风力发电及储能电站项目的投资开发和运营管理，2025年公司存量项目总装机规模67.85万千瓦。</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>绿电</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr"/>
-      <c r="D65" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>sh600418</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>江淮汽车</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>21.32</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>10.0103</v>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>汽车整车|公司是一家集全系列商用车、乘用车及动力总成等研产销和服务于一体,“先进节能汽车、新能源汽车、智能网联汽车”并举的综合型汽车企业集团。</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>汽车整车</t>
+          <t>电梯</t>
         </is>
       </c>
     </row>
@@ -3519,7 +2895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3546,46 +2922,46 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sz001216</t>
+          <t>sz000910</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>华瓷股份</t>
+          <t>大亚圣象</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh603230</t>
+          <t>sh601811</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz000504</t>
+          <t>sh600825</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>南华生物</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
@@ -3595,12 +2971,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz000910</t>
+          <t>sz001234</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>大亚圣象</t>
+          <t>泰慕士</t>
         </is>
       </c>
     </row>
@@ -3610,12 +2986,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz001317</t>
+          <t>sh600743</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>三羊马</t>
+          <t>华远控股</t>
         </is>
       </c>
     </row>
@@ -3625,12 +3001,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh603068</t>
+          <t>sh600503</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>博通集成</t>
+          <t>华丽家族</t>
         </is>
       </c>
     </row>
@@ -3640,42 +3016,42 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sz000560</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>我爱我家</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sz002614</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>奥佳华</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sz002178</t>
+          <t>sh603636</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>延华智能</t>
+          <t>南威软件</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3061,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sz001234</t>
+          <t>sh605058</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>泰慕士</t>
+          <t>澳弘电子</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3076,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>sh600664</t>
+          <t>sh600418</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>江淮汽车</t>
         </is>
       </c>
     </row>
@@ -3715,192 +3091,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>sh600743</t>
+          <t>sz002238</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>华远控股</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>sz000756</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>新华制药</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>sh603020</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>爱普股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>sh600721</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>百花医药</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>sh600503</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>华丽家族</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>sz000560</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>我爱我家</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>sh603580</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>艾艾精工</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>sz002259</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>升达林业</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>sz002614</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>奥佳华</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>sz002303</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>美盈森</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>sz300110</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>华仁药业</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>sh603636</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>南威软件</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>sz000607</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>华媒控股</t>
+          <t>天威视讯</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,20 +476,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="131" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="99" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="422" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="255" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,1016 +552,1015 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.8411</v>
+        <v>0.6992</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>9月22日，江西省宏瑞兴科技股份有限公司发布调价通知，将覆铜板产品出厂价格上调10%，这是继中国巨石9月对电子布厚布、薄布分别提价15%和20%之后的又一轮材料涨价。</t>
+          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh605058</t>
+          <t>sh600802</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>福建水泥</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>58.6</v>
+        <v>6.62</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.0056</v>
+        <v>9.966800000000001</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>9天7板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
+          <t>福建+水泥|公司主要从事水泥及熟料的生产及销售，拥有7条新型干法熟料水泥生产线，具备年产熟料784.3万吨、水泥1164万吨。公司是福建地区产能规模最大的水泥制造企业，也是福建省水泥行业唯一的一家上市公司。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>福建, 水泥</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.8411</v>
+        <v>0.6992</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>9月22日，江西省宏瑞兴科技股份有限公司发布调价通知，将覆铜板产品出厂价格上调10%，这是继中国巨石9月对电子布厚布、薄布分别提价15%和20%之后的又一轮材料涨价。</t>
+          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz000910</t>
+          <t>sh600815</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>大亚圣象</t>
+          <t>厦工股份</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>7.58</v>
+        <v>4.65</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.0145</v>
+        <v>9.9291</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司研发生产的超薄PCB纤维板主要用途电子线路垫板。</t>
+          <t>福建+工程机械|公司核心竞争力包含装载机、挖掘机、道路机械、叉车等工程机械整机产品与核心零部件的研发、制造和营销服务能力。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>福建, 工程机械</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.8411</v>
+        <v>0.6992</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9月22日，江西省宏瑞兴科技股份有限公司发布调价通知，将覆铜板产品出厂价格上调10%，这是继中国巨石9月对电子布厚布、薄布分别提价15%和20%之后的又一轮材料涨价。</t>
+          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh603328</t>
+          <t>sz000592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>依顿电子</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15.2</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.9855</v>
+        <v>10.0251</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司专注于高精度、高密度双层及多层印制电路板的研发、生产和销售业务，作为首批进入国际大厂汽车PCB核心供应链的PCB厂商，公司PCB产品供货覆盖传统汽车零部件。
-2026年8月6日公告，公司拟使用自有资金及自筹资金投资建设高端印制电路板智能制造项目，计划总投资29.79亿元。投资项目主要围绕市场高端印制电路板需求，建设高端高速高多层PCB智能制造项目。</t>
+          <t>福建+林业|公司在林木业务方面已基本形成“林板一体化”的发展产业链，拥有经营林区近90万亩，在福建省处于行业领先龙头地位。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>福建, 林业</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.8411</v>
+        <v>0.6992</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9月22日，江西省宏瑞兴科技股份有限公司发布调价通知，将覆铜板产品出厂价格上调10%，这是继中国巨石9月对电子布厚布、薄布分别提价15%和20%之后的又一轮材料涨价。</t>
+          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz301150</t>
+          <t>sz300300</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>中一科技</t>
+          <t>海峡创新</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>49.2</v>
+        <v>10.81</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>20</v>
+        <v>19.9778</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>PCB铜箔|在电子电路铜箔方面，公司产品规格覆盖8μm到210μm，并逐步向高端电子电路铜箔领域延伸，已经实现HDI用铜箔、RTF等产品批量销售，HVLP产品通过多家客户验证。</t>
+          <t>福建+创投|1.公司是平潭综合实验区金融控股集团旗下上市公司
+2.上市公司投资参控股的企业有50余家，符合“独角兽”、“新经济”类型的为数众多，比如极光推送、京东金融等</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>PCB铜箔</t>
+          <t>福建, 创投</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.8411</v>
+        <v>0.6992</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9月22日，江西省宏瑞兴科技股份有限公司发布调价通知，将覆铜板产品出厂价格上调10%，这是继中国巨石9月对电子布厚布、薄布分别提价15%和20%之后的又一轮材料涨价。</t>
+          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz002909</t>
+          <t>sz000905</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>集泰股份</t>
+          <t>厦门港务</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>7.54</v>
+        <v>9.81</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.073</v>
+        <v>9.977600000000001</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司PCB三防漆涵盖有机硅、UV等多个系列，主要用于PCB电路板及电子元器件表面防护，可应用于智能设备、汽车电子、消费电子、工业控制、通信设备等场景。</t>
+          <t>福建+港口|公司作为厦门港区规模最大综合物流服务商，拥有散杂货码头及后方堆场等稀缺资源、完善的港口配套与增值服务、较为完整的物流业务链条，形成了内外贸航线、海陆空物流体系。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>福建, 港口</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1.8411</v>
+        <v>0.6992</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9月22日，江西省宏瑞兴科技股份有限公司发布调价通知，将覆铜板产品出厂价格上调10%，这是继中国巨石9月对电子布厚布、薄布分别提价15%和20%之后的又一轮材料涨价。</t>
+          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh603124</t>
+          <t>sz000753</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>江南新材</t>
+          <t>漳州发展</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>145</v>
+        <v>5.35</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9.9985</v>
+        <v>10.0823</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>PCB材料|公司核心产品包括铜球系列、氧化铜粉系列及高精密铜基散热片系列三大产品类别，应用于PCB镀铜制程，下游客户覆盖大多数境内外一线PCB制造企业，包括鹏鼎控股、东山精密、健鼎科技、深南电路、瀚宇博德、景旺电子、志超科技、奥士康、胜宏科技、崇达技术、定颖电子、博敏电子等。</t>
+          <t>福建+汽车后市场|福建本地上市公司，主营汽贸业务，目前已成立漳发汽车集团，实现集团化经营管理，旗下已有的品牌授权包含长安福特，北汽新能源，奇瑞新能源等。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>PCB材料</t>
+          <t>福建, 汽车后市场</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.782</v>
+        <v>0.6992</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Muse爆火，提振市场对CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%。</t>
+          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh603396</t>
+          <t>sz002679</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>金辰股份</t>
+          <t>福建金森</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>32.4</v>
+        <v>11.58</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.017</v>
+        <v>9.971499999999999</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>半导体设备|2026年8月25日公告，公司拟与江苏南通苏锡通科技产业园区管理委员会签订投资协议，投资设立“半导体装备研发及制造项目”，项目投资总额约10亿元。公司拟设立全资子公司辰光微电半导体设备(南通)有限公司作为项目公司，注册资本1000万元，持股比例100%。项目将建设现代化厂房和高标准洁净室，搭建以TGV玻璃基封装为代表的半导体设备生产试验线，推动超快激光诱导改质设备等半导体专用设备的研发与制造验证。</t>
+          <t>福建+林业|公司主营业务为森林培育营造，森林保有管护，木材生产销售，林业服务。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>半导体设备</t>
+          <t>福建, 林业</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.782</v>
+        <v>0.6992</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Muse爆火，提振市场对CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%。</t>
+          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz002119</t>
+          <t>920748.BJ</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>康强电子</t>
+          <t>路桥信息</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>26.92</v>
+        <v>36.5</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.0123</v>
+        <v>29.9858</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>封装材料|公司是一家专业从事各类半导体封装材料引线框架、键合丝等半导体封装材料的开发、生产、销售的高新技术企业，主要产品引线框架和键合丝国内市场规模处于领先地位，产品覆盖国内知名的半导体后封装企业。</t>
+          <t>福建+车联网|公司是厦门国有资本运营有限责任公司旗下上市公司。公司的车路协同路侧融合感知系统通过目标识别完成对路段、转角盲区范围内的机动车、非机动车、行人的识别检测以及定位，实现交叉口碰撞预警、弱势交通参与者碰撞预警、交叉口车速引导、前方拥堵提醒、紧急车辆提醒、道路危险状况提示、限速预警、信息服务等功能。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>封装材料</t>
+          <t>福建, 车联网</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.782</v>
+        <v>0.6992</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Muse爆火，提振市场对CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%。</t>
+          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz002989</t>
+          <t>sz002264</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>中天精装</t>
+          <t>新 华 都</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>27.96</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>9.992099999999999</v>
+        <v>10.0135</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>载板|公司间接参股科睿斯半导体主营业务为FCBGA（ABF)高端载板的生产和销售，产品主要应用于CPU、GPU、AI及车载等高算力芯片的封装。</t>
+          <t>福建+零售+AI|1.公司主要业务为互联网营销和超市百货业务，旗下久爱致和服务于多家国际、国内知名企业，也是天猫及京东等多家电子商务平台的合作伙伴。
+2.公司结合AI大模型与电商场景，已开发并上线试运行智能化平台“久爱AI”，一期版本开放商品评论分析、商品信息采集、违禁词风险评估、摘要抽取、文案大纲助手、简历筛选6项AI工具，为优化营销策略、产品结构和日常办公提供技术支持。
+3.阿里巴巴成都及杭州瀚云均为公司股东。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>载板</t>
+          <t>福建, 零售, AI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.782</v>
+        <v>-1.06</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Muse爆火，提振市场对CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%。</t>
+          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh603991</t>
+          <t>sz002614</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>领先股份</t>
+          <t>奥佳华</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>185.57</v>
+        <v>8.33</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
+        <v>10.0396</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">半导体设备|子公司苏州桔云主要从事半导体专用设备的研发、生产和销售，主要产品包括清洗设备、腐蚀设备、涂胶显影设备、去胶设备、烘箱设备、分片设备等，产品线较为丰富。苏州桔云专注于后道先进封装领域设备的研发，并逐步向前道拓展，围绕清洗设备、烘箱设备等持续深耕细作，形成自身独特的产品及技术优势，并凭借其较高的性价比优势和定制化、快速响应的客户服务优势不断扩大市场份额。
-</t>
+          <t>机器人+“华”字辈|公司AI按摩机器人2.0（OG-8598Plus），已实现服务功能与产品有机结合，运用人脸识别、疲感侦测、“千人千方”智能AI算法、云端个人健康数据库、新一代4D无刷变频温感机芯等新技术构建围绕用户健康的检测-分析-调理闭环服务系统，关注每一位用户的健康状态，为用户远程推送“量身定制”的专属按摩解决方案，构建家庭健康管理服务生态。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>半导体设备</t>
+          <t>机器人, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.782</v>
+        <v>-1.06</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Muse爆火，提振市场对CPU需求增长的预期，ARM、英特尔等多只半导体芯片股大涨超10%。</t>
+          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh688512</t>
+          <t>sh603949</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>慧智微-U</t>
+          <t>雪龙集团</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>17.32</v>
+        <v>16.9</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>20.0277</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+        <v>10.026</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">射频前端芯片|公司是一家为智能手机、物联网等领域提供射频前端的芯片设计公司，主营业务为射频前端芯片及模组的研发、设计和销售。公司具备全套射频前端芯片设计能力和集成化模组研发能力，技术体系以功率放大器（PA）的设计能力为核心，兼具低噪声放大器（LNA）、射频开关（Switch）、集成无源器件滤波器（IPD Filter）等射频器件的设计能力，产品系列覆盖的通信频段需求包括2G、3G、4G、3GHz以下的5G重耕频段、3GHz~6GHz 的5G新频段等，可为客户提供无线通信射频前端发射模组、接收模组等。2021年公司在智能手机领域5G L-PAMiF出货量为1132.33万颗，同口径下市占率估算约为1.96%，在国产厂商中排名第二。公司的射频前端模组已经在三星全球畅销系列A22 5G手机和OPPO、vivo、荣耀等智能手机机型中实现大规模量产，并进入闻泰科技、华勤通讯和龙旗科技等一线移动终端设备ODM厂商，拥有较为优质的客户结构。
-</t>
+          <t>机器人|公司作为有限合伙人通过深创投中小企业发展基金（新疆）有限合伙企业间接持股杭州宇树科技有限公司。目前，深创投中小企业发展基金（新疆）有限合伙企业对杭州宇树科技有限公司的持股比例为1.3546%；公司对深创投中小企业发展基金（新疆）有限合伙企业的持股比例为0.7239%。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>射频前端芯片</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.8371999999999999</v>
+        <v>-1.06</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>日前算力租赁厂商Nebius宣布GPU云服务价格上调17%至21%。渤海证券研报称，当前围绕Token的调用、分发与结算，一套新的价值体系正在加速形成，并成为人工智能产业可能变现的重要路径，持续看好AI时代“词元经济”发展浪潮下算力租赁等AI云计算服务环节。</t>
+          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603636</t>
+          <t>sh603500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>南威软件</t>
+          <t>祥和实业</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>8.81</v>
+        <v>10.42</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9.987500000000001</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.0317</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>算力|1.公司于2024年4月获得北京市发展和改革委员会批准，建设2300PFlops算力的“北京七星园数字经济产业智算中心”，用于服务企业人工智能发展、政府公共算力及企业算力需求。
-2.公司已发布AI智能体服务平台“白泽启元”、政务公文写作与协同平台“白泽文墨”、智能体客服平台“白泽对话管理”以及智能体BI产品“白泽云图”等白泽系列四款大模型智能体产品。</t>
+          <t>超级电容+机器人|1.公司紧跟铝电解电容器技术迭代，先后开发成功V-CHIP电容底座、车用耐振动底座以及应用于超级电容、锂电池、耐550V以上特高压、耐150℃电容器用橡胶密封塞、轴向电容器盖板等产品。
+2.公司于2024年4月30日成立子公司祥和智能，研发、制造和销售工业机器人、智能机器人及人工智能应用软件开发等系祥和智能的经营范围。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>算力</t>
+          <t>超级电容, 机器人</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.8371999999999999</v>
+        <v>-1.06</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>日前算力租赁厂商Nebius宣布GPU云服务价格上调17%至21%。渤海证券研报称，当前围绕Token的调用、分发与结算，一套新的价值体系正在加速形成，并成为人工智能产业可能变现的重要路径，持续看好AI时代“词元经济”发展浪潮下算力租赁等AI云计算服务环节。</t>
+          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz002238</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>天威视讯</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>7.66</v>
+        <v>9.68</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.0575</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">算力工程|公司初步形成位于深圳市福田区、南山区、龙华区以及深汕合作区的3000个5-8KW 机柜规模的数据中心布局，正在加紧推进系统调试、检测、认证、以及销售运维团队招选等正式投产前相关运营准备工作，未来将结合自身经营状况和行业发展状况来评估包括算力服务在内的增值业务的必要性、可行性和经济效益，再研究是否推出相应的数据中心增值服务业务。
-</t>
+          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-0.8371999999999999</v>
+        <v>-1.06</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>日前算力租赁厂商Nebius宣布GPU云服务价格上调17%至21%。渤海证券研报称，当前围绕Token的调用、分发与结算，一套新的价值体系正在加速形成，并成为人工智能产业可能变现的重要路径，持续看好AI时代“词元经济”发展浪潮下算力租赁等AI云计算服务环节。</t>
+          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz002849</t>
+          <t>sh605018</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>威星智能</t>
+          <t>长华集团</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>23</v>
+        <v>12.74</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9.995200000000001</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.0173</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>算力|2023年7月24日公告，近日，公司与贵安管委会、摩尔线程签署《贵安智算中心项目投资合作协议》，三方拟在贵安新区建立智算中心，在3D图形渲染和视觉设计、高性能科学计算、HDV高速视频解编码、AI训练和推理等应用领域构建深度合作关系。</t>
+          <t>机器人|公司完成行星滚柱丝杠产线设计，一期规划年产20万套。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>算力</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.8371999999999999</v>
+        <v>-1.06</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>日前算力租赁厂商Nebius宣布GPU云服务价格上调17%至21%。渤海证券研报称，当前围绕Token的调用、分发与结算，一套新的价值体系正在加速形成，并成为人工智能产业可能变现的重要路径，持续看好AI时代“词元经济”发展浪潮下算力租赁等AI云计算服务环节。</t>
+          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh603803</t>
+          <t>sz301699</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>瑞斯康达</t>
+          <t>洛轴股份</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>12.87</v>
+        <v>35.54</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10</v>
+        <v>19.9865</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>算力交换机|1.在高端光模块领域，公司联营企业易锐光电是中国少数产业链上下游关键层面具备完整核心技术和解决方案的高科技企业，新一代基于自主知识产权的25G/100G/超100G集成光收发芯片的光通信模块及光组件，用于电信网络城域网和大型数据中心网络。
-2.2022年，公司自主研发的100%国产化工业以太网交换机在电力DCS系统实现应用。</t>
+          <t>机器人+商业航天|1.公司针对国产机器人产业发展需求，开展机器人专用精密轴承设计和制造、测试、寿命试验等技术研究，研制出了薄壁等截面、交叉圆柱滚子两种系列轴承以及RV减速器、谐波减速器专用系列精密轴承。
+2.公司为航空航天等高端装备研制的多款关键轴承应用于“神舟系列”“嫦娥系列”、天宫空间站、天和核心舱、问天实验舱、梦天实验舱等重大航天工程，为国家航空航天发展作出贡献。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>算力交换机</t>
+          <t>机器人, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>科学仪器</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5.038200000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>华泰证券研报指出，随着数据中心网络向800G、1.6T演进，高速连接器、线缆及高端PCB对信号完整性与良率管控的要求持续提高，带动VNA测试需求增长；同时测试向更高频率、更多端口及自动化方向升级，有望推动VNA量价齐升。</t>
+          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh688628</t>
+          <t>sh603767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">优利德  </t>
+          <t>中马传动</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>114.44</v>
+        <v>14.74</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>19.9958</v>
+        <v>10</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>PCB检测|公司致力于测试测量仪器仪表的研发、生产和销售，涉及电子电工、测试仪器、温度及环境、电力及高压、测绘测量等产品线，是行业内产品系列较为丰富和齐全的企业。测试仪器产品包括实验系统综合测试平台、示波器、信号发生器、频谱分析仪、电源负载和电子元器件测试仪等产品。</t>
+          <t>机器人|公司招股说明书显示，将以现有汽车变速器齿轮、汽车转向器齿轮、汽车油泵轴齿轮、汽车发动机齿轮、摩托车发动机齿轮、农机变速器齿轮为发展基础，大力开拓汽车自动变速器行星齿轮、工业机器人减速器齿轮等高精度齿轮产品领域。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>PCB检测</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>科学仪器</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>5.038200000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>华泰证券研报指出，随着数据中心网络向800G、1.6T演进，高速连接器、线缆及高端PCB对信号完整性与良率管控的要求持续提高，带动VNA测试需求增长；同时测试向更高频率、更多端口及自动化方向升级，有望推动VNA量价齐升。</t>
+          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz002819</t>
+          <t>sz002164</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东方中科</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>24.24</v>
+        <v>13.06</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.981900000000001</v>
+        <v>10.0253</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">测试测量仪器|公司定位为电子测试测量领域领先的综合服务商，专注于为客户提供包括仪器销售、租赁、系统集成，主要产品包括示波器、数据记录仪、频谱分析仪、光谱仪、质谱仪、色谱仪等。
-</t>
+          <t>机器人+风电|1.公司的产品包括行星减速器等，杭州湾电机、减速器部分车间已投入生产。
+2.公司研发的风电齿轮箱应用于风电市场。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>测试测量仪器</t>
+          <t>机器人, 风电</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>科学仪器</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>5.038200000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>华泰证券研报指出，随着数据中心网络向800G、1.6T演进，高速连接器、线缆及高端PCB对信号完整性与良率管控的要求持续提高，带动VNA测试需求增长；同时测试向更高频率、更多端口及自动化方向升级，有望推动VNA量价齐升。</t>
+          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh688337</t>
+          <t>sz301311</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>普源精电</t>
+          <t>昆船智能</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>57.18</v>
+        <v>17.98</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>20</v>
+        <v>20.0267</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">科学仪器|2023年9月17日公告，公司首次正式公开发布13GHz带宽的DS80000系列数字示波器。该新产品通过自研核心技术平台，首次实现国产数字示波器产品带宽达到13GHz，具备国内行业技术领先优势和核心技术壁垒。
-</t>
+          <t>机器人+烟草|1.公司产品有机器人和AGV，广泛应用于制造行业的自动化生产线、自动装配流水线的物料上下线，流通企业的物料码垛搬运、集装箱搬运、自动拣选以及智慧停车等自动搬运场景。
+2.公司智能产线以烟草行业为起点，为客户提供烟草领域全产业链的系统解决方案，已涉及电子烟领域相关业务。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>科学仪器</t>
+          <t>机器人, 烟草</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>科学仪器</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>5.038200000000001</v>
+        <v>-0.7504000000000001</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>华泰证券研报指出，随着数据中心网络向800G、1.6T演进，高速连接器、线缆及高端PCB对信号完整性与良率管控的要求持续提高，带动VNA测试需求增长；同时测试向更高频率、更多端口及自动化方向升级，有望推动VNA量价齐升。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh688056</t>
+          <t>sh603230</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>莱伯泰科</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>52.92</v>
+        <v>18.47</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+        <v>10.006</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>7天6板</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>实验分析仪器|公司是一家专业从事实验分析仪器研发、生产和销售、提供洁净环保型实验室解决方案以及实验室耗材和相关服务的高新技术企业，致力于研发全自动实验检测平台，联接包括样品采集与处理、自动化进样、分析检测、智能数据分析在内的全检测流程，覆盖并联通实验分析的各个环节，为环境监测、食品检测、医疗制药、地质勘测等领域的用户提供自动化、系统化的实验分析检测整体解决方案。公司是全球范围内能将多种类和多功能的样品前处理技术与全自动分析实验分析检测平台组合成全自动实验分析仪器系统的主要实验分析仪器供应商之一。</t>
+          <t>传媒+“华”字辈|公司的最终控制人为内蒙古自治区人民政府。公司主营业务是出版物的批发、零售；文体用品零售；音像制品发行</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>实验分析仪器</t>
+          <t>传媒, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.05810000000000001</v>
+        <v>-0.7504000000000001</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>消息面上，网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高；截至9月19日，9月上海二手房累计成交15597套，同比上涨28%。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh600743</t>
+          <t>sh601811</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>华远控股</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2.82</v>
+        <v>20.35</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.1562</v>
+        <v>10</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>5天5板</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>房地产+并购重组|2025年4月，公司完成了重大资产重组，已将持有的房地产开发业务相关资产及负债转让至公司控股股东华远集团，实现了从重资产开发商向轻资产服务商的价值重构。</t>
+          <t>并购重组+传媒|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>房地产, 并购重组</t>
+          <t>并购重组, 传媒</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.05810000000000001</v>
+        <v>-0.7504000000000001</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>消息面上，网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高；截至9月19日，9月上海二手房累计成交15597套，同比上涨28%。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz000560</t>
+          <t>sh600825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>3.86</v>
+        <v>7.77</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.971499999999999</v>
+        <v>10.0567</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>4天4板</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>地产中介|地产平台运营商，基于二十余年的锐意进取，以专业、安全、高效的运营管理体系为支撑，为客户提供高品质、一站式的居住全生命周期综合服务。</t>
+          <t>并购重组+传媒|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>地产中介</t>
+          <t>并购重组, 传媒</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.05810000000000001</v>
+        <v>-0.7504000000000001</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>消息面上，网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高；截至9月19日，9月上海二手房累计成交15597套，同比上涨28%。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh600503</t>
+          <t>sz002238</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>华丽家族</t>
+          <t>天威视讯</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>2.94</v>
+        <v>8.43</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.1124</v>
+        <v>10.0522</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -1570,437 +1569,453 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>房地产开发|公司是一家以房地产开发为主营业务，以改善型产品为主的中小型房地产企业，房地产开发业务主要分布在上海、苏州和遵义三地，打造了上海檀宫、华丽家族浦东花园、华丽家族古北花园等精品楼盘。截至2024年12月31日，公司土地储备面积约6.5万平方米，包含苏州项目待开发土地面积约2.32万平方米、遵义项目待开发土地面积约4.18万平方米。</t>
+          <t>传媒+算力|1.公司是深圳地区最主要的电视服务提供商，主要向用户提供有线数字业务（包括基本收视、增值业务）、互联网宽带接入服务、视频购物服务和政企项目服务。
+2.公司初步形成位于深圳市福田区、南山区、龙华区以及深汕合作区的3000个5-8KW 机柜规模的数据中心布局。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>传媒, 算力</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.05810000000000001</v>
+        <v>-0.7504000000000001</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>消息面上，网上房地产数据显示，9月19日上海二手房（含商业）单日网签成交1495套，创2026年下半年以来单日网签新高；截至9月19日，9月上海二手房累计成交15597套，同比上涨28%。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh600605</t>
+          <t>sh600358</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>汇通能源</t>
+          <t>国旅联合</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>31.61</v>
+        <v>5.72</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.9861</v>
+        <v>10</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>房屋租赁|公司的主营业务为房屋租赁，物业服务及房地产开发与销售等。公司房产管理团队负责公司房产招商租赁及运营管理，同时对公司持有的空置房产，厂房等重新规划和定位，因地制宜地提出经营方案。公司房产租赁项目主要集中在上海中心城区，出租建筑面积过万平方米的行政区域有静安区，闵行，虹口，浦东新区及宝山区。此外，公司也积极在尝试通过承租获取房产使用权和收益权。公司房产管理团队同时对出租房产提供物业服务，同时负责运营郑州“百年德化·风情购物公园”项目。公司住宅地产开发业务实施聚焦和城市深耕战略，在江西市场，以南昌为根据地，快速建立住宅开发的操盘能力，通过项目的成功树立品牌。</t>
+          <t>传媒+旅游|1.公司的主要业务包括互联网营销、个性化旅行综合服务业务、旅游目的地建设和运营业务，子公司新线中视、国联文化是互联网营销业务的经营主体。
+2.公司旅游业务围绕“目的地项目、合作资源圈、运营服务商”三方面的拓展，与地方政府、景区、企业围绕乡村振兴、主题乐园、旅游目的地的策划、规划、建设、运营展开深度合作，为旅游项目提供整体解决方案。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>房屋租赁</t>
+          <t>传媒, 旅游</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>建材</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.1403</v>
+        <v>0.5704</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>住建部表示，“十五五”时期提升人民群众居住水平关键是建设好房子。将层高标准从原来的2.8米提高到3米；为解决老年群体上下楼的问题，新标准提出4楼及以上住宅都要加装电梯。</t>
+          <t>工业和信息化部、商务部、市场监管总局印发《轻工纺织产业发展“十五五”规划》。其中指出，发挥国家产融合作平台作用，引导金融机构为企业提供多元化融资服务，支持符合条件的重点行业企业上市融资。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sh600293</t>
+          <t>sz001234</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>泰慕士</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>3.7</v>
+        <v>35.4</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.119</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+        <v>10.0062</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>玻璃|中部最大、全国十强的玻璃生产企业，主营业务为平板玻璃及玻璃深加工和移动互联网终端产品销售及服务行业，已有浮法玻璃生产线五条，日熔化玻璃液3700吨，产能达到2460万重箱，有玻璃精深加工线五条，年玻璃精深加工500万平米。</t>
+          <t>纺织服装|公司主营业务为针织面料和针织服装的研发、生产和销售，主要为迪卡侬、森马服饰、蕉内、Quiksilver、佐丹奴、全棉时代、曼妮芬、安踏、波司登等知名服装品牌提供贴牌加工服务。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>纺织服装</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>建材</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.1403</v>
+        <v>0.5704</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>住建部表示，“十五五”时期提升人民群众居住水平关键是建设好房子。将层高标准从原来的2.8米提高到3米；为解决老年群体上下楼的问题，新标准提出4楼及以上住宅都要加装电梯。</t>
+          <t>工业和信息化部、商务部、市场监管总局印发《轻工纺织产业发展“十五五”规划》。其中指出，发挥国家产融合作平台作用，引导金融机构为企业提供多元化融资服务，支持符合条件的重点行业企业上市融资。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sh600802</t>
+          <t>sz000850</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>华茂股份</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>6.02</v>
+        <v>5.12</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10.0548</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+        <v>10.1075</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>水泥|公司主要从事水泥及熟料的生产及销售，拥有7条新型干法熟料水泥生产线，具备年产熟料784.3万吨、水泥1164万吨。公司是福建地区产能规模最大的水泥制造企业，也是福建省水泥行业唯一的一家上市公司。</t>
+          <t>纺织服装+“华”字辈|公司专注于棉、毛、麻、丝和人造纤维的纯、混纺纱线及其织物、针织品、服装、印染加工；纺织设备及配件、家用纺织品销售；投资管理。公司产品包括纱线系列产品，坯布面料系列产品、色织面料系列产品和功能性产业用布等。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>纺织服装, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>建材</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.1403</v>
+        <v>0.5704</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>住建部表示，“十五五”时期提升人民群众居住水平关键是建设好房子。将层高标准从原来的2.8米提高到3米；为解决老年群体上下楼的问题，新标准提出4楼及以上住宅都要加装电梯。</t>
+          <t>工业和信息化部、商务部、市场监管总局印发《轻工纺织产业发展“十五五”规划》。其中指出，发挥国家产融合作平台作用，引导金融机构为企业提供多元化融资服务，支持符合条件的重点行业企业上市融资。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sz002541</t>
+          <t>sh600843</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>鸿路钢构</t>
+          <t>上工申贝</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>19.69</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
+        <v>9.9869</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>建材|国内钢结构品种最齐全的制造企业，主营业务主要有钢结构制造销售、新型建材产品生产销售、钢结构工程专业承包、智能立体车库生产销售及钢结构装配式建筑总承包等五大类业务。</t>
+          <t>纺织机械|公司已经成长为一家占据全球缝制技术制高点并为客户量身定制工业4.0应用解决方案的专业设备供应商，主要产品有缝纫、绣花、裁切、焊接等缝制工艺设备，机器人焊接、组装生产线，程控机械加工流水线，以及智能仓储、自动传输装置等。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>建材</t>
+          <t>纺织机械</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>纺织服装</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-0.0221</v>
+        <v>0.5704</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>无人机视频显示，特斯拉Optimus在美国得州的专用生产线建设主结构可能接近完工，钢结构、混凝土浇筑等施工正同步推进。该生产线计划2027年计划投产，年产能目标在1000万台。</t>
+          <t>工业和信息化部、商务部、市场监管总局印发《轻工纺织产业发展“十五五”规划》。其中指出，发挥国家产融合作平台作用，引导金融机构为企业提供多元化融资服务，支持符合条件的重点行业企业上市融资。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz002614</t>
+          <t>sz002029</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>七 匹 狼</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>7.57</v>
+        <v>9.26</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10.0291</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>9.9762</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司AI按摩机器人2.0（OG-8598Plus），已实现服务功能与产品有机结合，运用人脸识别、疲感侦测、“千人千方”智能AI算法、云端个人健康数据库、新一代4D无刷变频温感机芯等新技术构建围绕用户健康的检测-分析-调理闭环服务系统，关注每一位用户的健康状态，为用户远程推送“量身定制”的专属按摩解决方案，构建家庭健康管理服务生态。</t>
+          <t>纺织+机器人|1.主要从事“七匹狼”品牌男装的设计、生产和销售,主要产品包括衬衫、西服、裤装、茄克衫、针织衫等。
+2.公司母公司间接持有摩尔线程和宇树科技的部分股权。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>纺织, 机器人</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-0.0221</v>
+        <v>-1.9551</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>无人机视频显示，特斯拉Optimus在美国得州的专用生产线建设主结构可能接近完工，钢结构、混凝土浇筑等施工正同步推进。该生产线计划2027年计划投产，年产能目标在1000万台。</t>
+          <t>Anthropic宣布成立生命科学研究团队及实验室，并公布Claude参与生物学研究取得的早期成果。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh603949</t>
+          <t>sz002622</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>皓宸医疗</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>15.36</v>
+        <v>2.72</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.0287</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
+        <v>10.1215</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司作为有限合伙人通过深创投中小企业发展基金（新疆）有限合伙企业间接持股杭州宇树科技有限公司。目前，深创投中小企业发展基金（新疆）有限合伙企业对杭州宇树科技有限公司的持股比例为1.3546%；公司对深创投中小企业发展基金（新疆）有限合伙企业的持股比例为0.7239%。</t>
+          <t>口腔医疗|公司购买德伦医疗51.00%股权。德伦医疗是一家以口腔医疗服务连锁经营为核心，专注于口腔疾病的诊断、治疗以及口腔保健、修复服务等口腔医疗服务的企业。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>口腔医疗</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-0.0221</v>
+        <v>-1.9551</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>无人机视频显示，特斯拉Optimus在美国得州的专用生产线建设主结构可能接近完工，钢结构、混凝土浇筑等施工正同步推进。该生产线计划2027年计划投产，年产能目标在1000万台。</t>
+          <t>Anthropic宣布成立生命科学研究团队及实验室，并公布Claude参与生物学研究取得的早期成果。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh603373</t>
+          <t>sz000710</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>安邦护卫</t>
+          <t>贝瑞基因</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>47.96</v>
+        <v>11.01</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>机器人|温州安邦护卫联合温州理工学院科研团队打造了“智能安防中枢平台”，创新性地应用四足机器人技术，引入了安防巡逻机器人用于库房管理，进一步提升库房管理的智能化水平。</t>
+          <t>基因测序+AI医疗|1.公司依托其具有自主知识产权的cSMART核心技术为支撑，选择ctDNA作为肿瘤液体活检指标，开启了临床无创肿瘤基因检测的全新模式。
+2.公司自主研发NLPearl遗传疾病人工智能临床决策支持系统、CNVisi智能报告解读系统，为科研和临床工作者提供智能决策支持。公司的CNVisi™利用人工智能深度学习算法，挖掘20+权威公共数据库、百万自有CNV大数据以及20多万份CNV-seq临床实践报告，构建7大临床解读知识库，精准注释解读、一键查询信息、自定义设置参数、AI智能撰写报告。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>基因测序, AI医疗</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.3387</v>
+        <v>-1.9551</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>苹果首款折叠屏iPhone Duo有望推动折叠手机走向主流，并预计苹果未来将进一步扩充该产品线，推出更大屏幕的iPhone Duo Max。</t>
+          <t>Anthropic宣布成立生命科学研究团队及实验室，并公布Claude参与生物学研究取得的早期成果。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz002426</t>
+          <t>sz000790</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>胜利精密</t>
+          <t>华神科技</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2.96</v>
+        <v>4.68</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.0372</v>
+        <v>10.1176</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>消费电子|公司精密结构模组业务主要涉及精密金属结构件、塑胶结构件和盖板玻璃等产品的生产加工，广泛应用于电视、笔记本、手机、车载视窗，以及手表、手环等可穿戴智能终端产品上。</t>
+          <t>医药+“华”字辈|在合成生物领域，公司定位打造成为“中国合成生物行业技术及智能化生产的引领者，进入国内合成生物CDMO第一梯队”。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>医药, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.3387</v>
+        <v>-1.9551</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>苹果首款折叠屏iPhone Duo有望推动折叠手机走向主流，并预计苹果未来将进一步扩充该产品线，推出更大屏幕的iPhone Duo Max。</t>
+          <t>Anthropic宣布成立生命科学研究团队及实验室，并公布Claude参与生物学研究取得的早期成果。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz002635</t>
+          <t>sh603122</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>安洁科技</t>
+          <t>合富中国</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>16.79</v>
+        <v>14.93</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.0262</v>
+        <v>10.0221</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>消费电子|1.公司已有折叠屏相关技术储备，且已为多个品牌客户的多款折叠产品提供相关精密结构件和精密功能件。
-2.安洁科技公告称，公司全资子公司威斯东山拟以现金方式收购苏州志烽密姆粉末冶金有限公司51%股权，基础对价为2.04亿元，或有对价上限不超过5100万元，合计不超过2.55亿元。本次交易完成后，苏州志烽将成为公司控股子公司，纳入合并报表范围。苏州志烽以金属粉末注射成型（MIM）为核心工艺，主要为光通信互联、新能源汽车、高端医疗等领域配套产品，主要产品包括光模块芯片基座等。</t>
+          <t>医药+海峡两岸|1.公司系医疗流通领域的渠道商，具备与境内外试剂耗材和医疗设备原厂、各大代理商及医疗机构长期互惠、合作共赢的核心竞争力。
+2.公司为唯一一家海峡两岸市场“双上市”的医疗企业，其母公司合富医疗控股在台湾上市，公司实际控制人为台湾企业家王琼芝，在两岸医疗流通领域有深度合作。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>医药, 海峡两岸</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.3387</v>
+        <v>-0.9878</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>苹果首款折叠屏iPhone Duo有望推动折叠手机走向主流，并预计苹果未来将进一步扩充该产品线，推出更大屏幕的iPhone Duo Max。</t>
+          <t>SpaceX据悉已停止接受2028年以后的猎鹰9号火箭预订。随着猎鹰9号退出市场，火箭发射运力或在2030年前出现供不应求的局面。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -2008,534 +2023,543 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz002937</t>
+          <t>sh603278</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>兴瑞科技</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30.13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10.0037</v>
+        <v>9.988800000000001</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>消费电子|公司以模具技术和智能制造为核心，通过与客户同步设计，采用精密注塑／冲压和自动化组装等先进技术，为智能终端，汽车电子，消费电子等领域中高端客户提供定制化整体解决方案，为客户提供电子连接器、结构件、塑料外壳外壳、镶嵌注塑件等精密电子零部件产品及模具产品。智能终端领域主要客户为ARRIS、TECHNICOLOR、HUMAX、SAGEMCOM、仁宝电脑、金宝电子、富士康等；消费电子领域主要客户为柯尼卡美能达、SONY、SAMSUNG、LG、ABB等。</t>
+          <t>商业航天+机器人|1.公司投资联营企业湖北三江航天江北机械工程有限公司金额为6405.04万。湖北三江航天江北机械工程有限公司主要从事航天动力系统、天线罩等航天型号产品及特种压力容器产品等民用产品的研发生产。
+2.公司关注到近期市场上公司还涉及“人形机器人概念股”相关内容。公司现有主营业务仍以胎圈钢丝、钢帘线以及胶管钢丝的研发、生产和销售为主，公司机器人腱绳产品目前尚未批量生产，未产生实质性收益，且公司相关业务未来在技术研发、产品竞争能力、盈利能力等方面存在重大不确定性。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>商业航天, 机器人</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-0.0145</v>
+        <v>-0.9878</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华源证券最新研报指出，创新药行业多维向好，CRO需求逐步复苏。中国创新药审批与支付双端政策环境改善，临床CRO需求延续复苏态势，市场有望持续扩容。</t>
+          <t>SpaceX据悉已停止接受2028年以后的猎鹰9号火箭预订。随着猎鹰9号退出市场，火箭发射运力或在2030年前出现供不应求的局面。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh688656</t>
+          <t>sh688682</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">浩欧博  </t>
+          <t xml:space="preserve">霍莱沃  </t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>141.04</v>
+        <v>37.94</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>20.0034</v>
+        <v>19.9873</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>体外诊断试剂|公司专业从事体外诊断试剂的研发、生产和销售，专注于过敏性疾病和自身免疫性疾病的检测，所生产的检测试剂应用于过敏性疾病和自身免疫性疾病的临床辅助诊断，产品在全国各级医疗机构得到广泛使用。公司过敏产品已扩展到多个系列，覆盖69种IgE过敏原及80种食物特异性IgG过敏原，可检测的IgE过敏原数量国内领先。</t>
+          <t>商业航天|公司的多探头测试+实时频谱分析系统、近场扫描技术可助力具备高密度集成特性的算力卫星解决多源电磁干扰问题，实现电磁兼容测试在宽频域、动态负载方面的双重突破。此外，霍莱沃可在算力卫星设计阶段提供EMC仿真的应对方案，对太空等离子体和空间静电放电累积效应进行仿真分析找出薄弱环节、采用专用的EMC设计技术进行全面优化防护，并对敏感设备进行抗干扰和ESD试验验证，从而在设计阶段最大程度解决可能存在的电磁兼容问题。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>体外诊断试剂</t>
+          <t>商业航天</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-0.0145</v>
+        <v>-0.9878</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>消息面上，华源证券最新研报指出，创新药行业多维向好，CRO需求逐步复苏。中国创新药审批与支付双端政策环境改善，临床CRO需求延续复苏态势，市场有望持续扩容。</t>
+          <t>SpaceX据悉已停止接受2028年以后的猎鹰9号火箭预订。随着猎鹰9号退出市场，火箭发射运力或在2030年前出现供不应求的局面。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh603222</t>
+          <t>sz002413</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>济民健康</t>
+          <t>雷科防务</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>8.94</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>9.963099999999999</v>
+        <v>10.0613</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>医药|公司系浙江省医药行业重点骨干企业，产业已覆盖大输液、医疗器械、血液透析、体外诊断试剂、综合医疗服务等5大领域，初步构建形成“一主两翼”发展格局。主导产品“双管双阀非PVC软袋”大输液在华东、华南地区市场占有率达30%以上，国外销售东南亚、非洲、南美等30多个国家和地区。</t>
+          <t xml:space="preserve">商业航天|子公司恒达微波研发的“微波应答机天线”产品应用于长征五号B遥二运载火箭中搭载的核心舱。
+</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>商业航天</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-2.5779</v>
+        <v>-2.6211</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>国家版权局印发《版权工作“十五五”规划》，其中提出2030年版权质权融资登记金额目标为120亿元。</t>
+          <t>多家机构预计，2026年全球磷化铟供需缺口超70%；国内所有厂商出货量仅占全球供应量约一成，产业链紧张局面持续向上下游传导。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sh603042</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>华脉科技</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>18.5</v>
+        <v>18.73</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.988099999999999</v>
+        <v>9.9824</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>传媒+并购|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
+          <t>光纤+“华”字辈|公司是一家信息通信网络基础设施解决方案提供商，主要产品包括光纤、光缆、光器件及光配线设施全场景有线传输链路解决方案及系列产品。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>传媒, 并购</t>
+          <t>光纤, “华”字辈</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-2.5779</v>
+        <v>-2.6211</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>国家版权局印发《版权工作“十五五”规划》，其中提出2030年版权质权融资登记金额目标为120亿元。</t>
+          <t>多家机构预计，2026年全球磷化铟供需缺口超70%；国内所有厂商出货量仅占全球供应量约一成，产业链紧张局面持续向上下游传导。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sz002395</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>双象股份</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>7.06</v>
+        <v>14.05</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>9.9688</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.0235</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>传媒+并购|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
+          <t>光学级PMMA|双象股份2026年4月15日在投资者互动平台表示，公司光学级PMMA材料可应用于光学仪器、光学镜片等领域。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>传媒, 并购</t>
+          <t>光学级PMMA</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-0.8027</v>
+        <v>-2.6211</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>华泰证券研报判断，黄酒行业的量价逻辑有望迎来重构。从量的弹性看，消费场景稳步升级，先由江浙沪渗透率提升，后到全国市场的稳步拓展；从价的维度看，在行业竞争格局优化背景下，龙头企业合力培育品牌，稳步推动高端化进程。</t>
+          <t>多家机构预计，2026年全球磷化铟供需缺口超70%；国内所有厂商出货量仅占全球供应量约一成，产业链紧张局面持续向上下游传导。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz002286</t>
+          <t>sh603065</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>保龄宝</t>
+          <t>宿迁联盛</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>8.75</v>
+        <v>16.27</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.0629</v>
+        <v>10.0068</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>功能糖|公司主要产品完整覆盖高、中、低全品类功能糖产品，形成了完整的淀粉—淀粉糖—益生元—膳食纤维—功能糖醇及新糖源—益生元终端的金字塔式产品结构，可提供全品类的功能性低聚糖、功能性膳食纤维、功能性糖醇及新糖源等综合性应用解决方案、产品和服务。</t>
+          <t>磷化铟|宿迁联盛公告称，公司与朱蓉辉、汇智光芯签署《合资意向协议》，拟共同出资1000万元设立合资公司，从事磷化铟衬底的研发生产销售。其中公司出资700万元，持股70%。项目计划分两期建设，一期固定投资1亿元，预期年产12万片4-6英寸磷化铟衬底；二期预计追加投资2亿元，产能扩充至40万片/年。本次投资尚需提交股东会审议，存在较大不确定性。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>功能糖</t>
+          <t>磷化铟</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>科学仪器</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-1.3155</v>
+        <v>0.122</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>近日农业农村部召开全国“三秋”农业生产工作视频会议，会议强调，要紧盯不放抓好秋管秋收，密切关注超强厄尔尼诺气候影响，细化气象灾害和病虫草害应急预案，扎实推进高标准农田建设。</t>
+          <t>华泰证券研报指出，随着数据中心网络向800G、1.6T演进，高速连接器、线缆及高端PCB对信号完整性与良率管控的要求持续提高，带动VNA测试需求增长。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh600371</t>
+          <t>sz002819</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>万向德农</t>
+          <t>东方中科</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>17.28</v>
+        <v>26.66</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>9.993599999999999</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
+        <v>9.983499999999999</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>玉米种子|公司从事的主要业务为玉米杂交种子研发、生产、销售，主营包括但不限于“京科968”、“德单系列”等玉米杂交种的生产与销售。</t>
+          <t>VNA|旗下中科四点零已推出 VNA1009系列矢量网络分析仪，支持高精度S参数测量、多端口级联及大规模并行测试，直接面向产线量产环境。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>玉米种子</t>
+          <t>VNA</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>量子科技</t>
+          <t>科学仪器</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.5506</v>
+        <v>0.122</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>美股量子计算概念股IonQ盘后涨超5%，公司展示业界首个端到端实时量子纠错解码器。</t>
+          <t>华泰证券研报指出，随着数据中心网络向800G、1.6T演进，高速连接器、线缆及高端PCB对信号完整性与良率管控的要求持续提高，带动VNA测试需求增长。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sz002935</t>
+          <t>sz301689</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>天奥电子</t>
+          <t>电科思仪</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>17.52</v>
+        <v>83.88</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>9.981199999999999</v>
+        <v>20</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>量子|量子科技方面公司涉及的主要是量子精密测量领域。</t>
+          <t>VNA|电科思仪是国内电子测量仪器领域领军企业，2026年9月10日科思仪申请矢量网络分析仪相关专利，提升多端口矢网测量效率，降本减误。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>量子</t>
+          <t>VNA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1.895</v>
+        <v>-1.8366</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>京东方董事长陈炎顺在2026年京东方全球创新伙伴大会上宣布，未来五年公司研发投入将超800亿元，采购支出超8000亿元，明确未来一年内将敲定玻璃基钙钛矿器件与玻璃基封装载板两条量产线的投资计划。</t>
+          <t>国际半导体产业协会数据显示，2026年第二季度全球半导体设备销售额达405.3亿美元，同比增长23%、环比增长11%，连续两个季度刷新历史最高纪录，AI算力扩产带来的设备采购需求持续向上游传导。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh603773</t>
+          <t>sz002119</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>沃格光电</t>
+          <t>康强电子</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>102.5</v>
+        <v>29.61</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10.0021</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
+        <v>9.992599999999999</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板|公司具备的玻璃基微米级巨量互通技术（TGV技术），可应用于 2.5D/3D封装的垂直封装载板，终端应用场景包括大型AI算力服务器（CPU/GPU）、数据中心、自动驾驶、光通信、CPO光模块、射频（含手机）、5G/6G通信基站、MEMS（微型传感器）等高性能计算或高性能信号传输应用场景。</t>
+          <t>半导体封装材料|公司是一家专业从事各类半导体封装材料引线框架、键合丝等半导体封装材料的开发、生产、销售的高新技术企业，主要产品引线框架和键合丝国内市场规模处于领先地位，产品覆盖国内知名的半导体后封装企业。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>半导体封装材料</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>-1.8366</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>国际半导体产业协会数据显示，2026年第二季度全球半导体设备销售额达405.3亿美元，同比增长23%、环比增长11%，连续两个季度刷新历史最高纪录，AI算力扩产带来的设备采购需求持续向上游传导。</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sz001234</t>
+          <t>sh603375</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>泰慕士</t>
+          <t xml:space="preserve">盛景微  </t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>32.18</v>
+        <v>49.25</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10.0171</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.0067</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>纺织|公司主营业务为针织面料和针织服装的研发、生产和销售，主要为迪卡侬、森马服饰、蕉内、Quiksilver、佐丹奴、全棉时代、曼妮芬、安踏、波司登等知名服装品牌提供贴牌加工服务。</t>
+          <t>模拟芯片|公司是一家具备高性能、超低功耗芯片设计能力的电子器件提供商，主要产品为工业安全领域的电子控制模块。公司销售的产品包括电子控制模块、起爆控制器、放大器等。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>纺织</t>
+          <t>模拟芯片</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
+          <t>风电</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>-0.1419</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>“十五五”期间，我国将加强海洋开发利用保护，预计到2030年，全国海洋生产总值将突破13万亿元，海上风电装机容量实现翻一番，达到1亿千瓦。</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sh600418</t>
+          <t>sh601218</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>吉鑫科技</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>23.45</v>
+        <v>5.5</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>9.990599999999999</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>汽车|公司是一家集全系列商用车、乘用车及动力总成等研产销和服务于一体,“先进节能汽车、新能源汽车、智能网联汽车”并举的综合型汽车企业集团。</t>
+          <t>风电|公司是一家专注于研发、制造和销售大型风力发电机组用零部件的龙头企业，主要生产750KW-12MW风力发电机组用轮毂、底座、轴、轴承座等系列产品。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>汽车</t>
+          <t>风电</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+          <t>液冷IDC</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>-1.8716</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>浙商证券研报指出，第三季度是液冷行业从试点走向批量交付、业绩集中兑现的关键拐点，以英伟达VR200机柜规模化出货为核心驱动。</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz000850</t>
+          <t>sz002909</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>华茂股份</t>
+          <t>集泰股份</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4.65</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>9.9291</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+        <v>9.946899999999999</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>棉花|公司专注于棉、毛、麻、丝和人造纤维的纯、混纺纱线及其织物、针织品、服装、印染加工；纺织设备及配件、家用纺织品销售；投资管理。公司产品包括纱线系列产品，坯布面料系列产品、色织面料系列产品和功能性产业用布等。</t>
+          <t>PCB+液冷|1.公司PCB三防漆涵盖有机硅、UV等多个系列，主要用于PCB电路板及电子元器件表面防护，可应用于智能设备、汽车电子、消费电子、工业控制、通信设备等场景。
+2.公司当前研发的液冷导热硅油，其应用主要聚焦于数据中心及储能领域的热管理解决方案。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>棉花</t>
+          <t>PCB, 液冷</t>
         </is>
       </c>
     </row>
@@ -2552,33 +2576,37 @@
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sh600653</t>
+          <t>sz002321</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>申华控股</t>
+          <t>华英农业</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>1.87</v>
+        <v>2.27</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
+        <v>10.1942</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>汽车销售|公司汽车消费服务类业务可细分为三个部分，汽车销售服务业务、汽车文化产业园、汽车租赁业务等。公司主营华晨旗下的中华、金杯、华颂等汽车品牌销售，且通过2017年对申华晨宝的收购，实现了宝马等中高端汽车品牌补充，公司现有渭南汽博园和开封汽博园两个汽车文化产业项目。</t>
+          <t>鸭养殖+“华”字辈|主营业务为种鸭/鸡养殖、孵化、禽苗销售、饲料生产、商品鸭/鸡屠宰加工、冻品销售、熟食、羽绒及羽绒制品生产和销售。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>汽车销售</t>
+          <t>鸭养殖, “华”字辈</t>
         </is>
       </c>
     </row>
@@ -2595,33 +2623,37 @@
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh600230</t>
+          <t>sh603396</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>沧州大化</t>
+          <t>金辰股份</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>14.82</v>
+        <v>35.64</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>10.0223</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>化工|公司是我国首家规模生产TDI的公司，拥有年产15万吨TDI、10万吨PC、及配套的16万吨烧碱、造气原料气、20万吨双酚A等相关产品链相衔接、上下游原料相配套的生产规模。</t>
+          <t>玻璃基板|公司拟设立全资子公司辰光微电半导体设备(南通)有限公司作为项目公司，注册资本1000万元，持股比例100%。项目将建设现代化厂房和高标准洁净室，搭建以TGV玻璃基封装为代表的半导体设备生产试验线，推动超快激光诱导改质设备等半导体专用设备的研发与制造验证。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>玻璃基板</t>
         </is>
       </c>
     </row>
@@ -2638,33 +2670,33 @@
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sh603937</t>
+          <t>sh601567</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>丽岛新材</t>
+          <t>三星电气</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>12.97</v>
+        <v>16.25</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>10.0085</v>
+        <v>10.0203</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>锂电池|子公司安徽丽岛的主要产品为铝板带箔材料，产品可广泛应用于建筑材料、食品包装、电子电器、新能源电池、储能等市场领域。</t>
+          <t>签订数据中心项目|三星电气公告称，公司全资子公司奥克斯智能科技中标美国数据中心储能油变项目，合同金额总计1.32亿美元，约合8.85亿人民币，占公司2025年度经审计营收的6.16%。合同的履行将对公司经营业绩产生积极影响，是公司在美国配电业务数据中心领域的重要突破。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>签订数据中心项目</t>
         </is>
       </c>
     </row>
@@ -2681,33 +2713,33 @@
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sz002633</t>
+          <t>sz000498</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>申科股份</t>
+          <t>山东路桥</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>15.87</v>
+        <v>5.65</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>9.979200000000001</v>
+        <v>9.9222</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>轴承|公司主导产品为厚壁滑动轴承，主要配套于汽轮机、燃气轮机、水轮机、发动机、电动机、鼓风机、水泵、压缩机、风机等各类旋转机械。</t>
+          <t>控股股东增持|山东路桥公告称，公司控股股东高速集团及其一致行动人高速投资控股拟自公告披露之日起6个月内，以专项贷款和/或自有资金通过集中竞价方式增持公司股份，增持总金额不低于4.5亿元且不超过9亿元。其中，高速集团增持金额不低于3亿元且不超过6亿元，高速投资控股增持金额不低于1.5亿元且不超过3亿元。本次增持不设价格区间。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>轴承</t>
+          <t>控股股东增持</t>
         </is>
       </c>
     </row>
@@ -2724,34 +2756,33 @@
       </c>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh600843</t>
+          <t>sh600792</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>上工申贝</t>
+          <t>云煤能源</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>7.61</v>
+        <v>5.7</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>9.9711</v>
+        <v>10.0386</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>低空|1.2024年3月4日互动，碳纤维轻型运动飞机项目是公司参股的上海飞人科技涉及投资的项目之一。该项目消化吸收国外的飞机制造技术、进行民航的TC/VTC认证、零部件国产化的供应商认证。
-2.公司已经成长为一家占据全球缝制技术制高点并为客户量身定制工业4.0应用解决方案的专业设备供应商，主要产品有机器人焊接、组装生产线，程控机械加工流水线等。</t>
+          <t>焦炭|公司主要从事焦化业务，涉及焦炭及相关化工产品的生产和销售，主导产品为冶金焦炭。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>低空</t>
+          <t>焦炭</t>
         </is>
       </c>
     </row>
@@ -2768,33 +2799,33 @@
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh603067</t>
+          <t>sz002836</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>振华股份</t>
+          <t>新宏泽</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>39.86</v>
+        <v>12.27</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>9.989000000000001</v>
+        <v>10.0448</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>燃气轮机|公司金属铬产品在高温合金、铜基、铝基特种合金、高端焊接材料、溅射靶材等领域广泛应用，高温合金是燃气轮机的主要材料，单质铬的添加量在15%~20%之间。</t>
+          <t>烟标印刷|公司系专业烟标印刷服务供应商，主营业务为烟标的设计、生产及销售。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>燃气轮机</t>
+          <t>烟标印刷</t>
         </is>
       </c>
     </row>
@@ -2811,33 +2842,33 @@
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sz002638</t>
+          <t>sh600189</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>勤上股份</t>
+          <t xml:space="preserve">泉阳泉  </t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>4.74</v>
+        <v>9.1</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>9.976799999999999</v>
+        <v>10.0363</v>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>LED|公司半导体照明主要产品包括LED户外照明、LED景观照明、LED室内照明和LED显示屏等。</t>
+          <t>矿泉水+谐音“羊”|公司主要从事长白山天然饮用矿泉水的生产和销售，旗下主要产品“泉阳泉”牌长白山天然矿泉水。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>矿泉水, 谐音“羊”</t>
         </is>
       </c>
     </row>
@@ -2854,33 +2885,76 @@
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sz300931</t>
+          <t>sh603970</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>通用电梯</t>
+          <t>中农立华</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>19.21</v>
+        <v>12.17</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>19.9875</v>
+        <v>10.0362</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>电梯|公司主要从事电梯、自动扶梯、自动人行道的产品研发、设计、制造、销售、安装、改造及维保业务，是一家为各类建筑的电梯提供系统性的解决方案及全面的更新改造方案的科技创新型企业，产品线覆盖乘客电梯、观光电梯、医用电梯、家用电梯、载货电梯、汽车电梯、既有建筑加装电梯、自动扶梯、自动人行道等各系列电梯。公司承接了一系列政府机构、企事业单位、机场高铁站、大型地产项目及地标性建筑的电梯项目，代表性项目包括刚果(布)奥隆博国际机场、乌鲁木齐高铁站北广场项目、长沙通程逸城大酒店、新疆克拉玛依市行政综合楼、重庆北温泉9号、银川滨河新区景城安置区等。</t>
+          <t>农药+“华”字辈|实际控制人为中国供销集团有限公司。公司主要业务包括农药流通服务业务、植保技术服务业务和植保机械供应业务三大类。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>电梯</t>
+          <t>农药, “华”字辈</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sz002205</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>国统股份</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>9.982799999999999</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>建材|公司产品PCCP（预应力钢筒混凝土管）技术含量较高，规格齐全，公司积极推进产品结构及业务调整转型，通过PPP模式积极参与水务、地下综合管廊等市政基础设施的投资、建设、运营，培育新的利润增长点。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>建材</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2922,16 +2996,16 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sz000910</t>
+          <t>sh601811</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>大亚圣象</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
@@ -2941,42 +3015,42 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sh600825</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sz001234</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>泰慕士</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz001234</t>
+          <t>sz002614</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>泰慕士</t>
+          <t>奥佳华</t>
         </is>
       </c>
     </row>
@@ -2986,72 +3060,72 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh600743</t>
+          <t>sz002238</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>华远控股</t>
+          <t>天威视讯</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh600503</t>
+          <t>sh600802</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>华丽家族</t>
+          <t>福建水泥</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sz000560</t>
+          <t>sz000850</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>我爱我家</t>
+          <t>华茂股份</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sz002614</t>
+          <t>sh603949</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>雪龙集团</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sh603636</t>
+          <t>sz002119</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>南威软件</t>
+          <t>康强电子</t>
         </is>
       </c>
     </row>
@@ -3061,12 +3135,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sh605058</t>
+          <t>sh600843</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>上工申贝</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3150,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>sh600418</t>
+          <t>sz002819</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>东方中科</t>
         </is>
       </c>
     </row>
@@ -3091,12 +3165,27 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>sz002238</t>
+          <t>sz002909</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>天威视讯</t>
+          <t>集泰股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>sh603396</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>金辰股份</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,20 +476,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="99" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="255" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="240" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,2409 +552,1588 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.6992</v>
+        <v>-2.7261</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
+          <t>据报道，特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh600802</t>
+          <t>sh603949</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>雪龙集团</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6.62</v>
+        <v>18.59</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.966800000000001</v>
+        <v>10</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>福建+水泥|公司主要从事水泥及熟料的生产及销售，拥有7条新型干法熟料水泥生产线，具备年产熟料784.3万吨、水泥1164万吨。公司是福建地区产能规模最大的水泥制造企业，也是福建省水泥行业唯一的一家上市公司。</t>
+          <t>机器人|公司作为有限合伙人通过深创投中小企业发展基金（新疆）有限合伙企业间接持股杭州宇树科技有限公司。目前，深创投中小企业发展基金（新疆）有限合伙企业对杭州宇树科技有限公司的持股比例为1.3546%；公司对深创投中小企业发展基金（新疆）有限合伙企业的持股比例为0.7239%。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>福建, 水泥</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.6992</v>
+        <v>-2.7261</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
+          <t>据报道，特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh600815</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>厦工股份</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.65</v>
+        <v>10.65</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.9291</v>
+        <v>10.0207</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>福建+工程机械|公司核心竞争力包含装载机、挖掘机、道路机械、叉车等工程机械整机产品与核心零部件的研发、制造和营销服务能力。</t>
+          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>福建, 工程机械</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.6992</v>
+        <v>-2.7261</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
+          <t>据报道，特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz000592</t>
+          <t>sh603278</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>10.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.0251</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>福建+林业|公司在林木业务方面已基本形成“林板一体化”的发展产业链，拥有经营林区近90万亩，在福建省处于行业领先龙头地位。</t>
+          <t>商业航天+机器人|1.公司投资联营企业湖北三江航天江北机械工程有限公司金额为6405.04万。湖北三江航天江北机械工程有限公司主要从事航天动力系统、天线罩等航天型号产品及特种压力容器产品等民用产品的研发生产。
+2.公司关注到近期市场上公司还涉及“人形机器人概念股”相关内容。公司现有主营业务仍以胎圈钢丝、钢帘线以及胶管钢丝的研发、生产和销售为主，公司机器人腱绳产品目前尚未批量生产，未产生实质性收益，且公司相关业务未来在技术研发、产品竞争能力、盈利能力等方面存在重大不确定性。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>福建, 林业</t>
+          <t>商业航天, 机器人</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.6992</v>
+        <v>-2.7261</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
+          <t>据报道，特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz300300</t>
+          <t>sz002242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>海峡创新</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>10.81</v>
+        <v>10.33</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>19.9778</v>
+        <v>10.0106</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>福建+创投|1.公司是平潭综合实验区金融控股集团旗下上市公司
-2.上市公司投资参控股的企业有50余家，符合“独角兽”、“新经济”类型的为数众多，比如极光推送、京东金融等</t>
+          <t>机器人|公司持有深思考人工智能机器人科技（北京）有限公司7.92%的股份，旗下产品包括AI机器人。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>福建, 创投</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.6992</v>
+        <v>-2.7261</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
+          <t>据报道，特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz000905</t>
+          <t>sz002347</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>厦门港务</t>
+          <t>泰尔股份</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>9.81</v>
+        <v>6.42</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9.977600000000001</v>
+        <v>9.9315</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>福建+港口|公司作为厦门港区规模最大综合物流服务商，拥有散杂货码头及后方堆场等稀缺资源、完善的港口配套与增值服务、较为完整的物流业务链条，形成了内外贸航线、海陆空物流体系。</t>
+          <t>机器人+商业航天|1.2021年8月5日公司在互动平台表示，公司子公司燊泰智能的高线包装机器人市场占有率约42.4%。
+2.公司的激光技术、粉末材料可以应用于航空航天。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>福建, 港口</t>
+          <t>机器人, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.6992</v>
+        <v>-2.7261</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
+          <t>据报道，特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz000753</t>
+          <t>sz002480</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>漳州发展</t>
+          <t>新筑股份</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>5.35</v>
+        <v>5.65</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.0823</v>
+        <v>9.9222</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>福建+汽车后市场|福建本地上市公司，主营汽贸业务，目前已成立漳发汽车集团，实现集团化经营管理，旗下已有的品牌授权包含长安福特，北汽新能源，奇瑞新能源等。</t>
+          <t>机器人+并购重组|1.参股奥威科技参与研发的移动充电机器人目前处于对样机进行调试的阶段。
+2.9月23日晚间，新筑股份披露，拟以56.03亿元收购蜀道集团旗下四川蜀道清洁能源集团有限公司60%股权，同时出售磁浮及桥梁功能部件业务相关资产。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>福建, 汽车后市场</t>
+          <t>机器人, 并购重组</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.6992</v>
+        <v>-1.4294</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
+          <t>OpenAI对外表示，已暂停其最新一代人工智能模型的训练、评估，以及支持工具调用的推理工作，起因是内部测试中的AI智能体突破沙盒网络限制，触发安全预警，公司将借此机会升级安全隔离与对齐监控体系。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz002679</t>
+          <t>sz002912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>福建金森</t>
+          <t>中新赛克</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>11.58</v>
+        <v>26.47</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.971499999999999</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+        <v>10.0166</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>福建+林业|公司主营业务为森林培育营造，森林保有管护，木材生产销售，林业服务。</t>
+          <t>AI+网络安全|公司推出的小赛安全智脑产品，支持多模型底座，基于智能体、RAG等技术，包含渗透测试智能体、事件调查智能体、代码安全审计智能体，也配备了敏感数据识别、智能解码、安全知识问答等多种智能体应用，全方位满足安全运维场景下的各类用户需求，为企业数据与网络安全保驾护航。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>福建, 林业</t>
+          <t>AI, 网络安全</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.6992</v>
+        <v>-1.4294</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
+          <t>OpenAI对外表示，已暂停其最新一代人工智能模型的训练、评估，以及支持工具调用的推理工作，起因是内部测试中的AI智能体突破沙盒网络限制，触发安全预警，公司将借此机会升级安全隔离与对齐监控体系。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>920748.BJ</t>
+          <t>sh688244</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>路桥信息</t>
+          <t>永信至诚</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>36.5</v>
+        <v>19.8</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>29.9858</v>
+        <v>20</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>福建+车联网|公司是厦门国有资本运营有限责任公司旗下上市公司。公司的车路协同路侧融合感知系统通过目标识别完成对路段、转角盲区范围内的机动车、非机动车、行人的识别检测以及定位，实现交叉口碰撞预警、弱势交通参与者碰撞预警、交叉口车速引导、前方拥堵提醒、紧急车辆提醒、道路危险状况提示、限速预警、信息服务等功能。</t>
+          <t>AI+网络安全|在人工智能领域，公司网络靶场系列产品和“数字风洞”产品体系均是人工智能安全测试评估的基础设施平台，具备对人工智能相关产品和风险进行安全测试评估的能力。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>福建, 车联网</t>
+          <t>AI, 网络安全</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.6992</v>
+        <v>-1.4294</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>福建省人民政府印发《福建省美丽中国先行区建设实施方案》，提出到2030年底前基本建成美丽中国先行区。</t>
+          <t>OpenAI对外表示，已暂停其最新一代人工智能模型的训练、评估，以及支持工具调用的推理工作，起因是内部测试中的AI智能体突破沙盒网络限制，触发安全预警，公司将借此机会升级安全隔离与对齐监控体系。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz002264</t>
+          <t>sz002232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>新 华 都</t>
+          <t>启明信息</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>16.28</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.0135</v>
+        <v>10</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>福建+零售+AI|1.公司主要业务为互联网营销和超市百货业务，旗下久爱致和服务于多家国际、国内知名企业，也是天猫及京东等多家电子商务平台的合作伙伴。
-2.公司结合AI大模型与电商场景，已开发并上线试运行智能化平台“久爱AI”，一期版本开放商品评论分析、商品信息采集、违禁词风险评估、摘要抽取、文案大纲助手、简历筛选6项AI工具，为优化营销策略、产品结构和日常办公提供技术支持。
-3.阿里巴巴成都及杭州瀚云均为公司股东。</t>
+          <t>网络安全|子公司长春启明信息集成服务技术有限公司主要开展网络安全等级保护定级协助、等级保护建设咨询、等级保护方案设计、等级保护测评、等级保护培训、信息安全风险评估、安全运维服务以及应急响应等安全服务业务，是从事专业化的信息安全服务提供商。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>福建, 零售, AI</t>
+          <t>网络安全</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-1.06</v>
+        <v>-2.406</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
+          <t>据百川盈孚报价，2026年9月1日以来，分散染料价格一直维持在30元/千克的高位，相比6月22日的23元/千克上涨7元/千克，2个多月的时间价格上涨超30%。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz002614</t>
+          <t>sz301190</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>善水科技</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>8.33</v>
+        <v>24.95</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10.0396</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>20.0096</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>机器人+“华”字辈|公司AI按摩机器人2.0（OG-8598Plus），已实现服务功能与产品有机结合，运用人脸识别、疲感侦测、“千人千方”智能AI算法、云端个人健康数据库、新一代4D无刷变频温感机芯等新技术构建围绕用户健康的检测-分析-调理闭环服务系统，关注每一位用户的健康状态，为用户远程推送“量身定制”的专属按摩解决方案，构建家庭健康管理服务生态。</t>
+          <t>染料+农药+医药|公司主要经营染料中间体、农药和医药中间体的研发、生产和销售业务。公司生产的染料中间体包括6-硝体、氧体、5-硝体和邻氨基苯磺酸。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>机器人, “华”字辈</t>
+          <t>染料, 农药, 医药</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-1.06</v>
+        <v>-2.406</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
+          <t>据百川盈孚报价，2026年9月1日以来，分散染料价格一直维持在30元/千克的高位，相比6月22日的23元/千克上涨7元/千克，2个多月的时间价格上涨超30%。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh603949</t>
+          <t>sh605366</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>宏柏新材</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>16.9</v>
+        <v>10.14</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.026</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.978299999999999</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司作为有限合伙人通过深创投中小企业发展基金（新疆）有限合伙企业间接持股杭州宇树科技有限公司。目前，深创投中小企业发展基金（新疆）有限合伙企业对杭州宇树科技有限公司的持股比例为1.3546%；公司对深创投中小企业发展基金（新疆）有限合伙企业的持股比例为0.7239%。</t>
+          <t>有机硅+光纤上游|1.公司主营业务为功能性硅烷、纳米硅材料等硅基新材料及其他化学助剂的研发、生产与销售。
+2.公司重点布局2万吨光纤级高纯四氯化硅和5000吨电子级正硅酸乙酯等新兴产业项目，以满足下游光纤及电子半导体产业需求。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>有机硅, 光纤上游</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-1.06</v>
+        <v>-2.406</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
+          <t>据百川盈孚报价，2026年9月1日以来，分散染料价格一直维持在30元/千克的高位，相比6月22日的23元/千克上涨7元/千克，2个多月的时间价格上涨超30%。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603500</t>
+          <t>sh603968</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>祥和实业</t>
+          <t>醋化股份</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>10.42</v>
+        <v>11.63</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.0317</v>
+        <v>10.0284</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>超级电容+机器人|1.公司紧跟铝电解电容器技术迭代，先后开发成功V-CHIP电容底座、车用耐振动底座以及应用于超级电容、锂电池、耐550V以上特高压、耐150℃电容器用橡胶密封塞、轴向电容器盖板等产品。
-2.公司于2024年4月30日成立子公司祥和智能，研发、制造和销售工业机器人、智能机器人及人工智能应用软件开发等系祥和智能的经营范围。</t>
+          <t>染料|公司的双乙甲酯产品涉及分散染料领域。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>超级电容, 机器人</t>
+          <t>染料</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>AI医疗</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-1.06</v>
+        <v>-0.8985</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
+          <t>浙商证券表示，AI制药已从“算法叙事”进入“临床兑现”阶段，而药物研发迭代的限速步骤在湿实验，AI提效将催生更强烈的分子验证需求。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sz000513</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>丽珠集团</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>9.68</v>
+        <v>30.34</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>10.0073</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
+          <t>创新药+AI医疗|1.公司已根据技术成熟度和市场需求优化研发管线布局，聚焦消化道、精神神经、代谢、抗感染等重点领域的创新药、高壁垒复杂制剂及高临床价值产品研发。
+2.公司于2024年初布局自有云端算力，将AI战略融入研发全局。目前AI应用已覆盖研发、生产、销售及职能全链条，并在研发链条中由后端向前端系统推进，在靶点发现、工艺优化、临床决策等关键环节已取得初步成效，为创新加速提供新动能。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>创新药, AI医疗</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>AI医疗</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-1.06</v>
+        <v>-0.8985</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
+          <t>浙商证券表示，AI制药已从“算法叙事”进入“临床兑现”阶段，而药物研发迭代的限速步骤在湿实验，AI提效将催生更强烈的分子验证需求。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh605018</t>
+          <t>sz000503</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>长华集团</t>
+          <t>国新健康</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>12.74</v>
+        <v>7.44</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.0173</v>
+        <v>10.0592</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司完成行星滚柱丝杠产线设计，一期规划年产20万套。</t>
+          <t>AI医疗|公司在"三医协同"领域深耕多年，结合国家和行业标准，通过构建完整的医保、医疗、医药的专业知识体系，如专业的"四库二十四系统"知识体系，并运用人工智能、大数据等先进科技手段，逐渐形成了业内独特的行业竞争力。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>AI医疗</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-1.06</v>
+        <v>-0.9787</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
+          <t>根据中指研究院监测数据显示，截至9月24日，全国共出台房地产相关政策超870条，其中三季度全国出台房地产相关政策超280条，延续上半年政策高频落地趋势。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz301699</t>
+          <t>sz000011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>洛轴股份</t>
+          <t>深物业A</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>35.54</v>
+        <v>10.12</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>19.9865</v>
+        <v>10</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>机器人+商业航天|1.公司针对国产机器人产业发展需求，开展机器人专用精密轴承设计和制造、测试、寿命试验等技术研究，研制出了薄壁等截面、交叉圆柱滚子两种系列轴承以及RV减速器、谐波减速器专用系列精密轴承。
-2.公司为航空航天等高端装备研制的多款关键轴承应用于“神舟系列”“嫦娥系列”、天宫空间站、天和核心舱、问天实验舱、梦天实验舱等重大航天工程，为国家航空航天发展作出贡献。</t>
+          <t>房地产|公司经过多年发展，已形成了以房地产开发为主业，物业管理、物业租赁、出租汽车营运、餐饮服务、物流仓储、工程监理等为辅的跨行业、多元化的经营格局。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>机器人, 商业航天</t>
+          <t>房地产</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-1.06</v>
+        <v>-0.9787</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
+          <t>根据中指研究院监测数据显示，截至9月24日，全国共出台房地产相关政策超870条，其中三季度全国出台房地产相关政策超280条，延续上半年政策高频落地趋势。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh603767</t>
+          <t>sz000020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>中马传动</t>
+          <t>深华发Ａ</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>14.74</v>
+        <v>14.64</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10</v>
+        <v>9.9925</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司招股说明书显示，将以现有汽车变速器齿轮、汽车转向器齿轮、汽车油泵轴齿轮、汽车发动机齿轮、摩托车发动机齿轮、农机变速器齿轮为发展基础，大力开拓汽车自动变速器行星齿轮、工业机器人减速器齿轮等高精度齿轮产品领域。</t>
+          <t>房地产|公司在深圳市福田区华强北商圈及光明新区公明街道均拥有数万平方米的大型物业。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>房地产</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1.06</v>
+        <v>-1.3038</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
+          <t>浙江省海洋经济发展厅近日发布《浙江省海洋清洁能源产业发展指引》，《指引》提出，到2030年，全省海洋清洁能源及其装备产业规模突破3000亿元，海上风电装机超1000万千瓦。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz002164</t>
+          <t>sh601218</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>吉鑫科技</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>13.06</v>
+        <v>6.05</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.0253</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>机器人+风电|1.公司的产品包括行星减速器等，杭州湾电机、减速器部分车间已投入生产。
-2.公司研发的风电齿轮箱应用于风电市场。</t>
+          <t>风电|公司是一家专注于研发、制造和销售大型风力发电机组用零部件的龙头企业，主要生产750KW-12MW风力发电机组用轮毂、底座、轴、轴承座等系列产品。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>机器人, 风电</t>
+          <t>风电</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-1.06</v>
+        <v>-1.3038</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>近日，马斯克接受专访时指出，未来15年全球人形机器人或达到100亿台；未来20年可能达到1000亿台。</t>
+          <t>浙江省海洋经济发展厅近日发布《浙江省海洋清洁能源产业发展指引》，《指引》提出，到2030年，全省海洋清洁能源及其装备产业规模突破3000亿元，海上风电装机超1000万千瓦。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz301311</t>
+          <t>sz002342</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>昆船智能</t>
+          <t>巨力索具</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>17.98</v>
+        <v>8.68</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>20.0267</v>
+        <v>10.0127</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>机器人+烟草|1.公司产品有机器人和AGV，广泛应用于制造行业的自动化生产线、自动装配流水线的物料上下线，流通企业的物料码垛搬运、集装箱搬运、自动拣选以及智慧停车等自动搬运场景。
-2.公司智能产线以烟草行业为起点，为客户提供烟草领域全产业链的系统解决方案，已涉及电子烟领域相关业务。</t>
+          <t>风电+商业航天|1.公司新研制产品的应用与参与的项目包括全角度海上风电单叶片专用吊具、用于全球首台抗台风型深远海漂浮式海上风机的永久系泊索，以及参与建设的白鹤滩水电站、核电站等项目。
+2.公司为神舟十九号发射任务提供了火箭转运索具、总装索具、火箭分离索具等。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>机器人, 烟草</t>
+          <t>风电, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>出海概念</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-0.7504000000000001</v>
+        <v>-1.9261</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>据商务部网站，9月20日至23日，中美经贸团队在美国纽约和华盛顿举行经贸磋商，取得积极共识，为两国元首会晤贡献了经贸领域的成果。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh603230</t>
+          <t>sz002640</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>跨境通</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>18.47</v>
+        <v>3.96</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.006</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>7天6板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>传媒+“华”字辈|公司的最终控制人为内蒙古自治区人民政府。公司主营业务是出版物的批发、零售；文体用品零售；音像制品发行</t>
+          <t>跨境电商|公司主营业务包括跨境出口电商业务、跨境进口电商业务两大类，跨境通助力中国优质产品通过电商渠道输出到海外市场，同时将海外的优质产品进口到中国市场。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>传媒, “华”字辈</t>
+          <t>跨境电商</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>出海概念</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-0.7504000000000001</v>
+        <v>-1.9261</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>据商务部网站，9月20日至23日，中美经贸团队在美国纽约和华盛顿举行经贸磋商，取得积极共识，为两国元首会晤贡献了经贸领域的成果。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sz001368</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>通达创智</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>20.35</v>
+        <v>41.8</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>5天5板</t>
-        </is>
-      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>并购重组+传媒|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
+          <t>AI玩具+出海概念|1.公司在AI玩具等产品方面进行了相应的研发投入，已自主研发出多模态AI玩具。
+2.公司从事体育户外、家居生活、健康护理等消费品的研发、生产和销售。公司2024年境外收入占比77.08%。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 传媒</t>
+          <t>AI玩具, 出海概念</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>新能源汽车</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-0.7504000000000001</v>
+        <v>-2.5211</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>车市进入全年最关键冲量期。9月以来，超50款新车密集上市，覆盖6万的代步小车到50万的旗舰车型。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sh600418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>江淮汽车</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>7.77</v>
+        <v>25.22</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.0567</v>
+        <v>9.9869</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>4天3板</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>并购重组+传媒|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
+          <t>汽车整车|公司是一家集全系列商用车、乘用车及动力总成等研产销和服务于一体,“先进节能汽车、新能源汽车、智能网联汽车”并举的综合型汽车企业集团。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 传媒</t>
+          <t>汽车整车</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>新能源汽车</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-0.7504000000000001</v>
+        <v>-2.5211</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>车市进入全年最关键冲量期。9月以来，超50款新车密集上市，覆盖6万的代步小车到50万的旗舰车型。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz002238</t>
+          <t>sz000980</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>天威视讯</t>
+          <t>众泰汽车</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>8.43</v>
+        <v>2.24</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.0522</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>9.803900000000001</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>传媒+算力|1.公司是深圳地区最主要的电视服务提供商，主要向用户提供有线数字业务（包括基本收视、增值业务）、互联网宽带接入服务、视频购物服务和政企项目服务。
-2.公司初步形成位于深圳市福田区、南山区、龙华区以及深汕合作区的3000个5-8KW 机柜规模的数据中心布局。</t>
+          <t>汽车整车|公司是国内较早进入新能源汽车领域的车企，已具备新能源汽车完整的整车设计、试制、试验和零部件开发能力。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>传媒, 算力</t>
+          <t>汽车整车</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>玻璃基板</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-0.7504000000000001</v>
+        <v>-2.9072</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，市场看到传媒行业从传统内容服务商向AI语料供给方转型的可能性，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>英伟达正在评估采用玻璃基板方案，并与德国设备商SCHMID等企业开展合作，希望韩国、日本及中国台湾地区基板厂商在两年内完成玻璃基板开发，最快于2028年前落地。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh600358</t>
+          <t>sh603396</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>国旅联合</t>
+          <t>金辰股份</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>5.72</v>
+        <v>39.2</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
+        <v>9.988800000000001</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>传媒+旅游|1.公司的主要业务包括互联网营销、个性化旅行综合服务业务、旅游目的地建设和运营业务，子公司新线中视、国联文化是互联网营销业务的经营主体。
-2.公司旅游业务围绕“目的地项目、合作资源圈、运营服务商”三方面的拓展，与地方政府、景区、企业围绕乡村振兴、主题乐园、旅游目的地的策划、规划、建设、运营展开深度合作，为旅游项目提供整体解决方案。</t>
+          <t>玻璃基板|公司拟设立全资子公司辰光微电半导体设备(南通)有限公司作为项目公司，注册资本1000万元，持股比例100%。项目将建设现代化厂房和高标准洁净室，搭建以TGV玻璃基封装为代表的半导体设备生产试验线，推动超快激光诱导改质设备等半导体专用设备的研发与制造验证。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>传媒, 旅游</t>
+          <t>玻璃基板</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>纺织服装</t>
+          <t>玻璃基板</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.5704</v>
+        <v>-2.9072</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>工业和信息化部、商务部、市场监管总局印发《轻工纺织产业发展“十五五”规划》。其中指出，发挥国家产融合作平台作用，引导金融机构为企业提供多元化融资服务，支持符合条件的重点行业企业上市融资。</t>
+          <t>英伟达正在评估采用玻璃基板方案，并与德国设备商SCHMID等企业开展合作，希望韩国、日本及中国台湾地区基板厂商在两年内完成玻璃基板开发，最快于2028年前落地。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz001234</t>
+          <t>sz002962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>泰慕士</t>
+          <t>五方光电</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>35.4</v>
+        <v>14.76</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.0062</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>9.985099999999999</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>纺织服装|公司主营业务为针织面料和针织服装的研发、生产和销售，主要为迪卡侬、森马服饰、蕉内、Quiksilver、佐丹奴、全棉时代、曼妮芬、安踏、波司登等知名服装品牌提供贴牌加工服务。</t>
+          <t>玻璃基板|公司具有玻璃通孔TGV技术能力及一定的产品交付能力。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>纺织服装</t>
+          <t>玻璃基板</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>纺织服装</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.5704</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>工业和信息化部、商务部、市场监管总局印发《轻工纺织产业发展“十五五”规划》。其中指出，发挥国家产融合作平台作用，引导金融机构为企业提供多元化融资服务，支持符合条件的重点行业企业上市融资。</t>
-        </is>
-      </c>
+        <v>-1.8786</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz000850</t>
+          <t>sz002082</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>华茂股份</t>
+          <t>ST万邦</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>5.12</v>
+        <v>13.2</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10.1075</v>
+        <v>10</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>纺织服装+“华”字辈|公司专注于棉、毛、麻、丝和人造纤维的纯、混纺纱线及其织物、针织品、服装、印染加工；纺织设备及配件、家用纺织品销售；投资管理。公司产品包括纱线系列产品，坯布面料系列产品、色织面料系列产品和功能性产业用布等。</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>纺织服装, “华”字辈</t>
-        </is>
-      </c>
+          <t xml:space="preserve">ST股 | 在研发端，公司探索人工智能在创新药设计、筛选、实验设计等环节的应用，目前全球首个治疗胃轻瘫的中药1.1类新药“理中消痞颗粒”正在开展临床研究。 </t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>纺织服装</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.5704</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>工业和信息化部、商务部、市场监管总局印发《轻工纺织产业发展“十五五”规划》。其中指出，发挥国家产融合作平台作用，引导金融机构为企业提供多元化融资服务，支持符合条件的重点行业企业上市融资。</t>
-        </is>
-      </c>
+        <v>-1.8786</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh600843</t>
+          <t>sh600340</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>上工申贝</t>
+          <t xml:space="preserve">*ST华幸 </t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>9.9869</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.2564</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>纺织机械|公司已经成长为一家占据全球缝制技术制高点并为客户量身定制工业4.0应用解决方案的专业设备供应商，主要产品有缝纫、绣花、裁切、焊接等缝制工艺设备，机器人焊接、组装生产线，程控机械加工流水线，以及智能仓储、自动传输装置等。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>纺织机械</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是中国领先的产业新城运营商，以“经济发展、社会和谐、人民幸福”的产业新城和产业小镇为核心产品。</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>纺织服装</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>0.5704</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>工业和信息化部、商务部、市场监管总局印发《轻工纺织产业发展“十五五”规划》。其中指出，发挥国家产融合作平台作用，引导金融机构为企业提供多元化融资服务，支持符合条件的重点行业企业上市融资。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz002029</t>
+          <t>sh600825</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>七 匹 狼</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>9.26</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>9.9762</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+        <v>10.0386</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5天5板</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>纺织+机器人|1.主要从事“七匹狼”品牌男装的设计、生产和销售,主要产品包括衬衫、西服、裤装、茄克衫、针织衫等。
-2.公司母公司间接持有摩尔线程和宇树科技的部分股权。</t>
+          <t>并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>纺织, 机器人</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>-1.9551</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Anthropic宣布成立生命科学研究团队及实验室，并公布Claude参与生物学研究取得的早期成果。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz002622</t>
+          <t>sh600802</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>皓宸医疗</t>
+          <t>福建水泥</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>2.72</v>
+        <v>7.28</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.1215</v>
+        <v>9.969799999999999</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>口腔医疗|公司购买德伦医疗51.00%股权。德伦医疗是一家以口腔医疗服务连锁经营为核心，专注于口腔疾病的诊断、治疗以及口腔保健、修复服务等口腔医疗服务的企业。</t>
+          <t>福建+水泥|公司主要从事水泥及熟料的生产及销售，拥有7条新型干法熟料水泥生产线，具备年产熟料784.3万吨、水泥1164万吨。公司是福建地区产能规模最大的水泥制造企业，也是福建省水泥行业唯一的一家上市公司。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>口腔医疗</t>
+          <t>福建, 水泥</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>-1.9551</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Anthropic宣布成立生命科学研究团队及实验室，并公布Claude参与生物学研究取得的早期成果。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz000710</t>
+          <t>sz001330</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>贝瑞基因</t>
+          <t>博纳影业</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>11.01</v>
+        <v>6.36</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.99</v>
+        <v>10.0346</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>基因测序+AI医疗|1.公司依托其具有自主知识产权的cSMART核心技术为支撑，选择ctDNA作为肿瘤液体活检指标，开启了临床无创肿瘤基因检测的全新模式。
-2.公司自主研发NLPearl遗传疾病人工智能临床决策支持系统、CNVisi智能报告解读系统，为科研和临床工作者提供智能决策支持。公司的CNVisi™利用人工智能深度学习算法，挖掘20+权威公共数据库、百万自有CNV大数据以及20多万份CNV-seq临床实践报告，构建7大临床解读知识库，精准注释解读、一键查询信息、自定义设置参数、AI智能撰写报告。</t>
+          <t>AI院线电影|9月27日，博纳影业宣布，首部AI超写实院线电影《三星堆：未来往事》正式定档2026年10月23日登陆全国院线。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>基因测序, AI医疗</t>
+          <t>AI院线电影</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>-1.9551</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Anthropic宣布成立生命科学研究团队及实验室，并公布Claude参与生物学研究取得的早期成果。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz000790</t>
+          <t>sh600032</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>华神科技</t>
+          <t>浙江新能</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>4.68</v>
+        <v>7.43</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.1176</v>
+        <v>10.0741</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>医药+“华”字辈|在合成生物领域，公司定位打造成为“中国合成生物行业技术及智能化生产的引领者，进入国内合成生物CDMO第一梯队”。</t>
+          <t>绿电|公司的主营业务为水力发电、光伏发电、风力发电等可再生能源项目的投资、开发、建设和运营管理。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>医药, “华”字辈</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>-1.9551</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Anthropic宣布成立生命科学研究团队及实验室，并公布Claude参与生物学研究取得的早期成果。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh603122</t>
+          <t>sh600241</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>合富中国</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>14.93</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.0221</v>
+        <v>9.9863</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>医药+海峡两岸|1.公司系医疗流通领域的渠道商，具备与境内外试剂耗材和医疗设备原厂、各大代理商及医疗机构长期互惠、合作共赢的核心竞争力。
-2.公司为唯一一家海峡两岸市场“双上市”的医疗企业，其母公司合富医疗控股在台湾上市，公司实际控制人为台湾企业家王琼芝，在两岸医疗流通领域有深度合作。</t>
+          <t>锂电池|公司旗下九夷锂能主要经营锂离子电池、电池组的研发、生产、制造、系统集成、销售和服务，目标市场定位于电动工具、个人护理、家庭电子、消费品等小动力领域</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>医药, 海峡两岸</t>
+          <t>锂电池</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>-0.9878</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>SpaceX据悉已停止接受2028年以后的猎鹰9号火箭预订。随着猎鹰9号退出市场，火箭发射运力或在2030年前出现供不应求的局面。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh603278</t>
+          <t>sz001201</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>东瑞股份</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>16.13</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>9.988800000000001</v>
+        <v>10.0273</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>商业航天+机器人|1.公司投资联营企业湖北三江航天江北机械工程有限公司金额为6405.04万。湖北三江航天江北机械工程有限公司主要从事航天动力系统、天线罩等航天型号产品及特种压力容器产品等民用产品的研发生产。
-2.公司关注到近期市场上公司还涉及“人形机器人概念股”相关内容。公司现有主营业务仍以胎圈钢丝、钢帘线以及胶管钢丝的研发、生产和销售为主，公司机器人腱绳产品目前尚未批量生产，未产生实质性收益，且公司相关业务未来在技术研发、产品竞争能力、盈利能力等方面存在重大不确定性。</t>
+          <t>猪肉产业|公司主营业务为生猪的养殖和销售，主要产品为商品猪、仔猪、种猪等。此外，公司自行生产生猪养殖所需的饲料，并有部分饲料对外销售。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>商业航天, 机器人</t>
+          <t>猪肉产业</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>-0.9878</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>SpaceX据悉已停止接受2028年以后的猎鹰9号火箭预订。随着猎鹰9号退出市场，火箭发射运力或在2030年前出现供不应求的局面。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh688682</t>
+          <t>sh600488</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">霍莱沃  </t>
+          <t>津药药业</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>37.94</v>
+        <v>6.27</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>19.9873</v>
+        <v>10</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>商业航天|公司的多探头测试+实时频谱分析系统、近场扫描技术可助力具备高密度集成特性的算力卫星解决多源电磁干扰问题，实现电磁兼容测试在宽频域、动态负载方面的双重突破。此外，霍莱沃可在算力卫星设计阶段提供EMC仿真的应对方案，对太空等离子体和空间静电放电累积效应进行仿真分析找出薄弱环节、采用专用的EMC设计技术进行全面优化防护，并对敏感设备进行抗干扰和ESD试验验证，从而在设计阶段最大程度解决可能存在的电磁兼容问题。</t>
+          <t>创新药|公司于2024年成立创新研究院，负责创新药设计发现、研发以及引进孵化工作，JYSW003项目为津药生物科技（天津）有限公司委托公司创新研究院开展的创新药项目，适应症是银屑病，前期探索性研究结果初步显示药效明显、安全性优等特点。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>-0.9878</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>SpaceX据悉已停止接受2028年以后的猎鹰9号火箭预订。随着猎鹰9号退出市场，火箭发射运力或在2030年前出现供不应求的局面。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz002413</t>
+          <t>sz002852</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>雷科防务</t>
+          <t>道道全</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>8.970000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.0613</v>
+        <v>10.0124</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">商业航天|子公司恒达微波研发的“微波应答机天线”产品应用于长征五号B遥二运载火箭中搭载的核心舱。
-</t>
+          <t>菜籽油|菜籽油龙头，湖南最大油脂加工企业。以包装菜籽油类产品为主，拥有三大生产基地：岳阳、南京、重庆，三大基地协同发展，逐步向全国拓展。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>菜籽油</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>-2.6211</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>多家机构预计，2026年全球磷化铟供需缺口超70%；国内所有厂商出货量仅占全球供应量约一成，产业链紧张局面持续向上下游传导。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh603042</t>
+          <t>sh601579</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>华脉科技</t>
+          <t xml:space="preserve">会稽山  </t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>18.73</v>
+        <v>41.84</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.9824</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>9.9895</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>光纤+“华”字辈|公司是一家信息通信网络基础设施解决方案提供商，主要产品包括光纤、光缆、光器件及光配线设施全场景有线传输链路解决方案及系列产品。</t>
+          <t>黄酒|公司主要从事黄酒的生产、销售和研发等业务，公司及下属子公司主要拥有“会稽山”、“西塘”、“乌毡帽”、“唐宋”等主品牌，主要生产会稽山纯正、会稽山1743、水香国色、帝聚堂、大师兰亭、西塘本酒、乌毡帽冻藏冰雕、绿水青山等系列黄酒产品。公司黄酒产品销售主要集中在浙江地区、江苏地区和上海市等黄酒的传统消费区域，并建立起了全国性的销售渠道，还远销日本、新加坡、港澳及欧美等多个国家和地区。公司作为全国运营历史最悠久的黄酒企业之一，位居黄酒行业前三位。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>光纤, “华”字辈</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>光通信</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>-2.6211</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>多家机构预计，2026年全球磷化铟供需缺口超70%；国内所有厂商出货量仅占全球供应量约一成，产业链紧张局面持续向上下游传导。</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>sz002395</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>双象股份</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>14.05</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>10.0235</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>光学级PMMA|双象股份2026年4月15日在投资者互动平台表示，公司光学级PMMA材料可应用于光学仪器、光学镜片等领域。</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>光学级PMMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>光通信</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>-2.6211</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>多家机构预计，2026年全球磷化铟供需缺口超70%；国内所有厂商出货量仅占全球供应量约一成，产业链紧张局面持续向上下游传导。</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>sh603065</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>宿迁联盛</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>10.0068</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>磷化铟|宿迁联盛公告称，公司与朱蓉辉、汇智光芯签署《合资意向协议》，拟共同出资1000万元设立合资公司，从事磷化铟衬底的研发生产销售。其中公司出资700万元，持股70%。项目计划分两期建设，一期固定投资1亿元，预期年产12万片4-6英寸磷化铟衬底；二期预计追加投资2亿元，产能扩充至40万片/年。本次投资尚需提交股东会审议，存在较大不确定性。</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>磷化铟</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>科学仪器</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>华泰证券研报指出，随着数据中心网络向800G、1.6T演进，高速连接器、线缆及高端PCB对信号完整性与良率管控的要求持续提高，带动VNA测试需求增长。</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>sz002819</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东方中科</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>26.66</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>9.983499999999999</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>VNA|旗下中科四点零已推出 VNA1009系列矢量网络分析仪，支持高精度S参数测量、多端口级联及大规模并行测试，直接面向产线量产环境。</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>VNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>科学仪器</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>华泰证券研报指出，随着数据中心网络向800G、1.6T演进，高速连接器、线缆及高端PCB对信号完整性与良率管控的要求持续提高，带动VNA测试需求增长。</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>sz301689</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>电科思仪</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>83.88</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>VNA|电科思仪是国内电子测量仪器领域领军企业，2026年9月10日科思仪申请矢量网络分析仪相关专利，提升多端口矢网测量效率，降本减误。</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>VNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>芯片产业链</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>-1.8366</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>国际半导体产业协会数据显示，2026年第二季度全球半导体设备销售额达405.3亿美元，同比增长23%、环比增长11%，连续两个季度刷新历史最高纪录，AI算力扩产带来的设备采购需求持续向上游传导。</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>sz002119</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康强电子</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>29.61</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>9.992599999999999</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>半导体封装材料|公司是一家专业从事各类半导体封装材料引线框架、键合丝等半导体封装材料的开发、生产、销售的高新技术企业，主要产品引线框架和键合丝国内市场规模处于领先地位，产品覆盖国内知名的半导体后封装企业。</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>半导体封装材料</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>芯片产业链</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>-1.8366</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>国际半导体产业协会数据显示，2026年第二季度全球半导体设备销售额达405.3亿美元，同比增长23%、环比增长11%，连续两个季度刷新历史最高纪录，AI算力扩产带来的设备采购需求持续向上游传导。</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>sh603375</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">盛景微  </t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>49.25</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>10.0067</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>模拟芯片|公司是一家具备高性能、超低功耗芯片设计能力的电子器件提供商，主要产品为工业安全领域的电子控制模块。公司销售的产品包括电子控制模块、起爆控制器、放大器等。</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>模拟芯片</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>风电</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>-0.1419</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>“十五五”期间，我国将加强海洋开发利用保护，预计到2030年，全国海洋生产总值将突破13万亿元，海上风电装机容量实现翻一番，达到1亿千瓦。</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>sh601218</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>吉鑫科技</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>风电|公司是一家专注于研发、制造和销售大型风力发电机组用零部件的龙头企业，主要生产750KW-12MW风力发电机组用轮毂、底座、轴、轴承座等系列产品。</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>风电</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>液冷IDC</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>-1.8716</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>浙商证券研报指出，第三季度是液冷行业从试点走向批量交付、业绩集中兑现的关键拐点，以英伟达VR200机柜规模化出货为核心驱动。</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>sz002909</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>集泰股份</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>9.946899999999999</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>PCB+液冷|1.公司PCB三防漆涵盖有机硅、UV等多个系列，主要用于PCB电路板及电子元器件表面防护，可应用于智能设备、汽车电子、消费电子、工业控制、通信设备等场景。
-2.公司当前研发的液冷导热硅油，其应用主要聚焦于数据中心及储能领域的热管理解决方案。</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>PCB, 液冷</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>sz002321</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>华英农业</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>10.1942</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>6天3板</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>鸭养殖+“华”字辈|主营业务为种鸭/鸡养殖、孵化、禽苗销售、饲料生产、商品鸭/鸡屠宰加工、冻品销售、熟食、羽绒及羽绒制品生产和销售。</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>鸭养殖, “华”字辈</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>sh603396</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>金辰股份</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>35.64</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>玻璃基板|公司拟设立全资子公司辰光微电半导体设备(南通)有限公司作为项目公司，注册资本1000万元，持股比例100%。项目将建设现代化厂房和高标准洁净室，搭建以TGV玻璃基封装为代表的半导体设备生产试验线，推动超快激光诱导改质设备等半导体专用设备的研发与制造验证。</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>玻璃基板</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>sh601567</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>三星电气</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>10.0203</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>签订数据中心项目|三星电气公告称，公司全资子公司奥克斯智能科技中标美国数据中心储能油变项目，合同金额总计1.32亿美元，约合8.85亿人民币，占公司2025年度经审计营收的6.16%。合同的履行将对公司经营业绩产生积极影响，是公司在美国配电业务数据中心领域的重要突破。</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>签订数据中心项目</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>sz000498</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>山东路桥</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>9.9222</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>控股股东增持|山东路桥公告称，公司控股股东高速集团及其一致行动人高速投资控股拟自公告披露之日起6个月内，以专项贷款和/或自有资金通过集中竞价方式增持公司股份，增持总金额不低于4.5亿元且不超过9亿元。其中，高速集团增持金额不低于3亿元且不超过6亿元，高速投资控股增持金额不低于1.5亿元且不超过3亿元。本次增持不设价格区间。</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>控股股东增持</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>sh600792</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>云煤能源</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>10.0386</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>焦炭|公司主要从事焦化业务，涉及焦炭及相关化工产品的生产和销售，主导产品为冶金焦炭。</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>焦炭</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>sz002836</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>新宏泽</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>10.0448</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>烟标印刷|公司系专业烟标印刷服务供应商，主营业务为烟标的设计、生产及销售。</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>烟标印刷</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>sh600189</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">泉阳泉  </t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>10.0363</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>矿泉水+谐音“羊”|公司主要从事长白山天然饮用矿泉水的生产和销售，旗下主要产品“泉阳泉”牌长白山天然矿泉水。</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>矿泉水, 谐音“羊”</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>sh603970</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>中农立华</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>10.0362</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>农药+“华”字辈|实际控制人为中国供销集团有限公司。公司主要业务包括农药流通服务业务、植保技术服务业务和植保机械供应业务三大类。</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>农药, “华”字辈</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr"/>
-      <c r="D53" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>sz002205</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>国统股份</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>12.78</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>9.982799999999999</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>建材|公司产品PCCP（预应力钢筒混凝土管）技术含量较高，规格齐全，公司积极推进产品结构及业务调整转型，通过PPP模式积极参与水务、地下综合管廊等市政基础设施的投资、建设、运营，培育新的利润增长点。</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>建材</t>
+          <t>黄酒</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3000,72 +2179,72 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sh600825</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sh600802</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>福建水泥</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz001234</t>
+          <t>sh603949</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>泰慕士</t>
+          <t>雪龙集团</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002614</t>
+          <t>sh603396</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>金辰股份</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz002238</t>
+          <t>sh603278</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>天威视讯</t>
+          <t>大业股份</t>
         </is>
       </c>
     </row>
@@ -3075,12 +2254,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh600802</t>
+          <t>sh601218</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>吉鑫科技</t>
         </is>
       </c>
     </row>
@@ -3090,102 +2269,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sz000850</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>华茂股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>sh603949</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>雪龙集团</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>sz002119</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>康强电子</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>sh600843</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>上工申贝</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>sz002819</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>东方中科</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>sz002909</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>集泰股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>sh603396</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>金辰股份</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="99" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="240" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="287" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,868 +552,863 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-2.7261</v>
+        <v>2.2382</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>据报道，特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh603949</t>
+          <t>sh603200</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>18.59</v>
+        <v>40.67</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.0081</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司作为有限合伙人通过深创投中小企业发展基金（新疆）有限合伙企业间接持股杭州宇树科技有限公司。目前，深创投中小企业发展基金（新疆）有限合伙企业对杭州宇树科技有限公司的持股比例为1.3546%；公司对深创投中小企业发展基金（新疆）有限合伙企业的持股比例为0.7239%。</t>
+          <t>固态电池+液冷|1.公司生产的固态电解质粉体材料可以应用于锂离子固态电池，多形态固态电解质粉体材料（含油性、水性、浆料）年产50吨级产线主要采用的是氧化物技术路线，公司储备了硫化物、氯化物等固态电解质的其它固态电解质粉体技术路线。
+2.公司面向腾讯、华为、中国移动等重点客户数据中心提供循环水/空气蒸发冷却等专业服务。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>固态电池, 液冷</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-2.7261</v>
+        <v>2.2382</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>据报道，特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sz002866</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>传艺科技</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>10.65</v>
+        <v>15.36</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.0207</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0287</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
+          <t>固态电池+PCB|1.公司的半固态、固态电池处于研发阶段。
+2.公司专注于为行业领先客户提供全方位FPC产品及服务，根据下游不同终端产品对于FPC的定制化要求，为客户提供涵盖产品设计、研发和销售各个环节的整体解决方案。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>固态电池, PCB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-2.7261</v>
+        <v>2.2382</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>据报道，特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh603278</t>
+          <t>sz301513</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>尚水智能</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>10.78</v>
+        <v>51.42</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>商业航天+机器人|1.公司投资联营企业湖北三江航天江北机械工程有限公司金额为6405.04万。湖北三江航天江北机械工程有限公司主要从事航天动力系统、天线罩等航天型号产品及特种压力容器产品等民用产品的研发生产。
-2.公司关注到近期市场上公司还涉及“人形机器人概念股”相关内容。公司现有主营业务仍以胎圈钢丝、钢帘线以及胶管钢丝的研发、生产和销售为主，公司机器人腱绳产品目前尚未批量生产，未产生实质性收益，且公司相关业务未来在技术研发、产品竞争能力、盈利能力等方面存在重大不确定性。</t>
+          <t>次新+固态电池|公司半干法、干法极片制造设备已小批量交付中科院物理研究所、比亚迪、因湃电池等客户，用于液态锂离子电池及半固态、固态电池的研发制造和生产测试。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>商业航天, 机器人</t>
+          <t>次新, 固态电池</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-2.7261</v>
+        <v>2.2382</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>据报道，特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz002242</t>
+          <t>sz002074</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>10.33</v>
+        <v>28.68</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.0106</v>
+        <v>10.0115</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司持有深思考人工智能机器人科技（北京）有限公司7.92%的股份，旗下产品包括AI机器人。</t>
+          <t>固态电池|公司已成功研发出车规级全固态电池“金石电池”，这款30Ah的硫化物全固态电池采用了微纳化固体电解质、超薄膜包覆单晶正极和三维介孔硅负极材料技术。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>固态电池</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-2.7261</v>
+        <v>2.2382</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>据报道，特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz002347</t>
+          <t>sz002882</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>泰尔股份</t>
+          <t>金龙羽</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>6.42</v>
+        <v>24.51</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9.9315</v>
+        <v>10.009</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>机器人+商业航天|1.2021年8月5日公司在互动平台表示，公司子公司燊泰智能的高线包装机器人市场占有率约42.4%。
-2.公司的激光技术、粉末材料可以应用于航空航天。</t>
+          <t>固态电池|公司确定了多种电解质体系的应用方案和全固态电解质材料合成工艺路线，开发了低成本干法工艺制备的电解质产品，氧化物电解质产品已完成多家客户送样及评测。电芯方面，半固态电池性能已满足国标要求，并通过第三方检测机构的国标检测和安全测试。
+2026年1月12日公告，子公司金龙羽新能源（深圳）有限公司拟在深圳大鹏新区投资建设年产2GWh固态电池量产线项目，项目总投资约12亿元。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>机器人, 商业航天</t>
+          <t>固态电池</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-2.7261</v>
+        <v>2.2382</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>据报道，特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz002480</t>
+          <t>sz002058</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>新筑股份</t>
+          <t>紫竹高科</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>5.65</v>
+        <v>18.36</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9.9222</v>
+        <v>10.006</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>机器人+并购重组|1.参股奥威科技参与研发的移动充电机器人目前处于对样机进行调试的阶段。
-2.9月23日晚间，新筑股份披露，拟以56.03亿元收购蜀道集团旗下四川蜀道清洁能源集团有限公司60%股权，同时出售磁浮及桥梁功能部件业务相关资产。</t>
+          <t>固态电池|旗下紫江新材专注铝塑膜产品的研发，同时积极布局固态电池用铝塑膜产品，以适应未来固态电池行业发展带动的新增需求。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>机器人, 并购重组</t>
+          <t>固态电池</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-1.4294</v>
+        <v>2.2382</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>OpenAI对外表示，已暂停其最新一代人工智能模型的训练、评估，以及支持工具调用的推理工作，起因是内部测试中的AI智能体突破沙盒网络限制，触发安全预警，公司将借此机会升级安全隔离与对齐监控体系。</t>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz002912</t>
+          <t>sz002846</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>英联股份</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>26.47</v>
+        <v>11.88</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.0166</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>AI+网络安全|公司推出的小赛安全智脑产品，支持多模型底座，基于智能体、RAG等技术，包含渗透测试智能体、事件调查智能体、代码安全审计智能体，也配备了敏感数据识别、智能解码、安全知识问答等多种智能体应用，全方位满足安全运维场景下的各类用户需求，为企业数据与网络安全保驾护航。</t>
+          <t>固态电池|公司的复合铝箔、复合铜箔可以应用于固态电池。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>AI, 网络安全</t>
+          <t>固态电池</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-1.4294</v>
+        <v>2.2382</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>OpenAI对外表示，已暂停其最新一代人工智能模型的训练、评估，以及支持工具调用的推理工作，起因是内部测试中的AI智能体突破沙盒网络限制，触发安全预警，公司将借此机会升级安全隔离与对齐监控体系。</t>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh688244</t>
+          <t>920779.BJ</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>永信至诚</t>
+          <t>武汉蓝电</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>19.8</v>
+        <v>28.4</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>20</v>
+        <v>29.9771</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>AI+网络安全|在人工智能领域，公司网络靶场系列产品和“数字风洞”产品体系均是人工智能安全测试评估的基础设施平台，具备对人工智能相关产品和风险进行安全测试评估的能力。</t>
+          <t>固态电池测试|公司专注电池测试系统的开发、生产和销售，为二次电池（包括固态电池）提供专业检测服务。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>AI, 网络安全</t>
+          <t>固态电池测试</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-1.4294</v>
+        <v>2.0596</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>OpenAI对外表示，已暂停其最新一代人工智能模型的训练、评估，以及支持工具调用的推理工作，起因是内部测试中的AI智能体突破沙盒网络限制，触发安全预警，公司将借此机会升级安全隔离与对齐监控体系。</t>
+          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz002232</t>
+          <t>sh605058</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>启明信息</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>16.28</v>
+        <v>59.6</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+        <v>10.0037</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12天8板</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>网络安全|子公司长春启明信息集成服务技术有限公司主要开展网络安全等级保护定级协助、等级保护建设咨询、等级保护方案设计、等级保护测评、等级保护培训、信息安全风险评估、安全运维服务以及应急响应等安全服务业务，是从事专业化的信息安全服务提供商。</t>
+          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-2.406</v>
+        <v>2.0596</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>据百川盈孚报价，2026年9月1日以来，分散染料价格一直维持在30元/千克的高位，相比6月22日的23元/千克上涨7元/千克，2个多月的时间价格上涨超30%。</t>
+          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz301190</t>
+          <t>sh603328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>善水科技</t>
+          <t>依顿电子</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>24.95</v>
+        <v>14.44</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>20.0096</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
+        <v>9.9772</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>染料+农药+医药|公司主要经营染料中间体、农药和医药中间体的研发、生产和销售业务。公司生产的染料中间体包括6-硝体、氧体、5-硝体和邻氨基苯磺酸。</t>
+          <t>PCB|公司专注于高精度、高密度双层及多层印制电路板的研发、生产和销售业务，作为首批进入国际大厂汽车PCB核心供应链的PCB厂商，公司PCB产品供货覆盖传统汽车零部件。
+2026年8月6日公告，公司拟使用自有资金及自筹资金投资建设高端印制电路板智能制造项目，计划总投资29.79亿元。投资项目主要围绕市场高端印制电路板需求，建设高端高速高多层PCB智能制造项目。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>染料, 农药, 医药</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-2.406</v>
+        <v>2.0596</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>据百川盈孚报价，2026年9月1日以来，分散染料价格一直维持在30元/千克的高位，相比6月22日的23元/千克上涨7元/千克，2个多月的时间价格上涨超30%。</t>
+          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh605366</t>
+          <t>sz002913</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>宏柏新材</t>
+          <t>奥士康</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>10.14</v>
+        <v>91.08</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>9.978299999999999</v>
+        <v>10</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>有机硅+光纤上游|1.公司主营业务为功能性硅烷、纳米硅材料等硅基新材料及其他化学助剂的研发、生产与销售。
-2.公司重点布局2万吨光纤级高纯四氯化硅和5000吨电子级正硅酸乙酯等新兴产业项目，以满足下游光纤及电子半导体产业需求。</t>
+          <t>PCB|公司是一家集研发、生产、销售于一体的PCB领军企业，核心业务是研发、生产和销售高精密印制电路板，主要产品为单/双面板、高多层板、HDI板等，主要应用于数据中心及服务器、AIPC、通信及网络设备、汽车电子等领域。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>有机硅, 光纤上游</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-2.406</v>
+        <v>2.0596</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>据百川盈孚报价，2026年9月1日以来，分散染料价格一直维持在30元/千克的高位，相比6月22日的23元/千克上涨7元/千克，2个多月的时间价格上涨超30%。</t>
+          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603968</t>
+          <t>sz000823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>醋化股份</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>11.63</v>
+        <v>24.4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.0284</v>
+        <v>10.009</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>染料|公司的双乙甲酯产品涉及分散染料领域。</t>
+          <t>PCB|公司具备不同的印制板生产线，可接单跨度大，产能覆盖HDI板、任意层互连、高密度多层板以及快板业务。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>染料</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.8985</v>
+        <v>2.0596</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>浙商证券表示，AI制药已从“算法叙事”进入“临床兑现”阶段，而药物研发迭代的限速步骤在湿实验，AI提效将催生更强烈的分子验证需求。</t>
+          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz000513</t>
+          <t>sh688655</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>丽珠集团</t>
+          <t xml:space="preserve">迅捷兴  </t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30.34</v>
+        <v>75.7</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.0073</v>
+        <v>20.0063</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>创新药+AI医疗|1.公司已根据技术成熟度和市场需求优化研发管线布局，聚焦消化道、精神神经、代谢、抗感染等重点领域的创新药、高壁垒复杂制剂及高临床价值产品研发。
-2.公司于2024年初布局自有云端算力，将AI战略融入研发全局。目前AI应用已覆盖研发、生产、销售及职能全链条，并在研发链条中由后端向前端系统推进，在靶点发现、工艺优化、临床决策等关键环节已取得初步成效，为创新加速提供新动能。</t>
+          <t>PCB|公司主营业务为印制电路板（PCB）的研发、生产与销售，公司在光模块领域已积累了相关产品经验和客户，目前已可批量接单。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>创新药, AI医疗</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-0.8985</v>
+        <v>2.0596</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>浙商证券表示，AI制药已从“算法叙事”进入“临床兑现”阶段，而药物研发迭代的限速步骤在湿实验，AI提效将催生更强烈的分子验证需求。</t>
+          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz000503</t>
+          <t>sz002815</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>国新健康</t>
+          <t>崇达技术</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>7.44</v>
+        <v>24.44</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.0592</v>
+        <v>9.991</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>AI医疗|公司在"三医协同"领域深耕多年，结合国家和行业标准，通过构建完整的医保、医疗、医药的专业知识体系，如专业的"四库二十四系统"知识体系，并运用人工智能、大数据等先进科技手段，逐渐形成了业内独特的行业竞争力。</t>
+          <t>PCB+服务器|1.主营业务为印制电路板的生产和销售；主要产品为小批量印制电路板,产品类型覆盖HDI板、背板、厚铜板等。
+2.公司服务器产品客户是中兴通讯、新华三、云尖等，产品包括服务器主板和AI服务器。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>PCB, 服务器</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.9787</v>
+        <v>2.0596</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>根据中指研究院监测数据显示，截至9月24日，全国共出台房地产相关政策超870条，其中三季度全国出台房地产相关政策超280条，延续上半年政策高频落地趋势。</t>
+          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz000011</t>
+          <t>sh605258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>协和电子</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>10.12</v>
+        <v>44.01</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10</v>
+        <v>9.997499999999999</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>房地产|公司经过多年发展，已形成了以房地产开发为主业，物业管理、物业租赁、出租汽车营运、餐饮服务、物流仓储、工程监理等为辅的跨行业、多元化的经营格局。</t>
+          <t>PCB|公司主要从事印制电路板的研发、生产、销售以及SMT业务，PCB产品主要应用在汽车电子和高频通讯领域。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.9787</v>
+        <v>2.0596</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>根据中指研究院监测数据显示，截至9月24日，全国共出台房地产相关政策超870条，其中三季度全国出台房地产相关政策超280条，延续上半年政策高频落地趋势。</t>
+          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz000020</t>
+          <t>sh605198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>深华发Ａ</t>
+          <t xml:space="preserve">安德利  </t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>14.64</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.9925</v>
+        <v>9.9983</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>房地产|公司在深圳市福田区华强北商圈及光明新区公明街道均拥有数万平方米的大型物业。</t>
+          <t>PCB|安德利公告称，公司签署股权转让框架协议，公司拟以自有或自筹资金的方式收购宁波甬强科技有限公司（简称“甬强科技”）股东JIANGQI HE、QIANG YUAN、宁波源路载科技合伙企业（有限合伙）的部分股权。甬强科技主要产品为电子信息互连材料，包括覆铜板和半固化片。电子信息互连材料是制作印制电路板的核心材料。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1.3038</v>
+        <v>2.6502</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>浙江省海洋经济发展厅近日发布《浙江省海洋清洁能源产业发展指引》，《指引》提出，到2030年，全省海洋清洁能源及其装备产业规模突破3000亿元，海上风电装机超1000万千瓦。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，版权、优质文本数据的商业价值被重新评估。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh601218</t>
+          <t>sh600825</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>6.05</v>
+        <v>9.41</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10</v>
+        <v>10.0585</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>6天6板</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>风电|公司是一家专注于研发、制造和销售大型风力发电机组用零部件的龙头企业，主要生产750KW-12MW风力发电机组用轮毂、底座、轴、轴承座等系列产品。</t>
+          <t>传媒+并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>传媒, 并购重组</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-1.3038</v>
+        <v>2.6502</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>浙江省海洋经济发展厅近日发布《浙江省海洋清洁能源产业发展指引》，《指引》提出，到2030年，全省海洋清洁能源及其装备产业规模突破3000亿元，海上风电装机超1000万千瓦。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，版权、优质文本数据的商业价值被重新评估。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz002342</t>
+          <t>sh601811</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>巨力索具</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>8.68</v>
+        <v>20.37</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10.0127</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
+        <v>9.9892</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7天6板</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>风电+商业航天|1.公司新研制产品的应用与参与的项目包括全角度海上风电单叶片专用吊具、用于全球首台抗台风型深远海漂浮式海上风机的永久系泊索，以及参与建设的白鹤滩水电站、核电站等项目。
-2.公司为神舟十九号发射任务提供了火箭转运索具、总装索具、火箭分离索具等。</t>
+          <t>传媒+并购重组|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>风电, 商业航天</t>
+          <t>传媒, 并购重组</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>出海概念</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-1.9261</v>
+        <v>2.6502</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>据商务部网站，9月20日至23日，中美经贸团队在美国纽约和华盛顿举行经贸磋商，取得积极共识，为两国元首会晤贡献了经贸领域的成果。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，版权、优质文本数据的商业价值被重新评估。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz002640</t>
+          <t>sh603533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>跨境通</t>
+          <t>掌阅科技</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>3.96</v>
+        <v>23.65</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>10</v>
@@ -1421,719 +1416,1759 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>跨境电商|公司主营业务包括跨境出口电商业务、跨境进口电商业务两大类，跨境通助力中国优质产品通过电商渠道输出到海外市场，同时将海外的优质产品进口到中国市场。</t>
+          <t>传媒+AI|在数字阅读领域，掌阅APP现有书童导读、速览群书、书籍摘要、一键速读、逐句精读、思维导图等AI辅助阅读功能基础上，继续推出“AI讲书电台”，通过双人虚拟角色对话的创新形式，构建更具沉浸感和多元表达力的智能听书体验，为用户在不同阅读阶段提供陪伴式、交互式的内容服务。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>跨境电商</t>
+          <t>传媒, AI</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>出海概念</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-1.9261</v>
+        <v>2.6502</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>据商务部网站，9月20日至23日，中美经贸团队在美国纽约和华盛顿举行经贸磋商，取得积极共识，为两国元首会晤贡献了经贸领域的成果。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，版权、优质文本数据的商业价值被重新评估。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz001368</t>
+          <t>sz000607</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>通达创智</t>
+          <t>华媒控股</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>41.8</v>
+        <v>4.13</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10</v>
+        <v>10.1333</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>AI玩具+出海概念|1.公司在AI玩具等产品方面进行了相应的研发投入，已自主研发出多模态AI玩具。
-2.公司从事体育户外、家居生活、健康护理等消费品的研发、生产和销售。公司2024年境外收入占比77.08%。</t>
+          <t>传媒+AI|1.公司主要从事广告策划发布、报刊发行与印刷、教育等业务，涵盖平面媒体、网络媒体、移动新媒体、户外 媒体包括地铁媒体的广告承揽发布、企事业单位宣传公关的全案策划和实施。
+2.公司控股子公司中教未来的业务板块之一是IT教育。旗下部分幼儿园引进AI智能机器人，培养人机协同的兴趣和科学探索精神，以便适应AI智能对孩子学习的辅助作用。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>AI玩具, 出海概念</t>
+          <t>传媒, AI</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-2.5211</v>
+        <v>2.6502</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>车市进入全年最关键冲量期。9月以来，超50款新车密集上市，覆盖6万的代步小车到50万的旗舰车型。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，版权、优质文本数据的商业价值被重新评估。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh600418</t>
+          <t>sh603598</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>江淮汽车</t>
+          <t>引力传媒</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>25.22</v>
+        <v>19.13</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.9869</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>10.0058</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>汽车整车|公司是一家集全系列商用车、乘用车及动力总成等研产销和服务于一体,“先进节能汽车、新能源汽车、智能网联汽车”并举的综合型汽车企业集团。</t>
+          <t>传媒+AI|1.公司是一家以内容创意与科技创新驱动的卓越数字商业服务公司。
+2.公司已推出自有营销电商行业模型并推出三大智能体（Agent）-感知智能体、决策智能体、内容智能体，用以增强营销决策、创意素材、视频混剪等环节内容产出的精准性与稳定性。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>汽车整车</t>
+          <t>传媒, AI</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-2.5211</v>
+        <v>2.6502</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>车市进入全年最关键冲量期。9月以来，超50款新车密集上市，覆盖6万的代步小车到50万的旗舰车型。</t>
+          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，版权、优质文本数据的商业价值被重新评估。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz000980</t>
+          <t>sh601949</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>众泰汽车</t>
+          <t>中国出版</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>2.24</v>
+        <v>6.01</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9.803900000000001</v>
+        <v>10.0733</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>汽车整车|公司是国内较早进入新能源汽车领域的车企，已具备新能源汽车完整的整车设计、试制、试验和零部件开发能力。</t>
+          <t>AI+传媒|1.公司推动“文化+科技”业态创新，中华古籍大模型建设初步完成，东方“多AI平台协同工作流”提升视频生产效率。
+2.公司是以图书、报纸、期刊等出版物出版为主业，是集出版、发行、物资供应、印刷等业务于一体的大型出版企业，拥有丰富的作者、译者、内容资源。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>汽车整车</t>
+          <t>AI, 传媒</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-2.9072</v>
+        <v>3.1164</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>英伟达正在评估采用玻璃基板方案，并与德国设备商SCHMID等企业开展合作，希望韩国、日本及中国台湾地区基板厂商在两年内完成玻璃基板开发，最快于2028年前落地。</t>
+          <t>国务院常务会议9月28日召开，会议指出推出一批务实管用的增量政策，研究出台稳定房地产市场、促进就业增收等政策措施。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh603396</t>
+          <t>sz000011</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>金辰股份</t>
+          <t>深物业A</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>39.2</v>
+        <v>11.13</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.988800000000001</v>
+        <v>9.9802</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板|公司拟设立全资子公司辰光微电半导体设备(南通)有限公司作为项目公司，注册资本1000万元，持股比例100%。项目将建设现代化厂房和高标准洁净室，搭建以TGV玻璃基封装为代表的半导体设备生产试验线，推动超快激光诱导改质设备等半导体专用设备的研发与制造验证。</t>
+          <t>房地产|公司经过多年发展，已形成了以房地产开发为主业，物业管理、物业租赁、出租汽车营运、餐饮服务、物流仓储、工程监理等为辅的跨行业、多元化的经营格局。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>房地产</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-2.9072</v>
+        <v>3.1164</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>英伟达正在评估采用玻璃基板方案，并与德国设备商SCHMID等企业开展合作，希望韩国、日本及中国台湾地区基板厂商在两年内完成玻璃基板开发，最快于2028年前落地。</t>
+          <t>国务院常务会议9月28日召开，会议指出推出一批务实管用的增量政策，研究出台稳定房地产市场、促进就业增收等政策措施。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz002962</t>
+          <t>sh600657</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>五方光电</t>
+          <t>信达地产</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>14.76</v>
+        <v>3.38</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>9.985099999999999</v>
+        <v>10.0977</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板|公司具有玻璃通孔TGV技术能力及一定的产品交付能力。</t>
+          <t>房地产|中国信达资产管理股份有限公司旗下上市公司，中国信达房地产开发业务运作平台。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>房地产</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-1.8786</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
+        <v>3.1164</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>国务院常务会议9月28日召开，会议指出推出一批务实管用的增量政策，研究出台稳定房地产市场、促进就业增收等政策措施。</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz002082</t>
+          <t>sz002244</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>ST万邦</t>
+          <t>滨江集团</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>13.2</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ST股 | 在研发端，公司探索人工智能在创新药设计、筛选、实验设计等环节的应用，目前全球首个治疗胃轻瘫的中药1.1类新药“理中消痞颗粒”正在开展临床研究。 </t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t>房地产|公司具有建设部一级开发资质，全国民营企业500强，中国房地产企业50强，长三角房地产领军企业。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-1.8786</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr"/>
+        <v>3.1164</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>国务院常务会议9月28日召开，会议指出推出一批务实管用的增量政策，研究出台稳定房地产市场、促进就业增收等政策措施。</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh600340</t>
+          <t>sz000002</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST华幸 </t>
+          <t>万  科Ａ</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>1.29</v>
+        <v>4.08</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10.2564</v>
+        <v>9.973000000000001</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司是中国领先的产业新城运营商，以“经济发展、社会和谐、人民幸福”的产业新城和产业小镇为核心产品。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
+          <t>房地产|本集团的主营业务包括房地产开发和物业服务，本集团将自身定位进一步迭代升级为“城乡建设与生活服务商”。</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
+          <t>房地产概念</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>3.1164</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>国务院常务会议9月28日召开，会议指出推出一批务实管用的增量政策，研究出台稳定房地产市场、促进就业增收等政策措施。</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sh600325</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>华发股份</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>8.550000000000001</v>
+        <v>2.95</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10.0386</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>5天5板</t>
-        </is>
-      </c>
+        <v>10.0746</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
+          <t>房地产|公司主营业务为房地产开发与经营，拥有房地产一级开发资质。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>房地产</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr"/>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>工业和信息化部、国家发展改革委、交通运输部等七部门联合制定的《新型电池产业发展“十五五”规划》，《规划》提出，培优育强新型电池领域龙头企业，支持企业兼并重组。</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh600802</t>
+          <t>sh600241</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>7.28</v>
+        <v>8.84</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>9.969799999999999</v>
+        <v>9.950199999999999</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>福建+水泥|公司主要从事水泥及熟料的生产及销售，拥有7条新型干法熟料水泥生产线，具备年产熟料784.3万吨、水泥1164万吨。公司是福建地区产能规模最大的水泥制造企业，也是福建省水泥行业唯一的一家上市公司。</t>
+          <t>锂电池|公司旗下九夷锂能主要经营锂离子电池、电池组的研发、生产、制造、系统集成、销售和服务，目标市场定位于电动工具、个人护理、家庭电子、消费品等小动力领域。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>福建, 水泥</t>
+          <t>锂电池</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>工业和信息化部、国家发展改革委、交通运输部等七部门联合制定的《新型电池产业发展“十五五”规划》，《规划》提出，培优育强新型电池领域龙头企业，支持企业兼并重组。</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz001330</t>
+          <t>sz000036</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>华联控股</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>6.36</v>
+        <v>4.21</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.0346</v>
+        <v>9.9217</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>AI院线电影|9月27日，博纳影业宣布，首部AI超写实院线电影《三星堆：未来往事》正式定档2026年10月23日登陆全国院线。</t>
+          <t>房地产+盐湖提锂|1.公司主营业务为房地产开发和自有物业租赁管理业务。公司目前房地产开发业务主要集中在深圳、杭州、千岛湖等城市，物业资产及物业经营管理业务主要集中深圳、杭州、上海、千岛湖等区域。
+2.华联控股公告称，公司拟以自有或自筹资金约1.75亿美元（折合人民币12.35亿元）受让Lithium Chile Inc.和Steve Cochrane合计持有的Argentum Lithium S.A.100%股份，从而获得Arizaro项目80%的权益。同日，公司与交易对方签署了《股份购买协议》。标的公司未来的主要收入来源于盐湖提锂业务，其主要产品为电池级碳酸锂。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>AI院线电影</t>
+          <t>房地产, 盐湖提锂</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>工业和信息化部、国家发展改革委、交通运输部等七部门联合制定的《新型电池产业发展“十五五”规划》，《规划》提出，培优育强新型电池领域龙头企业，支持企业兼并重组。</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh600032</t>
+          <t>sz000068</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>浙江新能</t>
+          <t>华控赛格</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>7.43</v>
+        <v>3.54</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.0741</v>
+        <v>9.937899999999999</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司的主营业务为水力发电、光伏发电、风力发电等可再生能源项目的投资、开发、建设和运营管理。</t>
+          <t>电池负极材料|公司旗下奥原新材料主要从事石墨化深加工业务，锂离子电池负极材料产能约为6000吨/年。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>电池负极材料</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>工业和信息化部、国家发展改革委、交通运输部等七部门联合制定的《新型电池产业发展“十五五”规划》，《规划》提出，培优育强新型电池领域龙头企业，支持企业兼并重组。</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh600241</t>
+          <t>sh600152</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>维科技术</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>9.9863</v>
+        <v>10.0529</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>锂电池|公司旗下九夷锂能主要经营锂离子电池、电池组的研发、生产、制造、系统集成、销售和服务，目标市场定位于电动工具、个人护理、家庭电子、消费品等小动力领域</t>
+          <t>锂电池+钠电池|1.维科技术公告称，公司拟投资建设年产1300万只多极耳高倍率电池智能化改造项目，项目总投资7342万元，子公司江西维乐电池有限公司为项目的实施主体。该项目产品为聚合物软包电芯，主要应用于智能家居、无人机等智能硬件与消费电子领域。
+2.2022年9月9日，维科技术股份有限公司与浙江钠创新能源有限公司在浙江绍兴签订《深度合作战略框架协议》。协议约定，双方将深化钠电研发合作，共享各自在钠离子电池研发的技术积累，联合申报政府重大科研项目，共同参与钠离子电池相关行业标准和规范文件的制订。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>锂电池, 钠电池</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
+          <t>算力工程</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1.2997</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁商Nebius计划自10月1日起上调主要英伟达GPU按需租金，整体涨幅约17%至21%。</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz001201</t>
+          <t>sh603636</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>东瑞股份</t>
+          <t>南威软件</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>16.13</v>
+        <v>7.87</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10.0273</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
+        <v>10.0699</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>6天4板</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>猪肉产业|公司主营业务为生猪的养殖和销售，主要产品为商品猪、仔猪、种猪等。此外，公司自行生产生猪养殖所需的饲料，并有部分饲料对外销售。</t>
+          <t>算力+AI智能体|1.公司于2024年4月获得北京市发展和改革委员会批准，建设2300PFlops算力的“北京七星园数字经济产业智算中心”，用于服务企业人工智能发展、政府公共算力及企业算力需求。
+2.公司已发布AI智能体服务平台“白泽启元”、政务公文写作与协同平台“白泽文墨”、智能体客服平台“白泽对话管理”以及智能体BI产品“白泽云图”等白泽系列四款大模型智能体产品。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>猪肉产业</t>
+          <t>算力, AI智能体</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
+          <t>算力工程</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>1.2997</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁商Nebius计划自10月1日起上调主要英伟达GPU按需租金，整体涨幅约17%至21%。</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh600488</t>
+          <t>sh688685</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t xml:space="preserve">迈信林  </t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6.27</v>
+        <v>39.7</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10</v>
+        <v>20.0121</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司于2024年成立创新研究院，负责创新药设计发现、研发以及引进孵化工作，JYSW003项目为津药生物科技（天津）有限公司委托公司创新研究院开展的创新药项目，适应症是银屑病，前期探索性研究结果初步显示药效明显、安全性优等特点。</t>
+          <t>光通信+算力租赁|1.2023年11月21日公司在机构调研中透露，3um设备用在400GHz和800GHz光模块封装，目前已有多家客户通过测试。
+2.公司于2024年1月26日成立控股子公司瑞盈科技，公司持股51%，子公司独立打造算力服务平台。公司计划于2024年度共计采购500台算力服务器。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>光通信, 算力租赁</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr"/>
+          <t>算力工程</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1.2997</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁商Nebius计划自10月1日起上调主要英伟达GPU按需租金，整体涨幅约17%至21%。</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz002852</t>
+          <t>sh603322</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>道道全</t>
+          <t>超讯科技</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>8.9</v>
+        <v>29.1</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.0124</v>
+        <v>10.0189</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>菜籽油|菜籽油龙头，湖南最大油脂加工企业。以包装菜籽油类产品为主，拥有三大生产基地：岳阳、南京、重庆，三大基地协同发展，逐步向全国拓展。</t>
+          <t>算力租赁|公司作为沐曦GPU的行业总代理，把握千卡级算力集群的市场机遇，实现批量GPU算力卡的高效销售与交付；同时，大力发展算力建设与租赁服务，构筑了以大湾区广州白云区为起点，长三角江苏淮安、西北甘肃庆阳为重要支点，覆盖华南、中部、西北三大区域的“超讯算力网“。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>菜籽油</t>
+          <t>算力租赁</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr"/>
+          <t>算力工程</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>1.2997</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>算力租赁商Nebius计划自10月1日起上调主要英伟达GPU按需租金，整体涨幅约17%至21%。</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh601579</t>
+          <t>sh603602</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">会稽山  </t>
+          <t>纵横通信</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>41.84</v>
+        <v>12.71</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.9895</v>
+        <v>10.0433</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>黄酒|公司主要从事黄酒的生产、销售和研发等业务，公司及下属子公司主要拥有“会稽山”、“西塘”、“乌毡帽”、“唐宋”等主品牌，主要生产会稽山纯正、会稽山1743、水香国色、帝聚堂、大师兰亭、西塘本酒、乌毡帽冻藏冰雕、绿水青山等系列黄酒产品。公司黄酒产品销售主要集中在浙江地区、江苏地区和上海市等黄酒的传统消费区域，并建立起了全国性的销售渠道，还远销日本、新加坡、港澳及欧美等多个国家和地区。公司作为全国运营历史最悠久的黄酒企业之一，位居黄酒行业前三位。</t>
+          <t>AI应用+算力租赁|1.公司在全域数字营销业务中已应用AI技术，主要体现在： 1、AI作为生产工具，公司运用AI能力优化流量复用和用户标签分析，提升投放效率。
+2.旗下纵横智算聚焦算力资源整合、租赁及组网运营，目标为政企客户提供一站式算力服务。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>黄酒</t>
+          <t>AI应用, 算力租赁</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1.3536</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>当前AI应用正由浅层生成提效向深层商业结果加速渗透：74%的广告主已应用AI生成内容，62%用于投放管理。</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>sz002912</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>中新赛克</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>10.0113</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>AI+网络安全|公司推出的小赛安全智脑产品，支持多模型底座，基于智能体、RAG等技术，包含渗透测试智能体、事件调查智能体、代码安全审计智能体，也配备了敏感数据识别、智能解码、安全知识问答等多种智能体应用，全方位满足安全运维场景下的各类用户需求，为企业数据与网络安全保驾护航。</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>AI, 网络安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>1.3536</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>当前AI应用正由浅层生成提效向深层商业结果加速渗透：74%的广告主已应用AI生成内容，62%用于投放管理。</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>sz002799</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>环球印务</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>10.0583</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>AI应用|公司凌峰环球智慧工厂AI/智能化目前主要应用于包装工艺设计、APS计划排产、质量视觉检验、智能立库、自动物流等方面。</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1.3536</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>当前AI应用正由浅层生成提效向深层商业结果加速渗透：74%的广告主已应用AI生成内容，62%用于投放管理。</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>sh601519</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大智慧  </t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>10.0122</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>互联网金融+AI|DzhClaw是公司研发运营的AI智能辅助工具，依托第三方云厂商AI底座与大模型能力，结合自有金融数据为用户提供信息检索、市场复盘、数据分析等投研辅助服务，构建分层付费AI产品矩阵。</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>互联网金融, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>染料涂料</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1.3384</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>据百川盈孚报价，2026年9月1日以来，分散染料价格一直维持在30元/千克的高位，相比6月22日的23元/千克上涨7元/千克，2个多月的时间价格上涨超30%。</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>sz301190</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>善水科技</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>29.94</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>染料+医药中间体|公司主要经营染料中间体、农药和医药中间体的研发、生产和销售业务。公司生产的染料中间体包括6-硝体、氧体、5-硝体和邻氨基苯磺酸。</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>染料, 医药中间体</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>染料涂料</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1.3384</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>据百川盈孚报价，2026年9月1日以来，分散染料价格一直维持在30元/千克的高位，相比6月22日的23元/千克上涨7元/千克，2个多月的时间价格上涨超30%。</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>sh603188</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>亚邦股份</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>10.0897</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>染料|公司主要从事染料及染料中间体的销售与服务，是国内蒽醌结构染料生产专家工厂。</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>染料</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>染料涂料</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>1.3384</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>据百川盈孚报价，2026年9月1日以来，分散染料价格一直维持在30元/千克的高位，相比6月22日的23元/千克上涨7元/千克，2个多月的时间价格上涨超30%。</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>sh603980</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>吉华集团</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>9.950199999999999</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>染料+创新药|1.公司主要从事染料、染料中间体及其他化工产品的研发、生产和销售。
+2.旗下江苏康倍得药业股份有限公司是一家致力于仿制及创新透皮高端制剂、国内领先的透皮给药研发型制药企业。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>染料, 创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>0.7301</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>sh603949</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>雪龙集团</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>10.0054</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司作为有限合伙人通过深创投中小企业发展基金（新疆）有限合伙企业间接持股杭州宇树科技有限公司。目前，深创投中小企业发展基金（新疆）有限合伙企业对杭州宇树科技有限公司的持股比例为1.3546%；公司对深创投中小企业发展基金（新疆）有限合伙企业的持股比例为0.7239%。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>0.7301</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>sz000678</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>襄阳轴承</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>10.0469</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>0.7301</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>sz002242</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>九阳股份</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>9.971</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>机器人+谐音“羊”|公司持有深思考人工智能机器人科技（北京）有限公司7.92%的股份，旗下产品包括AI机器人。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 谐音“羊”</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>国家能源局发布1~8月份全国电力统计数据。截至8月底，全国累计发电装机容量41.03亿千瓦，同比增长11.1%。</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>sh600032</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>浙江新能</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>9.9596</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>绿电|公司的主营业务为水力发电、光伏发电、风力发电等可再生能源项目的投资、开发、建设和运营管理。</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>绿电</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>国家能源局发布1~8月份全国电力统计数据。截至8月底，全国累计发电装机容量41.03亿千瓦，同比增长11.1%。</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>sh600982</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>宁波能源</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>电力|公司主要从事热电联产、生物质发电、抽水蓄能和综合能源服务，以及能源类相关金融投资等业务。</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>-0.0393</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>9月28日，上海思璞锐与默沙东联合宣布，双方就在研临床前口服KRAS G12D（ON）抑制剂SPR2015达成全球独家授权协议。潜在总金额21.3亿美元.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>sh600488</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>10.0478</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>创新药|公司于2024年成立创新研究院，负责创新药设计发现、研发以及引进孵化工作，JYSW003项目为津药生物科技（天津）有限公司委托公司创新研究院开展的创新药项目，适应症是银屑病，前期探索性研究结果初步显示药效明显、安全性优等特点。</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>sh600189</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泉阳泉  </t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>10.0122</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>矿泉水+谐音“羊”|公司主要从事长白山天然饮用矿泉水的生产和销售，旗下主要产品“泉阳泉”牌长白山天然矿泉水。</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>矿泉水, 谐音“羊”</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>sz002205</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>国统股份</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>建材|公司产品PCCP（预应力钢筒混凝土管）技术含量较高，规格齐全，公司积极推进产品结构及业务调整转型，通过PPP模式积极参与水务、地下综合管廊等市政基础设施的投资、建设、运营，培育新的利润增长点。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>建材</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>sh601238</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>广汽集团</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>10.0196</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>并购重组|广汽集团公告称，公司拟通过发行股份购买一汽丰田汽车有限公司50%股权，并募集配套资金，本次发行价格为5.75 元/股。公司股票将于2026年9月29日开市起复牌。标的公司由一汽股份与丰田汽车合资组建，与广汽丰田形成南北双合资格局。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>sh605303</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>园林股份</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>10.0084</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>并购重组|园林股份公告称，公司拟通过发行股份及支付现金方式，向杭州华澜创企业管理咨询合伙企业(有限合伙)等98名股东收购华澜微93.5031%股份，并募集配套资金。标的公司主营国产存储控制器芯片及模组、阵列控制器芯片及模组的研发、设计及销售。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sz301560</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>众捷股份</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>20.0142</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>数据中心液冷|公司已成功与全球热管理解决方案领导者Boyd宝德集团建立合作，给Boyd北美和欧洲正在供应数据中心液冷的相关产品。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>数据中心液冷</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>sz002494</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>华斯股份</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>9.917400000000001</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>纺织|国内裘皮服装行业龙头，拥有华斯裘皮城、毛皮交易中心等资源。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>纺织</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sz002813</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>路畅科技</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>10.0083</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>智能驾驶|公司从事汽车车载导航系统的开发、生产、销售及服务，主要产品为汽车车载数码导航信息系统。公司先后与腾讯、百度、阿里巴巴等互联网巨头达成战略合作，共同推进国内车联网事业及汽车智能化的发展。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>智能驾驶</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>sh603630</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>拉芳家化</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>10.0353</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>美容护理|公司主要从事洗护类、护肤类、彩妆类产品的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>美容护理</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>sz002303</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>美盈森</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>10.0164</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>电子烟|公司全资子公司东莞美盈森顺利通过电子香烟制造商吉瑞科技验厂、打样测试、综合评估的审核程序，取得其包装供应资质，为其电子烟产品提供一体化包装服务。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>电子烟</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>sh605388</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>均瑶健康</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>9.983599999999999</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>乳业|公司主营常温乳酸菌系列饮品的研发、生产和销售，2011年起，公司战略进入常温乳酸菌饮品市场，推出“味动力”乳酸菌系列饮品，是国内最早生产与销售常温乳酸菌饮品的品牌企业之一。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>乳业</t>
         </is>
       </c>
     </row>
@@ -2148,7 +3183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2175,7 +3210,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -2190,16 +3225,16 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh600802</t>
+          <t>sh603949</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>雪龙集团</t>
         </is>
       </c>
     </row>
@@ -2209,27 +3244,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh603949</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh603396</t>
+          <t>sh600488</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>金辰股份</t>
+          <t>津药药业</t>
         </is>
       </c>
     </row>
@@ -2239,12 +3274,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh603278</t>
+          <t>sz002242</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
@@ -2254,12 +3289,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh601218</t>
+          <t>sh600241</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>
@@ -2269,12 +3304,57 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sz000011</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>深物业A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>sh600032</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>浙江新能</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>sz301190</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>善水科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>sz002912</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>中新赛克</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="99" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="94" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="287" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="255" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,15 +552,15 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.2382</v>
+        <v>2.0884</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
+          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -568,1182 +568,1196 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>sz000710</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>贝瑞基因</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>10.0202</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>基因检测+AI医疗|1.公司依托其具有自主知识产权的cSMART核心技术为支撑，选择ctDNA作为肿瘤液体活检指标，开启了临床无创肿瘤基因检测的全新模式。
+2.公司自主研发NLPearl遗传疾病人工智能临床决策支持系统、CNVisi智能报告解读系统，为科研和临床工作者提供智能决策支持。公司的CNVisi™利用人工智能深度学习算法，挖掘20+权威公共数据库、百万自有CNV大数据以及20多万份CNV-seq临床实践报告，构建7大临床解读知识库，精准注释解读、一键查询信息、自定义设置参数、AI智能撰写报告。</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>基因检测, AI医疗</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2.0884</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>sh688185</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">康希诺  </t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>102.64</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>20.0047</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>创新型疫苗|公司是一家致力于研发、生产与销售的创新型疫苗企业。在一批疫苗领域资深科学家和具备多年国际大型制药公司从业背景的资深技术专家的带领下，公司快速推进一系列国内创新疫苗的研发，研发管线涵盖预防脑膜炎、埃博拉病毒病、百白破、肺炎、结核病、带状疱疹等多个适应症的临床接种量较大的重磅疫苗。</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>创新型疫苗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2.0884</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>sh603538</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">美诺华  </t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>10.0038</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>CXO|公司正在加速打造CDMO一站式综合服务平台，为制药企业提供贯穿药品临床前研发、临床试验阶段以及上市审批、商业化生产等环节的综合性研发生产服务。</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>CXO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>2.0884</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>sh603590</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>康辰药业</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>32.11</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>10.0034</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>创新药|公司是一家以创新药研发为核心、以临床价值为导向，集研发、生产和销售于一体的创新药企业。公司主要产品为“密盖息”和“苏灵”。</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2.0884</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>sh688806</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>泰诺麦博-U</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>19.9922</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>创新药|泰诺麦博是一家面向全球市场、致力于血液制品替代疗法的创新生物制药企业，专注于全人源单抗新药的开发、制造与商业化。</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2.0884</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>sz000504</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>南华生物</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>10.0089</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>细胞治疗|公司是目前国内一家国资控股的干细胞、免疫细胞及组织工程产业主板上市公司，“生物医药”板块业务包括干细胞储存服务、化妆品的生产和销售、医疗器械设备及耗材的代理和销售。</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>细胞治疗</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2.0884</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>sz002755</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>奥赛康</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>9.9838</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>创新药|公司是一家创新与研发驱动的医药制造企业，公司药物治疗领域主要覆盖消化、抗肿瘤、抗感染、慢性病四大领域，业务涵盖原料药及制剂的研发、生产、销售，在中国医药细分市场具有较高的品牌影响力。</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2.0884</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>sh603127</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>昭衍新药</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>9.9955</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>CXO+AI制药|1.公司专注于药物全生命周期的安全性评价和监测，建立了独具特色的药物非临床研究服务、临床试验及相关服务。
+2.公司已将基于AI和行为组学的全自动行为学检测系统应用于多种CNS疾病模型如阿尔茨海默症、帕金森症和疼痛的评价中，支持了多个前沿药物如细胞治疗、基因治疗药物的非临床申报。</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>CXO, AI制药</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>sz002058</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>紫竹高科</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>10.0218</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>固态电池|旗下紫江新材专注铝塑膜产品的研发，同时积极布局固态电池用铝塑膜产品，以适应未来固态电池行业发展带动的新增需求。</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>sz002866</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>传艺科技</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>10.026</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>固态电池+PCB|1.公司的半固态、固态电池处于研发阶段。
+2.公司专注于为行业领先客户提供全方位FPC产品及服务，根据下游不同终端产品对于FPC的定制化要求，为客户提供涵盖产品设计、研发和销售各个环节的整体解决方案。</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>固态电池, PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>sh603200</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>上海洗霸</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>40.67</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>10.0081</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="G12" s="2" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>10.0074</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>固态电池+液冷|1.公司生产的固态电解质粉体材料可以应用于锂离子固态电池，多形态固态电解质粉体材料（含油性、水性、浆料）年产50吨级产线主要采用的是氧化物技术路线，公司储备了硫化物、氯化物等固态电解质的其它固态电解质粉体技术路线。
 2.公司面向腾讯、华为、中国移动等重点客户数据中心提供循环水/空气蒸发冷却等专业服务。</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>固态电池, 液冷</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>2.2382</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>sz002866</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>传艺科技</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>15.36</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>10.0287</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>固态电池+PCB|1.公司的半固态、固态电池处于研发阶段。
-2.公司专注于为行业领先客户提供全方位FPC产品及服务，根据下游不同终端产品对于FPC的定制化要求，为客户提供涵盖产品设计、研发和销售各个环节的整体解决方案。</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>固态电池, PCB</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>2.2382</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>sz301513</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>尚水智能</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>次新+固态电池|公司半干法、干法极片制造设备已小批量交付中科院物理研究所、比亚迪、因湃电池等客户，用于液态锂离子电池及半固态、固态电池的研发制造和生产测试。</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>次新, 固态电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>2.2382</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>sz002074</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>国轩高科</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>28.68</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>10.0115</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>固态电池|公司已成功研发出车规级全固态电池“金石电池”，这款30Ah的硫化物全固态电池采用了微纳化固体电解质、超薄膜包覆单晶正极和三维介孔硅负极材料技术。</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>2.2382</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>sz002882</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>金龙羽</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>24.51</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>10.009</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>固态电池|公司确定了多种电解质体系的应用方案和全固态电解质材料合成工艺路线，开发了低成本干法工艺制备的电解质产品，氧化物电解质产品已完成多家客户送样及评测。电芯方面，半固态电池性能已满足国标要求，并通过第三方检测机构的国标检测和安全测试。
-2026年1月12日公告，子公司金龙羽新能源（深圳）有限公司拟在深圳大鹏新区投资建设年产2GWh固态电池量产线项目，项目总投资约12亿元。</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>2.2382</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>sz002058</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>紫竹高科</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>18.36</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>10.006</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>固态电池|旗下紫江新材专注铝塑膜产品的研发，同时积极布局固态电池用铝塑膜产品，以适应未来固态电池行业发展带动的新增需求。</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>2.2382</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>sz002846</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>英联股份</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>固态电池|公司的复合铝箔、复合铜箔可以应用于固态电池。</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>2.2382</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>920779.BJ</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>武汉蓝电</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>29.9771</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>固态电池测试|公司专注电池测试系统的开发、生产和销售，为二次电池（包括固态电池）提供专业检测服务。</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>固态电池测试</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>PCB</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>2.0596</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>sh605058</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>澳弘电子</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>10.0037</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12天8板</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>PCB</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>PCB</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>2.0596</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>sh603328</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>依顿电子</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>9.9772</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>PCB|公司专注于高精度、高密度双层及多层印制电路板的研发、生产和销售业务，作为首批进入国际大厂汽车PCB核心供应链的PCB厂商，公司PCB产品供货覆盖传统汽车零部件。
-2026年8月6日公告，公司拟使用自有资金及自筹资金投资建设高端印制电路板智能制造项目，计划总投资29.79亿元。投资项目主要围绕市场高端印制电路板需求，建设高端高速高多层PCB智能制造项目。</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>PCB</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>PCB</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>2.0596</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>sz002913</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>奥士康</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>91.08</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>PCB|公司是一家集研发、生产、销售于一体的PCB领军企业，核心业务是研发、生产和销售高精密印制电路板，主要产品为单/双面板、高多层板、HDI板等，主要应用于数据中心及服务器、AIPC、通信及网络设备、汽车电子等领域。</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.0596</v>
+        <v>0.1294</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz000823</t>
+          <t>sh603928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>兴业股份</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>24.4</v>
+        <v>13.07</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.009</v>
+        <v>10.0168</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司具备不同的印制板生产线，可接单跨度大，产能覆盖HDI板、任意层互连、高密度多层板以及快板业务。</t>
+          <t>固态电池+光刻胶|1.公司已成功研发酚醛树脂，酚醛树脂在电池负极材料的应用有着显著的进步，是未来固态电池、钾离子电池等颠覆性技术的“核心材料基石”。
+2.公司已研发成功半导体光刻胶用酚醛树脂、特种半导体封装用酚醛树脂等一批特种有机合成功能新材料。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>固态电池, 光刻胶</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2.0596</v>
+        <v>0.1294</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
+          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh688655</t>
+          <t>sh603906</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">迅捷兴  </t>
+          <t>龙蟠科技</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>75.7</v>
+        <v>19.04</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>20.0063</v>
+        <v>9.994200000000001</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司主营业务为印制电路板（PCB）的研发、生产与销售，公司在光模块领域已积累了相关产品经验和客户，目前已可批量接单。</t>
+          <t>固态电池+液冷|1.公司全资子公司三金锂电主要专注于固态电池前驱体的开发，已建成一期5000吨产能。针对固态电池的高镍前驱体以及富锂锰基前驱体已通过客户小试认证，部分超高镍前驱体产品也正在和客户进行联合开发。
+2.子公司迪克化学发布第二代算力中心冷却液。该冷却液以乙二醇和丙二醇为基础，通过添加剂破解超大规模数据中心高效散热难题，支撑AI算力稳定运行。该产品目前以国内客户为主，围绕行业头部企业的算力中心推广应用。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>固态电池, 液冷</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2.0596</v>
+        <v>-0.72</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
+          <t>浙商证券指出，海外端，特斯拉开启新一轮人形机器人量产审厂，释放订单及产能扩建信号，四季度为特斯拉人形机器人产能爬坡关键验证期。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz002815</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>崇达技术</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>24.44</v>
+        <v>12.89</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9.991</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
+        <v>9.982900000000001</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>PCB+服务器|1.主营业务为印制电路板的生产和销售；主要产品为小批量印制电路板,产品类型覆盖HDI板、背板、厚铜板等。
-2.公司服务器产品客户是中兴通讯、新华三、云尖等，产品包括服务器主板和AI服务器。</t>
+          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>PCB, 服务器</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2.0596</v>
+        <v>-0.72</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
+          <t>浙商证券指出，海外端，特斯拉开启新一轮人形机器人量产审厂，释放订单及产能扩建信号，四季度为特斯拉人形机器人产能爬坡关键验证期。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh605258</t>
+          <t>sz002242</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>协和电子</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>44.01</v>
+        <v>12.5</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>9.997499999999999</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+        <v>10.0352</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司主要从事印制电路板的研发、生产、销售以及SMT业务，PCB产品主要应用在汽车电子和高频通讯领域。</t>
+          <t>AI机器人|公司持有深思考人工智能机器人科技（北京）有限公司7.92%的股份，旗下产品包括AI机器人。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>AI机器人</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.0596</v>
+        <v>-0.72</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>近期，多家机构研报指出，随着上游原材料价格持续上行，‌PCB（印制电路板）厂商已陆续启动重新报价‌。这一现象标志着产业链价格传导机制的打通，预计‌2026年第三季度‌将成为板块盈利改善的起涨点。</t>
+          <t>浙商证券指出，海外端，特斯拉开启新一轮人形机器人量产审厂，释放订单及产能扩建信号，四季度为特斯拉人形机器人产能爬坡关键验证期。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh605198</t>
+          <t>sz002164</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">安德利  </t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>65.68000000000001</v>
+        <v>13.26</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.9983</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+        <v>10.0415</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>PCB|安德利公告称，公司签署股权转让框架协议，公司拟以自有或自筹资金的方式收购宁波甬强科技有限公司（简称“甬强科技”）股东JIANGQI HE、QIANG YUAN、宁波源路载科技合伙企业（有限合伙）的部分股权。甬强科技主要产品为电子信息互连材料，包括覆铜板和半固化片。电子信息互连材料是制作印制电路板的核心材料。</t>
+          <t>机器人+风电|1.公司的产品包括行星减速器等，杭州湾电机、减速器部分车间已投入生产。
+2.公司研发的风电齿轮箱应用于风电市场。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>机器人, 风电</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2.6502</v>
+        <v>-0.72</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>浙商证券指出，海外端，特斯拉开启新一轮人形机器人量产审厂，释放订单及产能扩建信号，四季度为特斯拉人形机器人产能爬坡关键验证期。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sh600592</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>龙溪股份</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>9.41</v>
+        <v>16.2</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.0585</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6天6板</t>
-        </is>
-      </c>
+        <v>9.9796</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>传媒+并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
+          <t>机器人+商业航天|1.公司的关节轴承是机器人的主要配套件。
+2.公司主营产品关节轴承主要应用于工程机械、载重汽车和航空航天等领域。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>传媒, 并购重组</t>
+          <t>机器人, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2.6502</v>
+        <v>-0.72</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>浙商证券指出，海外端，特斯拉开启新一轮人形机器人量产审厂，释放订单及产能扩建信号，四季度为特斯拉人形机器人产能爬坡关键验证期。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sh605288</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>凯迪股份</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>20.37</v>
+        <v>71.83</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.9892</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7天6板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>传媒+并购重组|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
+          <t>机器人|公司主要产品为线性驱动系统，可以应用在机器人上。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>传媒, 并购重组</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2.6502</v>
+        <v>1.4674</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>根据农业农村部监测数据，2026年9月第3周，全国10个主产省生鲜乳均价为3.08元/公斤（环比微涨0.3%，同比上涨1.7%）。8月份主产省均价为3.06元/公斤。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh603533</t>
+          <t>sh605388</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>均瑶健康</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>23.65</v>
+        <v>7.39</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+        <v>9.9702</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>传媒+AI|在数字阅读领域，掌阅APP现有书童导读、速览群书、书籍摘要、一键速读、逐句精读、思维导图等AI辅助阅读功能基础上，继续推出“AI讲书电台”，通过双人虚拟角色对话的创新形式，构建更具沉浸感和多元表达力的智能听书体验，为用户在不同阅读阶段提供陪伴式、交互式的内容服务。</t>
+          <t>乳业|公司主营常温乳酸菌系列饮品的研发、生产和销售，2011年起，公司战略进入常温乳酸菌饮品市场，推出“味动力”乳酸菌系列饮品，是国内最早生产与销售常温乳酸菌饮品的品牌企业之一。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>传媒, AI</t>
+          <t>乳业</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2.6502</v>
+        <v>1.4674</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>根据农业农村部监测数据，2026年9月第3周，全国10个主产省生鲜乳均价为3.08元/公斤（环比微涨0.3%，同比上涨1.7%）。8月份主产省均价为3.06元/公斤。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz000607</t>
+          <t>sh600059</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>华媒控股</t>
+          <t>古越龙山</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>4.13</v>
+        <v>12.27</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.1333</v>
+        <v>10.0448</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>传媒+AI|1.公司主要从事广告策划发布、报刊发行与印刷、教育等业务，涵盖平面媒体、网络媒体、移动新媒体、户外 媒体包括地铁媒体的广告承揽发布、企事业单位宣传公关的全案策划和实施。
-2.公司控股子公司中教未来的业务板块之一是IT教育。旗下部分幼儿园引进AI智能机器人，培养人机协同的兴趣和科学探索精神，以便适应AI智能对孩子学习的辅助作用。</t>
+          <t>黄酒|公司所从事的主要业务是黄酒的制造、销售及研发，生产黄酒原酒、黄酒瓶装酒及少量果酒、白酒等，主要产品古越龙山、女儿红、状元红、沈永和、鉴湖牌等绍兴黄酒是中国首批国家地理标志产品。其中古越龙山是中国黄酒行业标志性品牌、唯一钓鱼台国宾馆国宴专用黄酒、“亚洲品牌500强”中唯一入选的黄酒品牌。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>传媒, AI</t>
+          <t>黄酒</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2.6502</v>
+        <v>1.4674</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>根据农业农村部监测数据，2026年9月第3周，全国10个主产省生鲜乳均价为3.08元/公斤（环比微涨0.3%，同比上涨1.7%）。8月份主产省均价为3.06元/公斤。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh603598</t>
+          <t>sz001318</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>引力传媒</t>
+          <t>阳光乳业</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>19.13</v>
+        <v>13.04</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.0058</v>
+        <v>10.0422</v>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>传媒+AI|1.公司是一家以内容创意与科技创新驱动的卓越数字商业服务公司。
-2.公司已推出自有营销电商行业模型并推出三大智能体（Agent）-感知智能体、决策智能体、内容智能体，用以增强营销决策、创意素材、视频混剪等环节内容产出的精准性与稳定性。</t>
+          <t>乳业|公司专注于乳制品及乳饮料的研发、生产和销售，并以低温乳制品、低温乳饮料为主打产品。公司针对儿童提高免疫力开发的“初乳” 产品。公司从事液态乳、含乳饮料等产品的研发、生产、销售。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>传媒, AI</t>
+          <t>乳业</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2.6502</v>
+        <v>1.4674</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>机构指出，国产大模型迭代提速，AI视频、AI短剧等应用商业化进程加快，版权、优质文本数据的商业价值被重新评估。</t>
+          <t>根据农业农村部监测数据，2026年9月第3周，全国10个主产省生鲜乳均价为3.08元/公斤（环比微涨0.3%，同比上涨1.7%）。8月份主产省均价为3.06元/公斤。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh601949</t>
+          <t>sh603919</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>中国出版</t>
+          <t xml:space="preserve">金徽酒  </t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>6.01</v>
+        <v>17.4</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.0733</v>
+        <v>9.987400000000001</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>AI+传媒|1.公司推动“文化+科技”业态创新，中华古籍大模型建设初步完成，东方“多AI平台协同工作流”提升视频生产效率。
-2.公司是以图书、报纸、期刊等出版物出版为主业，是集出版、发行、物资供应、印刷等业务于一体的大型出版企业，拥有丰富的作者、译者、内容资源。</t>
+          <t>白酒|公司代表产品有“金徽二十八年、金徽十八年、世纪金徽星级、柔和金徽、金徽正能量”等，营销网络已辐射甘肃、陕西、宁夏、新疆、西藏、内蒙、青海等西北市场，为西北地区强势白酒品牌。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>AI, 传媒</t>
+          <t>白酒</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3.1164</v>
+        <v>0.6698</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>国务院常务会议9月28日召开，会议指出推出一批务实管用的增量政策，研究出台稳定房地产市场、促进就业增收等政策措施。</t>
+          <t>中央气象台消息，今年下半年以来最强冷空气昨天夜间开始影响我国，未来三天将自北向南给中东部地区带来大风降温，10月1日早晨最低气温0℃线，将南压至华北北部和黑龙江中部一带。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sz000011</t>
+          <t>sh600356</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>恒丰纸业</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>11.13</v>
+        <v>11.46</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.9802</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.980799999999999</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>房地产|公司经过多年发展，已形成了以房地产开发为主业，物业管理、物业租赁、出租汽车营运、餐饮服务、物流仓储、工程监理等为辅的跨行业、多元化的经营格局。</t>
+          <t>电力+卷烟纸|1.公司旗下恒丰热电经营范围包括电力、热力产品生产等。
+2.公司主导产品为卷烟纸、滤嘴棒纸、铝箔衬纸和水松纸等，是国内卷烟辅料生产基地，五大卷烟辅料供应商之一。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>电力, 卷烟纸</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3.1164</v>
+        <v>0.6698</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>国务院常务会议9月28日召开，会议指出推出一批务实管用的增量政策，研究出台稳定房地产市场、促进就业增收等政策措施。</t>
+          <t>中央气象台消息，今年下半年以来最强冷空气昨天夜间开始影响我国，未来三天将自北向南给中东部地区带来大风降温，10月1日早晨最低气温0℃线，将南压至华北北部和黑龙江中部一带。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sh600657</t>
+          <t>sz000692</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>信达地产</t>
+          <t>惠天热电</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>3.38</v>
+        <v>4.59</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.0977</v>
+        <v>10.0719</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>房地产|中国信达资产管理股份有限公司旗下上市公司，中国信达房地产开发业务运作平台。</t>
+          <t>电力|惠天热电公告称，公司拟投资建设全胜热电配套长距离互联互通供热工程项目，计划总投资约14.05亿元。该项目旨在将全胜热电项目产生的热量输送至铁西热网，形成热电联产供热模式，提升区域供热保障能力。项目尚需提交股东会审议。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>3.1164</v>
+        <v>0.6698</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>国务院常务会议9月28日召开，会议指出推出一批务实管用的增量政策，研究出台稳定房地产市场、促进就业增收等政策措施。</t>
+          <t>中央气象台消息，今年下半年以来最强冷空气昨天夜间开始影响我国，未来三天将自北向南给中东部地区带来大风降温，10月1日早晨最低气温0℃线，将南压至华北北部和黑龙江中部一带。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz002244</t>
+          <t>sh605011</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>滨江集团</t>
+          <t>杭州热电</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>19.21</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10</v>
+        <v>10.0229</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>房地产|公司具有建设部一级开发资质，全国民营企业500强，中国房地产企业50强，长三角房地产领军企业。</t>
+          <t>电力|公司的最终控制人为杭州市人民政府。公司是一家主营工业园区热电联产、集中供热的节能环保型企业。公司提供的主要产品是蒸汽与电力。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>电力</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>3.1164</v>
+        <v>0.6698</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>国务院常务会议9月28日召开，会议指出推出一批务实管用的增量政策，研究出台稳定房地产市场、促进就业增收等政策措施。</t>
+          <t>中央气象台消息，今年下半年以来最强冷空气昨天夜间开始影响我国，未来三天将自北向南给中东部地区带来大风降温，10月1日早晨最低气温0℃线，将南压至华北北部和黑龙江中部一带。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sz000002</t>
+          <t>sh600131</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>万  科Ａ</t>
+          <t>国网信通</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>4.08</v>
+        <v>15.39</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>9.973000000000001</v>
+        <v>10.0071</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>房地产|本集团的主营业务包括房地产开发和物业服务，本集团将自身定位进一步迭代升级为“城乡建设与生活服务商”。</t>
+          <t>电力+智能电网|1.公司是集发配售电于一体的电力企业，拥有区域性独立配电网络。公司电力来源为：一是自有水电站和并网小水电发电量通过自有电网销售给终端客户；二是通过联网线路从国家电网四川省电力公司等单位趸购电量。
+2.公司围绕电力发-输-变-配-用-调各环节、源网荷储全场景，融合运用“大云物移智”等创新技术，拓展覆盖规划咨询、软件研发、工程实施、系统集成、运营运维等信息通信全产业链。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>电力, 智能电网</t>
         </is>
       </c>
     </row>
@@ -1754,136 +1768,137 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>3.1164</v>
+        <v>0.5402</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>国务院常务会议9月28日召开，会议指出推出一批务实管用的增量政策，研究出台稳定房地产市场、促进就业增收等政策措施。</t>
+          <t>我国将从10月1日起对居民使用新发放商业性个人住房贷款购房实施贴息。可享受贴息的贷款规模最高可达100万元，财政部门给予年化1个百分点的贴息，贴息期限最长5年。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sh600325</t>
+          <t>sz000011</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>华发股份</t>
+          <t>深物业A</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>2.95</v>
+        <v>12.24</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10.0746</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+        <v>9.973000000000001</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>房地产|公司主营业务为房地产开发与经营，拥有房地产一级开发资质。</t>
+          <t>物业管理|公司经过多年发展，已形成了以房地产开发为主业，物业管理、物业租赁、出租汽车营运、餐饮服务、物流仓储、工程监理等为辅的跨行业、多元化的经营格局。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>物业管理</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.505</v>
+        <v>0.5402</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>工业和信息化部、国家发展改革委、交通运输部等七部门联合制定的《新型电池产业发展“十五五”规划》，《规划》提出，培优育强新型电池领域龙头企业，支持企业兼并重组。</t>
+          <t>我国将从10月1日起对居民使用新发放商业性个人住房贷款购房实施贴息。可享受贴息的贷款规模最高可达100万元，财政部门给予年化1个百分点的贴息，贴息期限最长5年。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh600241</t>
+          <t>sz002188</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>中天服务</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>8.84</v>
+        <v>6.4</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>9.950199999999999</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.9656</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>锂电池|公司旗下九夷锂能主要经营锂离子电池、电池组的研发、生产、制造、系统集成、销售和服务，目标市场定位于电动工具、个人护理、家庭电子、消费品等小动力领域。</t>
+          <t>物业管理+旅游酒店|1.公司2021年主营业务变更为物业管理服务。物业管理服务指对住宅及非住宅的建筑及配套进行管理维护。
+2.旗下东阳市凤凰谷天澜酒店拥有203间客房及800平方米无柱式天澜宴会厅，配套健身房、恒温泳池等休闲设施。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>物业管理, 旅游酒店</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>房地产概念</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1.505</v>
+        <v>0.5402</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>工业和信息化部、国家发展改革委、交通运输部等七部门联合制定的《新型电池产业发展“十五五”规划》，《规划》提出，培优育强新型电池领域龙头企业，支持企业兼并重组。</t>
+          <t>我国将从10月1日起对居民使用新发放商业性个人住房贷款购房实施贴息。可享受贴息的贷款规模最高可达100万元，财政部门给予年化1个百分点的贴息，贴息期限最长5年。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz000036</t>
+          <t>sh600663</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>华联控股</t>
+          <t xml:space="preserve">陆家嘴  </t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>4.21</v>
+        <v>10.11</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.9217</v>
+        <v>10.0109</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>房地产+盐湖提锂|1.公司主营业务为房地产开发和自有物业租赁管理业务。公司目前房地产开发业务主要集中在深圳、杭州、千岛湖等城市，物业资产及物业经营管理业务主要集中深圳、杭州、上海、千岛湖等区域。
-2.华联控股公告称，公司拟以自有或自筹资金约1.75亿美元（折合人民币12.35亿元）受让Lithium Chile Inc.和Steve Cochrane合计持有的Argentum Lithium S.A.100%股份，从而获得Arizaro项目80%的权益。同日，公司与交易对方签署了《股份购买协议》。标的公司未来的主要收入来源于盐湖提锂业务，其主要产品为电池级碳酸锂。</t>
+          <t>房地产+参股券商|1.公司控股股东为上海陆家嘴（集团）有限公司。公司坚持以商业地产为核心，以金融服务为纽带，以商业零售为延伸。
+2.子公司陆金发持有爱建证券51.14%股权。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>房地产, 盐湖提锂</t>
+          <t>房地产, 参股券商</t>
         </is>
       </c>
     </row>
@@ -1894,41 +1909,45 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1.505</v>
+        <v>-0.172</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>工业和信息化部、国家发展改革委、交通运输部等七部门联合制定的《新型电池产业发展“十五五”规划》，《规划》提出，培优育强新型电池领域龙头企业，支持企业兼并重组。</t>
+          <t>中信证券研报称，从电池与能源管理产业链2026年上半年及2026年第二季度经营结果来看，下游需求保持高景气，产业链多数环节收入实现增长，盈利修复进一步向中上游扩散。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz000068</t>
+          <t>sh600241</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>华控赛格</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>3.54</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>9.937899999999999</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
+        <v>9.954800000000001</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>电池负极材料|公司旗下奥原新材料主要从事石墨化深加工业务，锂离子电池负极材料产能约为6000吨/年。</t>
+          <t>锂电池|公司旗下九夷锂能主要经营锂离子电池、电池组的研发、生产、制造、系统集成、销售和服务，目标市场定位于电动工具、个人护理、家庭电子、消费品等小动力领域。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>电池负极材料</t>
+          <t>锂电池</t>
         </is>
       </c>
     </row>
@@ -1939,229 +1958,223 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1.505</v>
+        <v>-0.172</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>工业和信息化部、国家发展改革委、交通运输部等七部门联合制定的《新型电池产业发展“十五五”规划》，《规划》提出，培优育强新型电池领域龙头企业，支持企业兼并重组。</t>
+          <t>中信证券研报称，从电池与能源管理产业链2026年上半年及2026年第二季度经营结果来看，下游需求保持高景气，产业链多数环节收入实现增长，盈利修复进一步向中上游扩散。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh600152</t>
+          <t>sz002388</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>维科技术</t>
+          <t>新亚制程</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>8.32</v>
+        <v>9.1</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.0529</v>
+        <v>10.0363</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>锂电池+钠电池|1.维科技术公告称，公司拟投资建设年产1300万只多极耳高倍率电池智能化改造项目，项目总投资7342万元，子公司江西维乐电池有限公司为项目的实施主体。该项目产品为聚合物软包电芯，主要应用于智能家居、无人机等智能硬件与消费电子领域。
-2.2022年9月9日，维科技术股份有限公司与浙江钠创新能源有限公司在浙江绍兴签订《深度合作战略框架协议》。协议约定，双方将深化钠电研发合作，共享各自在钠离子电池研发的技术积累，联合申报政府重大科研项目，共同参与钠离子电池相关行业标准和规范文件的制订。</t>
+          <t>锂电池+半导体|1.杉杉新材料为新亚新能源的控股子公司、公司的间接控股公司。杉杉新材料具有较好的市场竞争力和盈利能力，现有电解液产能3万吨、六氟磷酸锂产能2000吨，在建电解液产能3万吨、六氟磷酸锂产能4000吨。
+2.公司的底部填充胶COO602系列用于BGA、CSP和Flip chip底部填充制程，不仅可以助力电子产品的抗跌落性，还具有一定的导热的可靠性，在产品封装解决方案中起到非常重要的作用。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>锂电池, 钠电池</t>
+          <t>锂电池, 半导体</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>锂电池</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1.2997</v>
+        <v>-0.172</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>算力租赁商Nebius计划自10月1日起上调主要英伟达GPU按需租金，整体涨幅约17%至21%。</t>
+          <t>中信证券研报称，从电池与能源管理产业链2026年上半年及2026年第二季度经营结果来看，下游需求保持高景气，产业链多数环节收入实现增长，盈利修复进一步向中上游扩散。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh603636</t>
+          <t>sh603948</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>南威软件</t>
+          <t>建业股份</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>7.87</v>
+        <v>21.36</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10.0699</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>6天4板</t>
-        </is>
-      </c>
+        <v>9.989699999999999</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>算力+AI智能体|1.公司于2024年4月获得北京市发展和改革委员会批准，建设2300PFlops算力的“北京七星园数字经济产业智算中心”，用于服务企业人工智能发展、政府公共算力及企业算力需求。
-2.公司已发布AI智能体服务平台“白泽启元”、政务公文写作与协同平台“白泽文墨”、智能体客服平台“白泽对话管理”以及智能体BI产品“白泽云图”等白泽系列四款大模型智能体产品。</t>
+          <t>锂电池+半导体|1.公司三乙胺可用于锂电池电解液的制备。
+2.公司主营产品之一的超纯氨是超净高纯电子化学品，是超大规模集成电路（即芯片）制作过程中的关键性基础化工材料之一，主要用于芯片的清洗、蚀刻、掺杂和沉淀工艺。超纯氨是微电子氮化硅掩蔽膜的主要原材料。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>算力, AI智能体</t>
+          <t>锂电池, 半导体</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>新能源汽车</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1.2997</v>
+        <v>-0.3621</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>算力租赁商Nebius计划自10月1日起上调主要英伟达GPU按需租金，整体涨幅约17%至21%。</t>
+          <t>华为常务董事余承东日前表示，华为和江淮汽车合作的尊界SUV新车2027年年初有望上市。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh688685</t>
+          <t>sh600081</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">迈信林  </t>
+          <t>东风科技</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>39.7</v>
+        <v>11.89</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>20.0121</v>
+        <v>9.9907</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>光通信+算力租赁|1.2023年11月21日公司在机构调研中透露，3um设备用在400GHz和800GHz光模块封装，目前已有多家客户通过测试。
-2.公司于2024年1月26日成立控股子公司瑞盈科技，公司持股51%，子公司独立打造算力服务平台。公司计划于2024年度共计采购500台算力服务器。</t>
+          <t>汽车零部件|公司主营业务为汽车零部件生产、制造、销售相关业务，涵盖座舱与车身系统、制动及智能驾驶系统、电驱动系统、热管理系统、动力总成部件系统。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>光通信, 算力租赁</t>
+          <t>汽车零部件</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>新能源汽车</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1.2997</v>
+        <v>-0.3621</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>算力租赁商Nebius计划自10月1日起上调主要英伟达GPU按需租金，整体涨幅约17%至21%。</t>
+          <t>华为常务董事余承东日前表示，华为和江淮汽车合作的尊界SUV新车2027年年初有望上市。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh603322</t>
+          <t>sz002454</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>超讯科技</t>
+          <t>松芝股份</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>29.1</v>
+        <v>5.61</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.0189</v>
+        <v>10</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司作为沐曦GPU的行业总代理，把握千卡级算力集群的市场机遇，实现批量GPU算力卡的高效销售与交付；同时，大力发展算力建设与租赁服务，构筑了以大湾区广州白云区为起点，长三角江苏淮安、西北甘肃庆阳为重要支点，覆盖华南、中部、西北三大区域的“超讯算力网“。</t>
+          <t>汽车零部件|公司非常重视新能源汽车发展情况，在大中型客车空调业务板块，新能源客车空调发货量已占客车空调发货量的50%以上。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>汽车零部件</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
+          <t>新能源汽车</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1.2997</v>
+        <v>-0.3621</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>算力租赁商Nebius计划自10月1日起上调主要英伟达GPU按需租金，整体涨幅约17%至21%。</t>
+          <t>华为常务董事余承东日前表示，华为和江淮汽车合作的尊界SUV新车2027年年初有望上市。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh603602</t>
+          <t>sz300893</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>纵横通信</t>
+          <t>松原安全</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>12.71</v>
+        <v>15.13</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.0433</v>
+        <v>19.9841</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>AI应用+算力租赁|1.公司在全域数字营销业务中已应用AI技术，主要体现在： 1、AI作为生产工具，公司运用AI能力优化流量复用和用户标签分析，提升投放效率。
-2.旗下纵横智算聚焦算力资源整合、租赁及组网运营，目标为政企客户提供一站式算力服务。</t>
+          <t>汽车零部件|公司积极协同整车厂新能源汽车的汽车被动安全系统设计，已成功为吉利帝豪EV、奇瑞新能源eQ1、上汽通用五菱E200\E100等重要新能源车型配套高端汽车安全带总成。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>AI应用, 算力租赁</t>
+          <t>汽车零部件</t>
         </is>
       </c>
     </row>
@@ -2172,11 +2185,11 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1.3536</v>
+        <v>-0.4523</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>当前AI应用正由浅层生成提效向深层商业结果加速渗透：74%的广告主已应用AI生成内容，62%用于投放管理。</t>
+          <t>OpenAI最新推出了一款全天候在线的智能体“Dot”，Dot由GPT‑6 Astra驱动，能够操作电脑从各种已连接的应用程序中提取信息，用以开展研究、起草文件、开发软件等。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -2184,33 +2197,30 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz002912</t>
+          <t>sh605577</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>龙版传媒</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>29.12</v>
+        <v>16.28</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.0113</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>AI+网络安全|公司推出的小赛安全智脑产品，支持多模型底座，基于智能体、RAG等技术，包含渗透测试智能体、事件调查智能体、代码安全审计智能体，也配备了敏感数据识别、智能解码、安全知识问答等多种智能体应用，全方位满足安全运维场景下的各类用户需求，为企业数据与网络安全保驾护航。</t>
+          <t>AI漫剧+出版传媒|1.公司首部AI漫剧《穿越1988》完成170集制作上线，全网播放量突破1.2亿，红果热度值超4000万。
+2.公司地处哈尔滨，是我国东北地区出版发行行业的领先企业之一，公司拥有出版物“编、印、发”完整的产业链。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>AI, 网络安全</t>
+          <t>AI漫剧, 出版传媒</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2231,11 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1.3536</v>
+        <v>-0.4523</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>当前AI应用正由浅层生成提效向深层商业结果加速渗透：74%的广告主已应用AI生成内容，62%用于投放管理。</t>
+          <t>OpenAI最新推出了一款全天候在线的智能体“Dot”，Dot由GPT‑6 Astra驱动，能够操作电脑从各种已连接的应用程序中提取信息，用以开展研究、起草文件、开发软件等。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2233,24 +2243,24 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz002799</t>
+          <t>sz002316</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>环球印务</t>
+          <t>亚联发展</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>7.55</v>
+        <v>4.95</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.0583</v>
+        <v>10</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>AI应用|公司凌峰环球智慧工厂AI/智能化目前主要应用于包装工艺设计、APS计划排产、质量视觉检验、智能立库、自动物流等方面。</t>
+          <t>AI应用|公司基于华为Atlas人工智能计算平台开发的“无人值守变电站智能运检系统V6”及基于华为Tai Shan 200系列开发的“变电站智能网关系统V1.1”获得华为技术认证书，并且在南方电网顺利投放使用。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2266,11 +2276,11 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1.3536</v>
+        <v>-0.4523</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>当前AI应用正由浅层生成提效向深层商业结果加速渗透：74%的广告主已应用AI生成内容，62%用于投放管理。</t>
+          <t>OpenAI最新推出了一款全天候在线的智能体“Dot”，Dot由GPT‑6 Astra驱动，能够操作电脑从各种已连接的应用程序中提取信息，用以开展研究、起草文件、开发软件等。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -2278,29 +2288,29 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh601519</t>
+          <t>sh605287</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">大智慧  </t>
+          <t>德才股份</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>9.01</v>
+        <v>37.39</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10.0122</v>
+        <v>10.0029</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>互联网金融+AI|DzhClaw是公司研发运营的AI智能辅助工具，依托第三方云厂商AI底座与大模型能力，结合自有金融数据为用户提供信息检索、市场复盘、数据分析等投研辅助服务，构建分层付费AI产品矩阵。</t>
+          <t>AI漫剧|旗下奇想无限深耕“网文IP+AI漫剧”转化，与头部网文平台合作，将玄幻、甜宠等成熟IP快速落地，已产出多部爆款。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>互联网金融, AI</t>
+          <t>AI漫剧</t>
         </is>
       </c>
     </row>
@@ -2311,15 +2321,15 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1.3384</v>
+        <v>2.302</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>据百川盈孚报价，2026年9月1日以来，分散染料价格一直维持在30元/千克的高位，相比6月22日的23元/千克上涨7元/千克，2个多月的时间价格上涨超30%。</t>
+          <t>近期国内染料及上游中间体行情持续走高，“金九银十”纺织备货带动化工染料产业链景气上行。数据显示，自6月低点至今，分散染料报价累计上涨超30%，活性染料涨幅达到55%。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -2332,14 +2342,14 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>29.94</v>
+        <v>35.93</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>20</v>
+        <v>20.0067</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2360,15 +2370,15 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1.3384</v>
+        <v>2.302</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>据百川盈孚报价，2026年9月1日以来，分散染料价格一直维持在30元/千克的高位，相比6月22日的23元/千克上涨7元/千克，2个多月的时间价格上涨超30%。</t>
+          <t>近期国内染料及上游中间体行情持续走高，“金九银十”纺织备货带动化工染料产业链景气上行。数据显示，自6月低点至今，分散染料报价累计上涨超30%，活性染料涨幅达到55%。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -2381,12 +2391,16 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>4.91</v>
+        <v>5.4</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10.0897</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
+        <v>9.9796</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
           <t>染料|公司主要从事染料及染料中间体的销售与服务，是国内蒽醌结构染料生产专家工厂。</t>
@@ -2401,336 +2415,290 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>染料涂料</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>1.3384</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>据百川盈孚报价，2026年9月1日以来，分散染料价格一直维持在30元/千克的高位，相比6月22日的23元/千克上涨7元/千克，2个多月的时间价格上涨超30%。</t>
-        </is>
-      </c>
+        <v>0.2474</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sh603980</t>
+          <t>sz000911</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>吉华集团</t>
+          <t>*ST广糖</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>8.84</v>
+        <v>5.4</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>9.950199999999999</v>
+        <v>9.9796</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>染料+创新药|1.公司主要从事染料、染料中间体及其他化工产品的研发、生产和销售。
-2.旗下江苏康倍得药业股份有限公司是一家致力于仿制及创新透皮高端制剂、国内领先的透皮给药研发型制药企业。</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>染料, 创新药</t>
-        </is>
-      </c>
+          <t>ST股 | 主要从事机制糖的生产与销售业务。主要客户包括海天味业、加多宝、娃哈哈等。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>0.7301</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
-        </is>
-      </c>
+        <v>0.2474</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sh603949</t>
+          <t>sz000838</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>*ST发展</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>20.45</v>
+        <v>2.45</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>10.0054</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>9.865500000000001</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司作为有限合伙人通过深创投中小企业发展基金（新疆）有限合伙企业间接持股杭州宇树科技有限公司。目前，深创投中小企业发展基金（新疆）有限合伙企业对杭州宇树科技有限公司的持股比例为1.3546%；公司对深创投中小企业发展基金（新疆）有限合伙企业的持股比例为0.7239%。</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
+          <t>ST股 | 1.房地产板块的主营业务为房地产开发与销售，经营模式为商品房开发销售。公司业务范围主要在重庆市、江苏省连云港市和山东省威海市。
+2.财信发展公告称，公司控股股东财信地产及间接控股股东财信集团与投资人江西中久天然气集团有限公司签署《重整投资协议》，投资人拟收购财信发展20%至29.99%的股份。若投资人获得上述股份，将导致公司股权结构、控股股东和实际控制人发生变更，江西中久天然气集团实际控制人雍芝君将成为上市公司实际控制人，江西中久天然气集团将成为上市公司控股股东。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>0.7301</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
-        </is>
-      </c>
+        <v>0.2474</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sz002856</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>*ST美芝</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>11.72</v>
+        <v>20.22</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>10.0469</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.0109</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
+          <t>ST股 | 公司从事的主要业务为建筑装饰工程的设计与施工，主要为交通运输机构、文化产业、金融地产、政府机构、高端星级酒店集团等大型客户，提供跨领域全方位的综合工程服务。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0.7301</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉近几个月将Optimus人形机器人的产量提高了大约十倍，但公司仍在努力实现大规模可靠生产。</t>
-        </is>
-      </c>
+        <v>0.2474</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz002242</t>
+          <t>sz002694</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>*ST顾地</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>11.36</v>
+        <v>2.76</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>9.971</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.9602</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>机器人+谐音“羊”|公司持有深思考人工智能机器人科技（北京）有限公司7.92%的股份，旗下产品包括AI机器人。</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>机器人, 谐音“羊”</t>
-        </is>
-      </c>
+          <t>ST股 | 公司为国内有较大规模和影响力的塑胶建材制造商之一，主要产品有聚氯乙烯（PVC）系列管道、聚乙烯（PE）系列管道和聚丙烯（PP）系列管道等。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>0.3018</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>国家能源局发布1~8月份全国电力统计数据。截至8月底，全国累计发电装机容量41.03亿千瓦，同比增长11.1%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh600032</t>
+          <t>sh600825</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>浙江新能</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>8.17</v>
+        <v>10.35</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>9.9596</v>
+        <v>9.9894</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>7天7板</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司的主营业务为水力发电、光伏发电、风力发电等可再生能源项目的投资、开发、建设和运营管理。</t>
+          <t>并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>0.3018</v>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>国家能源局发布1~8月份全国电力统计数据。截至8月底，全国累计发电装机容量41.03亿千瓦，同比增长11.1%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sh600982</t>
+          <t>sh605303</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>宁波能源</t>
+          <t>园林股份</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>5.49</v>
+        <v>28.66</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
+        <v>10.0192</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>电力|公司主要从事热电联产、生物质发电、抽水蓄能和综合能源服务，以及能源类相关金融投资等业务。</t>
+          <t>并购重组|园林股份公告称，公司拟通过发行股份及支付现金方式，向杭州华澜创企业管理咨询合伙企业(有限合伙)等98名股东收购华澜微93.5031%股份，并募集配套资金。标的公司主营国产存储控制器芯片及模组、阵列控制器芯片及模组的研发、设计及销售。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>-0.0393</v>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>9月28日，上海思璞锐与默沙东联合宣布，双方就在研临床前口服KRAS G12D（ON）抑制剂SPR2015达成全球独家授权协议。潜在总金额21.3亿美元.</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sh600488</t>
+          <t>sz002962</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>五方光电</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>6.9</v>
+        <v>16.17</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>10.0478</v>
+        <v>10</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司于2024年成立创新研究院，负责创新药设计发现、研发以及引进孵化工作，JYSW003项目为津药生物科技（天津）有限公司委托公司创新研究院开展的创新药项目，适应症是银屑病，前期探索性研究结果初步显示药效明显、安全性优等特点。</t>
+          <t>玻璃基板|公司具有玻璃通孔TGV技术能力及一定的产品交付能力。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>玻璃基板</t>
         </is>
       </c>
     </row>
@@ -2747,37 +2715,33 @@
       </c>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh600189</t>
+          <t>sz001206</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">泉阳泉  </t>
+          <t>依依股份</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>9.01</v>
+        <v>18.62</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10.0122</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>9.982299999999999</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>矿泉水+谐音“羊”|公司主要从事长白山天然饮用矿泉水的生产和销售，旗下主要产品“泉阳泉”牌长白山天然矿泉水。</t>
+          <t>股权转让|依依股份公告称，公司控股股东、实际控制人高福忠、高健，持股5%以上股东卢俊美及其一致行动人卢俊江，董事高斌、杨丙发、张健与宿迁祝荣投资合伙企业签署《股份转让协议》，拟以17元/股协议转让合计1295万股(占总股本7%)，转让总价款2.2亿元。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>矿泉水, 谐音“羊”</t>
+          <t>股权转让</t>
         </is>
       </c>
     </row>
@@ -2794,37 +2758,33 @@
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sz002205</t>
+          <t>sh601118</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>国统股份</t>
+          <t>海南橡胶</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>12.76</v>
+        <v>6.37</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>10.0173</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>建材|公司产品PCCP（预应力钢筒混凝土管）技术含量较高，规格齐全，公司积极推进产品结构及业务调整转型，通过PPP模式积极参与水务、地下综合管廊等市政基础设施的投资、建设、运营，培育新的利润增长点。</t>
+          <t>橡胶|地处海南省海口市，海南省农垦投资控股集团旗下上市公司，是目前中国最大的天然橡胶生产企业。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>建材</t>
+          <t>橡胶</t>
         </is>
       </c>
     </row>
@@ -2841,33 +2801,34 @@
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sh601238</t>
+          <t>sh600072</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>广汽集团</t>
+          <t>中船科技</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>5.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>10.0196</v>
+        <v>9.9773</v>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>并购重组|广汽集团公告称，公司拟通过发行股份购买一汽丰田汽车有限公司50%股权，并募集配套资金，本次发行价格为5.75 元/股。公司股票将于2026年9月29日开市起复牌。标的公司由一汽股份与丰田汽车合资组建，与广汽丰田形成南北双合资格局。</t>
+          <t>风电+船舶|1.公司主要业务包括风力发电设备的制造、风电场和光伏电站的开发与运营、新能源工程建设服务等，在运营风光电场20个，合计权益容量137.33千瓦。
+2.中国船舶工业集团旗下上市公司，以设计咨询、工程总承包及城镇化建设三大业务为依托，积极布局豪华邮轮、舰船内装业务等。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>风电, 船舶</t>
         </is>
       </c>
     </row>
@@ -2884,33 +2845,33 @@
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sh605303</t>
+          <t>sh603739</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>园林股份</t>
+          <t>蔚蓝生物</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>26.05</v>
+        <v>14.04</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>10.0084</v>
+        <v>10.0313</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>并购重组|园林股份公告称，公司拟通过发行股份及支付现金方式，向杭州华澜创企业管理咨询合伙企业(有限合伙)等98名股东收购华澜微93.5031%股份，并募集配套资金。标的公司主营国产存储控制器芯片及模组、阵列控制器芯片及模组的研发、设计及销售。</t>
+          <t>饲料|公司是以酶制剂、微生态制剂的生产、研发和销售为主营业务的生物科技公司。公司生产的酶制剂产品已经广泛应用到饲料、纺织和食品等行业。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>饲料</t>
         </is>
       </c>
     </row>
@@ -2927,33 +2888,33 @@
       </c>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sz301560</t>
+          <t>sz002226</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>众捷股份</t>
+          <t>江南化工</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>33.88</v>
+        <v>5.34</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>20.0142</v>
+        <v>10.1031</v>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>数据中心液冷|公司已成功与全球热管理解决方案领导者Boyd宝德集团建立合作，给Boyd北美和欧洲正在供应数据中心液冷的相关产品。</t>
+          <t>民爆|公司主要从事工业炸药、工业雷管、工业索类等民用爆炸物品的研发、生产、销售。公司对西藏地区民爆市场的需求和发展潜力保持高度关注，下属四川宇泰特种工程技术有限公司、北方爆破科技有限公司在西藏均设有分公司。</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>数据中心液冷</t>
+          <t>民爆</t>
         </is>
       </c>
     </row>
@@ -2970,33 +2931,33 @@
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sz002494</t>
+          <t>sz002419</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>华斯股份</t>
+          <t>天虹股份</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>5.32</v>
+        <v>5.09</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>9.917400000000001</v>
+        <v>9.9352</v>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>纺织|国内裘皮服装行业龙头，拥有华斯裘皮城、毛皮交易中心等资源。</t>
+          <t>零售|公司控股股东是中国航空工业集团子公司中国航空技术国际控股有限公司旗下中国航空技术深圳有限公司，公司是国内拥有百货商场数量最多的连锁百货企业之一。</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>纺织</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
@@ -3013,33 +2974,33 @@
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sz002041</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>登海种业</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="H55" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>sz002813</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>路畅科技</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>26.38</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>10.0083</v>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>智能驾驶|公司从事汽车车载导航系统的开发、生产、销售及服务，主要产品为汽车车载数码导航信息系统。公司先后与腾讯、百度、阿里巴巴等互联网巨头达成战略合作，共同推进国内车联网事业及汽车智能化的发展。</t>
+          <t>种业|公司长期致力于玉米育种与高产栽培研究工作，是国内最早实施育繁推一体化的试点企业，公司的主要产品包括玉米杂交种、蔬菜杂交种、花卉种苗、小麦种、水稻种。公司的利润93%以上来源于玉米杂交种。</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>智能驾驶</t>
+          <t>种业</t>
         </is>
       </c>
     </row>
@@ -3056,33 +3017,33 @@
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>sh603630</t>
+          <t>sh603185</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>拉芳家化</t>
+          <t>弘元绿能</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>15.57</v>
+        <v>15.15</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>10.0353</v>
+        <v>10.0218</v>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>美容护理|公司主要从事洗护类、护肤类、彩妆类产品的研发、生产和销售。</t>
+          <t>光伏|公司已形成了包括硅料、单晶硅片、太阳能电池、太阳能组件的垂直一体化产能，向全球客户提供高效率、高质量的太阳能光伏组件产品，至今投产的高效太阳能光伏组件产品聚焦182、210大尺寸高效电池。</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>美容护理</t>
+          <t>光伏</t>
         </is>
       </c>
     </row>
@@ -3099,76 +3060,34 @@
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sz002303</t>
+          <t>sz001266</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>美盈森</t>
+          <t>宏英智能</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>6.7</v>
+        <v>39.96</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>10.0164</v>
+        <v>9.9917</v>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>电子烟|公司全资子公司东莞美盈森顺利通过电子香烟制造商吉瑞科技验厂、打样测试、综合评估的审核程序，取得其包装供应资质，为其电子烟产品提供一体化包装服务。</t>
+          <t>商业航天+液冷|1.公司智能电控产品已经批量应用于航天配套的相关领域。
+2.公司的液冷储能相关产品已实现批量应用，在数据中心应用场景下采用全浸没式液冷储能技术。</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>电子烟</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>sh605388</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>均瑶健康</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>9.983599999999999</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>乳业|公司主营常温乳酸菌系列饮品的研发、生产和销售，2011年起，公司战略进入常温乳酸菌饮品市场，推出“味动力”乳酸菌系列饮品，是国内最早生产与销售常温乳酸菌饮品的品牌企业之一。</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>乳业</t>
+          <t>商业航天, 液冷</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3210,7 +3129,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -3229,12 +3148,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh603949</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
@@ -3244,57 +3163,57 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sz002242</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh600488</t>
+          <t>sz000011</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>深物业A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz002242</t>
+          <t>sh600241</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh600241</t>
+          <t>sz301190</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>善水科技</t>
         </is>
       </c>
     </row>
@@ -3304,12 +3223,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sz000011</t>
+          <t>sh603200</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>上海洗霸</t>
         </is>
       </c>
     </row>
@@ -3319,12 +3238,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sh600032</t>
+          <t>sh605388</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>浙江新能</t>
+          <t>均瑶健康</t>
         </is>
       </c>
     </row>
@@ -3334,12 +3253,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sz301190</t>
+          <t>sz002866</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>善水科技</t>
+          <t>传艺科技</t>
         </is>
       </c>
     </row>
@@ -3349,12 +3268,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sz002912</t>
+          <t>sz002058</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>紫竹高科</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>sh605303</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>园林股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>sh603188</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>亚邦股份</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="94" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="255" customWidth="1" min="10" max="10"/>
+    <col width="209" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,366 +552,384 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.0884</v>
+        <v>1.161</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz000710</t>
+          <t>sz002058</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>贝瑞基因</t>
+          <t>紫竹高科</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>10.87</v>
+        <v>22.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.0202</v>
+        <v>10</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>基因检测+AI医疗|1.公司依托其具有自主知识产权的cSMART核心技术为支撑，选择ctDNA作为肿瘤液体活检指标，开启了临床无创肿瘤基因检测的全新模式。
-2.公司自主研发NLPearl遗传疾病人工智能临床决策支持系统、CNVisi智能报告解读系统，为科研和临床工作者提供智能决策支持。公司的CNVisi™利用人工智能深度学习算法，挖掘20+权威公共数据库、百万自有CNV大数据以及20多万份CNV-seq临床实践报告，构建7大临床解读知识库，精准注释解读、一键查询信息、自定义设置参数、AI智能撰写报告。</t>
+          <t>铝塑膜|旗下紫江新材专注铝塑膜产品的研发，同时积极布局固态电池用铝塑膜产品，以适应未来固态电池行业发展带动的新增需求。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>基因检测, AI医疗</t>
+          <t>铝塑膜</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.0884</v>
+        <v>1.161</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh688185</t>
+          <t>sz002866</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">康希诺  </t>
+          <t>传艺科技</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>102.64</v>
+        <v>18.59</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>20.0047</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>创新型疫苗|公司是一家致力于研发、生产与销售的创新型疫苗企业。在一批疫苗领域资深科学家和具备多年国际大型制药公司从业背景的资深技术专家的带领下，公司快速推进一系列国内创新疫苗的研发，研发管线涵盖预防脑膜炎、埃博拉病毒病、百白破、肺炎、结核病、带状疱疹等多个适应症的临床接种量较大的重磅疫苗。</t>
+          <t>固态电池+PCB|1.公司的半固态、固态电池处于研发阶段。
+2.公司专注于为行业领先客户提供全方位FPC产品及服务，根据下游不同终端产品对于FPC的定制化要求，为客户提供涵盖产品设计、研发和销售各个环节的整体解决方案。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>创新型疫苗</t>
+          <t>固态电池, PCB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.0884</v>
+        <v>1.161</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh603538</t>
+          <t>sh603200</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">美诺华  </t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>28.59</v>
+        <v>49.21</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.0038</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
+        <v>9.991099999999999</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>CXO|公司正在加速打造CDMO一站式综合服务平台，为制药企业提供贯穿药品临床前研发、临床试验阶段以及上市审批、商业化生产等环节的综合性研发生产服务。</t>
+          <t>固态电池+液冷|1.公司生产的固态电解质粉体材料可以应用于锂离子固态电池，多形态固态电解质粉体材料（含油性、水性、浆料）年产50吨级产线主要采用的是氧化物技术路线，公司储备了硫化物、氯化物等固态电解质的其它固态电解质粉体技术路线。
+2.公司面向腾讯、华为、中国移动等重点客户数据中心提供循环水/空气蒸发冷却等专业服务。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>CXO</t>
+          <t>固态电池, 液冷</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.0884</v>
+        <v>1.161</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh603590</t>
+          <t>sh603928</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>康辰药业</t>
+          <t>兴业股份</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>32.11</v>
+        <v>14.38</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.0034</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+        <v>10.023</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司是一家以创新药研发为核心、以临床价值为导向，集研发、生产和销售于一体的创新药企业。公司主要产品为“密盖息”和“苏灵”。</t>
+          <t>固态电池+光刻胶|1.公司已成功研发酚醛树脂，酚醛树脂在电池负极材料的应用有着显著的进步，是未来固态电池、钾离子电池等颠覆性技术的“核心材料基石”。
+2.公司已研发成功半导体光刻胶用酚醛树脂、特种半导体封装用酚醛树脂等一批特种有机合成功能新材料。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>固态电池, 光刻胶</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2.0884</v>
+        <v>1.161</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh688806</t>
+          <t>sh603906</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>泰诺麦博-U</t>
+          <t>龙蟠科技</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30.67</v>
+        <v>20.94</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>19.9922</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+        <v>9.979000000000001</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>创新药|泰诺麦博是一家面向全球市场、致力于血液制品替代疗法的创新生物制药企业，专注于全人源单抗新药的开发、制造与商业化。</t>
+          <t>固态电池+液冷|1.公司全资子公司三金锂电主要专注于固态电池前驱体的开发，已建成一期5000吨产能。针对固态电池的高镍前驱体以及富锂锰基前驱体已通过客户小试认证，部分超高镍前驱体产品也正在和客户进行联合开发。
+2.子公司迪克化学发布第二代算力中心冷却液。该冷却液以乙二醇和丙二醇为基础，通过添加剂破解超大规模数据中心高效散热难题，支撑AI算力稳定运行。该产品目前以国内客户为主，围绕行业头部企业的算力中心推广应用。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>固态电池, 液冷</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.0884</v>
+        <v>1.161</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz000504</t>
+          <t>sz002733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>南华生物</t>
+          <t>雄韬股份</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>12.42</v>
+        <v>18.89</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.0089</v>
+        <v>10.0175</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>细胞治疗|公司是目前国内一家国资控股的干细胞、免疫细胞及组织工程产业主板上市公司，“生物医药”板块业务包括干细胞储存服务、化妆品的生产和销售、医疗器械设备及耗材的代理和销售。</t>
+          <t>固态电池|公司会持续关注固态电池与机器人、低空飞行器技术融合的发展趋势和相关的应用；结合60AH的容量与机器人、低空飞行器的电源匹配需求，60Ah固态电池可以用在较大型的机器人和中大型的低空飞行器。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>细胞治疗</t>
+          <t>固态电池</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.0884</v>
+        <v>1.161</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz002755</t>
+          <t>sz002805</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>奥赛康</t>
+          <t>丰元股份</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>13.55</v>
+        <v>17.67</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.9838</v>
+        <v>10.0249</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司是一家创新与研发驱动的医药制造企业，公司药物治疗领域主要覆盖消化、抗肿瘤、抗感染、慢性病四大领域，业务涵盖原料药及制剂的研发、生产、销售，在中国医药细分市场具有较高的品牌影响力。</t>
+          <t>固态电池|公司对固态电池硫化物正极材料有技术储备，还参股了深耕于固态电池领域的中科深蓝汇泽新能源(常州)有限责任公司。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>固态电池</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.0884</v>
+        <v>1.161</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9月29日，Summit宣布，阿斯利康将出资20亿美元对该公司进行战略股权投资，并将主导推进依沃西联合阿斯利康的Sonesitatug Vedotin用于治疗多种胃肠道肿瘤的临床研究。</t>
+          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh603127</t>
+          <t>920627.BJ</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>昭衍新药</t>
+          <t>力王股份</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>49.3</v>
+        <v>17.83</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9.9955</v>
+        <v>29.9563</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>CXO+AI制药|1.公司专注于药物全生命周期的安全性评价和监测，建立了独具特色的药物非临床研究服务、临床试验及相关服务。
-2.公司已将基于AI和行为组学的全自动行为学检测系统应用于多种CNS疾病模型如阿尔茨海默症、帕金森症和疼痛的评价中，支持了多个前沿药物如细胞治疗、基因治疗药物的非临床申报。</t>
+          <t>固态电池|公司与清华大学深圳国际研究生院合作项目为低成本高功率锂离子电池和下一代高安全固态锂电池的研究与开发，对锂离子电池的关键技术进行合作开发，公司负责电池正极配方优化、正负极制备工艺的开发；清华大学深圳国际研究生院负责电解质离子运输机制的研究；双方共同完成低成本高功率电池的集成设计与开发。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>CXO, AI制药</t>
+          <t>固态电池</t>
         </is>
       </c>
     </row>
@@ -922,40 +940,37 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.1294</v>
+        <v>1.161</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
+          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz002058</t>
+          <t>sz300530</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>紫竹高科</t>
+          <t>领湃科技</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20.2</v>
+        <v>24.08</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.0218</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>19.9801</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>固态电池|旗下紫江新材专注铝塑膜产品的研发，同时积极布局固态电池用铝塑膜产品，以适应未来固态电池行业发展带动的新增需求。</t>
+          <t xml:space="preserve">固态电池|公司注重基础研发和前瞻技术开发，已经完成了NCM811电池化学体系研发，固态电解质及固态电池、干法电极及其制备技术的基础试验，相关专利正在申请或已获得授权。
+</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -967,418 +982,401 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.1294</v>
+        <v>-1.6289</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
+          <t>据报道，英伟达讨论再向人形机器人公司Figure投资10亿美元。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz002866</t>
+          <t>sz002242</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>16.9</v>
+        <v>13.75</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10.026</v>
+        <v>10</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天4板</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>固态电池+PCB|1.公司的半固态、固态电池处于研发阶段。
-2.公司专注于为行业领先客户提供全方位FPC产品及服务，根据下游不同终端产品对于FPC的定制化要求，为客户提供涵盖产品设计、研发和销售各个环节的整体解决方案。</t>
+          <t>AI机器人|公司持有深思考人工智能机器人科技（北京）有限公司7.92%的股份，旗下产品包括AI机器人。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>固态电池, PCB</t>
+          <t>AI机器人</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.1294</v>
+        <v>-1.6289</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
+          <t>据报道，英伟达讨论再向人形机器人公司Figure投资10亿美元。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh603200</t>
+          <t>sh601956</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>东贝集团</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>44.74</v>
+        <v>5.52</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.0074</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.9602</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>固态电池+液冷|1.公司生产的固态电解质粉体材料可以应用于锂离子固态电池，多形态固态电解质粉体材料（含油性、水性、浆料）年产50吨级产线主要采用的是氧化物技术路线，公司储备了硫化物、氯化物等固态电解质的其它固态电解质粉体技术路线。
-2.公司面向腾讯、华为、中国移动等重点客户数据中心提供循环水/空气蒸发冷却等专业服务。</t>
+          <t>机器人|2025年4月17日公司在互动平台表示，公司转子压缩机具备量产能力，正在进行客户匹配性能测试。另外，公司在洗衣机电机、空调电机、机器人关节电机等领域均有相关技术研发储备。人形机器人关节电机目前还处于研发测试阶段。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>固态电池, 液冷</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.1294</v>
+        <v>-1.6289</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
+          <t>据报道，英伟达讨论再向人形机器人公司Figure投资10亿美元。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603928</t>
+          <t>sh600400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>兴业股份</t>
+          <t>红豆股份</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>13.07</v>
+        <v>3.62</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.0168</v>
+        <v>10.0304</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>固态电池+光刻胶|1.公司已成功研发酚醛树脂，酚醛树脂在电池负极材料的应用有着显著的进步，是未来固态电池、钾离子电池等颠覆性技术的“核心材料基石”。
-2.公司已研发成功半导体光刻胶用酚醛树脂、特种半导体封装用酚醛树脂等一批特种有机合成功能新材料。</t>
+          <t>机器人+纺织|1.参股无锡福芯机器人有限公司经营范围包含：服务消费机器人制造、智能机器人销售、人工智能硬件销售、智能机器人的研发、人工智能应用软件开发、人工智能行业应用系统集成服务、大数据服务等。
+2.公司的主营业务为男装的生产与销售。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>固态电池, 光刻胶</t>
+          <t>机器人, 纺织</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.1294</v>
+        <v>2.1979</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>工信部等七部门联合制定的《新型电池产业发展“十五五”规划》9月28日正式发布。《规划》提出，目标是到2030年，全固态电池初步实现规模化应用。</t>
+          <t>Clarksons数据显示，第三季度VLCC平均收益达到277,995美元/天，进入10月初后部分航线收益已经超过160万美元/天，市场整体收益水平一度超过60万美元/天。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh603906</t>
+          <t>sh600026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>龙蟠科技</t>
+          <t>中远海能</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>19.04</v>
+        <v>22.62</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>9.994200000000001</v>
+        <v>10.0195</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>固态电池+液冷|1.公司全资子公司三金锂电主要专注于固态电池前驱体的开发，已建成一期5000吨产能。针对固态电池的高镍前驱体以及富锂锰基前驱体已通过客户小试认证，部分超高镍前驱体产品也正在和客户进行联合开发。
-2.子公司迪克化学发布第二代算力中心冷却液。该冷却液以乙二醇和丙二醇为基础，通过添加剂破解超大规模数据中心高效散热难题，支撑AI算力稳定运行。该产品目前以国内客户为主，围绕行业头部企业的算力中心推广应用。</t>
+          <t>油运|公司主营业务为从事国际和中国沿海原油及成品油运输、国际液化天然气(LNG)运输以及国际化学品运输，是中国沿海原油和成品油运输领域的龙头企业。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>固态电池, 液冷</t>
+          <t>油运</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-0.72</v>
+        <v>2.1979</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>浙商证券指出，海外端，特斯拉开启新一轮人形机器人量产审厂，释放订单及产能扩建信号，四季度为特斯拉人形机器人产能爬坡关键验证期。</t>
+          <t>Clarksons数据显示，第三季度VLCC平均收益达到277,995美元/天，进入10月初后部分航线收益已经超过160万美元/天，市场整体收益水平一度超过60万美元/天。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sh601975</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>招商南油</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>12.89</v>
+        <v>4.97</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9.982900000000001</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>9.9558</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
+          <t>油运|公司是招商局集团旗下从事油轮运输的专业化公司，市场定位为全球石化产品的运输服务商。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>油运</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.72</v>
+        <v>1.839</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>浙商证券指出，海外端，特斯拉开启新一轮人形机器人量产审厂，释放订单及产能扩建信号，四季度为特斯拉人形机器人产能爬坡关键验证期。</t>
+          <t>布伦特原油突破101美元/桶，日内涨0.86%；上期所燃油主力合约大涨16%。周二欧洲天然气价格上涨，涨幅最高达5.5%，至每兆瓦时77.55欧元。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz002242</t>
+          <t>sh600617</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>国新能源</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>12.5</v>
+        <v>3.74</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.0352</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>AI机器人|公司持有深思考人工智能机器人科技（北京）有限公司7.92%的股份，旗下产品包括AI机器人。</t>
+          <t>天然气|山西最大的天然气管网运营企业，管网建设方面公司在省内主要业务区域已取得绝对优势地位，省级天然气管网5000余公里，年管输涉及能力超过255亿立方米，管网覆盖全省11市104县（市、区）。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>AI机器人</t>
+          <t>天然气</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>天然气</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.72</v>
+        <v>1.839</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>浙商证券指出，海外端，特斯拉开启新一轮人形机器人量产审厂，释放订单及产能扩建信号，四季度为特斯拉人形机器人产能爬坡关键验证期。</t>
+          <t>布伦特原油突破101美元/桶，日内涨0.86%；上期所燃油主力合约大涨16%。周二欧洲天然气价格上涨，涨幅最高达5.5%，至每兆瓦时77.55欧元。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz002164</t>
+          <t>sz002490</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>宁波东力</t>
+          <t>山东墨龙</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>13.26</v>
+        <v>7.6</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.0415</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>9.9855</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>机器人+风电|1.公司的产品包括行星减速器等，杭州湾电机、减速器部分车间已投入生产。
-2.公司研发的风电齿轮箱应用于风电市场。</t>
+          <t>油气|全产业链石油钻采装备制造商，主要产品包括油气开采用管、流体及结构用管、抽油机、抽油泵、抽油杆、钻机用缸套、阀门散件及大型铸锻件等。公司产品主要用于石油、天然气、煤层气、页岩气等行业。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>机器人, 风电</t>
+          <t>油气</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>锂电池</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-0.72</v>
+        <v>0.2286</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>浙商证券指出，海外端，特斯拉开启新一轮人形机器人量产审厂，释放订单及产能扩建信号，四季度为特斯拉人形机器人产能爬坡关键验证期。</t>
+          <t>工业和信息化部、国家发展改革委等七部门近日联合印发《新型电池产业发展“十五五”规划》。《规划》提出到2030年，我国新型电池产业规模实现稳步增长的目标。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh600592</t>
+          <t>sh600241</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>龙溪股份</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>16.2</v>
+        <v>10.69</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.9796</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+        <v>9.9794</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>机器人+商业航天|1.公司的关节轴承是机器人的主要配套件。
-2.公司主营产品关节轴承主要应用于工程机械、载重汽车和航空航天等领域。</t>
+          <t>锂电池|公司旗下九夷锂能主要经营锂离子电池、电池组的研发、生产、制造、系统集成、销售和服务，目标市场定位于电动工具、个人护理、家庭电子、消费品等小动力领域。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>机器人, 商业航天</t>
+          <t>锂电池</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>锂电池</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-0.72</v>
+        <v>0.2286</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>浙商证券指出，海外端，特斯拉开启新一轮人形机器人量产审厂，释放订单及产能扩建信号，四季度为特斯拉人形机器人产能爬坡关键验证期。</t>
+          <t>工业和信息化部、国家发展改革委等七部门近日联合印发《新型电池产业发展“十五五”规划》。《规划》提出到2030年，我国新型电池产业规模实现稳步增长的目标。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh605288</t>
+          <t>sh605378</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>凯迪股份</t>
+          <t>野马电池</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>71.83</v>
+        <v>17.27</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>10</v>
@@ -1386,12 +1384,13 @@
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司主要产品为线性驱动系统，可以应用在机器人上。</t>
+          <t xml:space="preserve">锂电池|公司销售的锂电池主要为纽扣电池，应用于微型电子产品等。
+</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>锂电池</t>
         </is>
       </c>
     </row>
@@ -1402,45 +1401,41 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.4674</v>
+        <v>-0.1895</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>根据农业农村部监测数据，2026年9月第3周，全国10个主产省生鲜乳均价为3.08元/公斤（环比微涨0.3%，同比上涨1.7%）。8月份主产省均价为3.06元/公斤。</t>
+          <t>记者8日从国家税务总局获悉，增值税发票最新数据显示，国庆假期，全国服务消费旺盛，相关行业日均销售收入同比增长19.5%。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh605388</t>
+          <t>sz000869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>均瑶健康</t>
+          <t>张  裕Ａ</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>7.39</v>
+        <v>18.76</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.9702</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0293</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>乳业|公司主营常温乳酸菌系列饮品的研发、生产和销售，2011年起，公司战略进入常温乳酸菌饮品市场，推出“味动力”乳酸菌系列饮品，是国内最早生产与销售常温乳酸菌饮品的品牌企业之一。</t>
+          <t>葡萄酒|公司是国内葡萄酒行业龙头，拥有葡萄酒、白兰地、起泡酒等系列产品百余品种，涵盖高、中、低各档次。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>乳业</t>
+          <t>葡萄酒</t>
         </is>
       </c>
     </row>
@@ -1451,1115 +1446,1095 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.4674</v>
+        <v>-0.1895</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>根据农业农村部监测数据，2026年9月第3周，全国10个主产省生鲜乳均价为3.08元/公斤（环比微涨0.3%，同比上涨1.7%）。8月份主产省均价为3.06元/公斤。</t>
+          <t>记者8日从国家税务总局获悉，增值税发票最新数据显示，国庆假期，全国服务消费旺盛，相关行业日均销售收入同比增长19.5%。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh600059</t>
+          <t>sz002702</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>古越龙山</t>
+          <t>海欣食品</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>12.27</v>
+        <v>5.92</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.0448</v>
+        <v>10.0372</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>黄酒|公司所从事的主要业务是黄酒的制造、销售及研发，生产黄酒原酒、黄酒瓶装酒及少量果酒、白酒等，主要产品古越龙山、女儿红、状元红、沈永和、鉴湖牌等绍兴黄酒是中国首批国家地理标志产品。其中古越龙山是中国黄酒行业标志性品牌、唯一钓鱼台国宾馆国宴专用黄酒、“亚洲品牌500强”中唯一入选的黄酒品牌。</t>
+          <t>预制菜|主要从事冷冻和常温鱼肉制品和肉制品的生产和销售，包括各类鱼丸等。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>黄酒</t>
+          <t>预制菜</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>烟草</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.4674</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>根据农业农村部监测数据，2026年9月第3周，全国10个主产省生鲜乳均价为3.08元/公斤（环比微涨0.3%，同比上涨1.7%）。8月份主产省均价为3.06元/公斤。</t>
+          <t>7月28日国家烟草专卖局挂出《加热卷烟》强制性国家标准征求意见稿，意见反馈窗口到9月26日关闭。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz001318</t>
+          <t>sz002951</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>阳光乳业</t>
+          <t>金时科技</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>13.04</v>
+        <v>17.17</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.0422</v>
+        <v>9.993599999999999</v>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>乳业|公司专注于乳制品及乳饮料的研发、生产和销售，并以低温乳制品、低温乳饮料为主打产品。公司针对儿童提高免疫力开发的“初乳” 产品。公司从事液态乳、含乳饮料等产品的研发、生产、销售。</t>
+          <t>光纤+烟草|1.公司通过智芯一号股权基金间接参股苏州易缆微，易缆微是一家光纤通信产品研发生产商，致力于光纤通信系统、光网络系统、光电传感系统、物联网系统技术研究和试验发展及进出口业务。
+2.公司的主营业务为烟标等包装印刷品的研发、生产和销售，目前主要的包装印刷产品为烟标，是卷烟消费品的配套包装制品，具有防伪商标、外观形象、包装保护等功能。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>乳业</t>
+          <t>光纤, 烟草</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>烟草</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.4674</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>根据农业农村部监测数据，2026年9月第3周，全国10个主产省生鲜乳均价为3.08元/公斤（环比微涨0.3%，同比上涨1.7%）。8月份主产省均价为3.06元/公斤。</t>
+          <t>7月28日国家烟草专卖局挂出《加热卷烟》强制性国家标准征求意见稿，意见反馈窗口到9月26日关闭。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh603919</t>
+          <t>sz002565</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">金徽酒  </t>
+          <t>顺灏股份</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>17.4</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9.987400000000001</v>
+        <v>9.9526</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>白酒|公司代表产品有“金徽二十八年、金徽十八年、世纪金徽星级、柔和金徽、金徽正能量”等，营销网络已辐射甘肃、陕西、宁夏、新疆、西藏、内蒙、青海等西北市场，为西北地区强势白酒品牌。</t>
+          <t>商业航天+烟草|1.公司2025年6月以1.1亿元人民币投资北京轨道辰光科技有限公司，持股比例为19.30%。轨道辰光的主要业务是通过将算力卫星发射至晨昏轨道，组建太空数据中心，为客户提供算力服务，其经营范围包括微小卫星生产制造、微小卫星科研试验、互联网信息服务等。轨道辰光首颗试验星算力规模预计25p。
+2.公司的主要产品为真空镀铝纸及烟标产品等，主要下游客户为烟草生产企业和烟标印刷企业。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>商业航天, 烟草</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.6698</v>
+        <v>-1.9448</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>中央气象台消息，今年下半年以来最强冷空气昨天夜间开始影响我国，未来三天将自北向南给中东部地区带来大风降温，10月1日早晨最低气温0℃线，将南压至华北北部和黑龙江中部一带。</t>
+          <t>《科创板日报》记者独家获悉，亚马逊云科技旗下大模型服务平台Amazon Bedrock官宣接入智谱GLM-5.3，AWS基于模型调用量与智谱进行收入分成。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh600356</t>
+          <t>sz002774</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>恒丰纸业</t>
+          <t>快意电梯</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>11.46</v>
+        <v>19.04</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.980799999999999</v>
+        <v>9.994200000000001</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>电力+卷烟纸|1.公司旗下恒丰热电经营范围包括电力、热力产品生产等。
-2.公司主导产品为卷烟纸、滤嘴棒纸、铝箔衬纸和水松纸等，是国内卷烟辅料生产基地，五大卷烟辅料供应商之一。</t>
+          <t>电梯+AI应用|1.公司是全球范围内提供电梯综合解决方案的优秀民族电梯供应商和服务商之一。主要从事电梯、自动扶梯和自动人行道的设计研发、制造、销售及产品的安装、改造和维保服务。
+2.公司一直重视技术研发和创新，大力投入对系统、产品、服务等多维度的智能化、数字化建设；产品及技术方面，各种无接触呼梯产品、智能派梯系统、AI智能监控等多项技术已实际应用。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>电力, 卷烟纸</t>
+          <t>电梯, AI应用</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.6698</v>
+        <v>-1.9448</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>中央气象台消息，今年下半年以来最强冷空气昨天夜间开始影响我国，未来三天将自北向南给中东部地区带来大风降温，10月1日早晨最低气温0℃线，将南压至华北北部和黑龙江中部一带。</t>
+          <t>《科创板日报》记者独家获悉，亚马逊云科技旗下大模型服务平台Amazon Bedrock官宣接入智谱GLM-5.3，AWS基于模型调用量与智谱进行收入分成。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz000692</t>
+          <t>sz002869</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>惠天热电</t>
+          <t>金溢科技</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>4.59</v>
+        <v>19.14</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.0719</v>
+        <v>10</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>电力|惠天热电公告称，公司拟投资建设全胜热电配套长距离互联互通供热工程项目，计划总投资约14.05亿元。该项目旨在将全胜热电项目产生的热量输送至铁西热网，形成热电联产供热模式，提升区域供热保障能力。项目尚需提交股东会审议。</t>
+          <t>智能驾驶+AI应用|1.公司是智慧交通领域领先的数智化解决方案及产品提供商，打造了完整的车、路、云产品体系,包括车载V2X系列产品、路端V2X边端系统集成产品等。
+2.9月28日，据金溢科技官微，针对新能源商用车及储能电站热管理需求，金溢科技推出AI智能热管理液冷机组全栈解决方案。该方案覆盖商用车（3～120kW）与储能（3～100kW）双产品线。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>智能驾驶, AI应用</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.6698</v>
+        <v>-1.966</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>中央气象台消息，今年下半年以来最强冷空气昨天夜间开始影响我国，未来三天将自北向南给中东部地区带来大风降温，10月1日早晨最低气温0℃线，将南压至华北北部和黑龙江中部一带。</t>
+          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sh605011</t>
+          <t>sh600812</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>杭州热电</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>19.21</v>
+        <v>5.48</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10.0229</v>
+        <v>10.0402</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>电力|公司的最终控制人为杭州市人民政府。公司是一家主营工业园区热电联产、集中供热的节能环保型企业。公司提供的主要产品是蒸汽与电力。</t>
+          <t>链霉素|公司青霉素系列、头孢系列产品品种齐全，覆盖了原料药到制剂的大部分品种，形成了从发酵原料到半合成原料药再到制剂的完整产品链。是国内硫酸链霉素原料药及注射剂的核心生产企业。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>链霉素</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.6698</v>
+        <v>-1.966</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>中央气象台消息，今年下半年以来最强冷空气昨天夜间开始影响我国，未来三天将自北向南给中东部地区带来大风降温，10月1日早晨最低气温0℃线，将南压至华北北部和黑龙江中部一带。</t>
+          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh600131</t>
+          <t>sh600513</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>国网信通</t>
+          <t>联环药业</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>15.39</v>
+        <v>16.6</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10.0071</v>
+        <v>10.0066</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>电力+智能电网|1.公司是集发配售电于一体的电力企业，拥有区域性独立配电网络。公司电力来源为：一是自有水电站和并网小水电发电量通过自有电网销售给终端客户；二是通过联网线路从国家电网四川省电力公司等单位趸购电量。
-2.公司围绕电力发-输-变-配-用-调各环节、源网荷储全场景，融合运用“大云物移智”等创新技术，拓展覆盖规划咨询、软件研发、工程实施、系统集成、运营运维等信息通信全产业链。</t>
+          <t>创新药|主要产品有创新药物爱普列特片(川流)，新药依巴斯汀片(苏迪)、非洛地平片(联环尔定)、非洛地平缓释胶囊(联环笑定)等二十多个。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>电力, 智能电网</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>生物质能</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.5402</v>
+        <v>1.8217</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>我国将从10月1日起对居民使用新发放商业性个人住房贷款购房实施贴息。可享受贴息的贷款规模最高可达100万元，财政部门给予年化1个百分点的贴息，贴息期限最长5年。</t>
+          <t>泰国政府正考虑下调生物燃料消费税，压低价格并拉动消费。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz000011</t>
+          <t>sh688196</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>卓越新能</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>12.24</v>
+        <v>36.12</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>9.973000000000001</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>物业管理|公司经过多年发展，已形成了以房地产开发为主业，物业管理、物业租赁、出租汽车营运、餐饮服务、物流仓储、工程监理等为辅的跨行业、多元化的经营格局。</t>
+          <t>生物柴油|公司是国内第一家从事废弃油脂制备生物柴油的技术研发并率先实现工业化生产的企业，二十年来深耕生物柴油和生物基材料行业，是目前国内产销规模最大、出口量最多的生物柴油生产企业，并逐步形成以生物柴油为主，衍生深加工生物基材料的“生物质能化一体化”的产业布局。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>物业管理</t>
+          <t>生物柴油</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.5402</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>我国将从10月1日起对居民使用新发放商业性个人住房贷款购房实施贴息。可享受贴息的贷款规模最高可达100万元，财政部门给予年化1个百分点的贴息，贴息期限最长5年。</t>
-        </is>
-      </c>
+        <v>-0.8703000000000001</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz002188</t>
+          <t>sz002630</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>中天服务</t>
+          <t>*ST华西</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>6.4</v>
+        <v>1.57</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>9.9656</v>
+        <v>9.7902</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>物业管理+旅游酒店|1.公司2021年主营业务变更为物业管理服务。物业管理服务指对住宅及非住宅的建筑及配套进行管理维护。
-2.旗下东阳市凤凰谷天澜酒店拥有203间客房及800平方米无柱式天澜宴会厅，配套健身房、恒温泳池等休闲设施。</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>物业管理, 旅游酒店</t>
-        </is>
-      </c>
+          <t>ST股 | 目前公司核电业务主要集中在核三废处理领域，为业主项目提供核废物处理系统以及配套件。</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>房地产概念</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.5402</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>我国将从10月1日起对居民使用新发放商业性个人住房贷款购房实施贴息。可享受贴息的贷款规模最高可达100万元，财政部门给予年化1个百分点的贴息，贴息期限最长5年。</t>
-        </is>
-      </c>
+        <v>-0.8703000000000001</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh600663</t>
+          <t>sh603189</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">陆家嘴  </t>
+          <t xml:space="preserve">*ST网达 </t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>10.11</v>
+        <v>10.2</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.0109</v>
+        <v>10.0324</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>ST股 | 1.公司以AI大模型赋能全媒体的内容生产、运营、分发为主要着力点，重构现有内容运营编辑系统、媒资管理系统，研发了系列智能化内容生产系统。
+2.公司是阿里云的核心合作伙伴，在广电融媒体端有广泛深入的技术合作。</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>sh600825</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>10.0483</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>8天8板</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>sh605303</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>园林股份</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>10.014</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>并购重组|园林股份公告称，公司拟通过发行股份及支付现金方式，向杭州华澜创企业管理咨询合伙企业(有限合伙)等98名股东收购华澜微93.5031%股份，并募集配套资金。标的公司主营国产存储控制器芯片及模组、阵列控制器芯片及模组的研发、设计及销售。</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>sh600663</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">陆家嘴  </t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>9.9901</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>房地产+参股券商|1.公司控股股东为上海陆家嘴（集团）有限公司。公司坚持以商业地产为核心，以金融服务为纽带，以商业零售为延伸。
 2.子公司陆金发持有爱建证券51.14%股权。</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>房地产, 参股券商</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>锂电池</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>-0.172</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>中信证券研报称，从电池与能源管理产业链2026年上半年及2026年第二季度经营结果来看，下游需求保持高景气，产业链多数环节收入实现增长，盈利修复进一步向中上游扩散。</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>sh600241</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>时代万恒</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>9.954800000000001</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>锂电池|公司旗下九夷锂能主要经营锂离子电池、电池组的研发、生产、制造、系统集成、销售和服务，目标市场定位于电动工具、个人护理、家庭电子、消费品等小动力领域。</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>锂电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>锂电池</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>-0.172</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>中信证券研报称，从电池与能源管理产业链2026年上半年及2026年第二季度经营结果来看，下游需求保持高景气，产业链多数环节收入实现增长，盈利修复进一步向中上游扩散。</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>sz002388</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>新亚制程</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>10.0363</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>锂电池+半导体|1.杉杉新材料为新亚新能源的控股子公司、公司的间接控股公司。杉杉新材料具有较好的市场竞争力和盈利能力，现有电解液产能3万吨、六氟磷酸锂产能2000吨，在建电解液产能3万吨、六氟磷酸锂产能4000吨。
-2.公司的底部填充胶COO602系列用于BGA、CSP和Flip chip底部填充制程，不仅可以助力电子产品的抗跌落性，还具有一定的导热的可靠性，在产品封装解决方案中起到非常重要的作用。</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>锂电池, 半导体</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>锂电池</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>-0.172</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>中信证券研报称，从电池与能源管理产业链2026年上半年及2026年第二季度经营结果来看，下游需求保持高景气，产业链多数环节收入实现增长，盈利修复进一步向中上游扩散。</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>sh603948</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>建业股份</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>21.36</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>9.989699999999999</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>锂电池+半导体|1.公司三乙胺可用于锂电池电解液的制备。
-2.公司主营产品之一的超纯氨是超净高纯电子化学品，是超大规模集成电路（即芯片）制作过程中的关键性基础化工材料之一，主要用于芯片的清洗、蚀刻、掺杂和沉淀工艺。超纯氨是微电子氮化硅掩蔽膜的主要原材料。</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>锂电池, 半导体</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>-0.3621</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>华为常务董事余承东日前表示，华为和江淮汽车合作的尊界SUV新车2027年年初有望上市。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh600081</t>
+          <t>sz300522</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>东风科技</t>
+          <t>世名科技</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>11.89</v>
+        <v>16.56</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>9.9907</v>
+        <v>20</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>汽车零部件|公司主营业务为汽车零部件生产、制造、销售相关业务，涵盖座舱与车身系统、制动及智能驾驶系统、电驱动系统、热管理系统、动力总成部件系统。</t>
+          <t>PCB树脂|公司布局的高纯UV单体与电子碳氢树脂均作为PCB产业的上游，其中UV单体主要应用场景为PCB干膜光刻胶以及PCB油墨（线路油墨、阻焊油墨），电子碳氢树脂主要应用场景为PCB基础原料高速覆铜板。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>汽车零部件</t>
+          <t>PCB树脂</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>-0.3621</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>华为常务董事余承东日前表示，华为和江淮汽车合作的尊界SUV新车2027年年初有望上市。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz002454</t>
+          <t>sh603863</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>松芝股份</t>
+          <t>松炀资源</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>5.61</v>
+        <v>13.62</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10</v>
+        <v>10.0162</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>汽车零部件|公司非常重视新能源汽车发展情况，在大中型客车空调业务板块，新能源客车空调发货量已占客车空调发货量的50%以上。</t>
+          <t>造纸|公司主要从事环保再生纸的研发、生产和销售，是一家集废纸回收、环保造纸及涂布成型于一体，形成资源再生利用价值链的造纸企业。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>汽车零部件</t>
+          <t>造纸</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>-0.3621</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>华为常务董事余承东日前表示，华为和江淮汽车合作的尊界SUV新车2027年年初有望上市。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sz300893</t>
+          <t>sz002687</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>松原安全</t>
+          <t>乔治白</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>15.13</v>
+        <v>6.14</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>19.9841</v>
+        <v>10.0358</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>汽车零部件|公司积极协同整车厂新能源汽车的汽车被动安全系统设计，已成功为吉利帝豪EV、奇瑞新能源eQ1、上汽通用五菱E200\E100等重要新能源车型配套高端汽车安全带总成。</t>
+          <t>纺织|公司主要从事“乔治白”“giuseppe”品牌的职业装生产和销售。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>汽车零部件</t>
+          <t>纺织</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>-0.4523</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>OpenAI最新推出了一款全天候在线的智能体“Dot”，Dot由GPT‑6 Astra驱动，能够操作电脑从各种已连接的应用程序中提取信息，用以开展研究、起草文件、开发软件等。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh605577</t>
+          <t>sh603137</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>恒尚节能</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>16.28</v>
+        <v>19.56</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10</v>
+        <v>10.0112</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧+出版传媒|1.公司首部AI漫剧《穿越1988》完成170集制作上线，全网播放量突破1.2亿，红果热度值超4000万。
-2.公司地处哈尔滨，是我国东北地区出版发行行业的领先企业之一，公司拥有出版物“编、印、发”完整的产业链。</t>
+          <t>存储芯片|恒尚节能公告称，公司拟通过发行股份及支付现金方式购买深圳市金胜电子科技有限公司100%股权，并募集配套资金。公司股票将于2026年7月1日开市起复牌。标的公司主要从事存储器的研发设计、生产制造及销售，主要品牌包括KingSpec金胜维、YANSEN元存、OneBoom猛犸纪、MemoStone意石、Mixage采云纪等。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧, 出版传媒</t>
+          <t>存储芯片</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>-0.4523</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>OpenAI最新推出了一款全天候在线的智能体“Dot”，Dot由GPT‑6 Astra驱动，能够操作电脑从各种已连接的应用程序中提取信息，用以开展研究、起草文件、开发软件等。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz002316</t>
+          <t>sh605298</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>亚联发展</t>
+          <t>必得科技</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>4.95</v>
+        <v>44.97</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10</v>
+        <v>10.0049</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>AI应用|公司基于华为Atlas人工智能计算平台开发的“无人值守变电站智能运检系统V6”及基于华为Tai Shan 200系列开发的“变电站智能网关系统V1.1”获得华为技术认证书，并且在南方电网顺利投放使用。</t>
+          <t>股权转让|2026年6月14日公告，公司实际控制人王坚群、刘英与衢州启信企业管理合伙企业（有限合伙）签署了《股份转让协议》，王坚群和刘英拟以53.44元/股的价格向衢州启信转让其持有的公司合计1242.45万股股份（占公司总股本的6.6140%），股份转让价款合计6.64亿元。本次股份转让完成后，公司实际控制人由王坚群、刘英变更为王坚群，公司控股股东不变，仍为王坚群。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>股权转让</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>-0.4523</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>OpenAI最新推出了一款全天候在线的智能体“Dot”，Dot由GPT‑6 Astra驱动，能够操作电脑从各种已连接的应用程序中提取信息，用以开展研究、起草文件、开发软件等。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh605287</t>
+          <t>sz001300</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>德才股份</t>
+          <t>三柏硕</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>37.39</v>
+        <v>13.51</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10.0029</v>
+        <v>10.0163</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧|旗下奇想无限深耕“网文IP+AI漫剧”转化，与头部网文平台合作，将玄幻、甜宠等成熟IP快速落地，已产出多部爆款。</t>
+          <t>体育产业|公司是一家专注于休闲运动和健身器材系列产品研发、设计、生产和销售的高新技术企业。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧</t>
+          <t>体育产业</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>染料涂料</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>2.302</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>近期国内染料及上游中间体行情持续走高，“金九银十”纺织备货带动化工染料产业链景气上行。数据显示，自6月低点至今，分散染料报价累计上涨超30%，活性染料涨幅达到55%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sz301190</t>
+          <t>sh600408</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>善水科技</t>
+          <t>安泰集团</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>35.93</v>
+        <v>3.44</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>20.0067</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>9.904200000000001</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>染料+医药中间体|公司主要经营染料中间体、农药和医药中间体的研发、生产和销售业务。公司生产的染料中间体包括6-硝体、氧体、5-硝体和邻氨基苯磺酸。</t>
+          <t>焦炭|公司主营焦炭及其副产品，炼焦采用的是JN60-6型焦炉，产品主要销售给钢铁企业。目前公司焦炭年生产能力已达到240万吨，是山西省焦化龙头企业之一。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>染料, 医药中间体</t>
+          <t>焦炭</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>染料涂料</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>2.302</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>近期国内染料及上游中间体行情持续走高，“金九银十”纺织备货带动化工染料产业链景气上行。数据显示，自6月低点至今，分散染料报价累计上涨超30%，活性染料涨幅达到55%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh603188</t>
+          <t>sz001336</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>亚邦股份</t>
+          <t>楚环科技</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>5.4</v>
+        <v>20.65</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>9.9796</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.016</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>染料|公司主要从事染料及染料中间体的销售与服务，是国内蒽醌结构染料生产专家工厂。</t>
+          <t>环保|公司是一家集研发、设计、制造、销售、服务为一体的废气恶臭治理系统解决方案服务商，主要服务于市政污水处理厂、餐厨垃圾处理厂客户。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>染料</t>
+          <t>环保</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>0.2474</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sz000911</t>
+          <t>sh600310</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>*ST广糖</t>
+          <t>广西能源</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>5.4</v>
+        <v>4.97</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>9.9796</v>
+        <v>9.9558</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 主要从事机制糖的生产与销售业务。主要客户包括海天味业、加多宝、娃哈哈等。</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
+          <t>电力|公司主营业务为电力生产和销售，包括水力发电、火力发电、光伏发电，拥有完整的发、供电网络，电厂和电网“厂网合一”，发电、供电和配电业务一体化经营。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>0.2474</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz000838</t>
+          <t>sz301697</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>*ST发展</t>
+          <t>贝特利</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2.45</v>
+        <v>31.51</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>9.865500000000001</v>
+        <v>19.9924</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 1.房地产板块的主营业务为房地产开发与销售，经营模式为商品房开发销售。公司业务范围主要在重庆市、江苏省连云港市和山东省威海市。
-2.财信发展公告称，公司控股股东财信地产及间接控股股东财信集团与投资人江西中久天然气集团有限公司签署《重整投资协议》，投资人拟收购财信发展20%至29.99%的股份。若投资人获得上述股份，将导致公司股权结构、控股股东和实际控制人发生变更，江西中久天然气集团实际控制人雍芝君将成为上市公司实际控制人，江西中久天然气集团将成为上市公司控股股东。</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
+          <t>光模块导热凝胶|公司的导热凝胶产品已经送样给光模块头部客户。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>光模块导热凝胶</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>0.2474</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz002856</t>
+          <t>sh600722</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>*ST美芝</t>
+          <t>金牛化工</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20.22</v>
+        <v>16.19</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>10.0109</v>
+        <v>9.9864</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司从事的主要业务为建筑装饰工程的设计与施工，主要为交通运输机构、文化产业、金融地产、政府机构、高端星级酒店集团等大型客户，提供跨领域全方位的综合工程服务。</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
+          <t>煤化工|公司的主要业务为甲醇的生产和销售，产品方式为焦炉气制甲醇。公司的主要业务由持股50%的控股子公司金牛旭阳经营，金牛旭阳拥有的甲醇生产能力为20万吨/年。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>煤化工</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>0.2474</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz002694</t>
+          <t>sh603788</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>*ST顾地</t>
+          <t>宁波高发</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>2.76</v>
+        <v>15</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>9.9602</v>
+        <v>9.970700000000001</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司为国内有较大规模和影响力的塑胶建材制造商之一，主要产品有聚氯乙烯（PVC）系列管道、聚乙烯（PE）系列管道和聚丙烯（PP）系列管道等。</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
+          <t>汽车踏板|公司产品电子换挡器、汽车拉索、电子油门踏板皆已配套新能源车。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>汽车踏板</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2574,520 +2549,33 @@
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sh603073</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>彩蝶实业</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>10.35</v>
+        <v>22.97</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>9.9894</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>7天7板</t>
-        </is>
-      </c>
+        <v>10.0096</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
+          <t>化纤|公司专注于涤纶面料、无缝成衣和涤纶长丝的研发、生产和销售及染整受托加工业务。其中，涤纶长丝业务生产的DTY可以用于涤纶面料和无缝成衣的生产。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>sh605303</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>园林股份</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>28.66</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>10.0192</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>并购重组|园林股份公告称，公司拟通过发行股份及支付现金方式，向杭州华澜创企业管理咨询合伙企业(有限合伙)等98名股东收购华澜微93.5031%股份，并募集配套资金。标的公司主营国产存储控制器芯片及模组、阵列控制器芯片及模组的研发、设计及销售。</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>sz002962</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>五方光电</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>玻璃基板|公司具有玻璃通孔TGV技术能力及一定的产品交付能力。</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>玻璃基板</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>sz001206</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>依依股份</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>18.62</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>9.982299999999999</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>股权转让|依依股份公告称，公司控股股东、实际控制人高福忠、高健，持股5%以上股东卢俊美及其一致行动人卢俊江，董事高斌、杨丙发、张健与宿迁祝荣投资合伙企业签署《股份转让协议》，拟以17元/股协议转让合计1295万股(占总股本7%)，转让总价款2.2亿元。</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>股权转让</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>sh601118</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>海南橡胶</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>10.0173</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>橡胶|地处海南省海口市，海南省农垦投资控股集团旗下上市公司，是目前中国最大的天然橡胶生产企业。</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>橡胶</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>sh600072</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>中船科技</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>9.9773</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>风电+船舶|1.公司主要业务包括风力发电设备的制造、风电场和光伏电站的开发与运营、新能源工程建设服务等，在运营风光电场20个，合计权益容量137.33千瓦。
-2.中国船舶工业集团旗下上市公司，以设计咨询、工程总承包及城镇化建设三大业务为依托，积极布局豪华邮轮、舰船内装业务等。</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>风电, 船舶</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>sh603739</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>蔚蓝生物</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>14.04</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>10.0313</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>饲料|公司是以酶制剂、微生态制剂的生产、研发和销售为主营业务的生物科技公司。公司生产的酶制剂产品已经广泛应用到饲料、纺织和食品等行业。</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>饲料</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr"/>
-      <c r="D53" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>sz002226</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>江南化工</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>10.1031</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>民爆|公司主要从事工业炸药、工业雷管、工业索类等民用爆炸物品的研发、生产、销售。公司对西藏地区民爆市场的需求和发展潜力保持高度关注，下属四川宇泰特种工程技术有限公司、北方爆破科技有限公司在西藏均设有分公司。</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>民爆</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>sz002419</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>天虹股份</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>9.9352</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>零售|公司控股股东是中国航空工业集团子公司中国航空技术国际控股有限公司旗下中国航空技术深圳有限公司，公司是国内拥有百货商场数量最多的连锁百货企业之一。</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>零售</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>sz002041</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>登海种业</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>10.23</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>种业|公司长期致力于玉米育种与高产栽培研究工作，是国内最早实施育繁推一体化的试点企业，公司的主要产品包括玉米杂交种、蔬菜杂交种、花卉种苗、小麦种、水稻种。公司的利润93%以上来源于玉米杂交种。</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>种业</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>sh603185</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>弘元绿能</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>15.15</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>10.0218</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>光伏|公司已形成了包括硅料、单晶硅片、太阳能电池、太阳能组件的垂直一体化产能，向全球客户提供高效率、高质量的太阳能光伏组件产品，至今投产的高效太阳能光伏组件产品聚焦182、210大尺寸高效电池。</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>光伏</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>sz001266</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>宏英智能</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>39.96</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>9.9917</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>商业航天+液冷|1.公司智能电控产品已经批量应用于航天配套的相关领域。
-2.公司的液冷储能相关产品已实现批量应用，在数据中心应用场景下采用全浸没式液冷储能技术。</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>商业航天, 液冷</t>
+          <t>化纤</t>
         </is>
       </c>
     </row>
@@ -3102,7 +2590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3129,7 +2617,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -3148,27 +2636,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sz002242</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>九阳股份</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz002242</t>
+          <t>sh600241</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>
@@ -3178,12 +2666,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz000011</t>
+          <t>sh603200</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>深物业A</t>
+          <t>上海洗霸</t>
         </is>
       </c>
     </row>
@@ -3193,12 +2681,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh600241</t>
+          <t>sz002866</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>传艺科技</t>
         </is>
       </c>
     </row>
@@ -3208,27 +2696,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz301190</t>
+          <t>sz002058</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>善水科技</t>
+          <t>紫竹高科</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh603200</t>
+          <t>sh605303</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>园林股份</t>
         </is>
       </c>
     </row>
@@ -3238,12 +2726,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sh605388</t>
+          <t>sh603906</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>均瑶健康</t>
+          <t>龙蟠科技</t>
         </is>
       </c>
     </row>
@@ -3253,12 +2741,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sz002866</t>
+          <t>sh600663</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t xml:space="preserve">陆家嘴  </t>
         </is>
       </c>
     </row>
@@ -3268,42 +2756,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sz002058</t>
+          <t>sh603928</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>紫竹高科</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>sh605303</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>园林股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>sh603188</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>亚邦股份</t>
+          <t>兴业股份</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="91" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="209" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="278" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,2030 +552,3281 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>短剧</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.161</v>
+        <v>6.496300000000001</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
+          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz002058</t>
+          <t>sh605287</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>紫竹高科</t>
+          <t>德才股份</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>22.22</v>
+        <v>40.18</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10</v>
+        <v>9.991800000000001</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>铝塑膜|旗下紫江新材专注铝塑膜产品的研发，同时积极布局固态电池用铝塑膜产品，以适应未来固态电池行业发展带动的新增需求。</t>
+          <t>AI漫剧|旗下奇想无限深耕“网文IP+AI漫剧”转化，与头部网文平台合作，将玄幻、甜宠等成熟IP快速落地，已产出多部爆款。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>铝塑膜</t>
+          <t>AI漫剧</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>短剧</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.161</v>
+        <v>6.496300000000001</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
+          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz002866</t>
+          <t>sh605577</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>龙版传媒</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>18.59</v>
+        <v>16.2</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10</v>
+        <v>9.9796</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>固态电池+PCB|1.公司的半固态、固态电池处于研发阶段。
-2.公司专注于为行业领先客户提供全方位FPC产品及服务，根据下游不同终端产品对于FPC的定制化要求，为客户提供涵盖产品设计、研发和销售各个环节的整体解决方案。</t>
+          <t>AI漫剧+出版|公司首部AI漫剧《穿越1988》完成170集制作上线，全网播放量突破1.2亿，红果热度值超4000万。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>固态电池, PCB</t>
+          <t>AI漫剧, 出版</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>短剧</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.161</v>
+        <v>6.496300000000001</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
+          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh603200</t>
+          <t>sh603533</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>掌阅科技</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>49.21</v>
+        <v>25.44</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.991099999999999</v>
+        <v>9.987</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>固态电池+液冷|1.公司生产的固态电解质粉体材料可以应用于锂离子固态电池，多形态固态电解质粉体材料（含油性、水性、浆料）年产50吨级产线主要采用的是氧化物技术路线，公司储备了硫化物、氯化物等固态电解质的其它固态电解质粉体技术路线。
-2.公司面向腾讯、华为、中国移动等重点客户数据中心提供循环水/空气蒸发冷却等专业服务。</t>
+          <t>AI短剧|1.公司已经搭建起专业的短剧生产运营体系。公司2025年度AI短剧业务收入预计不超过2025年度主营业务收入的1%。
+2.MiniMax与掌阅科技合作的对话式AI应用“阅爱聊”，能让文学作品中的角色来到现实，与用户展开一场“跨次元”对谈。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>固态电池, 液冷</t>
+          <t>AI短剧</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>短剧</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.161</v>
+        <v>6.496300000000001</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
+          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh603928</t>
+          <t>sh601595</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>兴业股份</t>
+          <t>上海电影</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>14.38</v>
+        <v>24.74</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.023</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0044</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>固态电池+光刻胶|1.公司已成功研发酚醛树脂，酚醛树脂在电池负极材料的应用有着显著的进步，是未来固态电池、钾离子电池等颠覆性技术的“核心材料基石”。
-2.公司已研发成功半导体光刻胶用酚醛树脂、特种半导体封装用酚醛树脂等一批特种有机合成功能新材料。</t>
+          <t>AI+短剧|上影元已与多家大模型公司建立深度合作，联动公司参与发起设立的上影新视野基金，已布局“AI+社交”“AI+游戏”“AI+短剧”等泛娱乐产品。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>固态电池, 光刻胶</t>
+          <t>AI, 短剧</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>短剧</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.161</v>
+        <v>6.496300000000001</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
+          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh603906</t>
+          <t>sh601929</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>龙蟠科技</t>
+          <t>吉视传媒</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20.94</v>
+        <v>2.5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9.979000000000001</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.1322</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>固态电池+液冷|1.公司全资子公司三金锂电主要专注于固态电池前驱体的开发，已建成一期5000吨产能。针对固态电池的高镍前驱体以及富锂锰基前驱体已通过客户小试认证，部分超高镍前驱体产品也正在和客户进行联合开发。
-2.子公司迪克化学发布第二代算力中心冷却液。该冷却液以乙二醇和丙二醇为基础，通过添加剂破解超大规模数据中心高效散热难题，支撑AI算力稳定运行。该产品目前以国内客户为主，围绕行业头部企业的算力中心推广应用。</t>
+          <t>短剧|公司与吉林广播电视台、长影集团有限责任公司、深圳市来画科技文化有限公司联合签署战略合作协议，发挥四方优势，以联合出品、联合制作、委托制作、国际版制作等形式，共同策划推出微短剧、影视剧、专题片、虚实影像互动剧、社交游戏等精品视频内容与应用服务等精品内容。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>固态电池, 液冷</t>
+          <t>短剧</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>短剧</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1.161</v>
+        <v>6.496300000000001</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
+          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz002733</t>
+          <t>sz000892</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
+          <t>欢瑞世纪</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>18.89</v>
+        <v>4.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.0175</v>
+        <v>9.9773</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>固态电池|公司会持续关注固态电池与机器人、低空飞行器技术融合的发展趋势和相关的应用；结合60AH的容量与机器人、低空飞行器的电源匹配需求，60Ah固态电池可以用在较大型的机器人和中大型的低空飞行器。</t>
+          <t>AI+短剧|公司与上海阶跃星辰智能科技有限公司已达成战略合作，双方共建“麟跃”AI联合实验室，合作方向为短剧Agent产品，双方将合力打造短剧Agent产品，深化探索AI技术在相关影视应用、短剧管理与投流产品等方向的应用。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>AI, 短剧</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>短剧</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.161</v>
+        <v>6.496300000000001</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
+          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz002805</t>
+          <t>sz300364</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>丰元股份</t>
+          <t>中文在线</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>17.67</v>
+        <v>24.47</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.0249</v>
+        <v>20.0098</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>固态电池|公司对固态电池硫化物正极材料有技术储备，还参股了深耕于固态电池领域的中科深蓝汇泽新能源(常州)有限责任公司。</t>
+          <t>短剧+AI|1.在中短剧方面，根据公司旗下四月天小说网、17K小说网平合IP改编的作品初具规模，其中多部取得了单部播放量过亿的佳绩，如《姑娘好心机》、《就想和你谈恋爱》、《皇妃在娱乐圈当顶流》、《特工房东俏房客》、《霸婿崛起》等。
+2.公司于2023年发布AI大模型“中文逍遥”1.0版本，可实现一键生成万字小说、一张图写一部小说、一次读懂100万字小说。目前“中文逍遥”AI内容生产模型已实现持续进化，推出一键小说转剧本、一键本土化转译功能，持续提升用户体验，作者好评率提升70%。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>短剧, AI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>短剧</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1.161</v>
+        <v>6.496300000000001</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
+          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>920627.BJ</t>
+          <t>sz001330</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>力王股份</t>
+          <t>博纳影业</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>17.83</v>
+        <v>6.97</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>29.9563</v>
+        <v>9.9369</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>固态电池|公司与清华大学深圳国际研究生院合作项目为低成本高功率锂离子电池和下一代高安全固态锂电池的研究与开发，对锂离子电池的关键技术进行合作开发，公司负责电池正极配方优化、正负极制备工艺的开发；清华大学深圳国际研究生院负责电解质离子运输机制的研究；双方共同完成低成本高功率电池的集成设计与开发。</t>
+          <t>AI短剧|短剧业务方面，AIGC短剧《三星堆：未来启示录》由抖音联合出品，目前制作中的短剧项目如《天罗地网》《非遗手艺人》等，也已与红果短剧等头部短剧平台、中央广播电视总台及其他媒体平台开展合作，积极探索精品短剧的生产与发行新模式。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>AI短剧</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>短剧</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1.161</v>
+        <v>6.496300000000001</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>德邦证券研报指出，固态电池产业化拐点渐近，仅2026年上半年固态电池领域投资项目就超40个。</t>
+          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz300530</t>
+          <t>sz002343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>领湃科技</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>24.08</v>
+        <v>6.08</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>19.9801</v>
+        <v>9.9458</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>短剧|公司已形成了以自有IP为核心资源，以影视IP内容投资、开发、制作及发行为核心业务，积极延伸拓展电影、网络电影、网络微短剧、互动剧、小程序短剧、IP线下衍生等相关品类的业务体系。</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>6.496300000000001</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>sz300413</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>芒果超媒</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>19.9791</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>AI+短剧|1.在AI Agent方面，公司已经进行了相关技术储备和产品开发，推出AI Agent平台—“芒果西米露”平台，目前搭建超过70个智能体，覆盖节目创意、广告创意、内容审核等多个业务场景。
+2.微短剧业务是公司的战略重心之一，芒果TV依托互通互融的制作优势和“芒系”爆款IP的内容优势，致力于打造微短剧赛道的芒果品牌。</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>AI, 短剧</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>6.496300000000001</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>sh600715</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>文投控股</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>短剧|公司已针对短剧行业进行深入研究，并计划依托自身IP资源孵化优势，结合AIGC等工具的发展应用，探索文化内容与科技手段相融合的新型创作模式。</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>6.496300000000001</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>sz002181</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>粤 传 媒</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>9.953199999999999</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>AI短剧|子公司新媒体公司自主研发了AIGC内容生产一体化平台—“妙创”AIGC 内容生产平台，应用于《广州三部曲》《我为荔枝拍广告》等项目。平台覆盖火爆短剧、创意短视频、妙音AI音乐三大场景，适配从剧本拆解、创意分镜设计到图片与视频生成的各层次需求，为专业内容生产团队、企业品牌部门/融媒体中心、高校等单位提供内容创作服务。</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>AI短剧</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1.4482</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>sz000710</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>贝瑞基因</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>10.0292</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>基因检测+AI医疗|1.公司依托其具有自主知识产权的cSMART核心技术为支撑，选择ctDNA作为肿瘤液体活检指标，开启了临床无创肿瘤基因检测的全新模式。
+2.公司自主研发NLPearl遗传疾病人工智能临床决策支持系统、CNVisi智能报告解读系统，为科研和临床工作者提供智能决策支持。公司的CNVisi™利用人工智能深度学习算法，挖掘20+权威公共数据库、百万自有CNV大数据以及20多万份CNV-seq临床实践报告，构建7大临床解读知识库，精准注释解读、一键查询信息、自定义设置参数、AI智能撰写报告。</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>基因检测, AI医疗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1.4482</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>sh600812</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>华北制药</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>10.0365</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>链霉素|公司青霉素系列、头孢系列产品品种齐全，覆盖了原料药到制剂的大部分品种，形成了从发酵原料到半合成原料药再到制剂的完整产品链。是国内硫酸链霉素原料药及注射剂的核心生产企业。</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>链霉素</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>1.4482</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>sz300981</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>中红医疗</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>19.9795</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>医用手套|公司主要从事高品质丁腈手套、PVC手套等医用及工业用一次性防护手套的研发、生产与销售，是国内最早生产销售PVC手套和丁腈手套的企业之一。</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>医用手套</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1.4482</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>sz002675</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>东诚药业</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>9.9762</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>创新药|公司着力打造放射性诊疗一体化药物创新平台——烟台蓝纳成，其具有放射性诊疗一体化药物创新研发和全球领先的纳米递送技术的特点，适应症涵盖前列腺癌、胃癌、结直肠癌、鼻咽癌等多种癌症的诊断与治疗产品，其中部分产品进行中美双报。</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>1.4482</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>sh605177</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>东亚药业</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>9.9922</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>抗菌类药物|公司已掌握头孢克洛原料药关键中间体7-ACCA的生产技术，是行业内为数不多的可以从起始物料青霉素开始，全产业链合成头孢克洛原料药的公司之一。</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>抗菌类药物</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1.4482</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>sz002317</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>众生药业</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>10.0129</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>创新药|公司布局了几个治疗非酒精性脂肪性肝炎（NASH）的创新药，其中ZSP1601、ZSP0678、RAY1225项目处于临床试验的不同阶段。</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>0.8928999999999999</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>工信部等七部门联合印发的《新型电池产业发展“十五五”规划》：规划提出到2030年全固态电池初步实现规模化应用、长寿命锂电池循环寿命达1.5万次等目标。</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>sz002058</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>紫竹高科</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>9.991</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>固态电池|旗下紫江新材专注铝塑膜产品的研发，同时积极布局固态电池用铝塑膜产品，以适应未来固态电池行业发展带动的新增需求。</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0.8928999999999999</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>工信部等七部门联合印发的《新型电池产业发展“十五五”规划》：规划提出到2030年全固态电池初步实现规模化应用、长寿命锂电池循环寿命达1.5万次等目标。</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>sz002733</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>雄韬股份</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>10.0053</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>固态电池|公司固态电池产品是通过“原位聚合固态电解质技术”和“电极内部电解质动态成膜固化技术”两大核心技术的突破，彻底消除电池热失控风险，并解决“固-固”界面难题，完美适配数据中心、储能电站、轨道交通等对安全性有严苛要求的领域。</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>0.8928999999999999</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>工信部等七部门联合印发的《新型电池产业发展“十五五”规划》：规划提出到2030年全固态电池初步实现规模化应用、长寿命锂电池循环寿命达1.5万次等目标。</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>sz002805</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>丰元股份</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>10.017</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>固态电池|公司对固态电池硫化物正极材料有技术储备，还参股了深耕于固态电池领域的中科深蓝汇泽新能源(常州)有限责任公司。</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>0.8928999999999999</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>工信部等七部门联合印发的《新型电池产业发展“十五五”规划》：规划提出到2030年全固态电池初步实现规模化应用、长寿命锂电池循环寿命达1.5万次等目标。</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>sz300530</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>领湃科技</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>20.0166</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">固态电池|公司注重基础研发和前瞻技术开发，已经完成了NCM811电池化学体系研发，固态电解质及固态电池、干法电极及其制备技术的基础试验，相关专利正在申请或已获得授权。
 </t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>固态电池</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>0.8928999999999999</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>工信部等七部门联合印发的《新型电池产业发展“十五五”规划》：规划提出到2030年全固态电池初步实现规模化应用、长寿命锂电池循环寿命达1.5万次等目标。</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>sh600478</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科力远  </t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>9.9138</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>固态电池|公司主要针对固态电池核心零部件，开展干法电极的技术开发。</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0.8928999999999999</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>工信部等七部门联合印发的《新型电池产业发展“十五五”规划》：规划提出到2030年全固态电池初步实现规模化应用、长寿命锂电池循环寿命达1.5万次等目标。</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>sh603067</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>振华股份</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>10.0104</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>固态电池+铬|1.子公司厦门首能半固态电解液还处于向下游客户小批量供应，共同研发阶段。
+2.公司金属铬产品在高温合金、铜基、铝基特种合金、高端焊接材料、溅射靶材等领域广泛应用，高温合金是燃气轮机的主要材料，单质铬的添加量在15%~20%之间。</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>固态电池, 铬</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>机器人概念</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>-1.6289</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>据报道，英伟达讨论再向人形机器人公司Figure投资10亿美元。</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="B26" s="2" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>智元机器人上半年出货量超8600台，占全球市场35%和中国市场45%以上，并且在高基数下保持十倍级增长。</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>sz002242</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>九阳股份</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="G26" s="2" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>10.0364</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>5天5板</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>AI机器人|公司持有深思考人工智能机器人科技（北京）有限公司7.92%的股份，旗下产品包括AI机器人。</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>AI机器人</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>机器人概念</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>-1.6289</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>据报道，英伟达讨论再向人形机器人公司Figure投资10亿美元。</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>sh601956</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>东贝集团</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>9.9602</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>机器人|2025年4月17日公司在互动平台表示，公司转子压缩机具备量产能力，正在进行客户匹配性能测试。另外，公司在洗衣机电机、空调电机、机器人关节电机等领域均有相关技术研发储备。人形机器人关节电机目前还处于研发测试阶段。</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>机器人概念</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>-1.6289</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>据报道，英伟达讨论再向人形机器人公司Figure投资10亿美元。</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="B27" s="2" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>智元机器人上半年出货量超8600台，占全球市场35%和中国市场45%以上，并且在高基数下保持十倍级增长。</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>sh600400</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>红豆股份</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>10.0304</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="G27" s="2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>9.944799999999999</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>机器人+纺织|1.参股无锡福芯机器人有限公司经营范围包含：服务消费机器人制造、智能机器人销售、人工智能硬件销售、智能机器人的研发、人工智能应用软件开发、人工智能行业应用系统集成服务、大数据服务等。
 2.公司的主营业务为男装的生产与销售。</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>机器人, 纺织</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>航运</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>2.1979</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Clarksons数据显示，第三季度VLCC平均收益达到277,995美元/天，进入10月初后部分航线收益已经超过160万美元/天，市场整体收益水平一度超过60万美元/天。</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>sh600026</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>中远海能</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>10.0195</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>油运|公司主营业务为从事国际和中国沿海原油及成品油运输、国际液化天然气(LNG)运输以及国际化学品运输，是中国沿海原油和成品油运输领域的龙头企业。</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>油运</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>航运</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>2.1979</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Clarksons数据显示，第三季度VLCC平均收益达到277,995美元/天，进入10月初后部分航线收益已经超过160万美元/天，市场整体收益水平一度超过60万美元/天。</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>sh601975</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>招商南油</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>9.9558</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>油运|公司是招商局集团旗下从事油轮运输的专业化公司，市场定位为全球石化产品的运输服务商。</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>油运</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>天然气</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>1.839</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>布伦特原油突破101美元/桶，日内涨0.86%；上期所燃油主力合约大涨16%。周二欧洲天然气价格上涨，涨幅最高达5.5%，至每兆瓦时77.55欧元。</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>sh600617</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>国新能源</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>天然气|山西最大的天然气管网运营企业，管网建设方面公司在省内主要业务区域已取得绝对优势地位，省级天然气管网5000余公里，年管输涉及能力超过255亿立方米，管网覆盖全省11市104县（市、区）。</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>天然气</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>天然气</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>1.839</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>布伦特原油突破101美元/桶，日内涨0.86%；上期所燃油主力合约大涨16%。周二欧洲天然气价格上涨，涨幅最高达5.5%，至每兆瓦时77.55欧元。</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>sz002490</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>山东墨龙</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>9.9855</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>油气|全产业链石油钻采装备制造商，主要产品包括油气开采用管、流体及结构用管、抽油机、抽油泵、抽油杆、钻机用缸套、阀门散件及大型铸锻件等。公司产品主要用于石油、天然气、煤层气、页岩气等行业。</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>油气</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>锂电池</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>0.2286</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>工业和信息化部、国家发展改革委等七部门近日联合印发《新型电池产业发展“十五五”规划》。《规划》提出到2030年，我国新型电池产业规模实现稳步增长的目标。</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>sh600241</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>时代万恒</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>9.9794</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>锂电池|公司旗下九夷锂能主要经营锂离子电池、电池组的研发、生产、制造、系统集成、销售和服务，目标市场定位于电动工具、个人护理、家庭电子、消费品等小动力领域。</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>锂电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>锂电池</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>0.2286</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>工业和信息化部、国家发展改革委等七部门近日联合印发《新型电池产业发展“十五五”规划》。《规划》提出到2030年，我国新型电池产业规模实现稳步增长的目标。</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>sh605378</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>野马电池</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>17.27</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">锂电池|公司销售的锂电池主要为纽扣电池，应用于微型电子产品等。
-</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>锂电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>-0.1895</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>记者8日从国家税务总局获悉，增值税发票最新数据显示，国庆假期，全国服务消费旺盛，相关行业日均销售收入同比增长19.5%。</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>sz000869</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>张  裕Ａ</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>10.0293</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>葡萄酒|公司是国内葡萄酒行业龙头，拥有葡萄酒、白兰地、起泡酒等系列产品百余品种，涵盖高、中、低各档次。</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>葡萄酒</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>-0.1895</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>记者8日从国家税务总局获悉，增值税发票最新数据显示，国庆假期，全国服务消费旺盛，相关行业日均销售收入同比增长19.5%。</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>sz002702</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>海欣食品</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>10.0372</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>预制菜|主要从事冷冻和常温鱼肉制品和肉制品的生产和销售，包括各类鱼丸等。</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>预制菜</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>烟草</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>-0.5054999999999999</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>7月28日国家烟草专卖局挂出《加热卷烟》强制性国家标准征求意见稿，意见反馈窗口到9月26日关闭。</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>sz002951</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>金时科技</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>17.17</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>9.993599999999999</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>光纤+烟草|1.公司通过智芯一号股权基金间接参股苏州易缆微，易缆微是一家光纤通信产品研发生产商，致力于光纤通信系统、光网络系统、光电传感系统、物联网系统技术研究和试验发展及进出口业务。
-2.公司的主营业务为烟标等包装印刷品的研发、生产和销售，目前主要的包装印刷产品为烟标，是卷烟消费品的配套包装制品，具有防伪商标、外观形象、包装保护等功能。</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>光纤, 烟草</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>烟草</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>-0.5054999999999999</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>7月28日国家烟草专卖局挂出《加热卷烟》强制性国家标准征求意见稿，意见反馈窗口到9月26日关闭。</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>sz002565</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>顺灏股份</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>9.9526</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>商业航天+烟草|1.公司2025年6月以1.1亿元人民币投资北京轨道辰光科技有限公司，持股比例为19.30%。轨道辰光的主要业务是通过将算力卫星发射至晨昏轨道，组建太空数据中心，为客户提供算力服务，其经营范围包括微小卫星生产制造、微小卫星科研试验、互联网信息服务等。轨道辰光首颗试验星算力规模预计25p。
-2.公司的主要产品为真空镀铝纸及烟标产品等，主要下游客户为烟草生产企业和烟标印刷企业。</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>商业航天, 烟草</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>-1.9448</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>《科创板日报》记者独家获悉，亚马逊云科技旗下大模型服务平台Amazon Bedrock官宣接入智谱GLM-5.3，AWS基于模型调用量与智谱进行收入分成。</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>sz002774</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>快意电梯</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>19.04</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>9.994200000000001</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>电梯+AI应用|1.公司是全球范围内提供电梯综合解决方案的优秀民族电梯供应商和服务商之一。主要从事电梯、自动扶梯和自动人行道的设计研发、制造、销售及产品的安装、改造和维保服务。
-2.公司一直重视技术研发和创新，大力投入对系统、产品、服务等多维度的智能化、数字化建设；产品及技术方面，各种无接触呼梯产品、智能派梯系统、AI智能监控等多项技术已实际应用。</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>电梯, AI应用</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>-1.9448</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>《科创板日报》记者独家获悉，亚马逊云科技旗下大模型服务平台Amazon Bedrock官宣接入智谱GLM-5.3，AWS基于模型调用量与智谱进行收入分成。</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>sz002869</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>金溢科技</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>智能驾驶+AI应用|1.公司是智慧交通领域领先的数智化解决方案及产品提供商，打造了完整的车、路、云产品体系,包括车载V2X系列产品、路端V2X边端系统集成产品等。
-2.9月28日，据金溢科技官微，针对新能源商用车及储能电站热管理需求，金溢科技推出AI智能热管理液冷机组全栈解决方案。该方案覆盖商用车（3～120kW）与储能（3～100kW）双产品线。</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>智能驾驶, AI应用</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>医药</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>-1.966</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>sh600812</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>华北制药</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>10.0402</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>链霉素|公司青霉素系列、头孢系列产品品种齐全，覆盖了原料药到制剂的大部分品种，形成了从发酵原料到半合成原料药再到制剂的完整产品链。是国内硫酸链霉素原料药及注射剂的核心生产企业。</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>链霉素</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>医药</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>-1.966</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>sh600513</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>联环药业</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>10.0066</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>创新药|主要产品有创新药物爱普列特片(川流)，新药依巴斯汀片(苏迪)、非洛地平片(联环尔定)、非洛地平缓释胶囊(联环笑定)等二十多个。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>生物质能</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.8217</v>
+        <v>0.0219</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>泰国政府正考虑下调生物燃料消费税，压低价格并拉动消费。</t>
+          <t>智元机器人上半年出货量超8600台，占全球市场35%和中国市场45%以上，并且在高基数下保持十倍级增长。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sh688196</t>
+          <t>sh600843</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>卓越新能</t>
+          <t>上工申贝</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>36.12</v>
+        <v>8.18</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>20</v>
+        <v>9.946199999999999</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>生物柴油|公司是国内第一家从事废弃油脂制备生物柴油的技术研发并率先实现工业化生产的企业，二十年来深耕生物柴油和生物基材料行业，是目前国内产销规模最大、出口量最多的生物柴油生产企业，并逐步形成以生物柴油为主，衍生深加工生物基材料的“生物质能化一体化”的产业布局。</t>
+          <t>纺织机械+机器人|公司已经成长为一家占据全球缝制技术制高点并为客户量身定制工业4.0应用解决方案的专业设备供应商，主要产品有缝纫、绣花、裁切、焊接等缝制工艺设备，机器人焊接、组装生产线，程控机械加工流水线，以及智能仓储、自动传输装置等。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>生物柴油</t>
+          <t>纺织机械, 机器人</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-0.8703000000000001</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr"/>
+        <v>0.0219</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>智元机器人上半年出货量超8600台，占全球市场35%和中国市场45%以上，并且在高基数下保持十倍级增长。</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz002630</t>
+          <t>sz000420</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>*ST华西</t>
+          <t>吉林化纤</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1.57</v>
+        <v>3.81</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>9.7902</v>
+        <v>10.1156</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 目前公司核电业务主要集中在核三废处理领域，为业主项目提供核废物处理系统以及配套件。</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
+          <t>机器人+碳纤维|1.公司涉及的碳纤维产品处于产业链上游，可用于机器人制造。
+2.公司是我国主要粘胶纤维生产企业，产品包括粘胶长丝和粘胶短纤，连续多年成为全球优质的粘胶长丝供应商之一。</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 碳纤维</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-0.8703000000000001</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
+        <v>0.0219</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>智元机器人上半年出货量超8600台，占全球市场35%和中国市场45%以上，并且在高基数下保持十倍级增长。</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh603189</t>
+          <t>sz002480</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">*ST网达 </t>
+          <t>新筑股份</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>10.2</v>
+        <v>6</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.0324</v>
+        <v>10.0917</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 1.公司以AI大模型赋能全媒体的内容生产、运营、分发为主要着力点，重构现有内容运营编辑系统、媒资管理系统，研发了系列智能化内容生产系统。
-2.公司是阿里云的核心合作伙伴，在广电融媒体端有广泛深入的技术合作。</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t>机器人+液流电池|1.参股奥威科技参与研发的移动充电机器人目前处于对样机进行调试的阶段。
+2.2024年2月21日公告，子公司川发兴能拟启动建设60000m³/a短流程钒电解液生产线建设项目，项目总投资估算4.6亿元。</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 液流电池</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>智元机器人上半年出货量超8600台，占全球市场35%和中国市场45%以上，并且在高基数下保持十倍级增长。</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sz002979</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>雷赛智能</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>11.39</v>
+        <v>55.58</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.0483</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>8天8板</t>
-        </is>
-      </c>
+        <v>9.9941</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
+          <t>机器人|公司在人形机器人领域定位是伺服控制产品与解决方案提供商、为众多整机厂家提供系列化伺服控制核心部件和模组级解决方案。公司从2018年起持续耕耘机器人行业（AGV/AMR、协作机器人等），并于2023年底成功研发出高密度无框力矩电机、CD伺服驱动器、中空编码器、空心杯电机及配套的微型伺服系统等核心产品。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
+          <t>网络安全</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>3.6493</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic扩大先进AI模型访问权限，允许经过验证的机构对关键基础设施安全系统进行高风险攻击性测试。</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh605303</t>
+          <t>sz002912</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>园林股份</t>
+          <t>中新赛克</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>31.53</v>
+        <v>28.55</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.014</v>
+        <v>10.0193</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>8天4板</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>并购重组|园林股份公告称，公司拟通过发行股份及支付现金方式，向杭州华澜创企业管理咨询合伙企业(有限合伙)等98名股东收购华澜微93.5031%股份，并募集配套资金。标的公司主营国产存储控制器芯片及模组、阵列控制器芯片及模组的研发、设计及销售。</t>
+          <t>AI+网络安全|公司推出的小赛安全智脑产品，支持多模型底座，基于智能体、RAG等技术，包含渗透测试智能体、事件调查智能体、代码安全审计智能体，也配备了敏感数据识别、智能解码、安全知识问答等多种智能体应用，全方位满足安全运维场景下的各类用户需求，为企业数据与网络安全保驾护航。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>AI, 网络安全</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
+          <t>网络安全</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>3.6493</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic扩大先进AI模型访问权限，允许经过验证的机构对关键基础设施安全系统进行高风险攻击性测试。</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh600663</t>
+          <t>sz300369</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">陆家嘴  </t>
+          <t>绿盟科技</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>11.12</v>
+        <v>10.43</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>9.9901</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>20.023</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>房地产+参股券商|1.公司控股股东为上海陆家嘴（集团）有限公司。公司坚持以商业地产为核心，以金融服务为纽带，以商业零售为延伸。
-2.子公司陆金发持有爱建证券51.14%股权。</t>
+          <t>AI+网络安全|2024年公司推出了自主研发的“风云卫AI安全能力平台”，该平台融合大模型、小模型、知识图谱等核心能力，依托公司二十余年的网络安全研究积累与攻防对抗实践，构建了开放式PaaS架构，广泛适配于安全运营、检测响应、攻防实战等场景。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>房地产, 参股券商</t>
+          <t>AI, 网络安全</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
+          <t>网络安全</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>3.6493</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic扩大先进AI模型访问权限，允许经过验证的机构对关键基础设施安全系统进行高风险攻击性测试。</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz300522</t>
+          <t>sz002212</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>世名科技</t>
+          <t>天融信</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>16.56</v>
+        <v>7.56</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>20</v>
+        <v>10.0437</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>PCB树脂|公司布局的高纯UV单体与电子碳氢树脂均作为PCB产业的上游，其中UV单体主要应用场景为PCB干膜光刻胶以及PCB油墨（线路油墨、阻焊油墨），电子碳氢树脂主要应用场景为PCB基础原料高速覆铜板。</t>
+          <t>网络安全+AI|1.公司作为中国领先的网络安全、大数据与云服务提供商，为政府、金融、运营商、能源、卫生、教育、交通、制造等各行业客户提供网络安全产品、大数据产品和云服务。
+2.2024年11月26日公司在互动平台表示，AI Agent（智能体）是公司天问大模型关键技术之一，具备自然语言处理、风险预测、情报抽取等核心能力，应用于安全知识问答、日志分析、告警研判等安全运营场景。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>PCB树脂</t>
+          <t>网络安全, AI</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr"/>
+          <t>网络安全</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>3.6493</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic扩大先进AI模型访问权限，允许经过验证的机构对关键基础设施安全系统进行高风险攻击性测试。</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh603863</t>
+          <t>sh603232</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>松炀资源</t>
+          <t>格尔软件</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>13.62</v>
+        <v>16.98</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.0162</v>
+        <v>9.9741</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>造纸|公司主要从事环保再生纸的研发、生产和销售，是一家集废纸回收、环保造纸及涂布成型于一体，形成资源再生利用价值链的造纸企业。</t>
+          <t>AI+网络安全|1.公司的AI赋能旨在深化AI与密码学、安全、产品三大核心业务的融合,明确推动AI应用从工具引入向范式变革演进,实现“AI赋能效率、创新驱动升级”双重目标。
+2.公司自成立以来一直专注于信息安全行业PKI领域，主要从事以公钥基础设施PKI为核心的商用密码软件产品的研发、生产和销售及服务业务，为用户提供基于PKI的信息安全系列产品、安全服务和信息安全整体解决方案。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>造纸</t>
+          <t>AI, 网络安全</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr"/>
+          <t>网络安全</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>3.6493</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic扩大先进AI模型访问权限，允许经过验证的机构对关键基础设施安全系统进行高风险攻击性测试。</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sz002687</t>
+          <t>sh688152</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>乔治白</t>
+          <t>麒麟信安</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>6.14</v>
+        <v>45.85</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.0358</v>
+        <v>19.9948</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>纺织|公司主要从事“乔治白”“giuseppe”品牌的职业装生产和销售。</t>
+          <t>网络安全|公司操作系统、云计算产品以安全为特色，并和公司信息安全产品有机融合构成三位一体系统性整体安全，可满足国防领域高安全需求。公司自设立以来长期服务于国防单位，承建了众多国防单位信息化建设项目，并承担了多项国防单位委托的型号装备配套和技术预研项目，能快速理解并响应国防单位多样化的需求，目前主要应用于航天测发控、训练、指挥、办公、教育培训等。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>纺织</t>
+          <t>网络安全</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
+          <t>农业种植</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>4.6913</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>世界气象组织周四在月度气候公报中表示，今年的厄尔尼诺现象将在12月达到峰值前进一步增强，并且持续至2027年2月的可能性接近100%。</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh603137</t>
+          <t>sh601118</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>恒尚节能</t>
+          <t>海南橡胶</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>19.56</v>
+        <v>7.16</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.0112</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+        <v>9.9846</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>存储芯片|恒尚节能公告称，公司拟通过发行股份及支付现金方式购买深圳市金胜电子科技有限公司100%股权，并募集配套资金。公司股票将于2026年7月1日开市起复牌。标的公司主要从事存储器的研发设计、生产制造及销售，主要品牌包括KingSpec金胜维、YANSEN元存、OneBoom猛犸纪、MemoStone意石、Mixage采云纪等。</t>
+          <t>橡胶|地处海南省海口市，海南省农垦投资控股集团旗下上市公司，是目前中国最大的天然橡胶生产企业。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>存储芯片</t>
+          <t>橡胶</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
+          <t>农业种植</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>4.6913</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>世界气象组织周四在月度气候公报中表示，今年的厄尔尼诺现象将在12月达到峰值前进一步增强，并且持续至2027年2月的可能性接近100%。</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sh605298</t>
+          <t>sh600127</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>必得科技</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>44.97</v>
+        <v>15.18</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.0049</v>
+        <v>10</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>股权转让|2026年6月14日公告，公司实际控制人王坚群、刘英与衢州启信企业管理合伙企业（有限合伙）签署了《股份转让协议》，王坚群和刘英拟以53.44元/股的价格向衢州启信转让其持有的公司合计1242.45万股股份（占公司总股本的6.6140%），股份转让价款合计6.64亿元。本次股份转让完成后，公司实际控制人由王坚群、刘英变更为王坚群，公司控股股东不变，仍为王坚群。</t>
+          <t>大米|公司是我国粮食系统的第一家上市公司，是首批农业产业化国家重点龙头企业，国家水稻工程优质米示范基地。公司以优质粮油、新型健康食品和药品开发、生产、销售为发展方向，坚持农、工、科、贸一体化的现代农业产业化经营模式，主要产品有大米、面粉、面条、植物油、米粉、牛奶、糖果、果冻、药品等。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>股权转让</t>
+          <t>大米</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
+          <t>农业种植</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>4.6913</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>世界气象组织周四在月度气候公报中表示，今年的厄尔尼诺现象将在12月达到峰值前进一步增强，并且持续至2027年2月的可能性接近100%。</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sz001300</t>
+          <t>sh600371</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>三柏硕</t>
+          <t>万向德农</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>13.51</v>
+        <v>14.97</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10.0163</v>
+        <v>9.992700000000001</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>体育产业|公司是一家专注于休闲运动和健身器材系列产品研发、设计、生产和销售的高新技术企业。</t>
+          <t>种业|公司从事的主要业务为玉米杂交种子研发、生产、销售，主营包括但不限于“京科968”、“德单系列”等玉米杂交种的生产与销售。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>体育产业</t>
+          <t>种业</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
+          <t>农业种植</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>4.6913</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>世界气象组织周四在月度气候公报中表示，今年的厄尔尼诺现象将在12月达到峰值前进一步增强，并且持续至2027年2月的可能性接近100%。</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh600408</t>
+          <t>sh600354</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>安泰集团</t>
+          <t>敦煌种业</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3.44</v>
+        <v>9.99</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>9.904200000000001</v>
+        <v>10.022</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>焦炭|公司主营焦炭及其副产品，炼焦采用的是JN60-6型焦炉，产品主要销售给钢铁企业。目前公司焦炭年生产能力已达到240万吨，是山西省焦化龙头企业之一。</t>
+          <t>种业|公司目前主要从事各类农作物种子的研发、生产、加工、销售和脱水菜、番茄粉、番茄酱、啤酒花制品的加工、销售以及棉花及其副产品的收购、加工、仓储、贸易。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>焦炭</t>
+          <t>种业</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
+          <t>商业零售</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>3.3686</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>记者10月8日从国家税务总局获悉，增值税发票最新数据显示，国庆假期，全国服务消费旺盛，相关行业日均销售收入同比增长19.5%。</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sz001336</t>
+          <t>sh601086</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>楚环科技</t>
+          <t>国芳集团</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>20.65</v>
+        <v>14.94</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10.016</v>
+        <v>10.0147</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>环保|公司是一家集研发、设计、制造、销售、服务为一体的废气恶臭治理系统解决方案服务商，主要服务于市政污水处理厂、餐厨垃圾处理厂客户。</t>
+          <t>零售|公司从事以百货业为主，超市、电器为辅的连锁零售业务，是甘肃省内最大的连锁零售企业。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>环保</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
+          <t>商业零售</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>3.3686</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>记者10月8日从国家税务总局获悉，增值税发票最新数据显示，国庆假期，全国服务消费旺盛，相关行业日均销售收入同比增长19.5%。</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sh600310</t>
+          <t>sh603101</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>广西能源</t>
+          <t>汇嘉时代</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>4.97</v>
+        <v>7.99</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>9.9558</v>
+        <v>10.0551</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>电力|公司主营业务为电力生产和销售，包括水力发电、火力发电、光伏发电，拥有完整的发、供电网络，电厂和电网“厂网合一”，发电、供电和配电业务一体化经营。</t>
+          <t>零售|公司作为新疆地区百货商超零售连锁企业，经营业态涵盖购物中心、传统百货、超市等。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
+          <t>商业零售</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>3.3686</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>记者10月8日从国家税务总局获悉，增值税发票最新数据显示，国庆假期，全国服务消费旺盛，相关行业日均销售收入同比增长19.5%。</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz301697</t>
+          <t>sh600865</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>贝特利</t>
+          <t>百大集团</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>31.51</v>
+        <v>11.51</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>19.9924</v>
+        <v>10.0382</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>光模块导热凝胶|公司的导热凝胶产品已经送样给光模块头部客户。</t>
+          <t>零售|公司主营业务为商品零售，主要业态为百货商场，旗下杭州百货大楼是公司最主要的营收和利润来源，是杭州市区域龙头百货商场之一。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>光模块导热凝胶</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+          <t>商业零售</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>3.3686</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>记者10月8日从国家税务总局获悉，增值税发票最新数据显示，国庆假期，全国服务消费旺盛，相关行业日均销售收入同比增长19.5%。</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sh600722</t>
+          <t>sh605188</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>金牛化工</t>
+          <t>国光连锁</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>16.19</v>
+        <v>13.84</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>9.9864</v>
+        <v>10.0159</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>煤化工|公司的主要业务为甲醇的生产和销售，产品方式为焦炉气制甲醇。公司的主要业务由持股50%的控股子公司金牛旭阳经营，金牛旭阳拥有的甲醇生产能力为20万吨/年。</t>
+          <t>零售|公司自设立以来主要从事连锁超市、百货商场的运营业务。公司立足于江西省内，多年来通过深耕本地市场、持续推进门店升级转型，成为以生鲜、食品为核心品类的零售企业。公司是江西省商贸流通行业首家上市企业，江西本土领先的连锁经营企业。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>煤化工</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
+          <t>有机硅</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>2.8352</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东岳硅材公告，预计前三季度净利润同比增长19050%-19750%。</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sh603788</t>
+          <t>sh605399</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>宁波高发</t>
+          <t>晨光新材</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>15</v>
+        <v>13.06</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>9.970700000000001</v>
+        <v>10.0253</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>汽车踏板|公司产品电子换挡器、汽车拉索、电子油门踏板皆已配套新能源车。</t>
+          <t>有机硅|公司是国内功能性硅烷行业中产业链最为完整的企业之一，产品涉及功能性硅烷基础原料、中间体和成品，主营产品按照不同的官能团分为氨基硅烷、环氧基硅烷、氯丙基硅烷、含硫硅烷、原硅酸酯、甲基丙烯酰氧基硅烷、乙烯基硅烷、烷基硅烷、含氢硅烷等。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>汽车踏板</t>
+          <t>有机硅</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
+          <t>有机硅</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>2.8352</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东岳硅材公告，预计前三季度净利润同比增长19050%-19750%。</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh603073</t>
+          <t>sz300821</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>彩蝶实业</t>
+          <t>东岳硅材</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>22.97</v>
+        <v>17.15</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>10.0096</v>
+        <v>20.014</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>化纤|公司专注于涤纶面料、无缝成衣和涤纶长丝的研发、生产和销售及染整受托加工业务。其中，涤纶长丝业务生产的DTY可以用于涤纶面料和无缝成衣的生产。</t>
+          <t>业绩+有机硅|1.东岳硅材公告称，预计2026年前三季度归属于上市公司股东的净利润为5.47亿元-5.67亿元，同比增长19050%-19750%。2026年前三季度，受市场环境及行业供需格局改善影响，公司主要产品价格上涨。
+2.公司是我国有机硅行业中生产规模最大的企业之一，位列有机硅行业全球前十、中国第四，主要产品包括硅橡胶、硅油、气相白炭黑等有机硅下游深加工产品以及有机硅中间体等。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>化纤</t>
+          <t>业绩, 有机硅</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>有机硅</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>2.8352</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东岳硅材公告，预计前三季度净利润同比增长19050%-19750%。</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>sh603155</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新亚强  </t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>9.9786</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>半导体+有机硅|1.公司电子级六甲基二硅氮烷在电子芯片行业用于硅晶圆的表面改性，作为芯片光刻抗蚀剂的助黏剂和清洗剂用于半导体领域，已完成研发并开始生产销售。
+2.公司主要从事有机硅精细化学品研发、生产及销售，主要产品包括以六甲基二硅氮烷为核心的有机硅功能性助剂和苯基氯硅烷两大产品类别，包含十多种有机硅产品。</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>半导体, 有机硅</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>1.6005</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局增值税发票数据显示，国庆假期全国服务消费旺盛，相关行业日均销售收入同比增长19.5%，其中旅游游览和娱乐服务增长23.6%、餐饮服务增长9%。</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>sh600882</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>妙可蓝多</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>9.9948</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>奶酪|“妙可蓝多”已发展成为全国性的奶酪品牌，液态奶方面“广泽”稳居吉林省领先地位。</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>奶酪</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1.6005</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局增值税发票数据显示，国庆假期全国服务消费旺盛，相关行业日均销售收入同比增长19.5%，其中旅游游览和娱乐服务增长23.6%、餐饮服务增长9%。</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>sz002696</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>百洋股份</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>10.0752</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>水产|公司位于广西，水产品加工业务板块将着重研发以罗非鱼、生鱼、金鲳鱼、海鲈鱼为原料的内销产品。</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>水产</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>0.6099</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>据产业链最新调研，10月6家电池样本企业计划排产合计214.6GWh，同比大增57%，环比增长4%。正极、负极、电解液排产同比增幅均逼近或超过48%。</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>sh600241</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>时代万恒</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>10.0094</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>5天5板</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>锂电池|公司旗下九夷锂能主要经营锂离子电池、电池组的研发、生产、制造、系统集成、销售和服务，目标市场定位于电动工具、个人护理、家庭电子、消费品等小动力领域。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>锂电池</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>0.6099</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>据产业链最新调研，10月6家电池样本企业计划排产合计214.6GWh，同比大增57%，环比增长4%。正极、负极、电解液排产同比增幅均逼近或超过48%。</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>sz000546</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>金圆股份</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>9.9078</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>盐湖提锂|公司旗下控股子公司锂源矿业主要从事盐湖卤水锂、钾、硼等资源的勘查和开发。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>盐湖提锂</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>金融科技</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>4.2265</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>中国证券业协会日前在行业内通报了证券公司2026年上半年度经营情况：150家券商实现营业收入3298.10亿元、净利润1386.64亿元，同比分别增长31.38%、23.50%。</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>sh601519</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大智慧  </t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>9.952</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>互联网金融|公司是国内领先的互联网金融信息服务提供商，主要业务聚焦在证券信息服务平台、大数据及数据工程服务和境外业务三大板块。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>互联网金融</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sh603838</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST四通 </t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>10.0255</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>sh603398</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST沐邦 </t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>10.0257</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 1.沐邦高科公告，与铜陵狮子山高新技术产业开发区管理委员会、铜陵高新发展投资有限公司签订《项目投资协议书》，项目名称为年产10GW-N型高效电池片、10GW切片生产基地项目。
+2.公司上市的IP产品 “樱桃小丸子”第一期为“盲盒”类产品。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sz002082</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>ST万邦</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>10.0171</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST股 | 在研发端，公司探索人工智能在创新药设计、筛选、实验设计等环节的应用，目前全球首个治疗胃轻瘫的中药1.1类新药“理中消痞颗粒”正在开展临床研究。 </t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>sh600825</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>10.0088</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>9天9板</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>sh605058</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>澳弘电子</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>53.35</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>15天9板</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>sh601811</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>9.9947</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>10天7板</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>并购重组|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>sz001300</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>三柏硕</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>9.992599999999999</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>体育产业|公司是一家专注于休闲运动和健身器材系列产品研发、设计、生产和销售的高新技术企业。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>体育产业</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>sz001336</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>楚环科技</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>10.0242</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>环保|公司是一家集研发、设计、制造、销售、服务为一体的废气恶臭治理系统解决方案服务商，主要服务于市政污水处理厂、餐厨垃圾处理厂客户。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>环保</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>sh600408</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>安泰集团</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>9.883699999999999</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>焦炭|公司主营焦炭及其副产品，炼焦采用的是JN60-6型焦炉，产品主要销售给钢铁企业。目前公司焦炭年生产能力已达到240万吨，是山西省焦化龙头企业之一。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>焦炭</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>sz002692</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>远程股份</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>9.9307</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>电力电缆|公司的电力电缆、控制电缆、防火电缆等产品可应用于数据中心领域。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>电力电缆</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>sh605136</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>丽人丽妆</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>10.0233</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>化妆品电商|公司是国内领先的化妆品网络零售服务商，主要从事电商零售业务和品牌营销运营服务。公司运营的“相宜本草官方旗舰店”作为第一家入驻天猫平台的授权美妆品牌官方旗舰店，对电商美妆市场提供了积极推动和标杆作用。公司与施华蔻、兰芝、雅漾、雪花秀、相宜本草、芙丽芳丝、凡士林等超过60个品牌达成合作关系。</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>化妆品电商</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>sh600629</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>华建集团</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>10.0122</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>上海微电子概念|控股公司上海国投旗下子公司上海科技创业投资有限公司持有上海微电子13.275%股权，公司实控人是上海国资委。</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>上海微电子概念</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>sh600207</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>安彩高科</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>10.0196</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>玻璃基板|公司打破日本旭硝子的技术垄断，自研生产出了3mm、4mm光热超白浮法玻璃基板，全光谱透过率达到91%以上，同时积极布局光热玻璃基板企业认证， 目前已获得国内外多家企业认可。</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>玻璃基板</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>sh601069</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>西部黄金</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>9.983400000000001</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>黄金|公司主营业务为黄金采选及冶炼，同时从事铬矿石的开采。公司主要产品包括黄金、铬矿石、铁矿石，其中黄金是公司最主要的产品和最主要收入来源。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>sh600621</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>华鑫股份</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>10.0304</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>券商|公司以证券业务为主，以部分持有型物业经营业务为辅。公司通过全资子公司华鑫证券开展证券业务</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>sh601566</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">九牧王  </t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>9.978299999999999</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>纺织|国内商务休闲男装品牌的领先企业、国内男裤行业的龙头。主要从事男士商务休闲品牌服饰的生产和销售,主要产品包括男裤、茄克、衬衫、T恤和西装等。</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>纺织</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>sh603096</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新经典  </t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>10.0317</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>传媒|公司是一家以内容创意为核心的传媒企业，主要业务包括图书策划与发行、数字图书、图书零售，以及影视剧策划等版权延伸业务。</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>传媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>sz002811</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>郑中设计</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>9.982099999999999</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>半导体+AI应用|1.参股深迪半导体是中国首家研发设计商用消费级和汽车级微机电系统（MEMS）陀螺仪系列惯性传感器的公司，产品主要应用于IOT，手机智能终端，智能家居，人工智能，工业和智能驾舱等领域，并为客户提供增值算法服务。
+2.子公司犀照科技打造的“IDEAFUSION兆材云库数字化平台”专为室内设计师提供一站式全流程数字化服务，目前已全面对外开放，为不同的设计单位提供SaaS化服务，促进项目高效落地。“IDEAFUSION兆材云库数字化平台”部分功能已经接入DeepSeek模型，包括物料顾问检索推理场景、黑洞文本重写场景 、知识库顾问场景。</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>半导体, AI应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>sh603216</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>梦天家居</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>9.9954</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>家居+半导体|1.公司主要从事木门、墙板、柜类等定制化木质家具的设计、研发、生产和销售，为客户提供家居的整体空间解决方案。
+2.参股凌芯微通过创新整合极薄工艺、厚膜工艺、晶圆级封装三大核心制程，构建“CP测试-化镀-减薄-蚀刻-背金-晶圆级封装”一体化服务能力，覆盖功率器件中后段全流程制造需求，可高效支撑新能源汽车、工业控制、AI服务器、光伏储能等高端场景。</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>家居, 半导体</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>sz000736</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>中交发展</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>9.9156</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>房地产|公司是一家国有控股房地产上市公司。主营业务为房地产开发与经营。</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>房地产</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>sh605168</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三人行  </t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>10.0084</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>AI应用+算力租赁|1.在AI营销领域的应用方面，公司持续迭代优化营销领域多模态AI产品，成功构建 “一个”AI全链路营销智能体，逐步实现从策略生成、内容创作、智能投放到效果归因的全链路营销自动化闭环。
+2.公司设立子公司青海三人行绿能智算科技有限公司，从事算力租赁、算力解决方案服务等综合性算力服务业务。</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>AI应用, 算力租赁</t>
         </is>
       </c>
     </row>
@@ -2590,7 +3841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2617,7 +3868,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -2632,7 +3883,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -2647,7 +3898,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -2662,61 +3913,61 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh603200</t>
+          <t>sz002058</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>紫竹高科</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz002866</t>
+          <t>sz002733</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>传艺科技</t>
+          <t>雄韬股份</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz002058</t>
+          <t>sh600812</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>紫竹高科</t>
+          <t>华北制药</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh605303</t>
+          <t>sz002805</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>园林股份</t>
+          <t>丰元股份</t>
         </is>
       </c>
     </row>
@@ -2726,12 +3977,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sh603906</t>
+          <t>sz300530</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>龙蟠科技</t>
+          <t>领湃科技</t>
         </is>
       </c>
     </row>
@@ -2741,12 +3992,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sh600663</t>
+          <t>sz001300</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">陆家嘴  </t>
+          <t>三柏硕</t>
         </is>
       </c>
     </row>
@@ -2756,12 +4007,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sh603928</t>
+          <t>sz001336</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>兴业股份</t>
+          <t>楚环科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>sh600408</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>安泰集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>sh600400</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>红豆股份</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="91" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="278" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="363" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -556,15 +556,15 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6.496300000000001</v>
+        <v>2.9486</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -577,14 +577,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40.18</v>
+        <v>44.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.991800000000001</v>
+        <v>10.005</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>4天3板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -605,15 +605,15 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>6.496300000000001</v>
+        <v>2.9486</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -626,24 +626,24 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>16.2</v>
+        <v>17.82</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.9796</v>
+        <v>10</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>4天3板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧+出版|公司首部AI漫剧《穿越1988》完成170集制作上线，全网播放量突破1.2亿，红果热度值超4000万。</t>
+          <t>AI漫剧|公司首部AI漫剧《穿越1988》完成170集制作上线，全网播放量突破1.2亿，红果热度值超4000万。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧, 出版</t>
+          <t>AI漫剧</t>
         </is>
       </c>
     </row>
@@ -654,15 +654,15 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6.496300000000001</v>
+        <v>2.9486</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -675,25 +675,25 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>25.44</v>
+        <v>27.98</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.987</v>
+        <v>9.984299999999999</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>5天3板</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>AI短剧|1.公司已经搭建起专业的短剧生产运营体系。公司2025年度AI短剧业务收入预计不超过2025年度主营业务收入的1%。
+          <t>AI+短剧|1.公司已经搭建起专业的短剧生产运营体系。公司2025年度AI短剧业务收入预计不超过2025年度主营业务收入的1%。
 2.MiniMax与掌阅科技合作的对话式AI应用“阅爱聊”，能让文学作品中的角色来到现实，与用户展开一场“跨次元”对谈。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>AI短剧</t>
+          <t>AI, 短剧</t>
         </is>
       </c>
     </row>
@@ -704,36 +704,40 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6.496300000000001</v>
+        <v>2.9486</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh601595</t>
+          <t>sz001330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>上海电影</t>
+          <t>博纳影业</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24.74</v>
+        <v>7.67</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.0044</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+        <v>10.043</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>AI+短剧|上影元已与多家大模型公司建立深度合作，联动公司参与发起设立的上影新视野基金，已布局“AI+社交”“AI+游戏”“AI+短剧”等泛娱乐产品。</t>
+          <t>AI+短剧|短剧业务方面，AIGC短剧《三星堆：未来启示录》由抖音联合出品，目前制作中的短剧项目如《天罗地网》《非遗手艺人》等，也已与红果短剧等头部短剧平台、中央广播电视总台及其他媒体平台开展合作，积极探索精品短剧的生产与发行新模式。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -749,36 +753,40 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6.496300000000001</v>
+        <v>2.9486</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh601929</t>
+          <t>sz002343</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>吉视传媒</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2.5</v>
+        <v>6.69</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.1322</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+        <v>10.0329</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>短剧|公司与吉林广播电视台、长影集团有限责任公司、深圳市来画科技文化有限公司联合签署战略合作协议，发挥四方优势，以联合出品、联合制作、委托制作、国际版制作等形式，共同策划推出微短剧、影视剧、专题片、虚实影像互动剧、社交游戏等精品视频内容与应用服务等精品内容。</t>
+          <t>短剧|公司已形成了以自有IP为核心资源，以影视IP内容投资、开发、制作及发行为核心业务，积极延伸拓展电影、网络电影、网络微短剧、互动剧、小程序短剧、IP线下衍生等相关品类的业务体系。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -794,41 +802,45 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6.496300000000001</v>
+        <v>2.9486</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz000892</t>
+          <t>sh601929</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>欢瑞世纪</t>
+          <t>吉视传媒</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>4.85</v>
+        <v>2.75</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9.9773</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>AI+短剧|公司与上海阶跃星辰智能科技有限公司已达成战略合作，双方共建“麟跃”AI联合实验室，合作方向为短剧Agent产品，双方将合力打造短剧Agent产品，深化探索AI技术在相关影视应用、短剧管理与投流产品等方向的应用。</t>
+          <t>短剧|公司与吉林广播电视台、长影集团有限责任公司、深圳市来画科技文化有限公司联合签署战略合作协议，发挥四方优势，以联合出品、联合制作、委托制作、国际版制作等形式，共同策划推出微短剧、影视剧、专题片、虚实影像互动剧、社交游戏等精品视频内容与应用服务等精品内容。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>AI, 短剧</t>
+          <t>短剧</t>
         </is>
       </c>
     </row>
@@ -839,42 +851,45 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.496300000000001</v>
+        <v>2.9486</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz300364</t>
+          <t>sh601595</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>中文在线</t>
+          <t>上海电影</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>24.47</v>
+        <v>27.21</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>20.0098</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+        <v>9.9838</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>短剧+AI|1.在中短剧方面，根据公司旗下四月天小说网、17K小说网平合IP改编的作品初具规模，其中多部取得了单部播放量过亿的佳绩，如《姑娘好心机》、《就想和你谈恋爱》、《皇妃在娱乐圈当顶流》、《特工房东俏房客》、《霸婿崛起》等。
-2.公司于2023年发布AI大模型“中文逍遥”1.0版本，可实现一键生成万字小说、一张图写一部小说、一次读懂100万字小说。目前“中文逍遥”AI内容生产模型已实现持续进化，推出一键小说转剧本、一键本土化转译功能，持续提升用户体验，作者好评率提升70%。</t>
+          <t>AI+短剧|上影元已与多家大模型公司建立深度合作，联动公司参与发起设立的上影新视野基金，已布局“AI+社交”“AI+游戏”“AI+短剧”等泛娱乐产品。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>短剧, AI</t>
+          <t>AI, 短剧</t>
         </is>
       </c>
     </row>
@@ -885,41 +900,45 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.496300000000001</v>
+        <v>2.9486</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz001330</t>
+          <t>sz000892</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>欢瑞世纪</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>6.97</v>
+        <v>5.34</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9.9369</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+        <v>10.1031</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>AI短剧|短剧业务方面，AIGC短剧《三星堆：未来启示录》由抖音联合出品，目前制作中的短剧项目如《天罗地网》《非遗手艺人》等，也已与红果短剧等头部短剧平台、中央广播电视总台及其他媒体平台开展合作，积极探索精品短剧的生产与发行新模式。</t>
+          <t>AI+短剧|公司与上海阶跃星辰智能科技有限公司已达成战略合作，双方共建“麟跃”AI联合实验室，合作方向为短剧Agent产品，双方将合力打造短剧Agent产品，深化探索AI技术在相关影视应用、短剧管理与投流产品等方向的应用。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>AI短剧</t>
+          <t>AI, 短剧</t>
         </is>
       </c>
     </row>
@@ -930,262 +949,264 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.496300000000001</v>
+        <v>2.9486</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz002343</t>
+          <t>sz301052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>果麦文化</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>6.08</v>
+        <v>30.47</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>9.9458</v>
+        <v>20.0079</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>短剧|公司已形成了以自有IP为核心资源，以影视IP内容投资、开发、制作及发行为核心业务，积极延伸拓展电影、网络电影、网络微短剧、互动剧、小程序短剧、IP线下衍生等相关品类的业务体系。</t>
+          <t>AI+短剧|公司已规划拓展影视剧和动漫剧业务并发布AI漫画平台“爱漫阁”。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>AI, 短剧</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6.496300000000001</v>
+        <v>-0.6369</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+          <t>Anthropic发布最新AI模型Claude Haiku 5.5，用于执行那些对成本敏感的任务，新模型定价较Haiku 4.5大幅降低。大模型推理成本加速下降，AI应用端渗透有望提速。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz300413</t>
+          <t>sh605136</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>芒果超媒</t>
+          <t>丽人丽妆</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>23</v>
+        <v>10.38</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>19.9791</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
+        <v>9.957599999999999</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>AI+短剧|1.在AI Agent方面，公司已经进行了相关技术储备和产品开发，推出AI Agent平台—“芒果西米露”平台，目前搭建超过70个智能体，覆盖节目创意、广告创意、内容审核等多个业务场景。
-2.微短剧业务是公司的战略重心之一，芒果TV依托互通互融的制作优势和“芒系”爆款IP的内容优势，致力于打造微短剧赛道的芒果品牌。</t>
+          <t>电商+AI应用|1.公司是国内领先的化妆品网络零售服务商，主要从事电商零售业务和品牌营销运营服务。公司运营的“相宜本草官方旗舰店”作为第一家入驻天猫平台的授权美妆品牌官方旗舰店，对电商美妆市场提供了积极推动和标杆作用。公司与施华蔻、兰芝、雅漾、雪花秀、相宜本草、芙丽芳丝、凡士林等超过60个品牌达成合作关系。
+2.公司积极探索包括生成型AI产品在内的人工智能技术的应用，以提高工作效率和提升用户体验。在基础构建层面，公司已在着手进行部分人工智能软件的API接入工作，为后续相关智能运用推广做前期准备；在实际运营层面，公司考虑使用人工智能软件在优化商品描述、店铺商品图片设计、短视频制作、虚拟主播、客服服务沟通、客户评价分析等方面实现智能化，提高业务效率和质量；在营销层面，公司也计划使用人工智能软件进行广告图像设计和生成。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>AI, 短剧</t>
+          <t>电商, AI应用</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>6.496300000000001</v>
+        <v>-0.6369</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+          <t>Anthropic发布最新AI模型Claude Haiku 5.5，用于执行那些对成本敏感的任务，新模型定价较Haiku 4.5大幅降低。大模型推理成本加速下降，AI应用端渗透有望提速。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh600715</t>
+          <t>sz002990</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>文投控股</t>
+          <t>盛视科技</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1.76</v>
+        <v>55.95</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10</v>
+        <v>10.0079</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>短剧|公司已针对短剧行业进行深入研究，并计划依托自身IP资源孵化优势，结合AIGC等工具的发展应用，探索文化内容与科技手段相融合的新型创作模式。</t>
+          <t>AI应用+半导体|1.公司持续加大对人工智能、大数据、物联网等新一代信息技术的研发投入，旨在为客户提供符合未来发展的智能产品和“AI+行业”解决方案。公司在智慧口岸领域深耕二十余年，已成长为国内领先的智慧口岸查验系统整体解决方案提供商。
+2.参股的苏州亿铸智能科技有限公司是一家将新型存储器ReRAM及存算一体创新计算架构相结合，面向数据中心、云计算、中心侧服务器、自动驾驶及边缘计算等场景的大算力AI芯片公司。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>AI应用, 半导体</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>6.496300000000001</v>
+        <v>-0.6369</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>国内首部AI超写实院线电影《三星堆：未来往事》定档10月23日登陆全国院线。</t>
+          <t>Anthropic发布最新AI模型Claude Haiku 5.5，用于执行那些对成本敏感的任务，新模型定价较Haiku 4.5大幅降低。大模型推理成本加速下降，AI应用端渗透有望提速。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz002181</t>
+          <t>sz002908</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>粤 传 媒</t>
+          <t>德生科技</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>8.02</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9.953199999999999</v>
+        <v>10.0137</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>AI短剧|子公司新媒体公司自主研发了AIGC内容生产一体化平台—“妙创”AIGC 内容生产平台，应用于《广州三部曲》《我为荔枝拍广告》等项目。平台覆盖火爆短剧、创意短视频、妙音AI音乐三大场景，适配从剧本拆解、创意分镜设计到图片与视频生成的各层次需求，为专业内容生产团队、企业品牌部门/融媒体中心、高校等单位提供内容创作服务。</t>
+          <t>AI中医智能体|公司与初芯堂合作共创的AI中医智能体，接入了相关大模型，能够实现智能辅助诊疗、虚拟数字人自动化解读检测报告等；目前已应用社区、企业健康小屋、医馆、药店等场景。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>AI短剧</t>
+          <t>AI中医智能体</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1.4482</v>
+        <v>-0.6369</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+          <t>Anthropic发布最新AI模型Claude Haiku 5.5，用于执行那些对成本敏感的任务，新模型定价较Haiku 4.5大幅降低。大模型推理成本加速下降，AI应用端渗透有望提速。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz000710</t>
+          <t>sz002264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>贝瑞基因</t>
+          <t>新 华 都</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>11.3</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.0292</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>基因检测+AI医疗|1.公司依托其具有自主知识产权的cSMART核心技术为支撑，选择ctDNA作为肿瘤液体活检指标，开启了临床无创肿瘤基因检测的全新模式。
-2.公司自主研发NLPearl遗传疾病人工智能临床决策支持系统、CNVisi智能报告解读系统，为科研和临床工作者提供智能决策支持。公司的CNVisi™利用人工智能深度学习算法，挖掘20+权威公共数据库、百万自有CNV大数据以及20多万份CNV-seq临床实践报告，构建7大临床解读知识库，精准注释解读、一键查询信息、自定义设置参数、AI智能撰写报告。</t>
+          <t>零售+AI应用|1.公司主要业务为互联网营销和超市百货业务，旗下久爱致和服务于多家国际、国内知名企业，也是天猫及京东等多家电子商务平台的合作伙伴。
+2.公司结合AI大模型与电商场景，已开发并上线试运行智能化平台“久爱AI”，一期版本开放商品评论分析、商品信息采集、违禁词风险评估、摘要抽取、文案大纲助手、简历筛选6项AI工具，为优化营销策略、产品结构和日常办公提供技术支持。
+3.阿里巴巴成都及杭州瀚云均为公司股东。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>基因检测, AI医疗</t>
+          <t>零售, AI应用</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1.4482</v>
+        <v>-0.6581</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+          <t>据报道，“十五五”时期我国将投入超过5万亿元建设新型电网，规模远超“十四五”时期，到2030年将初步建成新型电网，可高效支撑28亿千瓦以上新能源消纳。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh600812</t>
+          <t>sz002692</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>远程股份</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>6.03</v>
+        <v>5.24</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.0365</v>
+        <v>10.084</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -1194,1020 +1215,1008 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>链霉素|公司青霉素系列、头孢系列产品品种齐全，覆盖了原料药到制剂的大部分品种，形成了从发酵原料到半合成原料药再到制剂的完整产品链。是国内硫酸链霉素原料药及注射剂的核心生产企业。</t>
+          <t>电缆+IDC电源|公司的电力电缆、控制电缆、防火电缆等产品可应用于数据中心领域。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>链霉素</t>
+          <t>电缆, IDC电源</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1.4482</v>
+        <v>-0.6581</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+          <t>据报道，“十五五”时期我国将投入超过5万亿元建设新型电网，规模远超“十四五”时期，到2030年将初步建成新型电网，可高效支撑28亿千瓦以上新能源消纳。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz300981</t>
+          <t>sh600192</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>中红医疗</t>
+          <t>长城电工</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23.36</v>
+        <v>7.93</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>19.9795</v>
+        <v>9.9861</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>医用手套|公司主要从事高品质丁腈手套、PVC手套等医用及工业用一次性防护手套的研发、生产与销售，是国内最早生产销售PVC手套和丁腈手套的企业之一。</t>
+          <t>电网设备|公司主要从事高中低压开关成套设备、高中低压电器元件、母线槽、电气传动自动化装置、新能源装备等电工电器类产品的研发、生产与销售，先后为三峡工程、载人航天、奥运鸟巢、青藏铁路等多项国家重点工程提供优质产品。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>医用手套</t>
+          <t>电网设备</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1.4482</v>
+        <v>-0.6581</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+          <t>据报道，“十五五”时期我国将投入超过5万亿元建设新型电网，规模远超“十四五”时期，到2030年将初步建成新型电网，可高效支撑28亿千瓦以上新能源消纳。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz002675</t>
+          <t>sh600560</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东诚药业</t>
+          <t>金自天正</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>13.89</v>
+        <v>12.53</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.9762</v>
+        <v>10.0088</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司着力打造放射性诊疗一体化药物创新平台——烟台蓝纳成，其具有放射性诊疗一体化药物创新研发和全球领先的纳米递送技术的特点，适应症涵盖前列腺癌、胃癌、结直肠癌、鼻咽癌等多种癌症的诊断与治疗产品，其中部分产品进行中美双报。</t>
+          <t>机器人+智能电网|1.公司部分无人化应用工程中使用工业机器人替代人工进行取样、存样、打码、搬运、检测等工作。
+2.公司主要产品电气传动装置、电力半导体元器件等均为电力电子相关产品，部分产品可用于智能电网行业。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>机器人, 智能电网</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>智能电网</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1.4482</v>
+        <v>-0.6581</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+          <t>据报道，“十五五”时期我国将投入超过5万亿元建设新型电网，规模远超“十四五”时期，到2030年将初步建成新型电网，可高效支撑28亿千瓦以上新能源消纳。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh605177</t>
+          <t>sz002441</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东亚药业</t>
+          <t>众业达</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>28.29</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.9922</v>
+        <v>10.0358</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>抗菌类药物|公司已掌握头孢克洛原料药关键中间体7-ACCA的生产技术，是行业内为数不多的可以从起始物料青霉素开始，全产业链合成头孢克洛原料药的公司之一。</t>
+          <t>电网设备|公司的中低压电气产品主要应用于输配电和配网等环节，服务于电源、电网以及各类具有配电需求的最终应用。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>抗菌类药物</t>
+          <t>电网设备</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1.4482</v>
+        <v>-1.6025</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+          <t>中共中央、国务院近日印发《关于发展新质生产力的意见》。意见提出，全面实施“人工智能+”行动。加快推进智能网联新能源汽车、人工智能手机和电脑、人形机器人等新一代智能终端场景应用。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz002317</t>
+          <t>sz002242</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>众生药业</t>
+          <t>九阳股份</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>25.49</v>
+        <v>16.64</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10.0129</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
+        <v>9.9802</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6天6板</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司布局了几个治疗非酒精性脂肪性肝炎（NASH）的创新药，其中ZSP1601、ZSP0678、RAY1225项目处于临床试验的不同阶段。</t>
+          <t>AI机器人|公司持有深思考人工智能机器人科技（北京）有限公司7.92%的股份，旗下产品包括AI机器人。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>AI机器人</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.8928999999999999</v>
+        <v>-1.6025</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>工信部等七部门联合印发的《新型电池产业发展“十五五”规划》：规划提出到2030年全固态电池初步实现规模化应用、长寿命锂电池循环寿命达1.5万次等目标。</t>
+          <t>中共中央、国务院近日印发《关于发展新质生产力的意见》。意见提出，全面实施“人工智能+”行动。加快推进智能网联新能源汽车、人工智能手机和电脑、人形机器人等新一代智能终端场景应用。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz002058</t>
+          <t>sh603528</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>紫竹高科</t>
+          <t>多伦科技</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>24.44</v>
+        <v>7.05</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.991</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>9.984400000000001</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>固态电池|旗下紫江新材专注铝塑膜产品的研发，同时积极布局固态电池用铝塑膜产品，以适应未来固态电池行业发展带动的新增需求。</t>
+          <t>AI应用+机器人|1.公司已开展多项人工智能驾考新技术研究，包括基于机器视觉的驾驶人注意力分配识别、基于机器视觉的道路环境目标识别、基于激光雷达的目标探测技术等。
+2.公司通过珠海星芯投资基金参与了众擎机器人科技有限公司Pre-A++轮融资，并持有其1.57%的股份。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>AI应用, 机器人</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.8928999999999999</v>
+        <v>-1.6025</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>工信部等七部门联合印发的《新型电池产业发展“十五五”规划》：规划提出到2030年全固态电池初步实现规模化应用、长寿命锂电池循环寿命达1.5万次等目标。</t>
+          <t>中共中央、国务院近日印发《关于发展新质生产力的意见》。意见提出，全面实施“人工智能+”行动。加快推进智能网联新能源汽车、人工智能手机和电脑、人形机器人等新一代智能终端场景应用。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz002733</t>
+          <t>sh603992</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
+          <t>松霖科技</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>20.78</v>
+        <v>20.94</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.0053</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.979000000000001</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>固态电池|公司固态电池产品是通过“原位聚合固态电解质技术”和“电极内部电解质动态成膜固化技术”两大核心技术的突破，彻底消除电池热失控风险，并解决“固-固”界面难题，完美适配数据中心、储能电站、轨道交通等对安全性有严苛要求的领域。</t>
+          <t>机器人|旗下松霖机器人与达闼机器人签署了战略合作框架协议，共同探索人形机器人垂直场景应用、核心部件创新升级、机器人出海及其他创新领域的产业机会。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.8928999999999999</v>
+        <v>-1.6025</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>工信部等七部门联合印发的《新型电池产业发展“十五五”规划》：规划提出到2030年全固态电池初步实现规模化应用、长寿命锂电池循环寿命达1.5万次等目标。</t>
+          <t>中共中央、国务院近日印发《关于发展新质生产力的意见》。意见提出，全面实施“人工智能+”行动。加快推进智能网联新能源汽车、人工智能手机和电脑、人形机器人等新一代智能终端场景应用。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz002805</t>
+          <t>sh603500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>丰元股份</t>
+          <t>祥和实业</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>19.44</v>
+        <v>11.04</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.017</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.9602</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>固态电池|公司对固态电池硫化物正极材料有技术储备，还参股了深耕于固态电池领域的中科深蓝汇泽新能源(常州)有限责任公司。</t>
+          <t>超级电容+机器人|1.公司紧跟铝电解电容器技术迭代，先后开发成功V-CHIP电容底座、车用耐振动底座以及应用于超级电容、锂电池、耐550V以上特高压、耐150℃电容器用橡胶密封塞、轴向电容器盖板等产品。
+2.公司于2024年4月30日成立子公司祥和智能，研发、制造和销售工业机器人、智能机器人及人工智能应用软件开发等系祥和智能的经营范围。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>超级电容, 机器人</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.8928999999999999</v>
+        <v>-2.0276</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>工信部等七部门联合印发的《新型电池产业发展“十五五”规划》：规划提出到2030年全固态电池初步实现规模化应用、长寿命锂电池循环寿命达1.5万次等目标。</t>
+          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz300530</t>
+          <t>sh600812</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>领湃科技</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>28.9</v>
+        <v>6.63</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>20.0166</v>
+        <v>9.950199999999999</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">固态电池|公司注重基础研发和前瞻技术开发，已经完成了NCM811电池化学体系研发，固态电解质及固态电池、干法电极及其制备技术的基础试验，相关专利正在申请或已获得授权。
-</t>
+          <t>链霉素|公司青霉素系列、头孢系列产品品种齐全，覆盖了原料药到制剂的大部分品种，形成了从发酵原料到半合成原料药再到制剂的完整产品链。是国内硫酸链霉素原料药及注射剂的核心生产企业。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>链霉素</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.8928999999999999</v>
+        <v>-2.0276</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>工信部等七部门联合印发的《新型电池产业发展“十五五”规划》：规划提出到2030年全固态电池初步实现规模化应用、长寿命锂电池循环寿命达1.5万次等目标。</t>
+          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh600478</t>
+          <t>sh600851</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">科力远  </t>
+          <t>海欣股份</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.9138</v>
+        <v>9.974399999999999</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>固态电池|公司主要针对固态电池核心零部件，开展干法电极的技术开发。</t>
+          <t>创新药|子公司上海海欣生物技术有限公司APDC项目主要用于结直肠癌治疗，目前海欣生物就APDC三期项目正多方面探索解决方案。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.8928999999999999</v>
+        <v>-2.0276</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>工信部等七部门联合印发的《新型电池产业发展“十五五”规划》：规划提出到2030年全固态电池初步实现规模化应用、长寿命锂电池循环寿命达1.5万次等目标。</t>
+          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sh603067</t>
+          <t>sz300006</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>振华股份</t>
+          <t>莱美药业</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>42.31</v>
+        <v>6.56</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.0104</v>
+        <v>19.9269</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>固态电池+铬|1.子公司厦门首能半固态电解液还处于向下游客户小批量供应，共同研发阶段。
-2.公司金属铬产品在高温合金、铜基、铝基特种合金、高端焊接材料、溅射靶材等领域广泛应用，高温合金是燃气轮机的主要材料，单质铬的添加量在15%~20%之间。</t>
+          <t>创新药|2025年4月30日公司在互动平台表示，子公司四川瀛瑞的纳米炭铁混悬注射液（CNSI-Fe）临床试验进展顺利；参股公司康德赛用于治疗晚期卵巢癌的个体化肿瘤疫苗项目（CUD002）、用于治疗中晚期肝硬化的巨噬细胞项目（CUD005）临床一期工作均在稳步推进中。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>固态电池, 铬</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.0219</v>
+        <v>2.0432</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>智元机器人上半年出货量超8600台，占全球市场35%和中国市场45%以上，并且在高基数下保持十倍级增长。</t>
+          <t>中信证券研报表示，AI剧产业链价值有望进一步向具备高商业化效率、优质IP与精品制作能力、高质量语料资源，以及与红果深度合作的公司集中。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz002242</t>
+          <t>sh603096</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t xml:space="preserve">新经典  </t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15.13</v>
+        <v>19.06</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10.0364</v>
+        <v>9.982699999999999</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5天5板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>AI机器人|公司持有深思考人工智能机器人科技（北京）有限公司7.92%的股份，旗下产品包括AI机器人。</t>
+          <t>传媒|公司是一家以内容创意为核心的传媒企业，主要业务包括图书策划与发行、数字图书、图书零售，以及影视剧策划等版权延伸业务。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>AI机器人</t>
+          <t>传媒</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.0219</v>
+        <v>2.0432</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>智元机器人上半年出货量超8600台，占全球市场35%和中国市场45%以上，并且在高基数下保持十倍级增长。</t>
+          <t>中信证券研报表示，AI剧产业链价值有望进一步向具备高商业化效率、优质IP与精品制作能力、高质量语料资源，以及与红果深度合作的公司集中。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh600400</t>
+          <t>sh603230</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>红豆股份</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>3.98</v>
+        <v>14.63</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>9.944799999999999</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>机器人+纺织|1.参股无锡福芯机器人有限公司经营范围包含：服务消费机器人制造、智能机器人销售、人工智能硬件销售、智能机器人的研发、人工智能应用软件开发、人工智能行业应用系统集成服务、大数据服务等。
-2.公司的主营业务为男装的生产与销售。</t>
+          <t>出版传媒|公司的最终控制人为内蒙古自治区人民政府。公司主营业务是出版物的批发、零售；文体用品零售；音像制品发行</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>机器人, 纺织</t>
+          <t>出版传媒</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.0219</v>
+        <v>-0.6907</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>智元机器人上半年出货量超8600台，占全球市场35%和中国市场45%以上，并且在高基数下保持十倍级增长。</t>
+          <t>有市场消息称，欧盟委员会决定对原产于中国的风力发电机塔筒及关键结构件发起反倾销与反补贴立案调查。对此，有上市风电企业表示此为假消息。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sh600843</t>
+          <t>sz002531</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>上工申贝</t>
+          <t>天顺风能</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>8.18</v>
+        <v>8.27</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>9.946199999999999</v>
+        <v>9.9734</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>纺织机械+机器人|公司已经成长为一家占据全球缝制技术制高点并为客户量身定制工业4.0应用解决方案的专业设备供应商，主要产品有缝纫、绣花、裁切、焊接等缝制工艺设备，机器人焊接、组装生产线，程控机械加工流水线，以及智能仓储、自动传输装置等。</t>
+          <t>风电|公司为国内领先的风塔专业生产商，主营产品为1.5MW及以上功率风机的风塔。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>纺织机械, 机器人</t>
+          <t>风电</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.0219</v>
+        <v>-0.6907</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>智元机器人上半年出货量超8600台，占全球市场35%和中国市场45%以上，并且在高基数下保持十倍级增长。</t>
+          <t>有市场消息称，欧盟委员会决定对原产于中国的风力发电机塔筒及关键结构件发起反倾销与反补贴立案调查。对此，有上市风电企业表示此为假消息。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz000420</t>
+          <t>sz002576</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>吉林化纤</t>
+          <t>通达动力</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>3.81</v>
+        <v>16.07</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.1156</v>
+        <v>9.9932</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>机器人+碳纤维|1.公司涉及的碳纤维产品处于产业链上游，可用于机器人制造。
-2.公司是我国主要粘胶纤维生产企业，产品包括粘胶长丝和粘胶短纤，连续多年成为全球优质的粘胶长丝供应商之一。</t>
+          <t>机器人+风电|1.公司生产的伺服电机铁芯可以应用于机器人领域。
+2.公司生产的定转子铁芯产品品种齐全，能够应用于不同种类和型号的电机、包括国标类普通电机，也包括高效电机、风力发电机、牵引电机、新能源汽车驱动电机等对定转子冲片和铁芯质量要求较高的电机产品。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>机器人, 碳纤维</t>
+          <t>机器人, 风电</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.0219</v>
+        <v>-0.7702</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>智元机器人上半年出货量超8600台，占全球市场35%和中国市场45%以上，并且在高基数下保持十倍级增长。</t>
+          <t>在人工智能公司Anthropic发生多起未经授权使用美国政府系统的安全事件后，美国政府宣布实施新的强制性AI安全事件报告要求。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz002480</t>
+          <t>sh603232</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>新筑股份</t>
+          <t>格尔软件</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>6</v>
+        <v>18.68</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.0917</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+        <v>10.0118</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>机器人+液流电池|1.参股奥威科技参与研发的移动充电机器人目前处于对样机进行调试的阶段。
-2.2024年2月21日公告，子公司川发兴能拟启动建设60000m³/a短流程钒电解液生产线建设项目，项目总投资估算4.6亿元。</t>
+          <t>AI+网络安全|1.公司的AI赋能旨在深化AI与密码学、安全、产品三大核心业务的融合,明确推动AI应用从工具引入向范式变革演进,实现“AI赋能效率、创新驱动升级”双重目标。
+2.公司自成立以来一直专注于信息安全行业PKI领域，主要从事以公钥基础设施PKI为核心的商用密码软件产品的研发、生产和销售及服务业务，为用户提供基于PKI的信息安全系列产品、安全服务和信息安全整体解决方案。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>机器人, 液流电池</t>
+          <t>AI, 网络安全</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>网络安全</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.0219</v>
+        <v>-0.7702</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>智元机器人上半年出货量超8600台，占全球市场35%和中国市场45%以上，并且在高基数下保持十倍级增长。</t>
+          <t>在人工智能公司Anthropic发生多起未经授权使用美国政府系统的安全事件后，美国政府宣布实施新的强制性AI安全事件报告要求。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz002979</t>
+          <t>sh688004</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>雷赛智能</t>
+          <t>博汇科技</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>55.58</v>
+        <v>37.25</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>9.9941</v>
+        <v>20.0064</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司在人形机器人领域定位是伺服控制产品与解决方案提供商、为众多整机厂家提供系列化伺服控制核心部件和模组级解决方案。公司从2018年起持续耕耘机器人行业（AGV/AMR、协作机器人等），并于2023年底成功研发出高密度无框力矩电机、CD伺服驱动器、中空编码器、空心杯电机及配套的微型伺服系统等核心产品。</t>
+          <t>网络安全+AI应用|1.公司对各类媒体内容进行多维度分析，精准识别敏感、违规内容，实现对广播电视、IPTV/OTT、互联网站、微信、微博、各类短视频、自媒体等传播媒介播放的视听内容进行监管。
+2.公司在人工智能、大数据、云计算领域已布局多年。通过综合运用人工智能深度学习算法，通过海量专项素材的机器学习，不断优化人脸识别、场景识别、语音识别、文字识别等智能化识别引擎，对各类媒体内容进行多维度分析，精准识别敏感、违规内容。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>网络安全, AI应用</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>3.6493</v>
+        <v>-1.2496</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Anthropic扩大先进AI模型访问权限，允许经过验证的机构对关键基础设施安全系统进行高风险攻击性测试。</t>
+          <t>中欧贸易投资磋商机制第二次例会日前召开，欧方澄清，欧盟对逆变器项目的融资指导文件不针对特定国家，双方将就该问题进一步磋商。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz002912</t>
+          <t>sh688517</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>中新赛克</t>
+          <t>金冠电气</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>28.55</v>
+        <v>21.18</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.0193</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>8天4板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>AI+网络安全|公司推出的小赛安全智脑产品，支持多模型底座，基于智能体、RAG等技术，包含渗透测试智能体、事件调查智能体、代码安全审计智能体，也配备了敏感数据识别、智能解码、安全知识问答等多种智能体应用，全方位满足安全运维场景下的各类用户需求，为企业数据与网络安全保驾护航。</t>
+          <t>电网设备+储能项目|1.公司长期服务于以特高压为骨干网架、各级电网协调发展的坚强智能电网建设，主要为用户提供交、直流金属氧化物避雷器及智能配电网系列产品。
+2.金冠电气公告称，公司全资子公司金冠光储充与SPIRO签订EPC总承包框架协议，合同总金额不超过2.96亿美元(含税)，标的为非洲区域内50个并网或离网光储充一体化电站项目。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>AI, 网络安全</t>
+          <t>电网设备, 储能项目</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>储能</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>3.6493</v>
+        <v>-1.2496</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Anthropic扩大先进AI模型访问权限，允许经过验证的机构对关键基础设施安全系统进行高风险攻击性测试。</t>
+          <t>中欧贸易投资磋商机制第二次例会日前召开，欧方澄清，欧盟对逆变器项目的融资指导文件不针对特定国家，双方将就该问题进一步磋商。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz300369</t>
+          <t>sz301658</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>绿盟科技</t>
+          <t>首航新能</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>10.43</v>
+        <v>27.12</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>20.023</v>
+        <v>20</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>AI+网络安全|2024年公司推出了自主研发的“风云卫AI安全能力平台”，该平台融合大模型、小模型、知识图谱等核心能力，依托公司二十余年的网络安全研究积累与攻防对抗实践，构建了开放式PaaS架构，广泛适配于安全运营、检测响应、攻防实战等场景。</t>
+          <t>储能电池|公司的储能电池主要为磷酸铁锂电池，能够适配多品牌光伏储能逆变器，主要应用于户用及小型工商业储能。公司光伏储能逆变器功率范围已涵盖3kW~20kW，适用于户用、小型工商业并离网储能多种场景。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>AI, 网络安全</t>
+          <t>储能电池</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3.6493</v>
+        <v>-2.2713</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Anthropic扩大先进AI模型访问权限，允许经过验证的机构对关键基础设施安全系统进行高风险攻击性测试。</t>
+          <t>受3D打印需求向好支撑，近期聚乳酸产业链产品价格维持高位。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz002212</t>
+          <t>sz300829</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>天融信</t>
+          <t>金丹科技</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7.56</v>
+        <v>28.02</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10.0437</v>
+        <v>20</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>网络安全+AI|1.公司作为中国领先的网络安全、大数据与云服务提供商，为政府、金融、运营商、能源、卫生、教育、交通、制造等各行业客户提供网络安全产品、大数据产品和云服务。
-2.2024年11月26日公司在互动平台表示，AI Agent（智能体）是公司天问大模型关键技术之一，具备自然语言处理、风险预测、情报抽取等核心能力，应用于安全知识问答、日志分析、告警研判等安全运营场景。</t>
+          <t>乳酸|公司目前主要产品为乳酸、乳酸钠和乳酸钙。乳酸系列产品广泛应用于食品、饲料、生物降解材料、工业、医药等领域。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>网络安全, AI</t>
+          <t>乳酸</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>化工</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>3.6493</v>
+        <v>-2.2713</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Anthropic扩大先进AI模型访问权限，允许经过验证的机构对关键基础设施安全系统进行高风险攻击性测试。</t>
+          <t>受3D打印需求向好支撑，近期聚乳酸产业链产品价格维持高位。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh603232</t>
+          <t>sh603968</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>格尔软件</t>
+          <t>醋化股份</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>16.98</v>
+        <v>13.05</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>9.9741</v>
+        <v>10.0337</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>AI+网络安全|1.公司的AI赋能旨在深化AI与密码学、安全、产品三大核心业务的融合,明确推动AI应用从工具引入向范式变革演进,实现“AI赋能效率、创新驱动升级”双重目标。
-2.公司自成立以来一直专注于信息安全行业PKI领域，主要从事以公钥基础设施PKI为核心的商用密码软件产品的研发、生产和销售及服务业务，为用户提供基于PKI的信息安全系列产品、安全服务和信息安全整体解决方案。</t>
+          <t>染料|公司的双乙甲酯产品涉及分散染料领域。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>AI, 网络安全</t>
+          <t>染料</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>3.6493</v>
+        <v>-2.302</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Anthropic扩大先进AI模型访问权限，允许经过验证的机构对关键基础设施安全系统进行高风险攻击性测试。</t>
+          <t>行业媒体报道，韩国正极材料企业EcoPro BM宣布，已经和三星SDI签署谅解备忘录（MOU），双方将围绕全固态电池材料开展合作，以推进硫化物系全固态电池于2027年实现商业化。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh688152</t>
+          <t>sh603032</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>麒麟信安</t>
+          <t>德新科技</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>45.85</v>
+        <v>20.42</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>19.9948</v>
+        <v>10.0216</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>网络安全|公司操作系统、云计算产品以安全为特色，并和公司信息安全产品有机融合构成三位一体系统性整体安全，可满足国防领域高安全需求。公司自设立以来长期服务于国防单位，承建了众多国防单位信息化建设项目，并承担了多项国防单位委托的型号装备配套和技术预研项目，能快速理解并响应国防单位多样化的需求，目前主要应用于航天测发控、训练、指挥、办公、教育培训等。</t>
+          <t>固态电池|公司从2021年起向清陶供应模具产品，用于固态电池的生产。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>固态电池</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>4.6913</v>
+        <v>-2.302</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>世界气象组织周四在月度气候公报中表示，今年的厄尔尼诺现象将在12月达到峰值前进一步增强，并且持续至2027年2月的可能性接近100%。</t>
+          <t>行业媒体报道，韩国正极材料企业EcoPro BM宣布，已经和三星SDI签署谅解备忘录（MOU），双方将围绕全固态电池材料开展合作，以推进硫化物系全固态电池于2027年实现商业化。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh601118</t>
+          <t>sz002591</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>海南橡胶</t>
+          <t>恒大高新</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
@@ -2216,1617 +2225,537 @@
       <c r="H37" s="2" t="n">
         <v>9.9846</v>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>橡胶|地处海南省海口市，海南省农垦投资控股集团旗下上市公司，是目前中国最大的天然橡胶生产企业。</t>
+          <t>服务器+固态电池|1.公司构建"通信服务-算力支撑"协同生态，旗下宝乐互动在AI算力服务器业务已拥有完整产线。
+2.公司申请的在国家有关发明专利机构审查的“固态电池专利”写到：该发明专利技术是一种复合固态锂离子电池及其制备方法，能够抑制高温下的复合固态电解质膜和负极片的膨胀，有利于电极界面的平整接触，特别是对负硅碳材料效果更明显，能改善电池循环寿命，提升电池安全性能。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>橡胶</t>
+          <t>服务器, 固态电池</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>4.6913</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>世界气象组织周四在月度气候公报中表示，今年的厄尔尼诺现象将在12月达到峰值前进一步增强，并且持续至2027年2月的可能性接近100%。</t>
-        </is>
-      </c>
+        <v>-1.7249</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sh600127</t>
+          <t>sz002667</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>*ST威领</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>15.18</v>
+        <v>24.41</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10</v>
+        <v>10.0045</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>大米|公司是我国粮食系统的第一家上市公司，是首批农业产业化国家重点龙头企业，国家水稻工程优质米示范基地。公司以优质粮油、新型健康食品和药品开发、生产、销售为发展方向，坚持农、工、科、贸一体化的现代农业产业化经营模式，主要产品有大米、面粉、面条、植物油、米粉、牛奶、糖果、果冻、药品等。</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>大米</t>
-        </is>
-      </c>
+          <t>*ST威领公告称，公司收到西藏山南锑金资源有限公司出具的要约收购报告书摘要。山南锑金拟向全体股东发出部分要约，收购股份数量为7817.745万股，要约价格为18元/股，占公司总股本的30%。本次要约收购所需资金总额预计不超过14.07亿元，收购人已存入履约保证金7.04亿元。要约收购完成后，山南锑金将最多持有公司30%股份，取得公司控制权。</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>4.6913</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>世界气象组织周四在月度气候公报中表示，今年的厄尔尼诺现象将在12月达到峰值前进一步增强，并且持续至2027年2月的可能性接近100%。</t>
-        </is>
-      </c>
+        <v>-1.7249</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sh600371</t>
+          <t>sz301030</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>万向德农</t>
+          <t>*ST仕净</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>14.97</v>
+        <v>4.5</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>9.992700000000001</v>
+        <v>20</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>种业|公司从事的主要业务为玉米杂交种子研发、生产、销售，主营包括但不限于“京科968”、“德单系列”等玉米杂交种的生产与销售。</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>种业</t>
-        </is>
-      </c>
+          <t>ST股 | 公司在制程污染防控领域服务了众多光伏、集成电路等泛半导体行业的优质客户，如晶科能源、天合光能、阿特斯、东方日升、英特尔、长鑫存储、先进半导体等。</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>农业种植</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>4.6913</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>世界气象组织周四在月度气候公报中表示，今年的厄尔尼诺现象将在12月达到峰值前进一步增强，并且持续至2027年2月的可能性接近100%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh600354</t>
+          <t>sh600825</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>敦煌种业</t>
+          <t>新华传媒</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>9.99</v>
+        <v>13.78</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10.022</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
+        <v>9.976100000000001</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>10天10板</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>种业|公司目前主要从事各类农作物种子的研发、生产、加工、销售和脱水菜、番茄粉、番茄酱、啤酒花制品的加工、销售以及棉花及其副产品的收购、加工、仓储、贸易。</t>
+          <t>并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>种业</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>商业零售</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>3.3686</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>记者10月8日从国家税务总局获悉，增值税发票最新数据显示，国庆假期，全国服务消费旺盛，相关行业日均销售收入同比增长19.5%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh601086</t>
+          <t>sh601811</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>14.94</v>
+        <v>23</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10.0147</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
+        <v>9.995200000000001</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>11天8板</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>零售|公司从事以百货业为主，超市、电器为辅的连锁零售业务，是甘肃省内最大的连锁零售企业。</t>
+          <t>并购重组|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>商业零售</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>3.3686</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>记者10月8日从国家税务总局获悉，增值税发票最新数据显示，国庆假期，全国服务消费旺盛，相关行业日均销售收入同比增长19.5%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sh603101</t>
+          <t>sh600241</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>汇嘉时代</t>
+          <t>时代万恒</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>7.99</v>
+        <v>12.94</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10.0551</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+        <v>10.034</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>6天6板</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>零售|公司作为新疆地区百货商超零售连锁企业，经营业态涵盖购物中心、传统百货、超市等。</t>
+          <t>锂电池|公司旗下九夷锂能主要经营锂离子电池、电池组的研发、生产、制造、系统集成、销售和服务，目标市场定位于电动工具、个人护理、家庭电子、消费品等小动力领域。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>锂电池</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>商业零售</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>3.3686</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>记者10月8日从国家税务总局获悉，增值税发票最新数据显示，国庆假期，全国服务消费旺盛，相关行业日均销售收入同比增长19.5%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sh600865</t>
+          <t>sz002696</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>百大集团</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>11.51</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>10.0382</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+        <v>9.9727</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>零售|公司主营业务为商品零售，主要业态为百货商场，旗下杭州百货大楼是公司最主要的营收和利润来源，是杭州市区域龙头百货商场之一。</t>
+          <t>水产|公司位于广西，水产品加工业务板块将着重研发以罗非鱼、生鱼、金鲳鱼、海鲈鱼为原料的内销产品。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>水产</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>商业零售</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>3.3686</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>记者10月8日从国家税务总局获悉，增值税发票最新数据显示，国庆假期，全国服务消费旺盛，相关行业日均销售收入同比增长19.5%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sh605188</t>
+          <t>sh600693</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>国光连锁</t>
+          <t>东百集团</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>13.84</v>
+        <v>11.18</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>10.0159</v>
+        <v>10.0394</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>零售|公司自设立以来主要从事连锁超市、百货商场的运营业务。公司立足于江西省内，多年来通过深耕本地市场、持续推进门店升级转型，成为以生鲜、食品为核心品类的零售企业。公司是江西省商贸流通行业首家上市企业，江西本土领先的连锁经营企业。</t>
+          <t>并购重组|东百集团公告称，公司全资子公司东百创智拟收购杭州快灵光电科技有限公司52.6667%股权，暂定转让对价3.16亿元。交易完成后，快灵光电及其子公司光特科技将纳入公司合并报表范围。标的公司主要从事光探测芯片研发生产销售。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>有机硅</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>2.8352</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>东岳硅材公告，预计前三季度净利润同比增长19050%-19750%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sh605399</t>
+          <t>sz301419</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>晨光新材</t>
+          <t>阿莱德</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>13.06</v>
+        <v>47.7</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10.0253</v>
+        <v>20</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>有机硅|公司是国内功能性硅烷行业中产业链最为完整的企业之一，产品涉及功能性硅烷基础原料、中间体和成品，主营产品按照不同的官能团分为氨基硅烷、环氧基硅烷、氯丙基硅烷、含硫硅烷、原硅酸酯、甲基丙烯酰氧基硅烷、乙烯基硅烷、烷基硅烷、含氢硅烷等。</t>
+          <t>液冷|公司的导热界面材料和液冷散热器件产品可根据其不同的形态、材料和特性，广泛应用于ICT通信、消费电子和光模块等场景，且部分产品如导热垫片、导热凝胶、热管、均温板等已在批量供货中。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>有机硅</t>
+          <t>液冷</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>有机硅</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>2.8352</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>东岳硅材公告，预计前三季度净利润同比增长19050%-19750%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sz300821</t>
+          <t>sh600831</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>东岳硅材</t>
+          <t>广电网络</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>17.15</v>
+        <v>3.91</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>20.014</v>
+        <v>10.1408</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>业绩+有机硅|1.东岳硅材公告称，预计2026年前三季度归属于上市公司股东的净利润为5.47亿元-5.67亿元，同比增长19050%-19750%。2026年前三季度，受市场环境及行业供需格局改善影响，公司主要产品价格上涨。
-2.公司是我国有机硅行业中生产规模最大的企业之一，位列有机硅行业全球前十、中国第四，主要产品包括硅橡胶、硅油、气相白炭黑等有机硅下游深加工产品以及有机硅中间体等。</t>
+          <t>重整|10月9日，公司收到西安市中院《决定书》，法院决定受理该预重整申请，并指定陕西广电网络传媒（集团）股份有限公司清算组为预重整临时管理人。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>业绩, 有机硅</t>
+          <t>重整</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>有机硅</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>2.8352</v>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>东岳硅材公告，预计前三季度净利润同比增长19050%-19750%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sh603155</t>
+          <t>sz001231</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">新亚强  </t>
+          <t>农心科技</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>15.43</v>
+        <v>25.61</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>9.9786</v>
+        <v>10.0086</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>半导体+有机硅|1.公司电子级六甲基二硅氮烷在电子芯片行业用于硅晶圆的表面改性，作为芯片光刻抗蚀剂的助黏剂和清洗剂用于半导体领域，已完成研发并开始生产销售。
-2.公司主要从事有机硅精细化学品研发、生产及销售，主要产品包括以六甲基二硅氮烷为核心的有机硅功能性助剂和苯基氯硅烷两大产品类别，包含十多种有机硅产品。</t>
+          <t>农药|公司的主营业务为农药制剂产品的研发、生产与销售，主要产品包括杀虫剂、杀菌剂和除草剂。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>半导体, 有机硅</t>
+          <t>农药</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>1.6005</v>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局增值税发票数据显示，国庆假期全国服务消费旺盛，相关行业日均销售收入同比增长19.5%，其中旅游游览和娱乐服务增长23.6%、餐饮服务增长9%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sh600882</t>
+          <t>sh603336</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>妙可蓝多</t>
+          <t>宏辉果蔬</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>21.13</v>
+        <v>10.45</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>9.9948</v>
+        <v>10</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>奶酪|“妙可蓝多”已发展成为全国性的奶酪品牌，液态奶方面“广泽”稳居吉林省领先地位。</t>
+          <t>果蔬+创新药|1.公司是一家集果蔬产品的种植管理、采后收购、产地预冷、冷冻仓储、预选分级、加工包装、冷链配送于一体的专业生鲜产品服务商。
+2.2026年4月28日公告，公司拟使用自有及自筹资金约7亿元收购江西施美药业股份有限公司41.128%股份。施美药业是一家致力于复方降压、降脂、降糖药和心脑血管药的现代化高科技创新型制药企业，已建成成熟的生产与经营体系，主营产品涵盖化学原料药及片剂、胶囊等主流制剂。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>奶酪</t>
+          <t>果蔬, 创新药</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>1.6005</v>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局增值税发票数据显示，国庆假期全国服务消费旺盛，相关行业日均销售收入同比增长19.5%，其中旅游游览和娱乐服务增长23.6%、餐饮服务增长9%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sz002696</t>
+          <t>sh601127</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t xml:space="preserve">赛力斯  </t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>7.32</v>
+        <v>51.24</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10.0752</v>
+        <v>10.0043</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>水产|公司位于广西，水产品加工业务板块将着重研发以罗非鱼、生鱼、金鲳鱼、海鲈鱼为原料的内销产品。</t>
+          <t>汽车整车|公司与华为进行“智选模式”的合作，华为深度参与设计车型和品牌打造，在技术和渠道方面全力赋能公司。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>水产</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>锂电池</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>0.6099</v>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>据产业链最新调研，10月6家电池样本企业计划排产合计214.6GWh，同比大增57%，环比增长4%。正极、负极、电解液排产同比增幅均逼近或超过48%。</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>sh600241</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>时代万恒</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>10.0094</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>5天5板</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>锂电池|公司旗下九夷锂能主要经营锂离子电池、电池组的研发、生产、制造、系统集成、销售和服务，目标市场定位于电动工具、个人护理、家庭电子、消费品等小动力领域。</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>锂电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>锂电池</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>0.6099</v>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>据产业链最新调研，10月6家电池样本企业计划排产合计214.6GWh，同比大增57%，环比增长4%。正极、负极、电解液排产同比增幅均逼近或超过48%。</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>sz000546</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>金圆股份</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>9.9078</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>盐湖提锂|公司旗下控股子公司锂源矿业主要从事盐湖卤水锂、钾、硼等资源的勘查和开发。</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>盐湖提锂</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>金融科技</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>4.2265</v>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>中国证券业协会日前在行业内通报了证券公司2026年上半年度经营情况：150家券商实现营业收入3298.10亿元、净利润1386.64亿元，同比分别增长31.38%、23.50%。</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>sh601519</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">大智慧  </t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>9.952</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>互联网金融|公司是国内领先的互联网金融信息服务提供商，主要业务聚焦在证券信息服务平台、大数据及数据工程服务和境外业务三大板块。</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>互联网金融</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>-0.0052</v>
-      </c>
-      <c r="C53" s="2" t="inlineStr"/>
-      <c r="D53" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>sh603838</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST四通 </t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>10.0255</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>-0.0052</v>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>sh603398</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST沐邦 </t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>10.0257</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 1.沐邦高科公告，与铜陵狮子山高新技术产业开发区管理委员会、铜陵高新发展投资有限公司签订《项目投资协议书》，项目名称为年产10GW-N型高效电池片、10GW切片生产基地项目。
-2.公司上市的IP产品 “樱桃小丸子”第一期为“盲盒”类产品。</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>-0.0052</v>
-      </c>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>sz002082</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>ST万邦</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>10.0171</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ST股 | 在研发端，公司探索人工智能在创新药设计、筛选、实验设计等环节的应用，目前全球首个治疗胃轻瘫的中药1.1类新药“理中消痞颗粒”正在开展临床研究。 </t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>sh600825</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>新华传媒</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>12.53</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>10.0088</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>9天9板</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>sh605058</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>澳弘电子</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>15天9板</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>PCB</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>sh601811</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>新华文轩</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>20.91</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>9.9947</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>10天7板</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>并购重组|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr"/>
-      <c r="D59" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>sz001300</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>三柏硕</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>9.992599999999999</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>体育产业|公司是一家专注于休闲运动和健身器材系列产品研发、设计、生产和销售的高新技术企业。</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>体育产业</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>sz001336</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>楚环科技</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>22.72</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>10.0242</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>环保|公司是一家集研发、设计、制造、销售、服务为一体的废气恶臭治理系统解决方案服务商，主要服务于市政污水处理厂、餐厨垃圾处理厂客户。</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>环保</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>sh600408</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>安泰集团</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>9.883699999999999</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>焦炭|公司主营焦炭及其副产品，炼焦采用的是JN60-6型焦炉，产品主要销售给钢铁企业。目前公司焦炭年生产能力已达到240万吨，是山西省焦化龙头企业之一。</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>焦炭</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>sz002692</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>远程股份</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>9.9307</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>电力电缆|公司的电力电缆、控制电缆、防火电缆等产品可应用于数据中心领域。</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>电力电缆</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr"/>
-      <c r="D63" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>sh605136</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>丽人丽妆</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>10.0233</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>化妆品电商|公司是国内领先的化妆品网络零售服务商，主要从事电商零售业务和品牌营销运营服务。公司运营的“相宜本草官方旗舰店”作为第一家入驻天猫平台的授权美妆品牌官方旗舰店，对电商美妆市场提供了积极推动和标杆作用。公司与施华蔻、兰芝、雅漾、雪花秀、相宜本草、芙丽芳丝、凡士林等超过60个品牌达成合作关系。</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>化妆品电商</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>sh600629</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>华建集团</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>10.0122</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>上海微电子概念|控股公司上海国投旗下子公司上海科技创业投资有限公司持有上海微电子13.275%股权，公司实控人是上海国资委。</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>上海微电子概念</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr"/>
-      <c r="D65" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>sh600207</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>安彩高科</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>10.0196</v>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>玻璃基板|公司打破日本旭硝子的技术垄断，自研生产出了3mm、4mm光热超白浮法玻璃基板，全光谱透过率达到91%以上，同时积极布局光热玻璃基板企业认证， 目前已获得国内外多家企业认可。</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>玻璃基板</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>sh601069</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>西部黄金</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>26.55</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>9.983400000000001</v>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>黄金|公司主营业务为黄金采选及冶炼，同时从事铬矿石的开采。公司主要产品包括黄金、铬矿石、铁矿石，其中黄金是公司最主要的产品和最主要收入来源。</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>黄金</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr"/>
-      <c r="D67" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>sh600621</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>华鑫股份</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>10.0304</v>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>券商|公司以证券业务为主，以部分持有型物业经营业务为辅。公司通过全资子公司华鑫证券开展证券业务</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>sh601566</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">九牧王  </t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>9.978299999999999</v>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>纺织|国内商务休闲男装品牌的领先企业、国内男裤行业的龙头。主要从事男士商务休闲品牌服饰的生产和销售,主要产品包括男裤、茄克、衬衫、T恤和西装等。</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>纺织</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr"/>
-      <c r="D69" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>sh603096</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">新经典  </t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>10.0317</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>传媒|公司是一家以内容创意为核心的传媒企业，主要业务包括图书策划与发行、数字图书、图书零售，以及影视剧策划等版权延伸业务。</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>传媒</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>sz002811</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>郑中设计</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>9.982099999999999</v>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>半导体+AI应用|1.参股深迪半导体是中国首家研发设计商用消费级和汽车级微机电系统（MEMS）陀螺仪系列惯性传感器的公司，产品主要应用于IOT，手机智能终端，智能家居，人工智能，工业和智能驾舱等领域，并为客户提供增值算法服务。
-2.子公司犀照科技打造的“IDEAFUSION兆材云库数字化平台”专为室内设计师提供一站式全流程数字化服务，目前已全面对外开放，为不同的设计单位提供SaaS化服务，促进项目高效落地。“IDEAFUSION兆材云库数字化平台”部分功能已经接入DeepSeek模型，包括物料顾问检索推理场景、黑洞文本重写场景 、知识库顾问场景。</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>半导体, AI应用</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr"/>
-      <c r="D71" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>sh603216</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>梦天家居</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>9.9954</v>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>家居+半导体|1.公司主要从事木门、墙板、柜类等定制化木质家具的设计、研发、生产和销售，为客户提供家居的整体空间解决方案。
-2.参股凌芯微通过创新整合极薄工艺、厚膜工艺、晶圆级封装三大核心制程，构建“CP测试-化镀-减薄-蚀刻-背金-晶圆级封装”一体化服务能力，覆盖功率器件中后段全流程制造需求，可高效支撑新能源汽车、工业控制、AI服务器、光伏储能等高端场景。</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>家居, 半导体</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>sz000736</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>中交发展</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>9.9156</v>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>房地产|公司是一家国有控股房地产上市公司。主营业务为房地产开发与经营。</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>房地产</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
-      <c r="D73" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>sh605168</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">三人行  </t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>10.0084</v>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>AI应用+算力租赁|1.在AI营销领域的应用方面，公司持续迭代优化营销领域多模态AI产品，成功构建 “一个”AI全链路营销智能体，逐步实现从策略生成、内容创作、智能投放到效果归因的全链路营销自动化闭环。
-2.公司设立子公司青海三人行绿能智算科技有限公司，从事算力租赁、算力解决方案服务等综合性算力服务业务。</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>AI应用, 算力租赁</t>
+          <t>汽车整车</t>
         </is>
       </c>
     </row>
@@ -3841,7 +2770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3868,7 +2797,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -3883,7 +2812,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -3898,7 +2827,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -3913,16 +2842,16 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002058</t>
+          <t>sh600812</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>紫竹高科</t>
+          <t>华北制药</t>
         </is>
       </c>
     </row>
@@ -3932,12 +2861,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz002733</t>
+          <t>sh603096</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>雄韬股份</t>
+          <t xml:space="preserve">新经典  </t>
         </is>
       </c>
     </row>
@@ -3947,12 +2876,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh600812</t>
+          <t>sz001330</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>博纳影业</t>
         </is>
       </c>
     </row>
@@ -3962,12 +2891,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sz002805</t>
+          <t>sz002696</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>丰元股份</t>
+          <t>百洋股份</t>
         </is>
       </c>
     </row>
@@ -3977,12 +2906,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sz300530</t>
+          <t>sh601595</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>领湃科技</t>
+          <t>上海电影</t>
         </is>
       </c>
     </row>
@@ -3992,12 +2921,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sz001300</t>
+          <t>sh605287</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>三柏硕</t>
+          <t>德才股份</t>
         </is>
       </c>
     </row>
@@ -4007,12 +2936,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sz001336</t>
+          <t>sh603232</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>楚环科技</t>
+          <t>格尔软件</t>
         </is>
       </c>
     </row>
@@ -4022,12 +2951,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>sh600408</t>
+          <t>sz000892</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>安泰集团</t>
+          <t>欢瑞世纪</t>
         </is>
       </c>
     </row>
@@ -4037,12 +2966,102 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>sh600400</t>
+          <t>sh605577</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>红豆股份</t>
+          <t>龙版传媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>sz002692</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>远程股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>sz002343</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>慈文传媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>sh605136</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>丽人丽妆</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>sh601811</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>sh603533</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>掌阅科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>sh601929</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>吉视传媒</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="95" customWidth="1" min="3" max="3"/>
+    <col width="114" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="363" customWidth="1" min="10" max="10"/>
+    <col width="278" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,15 +552,15 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.9486</v>
+        <v>2.4959</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>有市场消息称，10月以来，电子布涨价再次落地，涨幅为1.5元/米（7628型号），电子纱G75上涨3000元/吨，薄布（2116、1080型号）上涨2.5元/米。10月12日，多家电子布头部上市公司回应记者称，涨价消息属实。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -568,48 +568,48 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh605287</t>
+          <t>sh605058</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>德才股份</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>44.2</v>
+        <v>60.39</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.005</v>
+        <v>10</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4天3板</t>
+          <t>17天10板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧|旗下奇想无限深耕“网文IP+AI漫剧”转化，与头部网文平台合作，将玄幻、甜宠等成熟IP快速落地，已产出多部爆款。</t>
+          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.9486</v>
+        <v>2.4959</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>有市场消息称，10月以来，电子布涨价再次落地，涨幅为1.5元/米（7628型号），电子纱G75上涨3000元/吨，薄布（2116、1080型号）上涨2.5元/米。10月12日，多家电子布头部上市公司回应记者称，涨价消息属实。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -617,48 +617,44 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh605577</t>
+          <t>sz000823</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>龙版传媒</t>
+          <t>超声电子</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>17.82</v>
+        <v>22.32</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>10.0049</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧|公司首部AI漫剧《穿越1988》完成170集制作上线，全网播放量突破1.2亿，红果热度值超4000万。</t>
+          <t>PCB+业绩|超声电子公告称，预计2026年前三季度归属于上市公司股东的净利润为3.40亿元-3.60亿元，同比增长90.78%-102%。业绩变动主要系覆铜板行业维持高景气，量价齐升，公司覆铜板产品订单充足，产品售价上行，盈利能力提升；印制板业务持续优化产品结构，产能利用率提高，综合带动净利润同比大幅增长。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧</t>
+          <t>PCB, 业绩</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.9486</v>
+        <v>2.4959</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>有市场消息称，10月以来，电子布涨价再次落地，涨幅为1.5元/米（7628型号），电子纱G75上涨3000元/吨，薄布（2116、1080型号）上涨2.5元/米。10月12日，多家电子布头部上市公司回应记者称，涨价消息属实。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -666,49 +662,44 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh603533</t>
+          <t>sh605258</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>协和电子</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>27.98</v>
+        <v>40.55</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.984299999999999</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>10.0109</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>AI+短剧|1.公司已经搭建起专业的短剧生产运营体系。公司2025年度AI短剧业务收入预计不超过2025年度主营业务收入的1%。
-2.MiniMax与掌阅科技合作的对话式AI应用“阅爱聊”，能让文学作品中的角色来到现实，与用户展开一场“跨次元”对谈。</t>
+          <t>PCB|公司主要从事印制电路板的研发、生产、销售以及SMT业务，PCB产品主要应用在汽车电子和高频通讯领域。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>AI, 短剧</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.9486</v>
+        <v>2.4959</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>有市场消息称，10月以来，电子布涨价再次落地，涨幅为1.5元/米（7628型号），电子纱G75上涨3000元/吨，薄布（2116、1080型号）上涨2.5元/米。10月12日，多家电子布头部上市公司回应记者称，涨价消息属实。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -716,48 +707,45 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz001330</t>
+          <t>sh603328</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>依顿电子</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>7.67</v>
+        <v>13.34</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.043</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6天3板</t>
-        </is>
-      </c>
+        <v>9.975299999999999</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>AI+短剧|短剧业务方面，AIGC短剧《三星堆：未来启示录》由抖音联合出品，目前制作中的短剧项目如《天罗地网》《非遗手艺人》等，也已与红果短剧等头部短剧平台、中央广播电视总台及其他媒体平台开展合作，积极探索精品短剧的生产与发行新模式。</t>
+          <t>PCB|公司专注于高精度、高密度双层及多层印制电路板的研发、生产和销售业务，作为首批进入国际大厂汽车PCB核心供应链的PCB厂商，公司PCB产品供货覆盖传统汽车零部件。
+2026年8月6日公告，公司拟使用自有资金及自筹资金投资建设高端印制电路板智能制造项目，计划总投资29.79亿元。投资项目主要围绕市场高端印制电路板需求，建设高端高速高多层PCB智能制造项目。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>AI, 短剧</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2.9486</v>
+        <v>2.4959</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>有市场消息称，10月以来，电子布涨价再次落地，涨幅为1.5元/米（7628型号），电子纱G75上涨3000元/吨，薄布（2116、1080型号）上涨2.5元/米。10月12日，多家电子布头部上市公司回应记者称，涨价消息属实。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -765,48 +753,44 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz002343</t>
+          <t>sh603386</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>骏亚科技</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>6.69</v>
+        <v>17.47</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.0329</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0126</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>短剧|公司已形成了以自有IP为核心资源，以影视IP内容投资、开发、制作及发行为核心业务，积极延伸拓展电影、网络电影、网络微短剧、互动剧、小程序短剧、IP线下衍生等相关品类的业务体系。</t>
+          <t>PCB|公司主营业务为印制电路板（PCB）的研发、生产和销售，在人形机器人领域，公司成功导入国内头部客户并开始批量供货。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.9486</v>
+        <v>2.4959</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>有市场消息称，10月以来，电子布涨价再次落地，涨幅为1.5元/米（7628型号），电子纱G75上涨3000元/吨，薄布（2116、1080型号）上涨2.5元/米。10月12日，多家电子布头部上市公司回应记者称，涨价消息属实。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -814,48 +798,44 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh601929</t>
+          <t>sz301041</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>吉视传媒</t>
+          <t>金百泽</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2.75</v>
+        <v>40.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>短剧|公司与吉林广播电视台、长影集团有限责任公司、深圳市来画科技文化有限公司联合签署战略合作协议，发挥四方优势，以联合出品、联合制作、委托制作、国际版制作等形式，共同策划推出微短剧、影视剧、专题片、虚实影像互动剧、社交游戏等精品视频内容与应用服务等精品内容。</t>
+          <t>PCB|公司的PCB业务聚焦电子产品研发阶段的PCB样板和中小批量板需求，具备样板和中小批量的柔性制造和快速交付能力，自主开发的EDA辅助工具KBEDA-SKILL，适用于主流PCB LAYOUT软件。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.9486</v>
+        <v>2.4959</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>有市场消息称，10月以来，电子布涨价再次落地，涨幅为1.5元/米（7628型号），电子纱G75上涨3000元/吨，薄布（2116、1080型号）上涨2.5元/米。10月12日，多家电子布头部上市公司回应记者称，涨价消息属实。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -863,48 +843,44 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh601595</t>
+          <t>sz002579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>上海电影</t>
+          <t>中京电子</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>27.21</v>
+        <v>16.43</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.9838</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.9732</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>AI+短剧|上影元已与多家大模型公司建立深度合作，联动公司参与发起设立的上影新视野基金，已布局“AI+社交”“AI+游戏”“AI+短剧”等泛娱乐产品。</t>
+          <t>PCB|公司主营业务为印制电路板(PCB)的研发、生产、销售与服务，已获得AI PC的小批量订单。公司PCB产品可广泛应用于航天军工。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>AI, 短剧</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.9486</v>
+        <v>2.4959</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>有市场消息称，10月以来，电子布涨价再次落地，涨幅为1.5元/米（7628型号），电子纱G75上涨3000元/吨，薄布（2116、1080型号）上涨2.5元/米。10月12日，多家电子布头部上市公司回应记者称，涨价消息属实。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -912,48 +888,45 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz000892</t>
+          <t>sh603956</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>欢瑞世纪</t>
+          <t xml:space="preserve">威派格  </t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>5.34</v>
+        <v>8.15</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.1031</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.986499999999999</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>AI+短剧|公司与上海阶跃星辰智能科技有限公司已达成战略合作，双方共建“麟跃”AI联合实验室，合作方向为短剧Agent产品，双方将合力打造短剧Agent产品，深化探索AI技术在相关影视应用、短剧管理与投流产品等方向的应用。</t>
+          <t>AI应用+PCB|1.公司研发的“河图 AI” 平台产品已接入包括DeepSeek、智谱GLM等多款大模型，支持多用户交互及图文、视频等多模态数据处理，并广泛应用于智慧水厂、管网调度、智慧营销等多场景，以提升供水全流程的智能检测、调度优化、趋势预测和故障诊断能力，助力水务企业降本增效、优化资源配置。
+2.公司取得安徽提曼科技有限公司51.02%股权，安徽提曼主要产品系PCB微型钻针等。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>AI, 短剧</t>
+          <t>AI应用, PCB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.9486</v>
+        <v>2.4959</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>有市场消息称，10月以来，电子布涨价再次落地，涨幅为1.5元/米（7628型号），电子纱G75上涨3000元/吨，薄布（2116、1080型号）上涨2.5元/米。10月12日，多家电子布头部上市公司回应记者称，涨价消息属实。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -961,1801 +934,2784 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz301052</t>
+          <t>sh688655</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>果麦文化</t>
+          <t xml:space="preserve">迅捷兴  </t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30.47</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>20.0079</v>
+        <v>20.0034</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>AI+短剧|公司已规划拓展影视剧和动漫剧业务并发布AI漫画平台“爱漫阁”。</t>
+          <t>PCB|公司主营业务为印制电路板（PCB）的研发、生产与销售，公司在光模块领域已积累了相关产品经验和客户，目前已可批量接单。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>AI, 短剧</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>冰雪产业</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-0.6369</v>
+        <v>4.413799999999999</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Anthropic发布最新AI模型Claude Haiku 5.5，用于执行那些对成本敏感的任务，新模型定价较Haiku 4.5大幅降低。大模型推理成本加速下降，AI应用端渗透有望提速。</t>
+          <t>“冰雪之冠 龙江有约”黑龙江省冰雪旅游发展促进会2026—2027冰雪季推介会暨启动仪式在广州成功举行。据介绍，第二十八届哈尔滨冰雪大世界园区占地面积将扩至125万平方米，创造历届规模新高。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh605136</t>
+          <t>sz000530</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>丽人丽妆</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>10.38</v>
+        <v>5.73</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9.957599999999999</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.980799999999999</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>电商+AI应用|1.公司是国内领先的化妆品网络零售服务商，主要从事电商零售业务和品牌营销运营服务。公司运营的“相宜本草官方旗舰店”作为第一家入驻天猫平台的授权美妆品牌官方旗舰店，对电商美妆市场提供了积极推动和标杆作用。公司与施华蔻、兰芝、雅漾、雪花秀、相宜本草、芙丽芳丝、凡士林等超过60个品牌达成合作关系。
-2.公司积极探索包括生成型AI产品在内的人工智能技术的应用，以提高工作效率和提升用户体验。在基础构建层面，公司已在着手进行部分人工智能软件的API接入工作，为后续相关智能运用推广做前期准备；在实际运营层面，公司考虑使用人工智能软件在优化商品描述、店铺商品图片设计、短视频制作、虚拟主播、客服服务沟通、客户评价分析等方面实现智能化，提高业务效率和质量；在营销层面，公司也计划使用人工智能软件进行广告图像设计和生成。</t>
+          <t>液冷+冰雪产业|1.公司拥有数据中心相应的冷热解决方案。
+2.子公司冰山工程近年来承接了多项代表性工程，包括广州融创茂室内滑雪场项目、上海之星室内综合性冰雪场馆、陕西国际体育之窗等多个商业冰雪场馆项目。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>电商, AI应用</t>
+          <t>液冷, 冰雪产业</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>冰雪产业</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-0.6369</v>
+        <v>4.413799999999999</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Anthropic发布最新AI模型Claude Haiku 5.5，用于执行那些对成本敏感的任务，新模型定价较Haiku 4.5大幅降低。大模型推理成本加速下降，AI应用端渗透有望提速。</t>
+          <t>“冰雪之冠 龙江有约”黑龙江省冰雪旅游发展促进会2026—2027冰雪季推介会暨启动仪式在广州成功举行。据介绍，第二十八届哈尔滨冰雪大世界园区占地面积将扩至125万平方米，创造历届规模新高。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz002990</t>
+          <t>sz301010</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>盛视科技</t>
+          <t>晶雪节能</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>55.95</v>
+        <v>23.7</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.0079</v>
+        <v>20</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>AI应用+半导体|1.公司持续加大对人工智能、大数据、物联网等新一代信息技术的研发投入，旨在为客户提供符合未来发展的智能产品和“AI+行业”解决方案。公司在智慧口岸领域深耕二十余年，已成长为国内领先的智慧口岸查验系统整体解决方案提供商。
-2.参股的苏州亿铸智能科技有限公司是一家将新型存储器ReRAM及存算一体创新计算架构相结合，面向数据中心、云计算、中心侧服务器、自动驾驶及边缘计算等场景的大算力AI芯片公司。</t>
+          <t>冰雪产业|公司主营产品是冷库和工业建筑围护系统节能隔热保温材料。相关案例有哈尔滨万达茂滑雪场项目、宁波冰雪世界项目、苏州乐园森林世界、梧州启迪鸿星合景冰雪世界滑雪馆项目等。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>AI应用, 半导体</t>
+          <t>冰雪产业</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>冰雪产业</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.6369</v>
+        <v>4.413799999999999</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Anthropic发布最新AI模型Claude Haiku 5.5，用于执行那些对成本敏感的任务，新模型定价较Haiku 4.5大幅降低。大模型推理成本加速下降，AI应用端渗透有望提速。</t>
+          <t>“冰雪之冠 龙江有约”黑龙江省冰雪旅游发展促进会2026—2027冰雪季推介会暨启动仪式在广州成功举行。据介绍，第二十八届哈尔滨冰雪大世界园区占地面积将扩至125万平方米，创造历届规模新高。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz002908</t>
+          <t>sh600593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>德生科技</t>
+          <t>大连圣亚</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>8.02</v>
+        <v>49.83</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.0137</v>
+        <v>10</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>AI中医智能体|公司与初芯堂合作共创的AI中医智能体，接入了相关大模型，能够实现智能辅助诊疗、虚拟数字人自动化解读检测报告等；目前已应用社区、企业健康小屋、医馆、药店等场景。</t>
+          <t>冰雪产业|公司正在经营的哈尔滨景区包括哈尔滨极地公园海洋馆、哈尔滨极地公园极地馆、哈尔滨极地公园恐龙馆、哈尔滨极地公园北极熊体验馆、哈尔滨极地公园淘学企鹅馆。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>AI中医智能体</t>
+          <t>冰雪产业</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>冰雪产业</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.6369</v>
+        <v>4.413799999999999</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Anthropic发布最新AI模型Claude Haiku 5.5，用于执行那些对成本敏感的任务，新模型定价较Haiku 4.5大幅降低。大模型推理成本加速下降，AI应用端渗透有望提速。</t>
+          <t>“冰雪之冠 龙江有约”黑龙江省冰雪旅游发展促进会2026—2027冰雪季推介会暨启动仪式在广州成功举行。据介绍，第二十八届哈尔滨冰雪大世界园区占地面积将扩至125万平方米，创造历届规模新高。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz002264</t>
+          <t>sh600853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>新 华 都</t>
+          <t>龙建股份</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>9.9398</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>零售+AI应用|1.公司主要业务为互联网营销和超市百货业务，旗下久爱致和服务于多家国际、国内知名企业，也是天猫及京东等多家电子商务平台的合作伙伴。
-2.公司结合AI大模型与电商场景，已开发并上线试运行智能化平台“久爱AI”，一期版本开放商品评论分析、商品信息采集、违禁词风险评估、摘要抽取、文案大纲助手、简历筛选6项AI工具，为优化营销策略、产品结构和日常办公提供技术支持。
-3.阿里巴巴成都及杭州瀚云均为公司股东。</t>
+          <t>冰雪产业|子公司漠河市峰悦文化旅游发展有限公司在漠河观音山景区引入冰上龙舟、雪地摩托、冰上自行车、冰上爬犁、雪地滑梯、泼水成冰等系列冰雪活动。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>零售, AI应用</t>
+          <t>冰雪产业</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>冰雪产业</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-0.6581</v>
+        <v>4.413799999999999</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>据报道，“十五五”时期我国将投入超过5万亿元建设新型电网，规模远超“十四五”时期，到2030年将初步建成新型电网，可高效支撑28亿千瓦以上新能源消纳。</t>
+          <t>“冰雪之冠 龙江有约”黑龙江省冰雪旅游发展促进会2026—2027冰雪季推介会暨启动仪式在广州成功举行。据介绍，第二十八届哈尔滨冰雪大世界园区占地面积将扩至125万平方米，创造历届规模新高。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz002692</t>
+          <t>sz002639</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>远程股份</t>
+          <t>雪人集团</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>5.24</v>
+        <v>14.59</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.084</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0302</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>电缆+IDC电源|公司的电力电缆、控制电缆、防火电缆等产品可应用于数据中心领域。</t>
+          <t>核电+冰雪产业|1.公司已为中科院合肥物质研究所、理化所等多所研究院提供氦气螺杆压缩机，分别应用于全超导托克马克核聚变实验装置、航天试验等大科学工程应用领域。
+2.公司制冰、制冷设备已应用在冰雪运动赛事项目场馆内。近年来已参与多项冰雪项目建设，包括国家雪车雪橇中心、崇礼长城岭滑雪场等。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>电缆, IDC电源</t>
+          <t>核电, 冰雪产业</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>冰雪产业</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.6581</v>
+        <v>4.413799999999999</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>据报道，“十五五”时期我国将投入超过5万亿元建设新型电网，规模远超“十四五”时期，到2030年将初步建成新型电网，可高效支撑28亿千瓦以上新能源消纳。</t>
+          <t>“冰雪之冠 龙江有约”黑龙江省冰雪旅游发展促进会2026—2027冰雪季推介会暨启动仪式在广州成功举行。据介绍，第二十八届哈尔滨冰雪大世界园区占地面积将扩至125万平方米，创造历届规模新高。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh600192</t>
+          <t>sz000558</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>长城电工</t>
+          <t>天府文旅</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>7.93</v>
+        <v>3.84</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>9.9861</v>
+        <v>10.0287</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>电网设备|公司主要从事高中低压开关成套设备、高中低压电器元件、母线槽、电气传动自动化装置、新能源装备等电工电器类产品的研发、生产与销售，先后为三峡工程、载人航天、奥运鸟巢、青藏铁路等多项国家重点工程提供优质产品。</t>
+          <t>冰雪产业|公司旗下西岭滑雪场是我国南方地区规模最大、设备最齐全的室外天然滑雪场之一，拥有优质的冰雪山地旅游运动资源。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>冰雪产业</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>冰雪产业</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.6581</v>
+        <v>4.413799999999999</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>据报道，“十五五”时期我国将投入超过5万亿元建设新型电网，规模远超“十四五”时期，到2030年将初步建成新型电网，可高效支撑28亿千瓦以上新能源消纳。</t>
+          <t>“冰雪之冠 龙江有约”黑龙江省冰雪旅游发展促进会2026—2027冰雪季推介会暨启动仪式在广州成功举行。据介绍，第二十八届哈尔滨冰雪大世界园区占地面积将扩至125万平方米，创造历届规模新高。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh600560</t>
+          <t>sh603099</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>金自天正</t>
+          <t xml:space="preserve">长白山  </t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>12.53</v>
+        <v>45.85</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.0088</v>
+        <v>10.0048</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>机器人+智能电网|1.公司部分无人化应用工程中使用工业机器人替代人工进行取样、存样、打码、搬运、检测等工作。
-2.公司主要产品电气传动装置、电力半导体元器件等均为电力电子相关产品，部分产品可用于智能电网行业。</t>
+          <t>冰雪产业|公司拥有长白山三个景区道路运输独家经营权，冰雪是长白山旅游发展的最大潜力资源。公司依托“粉雪、林海、雾凇、温泉”等资源优势，建成开放“雪绒花”运动户外音乐餐厅，成为长白山度假生活新晋打卡地。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>机器人, 智能电网</t>
+          <t>冰雪产业</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>智能电网</t>
+          <t>染料涂料</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-0.6581</v>
+        <v>3.4578</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>据报道，“十五五”时期我国将投入超过5万亿元建设新型电网，规模远超“十四五”时期，到2030年将初步建成新型电网，可高效支撑28亿千瓦以上新能源消纳。</t>
+          <t>绍兴市三丰化工有限公司发布《调价函》，宣布自2026年10月10日（含）起，对旗下两款核心染料中间体产品进行价格上调。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz002441</t>
+          <t>sh603968</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>众业达</t>
+          <t>醋化股份</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>9.210000000000001</v>
+        <v>14.36</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.0358</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+        <v>10.0383</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>电网设备|公司的中低压电气产品主要应用于输配电和配网等环节，服务于电源、电网以及各类具有配电需求的最终应用。</t>
+          <t>染料|公司的双乙甲酯产品涉及分散染料领域。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>染料</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>染料涂料</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-1.6025</v>
+        <v>3.4578</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>中共中央、国务院近日印发《关于发展新质生产力的意见》。意见提出，全面实施“人工智能+”行动。加快推进智能网联新能源汽车、人工智能手机和电脑、人形机器人等新一代智能终端场景应用。</t>
+          <t>绍兴市三丰化工有限公司发布《调价函》，宣布自2026年10月10日（含）起，对旗下两款核心染料中间体产品进行价格上调。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz002242</t>
+          <t>sh603188</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>亚邦股份</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>16.64</v>
+        <v>5.46</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.9802</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6天6板</t>
-        </is>
-      </c>
+        <v>10.0806</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>AI机器人|公司持有深思考人工智能机器人科技（北京）有限公司7.92%的股份，旗下产品包括AI机器人。</t>
+          <t>染料|公司主要从事染料及染料中间体的销售与服务，是国内蒽醌结构染料生产专家工厂。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>AI机器人</t>
+          <t>染料</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>染料涂料</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-1.6025</v>
+        <v>3.4578</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>中共中央、国务院近日印发《关于发展新质生产力的意见》。意见提出，全面实施“人工智能+”行动。加快推进智能网联新能源汽车、人工智能手机和电脑、人形机器人等新一代智能终端场景应用。</t>
+          <t>绍兴市三丰化工有限公司发布《调价函》，宣布自2026年10月10日（含）起，对旗下两款核心染料中间体产品进行价格上调。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh603528</t>
+          <t>sz300107</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>建新股份</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>7.05</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.984400000000001</v>
+        <v>20.0278</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>AI应用+机器人|1.公司已开展多项人工智能驾考新技术研究，包括基于机器视觉的驾驶人注意力分配识别、基于机器视觉的道路环境目标识别、基于激光雷达的目标探测技术等。
-2.公司通过珠海星芯投资基金参与了众擎机器人科技有限公司Pre-A++轮融资，并持有其1.57%的股份。</t>
+          <t>染料|公司主营苯系中间体产品，产品涵盖染料中间体。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>AI应用, 机器人</t>
+          <t>染料</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>染料涂料</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-1.6025</v>
+        <v>3.4578</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>中共中央、国务院近日印发《关于发展新质生产力的意见》。意见提出，全面实施“人工智能+”行动。加快推进智能网联新能源汽车、人工智能手机和电脑、人形机器人等新一代智能终端场景应用。</t>
+          <t>绍兴市三丰化工有限公司发布《调价函》，宣布自2026年10月10日（含）起，对旗下两款核心染料中间体产品进行价格上调。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh603992</t>
+          <t>sz002748</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>松霖科技</t>
+          <t>世龙实业</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>20.94</v>
+        <v>13.1</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>9.979000000000001</v>
+        <v>9.9916</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>机器人|旗下松霖机器人与达闼机器人签署了战略合作框架协议，共同探索人形机器人垂直场景应用、核心部件创新升级、机器人出海及其他创新领域的产业机会。</t>
+          <t>染料|公司是国内AC发泡剂和氯化亚砜的主要生产商之一，具备氯化亚砜5万吨/年的产能，氯化亚砜产品主要应用于染料、医药、农药等行业。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>染料</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>染料涂料</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-1.6025</v>
+        <v>3.4578</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>中共中央、国务院近日印发《关于发展新质生产力的意见》。意见提出，全面实施“人工智能+”行动。加快推进智能网联新能源汽车、人工智能手机和电脑、人形机器人等新一代智能终端场景应用。</t>
+          <t>绍兴市三丰化工有限公司发布《调价函》，宣布自2026年10月10日（含）起，对旗下两款核心染料中间体产品进行价格上调。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh603500</t>
+          <t>sh603980</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>祥和实业</t>
+          <t>吉华集团</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>11.04</v>
+        <v>10.67</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.9602</v>
+        <v>10</v>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>超级电容+机器人|1.公司紧跟铝电解电容器技术迭代，先后开发成功V-CHIP电容底座、车用耐振动底座以及应用于超级电容、锂电池、耐550V以上特高压、耐150℃电容器用橡胶密封塞、轴向电容器盖板等产品。
-2.公司于2024年4月30日成立子公司祥和智能，研发、制造和销售工业机器人、智能机器人及人工智能应用软件开发等系祥和智能的经营范围。</t>
+          <t>染料+创新药|1.公司主要从事染料、染料中间体及其他化工产品的研发、生产和销售。
+2.旗下江苏康倍得药业股份有限公司是一家致力于仿制及创新透皮高端制剂、国内领先的透皮给药研发型制药企业。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>超级电容, 机器人</t>
+          <t>染料, 创新药</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-2.0276</v>
+        <v>2.0818</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+          <t>中信证券认为，光模块及上游器件需求延续高景气，行业头部公司年产能规划积极；技术迭代升级带来的新需求和价值量提升成为重要市场增量，全产业链仍处于快速成长期。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh600812</t>
+          <t>sz002184</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>海得控制</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>6.63</v>
+        <v>11.07</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9.950199999999999</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.0398</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>链霉素|公司青霉素系列、头孢系列产品品种齐全，覆盖了原料药到制剂的大部分品种，形成了从发酵原料到半合成原料药再到制剂的完整产品链。是国内硫酸链霉素原料药及注射剂的核心生产企业。</t>
+          <t>光通信+机器人|1.公司数字化业务的产品型谱中包含工业以太网交换机与光模块，主要应用于工业企业的数据中心、企业私有云构建业务。
+2.公司工业机器人的领域的应用主要在港口、冶金、煤炭、城市管廊等行业的无人化系统中，通过识别（信号与数据采集）、计算、反馈、纠偏、执行等系统功能实现设备与系统的自主控制与执行，解决工作环境恶劣，劳动强度较大等现象现实问题。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>链霉素</t>
+          <t>光通信, 机器人</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-2.0276</v>
+        <v>2.0818</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+          <t>中信证券认为，光模块及上游器件需求延续高景气，行业头部公司年产能规划积极；技术迭代升级带来的新需求和价值量提升成为重要市场增量，全产业链仍处于快速成长期。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh600851</t>
+          <t>sz001229</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>海欣股份</t>
+          <t>魅视科技</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>8.6</v>
+        <v>41.76</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.974399999999999</v>
+        <v>10.0105</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>创新药|子公司上海海欣生物技术有限公司APDC项目主要用于结直肠癌治疗，目前海欣生物就APDC三期项目正多方面探索解决方案。</t>
+          <t>AI应用+磷化铟|1.目前公司已经在视听产品中应用人工智能相关功能，如融入到业务流程的坐席人脸登录、现场恢复、坐席引导、语音指挥、隔空指挥、视频分析、数据AI识别采集等。
+2.2026年8月5日公告，公司已成立全资子公司珠海明曜新材料科技有限公司作为实施主体，注册资本1000万元，拟开展磷化铟半导体材料产业化项目的前期准备工作。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>AI应用, 磷化铟</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-2.0276</v>
+        <v>2.0818</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>俄罗斯联邦消费者权益保护和公益监督局6日在其官网发布通告称，供职于该国伊尔库茨克西伯利亚与远东防鼠疫研究所的一名患病工作人员病因诊断为“不明原因肺炎”。</t>
+          <t>中信证券认为，光模块及上游器件需求延续高景气，行业头部公司年产能规划积极；技术迭代升级带来的新需求和价值量提升成为重要市场增量，全产业链仍处于快速成长期。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz300006</t>
+          <t>sz002980</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>莱美药业</t>
+          <t>华盛昌</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>6.56</v>
+        <v>116.05</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>19.9269</v>
+        <v>10</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>创新药|2025年4月30日公司在互动平台表示，子公司四川瀛瑞的纳米炭铁混悬注射液（CNSI-Fe）临床试验进展顺利；参股公司康德赛用于治疗晚期卵巢癌的个体化肿瘤疫苗项目（CUD002）、用于治疗中晚期肝硬化的巨噬细胞项目（CUD005）临床一期工作均在稳步推进中。</t>
+          <t>光芯片测试|2026年2月27日公告，公司拟以现金方式收购深圳市伽蓝特科技有限公司100%股权，整体估值暂定为4.6亿元。同时，公司控股股东袁剑敏拟向伽蓝特创始股东余新文协议转让公司5%股份，协议转让事项以目标公司收购事项完成为实施的前提条件。伽蓝特专注于仪器仪表测试测量行业中的光通信模块和光芯片测试领域，本次股权收购为公司产业布局横向延伸。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>光芯片测试</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2.0432</v>
+        <v>2.0818</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>中信证券研报表示，AI剧产业链价值有望进一步向具备高商业化效率、优质IP与精品制作能力、高质量语料资源，以及与红果深度合作的公司集中。</t>
+          <t>中信证券认为，光模块及上游器件需求延续高景气，行业头部公司年产能规划积极；技术迭代升级带来的新需求和价值量提升成为重要市场增量，全产业链仍处于快速成长期。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sh603096</t>
+          <t>sh603042</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">新经典  </t>
+          <t>华脉科技</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>19.06</v>
+        <v>16.12</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>9.982699999999999</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0341</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>传媒|公司是一家以内容创意为核心的传媒企业，主要业务包括图书策划与发行、数字图书、图书零售，以及影视剧策划等版权延伸业务。</t>
+          <t>光纤|公司是一家信息通信网络基础设施解决方案提供商，主要产品包括光纤、光缆、光器件及光配线设施全场景有线传输链路解决方案及系列产品。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>传媒</t>
+          <t>光纤</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2.0432</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>中信证券研报表示，AI剧产业链价值有望进一步向具备高商业化效率、优质IP与精品制作能力、高质量语料资源，以及与红果深度合作的公司集中。</t>
+          <t>国信证券表示，Agent有望成为下一阶段AI应用商业化和推理算力需求增长的重要驱动力。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh603230</t>
+          <t>sz002949</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>华阳国际</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>14.63</v>
+        <v>14.32</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10</v>
+        <v>9.9846</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>出版传媒|公司的最终控制人为内蒙古自治区人民政府。公司主营业务是出版物的批发、零售；文体用品零售；音像制品发行</t>
+          <t>基建+AI应用|1.公司一直从事建筑设计和研发及其延伸业务，拥有建筑行业（建筑工程）甲级资质、工程造价咨询甲级资质、建筑工程施工总承包一级和市政公用工程施工总承包二级资质。
+2.公司已认证为百度飞桨技术生态伙伴，通过技术赋能加速AI应用场景落地，推动人工智能技术与建筑设计的深度结合，加速智慧建筑发展。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>出版传媒</t>
+          <t>基建, AI应用</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-0.6907</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>有市场消息称，欧盟委员会决定对原产于中国的风力发电机塔筒及关键结构件发起反倾销与反补贴立案调查。对此，有上市风电企业表示此为假消息。</t>
+          <t>国信证券表示，Agent有望成为下一阶段AI应用商业化和推理算力需求增长的重要驱动力。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz002531</t>
+          <t>sh603466</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>天顺风能</t>
+          <t xml:space="preserve">风语筑  </t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>8.27</v>
+        <v>13.57</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>9.9734</v>
+        <v>9.967600000000001</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>风电|公司为国内领先的风塔专业生产商，主营产品为1.5MW及以上功率风机的风塔。</t>
+          <t>机器人+AI应用|1.公司设立“具身智能研究院”，与松延机器人签署战略合作，并积极与头部AI硬件厂商对接，面向文化场馆、文旅街区等新文旅场景提供“场景策划—内容生成—算法部署—硬件集成—持续运营”一体化具身智能解决方案。
+2.公司将致力于加速虚拟现实（VR）和混合现实（MR）技术与人工智能生成内容（AIGC）技术的结合，推动交互式数字内容、VR/MR与AIGC技术在文化、博物馆和旅游等不同领域的应用。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>机器人, AI应用</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-0.6907</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>有市场消息称，欧盟委员会决定对原产于中国的风力发电机塔筒及关键结构件发起反倾销与反补贴立案调查。对此，有上市风电企业表示此为假消息。</t>
+          <t>国信证券表示，Agent有望成为下一阶段AI应用商业化和推理算力需求增长的重要驱动力。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz002576</t>
+          <t>sz002862</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>通达动力</t>
+          <t>实丰文化</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>16.07</v>
+        <v>15.95</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>9.9932</v>
+        <v>10</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>机器人+风电|1.公司生产的伺服电机铁芯可以应用于机器人领域。
-2.公司生产的定转子铁芯产品品种齐全，能够应用于不同种类和型号的电机、包括国标类普通电机，也包括高效电机、风力发电机、牵引电机、新能源汽车驱动电机等对定转子冲片和铁芯质量要求较高的电机产品。</t>
+          <t>AI玩具|公司与灵优智学合作开发的新一代AI玩具“AI魔法星”基于AIGC技术，运用豆包先进的大模型底层，进行二次训练出符合儿童对话习惯且脱离敏感话题的后台的模式。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>机器人, 风电</t>
+          <t>AI玩具</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-0.7702</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>在人工智能公司Anthropic发生多起未经授权使用美国政府系统的安全事件后，美国政府宣布实施新的强制性AI安全事件报告要求。</t>
+          <t>国信证券表示，Agent有望成为下一阶段AI应用商业化和推理算力需求增长的重要驱动力。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh603232</t>
+          <t>sz002587</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>格尔软件</t>
+          <t>奥拓电子</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>18.68</v>
+        <v>5.76</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.0118</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.9237</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>AI+网络安全|1.公司的AI赋能旨在深化AI与密码学、安全、产品三大核心业务的融合,明确推动AI应用从工具引入向范式变革演进,实现“AI赋能效率、创新驱动升级”双重目标。
-2.公司自成立以来一直专注于信息安全行业PKI领域，主要从事以公钥基础设施PKI为核心的商用密码软件产品的研发、生产和销售及服务业务，为用户提供基于PKI的信息安全系列产品、安全服务和信息安全整体解决方案。</t>
+          <t>AI+机器人|2023年2月1日公司在互动平台表示，公司智能服务型机器人已通过中国机器人产品认证，并申请了多项专利，已在多家银行成功应用。公司全资子公司南京奥拓是华为云AI认证合作伙伴，将不断的推动公司智能视讯业务与人工智能技术的结合。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>AI, 网络安全</t>
+          <t>AI, 机器人</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>网络安全</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-0.7702</v>
+        <v>0.6409</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>在人工智能公司Anthropic发生多起未经授权使用美国政府系统的安全事件后，美国政府宣布实施新的强制性AI安全事件报告要求。</t>
+          <t>韩国半导体产业协会宣布，将于14日至16日在首尔江南COEX会展中心举办为期三天的2026年韩国半导体展览会（SEDEX 2026）。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh688004</t>
+          <t>sz002811</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>博汇科技</t>
+          <t>郑中设计</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>37.25</v>
+        <v>20.27</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>20.0064</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
+        <v>9.983699999999999</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>网络安全+AI应用|1.公司对各类媒体内容进行多维度分析，精准识别敏感、违规内容，实现对广播电视、IPTV/OTT、互联网站、微信、微博、各类短视频、自媒体等传播媒介播放的视听内容进行监管。
-2.公司在人工智能、大数据、云计算领域已布局多年。通过综合运用人工智能深度学习算法，通过海量专项素材的机器学习，不断优化人脸识别、场景识别、语音识别、文字识别等智能化识别引擎，对各类媒体内容进行多维度分析，精准识别敏感、违规内容。</t>
+          <t>半导体+AI应用|1.参股深迪半导体是中国首家研发设计商用消费级和汽车级微机电系统（MEMS）陀螺仪系列惯性传感器的公司，产品主要应用于IOT，手机智能终端，智能家居，人工智能，工业和智能驾舱等领域，并为客户提供增值算法服务。
+2.子公司犀照科技打造的“IDEAFUSION兆材云库数字化平台”专为室内设计师提供一站式全流程数字化服务，目前已全面对外开放，为不同的设计单位提供SaaS化服务，促进项目高效落地。“IDEAFUSION兆材云库数字化平台”部分功能已经接入DeepSeek模型，包括物料顾问检索推理场景、黑洞文本重写场景 、知识库顾问场景。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>网络安全, AI应用</t>
+          <t>半导体, AI应用</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-1.2496</v>
+        <v>0.6409</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>中欧贸易投资磋商机制第二次例会日前召开，欧方澄清，欧盟对逆变器项目的融资指导文件不针对特定国家，双方将就该问题进一步磋商。</t>
+          <t>韩国半导体产业协会宣布，将于14日至16日在首尔江南COEX会展中心举办为期三天的2026年韩国半导体展览会（SEDEX 2026）。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh688517</t>
+          <t>sz002549</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>金冠电气</t>
+          <t>凯美特气</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>21.18</v>
+        <v>14.25</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>20</v>
+        <v>10.0386</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>电网设备+储能项目|1.公司长期服务于以特高压为骨干网架、各级电网协调发展的坚强智能电网建设，主要为用户提供交、直流金属氧化物避雷器及智能配电网系列产品。
-2.金冠电气公告称，公司全资子公司金冠光储充与SPIRO签订EPC总承包框架协议，合同总金额不超过2.96亿美元(含税)，标的为非洲区域内50个并网或离网光储充一体化电站项目。</t>
+          <t>电子特气|控股子公司凯美特电子特种稀有气体有限公司光刻气产品获得ASML子公司Cymer公司合格供应商认证。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>电网设备, 储能项目</t>
+          <t>电子特气</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>储能</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-1.2496</v>
+        <v>0.6409</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>中欧贸易投资磋商机制第二次例会日前召开，欧方澄清，欧盟对逆变器项目的融资指导文件不针对特定国家，双方将就该问题进一步磋商。</t>
+          <t>韩国半导体产业协会宣布，将于14日至16日在首尔江南COEX会展中心举办为期三天的2026年韩国半导体展览会（SEDEX 2026）。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz301658</t>
+          <t>sh603353</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>首航新能</t>
+          <t>和顺石油</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>27.12</v>
+        <v>37.9</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>20</v>
+        <v>10.0145</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>储能电池|公司的储能电池主要为磷酸铁锂电池，能够适配多品牌光伏储能逆变器，主要应用于户用及小型工商业储能。公司光伏储能逆变器功率范围已涵盖3kW~20kW，适用于户用、小型工商业并离网储能多种场景。</t>
+          <t>油气+半导体|1.公司是湖南省第一家获国家商务部批准取得成品油批发资质的民营石油企业，主营成品油批发零售，业务涵盖成品油采购、仓储、物流、批发、零售环节，在成品油流通领域形成完整产业链。
+2.2025年11月16日晚公告，公司拟以现金收购及增资方式取得上海奎芯集成电路设计有限公司不低于34%股权并通过表决权委托合计控制其51%表决权，交易完成后奎芯科技将纳入合并报表，布局高速接口IP及Chiplet解决方案。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>储能电池</t>
+          <t>油气, 半导体</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-2.2713</v>
+        <v>0.6409</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>受3D打印需求向好支撑，近期聚乳酸产业链产品价格维持高位。</t>
+          <t>韩国半导体产业协会宣布，将于14日至16日在首尔江南COEX会展中心举办为期三天的2026年韩国半导体展览会（SEDEX 2026）。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz300829</t>
+          <t>sz002430</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>金丹科技</t>
+          <t>杭氧股份</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>28.02</v>
+        <v>27.52</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>20</v>
+        <v>9.991999999999999</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>乳酸|公司目前主要产品为乳酸、乳酸钠和乳酸钙。乳酸系列产品广泛应用于食品、饲料、生物降解材料、工业、医药等领域。</t>
+          <t>电子特气|公司主要业务由设备工程业务及气体服务业务组成，生产和销售成套空气分离设备及部机、低温石化设备并提供EPC服务，生产和经营各类气体产品，并已拓展氢的制取、提纯、储运及加注、CCUS等新能源相关业务。公司生产的气体产品主要包括氧、氮、氩、氖、氦、氪、氙、二氧化碳、氢气、医疗气、电子大宗气、电子特气、高纯气、混合气等。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>乳酸</t>
+          <t>电子特气</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-2.2713</v>
+        <v>0.5858</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>受3D打印需求向好支撑，近期聚乳酸产业链产品价格维持高位。</t>
+          <t>据河南、山东、广东、安徽等地经销商、批发商和终端零售商获悉，渠道库存总体仍在去化，部分受访酒商库存同比下降约10%-20%，名酒大单品周转相对较快，部分终端库存已控制在1-2个月。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh603968</t>
+          <t>sz002696</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>醋化股份</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>13.05</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.0337</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
+        <v>10.0621</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>染料|公司的双乙甲酯产品涉及分散染料领域。</t>
+          <t>水产+鱼粉|1.公司位于广西，水产品加工业务板块将着重研发以罗非鱼、生鱼、金鲳鱼、海鲈鱼为原料的内销产品。
+2.公司下辖鱼粉厂的合计年产量约为1-2万吨，鱼油年产量约为2000-4000吨。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>染料</t>
+          <t>水产, 鱼粉</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-2.302</v>
+        <v>0.5858</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>行业媒体报道，韩国正极材料企业EcoPro BM宣布，已经和三星SDI签署谅解备忘录（MOU），双方将围绕全固态电池材料开展合作，以推进硫化物系全固态电池于2027年实现商业化。</t>
+          <t>据河南、山东、广东、安徽等地经销商、批发商和终端零售商获悉，渠道库存总体仍在去化，部分受访酒商库存同比下降约10%-20%，名酒大单品周转相对较快，部分终端库存已控制在1-2个月。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh603032</t>
+          <t>sz000995</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>德新科技</t>
+          <t>皇台酒业</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>20.42</v>
+        <v>12.25</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.0216</v>
+        <v>9.9641</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>固态电池|公司从2021年起向清陶供应模具产品，用于固态电池的生产。</t>
+          <t>葡萄酒|西北风格的名优白酒。葡萄酒产品依靠河西走廊得天独厚的地理优势，酒体品质达到了国际标准。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>葡萄酒</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-2.302</v>
+        <v>0.5858</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>行业媒体报道，韩国正极材料企业EcoPro BM宣布，已经和三星SDI签署谅解备忘录（MOU），双方将围绕全固态电池材料开展合作，以推进硫化物系全固态电池于2027年实现商业化。</t>
+          <t>据河南、山东、广东、安徽等地经销商、批发商和终端零售商获悉，渠道库存总体仍在去化，部分受访酒商库存同比下降约10%-20%，名酒大单品周转相对较快，部分终端库存已控制在1-2个月。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz002591</t>
+          <t>sh600199</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>恒大高新</t>
+          <t>金种子酒</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>7.16</v>
+        <v>7.6</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>9.9846</v>
+        <v>9.9855</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>服务器+固态电池|1.公司构建"通信服务-算力支撑"协同生态，旗下宝乐互动在AI算力服务器业务已拥有完整产线。
-2.公司申请的在国家有关发明专利机构审查的“固态电池专利”写到：该发明专利技术是一种复合固态锂离子电池及其制备方法，能够抑制高温下的复合固态电解质膜和负极片的膨胀，有利于电极界面的平整接触，特别是对负硅碳材料效果更明显，能改善电池循环寿命，提升电池安全性能。</t>
+          <t>白酒|公司白酒产品主要包括浓香型白酒金种子系列酒、种子系列酒、和泰系列酒、醉三秋系列酒和颍州系列酒等。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>服务器, 固态电池</t>
+          <t>白酒</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-1.7249</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
+        <v>0.5858</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>据河南、山东、广东、安徽等地经销商、批发商和终端零售商获悉，渠道库存总体仍在去化，部分受访酒商库存同比下降约10%-20%，名酒大单品周转相对较快，部分终端库存已控制在1-2个月。</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz002667</t>
+          <t>sz001318</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>*ST威领</t>
+          <t>阳光乳业</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>24.41</v>
+        <v>14.03</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.0045</v>
+        <v>10.0392</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>*ST威领公告称，公司收到西藏山南锑金资源有限公司出具的要约收购报告书摘要。山南锑金拟向全体股东发出部分要约，收购股份数量为7817.745万股，要约价格为18元/股，占公司总股本的30%。本次要约收购所需资金总额预计不超过14.07亿元，收购人已存入履约保证金7.04亿元。要约收购完成后，山南锑金将最多持有公司30%股份，取得公司控制权。</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t>乳业|公司专注于乳制品及乳饮料的研发、生产和销售，并以低温乳制品、低温乳饮料为主打产品。公司针对儿童提高免疫力开发的“初乳” 产品。公司从事液态乳、含乳饮料等产品的研发、生产、销售。</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>乳业</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ST股</t>
+          <t>振兴东北</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-1.7249</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
+        <v>1.5121</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>进入12月，冰雪旅游消费也迎来旺季。从历史数据上看，东北旅游热潮往往持续至春节。</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sz301030</t>
+          <t>sh600202</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>*ST仕净</t>
+          <t xml:space="preserve">哈空调  </t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>4.5</v>
+        <v>5.59</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>20</v>
+        <v>10.0394</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>ST股 | 公司在制程污染防控领域服务了众多光伏、集成电路等泛半导体行业的优质客户，如晶科能源、天合光能、阿特斯、东方日升、英特尔、长鑫存储、先进半导体等。</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
+          <t>东北+核电|公司从事的主营业务为各种高、中、低压空冷器的设计、制造和销售。主要产品包括石化空冷器和电站空冷器。此外，公司还设计、制造和销售核电站空气处理机组产品及其他工业空调产品。</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>东北, 核电</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
+          <t>振兴东北</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1.5121</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>进入12月，冰雪旅游消费也迎来旺季。从历史数据上看，东北旅游热潮往往持续至春节。</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sh601188</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>龙江交通</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>13.78</v>
+        <v>3.21</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>9.976100000000001</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>10天10板</t>
-        </is>
-      </c>
+        <v>9.9315</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
+          <t>东北+高速公路|公司地处黑龙江，黑龙江省唯一一家高速公路板块上市公司。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>东北, 高速公路</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
+          <t>振兴东北</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1.5121</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>进入12月，冰雪旅游消费也迎来旺季。从历史数据上看，东北旅游热潮往往持续至春节。</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sz000715</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>中兴商业</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>23</v>
+        <v>5.78</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>9.995200000000001</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>11天8板</t>
-        </is>
-      </c>
+        <v>10.0952</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>并购重组|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
+          <t>零售+东北|公司以商业零售为主要业务，经营业态包括百货、超市、网络购物平台等。主要分布于沈阳市核心商圈，辐射周边鞍山、抚顺、本溪、铁岭、辽阳等主要城市。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>零售, 东北</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
+          <t>电商</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>0.9214999999999999</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>中国物流与采购联合会今天（13日）发布9月份中国电商物流指数。指数环比小幅上行，线上消费需求集中释放，电商物流运行保持向好态势。</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sh600241</t>
+          <t>sh605136</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>丽人丽妆</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>12.94</v>
+        <v>11.42</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10.034</v>
+        <v>10.0193</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6天6板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>锂电池|公司旗下九夷锂能主要经营锂离子电池、电池组的研发、生产、制造、系统集成、销售和服务，目标市场定位于电动工具、个人护理、家庭电子、消费品等小动力领域。</t>
+          <t>电商+AI|1.公司是国内领先的化妆品网络零售服务商，主要从事电商零售业务和品牌营销运营服务。
+2.公司积极探索包括生成型AI产品在内的人工智能技术的应用，以提高工作效率和提升用户体验。在基础构建层面，公司已在着手进行部分人工智能软件的API接入工作，为后续相关智能运用推广做前期准备；在实际运营层面，公司考虑使用人工智能软件在优化商品描述、店铺商品图片设计、短视频制作、虚拟主播、客服服务沟通、客户评价分析等方面实现智能化，提高业务效率和质量；在营销层面，公司也计划使用人工智能软件进行广告图像设计和生成。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>锂电池</t>
+          <t>电商, AI</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
+          <t>电商</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>0.9214999999999999</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>中国物流与采购联合会今天（13日）发布9月份中国电商物流指数。指数环比小幅上行，线上消费需求集中释放，电商物流运行保持向好态势。</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz002696</t>
+          <t>sz002640</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>跨境通</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>3.89</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>9.9727</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.887</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>水产|公司位于广西，水产品加工业务板块将着重研发以罗非鱼、生鱼、金鲳鱼、海鲈鱼为原料的内销产品。</t>
+          <t>电商|公司主营业务包括跨境出口电商业务、跨境进口电商业务两大类，跨境通助力中国优质产品通过电商渠道输出到海外市场，同时将海外的优质产品进口到中国市场。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>水产</t>
+          <t>电商</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+          <t>电商</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>0.9214999999999999</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>中国物流与采购联合会今天（13日）发布9月份中国电商物流指数。指数环比小幅上行，线上消费需求集中释放，电商物流运行保持向好态势。</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sh600693</t>
+          <t>sh600228</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>东百集团</t>
+          <t>返利科技</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>11.18</v>
+        <v>10.14</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>10.0394</v>
+        <v>9.978299999999999</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>并购重组|东百集团公告称，公司全资子公司东百创智拟收购杭州快灵光电科技有限公司52.6667%股权，暂定转让对价3.16亿元。交易完成后，快灵光电及其子公司光特科技将纳入公司合并报表范围。标的公司主要从事光探测芯片研发生产销售。</t>
+          <t>电商+AI|公司基于人工智能技术开发了电商导购APP“如意”，可通过AI对话的交互方式为用户提供购物问答、建议清单、全网比价、评价提炼、评测聚合等网购服务。“如意”APP已获发第四批生成式人工智能（大模型）备案号告知书。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>并购重组</t>
+          <t>电商, AI</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
+          <t>短剧</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>0.5848</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz301419</t>
+          <t>sh605577</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>阿莱德</t>
+          <t>龙版传媒</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>47.7</v>
+        <v>19.6</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
+        <v>9.988800000000001</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>5天4板</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>液冷|公司的导热界面材料和液冷散热器件产品可根据其不同的形态、材料和特性，广泛应用于ICT通信、消费电子和光模块等场景，且部分产品如导热垫片、导热凝胶、热管、均温板等已在批量供货中。</t>
+          <t>AI漫剧|公司首部AI漫剧《穿越1988》完成170集制作上线，全网播放量突破1.2亿，红果热度值超4000万。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>液冷</t>
+          <t>AI漫剧</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
+          <t>短剧</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>0.5848</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh600831</t>
+          <t>sz002343</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>广电网络</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>3.91</v>
+        <v>7.36</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>10.1408</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
+        <v>10.0149</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>重整|10月9日，公司收到西安市中院《决定书》，法院决定受理该预重整申请，并指定陕西广电网络传媒（集团）股份有限公司清算组为预重整临时管理人。</t>
+          <t>短剧|公司已形成了以自有IP为核心资源，以影视IP内容投资、开发、制作及发行为核心业务，积极延伸拓展电影、网络电影、网络微短剧、互动剧、小程序短剧、IP线下衍生等相关品类的业务体系。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>重整</t>
+          <t>短剧</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
+          <t>短剧</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>0.5848</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+        </is>
+      </c>
       <c r="D47" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sz001231</t>
+          <t>sz002878</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>农心科技</t>
+          <t>元隆雅图</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>25.61</v>
+        <v>14.33</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>10.0086</v>
+        <v>9.977</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>农药|公司的主营业务为农药制剂产品的研发、生产与销售，主要产品包括杀虫剂、杀菌剂和除草剂。</t>
+          <t>短剧+AI|1.公司已于2023年开始布局短剧营销业务，包括迷你剧、互动剧等内容形式，为客户提供基于品牌传播的短剧定制和剧集宣发全链路服务。
+2.公司开发了新媒体广告业务系统AI智能助手QMi，该工具使用了ChatGPT技术助力品牌客户的新媒体营销服务。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>农药</t>
+          <t>短剧, AI</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr"/>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>0.8246</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>多位业内人士研判，整体而言，全A非金融行业三季度业绩有望延续高增长态势。</t>
+        </is>
+      </c>
       <c r="D48" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sh603336</t>
+          <t>sz000833</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>宏辉果蔬</t>
+          <t>粤桂股份</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>10.45</v>
+        <v>20.65</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>10</v>
+        <v>10.016</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>果蔬+创新药|1.公司是一家集果蔬产品的种植管理、采后收购、产地预冷、冷冻仓储、预选分级、加工包装、冷链配送于一体的专业生鲜产品服务商。
-2.2026年4月28日公告，公司拟使用自有及自筹资金约7亿元收购江西施美药业股份有限公司41.128%股份。施美药业是一家致力于复方降压、降脂、降糖药和心脑血管药的现代化高科技创新型制药企业，已建成成熟的生产与经营体系，主营产品涵盖化学原料药及片剂、胶囊等主流制剂。</t>
+          <t>业绩|粤桂股份公告称，预计2026年前三季度归属于上市公司股东的净利润为11.26亿元-11.95亿元，同比增长153.70%-169.24%。业绩变动主要系报告期内矿石、硫酸产品市场价格上行，公司持续深化降本增效，经营运行态势持续向好。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>果蔬, 创新药</t>
+          <t>业绩</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>0.8246</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>多位业内人士研判，整体而言，全A非金融行业三季度业绩有望延续高增长态势。</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh601127</t>
+          <t>sz002322</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">赛力斯  </t>
+          <t>理工能科</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>51.24</v>
+        <v>13.08</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10.0043</v>
+        <v>10.0084</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>汽车整车|公司与华为进行“智选模式”的合作，华为深度参与设计车型和品牌打造，在技术和渠道方面全力赋能公司。</t>
+          <t>业绩|理工能科公告称，预计2026年前三季度归属于上市公司股东的净利润为1.92亿元-2.14亿元，同比增长39.21%-55.33%。业绩变动主要系公司软件与信息化板块业务实现增长，该板块盈利提升所致。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>汽车整车</t>
+          <t>业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>-0.8024</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>机构认为，中国创新药正由“BD事件驱动”迈入“全球三期数据+全球注册”兑现期；10月ESMO等国际会议数据窗口来临，ADC、双抗等领域有望验证差异化竞争力。</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>sz002693</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>双成药业</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>10.0213</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>CXO|2022年4月21日公司在调研中表示，公司与国内外数家药企签订了CMO、CRO合作协议,有些项目已经开始执行,有些项目由于两年多的疫情受到影响和延迟。目前还有一些国际CMO项目正在洽谈中。CMO和CRO项目已经开始为公司的运营做出贡献。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>CXO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>-0.8024</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>机构认为，中国创新药正由“BD事件驱动”迈入“全球三期数据+全球注册”兑现期；10月ESMO等国际会议数据窗口来临，ADC、双抗等领域有望验证差异化竞争力。</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>sz002172</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>澳洋健康</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>10.0372</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>医疗服务|公司的医疗服务业务已形成医、康、养护联动发展模式，形成以澳洋医院总院为支撑，澳洋医院三兴分院、顺康医院、港城康复医院、优居壹佰护理院、张家港澳洋护理院联动发展。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>医疗服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>1.3151</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在珠海举办，参展企业超1100家，“首展”“首秀”展品占比约10%。</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>sh600391</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>航发科技</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>38.78</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>10.0142</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>军工+燃气轮机|公司主营业务为航空发动机及燃气轮机零部件的研发、制造、销售、服务。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>军工, 燃气轮机</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>-0.0378</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sz002667</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>*ST威领</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>9.995900000000001</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>*ST威领公告称，公司收到西藏山南锑金资源有限公司出具的要约收购报告书摘要。山南锑金拟向全体股东发出部分要约，收购股份数量为7817.745万股，要约价格为18元/股，占公司总股本的30%。本次要约收购所需资金总额预计不超过14.07亿元，收购人已存入履约保证金7.04亿元。要约收购完成后，山南锑金将最多持有公司30%股份，取得公司控制权。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>-0.0378</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>sz301030</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>*ST仕净</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 2023年2月21日公司在互动平台表示，公司目前已有制程污染防控设备应用于钙钛矿电池生产线。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>-0.0378</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sh600370</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST三房 </t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>9.8485</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 公司成为“PTA-瓶级聚酯切片”一体化布局的优势企业，PTA产品是郑州商品交易所PTA交割免检品牌，已开发出多种全系列的瓶级聚酯切片产品。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>sh603096</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新经典  </t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>10.021</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>传媒|公司是一家以内容创意为核心的传媒企业，主要业务包括图书策划与发行、数字图书、图书零售，以及影视剧策划等版权延伸业务。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>传媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>sz001231</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>农心科技</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>9.9961</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>农药+供销社|1.公司的主营业务为农药制剂产品的研发、生产与销售，主要产品包括杀虫剂、杀菌剂和除草剂。
+2.公司目前有部分经销商属于供销合作社系统，例如中国供销集团有限公司下属企业山东中农联合生物科技股份有限公司、中农立华生物科技股份有限公司等。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>农药, 供销社</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>sh600831</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>广电网络</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>9.974399999999999</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>重整|10月9日，公司收到西安市中院《决定书》，法院决定受理该预重整申请，并指定陕西广电网络传媒（集团）股份有限公司清算组为预重整临时管理人。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>重整</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>sh600693</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>东百集团</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>10.0179</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>并购重组|东百集团公告称，公司全资子公司东百创智拟收购杭州快灵光电科技有限公司52.6667%股权，暂定转让对价3.16亿元。交易完成后，快灵光电及其子公司光特科技将纳入公司合并报表范围。标的公司主要从事光探测芯片研发生产销售。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>sh600851</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>海欣股份</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>拟股权转让|海欣股份公告称，公司第一大股东凝瑞投资拟通过公开征集受让方方式转让所持公司无限售条件流通股1.21亿股，占公司总股本的10%。转让完成后，可能导致公司第一大股东发生变更。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>拟股权转让</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>sz000668</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>荣丰控股</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>10.0054</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>控股股东变更|荣丰控股公告称，公司控股股东盛世达与广州昕图签署股份转让协议，拟以每股18.63元转让29.99%股份。同时，以本次股份转让实施完成为前提，广州昕图拟发出部分要约收购5.01%股份。交易完成后，公司控股股东将变更为广州昕图，实际控制人变更为陈群萍。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>控股股东变更</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>sh600847</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>万里股份</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>10.0392</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>铅酸蓄电池|公司是中国铅酸蓄电池行业首家上市公司，以生产“万里”牌各型铅酸蓄电池闻名于世，被誉为“中国蓄能专家”。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>铅酸蓄电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>sz003037</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>三和管桩</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>10.0683</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>建材|公司的产品包括管桩、支护桩、波浪桩、U型板桩、组装式护坡构件、护坡组件及护坡结构等相关产品，广泛应用于河道维护和治理、航道沉排、排水沟、河湖港等水系生态治理与修复工程等水利建设领域。</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>建材</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>sh603767</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>中马传动</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>10.007</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司招股说明书显示，将以现有汽车变速器齿轮、汽车转向器齿轮、汽车油泵轴齿轮、汽车发动机齿轮、摩托车发动机齿轮、农机变速器齿轮为发展基础，大力开拓汽车自动变速器行星齿轮、工业机器人减速器齿轮等高精度齿轮产品领域。</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>sz002917</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>金奥博</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>并购重组|金奥博公告称，公司拟通过现金方式收购长春汇维科技股份有限公司80%股权，以取得目标公司的控股权。本次交易完成后，公司将在现有业务基础上，进一步拓展军工装备领域相关业务布局。</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>sh600237</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>铜峰电子</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>9.9878</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>薄膜电容器|公司主营业务为薄膜电容器及其薄膜材料的研发、生产和销售，具备行业特有的电容器用聚丙烯光膜—金属化薄膜—薄膜电容器上下游一体化产业链，产品涵盖聚丙烯薄膜、聚酯薄膜、金属化薄膜、电容器等众多品种。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>薄膜电容器</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>sh600802</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>9.9846</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>福建+建材|公司主要从事水泥及熟料的生产及销售，拥有7条新型干法熟料水泥生产线，具备年产熟料784.3万吨、水泥1164万吨。公司是福建地区产能规模最大的水泥制造企业，也是福建省水泥行业唯一的一家上市公司。</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>福建, 建材</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>sh603001</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>奥康国际</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>9.972300000000001</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>纺织|主要从事皮鞋及皮具产品的研发、生产、零售及分销业务,产品种类主要有商务正装鞋、休闲鞋、运动鞋等鞋类产品以及皮具配套产品。公司实施以“奥康”品牌为主, “康龙”、 “斯凯奇”等品牌为辅的多品牌运营策略。主品牌“奥康”在男鞋领域具有较强的市场竞争力。</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>纺织</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>sh600712</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>南宁百货</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>10.0559</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>零售|公司主要从事商业零售业务，地处广西南宁市，南宁市是华南经济圈、西南经济圈和中国—东盟经济圈的交汇点。</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>sh600281</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>华阳新材</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>9.9338</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>稀土|子公司太原华盛丰贵金属材料有限公司经营范围包含铂、钯、铑、银、镍贵金属系列催化剂、催化网及稀土高磁性材料的回收利用、加工、研究、生产、销售及技术服务。</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>稀土</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>sz002623</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>亚玛顿</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>10.0114</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>光伏玻璃+玻璃基板|1.国内光伏镀膜玻璃、大尺寸超薄光伏玻璃产品的先行及引领者，在行业内率先开发了更加轻量化、薄型化的1.6mm的光伏玻璃、BIPV美学、彩色镀膜玻璃、玻璃扩散板、一体化AG玻璃等具有核心竞争力的产品。
+2.2023年9月16日公司在官微透露，超高清玻璃基板产业项目占地800亩，由常州亚玛顿股份有限公司建设，主要建设年产5800万平方米的超高清玻璃基板生产基地。生产的超高清玻璃基板厚度为0.55毫米至1.1毫米，广泛应用于超高清电视、智能手机、电脑等智能电子产品显示屏制造。</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>光伏玻璃, 玻璃基板</t>
         </is>
       </c>
     </row>
@@ -2770,7 +3726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2797,46 +3753,46 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sz002696</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>百洋股份</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz002242</t>
+          <t>sh605577</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>龙版传媒</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh600241</t>
+          <t>sh605136</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>丽人丽妆</t>
         </is>
       </c>
     </row>
@@ -2846,27 +3802,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh600812</t>
+          <t>sh603096</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t xml:space="preserve">新经典  </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh603096</t>
+          <t>sz002343</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">新经典  </t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
@@ -2876,12 +3832,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz001330</t>
+          <t>sh600851</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>博纳影业</t>
+          <t>海欣股份</t>
         </is>
       </c>
     </row>
@@ -2891,12 +3847,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sz002696</t>
+          <t>sh600831</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>广电网络</t>
         </is>
       </c>
     </row>
@@ -2906,12 +3862,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sh601595</t>
+          <t>sz001231</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>上海电影</t>
+          <t>农心科技</t>
         </is>
       </c>
     </row>
@@ -2921,12 +3877,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sh605287</t>
+          <t>sh603968</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>德才股份</t>
+          <t>醋化股份</t>
         </is>
       </c>
     </row>
@@ -2936,132 +3892,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sh603232</t>
+          <t>sh600693</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>格尔软件</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>sz000892</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>欢瑞世纪</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>sh605577</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>龙版传媒</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>sz002692</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>远程股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>sz002343</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>慈文传媒</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>sh605136</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>丽人丽妆</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>sh601811</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>新华文轩</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>sh603533</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>掌阅科技</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>sh601929</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>吉视传媒</t>
+          <t>东百集团</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,20 +476,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="101" customWidth="1" min="3" max="3"/>
+    <col width="92" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="223" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="225" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,242 +552,233 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.6361</v>
+        <v>-2.7815</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>金禄电子发布公告，预计2026年前三季度归属于上市公司股东的净利润为1.80亿元-1.96亿元，同比增长192.88%-218.92%。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sh605058</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>23.25</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.9811</v>
+        <v>10.0031</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>13天9板</t>
+          <t>19天11板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>传媒+并购重组|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
+          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>传媒, 并购重组</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.6361</v>
+        <v>-2.7815</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>金禄电子发布公告，预计2026年前三季度归属于上市公司股东的净利润为1.80亿元-1.96亿元，同比增长192.88%-218.92%。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz002343</t>
+          <t>sh603386</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>骏亚科技</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>8.1</v>
+        <v>20.25</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.0543</v>
+        <v>9.9946</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>短剧|公司已形成了以自有IP为核心资源，以影视IP内容投资、开发、制作及发行为核心业务，积极延伸拓展电影、网络电影、网络微短剧、互动剧、小程序短剧、IP线下衍生等相关品类的业务体系。</t>
+          <t>PCB|公司主营业务为印制电路板（PCB）的研发、生产和销售，在人形机器人领域，公司成功导入国内头部客户并开始批量供货。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.6361</v>
+        <v>-2.7815</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>金禄电子发布公告，预计2026年前三季度归属于上市公司股东的净利润为1.80亿元-1.96亿元，同比增长192.88%-218.92%。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh603096</t>
+          <t>sz002815</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">新经典  </t>
+          <t>崇达技术</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>23.07</v>
+        <v>23.25</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.0143</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>9.9811</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>出版|公司是一家以内容创意为核心的传媒企业，主要业务包括图书策划与发行、数字图书、图书零售，以及影视剧策划等版权延伸业务。</t>
+          <t>PCB+业绩|崇达技术公告称，预计2026年前三季度归属于上市公司股东的净利润为5.95亿元-6.85亿元，同比增长89.73%-118.43%。报告期内，公司持续将产能向高价值客户倾斜，客户及订单结构进一步优化，高端产品出货占比提升明显，产品盈利能力有效修复；各生产基地产能利用充足，技术工艺迭代促使良率持续改善，叠加全流程精细化成本管控与降本增效举措落地，共同推动本期营收及归母净利润增长，预计2026年第三季度净利润实现同比、环比较快增长。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>出版</t>
+          <t>PCB, 业绩</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.6361</v>
+        <v>-2.7815</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>金禄电子发布公告，预计2026年前三季度归属于上市公司股东的净利润为1.80亿元-1.96亿元，同比增长192.88%-218.92%。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh603533</t>
+          <t>sz301282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>金禄电子</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>29.92</v>
+        <v>49.92</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7天4板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>短剧+AI|1.公司已经搭建起专业的短剧生产运营体系。公司2025年度AI短剧业务收入预计不超过2025年度主营业务收入的1%。
-2.MiniMax与掌阅科技合作的对话式AI应用“阅爱聊”，能让文学作品中的角色来到现实，与用户展开一场“跨次元”对谈。</t>
+          <t>PCB+业绩|金禄电子公告称，预计2026年前三季度归属于上市公司股东的净利润为1.80亿元-1.96亿元，同比增长192.88%-218.92%。2026年前三季度，公司深入贯彻既定营销战略，充分把握印制电路板行业供需结构性失衡带来的市场机遇，强化汽车应用领域大客户的横向拓展与纵向渗透；聚焦算力基础设施、人工智能、卫星通信等新兴产业应用领域，加速客户导入与订单落地；有序剥离低毛利、小体量业务，订单结构调整成效较为明显。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>短剧, AI</t>
+          <t>PCB, 业绩</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.6361</v>
+        <v>-2.7815</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>金禄电子发布公告，预计2026年前三季度归属于上市公司股东的净利润为1.80亿元-1.96亿元，同比增长192.88%-218.92%。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh603258</t>
+          <t>sz002134</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>电魂网络</t>
+          <t>天津普林</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>16.15</v>
+        <v>24.34</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.0136</v>
+        <v>9.9864</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>游戏|公司为一家拥有自主研发能力、运营能力的专业化网络游戏公司，致力于自主研发运营精品化的网络游戏。</t>
+          <t>PCB|公司主要从事印制电路板（PCB）的研发、生产及销售，产品类型覆盖单双面板、多层板、高多层板、HDI、高频高速板及厚铜板等，专注于中小批量、高多层、厚铜板、光电板和HDI领域的PCB领先企业。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
@@ -798,42 +789,45 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1.6361</v>
+        <v>-1.9125</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>腾讯近期低调上线内嵌于微信生态的“绿泡泡短剧”小程序，以“免费好剧，一点就看”为核心定位，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh601858</t>
+          <t>sh601811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>中国科传</t>
+          <t>新华文轩</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>26.11</v>
+        <v>25.58</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9.9832</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+        <v>10.0215</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14天10板</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>AI+出版|1.公司自主研发的SciEngine全流程数字出版与知识服务平台（V3.0）进一步集成了学术查重检测、审稿专家自动推荐、自动在线校对、科大讯飞智能翻译、AI秒读视频、文献挖掘和语义检索等多种工具，进一步提升了出版运营与知识服务能力。
-2.中科院旗下中国科技出版传媒集团所属上市公司，公司的主要业务包括图书出版业务、期刊业务、出版物进出口业务和知识服务业务等。</t>
+          <t>传媒+并购重组|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>AI, 出版</t>
+          <t>传媒, 并购重组</t>
         </is>
       </c>
     </row>
@@ -844,42 +838,45 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.6361</v>
+        <v>-1.9125</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>腾讯近期低调上线内嵌于微信生态的“绿泡泡短剧”小程序，以“免费好剧，一点就看”为核心定位，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh603598</t>
+          <t>sz002343</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>引力传媒</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>21.91</v>
+        <v>8.91</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5天5板</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>AI+短剧|1.公司已推出自有营销电商行业模型并推出三大智能体（Agent）-感知智能体、决策智能体、内容智能体，用以增强营销决策、创意素材、视频混剪等环节内容产出的精准性与稳定性。
-2.公司依托全链路整合能力，均衡发力于平台精品短剧、达人定制剧、小程序剧等多个细分领域。</t>
+          <t>短剧|公司已形成了以自有IP为核心资源，以影视IP内容投资、开发、制作及发行为核心业务，积极延伸拓展电影、网络电影、网络微短剧、互动剧、小程序短剧、IP线下衍生等相关品类的业务体系。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>AI, 短剧</t>
+          <t>短剧</t>
         </is>
       </c>
     </row>
@@ -890,92 +887,90 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1.6361</v>
+        <v>-1.9125</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>据Sensor Tower数据，字节跳动旗下短剧应用PineDrama上线约9个月后累计下载量突破1亿，日活跃用户约700万——成为海外短剧赛道增长最快的应用之一。</t>
+          <t>腾讯近期低调上线内嵌于微信生态的“绿泡泡短剧”小程序，以“免费好剧，一点就看”为核心定位，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz300299</t>
+          <t>sh603230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>富春股份</t>
+          <t>内蒙新华</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>6.88</v>
+        <v>14.52</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>20.0698</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>AI+短剧|1.公司已搭建本地化AI应用工具，其中AI绘图(美术)工具已在部分在研项目应用，实现一定的降本增效，并积极探索AIGC在程序、测试优化等环节实现应用工具。
-2.参股公司东阳留白影视文化有限公司系短剧《风声之双生谜局》的出品方。</t>
+          <t>出版|公司的最终控制人为内蒙古自治区人民政府。公司主营业务是出版物的批发、零售；文体用品零售；音像制品发行</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>AI, 短剧</t>
+          <t>出版</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-1.0512</v>
+        <v>-1.9125</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>机构研报指出，厄尔尼诺引发的秘鲁近海海水升温，会直接限制鳀鱼捕捞规模，压制鱼粉供给。据ING数据，当前全球鱼粉价格同比暴涨超75%。</t>
+          <t>腾讯近期低调上线内嵌于微信生态的“绿泡泡短剧”小程序，以“免费好剧，一点就看”为核心定位，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz002696</t>
+          <t>sh603999</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>读者传媒</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>9.75</v>
+        <v>7.62</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.0451</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>9.9567</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>水产+鱼粉|1.公司位于广西，水产品加工业务板块将着重研发以罗非鱼、生鱼、金鲳鱼、海鲈鱼为原料的内销产品。
-2.公司下辖鱼粉厂的合计年产量约为1-2万吨，鱼油年产量约为2000-4000吨。</t>
+          <t>出版|公司主要业务涵盖期刊、图书、教材教辅等纸质出版物的出版、发行、阅读服务及电子出版物、在线教育、文化创意等领域，形成主业突出、产业多元化的发展格局。“读者”品牌是公司发展的核心。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>水产, 鱼粉</t>
+          <t>出版</t>
         </is>
       </c>
     </row>
@@ -986,45 +981,46 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-1.0512</v>
+        <v>-1.9405</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>机构研报指出，厄尔尼诺引发的秘鲁近海海水升温，会直接限制鳀鱼捕捞规模，压制鱼粉供给。据ING数据，当前全球鱼粉价格同比暴涨超75%。</t>
+          <t>据河南、山东、广东、安徽等地经销商、批发商和终端零售商获悉，渠道库存总体仍在去化，部分受访酒商库存同比下降约10%-20%，名酒大单品周转相对较快，部分终端库存已控制在1-2个月。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz001318</t>
+          <t>sz002696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>阳光乳业</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>15.43</v>
+        <v>10.73</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9.9786</v>
+        <v>10.0513</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6天3板</t>
+          <t>5天5板</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>乳制品|公司专注于乳制品及乳饮料的研发、生产和销售，并以低温乳制品、低温乳饮料为主打产品。公司针对儿童提高免疫力开发的“初乳” 产品。公司从事液态乳、含乳饮料等产品的研发、生产、销售。</t>
+          <t>水产品+鱼粉|1.公司位于广西，水产品加工业务板块将着重研发以罗非鱼、生鱼、金鲳鱼、海鲈鱼为原料的内销产品。
+2.公司下辖鱼粉厂的合计年产量约为1-2万吨，鱼油年产量约为2000-4000吨。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>乳制品</t>
+          <t>水产品, 鱼粉</t>
         </is>
       </c>
     </row>
@@ -1035,151 +1031,154 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-1.0512</v>
+        <v>-1.9405</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>机构研报指出，厄尔尼诺引发的秘鲁近海海水升温，会直接限制鳀鱼捕捞规模，压制鱼粉供给。据ING数据，当前全球鱼粉价格同比暴涨超75%。</t>
+          <t>据河南、山东、广东、安徽等地经销商、批发商和终端零售商获悉，渠道库存总体仍在去化，部分受访酒商库存同比下降约10%-20%，名酒大单品周转相对较快，部分终端库存已控制在1-2个月。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh600097</t>
+          <t>sz001318</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>开创国际</t>
+          <t>阳光乳业</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>10.2</v>
+        <v>16.97</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.0324</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+        <v>9.980600000000001</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7天4板</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>水产+鱼粉|1.公司基本形成海洋捕捞、食品加工、海上运输、渔货贸易一体化产业结构格局，拥有完整的金枪鱼产业链。
-2.开创国际在互动平台表示，舟山食品加工厂已进入试生产阶段，生产加工后的鱼柳产品以销往国外为主，鱼粉销往国内市场。公司ALBO品牌罐头在天猫、京东均有销售。</t>
+          <t>乳业|公司专注于乳制品及乳饮料的研发、生产和销售，并以低温乳制品、低温乳饮料为主打产品。公司针对儿童提高免疫力开发的“初乳” 产品。公司从事液态乳、含乳饮料等产品的研发、生产、销售。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>水产, 鱼粉</t>
+          <t>乳业</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-1.3595</v>
+        <v>-1.9405</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>江西省宏瑞兴科技股份有限公司、松下、南亚塑胶等公司近期再度上调覆铜板（CCL）等产品价格。</t>
+          <t>据河南、山东、广东、安徽等地经销商、批发商和终端零售商获悉，渠道库存总体仍在去化，部分受访酒商库存同比下降约10%-20%，名酒大单品周转相对较快，部分终端库存已控制在1-2个月。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz000823</t>
+          <t>sz000995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>超声电子</t>
+          <t>皇台酒业</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>24.55</v>
+        <v>13.37</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9.991</v>
+        <v>10.0412</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>业绩+PCB|超声电子公告称，预计2026年前三季度归属于上市公司股东的净利润为3.40亿元-3.60亿元，同比增长90.78%-102%。业绩变动主要系覆铜板行业维持高景气，量价齐升，公司覆铜板产品订单充足，产品售价上行，盈利能力提升；印制板业务持续优化产品结构，产能利用率提高，综合带动净利润同比大幅增长。</t>
+          <t>葡萄酒|西北风格的名优白酒。葡萄酒产品依靠河西走廊得天独厚的地理优势，酒体品质达到了国际标准。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>业绩, PCB</t>
+          <t>葡萄酒</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-1.3595</v>
+        <v>-1.9405</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>江西省宏瑞兴科技股份有限公司、松下、南亚塑胶等公司近期再度上调覆铜板（CCL）等产品价格。</t>
+          <t>据河南、山东、广东、安徽等地经销商、批发商和终端零售商获悉，渠道库存总体仍在去化，部分受访酒商库存同比下降约10%-20%，名酒大单品周转相对较快，部分终端库存已控制在1-2个月。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz002860</t>
+          <t>sh603237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>星帅尔</t>
+          <t xml:space="preserve">五芳斋  </t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20.23</v>
+        <v>16.47</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.0054</v>
+        <v>10.02</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>并购重组+PCB|星帅尔公告称，公司拟通过发行股份及支付现金的方式收购梵宇科技100%股权，本次交易中，星帅尔购买交易对方合计持有的梵宇科技100%股权的暂估交易对价为8.4亿元。标的公司深耕于精密刀具制造装备及钻针半成品领域，通过长期自主研发创新，业务范围已形成“装备制造+钻针半成品”的协同布局，并积累了相应的技术壁垒与客户资源。</t>
+          <t>糯米|公司主要从事以糯米食品为主导的食品研发、生产和销售，目前已形成以粽子为主导，集月饼、汤圆、糕点、蛋制品、其他米制品等食品为一体的产品群。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>并购重组, PCB</t>
+          <t>糯米</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-1.3595</v>
+        <v>-1.5576</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>江西省宏瑞兴科技股份有限公司、松下、南亚塑胶等公司近期再度上调覆铜板（CCL）等产品价格。</t>
+          <t>10月13日，国家医保局召开会议，会议要求，要积极支持医药科技创新。探索建立医疗服务价格预立项制度，支持更多医药新技术新产品加快进入临床规模化应用。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1187,569 +1186,586 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz002552</t>
+          <t>sh600812</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>宝鼎科技</t>
+          <t>华北制药</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>45.8</v>
+        <v>6.57</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9.990400000000001</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
+        <v>10.0503</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>6天4板</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>业绩+PCB|宝鼎科技公告称，预计2026年前三季度归属于上市公司股东的净利润为3.30亿元-3.70亿元，同比增长536.88%-614.07%。主要原因是：第一，报告期内，覆铜板行业维持高景气，行业呈现量价齐升态势，公司控股子公司金宝电子覆铜板及电子铜箔业务扭亏为盈，产品销量及销售价格持续上升，导致营业收入及毛利率增长；第二，报告期内，国际黄金价格走势保持在高位震荡运行，子公司河西金矿成品金产品销售价格上涨，导致营业收入及毛利率增长。</t>
+          <t>链霉素|公司青霉素系列、头孢系列产品品种齐全，覆盖了原料药到制剂的大部分品种，形成了从发酵原料到半合成原料药再到制剂的完整产品链。是国内硫酸链霉素原料药及注射剂的核心生产企业。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>业绩, PCB</t>
+          <t>链霉素</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1.1646</v>
+        <v>-1.5576</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>十一长假结束后的第一周，动力煤市场快速回归:港口5500大卡平仓价站上1000-1008元/吨，某集团港口外购5500卡上调至991元/吨。</t>
+          <t>10月13日，国家医保局召开会议，会议要求，要积极支持医药科技创新。探索建立医疗服务价格预立项制度，支持更多医药新技术新产品加快进入临床规模化应用。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh600408</t>
+          <t>sh600721</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>安泰集团</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.06</v>
+        <v>12.05</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.0271</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>10.0457</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>焦炭|公司主营焦炭及其副产品，炼焦采用的是JN60-6型焦炉，产品主要销售给钢铁企业。目前公司焦炭年生产能力已达到240万吨，是山西省焦化龙头企业之一。</t>
+          <t>CXO|公司主营业务为药物发现、研究、技术服务，提供从药物发现、CMC、临床CRO、药品注册、CMO/API供应等新药开发全流程的服务及一体化的解决方案。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>焦炭</t>
+          <t>CXO</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1.1646</v>
+        <v>-1.5576</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>十一长假结束后的第一周，动力煤市场快速回归:港口5500大卡平仓价站上1000-1008元/吨，某集团港口外购5500卡上调至991元/吨。</t>
+          <t>10月13日，国家医保局召开会议，会议要求，要积极支持医药科技创新。探索建立医疗服务价格预立项制度，支持更多医药新技术新产品加快进入临床规模化应用。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh600121</t>
+          <t>sz300111</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>郑州煤电</t>
+          <t>向日葵</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>5.86</v>
+        <v>3.71</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.9437</v>
+        <v>20.0647</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>煤炭|公司主营业务为煤炭开采与销售，兼营煤炭相关物资和设备的采购与销售等贸易业务，所属矿厂主要分布在郑州所辖的新郑市、新密市和登封市，煤炭品种主要为无烟煤、贫煤和贫瘦煤，是优质的工业动力煤。公司2024年年报披露，主要矿区资源储量5.6亿吨、可采储量2.51亿吨、证实储量8448万吨。</t>
+          <t>医药|公司聚焦医药领域，目前已成为拥有较为完整的抗感染、抗高血压药物产业链，能够同时从事相关原料药和制剂研发、生产和销售的企业。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>医药</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>快递物流</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1.5822</v>
+        <v>-2.4735</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在珠海举办，参展企业超1100家，“首展”“首秀”展品占比约10%。</t>
+          <t>国家税务总局发票数据显示，前8个月，全国省际贸易稳步增长，重点区域外销辐射作用明显，交通物流和信息服务稳步增长，先进制造业省际流动加快。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz002917</t>
+          <t>sz002889</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>金奥博</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>12.1</v>
+        <v>13.01</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.974600000000001</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>并购重组+军工|金奥博公告称，公司拟通过现金方式收购长春汇维科技股份有限公司80%股权，以取得目标公司的控股权。本次交易完成后，公司将在现有业务基础上，进一步拓展军工装备领域相关业务布局。</t>
+          <t>光刻机+物流|1.公司将与国际头部芯片光刻机厂商合作，共同在深圳建设寄售维修保税仓库，为华南片区集成电路制造企业提供全天候快速响应的光刻机寄售维修服务。
+2.公司业务主要是基于全球中心仓提供供应链一体化服务，以及销售商品。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 军工</t>
+          <t>光刻机, 物流</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>快递物流</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-1.5822</v>
+        <v>-2.4735</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在珠海举办，参展企业超1100家，“首展”“首秀”展品占比约10%。</t>
+          <t>国家税务总局发票数据显示，前8个月，全国省际贸易稳步增长，重点区域外销辐射作用明显，交通物流和信息服务稳步增长，先进制造业省际流动加快。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh600391</t>
+          <t>sh603329</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>航发科技</t>
+          <t>上海雅仕</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>42.66</v>
+        <v>11.33</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10.0052</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>军工+燃气轮机|公司主营业务为航空发动机及燃气轮机零部件的研发、制造、销售、服务。</t>
+          <t>物流|公司拥有公、铁、水多式联运的综合物流网络，覆盖我国主要港口和城市，以南昆铁路干线和陇海铁路干线为核心运输通道，以防城港、钦州港、上海港、连云港等港口为重要的集散地，建立并延伸发展了多条集装箱多式联运路线。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>军工, 燃气轮机</t>
+          <t>物流</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>快递物流</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-2.0406</v>
+        <v>-2.4735</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>三丰化工发布调价函：近期上游原料乙萘酚、硝酸价格多次上涨，原料成本持续攀升，同时硝化行业生产管控趋严，产量产能受到大幅压缩，综合生产成本显著增加，因此氧体和硝体从15万元/吨，调整为从18万元/吨。</t>
+          <t>国家税务总局发票数据显示，前8个月，全国省际贸易稳步增长，重点区域外销辐射作用明显，交通物流和信息服务稳步增长，先进制造业省际流动加快。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh603968</t>
+          <t>sh603535</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>醋化股份</t>
+          <t>嘉诚国际</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>15.8</v>
+        <v>6.73</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.0279</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>9.9673</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>染料+乙腈|1.公司的双乙甲酯产品涉及分散染料领域。
-2.减肥药GLP多肽拉动高纯溶剂需求，乙腈20日涨价超112%，截至2026年10月12日，报21500元/吨，子公司立洋化学年产30000吨乙腈及联产15200吨硫酸铵、450吨丙酮扩产项目，目前已基本建成。</t>
+          <t>物流|公司的主营业务是为制造业客户提供定制化物流解决方案及全程供应链一体化综合物流服务。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>染料, 乙腈</t>
+          <t>物流</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>化工</t>
+          <t>业绩超预期</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-2.0406</v>
+        <v>-3.4319</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>三丰化工发布调价函：近期上游原料乙萘酚、硝酸价格多次上涨，原料成本持续攀升，同时硝化行业生产管控趋严，产量产能受到大幅压缩，综合生产成本显著增加，因此氧体和硝体从15万元/吨，调整为从18万元/吨。</t>
+          <t>三季报披露窗口开启，市场资金从高估值成长方向撤出后向盈利质量与业绩确定性方向聚集，现金流策略作为质量因子的代表受到关注。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz002469</t>
+          <t>sh605189</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>三维化学</t>
+          <t>富春染织</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>6.86</v>
+        <v>17.85</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>9.9359</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+        <v>9.9815</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>硫磺|公司主要从事以服务石化、化工、油品储运和煤化工行业为主的设计咨询与工程总承包业务，致力于包括硫资源回收在内的节能环保技术的研究与开发利用，自主研发的无在线炉硫磺回收工艺技术达到国际先进水平。公司累计承担设计、总承包硫磺回收装置近百套，是设计硫磺回收装置最多的工程公司。</t>
+          <t>业绩|富春染织公告称，预计2026年前三季度归属于上市公司股东的净利润为3.38亿元-3.78亿元，同比增长1348%-1519%。业绩变动主要系公司持续深化全产业链布局，智能工厂充分释放效能，单位产品能耗和成本明显降低，产品产销量与价格协同攀升所致。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>硫磺</t>
+          <t>业绩</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>冰雪产业</t>
+          <t>业绩超预期</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-0.4495</v>
+        <v>-3.4319</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨冰雪大世界与华特迪士尼（中国）有限公司合作，将在园区内打造以动画电影《冰雪奇缘》为灵感的主题区域，为全球首个以真冰真雪为载体的大型实景主题区。</t>
+          <t>三季报披露窗口开启，市场资金从高估值成长方向撤出后向盈利质量与业绩确定性方向聚集，现金流策略作为质量因子的代表受到关注。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>sz000722</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>湖南发展</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>10.0158</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>业绩|湖南发展公告称，预计2026年前三季度归属于上市公司股东的净利润为2.50亿元-2.90亿元，同比（重组前）增长290.45%-352.92%。业绩变动主要系公司实施重大资产重组，高电公司、铜电公司、清电公司、筱电公司成为控股子公司，水电装机规模大幅增长，且上游来水偏丰，发电量同比大幅增长。</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>-3.4319</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>三季报披露窗口开启，市场资金从高估值成长方向撤出后向盈利质量与业绩确定性方向聚集，现金流策略作为质量因子的代表受到关注。</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>sz000626</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>远大控股</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>9.976000000000001</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>业绩|远大控股公告称，预计2026年前三季度归属于上市公司股东的净利润为3.19亿元-3.60亿元，同比增长890%-1018%。业绩变动主要系公司大宗商品贸易板块经营效益显著改善，受益于多年积累的市场经验及供应链服务能力，板块盈利规模同比大幅提升。</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>染料涂料</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>-2.4475</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>6月低点至今，分散染料报价累计上涨超30%，活性染料涨幅达到55%；核心中间体H酸价格从61元/千克上涨至145元/千克，涨幅高达138%。</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>sz002748</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>世龙实业</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>9.991899999999999</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>氯化亚砜|公司是国内AC发泡剂和氯化亚砜的主要生产商之一，具备氯化亚砜5万吨/年的产能，氯化亚砜产品主要应用于染料、医药、农药等行业。</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>氯化亚砜</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>染料涂料</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>-2.4475</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>6月低点至今，分散染料报价累计上涨超30%，活性染料涨幅达到55%；核心中间体H酸价格从61元/千克上涨至145元/千克，涨幅高达138%。</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>sh603172</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>万丰股份</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>10.0214</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>分散染料|公司主营业务为分散染料及其滤饼的研发、生产及销售，产品以中高端分散染料为主，主要用于涤纶及其混纺织物的染色和印花，经分散染料印染加工的化纤纺织品，色泽艳丽，耐洗牢度优良，用途广泛。</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>分散染料</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>-2.6721</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>财政部等三部门发文明确，自2026年9月1日起至2028年12月31日，对钠离子电池、固态电池等免征消费税，定向扶持新技术路线。</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>sh603200</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>上海洗霸</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>53.35</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>固态电池+液冷|1.公司生产的固态电解质粉体材料可以应用于锂离子固态电池，多形态固态电解质粉体材料（含油性、水性、浆料）年产50吨级产线主要采用的是氧化物技术路线，公司储备了硫化物、氯化物等固态电解质的其它固态电解质粉体技术路线。
+2.公司面向腾讯、华为、中国移动等重点客户数据中心提供循环水/空气蒸发冷却等专业服务。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>固态电池, 液冷</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>sz000530</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>冰山冷热</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>9.9476</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="G27" s="2" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>液冷+冰雪产业|1.公司拥有数据中心相应的冷热解决方案。
 2.子公司冰山工程近年来承接了多项代表性工程，包括广州融创茂室内滑雪场项目、上海之星室内综合性冰雪场馆、陕西国际体育之窗等多个商业冰雪场馆项目。</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>液冷, 冰雪产业</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>业绩超预期</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>-1.9284</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>中金公司研报表示，三季报有望为市场带来一定的业绩支撑，投资者信心有望修复。</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>sh605189</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>富春染织</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>16.23</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>10.0339</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>业绩|富春染织公告称，预计2026年前三季度归属于上市公司股东的净利润为3.38亿元-3.78亿元，同比增长1348%-1519%。业绩变动主要系公司持续深化全产业链布局，智能工厂充分释放效能，单位产品能耗和成本明显降低，产品产销量与价格协同攀升所致。</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>业绩</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>-0.9379000000000001</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>sz000010</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>*ST美丽</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>9.7744</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司逐步拓展主营延伸业务向大数据算力等新兴产业倾斜，设立美丽算力科技运营（海南）有限公司。</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>-0.9379000000000001</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>sz300338</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>*ST开元</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>20.1646</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 全资子公司恒企教育控股广州多迪（教育培训业）90%股权。</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>-0.9379000000000001</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>sz000609</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>*ST中迪</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>9.27</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>9.964399999999999</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司房地产项目位于重庆、成都、达州，重庆的“两江中迪广场”主要为商业项目。</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>sz000668</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>荣丰控股</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>10.0195</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>实控人变更|荣丰控股公告称，公司控股股东盛世达与广州昕图签署股份转让协议，拟以每股18.63元转让29.99%股份。同时，以本次股份转让实施完成为前提，广州昕图拟发出部分要约收购5.01%股份。交易完成后，公司控股股东将变更为广州昕图，实际控制人变更为陈群萍。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>实控人变更</t>
         </is>
       </c>
     </row>
@@ -1766,37 +1782,37 @@
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sh600847</t>
+          <t>sh600281</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>万里股份</t>
+          <t>华阳新材</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15.43</v>
+        <v>5.21</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>9.9786</v>
+        <v>9.9156</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天2板</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>铅酸蓄电池|公司是中国铅酸蓄电池行业首家上市公司，以生产“万里”牌各型铅酸蓄电池闻名于世，被誉为“中国蓄能专家”。</t>
+          <t>稀土|子公司太原华盛丰贵金属材料有限公司经营范围包含铂、钯、铑、银、镍贵金属系列催化剂、催化网及稀土高磁性材料的回收利用、加工、研究、生产、销售及技术服务。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>铅酸蓄电池</t>
+          <t>稀土</t>
         </is>
       </c>
     </row>
@@ -1813,37 +1829,33 @@
       </c>
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh601188</t>
+          <t>sz001225</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>龙江交通</t>
+          <t>和泰机电</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>3.53</v>
+        <v>38.5</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>9.9688</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>东北+高速公路|公司地处黑龙江，黑龙江省唯一一家高速公路板块上市公司。</t>
+          <t>机器人|公司通过持续实施自动化、智能化改造，更新迭代生产设备，在物料输送设备制造领域的生产工艺已相对成熟，应用了机器人自动焊接技术，机器人视觉识别自动上下料、自动装箱等技术。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>东北, 高速公路</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -1860,37 +1872,34 @@
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh600202</t>
+          <t>sz003029</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">哈空调  </t>
+          <t>吉大正元</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>6.15</v>
+        <v>19.99</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.0179</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0165</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>冰雪产业注入预期|公司同一实控人哈尔滨国资委旗下马迭尔集团是其唯一文旅平台，旗下拳头品牌哈尔滨冰雪大世界、太阳岛风景区、亚布力等，或有资产注入预期。</t>
+          <t>数字货币+网络安全|1.1.公司积极关注数字货币的发展趋势，持续推进面向数字货币的新业务应用及技术研究项目，为数字货币提供可信安全支撑。
+2.公司为央行、国有银行等金融机构提供信息PKI密码安全基础设施、身份安全、数据保护、签验等产品、技术及解决方案，公司积极关注数字货币的发展趋势，持续推进面向数字货币的新业务应用及技术研究项目，为数字货币提供可信安全支撑。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>冰雪产业注入预期</t>
+          <t>数字货币, 网络安全</t>
         </is>
       </c>
     </row>
@@ -1907,37 +1916,33 @@
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz300006</t>
+          <t>sz002103</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>莱美药业</t>
+          <t>广博股份</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>20.0608</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>9.970700000000001</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>纳米炭铁抗癌|10月9日，四川大学华西医院联合恩施州中心医院，正式对外公布了全球首个铁死亡诱导剂的I期临床试验结果。纳米炭铁混悬注射液是四川瀛瑞医药科技有限公司（莱美药业控股子公司）在纳米炭混悬注射液基础上研发的新一代纳米药物，属于抗癌类制剂。</t>
+          <t>文具|公司文教办公用品业务主要包括时尚办公文具、文创生活以及办公直销三大品类。公司电商板块持续推动数智化营销。组建完成Kinbor私域营销团队，策略性调整淘宝天猫店运营方向以学生文创方面转型。Fizz板块通过开发设计以轻松办公为主题系列的产品，主打高端文具产品市场，持续将时尚元素融入办公用品。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>纳米炭铁抗癌</t>
+          <t>文具</t>
         </is>
       </c>
     </row>
@@ -1954,37 +1959,33 @@
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh603992</t>
+          <t>sz002836</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>松霖科技</t>
+          <t>新宏泽</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>24.61</v>
+        <v>11.85</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.0134</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>10.0279</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>机器人|旗下松霖机器人与达闼机器人签署了战略合作框架协议，共同探索人形机器人垂直场景应用、核心部件创新升级、机器人出海及其他创新领域的产业机会。</t>
+          <t>烟标|公司系专业烟标印刷服务供应商，主营业务为烟标的设计、生产及销售。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>烟标</t>
         </is>
       </c>
     </row>
@@ -2001,33 +2002,33 @@
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz002813</t>
+          <t>sh600668</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>路畅科技</t>
+          <t>尖峰集团</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>29.02</v>
+        <v>7.99</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10.0076</v>
+        <v>10.0551</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>实控人变更|路畅科技公告称，公司控股股东中联重科与远卓天使签署《股份转让协议》，拟以25元/股转让3598.8万股股份(占总股本29.99%)，转让价款总额8.997亿元。交易完成后，公司控股股东将变更为远卓天使，实控人变更为张五堂。此外，远卓天使将指定要约人发起部分要约收购，预定收购比例不低于14%，要约价25元/股。</t>
+          <t>创新药|尖峰药业及其下属控股子公司在研抗肿瘤新药主要有JFAN-1001。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>实控人变更</t>
+          <t>创新药</t>
         </is>
       </c>
     </row>
@@ -2044,34 +2045,33 @@
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz001299</t>
+          <t>sh603690</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>美能能源</t>
+          <t>至纯科技</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>10.92</v>
+        <v>23.77</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>9.969799999999999</v>
+        <v>9.9954</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>天然气+储能|1.公司是一家长期专注于清洁能源供应领域的专业化城市燃气综合运营服务商，主要从事城镇燃气的输配与运营业务，包括天然气终端销售和服务以及天然气用户设施设备安装业务。
-2.公司于2024年开始进行美能能源总部暨西安智慧能源研究院建设项目建设，聚焦新能源、新材料、新技术以及多能互补系统、储能系统、综合能源智慧运营系统的研发和应用，为清洁能源产业化利用提供技术方向和解决方案。</t>
+          <t>半导体设备|公司是国内主流气体化学品相关的高纯工艺系统及半导体装备的合格供应商，高纯工艺系统产品主要包括气体高纯工艺设备及系统、化学品高纯工艺设备及系统以及物料及水系统。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>天然气, 储能</t>
+          <t>半导体设备</t>
         </is>
       </c>
     </row>
@@ -2088,33 +2088,33 @@
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh603656</t>
+          <t>sh605003</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>泰禾智能</t>
+          <t>众望布艺</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>19.06</v>
+        <v>25.96</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>9.982699999999999</v>
+        <v>10</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>智能检测分选装备|公司致力于提高社会生产的智能化，自动化水平，主营智能装备制造业，研发，生产和销售智能检测分选装备与智能制造装备（工业机器人），并为部分行业用户提供个性化，多样化，系统化的自动化生产整体解决方案。</t>
+          <t>纺织|公司主营业务为中高档装饰面料及制品的研发、设计、生产与销售。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>智能检测分选装备</t>
+          <t>纺织</t>
         </is>
       </c>
     </row>
@@ -2131,33 +2131,33 @@
       </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sz000601</t>
+          <t>sz002543</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>韶能股份</t>
+          <t>万和电气</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>6.82</v>
+        <v>7.88</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10</v>
+        <v>10.0559</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>绿电|公司自成立以来，一直以能源的投资开发经营为主营业务，在不断巩固和发展水电产业的基础上，重点发展生物质能发电、加油加气充电一体化站等业务。</t>
+          <t>热泵|公司是国内热水器行业龙头企业，拥有产品、渠道与品牌优势，空气能热泵业务发展潜力大。子公司广东万和新能源科技有限公司负责空气能热泵相关业务。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>绿电</t>
+          <t>热泵</t>
         </is>
       </c>
     </row>
@@ -2174,163 +2174,33 @@
       </c>
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz000573</t>
+          <t>sz002945</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>粤宏远Ａ</t>
+          <t>华林证券</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>4.33</v>
+        <v>15.39</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>9.8985</v>
+        <v>10.0071</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>房地产|公司以房地产开发为主营业务，同时经营含铅废旧资源回收与利用、工业区厂房租赁、水电工程建设、新能源汽车废旧动力蓄电池回收利用等业务。</t>
+          <t>券商|西藏地区唯一一家上市券商，主要通过总部以及下属分支机构从事财富管理、投资银行、资产管理以及自营业务等，通过全资子公司从事另类投资业务、私募股权投资业务。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>房地产</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>sz002029</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>七 匹 狼</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>9.979200000000001</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>纺织+机器人|1.主要从事“七匹狼”品牌男装的设计、生产和销售,主要产品包括衬衫、西服、裤装、茄克衫、针织衫等。
-2.公司母公司间接持有摩尔线程和宇树科技的部分股权。</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>纺织, 机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>sh600252</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>中恒集团</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>10.2222</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>莱美药业控股股东|中恒集团是莱美药业的控股股东，纳米炭铁混悬注射液是四川瀛瑞医药科技有限公司（莱美药业控股子公司）在纳米炭混悬注射液基础上研发的新一代纳米药物，属于抗癌类制剂。</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>莱美药业控股股东</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>sz001216</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>华瓷股份</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>9.9954</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>氧化锆粉体|子公司氧化锆粉体纯度最高可达99.995%，产品可适配新能源研磨、齿科陶瓷、MLCC等不同领域使用需求。</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>氧化锆粉体</t>
+          <t>券商</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2372,46 +2242,46 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sh603096</t>
+          <t>sz002696</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">新经典  </t>
+          <t>百洋股份</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz002696</t>
+          <t>sz002343</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>慈文传媒</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz002343</t>
+          <t>sz000530</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2291,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh603968</t>
+          <t>sz001318</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>醋化股份</t>
+          <t>阳光乳业</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2306,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz002917</t>
+          <t>sh605189</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>金奥博</t>
+          <t>富春染织</t>
         </is>
       </c>
     </row>
@@ -2451,147 +2321,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh601188</t>
+          <t>sh601811</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>龙江交通</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>sz000668</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>荣丰控股</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>sz000823</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>超声电子</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>sh600391</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>航发科技</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>sz002813</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>路畅科技</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>sh600202</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">哈空调  </t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>sz001318</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>阳光乳业</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>sz000530</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>冰山冷热</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>sz002860</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>星帅尔</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>sh600847</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>万里股份</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="92" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="111" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="225" customWidth="1" min="10" max="10"/>
+    <col width="240" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,1655 +552,2791 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-2.7815</v>
+        <v>2.7181</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>金禄电子发布公告，预计2026年前三季度归属于上市公司股东的净利润为1.80亿元-1.96亿元，同比增长192.88%-218.92%。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh605058</t>
+          <t>sz002949</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>华阳国际</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>70.48999999999999</v>
+        <v>14.14</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.0031</v>
+        <v>10.0389</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>19天11板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
+          <t>基建+低空经济|1.公司一直从事建筑设计和研发及其延伸业务，拥有建筑行业（建筑工程）甲级资质、工程造价咨询甲级资质、建筑工程施工总承包一级和市政公用工程施工总承包二级资质。
+2.公司涉及低空经济的业务主要是关于航空小镇的规划设计，目前已承接江西共青城环南湖、辽宁太平湾规划设计项目。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>基建, 低空经济</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-2.7815</v>
+        <v>2.7181</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>金禄电子发布公告，预计2026年前三季度归属于上市公司股东的净利润为1.80亿元-1.96亿元，同比增长192.88%-218.92%。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh603386</t>
+          <t>sh603197</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>骏亚科技</t>
+          <t>保隆科技</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20.25</v>
+        <v>29.39</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.9946</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>9.9925</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司主营业务为印制电路板（PCB）的研发、生产和销售，在人形机器人领域，公司成功导入国内头部客户并开始批量供货。</t>
+          <t>低空经济|公司的空气弹簧和双目立体视觉摄像头已获得头部新势力车企的飞行汽车项目定点。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>低空经济</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-2.7815</v>
+        <v>2.7181</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>金禄电子发布公告，预计2026年前三季度归属于上市公司股东的净利润为1.80亿元-1.96亿元，同比增长192.88%-218.92%。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz002815</t>
+          <t>sz002085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>崇达技术</t>
+          <t>万丰奥威</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>23.25</v>
+        <v>9.91</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.9811</v>
+        <v>9.988900000000001</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>PCB+业绩|崇达技术公告称，预计2026年前三季度归属于上市公司股东的净利润为5.95亿元-6.85亿元，同比增长89.73%-118.43%。报告期内，公司持续将产能向高价值客户倾斜，客户及订单结构进一步优化，高端产品出货占比提升明显，产品盈利能力有效修复；各生产基地产能利用充足，技术工艺迭代促使良率持续改善，叠加全流程精细化成本管控与降本增效举措落地，共同推动本期营收及归母净利润增长，预计2026年第三季度净利润实现同比、环比较快增长。</t>
+          <t>低空经济|公司子公司万丰飞机与全球某知名主机厂已达成战略合作，拟在eVTOL原型机开发、电池系统、工业设计、航空工程、模具及工装制造、供应链及大规模量产、航空适航认证、品牌力和B2C/B2B销售和售后网络资源等领域深度合作并为合资公司提供支持。公司钻石eDA40纯电动飞机已成功首飞。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>PCB, 业绩</t>
+          <t>低空经济</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-2.7815</v>
+        <v>2.7181</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>金禄电子发布公告，预计2026年前三季度归属于上市公司股东的净利润为1.80亿元-1.96亿元，同比增长192.88%-218.92%。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz301282</t>
+          <t>sz002869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>金禄电子</t>
+          <t>金溢科技</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>49.92</v>
+        <v>20.58</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>20</v>
+        <v>9.9947</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>PCB+业绩|金禄电子公告称，预计2026年前三季度归属于上市公司股东的净利润为1.80亿元-1.96亿元，同比增长192.88%-218.92%。2026年前三季度，公司深入贯彻既定营销战略，充分把握印制电路板行业供需结构性失衡带来的市场机遇，强化汽车应用领域大客户的横向拓展与纵向渗透；聚焦算力基础设施、人工智能、卫星通信等新兴产业应用领域，加速客户导入与订单落地；有序剥离低毛利、小体量业务，订单结构调整成效较为明显。</t>
+          <t>低空智联产品|公司低空智联产品线深耕“高速+低空”特色垂直场景，依托自身在智能交通领域沉淀的融合感知、AI识别、车路通信核心技术，将机器视觉、物联网技术跨界迁移至无人机领域，打造“自动机场+无人机+AI”一体化智能巡检与监测解决方案，精准赋能交通、应急、工程、政务等多行业数字化、智能化升级。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>PCB, 业绩</t>
+          <t>低空智联产品</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-2.7815</v>
+        <v>2.7181</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>金禄电子发布公告，预计2026年前三季度归属于上市公司股东的净利润为1.80亿元-1.96亿元，同比增长192.88%-218.92%。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz002134</t>
+          <t>sz300411</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>天津普林</t>
+          <t>金盾股份</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>24.34</v>
+        <v>9.6</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9.9864</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>PCB|公司主要从事印制电路板（PCB）的研发、生产及销售，产品类型覆盖单双面板、多层板、高多层板、HDI、高频高速板及厚铜板等，专注于中小批量、高多层、厚铜板、光电板和HDI领域的PCB领先企业。</t>
+          <t>军工+低空经济|1.公司旗下全资子公司中强科技主要从事军用隐身材料、伪装网（遮障）、伪装涂料和重防腐涂料等产品的研发、生产、销售和技术服务。
+2.2024年1月12日公司在互动平台表示，公司已经跟清华大学合作完成飞行汽车叶轮的样机研发，目前正在推动项目的产业化。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>军工, 低空经济</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-1.9125</v>
+        <v>2.7181</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>腾讯近期低调上线内嵌于微信生态的“绿泡泡短剧”小程序，以“免费好剧，一点就看”为核心定位，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sz001696</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>宗申动力</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>25.58</v>
+        <v>15.87</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.0215</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14天10板</t>
-        </is>
-      </c>
+        <v>9.979200000000001</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>传媒+并购重组|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
+          <t>低空经济+商业航天|1.公司是国内专业化小型热动力机械产品制造基地之一，子公司航发公司主要聚焦无人机及通航有人飞机动力领域，已取得关键突破和一定的市场覆盖；公司在＂发动机+”业务方面，已开始参与某型飞机配套项目科研。
+2.参股子公司航天神舟飞行器公司业务性质为航空航天和其他运输设备制造业。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>传媒, 并购重组</t>
+          <t>低空经济, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-1.9125</v>
+        <v>2.7181</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>腾讯近期低调上线内嵌于微信生态的“绿泡泡短剧”小程序，以“免费好剧，一点就看”为核心定位，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz002343</t>
+          <t>920690.BJ</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>捷众科技</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>8.91</v>
+        <v>19.24</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5天5板</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>短剧|公司已形成了以自有IP为核心资源，以影视IP内容投资、开发、制作及发行为核心业务，积极延伸拓展电影、网络电影、网络微短剧、互动剧、小程序短剧、IP线下衍生等相关品类的业务体系。</t>
+          <t>低空经济+机器人|1.公司核心产品精密注塑齿轮将应用于小鹏汇天飞行汽车上。
+2.2.公司与杭州云深处科技股份有限公司达成深度合作，正式签订产品开发协议，共同推进机器人轻量化升级、有效降低生产成本，努力实现核心部件“以塑代钢”的技术突破，双方将联合研发适用于人形机器人及四足机器人关节部位的专用齿轮，助力机器人核心零部件性能与成本优势的双重提升。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>低空经济, 机器人</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-1.9125</v>
+        <v>2.7181</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>腾讯近期低调上线内嵌于微信生态的“绿泡泡短剧”小程序，以“免费好剧，一点就看”为核心定位，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh603230</t>
+          <t>sz002510</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>内蒙新华</t>
+          <t>天汽模</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>14.52</v>
+        <v>5.96</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>9.963099999999999</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>出版|公司的最终控制人为内蒙古自治区人民政府。公司主营业务是出版物的批发、零售；文体用品零售；音像制品发行</t>
+          <t>低空经济|在低空经济领域，公司持续发力通用航空市场，成为小鹏汇天陆地航母Evtol机型、通航国际LE700机型、冠一航空GA20机型项目定点供应商。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>出版</t>
+          <t>低空经济</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-1.9125</v>
+        <v>2.7181</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>腾讯近期低调上线内嵌于微信生态的“绿泡泡短剧”小程序，以“免费好剧，一点就看”为核心定位，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh603999</t>
+          <t>sz001319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>读者传媒</t>
+          <t>铭科精技</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>7.62</v>
+        <v>21.4</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>9.9567</v>
+        <v>10.0257</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>出版|公司主要业务涵盖期刊、图书、教材教辅等纸质出版物的出版、发行、阅读服务及电子出版物、在线教育、文化创意等领域，形成主业突出、产业多元化的发展格局。“读者”品牌是公司发展的核心。</t>
+          <t>低空经济+机器人|1.公司已承接小鹏汇天飞行汽车产品部分模具及零部件的生产交付。
+2.2024年9月12日公司在互动平台表示，近期在东莞市塘厦镇拿地新建相关产业项目，该项目建成后主要涉及到汽车五金模具、汽车零部件及人形机器人机械手臂总成等业务，项目建设周期为两年左右。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>出版</t>
+          <t>低空经济, 机器人</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-1.9405</v>
+        <v>2.7181</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>据河南、山东、广东、安徽等地经销商、批发商和终端零售商获悉，渠道库存总体仍在去化，部分受访酒商库存同比下降约10%-20%，名酒大单品周转相对较快，部分终端库存已控制在1-2个月。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz002696</t>
+          <t>sz000099</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>中信海直</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>10.73</v>
+        <v>14.75</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10.0513</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5天5板</t>
-        </is>
-      </c>
+        <v>9.9925</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>水产品+鱼粉|1.公司位于广西，水产品加工业务板块将着重研发以罗非鱼、生鱼、金鲳鱼、海鲈鱼为原料的内销产品。
-2.公司下辖鱼粉厂的合计年产量约为1-2万吨，鱼油年产量约为2000-4000吨。</t>
+          <t>低空经济|公司具有通用航空全业务运营的资质和能力，低空飞行方面，公司开通观光、短途运输等业务，已有深圳城际观光，深圳—珠海、舟山—东极岛、深圳—金沙湾等摆渡飞行航线。公司与腾讯投资的德国eVTOL企业Lilium有合作，计划建立eVTOL运营网络，包括战略性生产基地、试飞、售后服务。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>水产品, 鱼粉</t>
+          <t>低空经济</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-1.9405</v>
+        <v>2.7181</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>据河南、山东、广东、安徽等地经销商、批发商和终端零售商获悉，渠道库存总体仍在去化，部分受访酒商库存同比下降约10%-20%，名酒大单品周转相对较快，部分终端库存已控制在1-2个月。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz001318</t>
+          <t>sh600178</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>阳光乳业</t>
+          <t>东安动力</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>16.97</v>
+        <v>10.25</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>9.980600000000001</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7天4板</t>
-        </is>
-      </c>
+        <v>9.9785</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>乳业|公司专注于乳制品及乳饮料的研发、生产和销售，并以低温乳制品、低温乳饮料为主打产品。公司针对儿童提高免疫力开发的“初乳” 产品。公司从事液态乳、含乳饮料等产品的研发、生产、销售。</t>
+          <t>低空经济|2024年9月11日公司官微透露，东安动力高效增程发动机搭载小鹏汇天飞行汽车量产启动，此款产品为全球唯一能装下“飞机”的汽车提供“移动超充”，将成为公司市场开拓新的发力点。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>乳业</t>
+          <t>低空经济</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-1.9405</v>
+        <v>2.7181</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>据河南、山东、广东、安徽等地经销商、批发商和终端零售商获悉，渠道库存总体仍在去化，部分受访酒商库存同比下降约10%-20%，名酒大单品周转相对较快，部分终端库存已控制在1-2个月。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz000995</t>
+          <t>sh603348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>皇台酒业</t>
+          <t>文灿股份</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>13.37</v>
+        <v>15.31</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.0412</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>9.9856</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>葡萄酒|西北风格的名优白酒。葡萄酒产品依靠河西走廊得天独厚的地理优势，酒体品质达到了国际标准。</t>
+          <t>低空经济|公司已获得某飞行汽车的相关铝合金零部件定点。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>葡萄酒</t>
+          <t>低空经济</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-1.9405</v>
+        <v>2.7181</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>据河南、山东、广东、安徽等地经销商、批发商和终端零售商获悉，渠道库存总体仍在去化，部分受访酒商库存同比下降约10%-20%，名酒大单品周转相对较快，部分终端库存已控制在1-2个月。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh603237</t>
+          <t>sz300045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">五芳斋  </t>
+          <t>华力创通</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>16.47</v>
+        <v>12.7</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.02</v>
+        <v>20.0378</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>糯米|公司主要从事以糯米食品为主导的食品研发、生产和销售，目前已形成以粽子为主导，集月饼、汤圆、糕点、蛋制品、其他米制品等食品为一体的产品群。</t>
+          <t>低空经济|上海子公司依托公司卫星通信、卫星导航、航电系统、无人系统等既有核心技术，重点拓展长三角地区民用航空、低空经济、商业航天配套等行业市场。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>糯米</t>
+          <t>低空经济</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-1.5576</v>
+        <v>2.7181</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10月13日，国家医保局召开会议，会议要求，要积极支持医药科技创新。探索建立医疗服务价格预立项制度，支持更多医药新技术新产品加快进入临床规模化应用。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh600812</t>
+          <t>sh603239</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>华北制药</t>
+          <t>浙江仙通</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>6.57</v>
+        <v>14.43</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.0503</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>6天4板</t>
-        </is>
-      </c>
+        <v>9.9848</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>链霉素|公司青霉素系列、头孢系列产品品种齐全，覆盖了原料药到制剂的大部分品种，形成了从发酵原料到半合成原料药再到制剂的完整产品链。是国内硫酸链霉素原料药及注射剂的核心生产企业。</t>
+          <t>低空经济+机器人|1.公司能够为飞行汽车提供密封条。
+2.2025年9月25日公告，公司拟以4000万元对浩海星空进行增资，投资完成后持有浩海星空10%的股份。增资完成后，公司与浩海星空拟出资设立合资公司，合资公司由浙江仙通控股，注册在浙江省台州市仙居县，合资公司注册资本2000万元人民币，其中公司认缴出资1020万元，占注册资本的51%。本次合作事项为机器人业务相关。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>链霉素</t>
+          <t>低空经济, 机器人</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-1.5576</v>
+        <v>2.7181</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>10月13日，国家医保局召开会议，会议要求，要积极支持医药科技创新。探索建立医疗服务价格预立项制度，支持更多医药新技术新产品加快进入临床规模化应用。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh600721</t>
+          <t>sz300681</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>英搏尔</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>12.05</v>
+        <v>20.84</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.0457</v>
+        <v>19.977</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>CXO|公司主营业务为药物发现、研究、技术服务，提供从药物发现、CMC、临床CRO、药品注册、CMO/API供应等新药开发全流程的服务及一体化的解决方案。</t>
+          <t>低空经济|2025年1月8日公告，公司与亿航智能拟共同设立合资公司，投资额为1000万元，其中英搏尔出资600万元，持股60%，亿航智能出资400万元，持股40%。合资公司将围绕eVTOL产品生产制造以及上游零部件产业链展开深入合作。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>CXO</t>
+          <t>低空经济</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>低空经济</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-1.5576</v>
+        <v>2.7181</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10月13日，国家医保局召开会议，会议要求，要积极支持医药科技创新。探索建立医疗服务价格预立项制度，支持更多医药新技术新产品加快进入临床规模化应用。</t>
+          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz300111</t>
+          <t>sz301586</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>向日葵</t>
+          <t>佳力奇</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>3.71</v>
+        <v>33</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>20.0647</v>
+        <v>20</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>医药|公司聚焦医药领域，目前已成为拥有较为完整的抗感染、抗高血压药物产业链，能够同时从事相关原料药和制剂研发、生产和销售的企业。</t>
+          <t>低空经济|公司专注于航空复材零部件的研发、生产、销售及相关服务，已于2022年与广东汇天航空航天科技有限公司签署《技术开发合同》，并形成销售收入。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>低空经济</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>快递物流</t>
+          <t>军工</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-2.4735</v>
+        <v>2.492</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局发票数据显示，前8个月，全国省际贸易稳步增长，重点区域外销辐射作用明显，交通物流和信息服务稳步增长，先进制造业省际流动加快。</t>
+          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>sz002917</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>金奥博</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>10.0092</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4天3板</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>并购重组+军工|金奥博公告称，公司拟通过现金方式收购长春汇维科技股份有限公司80%股权，以取得目标公司的控股权。本次交易完成后，公司将在现有业务基础上，进一步拓展军工装备领域相关业务布局。</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>并购重组, 军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2.492</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>sh601606</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>长城军工</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>9.9931</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>军工|公司为控股型公司，主营业务均通过子公司开展，以军品业务为主，下属四家军品子公司神剑科技、方圆机电、东风机电、红星机电均属重点军工企业，并在其对应领域占据重要地位，主要从事迫击炮弹系列、光电对抗系列、单兵火箭系列、引信系列、子弹药系列、火工品系列等产品的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>2.492</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>sz300581</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>晨曦航空</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>20.0203</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>军工|公司是国内少数同时拥有航空技术信息化中最关键的导航、控制、通讯、（航空）计算机等核心技术的企业，主要产品均为军品，最终用户为国内军方，涉及航空惯性导航、航空发动机电子及无人机领域。</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>2.492</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>sz002683</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>广东宏大</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>10.0158</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>军工|公司拥有军工“三证”、是全国保留军工能力的十四家地方军工企业之一，公司以子公司广东明华机械有限公司为实施平台，孵化多个前瞻性军工项目研发平台。广东宏大曾携自主研发的HD-1A超声速巡航导弹武器系统参加珠海航展。</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>2.492</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>sz002933</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>新兴装备</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>9.988099999999999</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>机器人+军工|1.公司的伺服控制等技术可以应用到人形机器人旋转、直行关节上，目前正在进行相关产品的研发工作。
+2.公司是军工领域高端装备制造的高新技术企业，主营业务是以伺服控制技术为核心的航空装备产品的研发、生产、销售及相关服务。</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>2.492</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>sz000576</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>甘化科工</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>10.0376</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>军工+半导体|1.公司通过收购沈阳含能控股权和升华电源100%股权新增军工业务板块。升华电源主要产品服务于机载、舰载、弹载等多种武器平台，主要客户涵盖国内知名军工企业、军工科研院所、军工厂等。
+2.公司参股公司锴威特半导体专注于智能功率器件与功率集成芯片的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>军工, 半导体</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>2.492</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>sh600148</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>长春一东</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>军工央企|公司控股股东是中国兵器工业集团子公司东北工业集团旗下吉林东光集团，公司主要从事汽车离合器及液压举升机构等汽车零部件的研发、生产与销售。</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>军工央企</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2.492</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>sz002535</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>林州重机</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>9.9567</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>军工+机器人|1.公司与多家大型军工集团建立了合作关系，并承接、交付了多批次的订单。
+2.公司曾于14年定增募资1.02亿元用于工业机器人产业化（一期）项目。</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>军工, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>2.492</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>sh600501</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>航天晨光</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>9.971299999999999</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>军工+商业航天|1.中国航天科工集团旗下上市公司，军工及核非标设备与服务板块主营产品有军用特种油料装备(各型加油车、泵站方舱、加油装置)、飞机加油车、测控惯导设备、核电“三废”处理设备及相关服务等。
+2.公司作为中国航天型号产品用金属软管的定点研制生产单位，陆续为国家多项航天工程提供配套产品。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>军工, 商业航天</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>2.492</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>sz002724</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>海洋王</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>10.0719</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>军工|公司是武器装备科研生产三级保密资格单位，设有专门的军品事业部负责军品的销售。</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>2.492</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>920006.BJ</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>晟楠科技</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>29.9769</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>军工|公司主要从事航空装备制造、军用电源领域相关产品的研发、生产和销售。主要产品包括航空减速控制器、航空阻尼器等航空机械类产品以及变压整流器、继电器盒等综合电源类产品等。公司产品应用于军用飞机、车辆、电子设备。</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>10月12日晚间，新剑传动发布了创业板上市审核问询函的回复文件，系统梳理了其与特斯拉Optimus产业链的合作关系及行业判断。文件中明确：特斯拉Optimus V3的硬件设计方案已基本冻结定型，即将进入量产周期。</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>sh603015</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>弘讯科技</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>9.9796</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>机器人+核聚变|1.公司积极推进多关节、蜘蛛手即DELTA分拣式机器人等多个成熟产品的销售推广。
+2.在特殊物理专案方面，公司意大利子公司EEI参与的欧洲主导之跨国人造太阳项目（FusionforEnergy，F4E）。</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 核聚变</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>10月12日晚间，新剑传动发布了创业板上市审核问询函的回复文件，系统梳理了其与特斯拉Optimus产业链的合作关系及行业判断。文件中明确：特斯拉Optimus V3的硬件设计方案已基本冻结定型，即将进入量产周期。</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>sz002614</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>奥佳华</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>10.0376</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>福建+机器人|公司AI按摩机器人2.0（OG-8598Plus），已实现服务功能与产品有机结合，运用人脸识别、疲感侦测、“千人千方”智能AI算法、云端个人健康数据库、新一代4D无刷变频温感机芯等新技术构建围绕用户健康的检测-分析-调理闭环服务系统，关注每一位用户的健康状态，为用户远程推送“量身定制”的专属按摩解决方案，构建家庭健康管理服务生态。</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>福建, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>10月12日晚间，新剑传动发布了创业板上市审核问询函的回复文件，系统梳理了其与特斯拉Optimus产业链的合作关系及行业判断。文件中明确：特斯拉Optimus V3的硬件设计方案已基本冻结定型，即将进入量产周期。</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>sh603305</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>旭升集团</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>10.0101</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司目前已组建全新的系统集成事业部，对新能源汽车被动安全系统、铝合金底盘系统、新能源储能系统及智能机器人轻量化骨架等进行前沿研发。</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>10月12日晚间，新剑传动发布了创业板上市审核问询函的回复文件，系统梳理了其与特斯拉Optimus产业链的合作关系及行业判断。文件中明确：特斯拉Optimus V3的硬件设计方案已基本冻结定型，即将进入量产周期。</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>sh600699</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>均胜电子</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>10.0271</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>机器人+智能驾驶|1.公司定位“汽车+机器人Tier1”，全面布局人形机器人领域，向包括全球车企在内的具身智能机器人相关公司提供软硬件及解决方案。
+2.公司与大唐集团旗下的辰芯科技签署战略合作协议，联手发力汽车智能车联技术，打造新一代TBOX和V2X车用电子产品。</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 智能驾驶</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>10月12日晚间，新剑传动发布了创业板上市审核问询函的回复文件，系统梳理了其与特斯拉Optimus产业链的合作关系及行业判断。文件中明确：特斯拉Optimus V3的硬件设计方案已基本冻结定型，即将进入量产周期。</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>sz000887</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>中鼎股份</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>9.9938</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>机器人+液冷|1.中鼎股份公告称，公司与众擎机器人为加强双方合作关系，围绕人形机器人相关产品展开合作，于近日签署了战略合作协议。
+2.子公司中鼎流体及中鼎智能热系统主导热管理系统总成业务的发展，在汽车热管理业务基础上积极布局储能热管理及超算中心热管理。基于自研热管理控制器及控制算法，管路系统及密封等核心技术，公司在储能领域已推出系列化液冷机组，及浸没式液冷机组；超算中心热管理领域主要产品为CDU（冷液分配装置）。</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 液冷</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>碳纤维</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>3.5016</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉新款Roadster跑车亮相，据介绍车辆使用镁、钛和碳纤维等轻质高强度材料降低整车质量。</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>sh600860</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>京城股份</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>10.0139</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>碳纤维+机器人|1.公司已经完全掌握了70MPa的铝合金内胆碳纤维缠绕气瓶的技术。
+2.2.公司持有北洋天青80.00%的股权，北洋天青立足于家电和3C行业，是一家生产线的智能化升级改造行业解决方案提供商，为制造企业提供基于云端、算法驱动、灵活可配置的多平台实时协同系统，搭配机器人应用、自动化设备、智能物流等硬件设施。</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>碳纤维, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>碳纤维</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>3.5016</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉新款Roadster跑车亮相，据介绍车辆使用镁、钛和碳纤维等轻质高强度材料降低整车质量。</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>sh600843</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>上工申贝</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>9.963099999999999</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>碳纤维+低空经济|公司通过下属子公司SGIA完成对美国ICON公司有效资产的购买，ICON公司主要从事设计、生产及销售碳纤维轻型双座运动型飞机。</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>碳纤维, 低空经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>碳纤维</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>3.5016</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉新款Roadster跑车亮相，据介绍车辆使用镁、钛和碳纤维等轻质高强度材料降低整车质量。</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>sh603013</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>亚普股份</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>9.970700000000001</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>碳纤维+机器人|1.公司参与制定了3项团体标准，分别是《70MPaIV 型储氢瓶压力容器用高性能碳纤维》《储能电池集成式液冷设备技术规范》和《碳纤维缠绕储氢气瓶无损失效检测方法。
+2.2025年5月28日公告，公司拟以自有资金购买上海飞驰高科技有限公司等11名交易对方持有的上海赢双电机科技股份有限公司约54.50%股份，交易对价约5.78亿元。其产品旋转变压器是高性能电动化的关键核心部件，是节能与新能源汽车、先进轨道交通装备、高档数控机床和机器人的核心基础零部件。</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>碳纤维, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>碳纤维</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>3.5016</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉新款Roadster跑车亮相，据介绍车辆使用镁、钛和碳纤维等轻质高强度材料降低整车质量。</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>sz000420</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>吉林化纤</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>9.915000000000001</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>碳纤维+低空经济|公司碳纤维下游客户有在汽车领域上应用，飞机领域正在开发。小鹏飞行汽车旅航者X2整机碳纤维零部件均由HRC承制。2022年12月，HRC与吉林化纤签署《战略合作及供货框架协议》。</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>碳纤维, 低空经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>-0.0587</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>早盘韩国股市高开高走，存储芯片龙头SK海力士涨逾3%，三星电子涨近3%。</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>sz002889</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>东方嘉盛</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>13.01</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>9.974600000000001</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="G38" s="2" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>9.9923</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>光刻机+物流|1.公司将与国际头部芯片光刻机厂商合作，共同在深圳建设寄售维修保税仓库，为华南片区集成电路制造企业提供全天候快速响应的光刻机寄售维修服务。
 2.公司业务主要是基于全球中心仓提供供应链一体化服务，以及销售商品。</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>光刻机, 物流</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>快递物流</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>-2.4735</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局发票数据显示，前8个月，全国省际贸易稳步增长，重点区域外销辐射作用明显，交通物流和信息服务稳步增长，先进制造业省际流动加快。</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>-0.0587</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>早盘韩国股市高开高走，存储芯片龙头SK海力士涨逾3%，三星电子涨近3%。</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>sz001358</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>兴欣新材</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>10.0221</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>光刻胶|公司在电子化学品领域的产品主要是 N-羟乙基哌嗪以及N,N-二甲基丙酰胺，主要用于生产面板的光刻胶剥离液。</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>光刻胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>-0.0587</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>早盘韩国股市高开高走，存储芯片龙头SK海力士涨逾3%，三星电子涨近3%。</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>sh603173</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福斯达  </t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>30.05</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>9.992700000000001</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>油气+电子特气|1.公司的液化天然气装置（LNG装置）产品包括常规天然气液化提纯设备、化工尾气分离提纯液化设备、非常规天然气提纯液化设备，主要应用于天然气、石油化工等行业。
+2.公司已经有向客户提供空分设备并向下游半导体用户供气。</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>油气, 电子特气</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>-0.0587</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>早盘韩国股市高开高走，存储芯片龙头SK海力士涨逾3%，三星电子涨近3%。</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>sh605178</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>时空科技</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>10.009</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>存储芯片|2025年10月9日公告，公司正在筹划以发行股份及支付现金的方式购买深圳市嘉合劲威电子科技有限公司的控股权，同时拟发行股份募集配套资金。本次交易预计构成重大资产重组。嘉合劲威业务核心围绕存储产品及相关应用展开，现已形成固件算法开发、存储芯片测试、集成封装设计、存储产品定制等核心竞争力，其存储芯片产品广泛应用于移动智能终端、PC、行业终端、数据中心等多个信息技术领域。</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>存储芯片</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>量子科技</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>0.6799000000000001</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>谷歌量子人工智能发布量子计算重大突破，团队在Willow处理器上验证“魔法态培育”技术，将相关量子态的错误率降至未经培育时的约1/40，获得逻辑保真度达99.99%的T态。</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>sh603329</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>上海雅仕</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="H19" s="2" t="n">
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>sz003029</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>吉大正元</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>10.005</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>量子科技+网络安全|1.公司实现抗量子签名的算法，并成功开发传统密码和抗量子密码混合模式的密钥生成以及证书签发功能，完成抗量子算法与数字证书技术的结合，以进一步提升数字认证基础设施的安全性。
+2.公司为央行、国有银行等金融机构提供信息PKI密码安全基础设施、身份安全、数据保护、签验等产品、技术及解决方案，公司积极关注数字货币的发展趋势，持续推进面向数字货币的新业务应用及技术研究项目，为数字货币提供可信安全支撑。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>量子科技, 网络安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>量子科技</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>0.6799000000000001</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>谷歌量子人工智能发布量子计算重大突破，团队在Willow处理器上验证“魔法态培育”技术，将相关量子态的错误率降至未经培育时的约1/40，获得逻辑保真度达99.99%的T态。</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>sz002767</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>先锋电子</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="H43" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>物流|公司拥有公、铁、水多式联运的综合物流网络，覆盖我国主要港口和城市，以南昆铁路干线和陇海铁路干线为核心运输通道，以防城港、钦州港、上海港、连云港等港口为重要的集散地，建立并延伸发展了多条集装箱多式联运路线。</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>快递物流</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>-2.4735</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局发票数据显示，前8个月，全国省际贸易稳步增长，重点区域外销辐射作用明显，交通物流和信息服务稳步增长，先进制造业省际流动加快。</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>量子科技+机器人|1.公司基于量子加密通信技术实现防窃听检测的先锋电子物联网智能膜式燃气表已在合肥市部分居民小区连续稳定运行多年。
+2.参股公司智驰华芯主营业务为汽车、工业和机器人等控制机构和探测模块的核心传感器，从传感器芯片到传感器系统完整的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>量子科技, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>量子科技</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>0.6799000000000001</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>谷歌量子人工智能发布量子计算重大突破，团队在Willow处理器上验证“魔法态培育”技术，将相关量子态的错误率降至未经培育时的约1/40，获得逻辑保真度达99.99%的T态。</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>sh603535</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>嘉诚国际</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>9.9673</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>物流|公司的主营业务是为制造业客户提供定制化物流解决方案及全程供应链一体化综合物流服务。</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>业绩超预期</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>-3.4319</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>三季报披露窗口开启，市场资金从高估值成长方向撤出后向盈利质量与业绩确定性方向聚集，现金流策略作为质量因子的代表受到关注。</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>sz002076</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>星光股份</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>10.1523</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>量子科技|子公司广州天芯量子拥有量子密钥分发、量子VPN加密、量子密钥管理等核心技术，已先后开发量子密钥分发产品、量子密钥管理终端、量子光交换机、量子波分复用终端、量子密钥应用设备、云防线及安全态势感知平台等产品。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>量子科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>据福州、厦门海关统计，今年前三季度，福建外贸进出口1.52万亿元，同比增长7.4%。其中，出口8844.4亿元，增长1.4%；进口6375.2亿元，增长17%。</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>sh605189</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>富春染织</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>9.9815</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>sh600802</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>福建水泥</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>10.0649</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>福建+水泥|公司主要从事水泥及熟料的生产及销售，拥有7条新型干法熟料水泥生产线，具备年产熟料784.3万吨、水泥1164万吨。公司是福建地区产能规模最大的水泥制造企业，也是福建省水泥行业唯一的一家上市公司。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>福建, 水泥</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>据福州、厦门海关统计，今年前三季度，福建外贸进出口1.52万亿元，同比增长7.4%。其中，出口8844.4亿元，增长1.4%；进口6375.2亿元，增长17%。</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>sz000701</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>厦门信达</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>10.0616</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>福建+大宗商品贸易|公司是厦门国贸控股集团旗下上市公司。公司供应链业务以大宗商品贸易为载体，以有色金属和黑色大宗商品贸易业务为主。</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>福建, 大宗商品贸易</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>据福州、厦门海关统计，今年前三季度，福建外贸进出口1.52万亿元，同比增长7.4%。其中，出口8844.4亿元，增长1.4%；进口6375.2亿元，增长17%。</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>sh603668</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>天马科技</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>10.0583</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>福建+水产|公司是国内特种水产配合饲料品种最为齐全的企业之一，产品主要应用于鳗鲡、石斑鱼、大黄鱼、龟、鳖、鲟鱼、鲑鳟、鲆鲽鳎、鲍、海参等特种水产动物从种苗期至养成期的人工养殖全阶段。</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>福建, 水产</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>-2.1065</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>腾讯上线“绿泡泡短剧”小程序，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>sz000607</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>华媒控股</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>10.0239</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>AI短剧|传媒子公司扩大媒体数字化应用，打造“数字人文杰”、“审点芯”数字人、“杭州迹忆”平台、“杭州文博金牌推荐官1号”苏东坡数字人IP等产品，探索AI短剧平台研发。</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>AI短剧</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>-2.1065</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>腾讯上线“绿泡泡短剧”小程序，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>sh603636</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>南威软件</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>9.9863</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>短剧出海|南威软件在互动平台表示，公司AI短剧业务首部海外AI短剧已于8月制作完成。按照规划，2026年下半年计划出品25部高质量AI短剧，整体产能规划为年产超100部，公司海外短剧自有发行APP预计11月上线.</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>短剧出海</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>-2.1065</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>腾讯上线“绿泡泡短剧”小程序，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>sh601999</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>出版传媒</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>短剧+AI|公司所属音像社、电子社等公司，参与制作视频短剧等作品，部分制作中使用AI技术，作品在学习强国、红果等平台播放。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>短剧, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>1.8063</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>北京时间2026年10月14日晚，国星宇航在东风商业航天创新试验区使用朱雀二号改进型Y4运载火箭，成功将“星算”计划02组星座晨昏轨道8颗卫星发射升空。</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>sh603278</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>大业股份</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>9.988900000000001</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>商业航天+机器人|1.公司投资联营企业湖北三江航天江北机械工程有限公司金额为6405.04万。湖北三江航天江北机械工程有限公司主要从事航天动力系统、天线罩等航天型号产品及特种压力容器产品等民用产品的研发生产。
+2.公司关注到近期市场上公司还涉及“人形机器人概念股”相关内容。公司现有主营业务仍以胎圈钢丝、钢帘线以及胶管钢丝的研发、生产和销售为主，公司机器人腱绳产品目前尚未批量生产，未产生实质性收益，且公司相关业务未来在技术研发、产品竞争能力、盈利能力等方面存在重大不确定性。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>商业航天, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>1.8063</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>北京时间2026年10月14日晚，国星宇航在东风商业航天创新试验区使用朱雀二号改进型Y4运载火箭，成功将“星算”计划02组星座晨昏轨道8颗卫星发射升空。</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>sh688592</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>司南导航</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>19.9808</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>商业航天|公司自成立以来一直致力于高精度卫星导航专用芯片和差分定位（RTK）技术的研究与开发，基于北斗以及其他全球卫星导航系统（GNSS），向客户提供实时定位精度为厘米、毫米级的高精度卫星导航定位板卡/模块、数据采集设备、农机自动驾驶系统以及数据应用及系统解决方案。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>冰雪产业</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>1.1038</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>《2026中国冰雪产业发展研究报告》15日在北京正式发布，2025-2026冰雪季全国居民冰雪运动参与人数达3.08亿，冰雪旅游游客约2.2亿人次，冰雪产业规模突破万亿，运动消费规模达2050亿元，同比增长约9.3%。</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sz000530</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>冰山冷热</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>9.9567</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>冰雪产业|子公司冰山工程近年来承接了多项代表性工程，包括广州融创茂室内滑雪场项目、上海之星室内综合性冰雪场馆、陕西国际体育之窗等多个商业冰雪场馆项目。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>冰雪产业</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>冰雪产业</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>1.1038</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>《2026中国冰雪产业发展研究报告》15日在北京正式发布，2025-2026冰雪季全国居民冰雪运动参与人数达3.08亿，冰雪旅游游客约2.2亿人次，冰雪产业规模突破万亿，运动消费规模达2050亿元，同比增长约9.3%。</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>sh603955</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>大千生态</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>9.986000000000001</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>冰雪产业|2025年12月，旗下江苏大千文旅与柳叶湖旅游度假区正式签约。项目以“沉浸式体验、全年龄段适配”为核心，精心打造奇趣雪乡乐园、戏雪乐园、侏罗纪秘境、梦幻绿野仙踪等六大核心体验区，设置20多条滑道、恐龙主题展区、冰雪雕塑区及免费互动项目。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>冰雪产业</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>-0.6261</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>10月15日，阿斯利康与Insitro签署价值18.6亿美元的人工智能药物研发协议，旨在帮助寻找治疗肝脏和心脏疾病的新药。</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sh603168</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>莎普爱思</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>10.0529</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>眼药|公司是一家以生产、研发和销售化学制剂药和中成药为主要业务的医药制造企业。化学制剂药主要涵盖眼科用药（抗白内障类）、抗微生物药（头孢菌素类）、抗微生物药（喹诺酮类）和调节水、电解质及酸碱平衡药等细分治疗领域，主要产品包括莎普爱思滴眼液、大输液和头孢克肟产品等，其中莎普爱思滴眼液在抗白内障药物市场中处于行业前列。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>眼药</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>sh601811</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>新华文轩</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>10.0078</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>15天11板</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>并购重组+传媒|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>并购重组, 传媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>sh603999</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>读者传媒</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>9.973799999999999</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>2天2板</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>业绩|富春染织公告称，预计2026年前三季度归属于上市公司股东的净利润为3.38亿元-3.78亿元，同比增长1348%-1519%。业绩变动主要系公司持续深化全产业链布局，智能工厂充分释放效能，单位产品能耗和成本明显降低，产品产销量与价格协同攀升所致。</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>业绩</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>业绩超预期</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>-3.4319</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>三季报披露窗口开启，市场资金从高估值成长方向撤出后向盈利质量与业绩确定性方向聚集，现金流策略作为质量因子的代表受到关注。</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>sz000722</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>湖南发展</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>10.0158</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>业绩|湖南发展公告称，预计2026年前三季度归属于上市公司股东的净利润为2.50亿元-2.90亿元，同比（重组前）增长290.45%-352.92%。业绩变动主要系公司实施重大资产重组，高电公司、铜电公司、清电公司、筱电公司成为控股子公司，水电装机规模大幅增长，且上游来水偏丰，发电量同比大幅增长。</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>业绩</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>业绩超预期</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>-3.4319</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>三季报披露窗口开启，市场资金从高估值成长方向撤出后向盈利质量与业绩确定性方向聚集，现金流策略作为质量因子的代表受到关注。</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>sz000626</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>远大控股</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>9.976000000000001</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>业绩|远大控股公告称，预计2026年前三季度归属于上市公司股东的净利润为3.19亿元-3.60亿元，同比增长890%-1018%。业绩变动主要系公司大宗商品贸易板块经营效益显著改善，受益于多年积累的市场经验及供应链服务能力，板块盈利规模同比大幅提升。</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>业绩</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>染料涂料</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>-2.4475</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>6月低点至今，分散染料报价累计上涨超30%，活性染料涨幅达到55%；核心中间体H酸价格从61元/千克上涨至145元/千克，涨幅高达138%。</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>sz002748</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>世龙实业</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>9.991899999999999</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>出版发行|公司主要业务涵盖期刊、图书、教材教辅等纸质出版物的出版、发行、阅读服务及电子出版物、在线教育、文化创意等领域，形成主业突出、产业多元化的发展格局。“读者”品牌是公司发展的核心。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>出版发行</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>sh600668</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>尖峰集团</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>10.0125</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>创新药|尖峰药业及其下属控股子公司在研抗肿瘤新药主要有JFAN-1001。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>创新药</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>sz000573</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>粤宏远Ａ</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>10.0985</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>3天2板</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>氯化亚砜|公司是国内AC发泡剂和氯化亚砜的主要生产商之一，具备氯化亚砜5万吨/年的产能，氯化亚砜产品主要应用于染料、医药、农药等行业。</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>氯化亚砜</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>染料涂料</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>-2.4475</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>6月低点至今，分散染料报价累计上涨超30%，活性染料涨幅达到55%；核心中间体H酸价格从61元/千克上涨至145元/千克，涨幅高达138%。</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>sh603172</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>万丰股份</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>20.53</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>10.0214</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>分散染料|公司主营业务为分散染料及其滤饼的研发、生产及销售，产品以中高端分散染料为主，主要用于涤纶及其混纺织物的染色和印花，经分散染料印染加工的化纤纺织品，色泽艳丽，耐洗牢度优良，用途广泛。</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>分散染料</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>-2.6721</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>财政部等三部门发文明确，自2026年9月1日起至2028年12月31日，对钠离子电池、固态电池等免征消费税，定向扶持新技术路线。</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>sh603200</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>上海洗霸</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>53.35</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>固态电池+液冷|1.公司生产的固态电解质粉体材料可以应用于锂离子固态电池，多形态固态电解质粉体材料（含油性、水性、浆料）年产50吨级产线主要采用的是氧化物技术路线，公司储备了硫化物、氯化物等固态电解质的其它固态电解质粉体技术路线。
-2.公司面向腾讯、华为、中国移动等重点客户数据中心提供循环水/空气蒸发冷却等专业服务。</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>固态电池, 液冷</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>并购重组|粤宏远A公告称，公司拟以现金方式受让深圳市金旺达机电有限公司100%股权，交易价格不超过5.5亿元。标的公司生产基地位于东莞市，专注于精密传动功能部件领域生产制造，核心产品包括精密直线导轨、精密滚珠丝杠、精密行星滚柱丝杠、精密减速机、KKR钢基模组、GTHA内嵌式铝基模组、铝基丝杠模组等。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>sz000530</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>冰山冷热</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>液冷+冰雪产业|1.公司拥有数据中心相应的冷热解决方案。
-2.子公司冰山工程近年来承接了多项代表性工程，包括广州融创茂室内滑雪场项目、上海之星室内综合性冰雪场馆、陕西国际体育之窗等多个商业冰雪场馆项目。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>液冷, 冰雪产业</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>sh600825</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>新华传媒</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>10.0145</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>并购重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>sh600281</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>华阳新材</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>9.9156</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>稀土|子公司太原华盛丰贵金属材料有限公司经营范围包含铂、钯、铑、银、镍贵金属系列催化剂、催化网及稀土高磁性材料的回收利用、加工、研究、生产、销售及技术服务。</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>稀土</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>sh600418</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>9.9803</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>汽车整车|公司是一家集全系列商用车、乘用车及动力总成等研产销和服务于一体,“先进节能汽车、新能源汽车、智能网联汽车”并举的综合型汽车企业集团。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>汽车整车</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>sz001225</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>和泰机电</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>机器人|公司通过持续实施自动化、智能化改造，更新迭代生产设备，在物料输送设备制造领域的生产工艺已相对成熟，应用了机器人自动焊接技术，机器人视觉识别自动上下料、自动装箱等技术。</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>sz003029</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>吉大正元</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>10.0165</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>数字货币+网络安全|1.1.公司积极关注数字货币的发展趋势，持续推进面向数字货币的新业务应用及技术研究项目，为数字货币提供可信安全支撑。
-2.公司为央行、国有银行等金融机构提供信息PKI密码安全基础设施、身份安全、数据保护、签验等产品、技术及解决方案，公司积极关注数字货币的发展趋势，持续推进面向数字货币的新业务应用及技术研究项目，为数字货币提供可信安全支撑。</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>数字货币, 网络安全</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>sz002103</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>广博股份</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>9.970700000000001</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>文具|公司文教办公用品业务主要包括时尚办公文具、文创生活以及办公直销三大品类。公司电商板块持续推动数智化营销。组建完成Kinbor私域营销团队，策略性调整淘宝天猫店运营方向以学生文创方面转型。Fizz板块通过开发设计以轻松办公为主题系列的产品，主打高端文具产品市场，持续将时尚元素融入办公用品。</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>文具</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>sz002836</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>新宏泽</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>10.0279</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>烟标|公司系专业烟标印刷服务供应商，主营业务为烟标的设计、生产及销售。</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>烟标</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>sh600668</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>尖峰集团</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>10.0551</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>创新药|尖峰药业及其下属控股子公司在研抗肿瘤新药主要有JFAN-1001。</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>创新药</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>sh603690</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>至纯科技</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>23.77</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>9.9954</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>半导体设备|公司是国内主流气体化学品相关的高纯工艺系统及半导体装备的合格供应商，高纯工艺系统产品主要包括气体高纯工艺设备及系统、化学品高纯工艺设备及系统以及物料及水系统。</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>半导体设备</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr"/>
-      <c r="D35" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>sh605003</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>众望布艺</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>25.96</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>纺织|公司主营业务为中高档装饰面料及制品的研发、设计、生产与销售。</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>纺织</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>sz002543</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>万和电气</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>10.0559</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>热泵|公司是国内热水器行业龙头企业，拥有产品、渠道与品牌优势，空气能热泵业务发展潜力大。子公司广东万和新能源科技有限公司负责空气能热泵相关业务。</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>热泵</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>sz002945</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>华林证券</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>10.0071</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>券商|西藏地区唯一一家上市券商，主要通过总部以及下属分支机构从事财富管理、投资银行、资产管理以及自营业务等，通过全资子公司从事另类投资业务、私募股权投资业务。</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>券商</t>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>sh600319</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>亚星化学</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>10.0478</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>化工|公司主营氯化聚乙烯（CPE）、离子膜烧碱、水合肼、ADC发泡剂等高科技化学产品，同时从事新型化学材料的开发和研究，是目前世界上最主要的含氯聚合物研发生产企业。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
         </is>
       </c>
     </row>
@@ -2215,7 +3351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2242,31 +3378,31 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sz002696</t>
+          <t>sh600825</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>新华传媒</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz002343</t>
+          <t>sz000530</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>慈文传媒</t>
+          <t>冰山冷热</t>
         </is>
       </c>
     </row>
@@ -2276,27 +3412,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz000530</t>
+          <t>sh601811</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>新华文轩</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz001318</t>
+          <t>sz002889</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>阳光乳业</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
     </row>
@@ -2306,12 +3442,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh605189</t>
+          <t>sz003029</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>富春染织</t>
+          <t>吉大正元</t>
         </is>
       </c>
     </row>
@@ -2321,12 +3457,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sh600668</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>尖峰集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>sh603999</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>读者传媒</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="111" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="101" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="240" customWidth="1" min="10" max="10"/>
+    <col width="282" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,459 +552,463 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.7181</v>
+        <v>0.8078</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>央视新闻报道，10月15日从市场监管总局获悉，我国首批六项人形机器人领域国家标准已正式批准发布，将于2027年4月1日起正式实施。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz002949</t>
+          <t>sh600860</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>华阳国际</t>
+          <t>京城股份</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>14.14</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.0389</v>
+        <v>9.987400000000001</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>基建+低空经济|1.公司一直从事建筑设计和研发及其延伸业务，拥有建筑行业（建筑工程）甲级资质、工程造价咨询甲级资质、建筑工程施工总承包一级和市政公用工程施工总承包二级资质。
-2.公司涉及低空经济的业务主要是关于航空小镇的规划设计，目前已承接江西共青城环南湖、辽宁太平湾规划设计项目。</t>
+          <t>碳纤维+机器人|1.公司已经完全掌握了70MPa的铝合金内胆碳纤维缠绕气瓶的技术。
+2.2.公司持有北洋天青80.00%的股权，北洋天青立足于家电和3C行业，是一家生产线的智能化升级改造行业解决方案提供商，为制造企业提供基于云端、算法驱动、灵活可配置的多平台实时协同系统，搭配机器人应用、自动化设备、智能物流等硬件设施。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>基建, 低空经济</t>
+          <t>碳纤维, 机器人</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.7181</v>
+        <v>0.8078</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>央视新闻报道，10月15日从市场监管总局获悉，我国首批六项人形机器人领域国家标准已正式批准发布，将于2027年4月1日起正式实施。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh603197</t>
+          <t>sh603278</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>保隆科技</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>29.39</v>
+        <v>10.9</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.9925</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+        <v>9.9899</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>低空经济|公司的空气弹簧和双目立体视觉摄像头已获得头部新势力车企的飞行汽车项目定点。</t>
+          <t>商业航天+机器人|1.公司投资联营企业湖北三江航天江北机械工程有限公司金额为6405.04万。湖北三江航天江北机械工程有限公司主要从事航天动力系统、天线罩等航天型号产品及特种压力容器产品等民用产品的研发生产。
+2.公司关注到近期市场上公司还涉及“人形机器人概念股”相关内容。公司现有主营业务仍以胎圈钢丝、钢帘线以及胶管钢丝的研发、生产和销售为主，公司机器人腱绳产品目前尚未批量生产，未产生实质性收益，且公司相关业务未来在技术研发、产品竞争能力、盈利能力等方面存在重大不确定性。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>商业航天, 机器人</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.7181</v>
+        <v>0.8078</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>央视新闻报道，10月15日从市场监管总局获悉，我国首批六项人形机器人领域国家标准已正式批准发布，将于2027年4月1日起正式实施。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sz002085</t>
+          <t>sh605488</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>万丰奥威</t>
+          <t>福莱新材</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>9.91</v>
+        <v>28.17</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.988900000000001</v>
+        <v>9.9961</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>低空经济|公司子公司万丰飞机与全球某知名主机厂已达成战略合作，拟在eVTOL原型机开发、电池系统、工业设计、航空工程、模具及工装制造、供应链及大规模量产、航空适航认证、品牌力和B2C/B2B销售和售后网络资源等领域深度合作并为合资公司提供支持。公司钻石eDA40纯电动飞机已成功首飞。</t>
+          <t>机器人|2024年12月26日公司在互动平台表示，柔性传感器是相对前沿技术的应用，未来的应用场景广泛，公司从当前的整体定位去看，主要有以下几个方向：人形机器人电子皮肤的应用、工业检测应用、智能穿戴、健康监测等领域，公司目前在和一些公司合作研发。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.7181</v>
+        <v>0.8078</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>央视新闻报道，10月15日从市场监管总局获悉，我国首批六项人形机器人领域国家标准已正式批准发布，将于2027年4月1日起正式实施。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz002869</t>
+          <t>sh603626</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>金溢科技</t>
+          <t>科森科技</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20.58</v>
+        <v>22.21</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9.9947</v>
+        <v>10.005</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>低空智联产品|公司低空智联产品线深耕“高速+低空”特色垂直场景，依托自身在智能交通领域沉淀的融合感知、AI识别、车路通信核心技术，将机器视觉、物联网技术跨界迁移至无人机领域，打造“自动机场+无人机+AI”一体化智能巡检与监测解决方案，精准赋能交通、应急、工程、政务等多行业数字化、智能化升级。</t>
+          <t>机器人+折叠屏|1.公司不生产机器人产品，公司为某品牌家用机器人提供相关结构件。
+2.公司生产的折叠屏手机铰链已量产。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>低空智联产品</t>
+          <t>机器人, 折叠屏</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2.7181</v>
+        <v>0.8078</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>央视新闻报道，10月15日从市场监管总局获悉，我国首批六项人形机器人领域国家标准已正式批准发布，将于2027年4月1日起正式实施。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz300411</t>
+          <t>sz002164</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>金盾股份</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>9.6</v>
+        <v>14.69</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20</v>
+        <v>10.0375</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>军工+低空经济|1.公司旗下全资子公司中强科技主要从事军用隐身材料、伪装网（遮障）、伪装涂料和重防腐涂料等产品的研发、生产、销售和技术服务。
-2.2024年1月12日公司在互动平台表示，公司已经跟清华大学合作完成飞行汽车叶轮的样机研发，目前正在推动项目的产业化。</t>
+          <t>机器人+风电|1.公司的产品包括行星减速器等，杭州湾电机、减速器部分车间已投入生产。
+2.公司研发的风电齿轮箱应用于风电市场。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>军工, 低空经济</t>
+          <t>机器人, 风电</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.7181</v>
+        <v>0.8078</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>央视新闻报道，10月15日从市场监管总局获悉，我国首批六项人形机器人领域国家标准已正式批准发布，将于2027年4月1日起正式实施。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz001696</t>
+          <t>sz301119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>宗申动力</t>
+          <t>正强股份</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15.87</v>
+        <v>34.31</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9.979200000000001</v>
+        <v>20.007</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>低空经济+商业航天|1.公司是国内专业化小型热动力机械产品制造基地之一，子公司航发公司主要聚焦无人机及通航有人飞机动力领域，已取得关键突破和一定的市场覆盖；公司在＂发动机+”业务方面，已开始参与某型飞机配套项目科研。
-2.参股子公司航天神舟飞行器公司业务性质为航空航天和其他运输设备制造业。</t>
+          <t>机器人|公司围绕机器人关节模组、精密传动部件等核心环节持续投入，目前已实现送样验证到小批量供货的实质性推进。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>低空经济, 商业航天</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.7181</v>
+        <v>0.8078</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>央视新闻报道，10月15日从市场监管总局获悉，我国首批六项人形机器人领域国家标准已正式批准发布，将于2027年4月1日起正式实施。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>920690.BJ</t>
+          <t>sh603040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>捷众科技</t>
+          <t xml:space="preserve">新坐标  </t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>19.24</v>
+        <v>40.6</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>30</v>
+        <v>9.997300000000001</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>低空经济+机器人|1.公司核心产品精密注塑齿轮将应用于小鹏汇天飞行汽车上。
-2.2.公司与杭州云深处科技股份有限公司达成深度合作，正式签订产品开发协议，共同推进机器人轻量化升级、有效降低生产成本，努力实现核心部件“以塑代钢”的技术突破，双方将联合研发适用于人形机器人及四足机器人关节部位的专用齿轮，助力机器人核心零部件性能与成本优势的双重提升。</t>
+          <t>机器人|2025年4月28日公告，公司拟与陀曼智能、孙立松共同出资设立杭州九月八精密传动科技有限公司，研发、生产和销售滚柱丝杠、滚珠丝杠等精密传动零部件。公司认缴出资人民币7700万元，持有标的公司77%股权。设立合资公司与公司的业务及战略规划相匹配，有利于提升公司的综合竞争力和优化业务结构。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>低空经济, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.7181</v>
+        <v>0.8078</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>央视新闻报道，10月15日从市场监管总局获悉，我国首批六项人形机器人领域国家标准已正式批准发布，将于2027年4月1日起正式实施。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz002510</t>
+          <t>sh603286</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>天汽模</t>
+          <t>日盈电子</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>5.96</v>
+        <v>42.74</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9.963099999999999</v>
+        <v>10.0129</v>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>低空经济|在低空经济领域，公司持续发力通用航空市场，成为小鹏汇天陆地航母Evtol机型、通航国际LE700机型、冠一航空GA20机型项目定点供应商。</t>
+          <t>机器人|公司看好汽车零部件企业进军人形机器人领域的产业机遇，积极投入以柔性触觉传感电子皮肤为代表的新产品开发，公司压阻式的电子皮肤样品已研发成功。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.7181</v>
+        <v>0.8078</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>央视新闻报道，10月15日从市场监管总局获悉，我国首批六项人形机器人领域国家标准已正式批准发布，将于2027年4月1日起正式实施。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz001319</t>
+          <t>sh603119</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>铭科精技</t>
+          <t>浙江荣泰</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>21.4</v>
+        <v>45.87</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.0257</v>
+        <v>10</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>低空经济+机器人|1.公司已承接小鹏汇天飞行汽车产品部分模具及零部件的生产交付。
-2.2024年9月12日公司在互动平台表示，近期在东莞市塘厦镇拿地新建相关产业项目，该项目建成后主要涉及到汽车五金模具、汽车零部件及人形机器人机械手臂总成等业务，项目建设周期为两年左右。</t>
+          <t>机器人|2025年6月25日公告，公司与广东金力智能传动技术股份有限公司及其股东吕志峰、黎冬阳签署《意向协议书》，拟通过股份转让和增资的方式合计持有金力传动不低于15%的股份。目标公司在微型智能传动产品的研发和生产领域具有较高的知名度和影响力，具有较强的自主研发能力和行业竞争实力，有助于公司快速进入智能传动、人形机器人等新兴领域。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>低空经济, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2.7181</v>
+        <v>0.8078</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>央视新闻报道，10月15日从市场监管总局获悉，我国首批六项人形机器人领域国家标准已正式批准发布，将于2027年4月1日起正式实施。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz000099</t>
+          <t>sz003021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>中信海直</t>
+          <t>兆威机电</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>14.75</v>
+        <v>67.22</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9.9925</v>
+        <v>9.9984</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>低空经济|公司具有通用航空全业务运营的资质和能力，低空飞行方面，公司开通观光、短途运输等业务，已有深圳城际观光，深圳—珠海、舟山—东极岛、深圳—金沙湾等摆渡飞行航线。公司与腾讯投资的德国eVTOL企业Lilium有合作，计划建立eVTOL运营网络，包括战略性生产基地、试飞、售后服务。</t>
+          <t>机器人+消费电子|1.公司聚焦手指等运动执行应用部位，开发仿生机器人灵巧手产品，该产品与公司的技术能力相契合,系公司未来平台化产品的重点布局。
+2.公司的微型传动系统可以应用于AR/VR领域，具体如磁感应系统、瞳距调节驱动系统、头部自动松紧装置、智能眼镜隐藏式微型扬声器等。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>机器人, 消费电子</t>
         </is>
       </c>
     </row>
@@ -1015,41 +1019,46 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2.7181</v>
+        <v>-0.168</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>北京时间10月16日，特斯拉发布第二代Roadster跑车，预计2028年开启交付。发布会直播中，新车型可借助推进器及大功率风扇等装置，展示了倒置坡道行驶、短暂腾空及空中旋转等动作。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh600178</t>
+          <t>sz003029</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东安动力</t>
+          <t>吉大正元</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>10.25</v>
+        <v>24.19</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>9.9785</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+        <v>10.0045</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>低空经济|2024年9月11日公司官微透露，东安动力高效增程发动机搭载小鹏汇天飞行汽车量产启动，此款产品为全球唯一能装下“飞机”的汽车提供“移动超充”，将成为公司市场开拓新的发力点。</t>
+          <t>低空经济+网络安全|1.2024年5月21日公司在互动平台表示，公司在载人航天、卫星通信等相关领域的技术和项目经验可以成功应用于低空经济相关的商业航天、卫星互联网、低空飞行、低空通信等领域。
+2.公司为央行、国有银行等金融机构提供信息PKI密码安全基础设施、身份安全、数据保护、签验等产品、技术及解决方案，公司积极关注数字货币的发展趋势，持续推进面向数字货币的新业务应用及技术研究项目，为数字货币提供可信安全支撑。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>低空经济, 网络安全</t>
         </is>
       </c>
     </row>
@@ -1060,41 +1069,45 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.7181</v>
+        <v>-0.168</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>北京时间10月16日，特斯拉发布第二代Roadster跑车，预计2028年开启交付。发布会直播中，新车型可借助推进器及大功率风扇等装置，展示了倒置坡道行驶、短暂腾空及空中旋转等动作。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603348</t>
+          <t>sh603197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>文灿股份</t>
+          <t>保隆科技</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>15.31</v>
+        <v>32.33</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9.9856</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+        <v>10.0034</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>低空经济|公司已获得某飞行汽车的相关铝合金零部件定点。</t>
+          <t>飞行汽车|公司的空气弹簧和双目立体视觉摄像头已获得头部新势力车企的飞行汽车项目定点。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>飞行汽车</t>
         </is>
       </c>
     </row>
@@ -1105,41 +1118,45 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2.7181</v>
+        <v>-0.168</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>北京时间10月16日，特斯拉发布第二代Roadster跑车，预计2028年开启交付。发布会直播中，新车型可借助推进器及大功率风扇等装置，展示了倒置坡道行驶、短暂腾空及空中旋转等动作。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz300045</t>
+          <t>sh600178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>华力创通</t>
+          <t>东安动力</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>12.7</v>
+        <v>11.28</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>20.0378</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+        <v>10.0488</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>低空经济|上海子公司依托公司卫星通信、卫星导航、航电系统、无人系统等既有核心技术，重点拓展长三角地区民用航空、低空经济、商业航天配套等行业市场。</t>
+          <t>飞行汽车|2024年9月11日公司官微透露，东安动力高效增程发动机搭载小鹏汇天飞行汽车量产启动，此款产品为全球唯一能装下“飞机”的汽车提供“移动超充”，将成为公司市场开拓新的发力点。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>飞行汽车</t>
         </is>
       </c>
     </row>
@@ -1150,42 +1167,45 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2.7181</v>
+        <v>-0.168</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>北京时间10月16日，特斯拉发布第二代Roadster跑车，预计2028年开启交付。发布会直播中，新车型可借助推进器及大功率风扇等装置，展示了倒置坡道行驶、短暂腾空及空中旋转等动作。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh603239</t>
+          <t>sh603348</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>浙江仙通</t>
+          <t>文灿股份</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>14.43</v>
+        <v>16.84</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9.9848</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
+        <v>9.993499999999999</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>低空经济+机器人|1.公司能够为飞行汽车提供密封条。
-2.2025年9月25日公告，公司拟以4000万元对浩海星空进行增资，投资完成后持有浩海星空10%的股份。增资完成后，公司与浩海星空拟出资设立合资公司，合资公司由浙江仙通控股，注册在浙江省台州市仙居县，合资公司注册资本2000万元人民币，其中公司认缴出资1020万元，占注册资本的51%。本次合作事项为机器人业务相关。</t>
+          <t>飞行汽车|公司已获得某飞行汽车的相关铝合金零部件定点。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>低空经济, 机器人</t>
+          <t>飞行汽车</t>
         </is>
       </c>
     </row>
@@ -1196,41 +1216,45 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2.7181</v>
+        <v>-0.168</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>北京时间10月16日，特斯拉发布第二代Roadster跑车，预计2028年开启交付。发布会直播中，新车型可借助推进器及大功率风扇等装置，展示了倒置坡道行驶、短暂腾空及空中旋转等动作。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz300681</t>
+          <t>sz002085</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>英搏尔</t>
+          <t>万丰奥威</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>20.84</v>
+        <v>10.9</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>19.977</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+        <v>9.9899</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>低空经济|2025年1月8日公告，公司与亿航智能拟共同设立合资公司，投资额为1000万元，其中英搏尔出资600万元，持股60%，亿航智能出资400万元，持股40%。合资公司将围绕eVTOL产品生产制造以及上游零部件产业链展开深入合作。</t>
+          <t>飞行汽车|公司子公司万丰飞机与全球某知名主机厂已达成战略合作，拟在eVTOL原型机开发、电池系统、工业设计、航空工程、模具及工装制造、供应链及大规模量产、航空适航认证、品牌力和B2C/B2B销售和售后网络资源等领域深度合作并为合资公司提供支持。公司钻石eDA40纯电动飞机已成功首飞。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>飞行汽车</t>
         </is>
       </c>
     </row>
@@ -1241,2102 +1265,1519 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.7181</v>
+        <v>-0.168</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>特斯拉周四在美国得克萨斯州麦格雷戈SpaceX测试基地举办Roadster的发布会，这是该公司首款可实现自主升空并控制姿态的量产乘用车。</t>
+          <t>北京时间10月16日，特斯拉发布第二代Roadster跑车，预计2028年开启交付。发布会直播中，新车型可借助推进器及大功率风扇等装置，展示了倒置坡道行驶、短暂腾空及空中旋转等动作。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz301586</t>
+          <t>sh600686</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>佳力奇</t>
+          <t>金龙汽车</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>33</v>
+        <v>10.35</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>20</v>
+        <v>9.9894</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>低空经济|公司专注于航空复材零部件的研发、生产、销售及相关服务，已于2022年与广东汇天航空航天科技有限公司签署《技术开发合同》，并形成销售收入。</t>
+          <t>福建+低空经济|公司与云端无人机签署技术开发合作协议，共同研发一款适用于主流无人机起降的车顶机场模块，包含车顶机场内部结构、自动充电、定位、视觉模块，无人机随车跟随、车顶机场与无人机的通信系统等。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>低空经济</t>
+          <t>福建, 低空经济</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2.492</v>
+        <v>-0.2773</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+          <t>截至10月15日，A股已有16家PCB概念股发布2026年三季度业绩预告，其中14家预增、2家略增，预喜率达到100%。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz002917</t>
+          <t>sh605058</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>金奥博</t>
+          <t>澳弘电子</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>11.98</v>
+        <v>72.41</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.0092</v>
+        <v>9.9954</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4天3板</t>
+          <t>21天12板</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>并购重组+军工|金奥博公告称，公司拟通过现金方式收购长春汇维科技股份有限公司80%股权，以取得目标公司的控股权。本次交易完成后，公司将在现有业务基础上，进一步拓展军工装备领域相关业务布局。</t>
+          <t>PCB|公司业务以印制电路板的研发、生产和销售为主，打造了覆盖多元化应用场景的差异化产品矩阵，从传统的单面板、双面板、多层板、金属基板扩展出更多符合客户新需求的埋铜块板、铝基盲孔板、HDI板、塞铜浆板、MINILED板、热电分离铜基板、多层陶瓷板等。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>并购重组, 军工</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2.492</v>
+        <v>-0.2773</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+          <t>截至10月15日，A股已有16家PCB概念股发布2026年三季度业绩预告，其中14家预增、2家略增，预喜率达到100%。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh601606</t>
+          <t>sz301591</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>长城军工</t>
+          <t>肯特股份</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>31.92</v>
+        <v>47.47</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.9931</v>
+        <v>19.9949</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>军工|公司为控股型公司，主营业务均通过子公司开展，以军品业务为主，下属四家军品子公司神剑科技、方圆机电、东风机电、红星机电均属重点军工企业，并在其对应领域占据重要地位，主要从事迫击炮弹系列、光电对抗系列、单兵火箭系列、引信系列、子弹药系列、火工品系列等产品的研发、生产和销售。</t>
+          <t>PTFE|公司四氟膜产品可应用于PCB覆铜板，代表客户有生益科技等。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>PTFE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2.492</v>
+        <v>-0.2773</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+          <t>截至10月15日，A股已有16家PCB概念股发布2026年三季度业绩预告，其中14家预增、2家略增，预喜率达到100%。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz300581</t>
+          <t>sh605258</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>晨曦航空</t>
+          <t>协和电子</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>11.81</v>
+        <v>42.9</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>20.0203</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>军工|公司是国内少数同时拥有航空技术信息化中最关键的导航、控制、通讯、（航空）计算机等核心技术的企业，主要产品均为军品，最终用户为国内军方，涉及航空惯性导航、航空发动机电子及无人机领域。</t>
+          <t>PCB|公司主要从事印制电路板的研发、生产、销售以及SMT业务，PCB产品主要应用在汽车电子和高频通讯领域。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2.492</v>
+        <v>-0.2773</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+          <t>截至10月15日，A股已有16家PCB概念股发布2026年三季度业绩预告，其中14家预增、2家略增，预喜率达到100%。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz002683</t>
+          <t>sz002886</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>广东宏大</t>
+          <t>沃特股份</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>27.9</v>
+        <v>24.01</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.0158</v>
+        <v>9.9863</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>军工|公司拥有军工“三证”、是全国保留军工能力的十四家地方军工企业之一，公司以子公司广东明华机械有限公司为实施平台，孵化多个前瞻性军工项目研发平台。广东宏大曾携自主研发的HD-1A超声速巡航导弹武器系统参加珠海航展。</t>
+          <t>PTFE|公司PTFE薄膜和ePTFE薄膜能够满足下游PCB行业客户需求。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>PTFE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2.492</v>
+        <v>-0.2773</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+          <t>截至10月15日，A股已有16家PCB概念股发布2026年三季度业绩预告，其中14家预增、2家略增，预喜率达到100%。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz002933</t>
+          <t>sz300852</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>新兴装备</t>
+          <t>四会富仕</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>27.75</v>
+        <v>76.94</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.988099999999999</v>
+        <v>19.9938</v>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>机器人+军工|1.公司的伺服控制等技术可以应用到人形机器人旋转、直行关节上，目前正在进行相关产品的研发工作。
-2.公司是军工领域高端装备制造的高新技术企业，主营业务是以伺服控制技术为核心的航空装备产品的研发、生产、销售及相关服务。</t>
+          <t>业绩+PCB|四会富仕公告称，第三季度营收为8.57亿元，同比增长59.78%；净利润为1.76亿元，同比增长217.22%。前三季度营收为20.90亿元，同比增长49.68%；净利润为2.64亿元，同比增长101.67%。业绩增长主要是工业控制、汽车电子、以及通讯领域订单增长所致。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>机器人, 军工</t>
+          <t>业绩, PCB</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>物理AI</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2.492</v>
+        <v>5.6256</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
+          <t>当地时间10月20日至22日，英伟达GTC大会将在德国柏林举行，据官方介绍，大会将聚焦加速计算、智能体AI、物理AI、机器人、开源模型、AI基础设施等方向。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz000576</t>
+          <t>sh603859</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>甘化科工</t>
+          <t>能科科技</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>8.77</v>
+        <v>38.82</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.0376</v>
+        <v>10.0028</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
+          <t>物流AI|公司精准卡位具身智能“大脑”角色，构建起从“感知—决策—执行—评估”的物理AI全链条能力，成功打造可独立运行的“端侧单体大脑”，实现在工业及特种场景下的深度应用，并逐步建立本体小脑到应用大脑的中间层链接标准。</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>物流AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>5.6256</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>当地时间10月20日至22日，英伟达GTC大会将在德国柏林举行，据官方介绍，大会将聚焦加速计算、智能体AI、物理AI、机器人、开源模型、AI基础设施等方向。</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>sz301313</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>凡拓数创</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>物理AI|公司形成了以数字孪生引擎、低代码平台、AI算法、行业小模型、IoT、大数据、知识图谱、物理AI工具链为核心的完整技术底座，并构建起“物理AI 3D数字孪生”核心技术体系。</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>5.6256</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>当地时间10月20日至22日，英伟达GTC大会将在德国柏林举行，据官方介绍，大会将聚焦加速计算、智能体AI、物理AI、机器人、开源模型、AI基础设施等方向。</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>sh688507</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>索辰科技</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>19.9967</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>物理AI|公司物理AI聚焦于多物理场仿真、物理规律驱动的智能体训练及行业级应用，面向新能源电池、具身智能、低空经济等领域的虚拟训练，具备自主可控、安全可定制等优势。</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>0.5539999999999999</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>据报道，10月19日珠海航展门票正式开售，本次航展首次开放海上展区，包括海上装备、无人机在内的一批新装备、新技术将集中亮相。</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>sz002724</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>海洋王</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>10.0654</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>军工|公司是武器装备科研生产三级保密资格单位，设有专门的军品事业部负责军品的销售。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>0.5539999999999999</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>据报道，10月19日珠海航展门票正式开售，本次航展首次开放海上展区，包括海上装备、无人机在内的一批新装备、新技术将集中亮相。</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>sh600148</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>长春一东</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>10.0123</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>军工央企|公司控股股东是中国兵器工业集团子公司东北工业集团旗下吉林东光集团，公司主要从事汽车离合器及液压举升机构等汽车零部件的研发、生产与销售。</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>军工央企</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.5539999999999999</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>据报道，10月19日珠海航展门票正式开售，本次航展首次开放海上展区，包括海上装备、无人机在内的一批新装备、新技术将集中亮相。</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>sz000576</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>甘化科工</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>10.0342</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>军工+半导体|1.公司通过收购沈阳含能控股权和升华电源100%股权新增军工业务板块。升华电源主要产品服务于机载、舰载、弹载等多种武器平台，主要客户涵盖国内知名军工企业、军工科研院所、军工厂等。
 2.公司参股公司锴威特半导体专注于智能功率器件与功率集成芯片的研发、生产和销售。</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>军工, 半导体</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>2.492</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>sh600148</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>长春一东</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>16.28</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>军工央企|公司控股股东是中国兵器工业集团子公司东北工业集团旗下吉林东光集团，公司主要从事汽车离合器及液压举升机构等汽车零部件的研发、生产与销售。</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>军工央企</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>2.492</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>sz002535</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>林州重机</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>9.9567</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>军工+机器人|1.公司与多家大型军工集团建立了合作关系，并承接、交付了多批次的订单。
-2.公司曾于14年定增募资1.02亿元用于工业机器人产业化（一期）项目。</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>军工, 机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>2.492</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>sh600501</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>航天晨光</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>9.971299999999999</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>军工+商业航天|1.中国航天科工集团旗下上市公司，军工及核非标设备与服务板块主营产品有军用特种油料装备(各型加油车、泵站方舱、加油装置)、飞机加油车、测控惯导设备、核电“三废”处理设备及相关服务等。
-2.公司作为中国航天型号产品用金属软管的定点研制生产单位，陆续为国家多项航天工程提供配套产品。</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>军工, 商业航天</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>2.492</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>sz002724</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>海洋王</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>10.0719</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>军工|公司是武器装备科研生产三级保密资格单位，设有专门的军品事业部负责军品的销售。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>2.492</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>第十六届中国国际航空航天博览会将于2026年12月7日至13日在广东珠海举办。本届航展展览规模再创新高、国际合作广度持续拓展、展演维度加快延伸，中国空军、海军多型新型装备将同台亮相。</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>920006.BJ</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>晟楠科技</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>22.46</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>29.9769</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>军工|公司主要从事航空装备制造、军用电源领域相关产品的研发、生产和销售。主要产品包括航空减速控制器、航空阻尼器等航空机械类产品以及变压整流器、继电器盒等综合电源类产品等。公司产品应用于军用飞机、车辆、电子设备。</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.076</v>
+        <v>0.5316000000000001</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>10月12日晚间，新剑传动发布了创业板上市审核问询函的回复文件，系统梳理了其与特斯拉Optimus产业链的合作关系及行业判断。文件中明确：特斯拉Optimus V3的硬件设计方案已基本冻结定型，即将进入量产周期。</t>
+          <t>江苏电力交易中心近日正式印发的《2027年江苏电力零售市场交易工作指引》，其中明确取消固定价格电量比例、现货市场价格联动电量比例、比例分成方式等要求，着力推进电能量价格传导批发市场价格。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh603015</t>
+          <t>sh603693</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>弘讯科技</t>
+          <t>江苏新能</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>10.8</v>
+        <v>13.53</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>9.9796</v>
+        <v>10</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>机器人+核聚变|1.公司积极推进多关节、蜘蛛手即DELTA分拣式机器人等多个成熟产品的销售推广。
-2.在特殊物理专案方面，公司意大利子公司EEI参与的欧洲主导之跨国人造太阳项目（FusionforEnergy，F4E）。</t>
+          <t>绿电|公司的主营业务为新能源发电项目的投资开发、建设运营及电力销售，目前主要包括风能发电、生物质能发电和光伏发电三个板块。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>机器人, 核聚变</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1.076</v>
+        <v>0.5316000000000001</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10月12日晚间，新剑传动发布了创业板上市审核问询函的回复文件，系统梳理了其与特斯拉Optimus产业链的合作关系及行业判断。文件中明确：特斯拉Optimus V3的硬件设计方案已基本冻结定型，即将进入量产周期。</t>
+          <t>江苏电力交易中心近日正式印发的《2027年江苏电力零售市场交易工作指引》，其中明确取消固定价格电量比例、现货市场价格联动电量比例、比例分成方式等要求，着力推进电能量价格传导批发市场价格。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz002614</t>
+          <t>sh600032</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>奥佳华</t>
+          <t>浙江新能</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>8.77</v>
+        <v>7.79</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.0376</v>
+        <v>10.0282</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>福建+机器人|公司AI按摩机器人2.0（OG-8598Plus），已实现服务功能与产品有机结合，运用人脸识别、疲感侦测、“千人千方”智能AI算法、云端个人健康数据库、新一代4D无刷变频温感机芯等新技术构建围绕用户健康的检测-分析-调理闭环服务系统，关注每一位用户的健康状态，为用户远程推送“量身定制”的专属按摩解决方案，构建家庭健康管理服务生态。</t>
+          <t>绿电|公司的主营业务为水力发电、光伏发电、风力发电等可再生能源项目的投资、开发、建设和运营管理。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>福建, 机器人</t>
+          <t>绿电</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1.076</v>
+        <v>0.5316000000000001</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10月12日晚间，新剑传动发布了创业板上市审核问询函的回复文件，系统梳理了其与特斯拉Optimus产业链的合作关系及行业判断。文件中明确：特斯拉Optimus V3的硬件设计方案已基本冻结定型，即将进入量产周期。</t>
+          <t>江苏电力交易中心近日正式印发的《2027年江苏电力零售市场交易工作指引》，其中明确取消固定价格电量比例、现货市场价格联动电量比例、比例分成方式等要求，着力推进电能量价格传导批发市场价格。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh603305</t>
+          <t>sh601778</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>旭升集团</t>
+          <t>晶科科技</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>10.88</v>
+        <v>3.58</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.0101</v>
+        <v>10.1538</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司目前已组建全新的系统集成事业部，对新能源汽车被动安全系统、铝合金底盘系统、新能源储能系统及智能机器人轻量化骨架等进行前沿研发。</t>
+          <t>算电协同|公司与中卫市人民政府签署《投资协议》，就宁夏中卫1GW算力中心项目达成合作意向。该项目计划总投资约245亿元，占地约800亩，计划部署机柜约5万架，分三期建设。公司作为投资主体，将牵头推进前期工作并引入战略合作方共同投资。本项目旨在构建“新能源+算力”算电协同生态，推动公司向绿色算力与综合能源服务商转型。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>算电协同</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1.076</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>10月12日晚间，新剑传动发布了创业板上市审核问询函的回复文件，系统梳理了其与特斯拉Optimus产业链的合作关系及行业判断。文件中明确：特斯拉Optimus V3的硬件设计方案已基本冻结定型，即将进入量产周期。</t>
+          <t>据巴克莱最新报告，10月份DDR5内存现货价格环比上涨8%，三个月内上涨20%。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh600699</t>
+          <t>sz002889</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>均胜电子</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>20.3</v>
+        <v>15.74</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.0271</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
+        <v>9.993</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>机器人+智能驾驶|1.公司定位“汽车+机器人Tier1”，全面布局人形机器人领域，向包括全球车企在内的具身智能机器人相关公司提供软硬件及解决方案。
-2.公司与大唐集团旗下的辰芯科技签署战略合作协议，联手发力汽车智能车联技术，打造新一代TBOX和V2X车用电子产品。</t>
+          <t>光刻机+物流|1.公司将与国际头部芯片光刻机厂商合作，共同在深圳建设寄售维修保税仓库，为华南片区集成电路制造企业提供全天候快速响应的光刻机寄售维修服务。
+2.公司业务主要是基于全球中心仓提供供应链一体化服务，以及销售商品。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>机器人, 智能驾驶</t>
+          <t>光刻机, 物流</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1.076</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>10月12日晚间，新剑传动发布了创业板上市审核问询函的回复文件，系统梳理了其与特斯拉Optimus产业链的合作关系及行业判断。文件中明确：特斯拉Optimus V3的硬件设计方案已基本冻结定型，即将进入量产周期。</t>
+          <t>据巴克莱最新报告，10月份DDR5内存现货价格环比上涨8%，三个月内上涨20%。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz000887</t>
+          <t>sz301666</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>中鼎股份</t>
+          <t>大普微-UW</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>17.72</v>
+        <v>328.51</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>9.9938</v>
+        <v>19.9993</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>机器人+液冷|1.中鼎股份公告称，公司与众擎机器人为加强双方合作关系，围绕人形机器人相关产品展开合作，于近日签署了战略合作协议。
-2.子公司中鼎流体及中鼎智能热系统主导热管理系统总成业务的发展，在汽车热管理业务基础上积极布局储能热管理及超算中心热管理。基于自研热管理控制器及控制算法，管路系统及密封等核心技术，公司在储能领域已推出系列化液冷机组，及浸没式液冷机组；超算中心热管理领域主要产品为CDU（冷液分配装置）。</t>
+          <t>存储芯片|大普微是国内领先的本土企业级SSD供应商，公司客户包括Google、Nvidia、xAI、字节跳动、腾讯、阿里巴巴、京东、百度、美团、快手、Deepseek、小红书、滴滴等知名企业。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>机器人, 液冷</t>
+          <t>存储芯片</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>碳纤维</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3.5016</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>特斯拉新款Roadster跑车亮相，据介绍车辆使用镁、钛和碳纤维等轻质高强度材料降低整车质量。</t>
+          <t>据巴克莱最新报告，10月份DDR5内存现货价格环比上涨8%，三个月内上涨20%。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh600860</t>
+          <t>sh605255</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>京城股份</t>
+          <t>天普股份</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7.91</v>
+        <v>55.88</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10.0139</v>
+        <v>10</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>碳纤维+机器人|1.公司已经完全掌握了70MPa的铝合金内胆碳纤维缠绕气瓶的技术。
-2.2.公司持有北洋天青80.00%的股权，北洋天青立足于家电和3C行业，是一家生产线的智能化升级改造行业解决方案提供商，为制造企业提供基于云端、算法驱动、灵活可配置的多平台实时协同系统，搭配机器人应用、自动化设备、智能物流等硬件设施。</t>
+          <t>中昊芯英入主|天普股份公告称，中昊芯英要约收购期限届满，预受要约的股东账户总数为3户，预受要约股份总数为201股，占上市公司股份总数的0.00008%。收购完成后，收购人中昊芯英直接持有天普股份1441.38万股股份，占总股本的10.75008%。收购人及其一致行动人直接持有公司2514.02万股股份、通过控制浙江天普控股有限公司间接控制公司6642万股股份，共计控制上市公司9156.02万股股份，占公司总股本的68.28774%。中昊芯英是国内掌握TPU架构训推一体AI芯片核心技术的公司，致力于打造“自研训练芯片+超算集群+预训练大模型”的产业价值链。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>碳纤维, 机器人</t>
+          <t>中昊芯英入主</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>碳纤维</t>
+          <t>染料涂料</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>3.5016</v>
+        <v>1.4568</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>特斯拉新款Roadster跑车亮相，据介绍车辆使用镁、钛和碳纤维等轻质高强度材料降低整车质量。</t>
+          <t>机构研报指出，年初至今，染料上游中间体开启暴涨模式，还原物年内暴涨600%，H酸涨幅也达到275%，成品染料也在同步跟涨。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh600843</t>
+          <t>sh603188</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>上工申贝</t>
+          <t>亚邦股份</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>8.94</v>
+        <v>5.56</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>9.963099999999999</v>
+        <v>10.099</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>碳纤维+低空经济|公司通过下属子公司SGIA完成对美国ICON公司有效资产的购买，ICON公司主要从事设计、生产及销售碳纤维轻型双座运动型飞机。</t>
+          <t>染料|公司主要从事染料及染料中间体的销售与服务，是国内蒽醌结构染料生产专家工厂。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>碳纤维, 低空经济</t>
+          <t>染料</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>碳纤维</t>
+          <t>染料涂料</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>3.5016</v>
+        <v>1.4568</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>特斯拉新款Roadster跑车亮相，据介绍车辆使用镁、钛和碳纤维等轻质高强度材料降低整车质量。</t>
+          <t>机构研报指出，年初至今，染料上游中间体开启暴涨模式，还原物年内暴涨600%，H酸涨幅也达到275%，成品染料也在同步跟涨。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh603013</t>
+          <t>sz300798</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>亚普股份</t>
+          <t>锦鸡股份</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.970700000000001</v>
+        <v>19.9478</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>碳纤维+机器人|1.公司参与制定了3项团体标准，分别是《70MPaIV 型储氢瓶压力容器用高性能碳纤维》《储能电池集成式液冷设备技术规范》和《碳纤维缠绕储氢气瓶无损失效检测方法。
-2.2025年5月28日公告，公司拟以自有资金购买上海飞驰高科技有限公司等11名交易对方持有的上海赢双电机科技股份有限公司约54.50%股份，交易对价约5.78亿元。其产品旋转变压器是高性能电动化的关键核心部件，是节能与新能源汽车、先进轨道交通装备、高档数控机床和机器人的核心基础零部件。</t>
+          <t>染料+算力租赁|1.公司是国内居于行业前列的专业染料生产商，研发技术能力较强，已经形成较大的生产和销售规模，主营业务为染料的研发、生产和销售，主要产品为活性染料，用于纺织品的染色和印花。
+2.公司已经完成了近1600P商业智算设备的购置和算力网络的组网及调测工作，开发上线了算力运营系统平台，已具备从资源保障、到算力网络运营、再到人才储备的完整的算力服务支持体系。公司计划建设具备10000P算力覆盖全国的算力网络。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>碳纤维, 机器人</t>
+          <t>染料, 算力租赁</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>碳纤维</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>3.5016</v>
+        <v>-0.4135</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>特斯拉新款Roadster跑车亮相，据介绍车辆使用镁、钛和碳纤维等轻质高强度材料降低整车质量。</t>
+          <t>机构研报指出，从景气角度看，1.6T即将超大规模上量，NPO、CPO等新方案百花齐放，2027年生态成熟几成定局，行业2028-2030年的景气度可以预见。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz000420</t>
+          <t>sh603330</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>吉林化纤</t>
+          <t>天洋新材</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3.88</v>
+        <v>9.43</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>9.915000000000001</v>
+        <v>10.035</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>碳纤维+低空经济|公司碳纤维下游客户有在汽车领域上应用，飞机领域正在开发。小鹏飞行汽车旅航者X2整机碳纤维零部件均由HRC承制。2022年12月，HRC与吉林化纤签署《战略合作及供货框架协议》。</t>
+          <t>光模块用胶|公司电子胶板块光模块透镜固定用胶、底填胶等产品已经进入半导体及汽车电子领域小批量供货。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>碳纤维, 低空经济</t>
+          <t>光模块用胶</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>光通信</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-0.0587</v>
+        <v>-0.4135</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>早盘韩国股市高开高走，存储芯片龙头SK海力士涨逾3%，三星电子涨近3%。</t>
+          <t>机构研报指出，从景气角度看，1.6T即将超大规模上量，NPO、CPO等新方案百花齐放，2027年生态成熟几成定局，行业2028-2030年的景气度可以预见。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz002889</t>
+          <t>sh600487</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>14.31</v>
+        <v>50.25</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>9.9923</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0044</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>光刻机+物流|1.公司将与国际头部芯片光刻机厂商合作，共同在深圳建设寄售维修保税仓库，为华南片区集成电路制造企业提供全天候快速响应的光刻机寄售维修服务。
-2.公司业务主要是基于全球中心仓提供供应链一体化服务，以及销售商品。</t>
+          <t>业绩+光纤|1.亨通光电公告称，预计2026年前三季度归属于上市公司股东的净利润为59.7亿元-63.7亿元，同比增长151.27%-168.1%。
+2.公司拥有全球光纤通信（光棒-光纤-光缆-光器件-光网络及海洋光网络）、量子通信、数据通信全产业链及自主核心技术，致力于提供光纤光网、量子保密通信、海洋观测网及智慧海洋工程系统解决方案及设计-施工-运维服务为一体的工程EPC总包服务， 目前已形成“产品+平台+服务”综合服务模式，已成为通信产业全价值链综合服务商。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>光刻机, 物流</t>
+          <t>业绩, 光纤</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>数据要素</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-0.0587</v>
+        <v>0.0965</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>早盘韩国股市高开高走，存储芯片龙头SK海力士涨逾3%，三星电子涨近3%。</t>
+          <t>10月14日，山东省人民政府办公厅印发《关于加快推进数据产业高质量发展的实施意见》，提出开展数据企业梯度培育行动，发现培育一批成长型数据企业，支持符合条件的数据企业依规享受金融服务、算力支持等政策。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sz001358</t>
+          <t>sz002368</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>兴欣新材</t>
+          <t>太极股份</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>24.92</v>
+        <v>12.75</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10.0221</v>
+        <v>10.0086</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>光刻胶|公司在电子化学品领域的产品主要是 N-羟乙基哌嗪以及N,N-二甲基丙酰胺，主要用于生产面板的光刻胶剥离液。</t>
+          <t>数据要素|2021年11月23日公司在互动平台表示，公司积极布局并探索数据运营服务的价值，与北京市加强合作，承担了北京数据交易平台的技术开发及支撑服务。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>光刻胶</t>
+          <t>数据要素</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-0.0587</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>早盘韩国股市高开高走，存储芯片龙头SK海力士涨逾3%，三星电子涨近3%。</t>
-        </is>
-      </c>
+        <v>-1.1512</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh603173</t>
+          <t>sh688121</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">福斯达  </t>
+          <t xml:space="preserve">*ST卓然 </t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30.05</v>
+        <v>0.97</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>9.992700000000001</v>
+        <v>19.7531</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>油气+电子特气|1.公司的液化天然气装置（LNG装置）产品包括常规天然气液化提纯设备、化工尾气分离提纯液化设备、非常规天然气提纯液化设备，主要应用于天然气、石油化工等行业。
-2.公司已经有向客户提供空分设备并向下游半导体用户供气。</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>油气, 电子特气</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是大型炼油化工专用装备模块化、集成化制造的提供商，专业为石油化工、炼油、天然气化工等领域的客户提供设计、制造、安装和服务一体化的解决方案。</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>-0.0587</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>早盘韩国股市高开高走，存储芯片龙头SK海力士涨逾3%，三星电子涨近3%。</t>
-        </is>
-      </c>
+        <v>-1.1512</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh605178</t>
+          <t>sz002207</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>时空科技</t>
+          <t>*ST准油</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>61.44</v>
+        <v>5.53</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10.009</v>
+        <v>9.9404</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>存储芯片|2025年10月9日公告，公司正在筹划以发行股份及支付现金的方式购买深圳市嘉合劲威电子科技有限公司的控股权，同时拟发行股份募集配套资金。本次交易预计构成重大资产重组。嘉合劲威业务核心围绕存储产品及相关应用展开，现已形成固件算法开发、存储芯片测试、集成封装设计、存储产品定制等核心竞争力，其存储芯片产品广泛应用于移动智能终端、PC、行业终端、数据中心等多个信息技术领域。</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>存储芯片</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是为石油、天然气开采企业提供油田动态监测和提高采收率技术服务的专业化企业，已形成油田动态监测资料录取、资料解释研究和应用、治理方案编制、增产措施施工及效果评价等综合技术服务能力，是西部地区实力较强的一体化油田稳产、增产技术服务企业，能够提供油田增产、油田管理和配套建设等“一站式”技术服务。</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>量子科技</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.6799000000000001</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>谷歌量子人工智能发布量子计算重大突破，团队在Willow处理器上验证“魔法态培育”技术，将相关量子态的错误率降至未经培育时的约1/40，获得逻辑保真度达99.99%的T态。</t>
-        </is>
-      </c>
+        <v>-1.1512</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sz003029</t>
+          <t>sz002514</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>*ST宝馨</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>21.99</v>
+        <v>2.46</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10.005</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.821399999999999</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>量子科技+网络安全|1.公司实现抗量子签名的算法，并成功开发传统密码和抗量子密码混合模式的密钥生成以及证书签发功能，完成抗量子算法与数字证书技术的结合，以进一步提升数字认证基础设施的安全性。
-2.公司为央行、国有银行等金融机构提供信息PKI密码安全基础设施、身份安全、数据保护、签验等产品、技术及解决方案，公司积极关注数字货币的发展趋势，持续推进面向数字货币的新业务应用及技术研究项目，为数字货币提供可信安全支撑。</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>量子科技, 网络安全</t>
-        </is>
-      </c>
+          <t>ST股 | 1.公司相关下属子公司主要从事智能作业机器人等设备的设计研发、生产制造及销售，可应用于农业、电气及自动化等。
+2.公司目前供货为光伏行业电池制备用硅片M10（18X）与M12（210）的专用设备，目前主要专注在湿法工艺制程，槽式加工设备与水平链式加工设备，主要设备有制绒机，碱抛机，酸抛机，清洗机。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>量子科技</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>0.6799000000000001</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>谷歌量子人工智能发布量子计算重大突破，团队在Willow处理器上验证“魔法态培育”技术，将相关量子态的错误率降至未经培育时的约1/40，获得逻辑保真度达99.99%的T态。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz002767</t>
+          <t>sz002343</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>先锋电子</t>
+          <t>慈文传媒</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>18.04</v>
+        <v>10.26</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+        <v>9.9678</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>7天6板</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>量子科技+机器人|1.公司基于量子加密通信技术实现防窃听检测的先锋电子物联网智能膜式燃气表已在合肥市部分居民小区连续稳定运行多年。
-2.参股公司智驰华芯主营业务为汽车、工业和机器人等控制机构和探测模块的核心传感器，从传感器芯片到传感器系统完整的研发、生产和销售。</t>
+          <t>短剧|公司已形成了以自有IP为核心资源，以影视IP内容投资、开发、制作及发行为核心业务，积极延伸拓展电影、网络电影、网络微短剧、互动剧、小程序短剧、IP线下衍生等相关品类的业务体系。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>量子科技, 机器人</t>
+          <t>短剧</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>量子科技</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>0.6799000000000001</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>谷歌量子人工智能发布量子计算重大突破，团队在Willow处理器上验证“魔法态培育”技术，将相关量子态的错误率降至未经培育时的约1/40，获得逻辑保真度达99.99%的T态。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz002076</t>
+          <t>sz001216</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>星光股份</t>
+          <t>华瓷股份</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>2.17</v>
+        <v>24.31</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>10.1523</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>量子科技|子公司广州天芯量子拥有量子密钥分发、量子VPN加密、量子密钥管理等核心技术，已先后开发量子密钥分发产品、量子密钥管理终端、量子光交换机、量子波分复用终端、量子密钥应用设备、云防线及安全态势感知平台等产品。</t>
+          <t>氧化锆粉体|子公司氧化锆粉体纯度最高可达99.995%，产品可适配新能源研磨、齿科陶瓷、MLCC等不同领域使用需求。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>量子科技</t>
+          <t>氧化锆粉体</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>0.5746</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>据福州、厦门海关统计，今年前三季度，福建外贸进出口1.52万亿元，同比增长7.4%。其中，出口8844.4亿元，增长1.4%；进口6375.2亿元，增长17%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sh600802</t>
+          <t>sh600267</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>福建水泥</t>
+          <t>海正药业</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>6.78</v>
+        <v>12.06</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10.0649</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.0365</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>福建+水泥|公司主要从事水泥及熟料的生产及销售，拥有7条新型干法熟料水泥生产线，具备年产熟料784.3万吨、水泥1164万吨。公司是福建地区产能规模最大的水泥制造企业，也是福建省水泥行业唯一的一家上市公司。</t>
+          <t>业绩|公司预计2026年1-9月实现归母净利润11.50亿元，同比增长149.46%。主要系公司创新药及宠物药产品销售稳步增长，销量提升有效释放生产规模效应，带动生产成本持续下降，以及产品结构优化、整体运营效率的改善，公司主营业务盈利能力稳步提升。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>福建, 水泥</t>
+          <t>业绩</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>0.5746</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>据福州、厦门海关统计，今年前三季度，福建外贸进出口1.52万亿元，同比增长7.4%。其中，出口8844.4亿元，增长1.4%；进口6375.2亿元，增长17%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sz000701</t>
+          <t>sz002929</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>厦门信达</t>
+          <t>润建股份</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>5.36</v>
+        <v>46.4</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>10.0616</v>
+        <v>10.0047</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>福建+大宗商品贸易|公司是厦门国贸控股集团旗下上市公司。公司供应链业务以大宗商品贸易为载体，以有色金属和黑色大宗商品贸易业务为主。</t>
+          <t>Token出海|润建股份公告称，旗下五象云谷词元工厂与×海外企业签订2亿美元Token服务订单，合同期1年，为公司Token出海首笔重大商业化订单。该模式采用境内算力部署、海外API远程调用，按Token消耗结算。本次订单是词元出海业务落地闭环重要里程碑，树立业务范本。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>福建, 大宗商品贸易</t>
+          <t>Token出海</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>0.5746</v>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>据福州、厦门海关统计，今年前三季度，福建外贸进出口1.52万亿元，同比增长7.4%。其中，出口8844.4亿元，增长1.4%；进口6375.2亿元，增长17%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sh603668</t>
+          <t>sz001323</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>天马科技</t>
+          <t>慕思股份</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>7.55</v>
+        <v>20.21</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>10.0583</v>
+        <v>10.0163</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>福建+水产|公司是国内特种水产配合饲料品种最为齐全的企业之一，产品主要应用于鳗鲡、石斑鱼、大黄鱼、龟、鳖、鲟鱼、鲑鳟、鲆鲽鳎、鲍、海参等特种水产动物从种苗期至养成期的人工养殖全阶段。</t>
+          <t>家居|公司主要从事健康睡眠系统的研发、生产和销售，主要产品包括中高端床垫、床架、床品和其他产品，其中床垫为公司核心产品。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>福建, 水产</t>
+          <t>家居</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>-2.1065</v>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>腾讯上线“绿泡泡短剧”小程序，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sz000607</t>
+          <t>sh600329</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>华媒控股</t>
+          <t xml:space="preserve">达仁堂  </t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>4.61</v>
+        <v>40.92</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>10.0239</v>
+        <v>10</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>AI短剧|传媒子公司扩大媒体数字化应用，打造“数字人文杰”、“审点芯”数字人、“杭州迹忆”平台、“杭州文博金牌推荐官1号”苏东坡数字人IP等产品，探索AI短剧平台研发。</t>
+          <t>中药|公司是以绿色中药为核心，集生产、经营、科研为一体，业务涵盖中药全产业链，覆盖中药材种植、中药材贸易、中成药研发生产及销售、中药饮片生产销售、医药商业物流、药品零售、化学原料及制剂、生物医药、营养保健品的研发生产销售等众多领域。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>AI短剧</t>
+          <t>中药</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>-2.1065</v>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>腾讯上线“绿泡泡短剧”小程序，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sh603636</t>
+          <t>sz002626</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>南威软件</t>
+          <t>金达威</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>18.38</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>9.9863</v>
+        <v>9.994</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>短剧出海|南威软件在互动平台表示，公司AI短剧业务首部海外AI短剧已于8月制作完成。按照规划，2026年下半年计划出品25部高质量AI短剧，整体产能规划为年产超100部，公司海外短剧自有发行APP预计11月上线.</t>
+          <t>鱼油|国海证券研报指出，厄尔尼诺引发秘鲁鳀鱼产量骤降，饲料级鱼油价格大涨。公司万吨藻油产能已进入爬坡阶段。藻油直接从微生物中提取获得，解决了鱼油重金属污染风险、供应链不稳定问题，行业逐步萌芽，近期鱼油价格大涨预计显著加速藻油Omega-3对鱼油的替代。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>短剧出海</t>
+          <t>鱼油</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>短剧</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>-2.1065</v>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>腾讯上线“绿泡泡短剧”小程序，直接对标字节跳动旗下日活接近2亿的红果短剧，引发行业广泛关注。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sh601999</t>
+          <t>sz001211</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>出版传媒</t>
+          <t>双枪科技</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>8.25</v>
+        <v>28.74</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>10</v>
+        <v>9.9885</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>短剧+AI|公司所属音像社、电子社等公司，参与制作视频短剧等作品，部分制作中使用AI技术，作品在学习强国、红果等平台播放。</t>
+          <t>餐厨具|公司是一家领先的日用餐厨具供应商，拥有筷子、砧板、勺铲、签类和其他餐厨具5个大类，超过1000种单品。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>短剧, AI</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>商业航天</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>1.8063</v>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>北京时间2026年10月14日晚，国星宇航在东风商业航天创新试验区使用朱雀二号改进型Y4运载火箭，成功将“星算”计划02组星座晨昏轨道8颗卫星发射升空。</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>sh603278</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>大业股份</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>9.988900000000001</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>商业航天+机器人|1.公司投资联营企业湖北三江航天江北机械工程有限公司金额为6405.04万。湖北三江航天江北机械工程有限公司主要从事航天动力系统、天线罩等航天型号产品及特种压力容器产品等民用产品的研发生产。
-2.公司关注到近期市场上公司还涉及“人形机器人概念股”相关内容。公司现有主营业务仍以胎圈钢丝、钢帘线以及胶管钢丝的研发、生产和销售为主，公司机器人腱绳产品目前尚未批量生产，未产生实质性收益，且公司相关业务未来在技术研发、产品竞争能力、盈利能力等方面存在重大不确定性。</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>商业航天, 机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>商业航天</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>1.8063</v>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>北京时间2026年10月14日晚，国星宇航在东风商业航天创新试验区使用朱雀二号改进型Y4运载火箭，成功将“星算”计划02组星座晨昏轨道8颗卫星发射升空。</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>sh688592</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>司南导航</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>24.98</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>19.9808</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>商业航天|公司自成立以来一直致力于高精度卫星导航专用芯片和差分定位（RTK）技术的研究与开发，基于北斗以及其他全球卫星导航系统（GNSS），向客户提供实时定位精度为厘米、毫米级的高精度卫星导航定位板卡/模块、数据采集设备、农机自动驾驶系统以及数据应用及系统解决方案。</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>商业航天</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>1.1038</v>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>《2026中国冰雪产业发展研究报告》15日在北京正式发布，2025-2026冰雪季全国居民冰雪运动参与人数达3.08亿，冰雪旅游游客约2.2亿人次，冰雪产业规模突破万亿，运动消费规模达2050亿元，同比增长约9.3%。</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>sz000530</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>冰山冷热</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>9.9567</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业|子公司冰山工程近年来承接了多项代表性工程，包括广州融创茂室内滑雪场项目、上海之星室内综合性冰雪场馆、陕西国际体育之窗等多个商业冰雪场馆项目。</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>1.1038</v>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>《2026中国冰雪产业发展研究报告》15日在北京正式发布，2025-2026冰雪季全国居民冰雪运动参与人数达3.08亿，冰雪旅游游客约2.2亿人次，冰雪产业规模突破万亿，运动消费规模达2050亿元，同比增长约9.3%。</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>sh603955</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>大千生态</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>23.57</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>9.986000000000001</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业|2025年12月，旗下江苏大千文旅与柳叶湖旅游度假区正式签约。项目以“沉浸式体验、全年龄段适配”为核心，精心打造奇趣雪乡乐园、戏雪乐园、侏罗纪秘境、梦幻绿野仙踪等六大核心体验区，设置20多条滑道、恐龙主题展区、冰雪雕塑区及免费互动项目。</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>医药</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>-0.6261</v>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>10月15日，阿斯利康与Insitro签署价值18.6亿美元的人工智能药物研发协议，旨在帮助寻找治疗肝脏和心脏疾病的新药。</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>sh603168</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>莎普爱思</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>10.0529</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>眼药|公司是一家以生产、研发和销售化学制剂药和中成药为主要业务的医药制造企业。化学制剂药主要涵盖眼科用药（抗白内障类）、抗微生物药（头孢菌素类）、抗微生物药（喹诺酮类）和调节水、电解质及酸碱平衡药等细分治疗领域，主要产品包括莎普爱思滴眼液、大输液和头孢克肟产品等，其中莎普爱思滴眼液在抗白内障药物市场中处于行业前列。</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>眼药</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>sh601811</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>新华文轩</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>10.0078</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>15天11板</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>并购重组+传媒|新华文轩公告称，公司拟以自有资金收购控股股东四川新华出版发行集团持有的四川民族出版社有限责任公司100%股权，收购价格为3.46亿元。本次交易构成关联交易，不构成重大资产重组。本次收购有利于本公司进一步完善在民族出版领域的布局，同时，有助于解决潜在同业竞争问题。</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>并购重组, 传媒</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>sh603999</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>读者传媒</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>9.973799999999999</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>出版发行|公司主要业务涵盖期刊、图书、教材教辅等纸质出版物的出版、发行、阅读服务及电子出版物、在线教育、文化创意等领域，形成主业突出、产业多元化的发展格局。“读者”品牌是公司发展的核心。</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>出版发行</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>sh600668</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>尖峰集团</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>10.0125</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>创新药|尖峰药业及其下属控股子公司在研抗肿瘤新药主要有JFAN-1001。</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>创新药</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr"/>
-      <c r="D59" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>sz000573</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>粤宏远Ａ</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>10.0985</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>并购重组|粤宏远A公告称，公司拟以现金方式受让深圳市金旺达机电有限公司100%股权，交易价格不超过5.5亿元。标的公司生产基地位于东莞市，专注于精密传动功能部件领域生产制造，核心产品包括精密直线导轨、精密滚珠丝杠、精密行星滚柱丝杠、精密减速机、KKR钢基模组、GTHA内嵌式铝基模组、铝基丝杠模组等。</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>sh600825</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>新华传媒</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>10.0145</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>并购重组|新华传媒公告称，公司拟以发行股份方式购买上海界面财联社科技股份有限公司100%股权，发行价格确定为3.93元/股，预计构成重大资产重组及关联交易。公司股票将于2026年9月21日复牌。本次交易完成后，上市公司将在原有图书发行与报刊经营业务基础上，新增财经新媒体运营、商业信息服务、金融资讯服务及互联网广告服务业务，业务结构进一步丰富。</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>sh600418</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>江淮汽车</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>22.37</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>9.9803</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>汽车整车|公司是一家集全系列商用车、乘用车及动力总成等研产销和服务于一体,“先进节能汽车、新能源汽车、智能网联汽车”并举的综合型汽车企业集团。</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>汽车整车</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>sh600319</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>亚星化学</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>10.0478</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>化工|公司主营氯化聚乙烯（CPE）、离子膜烧碱、水合肼、ADC发泡剂等高科技化学产品，同时从事新型化学材料的开发和研究，是目前世界上最主要的含氯聚合物研发生产企业。</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>化工</t>
+          <t>餐厨具</t>
         </is>
       </c>
     </row>
@@ -3351,7 +2792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3378,46 +2819,46 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sh600825</t>
+          <t>sz002889</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>新华传媒</t>
+          <t>东方嘉盛</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz000530</t>
+          <t>sz003029</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>冰山冷热</t>
+          <t>吉大正元</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh601811</t>
+          <t>sh600178</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>新华文轩</t>
+          <t>东安动力</t>
         </is>
       </c>
     </row>
@@ -3427,12 +2868,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002889</t>
+          <t>sz002724</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>东方嘉盛</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>
@@ -3442,12 +2883,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz003029</t>
+          <t>sz000576</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>吉大正元</t>
+          <t>甘化科工</t>
         </is>
       </c>
     </row>
@@ -3457,12 +2898,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh600668</t>
+          <t>sh603197</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>尖峰集团</t>
+          <t>保隆科技</t>
         </is>
       </c>
     </row>
@@ -3472,12 +2913,72 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh603999</t>
+          <t>sh600860</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>读者传媒</t>
+          <t>京城股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>sh603278</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>大业股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>sz002085</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>万丰奥威</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>sh600148</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>长春一东</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>sh603348</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>文灿股份</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="278" customWidth="1" min="10" max="10"/>
+    <col width="266" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -552,225 +552,222 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.5004</v>
+        <v>-1.969</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>火山引擎发起精品AI剧激励计划，面向使用Seedance制作并在红果短剧APP上线的精品AI漫短剧提供激励。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh603999</t>
+          <t>sh603278</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>读者传媒</t>
+          <t>大业股份</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>7.47</v>
+        <v>14.51</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.0147</v>
+        <v>10.0076</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>5天3板</t>
+          <t>5天5板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>出版媒体|公司主要业务涵盖期刊、图书、教材教辅等纸质出版物的出版、发行、阅读服务及电子出版物、在线教育、文化创意等领域，形成主业突出、产业多元化的发展格局。“读者”品牌是公司发展的核心。</t>
+          <t>机器人|大业股份10月21日公告称，公司机器人腱绳产品目前尚未批量生产，未产生实质性收益，且公司相关业务未来在技术研发、产品竞争能力、盈利能力等方面存在重大不确定性。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>出版媒体</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.5004</v>
+        <v>-1.969</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>火山引擎发起精品AI剧激励计划，面向使用Seedance制作并在红果短剧APP上线的精品AI漫短剧提供激励。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz002181</t>
+          <t>sz003021</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>粤 传 媒</t>
+          <t>兆威机电</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>11.14</v>
+        <v>83.39</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.9704</v>
+        <v>9.998700000000001</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>AI短剧|子公司新媒体公司自主研发了AIGC内容生产一体化平台—“妙创”AIGC 内容生产平台，应用于《广州三部曲》《我为荔枝拍广告》等项目。平台覆盖火爆短剧、创意短视频、妙音AI音乐三大场景，适配从剧本拆解、创意分镜设计到图片与视频生成的各层次需求，为专业内容生产团队、企业品牌部门/融媒体中心、高校等单位提供内容创作服务。</t>
+          <t>机器人+消费电子|1.公司聚焦手指等运动执行应用部位，开发仿生机器人灵巧手产品，该产品与公司的技术能力相契合,系公司未来平台化产品的重点布局。
+2.公司的微型传动系统可以应用于AR/VR领域，具体如磁感应系统、瞳距调节驱动系统、头部自动松紧装置、智能眼镜隐藏式微型扬声器等。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>AI短剧</t>
+          <t>机器人, 消费电子</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.5004</v>
+        <v>-1.969</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>火山引擎发起精品AI剧激励计划，面向使用Seedance制作并在红果短剧APP上线的精品AI漫短剧提供激励。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh601999</t>
+          <t>sz002535</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>出版传媒</t>
+          <t>林州重机</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>7.8</v>
+        <v>2.75</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.0141</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>短剧+AI|公司所属音像社、电子社等公司，参与制作视频短剧等作品，部分制作中使用AI技术，作品在学习强国、红果等平台播放。</t>
+          <t>军工+机器人|1.公司与多家大型军工集团建立了合作关系，并承接、交付了多批次的订单。
+2.公司曾于14年定增募资1.02亿元用于工业机器人产业化（一期）项目。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>短剧, AI</t>
+          <t>军工, 机器人</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.5004</v>
+        <v>-1.969</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>火山引擎发起精品AI剧激励计划，面向使用Seedance制作并在红果短剧APP上线的精品AI漫短剧提供激励。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz002238</t>
+          <t>sh603028</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>天威视讯</t>
+          <t xml:space="preserve">赛福天  </t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>7.61</v>
+        <v>7.76</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9.9711</v>
+        <v>10.0709</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>短剧+数据中心|1.公司参股企业中广电传媒与北京点众科技在短剧上进行合作，由点众科技负责应用开发、节目制作、终端运营和流量投放，陆续在微信小程序、快应用、IOS等平台推出短剧产品。
-2.公司初步形成位于深圳市福田区、南山区、龙华区以及深汕合作区的3000个5-8KW 机柜规模的数据中心布局，正在加紧推进系统调试、检测、认证、以及销售运维团队招选等正式投产前相关运营准备工作，未来将结合自身经营状况和行业发展状况来评估包括算力服务在内的增值业务的必要性、可行性和经济效益，再研究是否推出相应的数据中心增值服务业务。</t>
+          <t>机器人|在工业机器人领域，公司凭借对钢丝绳在升降与传动系统中核心技术的深度研发与创新应用，成功突破了传统业务的边界，开辟了全新的市场空间。通过为仓储智能机器人企业深圳市海柔创新科技有限公司提供高性能的升降配件解决方案，公司实现了从传统制造业向高端智能装备领域的跨越式发展。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>短剧, 数据中心</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.5004</v>
+        <v>-1.969</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>火山引擎发起精品AI剧激励计划，面向使用Seedance制作并在红果短剧APP上线的精品AI漫短剧提供激励。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh600715</t>
+          <t>sh603350</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>文投控股</t>
+          <t xml:space="preserve">安乃达  </t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1.87</v>
+        <v>29.48</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>10</v>
@@ -778,392 +775,389 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>短剧+AI|公司已针对短剧行业进行深入研究，并计划依托自身IP资源孵化优势，结合AIGC等工具的发展应用，探索文化内容与科技手段相融合的新型创作模式。</t>
+          <t>机器人|公司参与了浙江智鼎机器人有限公司的增资扩股，智鼎机器人是智元机器人第一个独立运营的成熟具身智能机器人子公司。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>短剧, AI</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1.5004</v>
+        <v>-1.969</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>火山引擎发起精品AI剧激励计划，面向使用Seedance制作并在红果短剧APP上线的精品AI漫短剧提供激励。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh603721</t>
+          <t>sz002249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>中广天择</t>
+          <t>大洋电机</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20.82</v>
+        <v>7.06</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9.9842</v>
+        <v>9.9688</v>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧|公司积极布局纪实IP、微短剧、AI漫剧、中长剧等多元内容赛道，构建多层次、差异化的内容供给与运营体系。在短剧及中长剧领域，公司以制作、投资与分账发行相结合的模式稳步推进项目落地，内容制作与市场运营能力持续提升，优质项目储备不断充实。</t>
+          <t>机器人+稀土|1.公司前瞻技术研究院已设立前瞻技术研究项目--人形机器人电机项目，其中涉及包括无框力矩电机在内的多项研究。
+2.公司持有宁波科星材料科技有限公司51%的股份，宁波科星是一家专注于烧结钐钴、烧结钕铁硼永磁材料及产品研发和制造的高新技术企业，产品广泛应用于曳引机、汽车、电子信息、医疗、航空航天、国防等领域。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧</t>
+          <t>机器人, 稀土</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.5004</v>
+        <v>-1.969</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>火山引擎发起精品AI剧激励计划，面向使用Seedance制作并在红果短剧APP上线的精品AI漫短剧提供激励。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz301102</t>
+          <t>sz301502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>兆讯传媒</t>
+          <t>华阳智能</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>11.41</v>
+        <v>54</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>19.979</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>传媒+AI|1.公司基于中国高铁网格状的布局自建了一张覆盖全国的高铁数字媒体网络，并以此为依托从事高铁数字媒体资源的开发、运营和广告发布业务。
-2.公司在创意和技术方面一直精心打磨，对于AI数字系统的运用特别是数字图像板块正在积极探索与升级的过程中，当前AI系统已经运用到户外裸眼3D的制作环节，包括原画设计、场景构筑、三维工程树文件管理、三维抠像等。</t>
+          <t>机器人|公司的无框电机可应用于机器人、协作机器人及高端医疗器械等领域。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>传媒, AI</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1.6798</v>
+        <v>-1.969</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz002368</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>太极股份</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>14.67</v>
+        <v>12.03</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9.969999999999999</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>9.9634</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>数据要素|2021年11月23日公司在互动平台表示，公司积极布局并探索数据运营服务的价值，与北京市加强合作，承担了北京数据交易平台的技术开发及支撑服务。</t>
+          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1.6798</v>
+        <v>-1.969</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh603138</t>
+          <t>sh603528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>海量数据</t>
+          <t>多伦科技</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>15.38</v>
+        <v>7.4</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.0143</v>
+        <v>9.955400000000001</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>数据要素|公司是国内主要的关系型数据库产品提供商，也是国内数据库基础软件产业发展的重要参与者和推动者。公司的企业级大数据平台提供全域数据资产管理功能，可以帮助客户采集和汇聚数据，经过治理后形成数据资产，为数字化应用提供支撑。该平台可实现全过程可视化，能快速开发数据类应用系统。</t>
+          <t>机器人|1.公司已开展多项人工智能驾考新技术研究，包括基于机器视觉的驾驶人注意力分配识别、基于机器视觉的道路环境目标识别、基于激光雷达的目标探测技术等。
+2.公司通过珠海星芯投资基金参与了众擎机器人科技有限公司Pre-A++轮融资，并持有其1.57%的股份。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1.6798</v>
+        <v>-1.969</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh600271</t>
+          <t>sh603089</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>航天信息</t>
+          <t>正裕工业</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>7.4</v>
+        <v>10.81</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9.955400000000001</v>
+        <v>9.9695</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>数据安全|公司研发了数据安全治理平台，推动数据资产化赋能管理决策；隐私计算平台助力数据安全融合与共享，促进数据要素的价值释放与产业升级；数据库透明加密系统主动防御筑牢安全底线，推动密码合规建设；数据库脱敏系统灵活保护企业隐私，实现数据外发安全可控。</t>
+          <t>机器人|公司布局机器人零部件赛道，致力于机器人用柔性触觉传感技术的研发、传感器的设计与制造、以及信号处理系统的开发与测试，已完成核心产品的技术攻关与样品研发。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>数据安全</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1.6798</v>
+        <v>-1.969</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz301159</t>
+          <t>sz301023</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>三维天地</t>
+          <t>奕帆传动</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>38.76</v>
+        <v>32.48</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>20</v>
+        <v>19.9852</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>数据要素|公司是国内技术实力较强、团队规模较大、项目业绩较多的检验检测信息化和数据资产管理服务供应商，数据资产管理平台定位于基于人工智能与知识图谱的面向企业数据价值落地的产品型解决方案，实现数据资产全域、全过程、全生命周期的价值落地。</t>
+          <t>机器人|2024年11月22日公司接受调研时表示，公司的电机可以运用在不同的应用场景，不仅限于“人形机器人”，前期会主要运用在桁架机器人、协作机器人、医疗、仪表仪器、云台等领域。目前，公司正处于产品研发设计的关键阶段，预计在明年，会通过验证并小批量供货。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1.6798</v>
+        <v>-1.969</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh688500</t>
+          <t>sh603370</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>慧辰股份</t>
+          <t>华新精科</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>37.56</v>
+        <v>28.71</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>数据要素|在数据要素方面，公司形成数据分析、数据挖掘、数据运营的核心能力，积累了广泛的数据应用场景（通信、ICT、快消品、汽车、金融、烟草、旅游等领域），形成了 XMfactory、DMengine标准化产品。</t>
+          <t>机器人|公司铁芯产品下游应用广阔，可应用于机器人关节等相关部位的电机。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.1078</v>
+        <v>-1.969</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2026欧洲肿瘤内科学会（ESMO）年会将于10月23-27日在马德里举办，本届大会共有29项国产创新药研究入选突破性摘要LBA，占全部LBA约三分之一。</t>
+          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz300006</t>
+          <t>sh603728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>莱美药业</t>
+          <t>鸣志电器</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>54.47</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>20</v>
+        <v>9.995999999999999</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>纳米炭抗癌|10月9日，四川大学华西医院联合恩施州中心医院，正式对外公布了全球首个铁死亡诱导剂的I期临床试验结果。纳米炭铁混悬注射液是四川瀛瑞医药科技有限公司（莱美药业控股子公司）在纳米炭混悬注射液基础上研发的新一代纳米药物，属于抗癌类制剂。</t>
+          <t>机器人|公司的无刷电机模组、无齿槽空心杯电机模组、无框和交流伺服电机及驱动与控制系统、精密丝杠传动模组、轮毂/轮边电机模组、旋转/顶升机构模组等的在机器人的各主要运动控制功能模块中广泛适用。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>纳米炭抗癌</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>一带一路</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-0.1078</v>
+        <v>-1.8697</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2026欧洲肿瘤内科学会（ESMO）年会将于10月23-27日在马德里举办，本届大会共有29项国产创新药研究入选突破性摘要LBA，占全部LBA约三分之一。</t>
+          <t>乌克兰总统泽连斯基当地时间10月21日在接受采访时表示，乌方可在保留至少75%领土控制权的基础上达成和平协议。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1171,45 +1165,44 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh600252</t>
+          <t>sz001360</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>中恒集团</t>
+          <t>南矿集团</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2.38</v>
+        <v>18.58</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.1852</v>
+        <v>10.0059</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>医药+莱美药业股东|1.公司是以制药为核心业务，旗下广西梧州制药(集团)股份有限公司已发展成为一家集研发、生产、销售、服务于一体的现代化综合型高新技术制药企业，为广西龙头药品生产企业、华南区大型中药注射剂生产企业。
-2.中恒集团是莱美药业的控股股东，纳米炭铁混悬注射液是四川瀛瑞医药科技有限公司（莱美药业控股子公司）在纳米炭混悬注射液基础上研发的新一代纳米药物，属于抗癌类制剂。</t>
+          <t>一带一路+工程机械|公司主营业务为砂石骨料和金属矿山相关的破碎、筛分设备的研发、设计、生产、销售及后市场服务，是国内技术领先的中高端矿机装备供应服务商之一。公司下游市场之一的砂石骨料行业长期受益于“一带一路”振兴战略。公司的主要海外销售区域分布在南非、美国、俄罗斯、刚果金、纳米比亚等国家地区。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>医药, 莱美药业股东</t>
+          <t>一带一路, 工程机械</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>一带一路</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.1078</v>
+        <v>-1.8697</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026欧洲肿瘤内科学会（ESMO）年会将于10月23-27日在马德里举办，本届大会共有29项国产创新药研究入选突破性摘要LBA，占全部LBA约三分之一。</t>
+          <t>乌克兰总统泽连斯基当地时间10月21日在接受采访时表示，乌方可在保留至少75%领土控制权的基础上达成和平协议。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1217,44 +1210,45 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz000788</t>
+          <t>sz002097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>北大医药</t>
+          <t>山河智能</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>5.86</v>
+        <v>7.26</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>9.9437</v>
+        <v>10</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>创新药|公司已建立起自主知识产权、仿创技术、技术创新为一体的技术核心体系，研发领 域聚焦于抗感染类、镇痛类、精神类、慢病类等创新药、高端仿制药和大市场品种，为企业发展提供持续优化的产品结技术中心可独立完成仿制药、一致性评价品种的研发全流程，也可开展创新药的药学部分研究工作。</t>
+          <t>一带一路+机器人|1.公司主要产品包括挖掘机械、桩工机械、高空机械、矿山设备、 应急救援设备、油气管道设备、铁路维保设备及绿色能源开采装备。公司助力一带一路，成功参与泰国“中泰铁路项目”、马来西亚“东马铁路”、秘鲁安第斯高速公路、尼日利亚卡卡铁路、哥伦比亚波哥大地铁等境外项目。
+2.公司无人化产品包括遥控挖掘机、遥控装载机、应急救援机器人、破拆机器人、无人矿卡等工程机械类产品，与中科慧拓等多家科研单位联手打造的智能运载机器人SWK90EA载山CarMoy，是我国首台套具备产业化标准要求以及完全自主知识产权的新能源运载装备。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>创新药</t>
+          <t>一带一路, 机器人</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>一带一路</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.1078</v>
+        <v>-1.8697</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2026欧洲肿瘤内科学会（ESMO）年会将于10月23-27日在马德里举办，本届大会共有29项国产创新药研究入选突破性摘要LBA，占全部LBA约三分之一。</t>
+          <t>乌克兰总统泽连斯基当地时间10月21日在接受采访时表示，乌方可在保留至少75%领土控制权的基础上达成和平协议。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -1262,44 +1256,45 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz000518</t>
+          <t>sh603280</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>四环生物</t>
+          <t>南方路机</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>3.63</v>
+        <v>29.06</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10</v>
+        <v>9.9924</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>医药|公司主要产品有重组人白细胞介素－2、重组人表皮生长因子、重组人粒细胞集落刺激因子、重组人红细胞生成素、肝炎诊断试剂、体外诊断试剂、注射剂等。</t>
+          <t>一带一路+机器人|1.公司主要从事工程搅拌设备、原生骨料加工处理设备、骨料资源化再生处理设备的设计、研发、生产和销售，目前公司已逐步建立出口经销渠道，产品销售业务拓展至俄罗斯、东南亚、非洲、澳大利亚等国家和地区。
+2.公司的建筑垃圾资源化处理设备的智能分拣机器人，能高效应对混合建筑垃圾、建筑混合废弃物、橡胶、木头等物料进行分拣，实现对建筑垃圾、装修垃圾等物料的分类回收和再利用，与公司其他产品均可广泛运用于灾后重建。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>一带一路, 机器人</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>一带一路</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-0.2141</v>
+        <v>-1.8697</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>国家发展改革委日前召开10月份新闻发布会。国家发展改革委国民经济综合司副司长左刚表示，正在研究制定扩大内需战略实施方案，并将加快推动印发实施。</t>
+          <t>乌克兰总统泽连斯基当地时间10月21日在接受采访时表示，乌方可在保留至少75%领土控制权的基础上达成和平协议。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1307,309 +1302,303 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz002696</t>
+          <t>sz002307</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>北新路桥</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>10.52</v>
+        <v>3.39</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.0418</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9天7板</t>
-        </is>
-      </c>
+        <v>10.0649</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>水产品+鱼粉|1.公司位于广西，水产品加工业务板块将着重研发以罗非鱼、生鱼、金鲳鱼、海鲈鱼为原料的内销产品。
-2.公司下辖鱼粉厂的合计年产量约为1-2万吨，鱼油年产量约为2000-4000吨。</t>
+          <t>一带一路+基建|公司已在一带一路沿线7个国家设立办事处（巴基斯坦、蒙古国、柬埔寨、阿富汗、哈萨克斯坦、塔吉克斯坦、吉尔吉斯斯坦）。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>水产品, 鱼粉</t>
+          <t>一带一路, 基建</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>军工</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-0.2141</v>
+        <v>-2.5208</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>国家发展改革委日前召开10月份新闻发布会。国家发展改革委国民经济综合司副司长左刚表示，正在研究制定扩大内需战略实施方案，并将加快推动印发实施。</t>
+          <t>10月19日珠海航展门票正式开售，本次航展首次开放海上展区，包括海上装备、无人机在内的一批新装备、新技术将集中亮相。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh603696</t>
+          <t>sz002724</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>安记食品</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>14.96</v>
+        <v>11.21</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10</v>
+        <v>10.0098</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>5天5板</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>福建+调味品|公司专注于调味品的研发、生产和销售，主要产品包括复合调味粉、天然提取物调味料、香辛料、酱类、风味清汤等五大类500多个品种。</t>
+          <t>军工|公司是武器装备科研生产三级保密资格单位，设有专门的军品事业部负责军品的销售。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>福建, 调味品</t>
+          <t>军工</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>军工</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-0.2141</v>
+        <v>-2.5208</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>国家发展改革委日前召开10月份新闻发布会。国家发展改革委国民经济综合司副司长左刚表示，正在研究制定扩大内需战略实施方案，并将加快推动印发实施。</t>
+          <t>10月19日珠海航展门票正式开售，本次航展首次开放海上展区，包括海上装备、无人机在内的一批新装备、新技术将集中亮相。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz002086</t>
+          <t>sh600698</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>东方海洋</t>
+          <t>湖南天雁</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2.39</v>
+        <v>7.59</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.1382</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>水产+医药|1.公司主营业务为海洋水产品加工和海水养殖，其中海参养殖是公司海水养殖的传统主导业务。
-2.公司大健康事业部已布局免疫技术平台、质谱技术平台、分子技术平台及第三方医学检验实验室等四大平台。</t>
+          <t>军工|中国兵器装备集团旗下上市公司，公司拥有多个“全国第一”称号：第一个生产装甲车、坦克等军用大功率柴油发动机涡轮增压器、第一个研发并生产用于装甲车、坦克等冷却风机等。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>水产, 医药</t>
+          <t>军工</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-0.2141</v>
+        <v>-3.1631</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>国家发展改革委日前召开10月份新闻发布会。国家发展改革委国民经济综合司副司长左刚表示，正在研究制定扩大内需战略实施方案，并将加快推动印发实施。</t>
+          <t>市场调查机构集邦咨询（TrendForce）援引多方报道称，预估2026年第四季度DRAM合约价格环比上涨约20%。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh605388</t>
+          <t>sh603330</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>均瑶健康</t>
+          <t>天洋新材</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>7.32</v>
+        <v>11.1</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.0752</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+        <v>10.0099</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4天3板</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>乳酸菌饮品|公司主营常温乳酸菌系列饮品的研发、生产和销售，2011年起，公司战略进入常温乳酸菌饮品市场，推出“味动力”乳酸菌系列饮品，是国内最早生产与销售常温乳酸菌饮品的品牌企业之一。</t>
+          <t>半导体材料|公司电子胶板块光模块透镜固定用胶、底填胶等产品已经进入半导体及汽车电子领域小批量供货。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>乳酸菌饮品</t>
+          <t>半导体材料</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>芯片产业链</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-0.3145</v>
+        <v>-3.1631</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>记者采访业内专家了解到，作为特斯拉重点布局的长期增长方向，Optimus若顺利进入量产爬坡阶段，有望拉动我国执行器、减速器、传感器等零部件需求释放。</t>
+          <t>市场调查机构集邦咨询（TrendForce）援引多方报道称，预估2026年第四季度DRAM合约价格环比上涨约20%。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh603278</t>
+          <t>sh603933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>睿能科技</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>13.19</v>
+        <v>19.04</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.0083</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
+        <v>9.994200000000001</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>商业航天+机器人|1.公司投资联营企业湖北三江航天江北机械工程有限公司金额为6405.04万。湖北三江航天江北机械工程有限公司主要从事航天动力系统、天线罩等航天型号产品及特种压力容器产品等民用产品的研发生产。
-2.公司关注到近期市场上公司还涉及“人形机器人概念股”相关内容。公司现有主营业务仍以胎圈钢丝、钢帘线以及胶管钢丝的研发、生产和销售为主，公司机器人腱绳产品目前尚未批量生产，未产生实质性收益，且公司相关业务未来在技术研发、产品竞争能力、盈利能力等方面存在重大不确定性。</t>
+          <t>机器人+半导体|1.公司RA1、RA3系列伺服驱动器和MC2、MA3系列伺服电机已应用到机器人领域，包括不同载荷的四关节、六关节等工业机器人和协作机器人。
+2.公司分销的主要产品包括微控制器芯片、功率器件及模组、电源管理及驱动芯片、模拟及混合信号芯片、存储芯片等。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>商业航天, 机器人</t>
+          <t>机器人, 半导体</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>数据要素</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-0.3145</v>
+        <v>-3.9425</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>记者采访业内专家了解到，作为特斯拉重点布局的长期增长方向，Optimus若顺利进入量产爬坡阶段，有望拉动我国执行器、减速器、传感器等零部件需求释放。</t>
+          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz002347</t>
+          <t>sh601999</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>泰尔股份</t>
+          <t>出版传媒</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>7.27</v>
+        <v>8.58</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9.9849</v>
+        <v>10</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>5天3板</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>机器人+商业航天|1.2021年8月5日公司在互动平台表示，公司子公司燊泰智能的高线包装机器人市场占有率约42.4%。
-2.公司的激光技术、粉末材料可以应用于航空航天。</t>
+          <t>数据要素+AI短剧|1.子公司北方国家版权交易中心的主营业务主要是版权及知识产权的登记（确权）、交易、开发及会展培训等。
+2.公司所属音像社、电子社等公司，参与制作视频短剧等作品，部分制作中使用AI技术，作品在学习强国、红果等平台播放。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>机器人, 商业航天</t>
+          <t>数据要素, AI短剧</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>数据要素</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-0.3145</v>
+        <v>-3.9425</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>记者采访业内专家了解到，作为特斯拉重点布局的长期增长方向，Optimus若顺利进入量产爬坡阶段，有望拉动我国执行器、减速器、传感器等零部件需求释放。</t>
+          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sz001239</t>
+          <t>sh603138</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>永达股份</t>
+          <t>海量数据</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>14.74</v>
+        <v>16.92</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10</v>
+        <v>10.013</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -1618,1259 +1607,460 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>机器人+风电|1.子公司江苏金源高端装备有限公司的主营业务为高速重载齿轮锻件的研发、生产和销售，产品部分应用于机器人领域。
-2.公司的风力发电设备类产品类型丰富，其中直驱技术路线产品包括定、转子支架；半直驱技术路线技术产品主要包括锁定盘等；双馈技术路线产品主要包括机舱底座、机座等。</t>
+          <t>数据要素|公司是国内主要的关系型数据库产品提供商，也是国内数据库基础软件产业发展的重要参与者和推动者。公司的企业级大数据平台提供全域数据资产管理功能，可以帮助客户采集和汇聚数据，经过治理后形成数据资产，为数字化应用提供支撑。该平台可实现全过程可视化，能快速开发数据类应用系统。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>机器人, 风电</t>
+          <t>数据要素</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>-0.3145</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>记者采访业内专家了解到，作为特斯拉重点布局的长期增长方向，Optimus若顺利进入量产爬坡阶段，有望拉动我国执行器、减速器、传感器等零部件需求释放。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz002242</t>
+          <t>sz002076</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t>星光股份</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>22.62</v>
+        <v>2.7</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.0195</v>
+        <v>10.2041</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>5天4板</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>AI机器人|公司持有深思考人工智能机器人科技（北京）有限公司7.92%的股份，旗下产品包括AI机器人。</t>
+          <t>量子科技|子公司广州天芯量子拥有量子密钥分发、量子VPN加密、量子密钥管理等核心技术，已先后开发量子密钥分发产品、量子密钥管理终端、量子光交换机、量子波分复用终端、量子密钥应用设备、云防线及安全态势感知平台等产品。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>AI机器人</t>
+          <t>量子科技</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>0.9952000000000001</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>超微电脑第一财季净销售额初步估计为185亿至195亿美元，市场预计为149.9亿美元。公司股价盘后涨超10%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sh603330</t>
+          <t>sh600293</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>天洋新材</t>
+          <t>三峡新材</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>10.09</v>
+        <v>5.23</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10.0327</v>
+        <v>10.1053</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>光模块固定用胶|公司电子胶板块光模块透镜固定用胶、底填胶等产品已经进入半导体及汽车电子领域小批量供货。</t>
+          <t>并购重组|三峡新材公告称，公司拟通过发行股份及支付现金方式取得珠海市赛纬电子材料股份有限公司100%股权，并向包括控股股东当阳城投在内的不超过35名特定投资者发行股份募集配套资金，总额不超过10亿元。标的公司主营锂离子电池电解液的研发、生产和销售。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>光模块固定用胶</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>0.9952000000000001</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>超微电脑第一财季净销售额初步估计为185亿至195亿美元，市场预计为149.9亿美元。公司股价盘后涨超10%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sz002792</t>
+          <t>sh600838</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>通宇通讯</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>32.09</v>
+        <v>10</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10.0103</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
+        <v>10.011</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>光模块+6G|1.间接参股25.58%的深圳光为致力于各类光模块研发，目前已成功研发出了包括100G CFP2、400G QSFP-DD等系列在内的多个光模块产品类型。
-2.佳贤通信是基于英伟达CUDA Aerial开源生态平台开展6GAI-RAN基站技术研发工作，未与英伟达签署任何研发合作协议或战略合作框架协议，与英伟达之间不存在任何形式的研发合作、联合开发关系。相关产品目前仍处前期研发阶段，未实现商业化应用，未对佳贤通信经营业绩产生影响。公司拟以3亿元购买佳贤通信25%股权，交易完成后不纳入合并报表范围，采用权益法核算。</t>
+          <t>零售|公司控股股东为上海九百（集团）有限公司。目前已经发展成为涉及洗涤化工产品生产销售及洗染服务、酒类产品批发等多种业态的综合性企业。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>光模块, 6G</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>光通信</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>0.9952000000000001</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>超微电脑第一财季净销售额初步估计为185亿至195亿美元，市场预计为149.9亿美元。公司股价盘后涨超10%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz300296</t>
+          <t>sh600202</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>利亚德</t>
+          <t xml:space="preserve">哈空调  </t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>5.63</v>
+        <v>6.13</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>20.0426</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+        <v>10.0539</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>光通信+物理AI|1.在光通信领域，公司己与中科院开展研发合作，并已向中科院提供Micro LED光模块产品，用于替代原有传统光传输方案。
-2.OptiTrack作为公司AI与空间计算板块的核心产品，具备较强的技术通用性和场景延展能力，除机器人领域外，已广泛应用于影视拍摄、游戏与动画制作、虚拟拍摄、体育教学及医疗康复等多个领域，也为相关技术在物理AI方向的持续拓展奠定了基础。</t>
+          <t>冰雪产业注入预期|公司同一实控人哈尔滨国资委旗下马迭尔集团是其唯一文旅平台，旗下拳头品牌哈尔滨冰雪大世界、太阳岛风景区、亚布力等，或有资产注入预期。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>光通信, 物理AI</t>
+          <t>冰雪产业注入预期</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>0.9126000000000001</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>工业和信息化部信息通信管理局局长谢存表示，截至2026年9月底，我国智能算力规模达2592EFLOPS，同比增长146%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz002929</t>
+          <t>sh600261</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>润建股份</t>
+          <t>阳光照明</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>56.14</v>
+        <v>3.6</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>9.9922</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
+        <v>10.0917</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Token出海|润建股份公告称，旗下五象云谷词元工厂与×海外企业签订2亿美元Token服务订单，合同期1年，为公司Token出海首笔重大商业化订单。该模式采用境内算力部署、海外API远程调用，按Token消耗结算。本次订单是词元出海业务落地闭环重要里程碑，树立业务范本。</t>
+          <t>灯具|公司是中国最大的节能灯生产和出口基地之一，国家级高新技术企业。主要生产紧凑型节能荧光灯、电子节能灯、直管型荧光灯、T5大功率节能荧光灯及配套灯具、CCFL荧光屏背景光源及各类台灯系列。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Token出海</t>
+          <t>灯具</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>0.9126000000000001</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>工业和信息化部信息通信管理局局长谢存表示，截至2026年9月底，我国智能算力规模达2592EFLOPS，同比增长146%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sh603636</t>
+          <t>sh600192</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>南威软件</t>
+          <t>长城电工</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.0112</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>10.0396</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>算力租赁+AI短剧|1.公司于2024年4月获得北京市发展和改革委员会批准，建设2300PFlops算力的“北京七星园数字经济产业智算中心”，用于服务企业人工智能发展、政府公共算力及企业算力需求。
-2.南威软件在互动平台表示，公司AI短剧业务首部海外AI短剧已于8月制作完成。按照规划，2026年下半年计划出品25部高质量AI短剧，整体产能规划为年产超100部，公司海外短剧自有发行APP预计11月上线。</t>
+          <t>电网设备|公司主要从事高中低压开关成套设备、高中低压电器元件、母线槽、电气传动自动化装置、新能源装备等电工电器类产品的研发、生产与销售，先后为三峡工程、载人航天、奥运鸟巢、青藏铁路等多项国家重点工程提供优质产品。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>算力租赁, AI短剧</t>
+          <t>电网设备</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>算力工程</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>0.9126000000000001</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>工业和信息化部信息通信管理局局长谢存表示，截至2026年9月底，我国智能算力规模达2592EFLOPS，同比增长146%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh603629</t>
+          <t>sz002983</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>利通电子</t>
+          <t>芯瑞达</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>92.03</v>
+        <v>23.43</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.0048</v>
+        <v>10</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>算力租赁|公司AI算力业务主要是以云交付方式为客户提供AI算力产品，具体业务形态包括AI设备经销、算力优化、并机集群、算力云输出与持续运维支持与技术服务。公司2025年中报披露，可调度的算力资源用于客户算力云服务的规模逾29000P。</t>
+          <t>消费电子|公司已将AI+AR眼镜核心显示技术与光机组件布局定位为种子业务。公司计划在完成核心技术的进一步工程化验证后，推出具有竞争力的全彩MicroLED微显示与AR光机组件解决方案，为AI+AR眼镜产业化应用提供核心显示能力支撑。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>算力租赁</t>
+          <t>消费电子</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>0.1488</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>据Counterpoint预计，全球市场生成式AI手机渗透率将在2027年达到52%，端侧AI由高端卖点转为出厂标配。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sz002313</t>
+          <t>sz000530</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>日海智能</t>
+          <t>冰山冷热</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>9.68</v>
+        <v>9.49</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.965200000000001</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>机器人+端侧AI|1.公司通信模组可应用于送餐机器人、方舱机器人等设备。
-2.公司有智能模组产品，部分产品可以提供10-15TOPS左右的算力，满足智能终端对于中低算力边缘计算的需求。</t>
+          <t>冰雪产业|子公司冰山工程近年来承接了多项代表性工程，包括广州融创茂室内滑雪场项目、上海之星室内综合性冰雪场馆、陕西国际体育之窗等多个商业冰雪场馆项目。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>机器人, 端侧AI</t>
+          <t>冰雪产业</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>0.1488</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>据Counterpoint预计，全球市场生成式AI手机渗透率将在2027年达到52%，端侧AI由高端卖点转为出厂标配。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sh603236</t>
+          <t>sh601091</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>移远通信</t>
+          <t>沈鼓集团</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>83.72</v>
+        <v>21.58</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>9.998700000000001</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.989800000000001</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>端侧AI|公司的智能模组产品线提供4G、5G、AI算力等不同系列的20多款产品。其中智能AI模组可被广泛应用于工业质检、智能相机、户外机器人、边缘计算盒子、无人机、智慧零售等领域，助力不同行业的AI客户产品落地。</t>
+          <t>次新+核电|公司是我国通用机械工业的战略型、支柱型、领军型企业，承担为石油、化工、电力、天然气、新能源等领域提供重大技术装备和成套解决方案的国产化任务，是世界上少数能够自主设计制造大型复杂压缩机、高端核主泵等重大技术装备的制造厂商之一。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>端侧AI</t>
+          <t>次新, 核电</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>0.1488</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>据Counterpoint预计，全球市场生成式AI手机渗透率将在2027年达到52%，端侧AI由高端卖点转为出厂标配。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh688286</t>
+          <t>sz300839</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>敏芯股份</t>
+          <t>博汇股份</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>52.81</v>
+        <v>19.92</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>19.9955</v>
+        <v>20</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>端侧AI|公司的MEMS麦克风产品已经广泛应用在智能手机、平板电脑、笔记本电脑、智能家居、可穿戴设备等消费电子产品中，目前已使用公司产品的品牌包括华为、传音、小米、百度、阿里巴巴、联想、索尼、LG等。</t>
+          <t xml:space="preserve">石油化工|公司主营业务是对催化裂化后的燃料油即催化油浆进行深加工，采用自行研发的间歇式加工生产工艺、连续式生产工艺以及分子蒸馏和沉降等技术，对作为工业锅炉燃料的催化油浆综合再利用，研发、 生产和销售作为化工原料的沥青助剂、橡胶助剂、润滑油助剂等重芳烃产品和更为纯净的轻质燃料油。目前芳烃系列产品生产和使用主要区域集中在华东和华南地区。
+2024年1月31日公告，公司与宁波经济技术开发区管理委员会签订投资合作协议，拟在青峙化工新材料产业园投资建设160万吨/年新材料及高端化学品一体化项目。
+</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>端侧AI</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>0.637</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>据报道，今年前三季，福建对欧盟进出口突破2000亿元，达2070.6亿元，同比增长5.6%，占同期全省进出口总值的13.6%。</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>sh600802</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>福建水泥</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>福建+水泥|公司主要从事水泥及熟料的生产及销售，拥有7条新型干法熟料水泥生产线，具备年产熟料784.3万吨、水泥1164万吨。公司是福建地区产能规模最大的水泥制造企业，也是福建省水泥行业唯一的一家上市公司。</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>福建, 水泥</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>0.637</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>据报道，今年前三季，福建对欧盟进出口突破2000亿元，达2070.6亿元，同比增长5.6%，占同期全省进出口总值的13.6%。</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>sh601566</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">九牧王  </t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>9.9893</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>福建+纺织|国内商务休闲男装品牌的领先企业、国内男裤行业的龙头。主要从事男士商务休闲品牌服饰的生产和销售,主要产品包括男裤、茄克、衬衫、T恤和西装等。</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>福建, 纺织</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>物理AI</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>3.2684</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>当地时间10月20日至22日，英伟达GTC大会将在德国柏林举行，据官方介绍，大会将聚焦加速计算、智能体AI、物理AI、机器人、开源模型、AI基础设施等方向。</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>sz002835</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>同为股份</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>10.0282</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>物理AI|公司定位是面向全球的、可信赖的视频监控产品、技术和解决方案提供商，公司的文搜技术基于自研的多模态AI大模型，将自然语言与视觉系统深度融合，打造交互式操作界面；具备强大的开放语义理解能力，可理解复杂查询语句，如“穿红衣服、背黑包、推婴儿车的女性”，通过实时目标检测与跨模态特征匹配，将文本语义与视频图像精准对齐，实现人类语言与机器视觉的无缝“对话”。</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>物理AI</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>sz002724</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>海洋王</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>10.0432</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>军工|公司是武器装备科研生产三级保密资格单位，设有专门的军品事业部负责军品的销售。</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>sh600178</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东安动力</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>9.991899999999999</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>飞行汽车|2024年9月11日公司官微透露，东安动力高效增程发动机搭载小鹏汇天飞行汽车量产启动，此款产品为全球唯一能装下“飞机”的汽车提供“移动超充”，将成为公司市场开拓新的发力点。</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>飞行汽车</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>sz002076</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>星光股份</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>9.865500000000001</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>量子科技|子公司广州天芯量子拥有量子密钥分发、量子VPN加密、量子密钥管理等核心技术，已先后开发量子密钥分发产品、量子密钥管理终端、量子光交换机、量子波分复用终端、量子密钥应用设备、云防线及安全态势感知平台等产品。</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>量子科技</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>sz001216</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>华瓷股份</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>9.9956</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>6天3板</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>MLCC|子公司氧化锆粉体纯度最高可达99.995%，产品可适配新能源研磨、齿科陶瓷、MLCC等不同领域使用需求。</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>MLCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>sh600293</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>三峡新材</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>9.9537</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>并购重组|三峡新材公告称，公司拟通过发行股份及支付现金方式取得珠海市赛纬电子材料股份有限公司100%股权，并向包括控股股东当阳城投在内的不超过35名特定投资者发行股份募集配套资金，总额不超过10亿元。标的公司主营锂离子电池电解液的研发、生产和销售。</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>sh603332</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>苏州龙杰</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>9.965300000000001</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>业绩|苏州龙杰公告称，第三季度营业收入为6.59亿元，同比增长48.24%；净利润为6172.78万元，同比增长189.28%。前三季度营业收入为15.68亿元，同比增长36.91%；净利润为1.16亿元，同比增长113.12%。</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>业绩</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>sz002565</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>顺灏股份</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>8.48</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>9.987</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>商业航天+烟草|1.公司2025年6月以1.1亿元人民币投资北京轨道辰光科技有限公司，持股比例为19.30%。轨道辰光的主要业务是通过将算力卫星发射至晨昏轨道，组建太空数据中心，为客户提供算力服务，其经营范围包括微小卫星生产制造、微小卫星科研试验、互联网信息服务等。轨道辰光首颗试验星算力规模预计25p。
-2.公司的主要产品为真空镀铝纸及烟标产品等，主要下游客户为烟草生产企业和烟标印刷企业。</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>商业航天, 烟草</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>sz001201</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>东瑞股份</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>9.9931</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>猪肉|公司主营业务为生猪的养殖和销售，主要产品为商品猪、仔猪、种猪等。此外，公司自行生产生猪养殖所需的饲料，并有部分饲料对外销售。</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>猪肉</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>sz002591</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>恒大高新</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>算力服务器|公司构建"通信服务-算力支撑"协同生态，旗下宝乐互动在AI算力服务器业务已拥有完整产线。</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>算力服务器</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>sz002639</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>雪人集团</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>15.18</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>液冷+冰雪产业|1.公司制冷压缩机与机组可作为液冷服务器的配套冷源，为Facebook丹麦数据中心(液冷)提供第三代低充注的氨制冷技术。
-2.公司制冰、制冷设备已应用在冰雪运动赛事项目场馆内。近年来已参与多项冰雪项目建设，包括国家雪车雪橇中心、崇礼长城岭滑雪场等。</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>液冷, 冰雪产业</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>sh600202</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">哈空调  </t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>10.0791</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业注入预期|公司同一实控人哈尔滨国资委旗下马迭尔集团是其唯一文旅平台，旗下拳头品牌哈尔滨冰雪大世界、太阳岛风景区、亚布力等，或有资产注入预期。</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业注入预期</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>sz002811</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>郑中设计</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>24.16</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>10.0182</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>半导体+AI应用|1.参股深迪半导体是中国首家研发设计商用消费级和汽车级微机电系统（MEMS）陀螺仪系列惯性传感器的公司，产品主要应用于IOT，手机智能终端，智能家居，人工智能，工业和智能驾舱等领域，并为客户提供增值算法服务。
-2.子公司犀照科技打造的“IDEAFUSION兆材云库数字化平台”专为室内设计师提供一站式全流程数字化服务，目前已全面对外开放，为不同的设计单位提供SaaS化服务，促进项目高效落地。“IDEAFUSION兆材云库数字化平台”部分功能已经接入DeepSeek模型，包括物料顾问检索推理场景、黑洞文本重写场景 、知识库顾问场景。</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>半导体, AI应用</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>sz002112</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>三变科技</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>9.9848</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>IDC电源|公司主变产品已走进马斯克X AI超级计算机中心。</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>IDC电源</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>sh600838</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>上海九百</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>10.0484</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>零售|公司控股股东为上海九百（集团）有限公司。目前已经发展成为涉及洗涤化工产品生产销售及洗染服务、酒类产品批发等多种业态的综合性企业。</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>零售</t>
+          <t>石油化工</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2912,46 +2102,46 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sh600178</t>
+          <t>sz002724</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>东安动力</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz002724</t>
+          <t>sh603278</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>大业股份</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh603278</t>
+          <t>sz002076</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>星光股份</t>
         </is>
       </c>
     </row>
@@ -2961,12 +2151,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sz002929</t>
+          <t>sh600293</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>润建股份</t>
+          <t>三峡新材</t>
         </is>
       </c>
     </row>
@@ -2976,12 +2166,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz002696</t>
+          <t>sh601999</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>出版传媒</t>
         </is>
       </c>
     </row>
@@ -2991,12 +2181,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh603236</t>
+          <t>sh600838</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>移远通信</t>
+          <t>上海九百</t>
         </is>
       </c>
     </row>
@@ -3006,12 +2196,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sz001239</t>
+          <t>sh603330</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>永达股份</t>
+          <t>天洋新材</t>
         </is>
       </c>
     </row>
@@ -3021,12 +2211,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sz002242</t>
+          <t>sh600202</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>九阳股份</t>
+          <t xml:space="preserve">哈空调  </t>
         </is>
       </c>
     </row>
@@ -3036,117 +2226,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sz002076</t>
+          <t>sh603138</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>星光股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>sz002313</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>日海智能</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>sz002835</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>同为股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>sh603696</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>安记食品</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>sh603636</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>南威软件</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>sz002347</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>泰尔股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>sz002181</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>粤 传 媒</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>sh600293</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>三峡新材</t>
+          <t>海量数据</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="266" customWidth="1" min="10" max="10"/>
+    <col width="319" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -556,15 +556,15 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-1.969</v>
+        <v>3.6812</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -577,14 +577,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>14.51</v>
+        <v>15.96</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.0076</v>
+        <v>9.9931</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>5天5板</t>
+          <t>6天6板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -605,15 +605,15 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-1.969</v>
+        <v>3.6812</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -626,14 +626,14 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>83.39</v>
+        <v>91.73</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.998700000000001</v>
+        <v>10.0012</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>5天3板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -655,87 +655,95 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-1.969</v>
+        <v>3.6812</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>sh605488</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>福莱新材</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>10.0058</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>机器人|2024年12月26日公司在互动平台表示，柔性传感器是相对前沿技术的应用，未来的应用场景广泛，公司从当前的整体定位去看，主要有以下几个方向：人形机器人电子皮肤的应用、工业检测应用、智能穿戴、健康监测等领域，公司目前在和一些公司合作研发。</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>sz002535</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>林州重机</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>10.1818</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>军工+机器人|1.公司与多家大型军工集团建立了合作关系，并承接、交付了多批次的订单。
 2.公司曾于14年定增募资1.02亿元用于工业机器人产业化（一期）项目。</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>军工, 机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>机器人概念</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>-1.969</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>sh603028</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">赛福天  </t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>10.0709</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>机器人|在工业机器人领域，公司凭借对钢丝绳在升降与传动系统中核心技术的深度研发与创新应用，成功突破了传统业务的边界，开辟了全新的市场空间。通过为仓储智能机器人企业深圳市海柔创新科技有限公司提供高性能的升降配件解决方案，公司实现了从传统制造业向高端智能装备领域的跨越式发展。</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -746,36 +754,40 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-1.969</v>
+        <v>3.6812</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh603350</t>
+          <t>sh603028</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">安乃达  </t>
+          <t xml:space="preserve">赛福天  </t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>29.48</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+        <v>10.0515</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司参与了浙江智鼎机器人有限公司的增资扩股，智鼎机器人是智元机器人第一个独立运营的成熟具身智能机器人子公司。</t>
+          <t>机器人|在工业机器人领域，公司凭借对钢丝绳在升降与传动系统中核心技术的深度研发与创新应用，成功突破了传统业务的边界，开辟了全新的市场空间。通过为仓储智能机器人企业深圳市海柔创新科技有限公司提供高性能的升降配件解决方案，公司实现了从传统制造业向高端智能装备领域的跨越式发展。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -791,42 +803,46 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-1.969</v>
+        <v>3.6812</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz002249</t>
+          <t>sh603280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>南方路机</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>7.06</v>
+        <v>31.97</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9.9688</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+        <v>10.0138</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>机器人+稀土|1.公司前瞻技术研究院已设立前瞻技术研究项目--人形机器人电机项目，其中涉及包括无框力矩电机在内的多项研究。
-2.公司持有宁波科星材料科技有限公司51%的股份，宁波科星是一家专注于烧结钐钴、烧结钕铁硼永磁材料及产品研发和制造的高新技术企业，产品广泛应用于曳引机、汽车、电子信息、医疗、航空航天、国防等领域。</t>
+          <t>一带一路+机器人|1.公司主要从事工程搅拌设备、原生骨料加工处理设备、骨料资源化再生处理设备的设计、研发、生产和销售，目前公司已逐步建立出口经销渠道，产品销售业务拓展至俄罗斯、东南亚、非洲、澳大利亚等国家和地区。
+2.公司的建筑垃圾资源化处理设备的智能分拣机器人，能高效应对混合建筑垃圾、建筑混合废弃物、橡胶、木头等物料进行分拣，实现对建筑垃圾、装修垃圾等物料的分类回收和再利用，与公司其他产品均可广泛运用于灾后重建。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>机器人, 稀土</t>
+          <t>一带一路, 机器人</t>
         </is>
       </c>
     </row>
@@ -837,15 +853,15 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-1.969</v>
+        <v>3.6812</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -858,12 +874,16 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>54</v>
+        <v>64.8</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>机器人|公司的无框电机可应用于机器人、协作机器人及高端医疗器械等领域。</t>
@@ -882,36 +902,40 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-1.969</v>
+        <v>3.6812</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sh603089</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>正裕工业</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>12.03</v>
+        <v>11.89</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9.9634</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+        <v>9.9907</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
+          <t>机器人|公司布局机器人零部件赛道，致力于机器人用柔性触觉传感技术的研发、传感器的设计与制造、以及信号处理系统的开发与测试，已完成核心产品的技术攻关与样品研发。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -927,37 +951,40 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-1.969</v>
+        <v>3.6812</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh603528</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>7.4</v>
+        <v>13.23</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>9.955400000000001</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+        <v>9.975100000000001</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>机器人|1.公司已开展多项人工智能驾考新技术研究，包括基于机器视觉的驾驶人注意力分配识别、基于机器视觉的道路环境目标识别、基于激光雷达的目标探测技术等。
-2.公司通过珠海星芯投资基金参与了众擎机器人科技有限公司Pre-A++轮融资，并持有其1.57%的股份。</t>
+          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -973,41 +1000,46 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-1.969</v>
+        <v>3.6812</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh603089</t>
+          <t>sh603528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>正裕工业</t>
+          <t>多伦科技</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>10.81</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9.9695</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司布局机器人零部件赛道，致力于机器人用柔性触觉传感技术的研发、传感器的设计与制造、以及信号处理系统的开发与测试，已完成核心产品的技术攻关与样品研发。</t>
+          <t>AI+机器人|1.公司已开展多项人工智能驾考新技术研究，包括基于机器视觉的驾驶人注意力分配识别、基于机器视觉的道路环境目标识别、基于激光雷达的目标探测技术等。
+2.公司通过珠海星芯投资基金参与了众擎机器人科技有限公司Pre-A++轮融资，并持有其1.57%的股份。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>AI, 机器人</t>
         </is>
       </c>
     </row>
@@ -1018,41 +1050,46 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-1.969</v>
+        <v>3.6812</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz301023</t>
+          <t>sz001283</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>奕帆传动</t>
+          <t>豪鹏科技</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>32.48</v>
+        <v>57.27</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>19.9852</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+        <v>10.0077</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>机器人|2024年11月22日公司接受调研时表示，公司的电机可以运用在不同的应用场景，不仅限于“人形机器人”，前期会主要运用在桁架机器人、协作机器人、医疗、仪表仪器、云台等领域。目前，公司正处于产品研发设计的关键阶段，预计在明年，会通过验证并小批量供货。</t>
+          <t>机器人+AI PC|1.公司已向某“AI+儿童陪伴”创新头部机器人品牌厂商完成电池产品送样，整体进度处于行业第一梯队。与此同时，公司已与某高水平机器人企业达成战略合作关系，未来将通过深度合作，共同推动包含人形机器人/机器狗在内的相关机器人应用领域的技术创新和市场拓展。
+2.公司是部分国际知名笔记本品牌客户的电池主力供应商之一，在电池能量密度、倍率性能、散热及温升控制等方面具备较大竞争优势和深厚的技术积累，目前公司已向部分客户供应AI PC机型配套的电池产品。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>机器人, AI PC</t>
         </is>
       </c>
     </row>
@@ -1063,28 +1100,28 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-1.969</v>
+        <v>3.6812</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603370</t>
+          <t>sh600506</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>华新精科</t>
+          <t>统一股份</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>28.71</v>
+        <v>16.83</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>10</v>
@@ -1092,12 +1129,13 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司铁芯产品下游应用广阔，可应用于机器人关节等相关部位的电机。</t>
+          <t>液冷+机器人|1.公司成功开发出一系列具有国际先进水平的浸没式绝缘冷却工艺，包括国际上被少数发达国家企业垄断的电子氟化液产品，实现了此类产品的国产替代。公司的浸没式冷却工艺能广泛应用于高密度数据中心、超算智算中心、大功率充电桩和储能系统。
+2.公司自主研发工业机器人减速机的150号合成齿轮油产品，经测试，与进口齿轮油产品性能参数相当。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>液冷, 机器人</t>
         </is>
       </c>
     </row>
@@ -1108,959 +1146,3243 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-1.969</v>
+        <v>3.6812</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>英伟达宣布升级Isaac通用机器人开发平台，推出新的人形机器人参考框架、仿真工作流及数据工具，旨在加速通用机器人开发。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sh603728</t>
+          <t>sz002354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>鸣志电器</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>54.47</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>9.995999999999999</v>
+        <v>10</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司的无刷电机模组、无齿槽空心杯电机模组、无框和交流伺服电机及驱动与控制系统、精密丝杠传动模组、轮毂/轮边电机模组、旋转/顶升机构模组等的在机器人的各主要运动控制功能模块中广泛适用。</t>
+          <t>机器人+短剧|1.在空间智能MaaS平台基础上，公司融合数据采集硬件、多模态数据处理技术、云边端算力，着力推进具身智能通用平台Behavision的建设，打造通用的大脑+小脑开发平台，以强大算力、高集成度和快速部署等优势，打造软硬一体、基垂融合的智能体新样板，为空间计算、具身智能、人形机器人等多场景应用提供通用智能化解决方案。
+2.在内容生产领域，公司打造影视级AI长视频创编平台CineART，面向Token经济发展带来的智能内容生产需求，积极拓展AI长视频、短剧和信息流广告等应用场景。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>机器人, 短剧</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>一带一路</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-1.8697</v>
+        <v>3.6812</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>乌克兰总统泽连斯基当地时间10月21日在接受采访时表示，乌方可在保留至少75%领土控制权的基础上达成和平协议。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz001360</t>
+          <t>sh603677</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>南矿集团</t>
+          <t>奇精机械</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>18.58</v>
+        <v>16.3</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.0059</v>
+        <v>9.986499999999999</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>一带一路+工程机械|公司主营业务为砂石骨料和金属矿山相关的破碎、筛分设备的研发、设计、生产、销售及后市场服务，是国内技术领先的中高端矿机装备供应服务商之一。公司下游市场之一的砂石骨料行业长期受益于“一带一路”振兴战略。公司的主要海外销售区域分布在南非、美国、俄罗斯、刚果金、纳米比亚等国家地区。</t>
+          <t>机器人|2026年4月30日公司在互动平台表示，公司尚在开拓的工业机器人零部件产品为减速器中的钢轮，现处于小批交样阶段。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>一带一路, 工程机械</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>一带一路</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-1.8697</v>
+        <v>3.6812</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>乌克兰总统泽连斯基当地时间10月21日在接受采访时表示，乌方可在保留至少75%领土控制权的基础上达成和平协议。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz002097</t>
+          <t>sh603337</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>山河智能</t>
+          <t>杰克科技</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>7.26</v>
+        <v>39.26</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10</v>
+        <v>10.0028</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>一带一路+机器人|1.公司主要产品包括挖掘机械、桩工机械、高空机械、矿山设备、 应急救援设备、油气管道设备、铁路维保设备及绿色能源开采装备。公司助力一带一路，成功参与泰国“中泰铁路项目”、马来西亚“东马铁路”、秘鲁安第斯高速公路、尼日利亚卡卡铁路、哥伦比亚波哥大地铁等境外项目。
-2.公司无人化产品包括遥控挖掘机、遥控装载机、应急救援机器人、破拆机器人、无人矿卡等工程机械类产品，与中科慧拓等多家科研单位联手打造的智能运载机器人SWK90EA载山CarMoy，是我国首台套具备产业化标准要求以及完全自主知识产权的新能源运载装备。</t>
+          <t>机器人|公司在2024年年报中透露，公司高端产品研发取得里程碑进展，高端AI缝纫机原型样机成功落地，“杰克1号”人形机器人、无人模板机等“机器人+AI人工智能+缝制机械”多技术融合的智能高端产品初具雏形。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>一带一路, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>一带一路</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-1.8697</v>
+        <v>3.6812</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>乌克兰总统泽连斯基当地时间10月21日在接受采访时表示，乌方可在保留至少75%领土控制权的基础上达成和平协议。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh603280</t>
+          <t>sh603081</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>南方路机</t>
+          <t>大丰实业</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>29.06</v>
+        <v>10.65</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.9924</v>
+        <v>10.0207</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>一带一路+机器人|1.公司主要从事工程搅拌设备、原生骨料加工处理设备、骨料资源化再生处理设备的设计、研发、生产和销售，目前公司已逐步建立出口经销渠道，产品销售业务拓展至俄罗斯、东南亚、非洲、澳大利亚等国家和地区。
-2.公司的建筑垃圾资源化处理设备的智能分拣机器人，能高效应对混合建筑垃圾、建筑混合废弃物、橡胶、木头等物料进行分拣，实现对建筑垃圾、装修垃圾等物料的分类回收和再利用，与公司其他产品均可广泛运用于灾后重建。</t>
+          <t>机器人|公司于2025年3月23日与智元机器人签订《战略合作协议》，双方拟共同投资设立合资公司（公司持股85%），聚焦多模态交互系统研发与智能终端场景化应用，打造"技术+场景"融合创新平台，构建基于语音、视觉、触觉、手势等多模态交互模型，研发出匹配文娱旅体商场景需求的具身智能产品并实现商业化落地。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>一带一路, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>一带一路</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1.8697</v>
+        <v>3.6812</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>乌克兰总统泽连斯基当地时间10月21日在接受采访时表示，乌方可在保留至少75%领土控制权的基础上达成和平协议。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz002307</t>
+          <t>sz301699</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>北新路桥</t>
+          <t>洛轴股份</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3.39</v>
+        <v>33.42</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.0649</v>
+        <v>20</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>一带一路+基建|公司已在一带一路沿线7个国家设立办事处（巴基斯坦、蒙古国、柬埔寨、阿富汗、哈萨克斯坦、塔吉克斯坦、吉尔吉斯斯坦）。</t>
+          <t>次新+机器人|公司针对国产机器人产业发展需求，开展机器人专用精密轴承设计和制造、测试、寿命试验等技术研究，研制出了薄壁等截面、交叉圆柱滚子两种系列轴承以及RV减速器、谐波减速器专用系列精密轴承。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>一带一路, 基建</t>
+          <t>次新, 机器人</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-2.5208</v>
+        <v>3.6812</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10月19日珠海航展门票正式开售，本次航展首次开放海上展区，包括海上装备、无人机在内的一批新装备、新技术将集中亮相。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sz002724</t>
+          <t>920091.BJ</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>大鹏工业</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>11.21</v>
+        <v>33.51</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10.0098</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5天5板</t>
-        </is>
-      </c>
+        <v>29.9845</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>军工|公司是武器装备科研生产三级保密资格单位，设有专门的军品事业部负责军品的销售。</t>
+          <t>机器人|公司凭借持续多年的研发投入与项目经验积累，目前已掌握应用于机加工生产线、装配线的主流精密清洗技术，对设备结构、功能实现、自动化控制、工业机器人集成和柔性化制造等领域理解深刻。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-2.5208</v>
+        <v>3.6812</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10月19日珠海航展门票正式开售，本次航展首次开放海上展区，包括海上装备、无人机在内的一批新装备、新技术将集中亮相。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh600698</t>
+          <t>sh600215</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>湖南天雁</t>
+          <t xml:space="preserve">派斯林  </t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>7.59</v>
+        <v>6.34</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10</v>
+        <v>10.0694</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>军工|中国兵器装备集团旗下上市公司，公司拥有多个“全国第一”称号：第一个生产装甲车、坦克等军用大功率柴油发动机涡轮增压器、第一个研发并生产用于装甲车、坦克等冷却风机等。</t>
+          <t>机器人|公司深入掌握工业机器人系统集成的设计、研发、制造、集成以及调试等全面技术能力，具有领先的机械设计能力、丰富的工艺经验、在线视觉智能引导定位与监测技术及提供智能一体化解决方案等技术优势。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>军工</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-3.1631</v>
+        <v>3.6812</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>市场调查机构集邦咨询（TrendForce）援引多方报道称，预估2026年第四季度DRAM合约价格环比上涨约20%。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh603330</t>
+          <t>sz002009</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>天洋新材</t>
+          <t>天奇股份</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>11.1</v>
+        <v>17.3</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.0099</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>9.9809</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>半导体材料|公司电子胶板块光模块透镜固定用胶、底填胶等产品已经进入半导体及汽车电子领域小批量供货。</t>
+          <t>锂电+机器人|1.公司全资孙公司锂致实业是一家碳酸锂生产商，主要生产电池级碳酸锂、工业级碳酸锂、氢氧化锂等锂盐产品和硫酸钠等，同时为用户提供技术咨询和支持服务。
+2.全资子公司无锡天捷自动化物流设备有限公司总承包建造了优必选位于昆明、深圳、重庆、贵阳等多地的人形机器人装配线项目，其中昆明工厂一期项目于2020年建成投产，为全国首条AI智能化人形机器人的装配线。
+2025年10月31日公告，公司与富士康新能源汽车产业发展（河南）有限公司签署《战略合作框架协议》，双方拟共同推动具身智能机器人在工业场景的深度应用与技术创新。双方将合作共建高标准的机器人数据采集中心与机器人实训中心，形成从数据生成、采集、训练到场景验证的完整技术闭环。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>半导体材料</t>
+          <t>锂电, 机器人</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-3.1631</v>
+        <v>3.6812</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>市场调查机构集邦咨询（TrendForce）援引多方报道称，预估2026年第四季度DRAM合约价格环比上涨约20%。</t>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh603933</t>
+          <t>sz002026</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>睿能科技</t>
+          <t>山东威达</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>19.04</v>
+        <v>11.04</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.994200000000001</v>
+        <v>9.9602</v>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>机器人|相继收购了上海拜骋电器有限公司、济南第一机床有限公司和苏州德迈科电气有限公司等，形成了精密机械零部件制造、中高档数控机床制造和机器人自动化三大互补的产业板块。</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>sz000559</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>万向钱潮</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司在机器人领域主要布局精密轴承和丝杠，目前相关产品尚处于开发验证阶段。</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>sh688071</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>华依科技</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司的惯导产品可以应用于人形机器人上，用于测量人形机器人自身的运动状态和姿态。</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>sh603901</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>永创智能</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>10.0228</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司在通过自主研发图像识别、视觉检测工业机器人等技术集成于公司智能包装生产线系列产品，提高智能包装生产线的柔性化和智能化；同时公司进一步完善标准包装设备产品的模块化分解，缩短标准包装设备产品的研发设计周期。</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>sz000810</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>创维数字</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>9.989000000000001</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司的EGO数据采集设备面向具身智能与机器人训练场景，已于海内外市场形成销售。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>sz300307</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>慈星股份</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司控股子公司东莞市中天自动化技术有限公司致力于从方案设计、精密加工、组装调试、现场实施以及售后支持等方面为客户提供优质产品和全方位的服务，主要从事3C行业、锂电行业、光伏行业，为客户提供标准化和定制化的自动化设备及整体工厂自动化解决方案，目前公司已经成为比亚迪、华为等知名品牌的供应商。</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>sz002979</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>雷赛智能</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>9.9939</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司在人形机器人领域定位是伺服控制产品与解决方案提供商、为众多整机厂家提供系列化伺服控制核心部件和模组级解决方案。公司从2018年起持续耕耘机器人行业（AGV/AMR、协作机器人等），并于2023年底成功研发出高密度无框力矩电机、CD伺服驱动器、中空编码器、空心杯电机及配套的微型伺服系统等核心产品。</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>sh688836</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>宇树科技-W</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>624</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>机器人|宇树科技是国际领先的高性能通用机器人企业，专注于高性能通用人形机器人、四足机器人、机器人组件及具身智能模型的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>sz002931</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>锋龙股份</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>9.994300000000001</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>优必选入主|锋龙股份公告称，本次股份协议转让已完成，公司控股股东变更为优必选，实际控制人变更为周剑。根据中国证券登记结算有限责任公司于2026年3月12日出具的《证券过户登记确认书》，本次协议转让事项过户登记手续已办理完毕，过户日期为2026年3月11日，过户股数为6552.99万股，占公司股份总数的29.99%，股份性质为无限售流通股。</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>优必选入主</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>sz000700</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>模塑科技</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>机器人|2025年12月16日公告，公司与国内某机器人企业签订零部件采购框架协议，并获得人形机器人外覆盖件小批量采购订单。</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>sh603448</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>天博智能</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>9.9941</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司将汽车传感器领域的算法、技术等拓展至具身智能领域，已开始为珞石（山东）机器人集团股份有限公司等机器人企业供应六维力传感器产品。</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>sz002380</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>科远智慧</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>10.0199</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>机器人+数据要素|1.以自主研发的HMI、PLC、运动控制器、伺服、变频器、机器人等产品为基础，为客户提供完整解决方案。
+2.公司研发的工业数据融合智能体是一款专为制造业设计的工业级数据融合与智能处理平台。该平台深度融合了异构数据智能融合、统一数据模型构建、智能数据分析与优化、业务流程支持等功能。</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 数据要素</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>sh603286</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>日盈电子</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>10.0086</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司看好汽车零部件企业进军人形机器人领域的产业机遇，积极投入以柔性触觉传感电子皮肤为代表的新产品开发，公司压阻式的电子皮肤样品已研发成功。</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>sz002747</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>埃斯顿</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>9.9887</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司参股的酷卓科技从事人形机器人部件及算法研发，已发布第一代人形机器人Codroid 01。</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>3.6812</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>sh688686</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奥普特  </t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>19.9969</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司专注于机器视觉核心软硬件的研发、生产和销售，为客户提供完整的机器视觉解决方案。机器视觉为机器人提供了精确的视觉感知能力，使其能够识别和处理各种物体；而机器人则利用这些视觉信息执行复杂的任务。</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>2.3967</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>三星电子及SK海力士正推进其中国厂房生产逾200层NAND晶片，将中国厂房技术提升至韩国厂房的水平。目前三星位于西安的工厂占公司全球NAND产量约40%，公司目标将目前生产约200层NAND晶片。</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>sh603933</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>睿能科技</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>9.979000000000001</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>机器人+半导体|1.公司RA1、RA3系列伺服驱动器和MC2、MA3系列伺服电机已应用到机器人领域，包括不同载荷的四关节、六关节等工业机器人和协作机器人。
 2.公司分销的主要产品包括微控制器芯片、功率器件及模组、电源管理及驱动芯片、模拟及混合信号芯片、存储芯片等。</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>机器人, 半导体</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>2.3967</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>三星电子及SK海力士正推进其中国厂房生产逾200层NAND晶片，将中国厂房技术提升至韩国厂房的水平。目前三星位于西安的工厂占公司全球NAND产量约40%，公司目标将目前生产约200层NAND晶片。</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>sz002077</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>大港股份</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>10.0084</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>先进封装|控股孙公司苏州科阳是少数掌握晶圆级芯片封装技术的公司之一，掌握了晶圆级芯片封装的TSV、micro-bumping（微凸点）和RDL等先进封装核心技术</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>先进封装</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>2.3967</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>三星电子及SK海力士正推进其中国厂房生产逾200层NAND晶片，将中国厂房技术提升至韩国厂房的水平。目前三星位于西安的工厂占公司全球NAND产量约40%，公司目标将目前生产约200层NAND晶片。</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>sz001298</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>好上好</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>10.0127</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>半导体+机器人|1.公司是国内知名的电子元器件分销商，目前销售的存储芯片主要有晶豪（ESMT）、复旦微、Giantec（聚辰）、GigaDevice （兆易创新）等品牌的DRAM、eMMC、FLASH等存储器。
+2.公司完成了音视频、接口、存储、连接、传感、电源等产品在多场景（无人机/扫地机/割草机）及多形态（四足/人形/外骨骼/协作）机器人的产线布局。</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>半导体, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2.3967</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>三星电子及SK海力士正推进其中国厂房生产逾200层NAND晶片，将中国厂房技术提升至韩国厂房的水平。目前三星位于西安的工厂占公司全球NAND产量约40%，公司目标将目前生产约200层NAND晶片。</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>sz301660</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>粤芯半导-U</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>20.0143</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>次新+半导体|粤芯半导体是专注于12英寸特色工艺晶圆代工的集成电路制造企业，致力于为境内外芯片设计企业提供晶圆代工服务和特色工艺解决方案，拥有两座12英寸晶圆厂、已实现产能6.33万片/月，工艺平台覆盖模拟和数模混合芯片及功率器件。</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>次新, 半导体</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>2.3967</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>三星电子及SK海力士正推进其中国厂房生产逾200层NAND晶片，将中国厂房技术提升至韩国厂房的水平。目前三星位于西安的工厂占公司全球NAND产量约40%，公司目标将目前生产约200层NAND晶片。</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>sh603160</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>汇顶科技</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>10.0097</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>半导体|公司主要产品为电容触控芯片和指纹识别芯片，除此之外为固定电话芯片产品。</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>2.3967</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>三星电子及SK海力士正推进其中国厂房生产逾200层NAND晶片，将中国厂房技术提升至韩国厂房的水平。目前三星位于西安的工厂占公司全球NAND产量约40%，公司目标将目前生产约200层NAND晶片。</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>sh688368</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>晶丰明源</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>105.96</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>模拟芯片|公司是国内领先的电源管理驱动类芯片设计企业之一，主营业务为电源管理驱动类芯片的研发与销售，自成立以来即专注于电源管理驱动类芯片。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>模拟芯片</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>9.494299999999999</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>据《科创板日报》，在2026世界物理AI大会暨宇树合作伙伴生态大会上，宇树科技创始人王兴兴表示，随着GPT-6的发布，目前物理AI已经看到被击穿的苗头，很可能最近1-2年或2-3年。</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>sz301313</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>凡拓数创</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>5天3板</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>物理AI|公司形成了以数字孪生引擎、低代码平台、AI算法、行业小模型、IoT、大数据、知识图谱、物理AI工具链为核心的完整技术底座，并构建起“物理AI 3D数字孪生”核心技术体系。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>9.494299999999999</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>据《科创板日报》，在2026世界物理AI大会暨宇树合作伙伴生态大会上，宇树科技创始人王兴兴表示，随着GPT-6的发布，目前物理AI已经看到被击穿的苗头，很可能最近1-2年或2-3年。</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>sz300296</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>利亚德</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>物理AI|子公司利亚德（北京）演艺文化有限公司致力于将LED科技应用于文化创意领域，为文艺演出、电视综艺节目、会展及其他各类舞台活动提供基于LED技术的舞台视觉效果工程技术服务，以及相关舞台视效产品的研发、生产和销售。</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>9.494299999999999</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>据《科创板日报》，在2026世界物理AI大会暨宇树合作伙伴生态大会上，宇树科技创始人王兴兴表示，随着GPT-6的发布，目前物理AI已经看到被击穿的苗头，很可能最近1-2年或2-3年。</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>sz002421</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>达实智能</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>9.9359</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>物理AI|达实智能将AI技术嵌入物联网平台，通过平台使AI具备对物理世界的感知与执行能力。平台V5版本基于判别式AI打造智慧冷源应用，V6版本实现了设备及能源诊断和AI视觉分析功能。V7版本首次接入大模型，诞生了基于生成式AI的智能体，V7.1版本迎来AI智能体2.0升级版本，为智慧园区打造了专属的超级智能体。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>9.494299999999999</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>据《科创板日报》，在2026世界物理AI大会暨宇树合作伙伴生态大会上，宇树科技创始人王兴兴表示，随着GPT-6的发布，目前物理AI已经看到被击穿的苗头，很可能最近1-2年或2-3年。</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>sh603859</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>能科科技</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>物理AI|公司精准卡位具身智能“大脑”角色，构建起从“感知—决策—执行—评估”的物理AI全链条能力，成功打造可独立运行的“端侧单体大脑”，实现在工业及特种场景下的深度应用，并逐步建立本体小脑到应用大脑的中间层链接标准。</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>9.494299999999999</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>据《科创板日报》，在2026世界物理AI大会暨宇树合作伙伴生态大会上，宇树科技创始人王兴兴表示，随着GPT-6的发布，目前物理AI已经看到被击穿的苗头，很可能最近1-2年或2-3年。</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>sh603466</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风语筑  </t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>10.0375</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>物理AI|公司投资松应科技，围绕物理AI仿真引擎开展技术合作；与松应科技共同设立控股子公司公司风应科技，聚焦物理AI仿真环境构建、合成数据生成及相关训练基础设施等方向开展业务。</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>2.2483</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>A股上市公司三季报披露进入加速期，绩优股获青睐。</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>sz002982</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>湘佳股份</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>10.0249</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>业绩|湘佳股份公告称，第三季度营业收入为13.15亿元，同比增长15.48%；归属于上市公司股东的净利润为7597.44万元，同比增长360.44%。前三季度营业收入为36.31亿元，同比增长10.98%；归属于上市公司股东的净利润为6387.96万元，同比增长185.84%。</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>2.2483</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>A股上市公司三季报披露进入加速期，绩优股获青睐。</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>sz300584</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>海辰药业</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>20.015</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>业绩|公司2026年1-9月实现营业收入6.15亿元，同比增长30.49%；归母净利润6225.56万元，同比增长90.51%。报告期内，公司业绩增长主要受益于锂电池电解液添加剂业务量产后收入大幅增加，同时公司优化研发项目布局、缩减市场相关费用投入，盈利能力持续提升。</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>2.2483</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>A股上市公司三季报披露进入加速期，绩优股获青睐。</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>sz001328</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>登康口腔</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>10.0169</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>业绩|公司2026年1-9月实现营业收入14.25亿元，同比增长16.05%；归母净利润约1.61亿元，同比增长18.32%。</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>2.2483</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>A股上市公司三季报披露进入加速期，绩优股获青睐。</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>sh603713</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>密尔克卫</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>66.66</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>业绩|公司2026年1-9月实现营业收入125.89亿元，同比增长17.98%；归母净利润约5.93亿元，同比增长12.96%。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>2.2483</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>A股上市公司三季报披露进入加速期，绩优股获青睐。</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>sz301101</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>明月镜片</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>35.34</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>业绩|公司2026年1-9月实现营业收入7.30亿元，同比增长16.54%；归母净利润约1.76亿元，同比增长18.29%。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>数据要素</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
-        <v>-3.9425</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B53" s="2" t="n">
+        <v>3.1121</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D53" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sh603721</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>中广天择</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>10.0051</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>AI漫剧+数据要素|1.公司积极布局纪实IP、微短剧、AI漫剧、中长剧等多元内容赛道，构建多层次、差异化的内容供给与运营体系。在短剧及中长剧领域，公司以制作、投资与分账发行相结合的模式稳步推进项目落地，内容制作与市场运营能力持续提升，优质项目储备不断充实。
+2.控股的湖南马栏山天择微链科技有限公司全面推进的“中国V链”, 致力打造运营全域数字资产保护及交易平台，平台利用区块链技术，将权利人提交的版权内容进行上链存证，对资产的版权进行保护。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>AI漫剧, 数据要素</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>数据要素</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>3.1121</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>sh688787</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>海天瑞声</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>数据要素|‌海天瑞声深耕AI训练数据领域超过20年，已形成覆盖数据采集、处理、标注、治理到应用落地的完整能力体系，服务全球上千家科技企业与科研机构 。‌‌‌</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>数据要素</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>数据要素</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>3.1121</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sh603171</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>税友股份</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>数据要素|公司积极布局业财税大数据商业服务业务，探索财税数据要素的多场景应用、多主体复用，重点布局“数据要素×金融服务”“数据要素×商贸流通”等场景的新产品和新服务。公司基于高质量数据底座，利用数据、算法的结合，将数据及数据模型服务运用于交易撮合、风险评估等场景，以提高客户营销及服务场景的效率和准确性，并有效降低交易风险。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>数据要素</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>数据要素</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>3.1121</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>920207.BJ</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>众诚科技</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>数据要素|公司通过平台升级，实现数据集成管理、数据交换管理、实时计算存储、元数据管理、数据标准管理、数据质量管理、主数据管理、数据资产管理、数据安全管理、数据生命周期管理十大模块的融合，各模块可独立或任意组合使用，打通数据治理各个环节，可快速满足政府、企业用户各类不同的数据治理场景需求。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>数据要素</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>金融科技</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>4.8231</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>业内人士认为，A股上市券商前三季度净利润有望在第三季度承压的情况下仍保持增长。</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>sh601519</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大智慧  </t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>9.988099999999999</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>互联网金融|公司是国内领先的互联网金融信息服务提供商，主要业务聚焦在证券信息服务平台、大数据及数据工程服务和境外业务三大板块。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>互联网金融</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>金融科技</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>4.8231</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>业内人士认为，A股上市券商前三季度净利润有望在第三季度承压的情况下仍保持增长。</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>sz301428</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>世纪恒通</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>金融科技|公司为保险及银行等金融机构、电信运营商、高速集团等大型企业客户提供整合后的车主信息服务资源，客户的车主用户可通过微信平台、小程序、APP、H5页面等享有车主信息服务，包括ETC办理、代驾、停车及汽车美容、保养、安全检测、年检代办等各项专享优惠及便捷服务。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>金融科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>金融科技</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>4.8231</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>业内人士认为，A股上市券商前三季度净利润有望在第三季度承压的情况下仍保持增长。</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>sz300561</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>汇金科技</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>金融科技+AI|1.公司是从事软件开发和系统集成信息技术服务的专业型企业，面向金融机构、政府部门、企事业单位提供一体化解决方案。
+2.公司人工智能技术在人脸识别、活体检测、语音处理、指静脉识别等方向有应用案例。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>金融科技, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>2.7819</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>财政部等三部门发文明确，自2026年9月1日起至2028年12月31日，对钠离子电池、固态电池等免征消费税，定向扶持新技术路线。</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>sz001301</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>尚太科技</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>45.71</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>10.012</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>固态电池|公司已获得多件与硅基负极材料等与固态电池相关的发明专利。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>2.7819</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>财政部等三部门发文明确，自2026年9月1日起至2028年12月31日，对钠离子电池、固态电池等免征消费税，定向扶持新技术路线。</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>sz002812</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>恩捷股份</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>10.0117</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>固态电池|公司已与北京卫蓝和天目先导成立了合资公司江苏三合，进行半固态电解质涂层隔膜及多种高端涂层隔膜的研发、生产。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>固态电池</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>2.7819</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>财政部等三部门发文明确，自2026年9月1日起至2028年12月31日，对钠离子电池、固态电池等免征消费税，定向扶持新技术路线。</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>sz001359</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>平安电工</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>PCB+固态电池|1.公司玻纤布产品主要分为工业级玻纤布和电子级玻纤布。其中电子级玻纤布可使基板具备优质的电气特性及机械强度，是主要用于印制电路覆铜板的绝缘增强材料。
+2.公司对固态电池行业的发展动态和趋势保持密切关注。云母是天然的高绝缘材料，耐高温、耐绝缘等特性可以在固态电池、人形机器人中有潜在的应用价值。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>PCB, 固态电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>商业零售</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>在10月22日国新办新闻发布会上，商务部市场运行和消费促进司司长杨沐表示，今年前三季度，服务零售额同比增长5%，比商品零售额高出4个百分点，预计未来一段时期，商品消费增速将保持平稳增长。</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>sh600838</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>上海九百</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>零售|公司控股股东为上海九百（集团）有限公司。目前已经发展成为涉及洗涤化工产品生产销售及洗染服务、酒类产品批发等多种业态的综合性企业。</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>商业零售</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>在10月22日国新办新闻发布会上，商务部市场运行和消费促进司司长杨沐表示，今年前三季度，服务零售额同比增长5%，比商品零售额高出4个百分点，预计未来一段时期，商品消费增速将保持平稳增长。</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>sh600865</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>百大集团</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>9.9602</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>零售|公司主营业务为商品零售，主要业态为百货商场，旗下杭州百货大楼是公司最主要的营收和利润来源，是杭州市区域龙头百货商场之一。</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>商业零售</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>在10月22日国新办新闻发布会上，商务部市场运行和消费促进司司长杨沐表示，今年前三季度，服务零售额同比增长5%，比商品零售额高出4个百分点，预计未来一段时期，商品消费增速将保持平稳增长。</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>sh600785</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>新华百货</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>9.9825</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>零售|公司是宁夏乃至西北地区较大的商业零售企业，主要从事商业零售、物流和商业物业出租业务，零售业务主要涉及百货商场、综合购物中心、超市连锁、电器及通信连锁。</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>网络安全</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>3.5051</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>广泛应用于网站和网络应用开发的编程语言PHP被曝出存在严重网络安全漏洞，需要进行紧急安全更新，亚洲多国政府与企业当前正紧急排查并加固旗下网站。</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>sh601999</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>出版传媒</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="H23" s="2" t="n">
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>sz300369</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>绿盟科技</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>19.9795</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>网络安全+AI|2024年公司推出了自主研发的“风云卫AI安全能力平台”，该平台融合大模型、小模型、知识图谱等核心能力，依托公司二十余年的网络安全研究积累与攻防对抗实践，构建了开放式PaaS架构，广泛适配于安全运营、检测响应、攻防实战等场景。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>网络安全, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>网络安全</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>3.5051</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>广泛应用于网站和网络应用开发的编程语言PHP被曝出存在严重网络安全漏洞，需要进行紧急安全更新，亚洲多国政府与企业当前正紧急排查并加固旗下网站。</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>sz002439</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>启明星辰</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>10.0146</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>网络安全+AI|1.公司是信息安全行业龙头，为政企用户提供网络安全软/硬件产品、安全管理平台、安全服务与解决方案。
+2.公司已完成了“安星”智能体与DeepSeek大模型的全面对接，并应用到安全运营、威胁检测、威胁情报、数据安全等全业务场景中，实现了安全智能化能力的再升级。</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>网络安全, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>消费电子</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>2.9914</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>机构研报指出，AI眼镜正处于由产品验证向快速放量过渡的关键阶段，科技巨头争相布局AI眼镜业务，预计该行业2025—2030年复合增速约60%。</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>sh603341</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>龙旗科技</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>9.9925</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>端侧AI|公司为全球头部消费电子品牌商和全球领先科技企业提供专业的智能产品综合服务，形成了涵盖智能手机、平板电脑、AI PC、AIoT产品及汽车电子等智能产品布局。</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>端侧AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>消费电子</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>2.9914</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>机构研报指出，AI眼镜正处于由产品验证向快速放量过渡的关键阶段，科技巨头争相布局AI眼镜业务，预计该行业2025—2030年复合增速约60%。</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>sz002241</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>歌尔股份</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>9.995200000000001</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>端侧AI+机器人|1.公司在与AR和智能眼镜相关的光机模组领域内有广泛的技术布局，包括应用DLP，LCoS，Micro-OLED，Micro-LED等不同微显示技术的相关产品。
+2.公司的扬声器、传感器、光学器件、精密结构件等产品均可以应用于多种类的终端硬件设备中，公司在机器人相关业务领域内有所布局，并已在智能制造领域内广泛应用机器视觉、机器人等相关技术。</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>端侧AI, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>2.906</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>国家广播电视总局印发《广播电视和网络视听“十五五”规划》。《规划》总体目标为到2030年，广电媒体全面挺进互联网主战场（包括“十五五”期间推出优秀电视剧（网络剧）100部；推出优秀微短剧500部。</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>sz002343</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>慈文传媒</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="H70" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>数据要素+AI短剧|1.子公司北方国家版权交易中心的主营业务主要是版权及知识产权的登记（确权）、交易、开发及会展培训等。
-2.公司所属音像社、电子社等公司，参与制作视频短剧等作品，部分制作中使用AI技术，作品在学习强国、红果等平台播放。</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>数据要素, AI短剧</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>数据要素</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>-3.9425</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>短剧|公司已形成了以自有IP为核心资源，以影视IP内容投资、开发、制作及发行为核心业务，积极延伸拓展电影、网络电影、网络微短剧、互动剧、小程序短剧、IP线下衍生等相关品类的业务体系。</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>2.906</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>国家广播电视总局印发《广播电视和网络视听“十五五”规划》。《规划》总体目标为到2030年，广电媒体全面挺进互联网主战场（包括“十五五”期间推出优秀电视剧（网络剧）100部；推出优秀微短剧500部。</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>sh603138</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>海量数据</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>16.92</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>10.013</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>数据要素|公司是国内主要的关系型数据库产品提供商，也是国内数据库基础软件产业发展的重要参与者和推动者。公司的企业级大数据平台提供全域数据资产管理功能，可以帮助客户采集和汇聚数据，经过治理后形成数据资产，为数字化应用提供支撑。该平台可实现全过程可视化，能快速开发数据类应用系统。</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>数据要素</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>sz000156</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>华数传媒</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>9.9857</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>短剧|公司积极关注相关行业的发展机遇，探索结合公司主营业务的产业机会，将发挥公司牌照、渠道、平台等优势，整合上下游产业链资源，赋能微短剧精品内容创作，已尝试和部分短剧平台公司开展内容审核业务合作。</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>有色金属概念</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>1.3079</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>三祥新材在投资者互动平台表示，公司锆系列产品价格均有不同幅度涨价，目前订单较为饱满。</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>sz001216</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>华瓷股份</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>10.0156</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>8天4板</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>氧化锆粉体|子公司江西金环旗下江西金瓷在氧化锆粉体研发领域历经多年持续投入并形成技术积淀，氧化锆粉体纯度最高可达99.995%，产品可适配新能源研磨、齿科陶瓷、MLCC等不同领域使用需求。</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>氧化锆粉体</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>0.5898</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>sh600187</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST国中 </t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>10.4762</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 1.国中水务2025年04月23日公告，终止重大资产重组事项。
+2.公司的主营业务为污水处理、自来水供应和环保工程技术服务，是具备全国范围内投资运营能力的水务环保企业。</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>0.5898</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>sh600745</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*ST闻泰 </t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>9.971499999999999</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 5月8日，*ST闻泰(600745)发布异动公告，前期公司子公司安世半导体以及安世半导体控股收到荷兰经济事务与气候政策部下达的部长令（Order）和阿姆斯特丹上诉法院企业法庭的裁决。截至目前，虽然上述部长令（Order）被宣布暂停，但企业法庭相关裁决依旧处于生效状态，公司对安世的控制权仍暂处于受限状态。</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="n">
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>sz002724</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>海洋王</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>9.991099999999999</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>6天6板</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>军工|公司是武器装备科研生产三级保密资格单位，设有专门的军品事业部负责军品的销售。</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>sz002474</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>榕基软件</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>10.0619</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>AI应用|公司以国内大模型为基座模型，归集高质量政务领域数据集，研发政务大模型，建立从数据治理、模型训练到场景落地的全栈AI能力。公司研发完成AI应用开发平台，提供推理引擎、模型管理、知识库管理等功能，支持可视化智能体编排服务。基于平台能力，公司发布了新一代政务智能办公解决方案，涵盖公文写作、公文纠错、政策摘要、流程协同、办公助手，语音转录、会议纪要生成以及知识引擎等智能化应用场景，并在福建、湖北等地的省市级党政机关单位取得试点应用突破。</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>AI应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>sz002945</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>华林证券</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>10.0287</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>券商|西藏地区唯一一家上市券商，主要通过总部以及下属分支机构从事财富管理、投资银行、资产管理以及自营业务等，通过全资子公司从事另类投资业务、私募股权投资业务。</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>sh600094</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大名城  </t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>10.0251</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>房地产+算力|1.公司以房地产为主业，主要从事住宅地产和商业地产的开发，打造城市综合运营商是公司中长期发展目标。
+2.2024年9月13日公告，公司控股子公司名城数字基于算力业务发展需要，向智算公司采购先进计算技术服务，包括但不限于算力和存储服务。此次交易标志着公司在智算中心项目的首期投资将实现落地并投入运营。</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>房地产, 算力</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>sz000972</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>中基健康</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>10.0271</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>农业种植|公司依托新疆得天独厚的地域和自然优势，致力于发展番茄“红色产业”，产业规模居于前列，产品行销世界数十国家和地区，是全球主要食品企业长期、固定的原料供应商。</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>农业种植</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>sz002322</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>理工能科</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>9.975899999999999</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>智能电网|公司是定额管理总站“定额电子版数据库”著作权的统一授权单位，并多次参与定额管理总站相关标准与规范的编制，电力工程造价工具软件获得定额管理总站重点推荐。凭借系统、高效的销售渠道和优质的售后服务，公司与两大电网、五大发电集团、两大辅业集团及其下属众多单位建立了良好的合作关系，并逐渐向电力系统外客户渗透，形成了优质的客户资源和庞大的用户群体。</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>智能电网</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>sz002612</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>朗姿股份</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>10.0065</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>化妆品|公司参股的公司L&amp;P Cosmetics Co., Ltd.是韩国知名化妆品公司，该公司主要研发、生产和销售各类护肤品，旗下品牌包括“Mediheal”、“T.P.O”、“Mediental”、“Labocare”等，主打产品为Mediheal面膜。</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>化妆品</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>sz002687</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>乔治白</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>9.934900000000001</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>纺织|公司主要从事“乔治白”“giuseppe”品牌的职业装生产和销售。</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>纺织</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
+      <c r="D83" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>sz002988</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>豪美新材</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="H83" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>sz002076</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>星光股份</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>10.2041</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5天4板</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>量子科技|子公司广州天芯量子拥有量子密钥分发、量子VPN加密、量子密钥管理等核心技术，已先后开发量子密钥分发产品、量子密钥管理终端、量子光交换机、量子波分复用终端、量子密钥应用设备、云防线及安全态势感知平台等产品。</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>量子科技</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>汽车零部件|公司专注于汽车零部件铝合金材料及部件研发和生产，包括电池托盘、防撞梁、副车架、减震支架、动力托架、电机部件等10余种产品。</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>汽车零部件</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>sh600293</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>三峡新材</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>10.1053</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>并购重组|三峡新材公告称，公司拟通过发行股份及支付现金方式取得珠海市赛纬电子材料股份有限公司100%股权，并向包括控股股东当阳城投在内的不超过35名特定投资者发行股份募集配套资金，总额不超过10亿元。标的公司主营锂离子电池电解液的研发、生产和销售。</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>sh600303</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>曙光股份</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>10.1754</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>汽车|公司是以整车、车桥及零部件为主营业务的跨地区的企业集团。</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>sh600838</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>上海九百</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>10.011</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>零售|公司控股股东为上海九百（集团）有限公司。目前已经发展成为涉及洗涤化工产品生产销售及洗染服务、酒类产品批发等多种业态的综合性企业。</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>零售</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>sh600202</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">哈空调  </t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>10.0539</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业注入预期|公司同一实控人哈尔滨国资委旗下马迭尔集团是其唯一文旅平台，旗下拳头品牌哈尔滨冰雪大世界、太阳岛风景区、亚布力等，或有资产注入预期。</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业注入预期</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>sh600261</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>阳光照明</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>10.0917</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>灯具|公司是中国最大的节能灯生产和出口基地之一，国家级高新技术企业。主要生产紧凑型节能荧光灯、电子节能灯、直管型荧光灯、T5大功率节能荧光灯及配套灯具、CCFL荧光屏背景光源及各类台灯系列。</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>灯具</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>sh600192</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>长城电工</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>10.0396</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>电网设备|公司主要从事高中低压开关成套设备、高中低压电器元件、母线槽、电气传动自动化装置、新能源装备等电工电器类产品的研发、生产与销售，先后为三峡工程、载人航天、奥运鸟巢、青藏铁路等多项国家重点工程提供优质产品。</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>电网设备</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>sz002983</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>芯瑞达</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>消费电子|公司已将AI+AR眼镜核心显示技术与光机组件布局定位为种子业务。公司计划在完成核心技术的进一步工程化验证后，推出具有竞争力的全彩MicroLED微显示与AR光机组件解决方案，为AI+AR眼镜产业化应用提供核心显示能力支撑。</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>消费电子</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>sz000530</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>冰山冷热</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>9.965200000000001</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业|子公司冰山工程近年来承接了多项代表性工程，包括广州融创茂室内滑雪场项目、上海之星室内综合性冰雪场馆、陕西国际体育之窗等多个商业冰雪场馆项目。</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>sh601091</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>沈鼓集团</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>21.58</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>9.989800000000001</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>次新+核电|公司是我国通用机械工业的战略型、支柱型、领军型企业，承担为石油、化工、电力、天然气、新能源等领域提供重大技术装备和成套解决方案的国产化任务，是世界上少数能够自主设计制造大型复杂压缩机、高端核主泵等重大技术装备的制造厂商之一。</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>次新, 核电</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>sz300839</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>博汇股份</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>19.92</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">石油化工|公司主营业务是对催化裂化后的燃料油即催化油浆进行深加工，采用自行研发的间歇式加工生产工艺、连续式生产工艺以及分子蒸馏和沉降等技术，对作为工业锅炉燃料的催化油浆综合再利用，研发、 生产和销售作为化工原料的沥青助剂、橡胶助剂、润滑油助剂等重芳烃产品和更为纯净的轻质燃料油。目前芳烃系列产品生产和使用主要区域集中在华东和华南地区。
-2024年1月31日公告，公司与宁波经济技术开发区管理委员会签订投资合作协议，拟在青峙化工新材料产业园投资建设160万吨/年新材料及高端化学品一体化项目。
-</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>石油化工</t>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>sh603838</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>四通股份</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>10.0149</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>陶瓷|公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>陶瓷</t>
         </is>
       </c>
     </row>
@@ -2075,7 +4397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2102,31 +4424,31 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sz002724</t>
+          <t>sh603278</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>大业股份</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sh603278</t>
+          <t>sz002724</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>海洋王</t>
         </is>
       </c>
     </row>
@@ -2136,27 +4458,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sz002076</t>
+          <t>sh600838</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>星光股份</t>
+          <t>上海九百</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh600293</t>
+          <t>sh603089</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>正裕工业</t>
         </is>
       </c>
     </row>
@@ -2166,12 +4488,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh601999</t>
+          <t>sh603528</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>出版传媒</t>
+          <t>多伦科技</t>
         </is>
       </c>
     </row>
@@ -2181,12 +4503,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sh600838</t>
+          <t>sz002535</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>林州重机</t>
         </is>
       </c>
     </row>
@@ -2196,12 +4518,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh603330</t>
+          <t>sz003021</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>天洋新材</t>
+          <t>兆威机电</t>
         </is>
       </c>
     </row>
@@ -2211,12 +4533,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sh600202</t>
+          <t>sh603028</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">哈空调  </t>
+          <t xml:space="preserve">赛福天  </t>
         </is>
       </c>
     </row>
@@ -2226,12 +4548,57 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sh603138</t>
+          <t>sz301502</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>海量数据</t>
+          <t>华阳智能</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>sz000678</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>襄阳轴承</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>sh603280</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>南方路机</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>sh603933</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>睿能科技</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,19 +476,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="99" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="319" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="252" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -556,45 +556,46 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh603278</t>
+          <t>sz002535</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>林州重机</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15.96</v>
+        <v>3.33</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.9931</v>
+        <v>9.901</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>6天6板</t>
+          <t>7天4板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>机器人|大业股份10月21日公告称，公司机器人腱绳产品目前尚未批量生产，未产生实质性收益，且公司相关业务未来在技术研发、产品竞争能力、盈利能力等方面存在重大不确定性。</t>
+          <t>军工+机器人|1.公司与多家大型军工集团建立了合作关系，并承接、交付了多批次的订单。
+2.公司曾于14年定增募资1.02亿元用于工业机器人产业化（一期）项目。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>军工, 机器人</t>
         </is>
       </c>
     </row>
@@ -605,46 +606,45 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz003021</t>
+          <t>sh603089</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>正裕工业</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>91.73</v>
+        <v>13.08</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.0012</v>
+        <v>10.0084</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>5天3板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>机器人+消费电子|1.公司聚焦手指等运动执行应用部位，开发仿生机器人灵巧手产品，该产品与公司的技术能力相契合,系公司未来平台化产品的重点布局。
-2.公司的微型传动系统可以应用于AR/VR领域，具体如磁感应系统、瞳距调节驱动系统、头部自动松紧装置、智能眼镜隐藏式微型扬声器等。</t>
+          <t>机器人|公司布局机器人零部件赛道，致力于机器人用柔性触觉传感技术的研发、传感器的设计与制造、以及信号处理系统的开发与测试，已完成核心产品的技术攻关与样品研发。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>机器人, 消费电子</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -655,40 +655,40 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh605488</t>
+          <t>sh603028</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>福莱新材</t>
+          <t xml:space="preserve">赛福天  </t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>38.15</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.0058</v>
+        <v>9.953199999999999</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5天3板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>机器人|2024年12月26日公司在互动平台表示，柔性传感器是相对前沿技术的应用，未来的应用场景广泛，公司从当前的整体定位去看，主要有以下几个方向：人形机器人电子皮肤的应用、工业检测应用、智能穿戴、健康监测等领域，公司目前在和一些公司合作研发。</t>
+          <t>机器人|在工业机器人领域，公司凭借对钢丝绳在升降与传动系统中核心技术的深度研发与创新应用，成功突破了传统业务的边界，开辟了全新的市场空间。通过为仓储智能机器人企业深圳市海柔创新科技有限公司提供高性能的升降配件解决方案，公司实现了从传统制造业向高端智能装备领域的跨越式发展。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,46 +704,46 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz002535</t>
+          <t>sh603528</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>林州重机</t>
+          <t>多伦科技</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3.03</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.1818</v>
+        <v>9.950900000000001</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6天3板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>军工+机器人|1.公司与多家大型军工集团建立了合作关系，并承接、交付了多批次的订单。
-2.公司曾于14年定增募资1.02亿元用于工业机器人产业化（一期）项目。</t>
+          <t>机器人|1.公司已开展多项人工智能驾考新技术研究，包括基于机器视觉的驾驶人注意力分配识别、基于机器视觉的道路环境目标识别、基于激光雷达的目标探测技术等。
+2.公司通过珠海星芯投资基金参与了众擎机器人科技有限公司Pre-A++轮融资，并持有其1.57%的股份。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>军工, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -754,40 +754,40 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sh603028</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">赛福天  </t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>8.539999999999999</v>
+        <v>14.55</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10.0515</v>
+        <v>9.9773</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>机器人|在工业机器人领域，公司凭借对钢丝绳在升降与传动系统中核心技术的深度研发与创新应用，成功突破了传统业务的边界，开辟了全新的市场空间。通过为仓储智能机器人企业深圳市海柔创新科技有限公司提供高性能的升降配件解决方案，公司实现了从传统制造业向高端智能装备领域的跨越式发展。</t>
+          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -803,46 +803,45 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh603280</t>
+          <t>sz301502</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>南方路机</t>
+          <t>华阳智能</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>31.97</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.0138</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>一带一路+机器人|1.公司主要从事工程搅拌设备、原生骨料加工处理设备、骨料资源化再生处理设备的设计、研发、生产和销售，目前公司已逐步建立出口经销渠道，产品销售业务拓展至俄罗斯、东南亚、非洲、澳大利亚等国家和地区。
-2.公司的建筑垃圾资源化处理设备的智能分拣机器人，能高效应对混合建筑垃圾、建筑混合废弃物、橡胶、木头等物料进行分拣，实现对建筑垃圾、装修垃圾等物料的分类回收和再利用，与公司其他产品均可广泛运用于灾后重建。</t>
+          <t>机器人|公司的无框电机可应用于机器人、协作机器人及高端医疗器械等领域。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>一带一路, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -853,31 +852,31 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sz301502</t>
+          <t>sh603337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>华阳智能</t>
+          <t>杰克科技</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>64.8</v>
+        <v>43.19</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>20</v>
+        <v>10.0102</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -886,7 +885,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司的无框电机可应用于机器人、协作机器人及高端医疗器械等领域。</t>
+          <t>机器人|公司在2024年年报中透露，公司高端产品研发取得里程碑进展，高端AI缝纫机原型样机成功落地，“杰克1号”人形机器人、无人模板机等“机器人+AI人工智能+缝制机械”多技术融合的智能高端产品初具雏形。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -902,31 +901,31 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sh603089</t>
+          <t>sz000559</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>正裕工业</t>
+          <t>万向钱潮</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>11.89</v>
+        <v>12.71</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9.9907</v>
+        <v>10.0433</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -935,7 +934,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司布局机器人零部件赛道，致力于机器人用柔性触觉传感技术的研发、传感器的设计与制造、以及信号处理系统的开发与测试，已完成核心产品的技术攻关与样品研发。</t>
+          <t>机器人|公司在机器人领域主要布局精密轴承和丝杠，目前相关产品尚处于开发验证阶段。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -951,31 +950,31 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sz002931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>锋龙股份</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>13.23</v>
+        <v>42.37</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>9.975100000000001</v>
+        <v>9.9948</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -984,12 +983,12 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
+          <t>优必选入主|锋龙股份公告称，本次股份协议转让已完成，公司控股股东变更为优必选，实际控制人变更为周剑。根据中国证券登记结算有限责任公司于2026年3月12日出具的《证券过户登记确认书》，本次协议转让事项过户登记手续已办理完毕，过户日期为2026年3月11日，过户股数为6552.99万股，占公司股份总数的29.99%，股份性质为无限售流通股。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>优必选入主</t>
         </is>
       </c>
     </row>
@@ -1000,31 +999,31 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh603528</t>
+          <t>sz000700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>模塑科技</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>13.07</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10</v>
+        <v>10.0168</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1033,13 +1032,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>AI+机器人|1.公司已开展多项人工智能驾考新技术研究，包括基于机器视觉的驾驶人注意力分配识别、基于机器视觉的道路环境目标识别、基于激光雷达的目标探测技术等。
-2.公司通过珠海星芯投资基金参与了众擎机器人科技有限公司Pre-A++轮融资，并持有其1.57%的股份。</t>
+          <t>机器人|2025年12月16日公告，公司与国内某机器人企业签订零部件采购框架协议，并获得人形机器人外覆盖件小批量采购订单。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>AI, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -1050,46 +1048,45 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz001283</t>
+          <t>sh603901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>豪鹏科技</t>
+          <t>永创智能</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>57.27</v>
+        <v>10.63</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.0077</v>
+        <v>10.0414</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4天2板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>机器人+AI PC|1.公司已向某“AI+儿童陪伴”创新头部机器人品牌厂商完成电池产品送样，整体进度处于行业第一梯队。与此同时，公司已与某高水平机器人企业达成战略合作关系，未来将通过深度合作，共同推动包含人形机器人/机器狗在内的相关机器人应用领域的技术创新和市场拓展。
-2.公司是部分国际知名笔记本品牌客户的电池主力供应商之一，在电池能量密度、倍率性能、散热及温升控制等方面具备较大竞争优势和深厚的技术积累，目前公司已向部分客户供应AI PC机型配套的电池产品。</t>
+          <t>机器人|公司在通过自主研发图像识别、视觉检测工业机器人等技术集成于公司智能包装生产线系列产品，提高智能包装生产线的柔性化和智能化；同时公司进一步完善标准包装设备产品的模块化分解，缩短标准包装设备产品的研发设计周期。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>机器人, AI PC</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -1100,42 +1097,41 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh600506</t>
+          <t>sz300916</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>统一股份</t>
+          <t>朗特智能</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>16.83</v>
+        <v>34.27</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10</v>
+        <v>19.993</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>液冷+机器人|1.公司成功开发出一系列具有国际先进水平的浸没式绝缘冷却工艺，包括国际上被少数发达国家企业垄断的电子氟化液产品，实现了此类产品的国产替代。公司的浸没式冷却工艺能广泛应用于高密度数据中心、超算智算中心、大功率充电桩和储能系统。
-2.公司自主研发工业机器人减速机的150号合成齿轮油产品，经测试，与进口齿轮油产品性能参数相当。</t>
+          <t>机器人|公司在机器人领域主要专注于扫地机器人智能控制器、清洁机器人及服务型机器人的组装及代工等。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>液冷, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -1146,42 +1142,42 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz002354</t>
+          <t>sz002178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>延华智能</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>8.029999999999999</v>
+        <v>5.34</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10</v>
+        <v>10.1031</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>机器人+短剧|1.在空间智能MaaS平台基础上，公司融合数据采集硬件、多模态数据处理技术、云边端算力，着力推进具身智能通用平台Behavision的建设，打造通用的大脑+小脑开发平台，以强大算力、高集成度和快速部署等优势，打造软硬一体、基垂融合的智能体新样板，为空间计算、具身智能、人形机器人等多场景应用提供通用智能化解决方案。
-2.在内容生产领域，公司打造影视级AI长视频创编平台CineART，面向Token经济发展带来的智能内容生产需求，积极拓展AI长视频、短剧和信息流广告等应用场景。</t>
+          <t>机器人+AI医疗|1.“建筑设施智能巡检机器人”为上海张江国家自主创新示范区专项发展资金重点项目，由子公司东方延华研发。
+2.在智慧医疗领域，公司研究开发了HIS系统、智能化电子病历系统、基于微服务的医院信息化集成平台，基于AI的临床辅助诊断系统、全流程医疗质量管理系统、智能决策分析系统、智能导诊系统、城市智慧救护车云服务平台、医疗质量信息管理平台、医院总值班信息系统平台、医护一体化平台等。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>机器人, 短剧</t>
+          <t>机器人, AI医疗</t>
         </is>
       </c>
     </row>
@@ -1192,36 +1188,36 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh603677</t>
+          <t>sh688648</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>奇精机械</t>
+          <t>中邮科技</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>16.3</v>
+        <v>34.66</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9.986499999999999</v>
+        <v>20.0139</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>机器人|2026年4月30日公司在互动平台表示，公司尚在开拓的工业机器人零部件产品为减速器中的钢轮，现处于小批交样阶段。</t>
+          <t>机器人|公司及子公司拥有的已授权专利情况包括：一种双承载分拣机器人（实用新型）、一种基于智能机器人的自动分拣矩阵系统（实用新型）。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1237,36 +1233,36 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sh603337</t>
+          <t>sz002708</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>杰克科技</t>
+          <t>光洋股份</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>39.26</v>
+        <v>15.65</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10.0028</v>
+        <v>9.978899999999999</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司在2024年年报中透露，公司高端产品研发取得里程碑进展，高端AI缝纫机原型样机成功落地，“杰克1号”人形机器人、无人模板机等“机器人+AI人工智能+缝制机械”多技术融合的智能高端产品初具雏形。</t>
+          <t>机器人|2024年12月2日公告，公司拟与安徽黄山高新技术开发区管理委员会签订《项目投资协议书》，在安徽省黄山高新区内拍取面积100亩土地使用权用于建设年产6000万套高端新能源汽车及机器人用精密零部件项目，以公司全资子公司黄山光洋传动科技有限公司为投资建设主体。本次项目投资总额预计为100,000万元。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1282,36 +1278,36 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh603081</t>
+          <t>sz001225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>大丰实业</t>
+          <t>和泰机电</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>10.65</v>
+        <v>31.08</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.0207</v>
+        <v>10.0177</v>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司于2025年3月23日与智元机器人签订《战略合作协议》，双方拟共同投资设立合资公司（公司持股85%），聚焦多模态交互系统研发与智能终端场景化应用，打造"技术+场景"融合创新平台，构建基于语音、视觉、触觉、手势等多模态交互模型，研发出匹配文娱旅体商场景需求的具身智能产品并实现商业化落地。</t>
+          <t>机器人|公司通过持续实施自动化、智能化改造，更新迭代生产设备，在物料输送设备制造领域的生产工艺已相对成熟，应用了机器人自动焊接技术，机器人视觉识别自动上下料、自动装箱等技术。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1327,41 +1323,41 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz301699</t>
+          <t>sz001331</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>洛轴股份</t>
+          <t>胜通能源</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>33.42</v>
+        <v>35.02</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>20</v>
+        <v>9.987400000000001</v>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>次新+机器人|公司针对国产机器人产业发展需求，开展机器人专用精密轴承设计和制造、测试、寿命试验等技术研究，研制出了薄壁等截面、交叉圆柱滚子两种系列轴承以及RV减速器、谐波减速器专用系列精密轴承。</t>
+          <t>七腾机器人入主|胜通能源公告称，七腾机器人向公司除收购人及其一致行动人外的全体股东发出部分要约收购，预定收购股份数量42,336,000股，占公司总股本的15%，要约价格为13.28元/股。要约收购期限为2026年4月28日至2026年5月27日，最后三个交易日预受要约不可撤销。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>次新, 机器人</t>
+          <t>七腾机器人入主</t>
         </is>
       </c>
     </row>
@@ -1372,41 +1368,42 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>920091.BJ</t>
+          <t>sh603683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>大鹏工业</t>
+          <t>晶华新材</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>33.51</v>
+        <v>17.16</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>29.9845</v>
+        <v>10</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司凭借持续多年的研发投入与项目经验积累，目前已掌握应用于机加工生产线、装配线的主流精密清洗技术，对设备结构、功能实现、自动化控制、工业机器人集成和柔性化制造等领域理解深刻。</t>
+          <t>机器人+固态电池|1.旗下子公司晶智感发布高自由度灵巧手全掌全触觉电子皮肤，该产品采用压阻式工艺，能为机器人的灵巧手提供触觉感知能力，可部署在手的各个区域。
+2.在新能源动力电池方面，针对新能源电池电芯、模组、PACK不同组件背胶要求特性，公司建立完善的产品类别，已成熟运用于软包电池、半固态电池。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>机器人, 固态电池</t>
         </is>
       </c>
     </row>
@@ -1417,36 +1414,36 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh600215</t>
+          <t>sh605333</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">派斯林  </t>
+          <t>沪光股份</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>6.34</v>
+        <v>18.1</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.0694</v>
+        <v>10.0304</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司深入掌握工业机器人系统集成的设计、研发、制造、集成以及调试等全面技术能力，具有领先的机械设计能力、丰富的工艺经验、在线视觉智能引导定位与监测技术及提供智能一体化解决方案等技术优势。</t>
+          <t>机器人|2026年8月12日，公司与北京辉羲智能信息技术有限公司、全能具身智能科技（苏州）有限公司、灵巧科技（昆山）有限公司四方正式签署具身智能战略合作仪式，依托沪光在汽车线束制造及场景化机器人应用方面的深厚积淀，叠加合作伙伴在芯片设计、具身智能算法及灵巧操作系统等维度的顶尖能力，有望构建起“场景定义—芯片赋能—技术落地”的闭环生态，为具身智能在工业领域的大规模应用打造可复制的标杆范式。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1462,43 +1459,41 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sz002009</t>
+          <t>sh688386</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>天奇股份</t>
+          <t>泛亚微透</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>17.3</v>
+        <v>46.56</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>9.9809</v>
+        <v>20</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>锂电+机器人|1.公司全资孙公司锂致实业是一家碳酸锂生产商，主要生产电池级碳酸锂、工业级碳酸锂、氢氧化锂等锂盐产品和硫酸钠等，同时为用户提供技术咨询和支持服务。
-2.全资子公司无锡天捷自动化物流设备有限公司总承包建造了优必选位于昆明、深圳、重庆、贵阳等多地的人形机器人装配线项目，其中昆明工厂一期项目于2020年建成投产，为全国首条AI智能化人形机器人的装配线。
-2025年10月31日公告，公司与富士康新能源汽车产业发展（河南）有限公司签署《战略合作框架协议》，双方拟共同推动具身智能机器人在工业场景的深度应用与技术创新。双方将合作共建高标准的机器人数据采集中心与机器人实训中心，形成从数据生成、采集、训练到场景验证的完整技术闭环。</t>
+          <t>机器人|在人形机器人方向，公司与柔性传感技术标杆企业苏州能斯达电子科技有限公司签署战略合作协议及委托开发协议，双方将聚焦机器人用ePTFE膜电子皮肤领域开展深度合作，携手打造技术协同、产业联动的创新生态，提升机器人用电子皮肤和关节等零部件性能，解决电子皮肤使用寿命、耐磨、抗压、防水透气等性能的技术瓶颈。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>锂电, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -1509,36 +1504,36 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sz002026</t>
+          <t>sh688585</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>山东威达</t>
+          <t>上纬新材</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>11.04</v>
+        <v>151.57</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.9602</v>
+        <v>19.9984</v>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>机器人|相继收购了上海拜骋电器有限公司、济南第一机床有限公司和苏州德迈科电气有限公司等，形成了精密机械零部件制造、中高档数控机床制造和机器人自动化三大互补的产业板块。</t>
+          <t>机器人|上纬新材消费级机器人启元Q1、启元T1双产品开启预订，用户可通过上纬启元官方小程序、天猫、抖音、B站官方店铺，以及线下体验活动参与预订，预计首批发货时间为今年9月。据了解，此前上纬新材与蓝思科技旗下蓝思智能机器人签约，落地首期万台级规模机器人产线合作；同时与卧龙电驱达成核心部件产线战略合作。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1554,36 +1549,36 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>3.6812</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sz000559</t>
+          <t>sh603331</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>万向钱潮</t>
+          <t>百达精工</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>11.55</v>
+        <v>12.91</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10</v>
+        <v>9.9659</v>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司在机器人领域主要布局精密轴承和丝杠，目前相关产品尚处于开发验证阶段。</t>
+          <t>机器人|公司已布局人形机器人灵巧手指部关节模组核心零部件以及具身机器人手部关节与腿部关节的核心铝制结构件等具身智能机器人核心零部件。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1595,1447 +1590,1421 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3.6812</v>
+        <v>0.7533</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sh688071</t>
+          <t>sz002696</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>华依科技</t>
+          <t>百洋股份</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>47.52</v>
+        <v>11.28</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
+        <v>10.0488</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>12天8板</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司的惯导产品可以应用于人形机器人上，用于测量人形机器人自身的运动状态和姿态。</t>
+          <t>水产品+鱼粉|1.公司位于广西，水产品加工业务板块将着重研发以罗非鱼、生鱼、金鲳鱼、海鲈鱼为原料的内销产品。
+2.公司下辖鱼粉厂的合计年产量约为1-2万吨，鱼油年产量约为2000-4000吨。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>水产品, 鱼粉</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3.6812</v>
+        <v>0.7533</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sh603901</t>
+          <t>sz002086</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>永创智能</t>
+          <t>东方海洋</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>9.66</v>
+        <v>2.3</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.0228</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+        <v>10.0478</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4天2板</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司在通过自主研发图像识别、视觉检测工业机器人等技术集成于公司智能包装生产线系列产品，提高智能包装生产线的柔性化和智能化；同时公司进一步完善标准包装设备产品的模块化分解，缩短标准包装设备产品的研发设计周期。</t>
+          <t>水产品+医药|1.公司主营业务为海洋水产品加工和海水养殖，其中海参养殖是公司海水养殖的传统主导业务。
+2.公司大健康事业部已布局免疫技术平台、质谱技术平台、分子技术平台及第三方医学检验实验室等四大平台。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>水产品, 医药</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>3.6812</v>
+        <v>0.7533</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz000810</t>
+          <t>sz001219</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>创维数字</t>
+          <t>青岛食品</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>10.02</v>
+        <v>13.62</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>9.989000000000001</v>
+        <v>10.0162</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司的EGO数据采集设备面向具身智能与机器人训练场景，已于海内外市场形成销售。</t>
+          <t>休闲食品|公司主要从事饼干与花生酱等休闲食品的研发、生产及销售，主要产品包括“青食”品牌钙奶饼干、“青食”品牌休闲饼干和“海友”品牌花生酱。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>休闲食品</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>3.6812</v>
+        <v>0.7533</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sz300307</t>
+          <t>sh603719</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>慈星股份</t>
+          <t>良品铺子</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>8.94</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>20</v>
+        <v>9.953199999999999</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司控股子公司东莞市中天自动化技术有限公司致力于从方案设计、精密加工、组装调试、现场实施以及售后支持等方面为客户提供优质产品和全方位的服务，主要从事3C行业、锂电行业、光伏行业，为客户提供标准化和定制化的自动化设备及整体工厂自动化解决方案，目前公司已经成为比亚迪、华为等知名品牌的供应商。</t>
+          <t>休闲食品|公司主营休闲食品，已形成覆盖肉类零食、坚果炒货、糖果糕点、果干果脯、素食山珍等多个品类、1000余种的产品组合。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>休闲食品</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>3.6812</v>
+        <v>0.7533</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz002979</t>
+          <t>sz002820</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>雷赛智能</t>
+          <t>桂发祥</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>54.15</v>
+        <v>10.19</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>9.9939</v>
+        <v>10.0432</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司在人形机器人领域定位是伺服控制产品与解决方案提供商、为众多整机厂家提供系列化伺服控制核心部件和模组级解决方案。公司从2018年起持续耕耘机器人行业（AGV/AMR、协作机器人等），并于2023年底成功研发出高密度无框力矩电机、CD伺服驱动器、中空编码器、空心杯电机及配套的微型伺服系统等核心产品。</t>
+          <t>休闲食品|公司是专业从事传统特色及其他休闲食品的研发、生产和销售的中华老字号企业，自产产品包括麻花、糕点、节令食品、天津风味方便食品等。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>休闲食品</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>3.6812</v>
+        <v>0.7533</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sh688836</t>
+          <t>sz001318</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>宇树科技-W</t>
+          <t>阳光乳业</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>624</v>
+        <v>12.1</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>机器人|宇树科技是国际领先的高性能通用机器人企业，专注于高性能通用人形机器人、四足机器人、机器人组件及具身智能模型的研发、生产和销售。</t>
+          <t>乳制品|公司专注于乳制品及乳饮料的研发、生产和销售，并以低温乳制品、低温乳饮料为主打产品。公司针对儿童提高免疫力开发的“初乳” 产品。公司从事液态乳、含乳饮料等产品的研发、生产、销售。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>乳制品</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>3.6812</v>
+        <v>0.7533</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz002931</t>
+          <t>sz000995</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>锋龙股份</t>
+          <t>皇台酒业</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>38.52</v>
+        <v>13.37</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>9.994300000000001</v>
+        <v>10.0412</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>优必选入主|锋龙股份公告称，本次股份协议转让已完成，公司控股股东变更为优必选，实际控制人变更为周剑。根据中国证券登记结算有限责任公司于2026年3月12日出具的《证券过户登记确认书》，本次协议转让事项过户登记手续已办理完毕，过户日期为2026年3月11日，过户股数为6552.99万股，占公司股份总数的29.99%，股份性质为无限售流通股。</t>
+          <t>葡萄酒|西北风格的名优白酒。葡萄酒产品依靠河西走廊得天独厚的地理优势，酒体品质达到了国际标准。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>优必选入主</t>
+          <t>葡萄酒</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>数据要素</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3.6812</v>
+        <v>0.5710999999999999</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>国联民生指出，国家数据集团有望推动公共数据由分散走向统筹，把数据资源优势转化为AI产业优势。具备数据要素运营、治理与安全能力的厂商有望充分受益。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sz000700</t>
+          <t>sh603138</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>模塑科技</t>
+          <t>海量数据</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>11.88</v>
+        <v>17</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
+        <v>10.0324</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>4天3板</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>机器人|2025年12月16日公告，公司与国内某机器人企业签订零部件采购框架协议，并获得人形机器人外覆盖件小批量采购订单。</t>
+          <t>数据要素+AI应用|1.公司是国内主要的关系型数据库产品提供商，也是国内数据库基础软件产业发展的重要参与者和推动者。公司的企业级大数据平台提供全域数据资产管理功能，可以帮助客户采集和汇聚数据，经过治理后形成数据资产，为数字化应用提供支撑。该平台可实现全过程可视化，能快速开发数据类应用系统。
+2.公司发布的企业级大数据应用平台提供AI驱动的增强分析功能，如时序预测分析、关联分析、根因分析等，助力数据驱动决策。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>数据要素, AI应用</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>数据要素</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>3.6812</v>
+        <v>0.5710999999999999</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>国联民生指出，国家数据集团有望推动公共数据由分散走向统筹，把数据资源优势转化为AI产业优势。具备数据要素运营、治理与安全能力的厂商有望充分受益。</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh603448</t>
+          <t>sh600822</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>天博智能</t>
+          <t>上海物贸</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>56.24</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>9.9941</v>
+        <v>9.976500000000001</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司将汽车传感器领域的算法、技术等拓展至具身智能领域，已开始为珞石（山东）机器人集团股份有限公司等机器人企业供应六维力传感器产品。</t>
+          <t>数据要素|旗下上海有色金属交易中心有限公司有研发的数据产品——有色金属现货指数查询，已在上海数据交易所备案并挂牌。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>数据要素</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>数据要素</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>3.6812</v>
+        <v>0.5710999999999999</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>国联民生指出，国家数据集团有望推动公共数据由分散走向统筹，把数据资源优势转化为AI产业优势。具备数据要素运营、治理与安全能力的厂商有望充分受益。</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz002380</t>
+          <t>sz002095</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>科远智慧</t>
+          <t>生 意 宝</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>27.67</v>
+        <v>16.48</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10.0199</v>
+        <v>10.0134</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>机器人+数据要素|1.以自主研发的HMI、PLC、运动控制器、伺服、变频器、机器人等产品为基础，为客户提供完整解决方案。
-2.公司研发的工业数据融合智能体是一款专为制造业设计的工业级数据融合与智能处理平台。该平台深度融合了异构数据智能融合、统一数据模型构建、智能数据分析与优化、业务流程支持等功能。</t>
+          <t>大宗商品数据商|公司是大宗商品数据商，主要跟踪能源、化工、橡塑、有色、钢铁、纺织、建材和农副八大行业的大宗原材料现货价格，以及上期所，郑商所，大商所和国外期货市场的期货价格数据。同时，为产业用户提供大宗原材料撮合服务。通过10多年的积累，已形成了价格、均价、涨跌榜、指数等数据产品形式，并形成了完整的价格数据采集、加工、研究和发布体系。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>机器人, 数据要素</t>
+          <t>大宗商品数据商</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>数据要素</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3.6812</v>
+        <v>0.5710999999999999</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>国联民生指出，国家数据集团有望推动公共数据由分散走向统筹，把数据资源优势转化为AI产业优势。具备数据要素运营、治理与安全能力的厂商有望充分受益。</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sh603286</t>
+          <t>sz002093</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>日盈电子</t>
+          <t>国脉科技</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>50.89</v>
+        <v>7.21</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10.0086</v>
+        <v>10.0763</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司看好汽车零部件企业进军人形机器人领域的产业机遇，积极投入以柔性触觉传感电子皮肤为代表的新产品开发，公司压阻式的电子皮肤样品已研发成功。</t>
+          <t>数据要素+AI应用|1.参股公司国脉生物以全球领先、低成本的“群体基因型数据库”建库技术与数据分析能力，为各地市解决公共卫生问题，为居民提供精准健康管理服务，同时运用区块链、分布式存储等技术解决数据安全、确权、交易中的痛点，激励用户、研究机构共享数据与算法，进一步提高数据在生态中的使用效率。
+2.公司一直高度重视人工智能在我司业务中的应用价值，已与多家主流大模型服务商建立合作关系，并结合各家平台的技术优势，打造更适配社区与居家养老场景的AI agent。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>数据要素, AI应用</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>业绩超预期</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>3.6812</v>
+        <v>-2.7035</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>部分机构策略展望研报认为，当前市场底部信号密集释放，进攻端关注三季报预期向好、产业趋势明确且基本面坚挺的超跌方向。</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sz002747</t>
+          <t>sh600826</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>兰生股份</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>29.18</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>9.9887</v>
+        <v>10.0402</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司参股的酷卓科技从事人形机器人部件及算法研发，已发布第一代人形机器人Codroid 01。</t>
+          <t>业绩|公司2026年7-9月实现营业收入6.37亿元，同比增长35.14%；归母净利润1.4亿元，同比增长12.97%。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>业绩</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>业绩超预期</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>3.6812</v>
+        <v>-2.7035</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>商务部消费促进司负责人谈2026年前三季度我国消费市场情况，绿色、智能、健康消费需求旺盛，商务部商务大数据显示，前三季度重点平台具身智能机器人销售额增长22.6%。</t>
+          <t>部分机构策略展望研报认为，当前市场底部信号密集释放，进攻端关注三季报预期向好、产业趋势明确且基本面坚挺的超跌方向。</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh688686</t>
+          <t>sh600980</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">奥普特  </t>
+          <t>北矿科技</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>153.2</v>
+        <v>18.95</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>19.9969</v>
+        <v>9.9826</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司专注于机器视觉核心软硬件的研发、生产和销售，为客户提供完整的机器视觉解决方案。机器视觉为机器人提供了精确的视觉感知能力，使其能够识别和处理各种物体；而机器人则利用这些视觉信息执行复杂的任务。</t>
+          <t>业绩|公司2026年1-9月实现营业收入10.30亿元，同比增长19.92%；归母净利润约1.09亿元，同比增长30.37%。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>业绩</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>业绩超预期</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2.3967</v>
+        <v>-2.7035</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>三星电子及SK海力士正推进其中国厂房生产逾200层NAND晶片，将中国厂房技术提升至韩国厂房的水平。目前三星位于西安的工厂占公司全球NAND产量约40%，公司目标将目前生产约200层NAND晶片。</t>
+          <t>部分机构策略展望研报认为，当前市场底部信号密集释放，进攻端关注三季报预期向好、产业趋势明确且基本面坚挺的超跌方向。</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sh603933</t>
+          <t>sz000411</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>睿能科技</t>
+          <t>英特集团</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>20.94</v>
+        <v>10.52</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>9.979000000000001</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0418</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>机器人+半导体|1.公司RA1、RA3系列伺服驱动器和MC2、MA3系列伺服电机已应用到机器人领域，包括不同载荷的四关节、六关节等工业机器人和协作机器人。
-2.公司分销的主要产品包括微控制器芯片、功率器件及模组、电源管理及驱动芯片、模拟及混合信号芯片、存储芯片等。</t>
+          <t>业绩|公司2026年7-9月实现营业收入88.21亿元，同比增长5.84%；归母净利润1.05亿元，同比增长41.59%。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>机器人, 半导体</t>
+          <t>业绩</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>物理AI</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>2.3967</v>
+        <v>0.4224000000000001</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>三星电子及SK海力士正推进其中国厂房生产逾200层NAND晶片，将中国厂房技术提升至韩国厂房的水平。目前三星位于西安的工厂占公司全球NAND产量约40%，公司目标将目前生产约200层NAND晶片。</t>
+          <t>智元正式开源AGIBOT WORLD 2026第四期“具身推理”（Physical Reasoning）——首个真实场景Physical Agent数据集。</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sz002077</t>
+          <t>sh605488</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>大港股份</t>
+          <t>福莱新材</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>13.08</v>
+        <v>41.97</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.0084</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
+        <v>10.0131</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>6天4板</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>先进封装|控股孙公司苏州科阳是少数掌握晶圆级芯片封装技术的公司之一，掌握了晶圆级芯片封装的TSV、micro-bumping（微凸点）和RDL等先进封装核心技术</t>
+          <t>物理AI|公司与浙江清华柔性电子技术研究院共建智能感知联合实验室，聚焦柔性电子皮肤与超宽域压力传感器研发；并与通智人工智能科技（北京）有限公司签署战略合作协议，推进“材料-感知-算法-终端”一体化的具身智能生态建设，强化触觉信号与AI大模型的深度融合。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>先进封装</t>
+          <t>物理AI</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>物理AI</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>2.3967</v>
+        <v>0.4224000000000001</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>三星电子及SK海力士正推进其中国厂房生产逾200层NAND晶片，将中国厂房技术提升至韩国厂房的水平。目前三星位于西安的工厂占公司全球NAND产量约40%，公司目标将目前生产约200层NAND晶片。</t>
+          <t>智元正式开源AGIBOT WORLD 2026第四期“具身推理”（Physical Reasoning）——首个真实场景Physical Agent数据集。</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sz001298</t>
+          <t>sz000810</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>好上好</t>
+          <t>创维数字</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>17.36</v>
+        <v>11.02</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10.0127</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
+        <v>9.98</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>半导体+机器人|1.公司是国内知名的电子元器件分销商，目前销售的存储芯片主要有晶豪（ESMT）、复旦微、Giantec（聚辰）、GigaDevice （兆易创新）等品牌的DRAM、eMMC、FLASH等存储器。
-2.公司完成了音视频、接口、存储、连接、传感、电源等产品在多场景（无人机/扫地机/割草机）及多形态（四足/人形/外骨骼/协作）机器人的产线布局。</t>
+          <t>数据采集|公司的EGO数据采集设备面向具身智能与机器人训练场景，已于海内外市场形成销售。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>半导体, 机器人</t>
+          <t>数据采集</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2.3967</v>
+        <v>0.1153</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>三星电子及SK海力士正推进其中国厂房生产逾200层NAND晶片，将中国厂房技术提升至韩国厂房的水平。目前三星位于西安的工厂占公司全球NAND产量约40%，公司目标将目前生产约200层NAND晶片。</t>
+          <t>据市场研究机构Omdia预测，亚太及大洋洲地区的AI智能体软件市场规模将从2025年的7.82亿美元跃升至2030年的112亿美元，年复合增长率达94%。</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sz301660</t>
+          <t>sh601900</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>粤芯半导-U</t>
+          <t>南方传媒</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>33.64</v>
+        <v>14.28</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>20.0143</v>
+        <v>10.0154</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>次新+半导体|粤芯半导体是专注于12英寸特色工艺晶圆代工的集成电路制造企业，致力于为境内外芯片设计企业提供晶圆代工服务和特色工艺解决方案，拥有两座12英寸晶圆厂、已实现产能6.33万片/月，工艺平台覆盖模拟和数模混合芯片及功率器件。</t>
+          <t>传媒+AI应用|1.公司是广东省出版集团以主要经营性资产和业务发起设立的股份制公司。公司旗下拥有出版、印刷、发行、报刊、数字、投资等一体化完整产业链。
+2.公司可应用AI技术的数字教育产品主要为粤教翔云数字教材应用平台。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>次新, 半导体</t>
+          <t>传媒, AI应用</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>2.3967</v>
+        <v>0.1153</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>三星电子及SK海力士正推进其中国厂房生产逾200层NAND晶片，将中国厂房技术提升至韩国厂房的水平。目前三星位于西安的工厂占公司全球NAND产量约40%，公司目标将目前生产约200层NAND晶片。</t>
+          <t>据市场研究机构Omdia预测，亚太及大洋洲地区的AI智能体软件市场规模将从2025年的7.82亿美元跃升至2030年的112亿美元，年复合增长率达94%。</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sh603160</t>
+          <t>sz300949</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>汇顶科技</t>
+          <t>奥雅股份</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>56.49</v>
+        <v>35.58</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10.0097</v>
+        <v>20</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>半导体|公司主要产品为电容触控芯片和指纹识别芯片，除此之外为固定电话芯片产品。</t>
+          <t>短剧+AI应用|1.公司建立了专门的短视频团队、短剧制作团队以及宣传片制作团队，这些团队毕业于海外知名电影学院，拥有非常国际化的视野和背景。
+2.“AI+IP”双引擎赋能是公司的长期策略，项目已广泛应用AI工具重塑工作流，落地项目包括广州花都蓝莓基地项目、衢州南孔洛嘉森乐园、顺德北滘体育（儿童）乐园等项目。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>短剧, AI应用</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>芯片产业链</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2.3967</v>
+        <v>0.9217</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>三星电子及SK海力士正推进其中国厂房生产逾200层NAND晶片，将中国厂房技术提升至韩国厂房的水平。目前三星位于西安的工厂占公司全球NAND产量约40%，公司目标将目前生产约200层NAND晶片。</t>
+          <t>万联证券认为，9月获批版号数量延续高位，进一步验证了版号供给常态化运行的稳定性。从年初至今，游戏版号审批节奏已逐步趋于平稳，行业供给端预期持续改善。</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sh688368</t>
+          <t>sh603258</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>晶丰明源</t>
+          <t>电魂网络</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>105.96</v>
+        <v>15.3</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>20</v>
+        <v>9.992800000000001</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>模拟芯片|公司是国内领先的电源管理驱动类芯片设计企业之一，主营业务为电源管理驱动类芯片的研发与销售，自成立以来即专注于电源管理驱动类芯片。</t>
+          <t>游戏|公司为一家拥有自主研发能力、运营能力的专业化网络游戏公司，致力于自主研发运营精品化的网络游戏。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>模拟芯片</t>
+          <t>游戏</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>物理AI</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>9.494299999999999</v>
+        <v>0.795</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》，在2026世界物理AI大会暨宇树合作伙伴生态大会上，宇树科技创始人王兴兴表示，随着GPT-6的发布，目前物理AI已经看到被击穿的苗头，很可能最近1-2年或2-3年。</t>
+          <t>据医药魔方统计，2026年1—9月中国创新药BD交易总额达1279.8亿美元，接近2025年全年水平；技术出口目录修订征求意见稿亦明确常见对外授权不受影响。</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sz301313</t>
+          <t>sh603716</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>凡拓数创</t>
+          <t>塞力医疗</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>61.44</v>
+        <v>16.06</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>5天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>物理AI|公司形成了以数字孪生引擎、低代码平台、AI算法、行业小模型、IoT、大数据、知识图谱、物理AI工具链为核心的完整技术底座，并构建起“物理AI 3D数字孪生”核心技术体系。</t>
+          <t>创新药+AI医疗|1.公司战略投资的心血管领域长效治疗性疫苗的创新性研发公司——武汉华纪元生物技术开发有限公司，其自主研发国家1类生物创新药HJY-ATRQβ-001正式获得国家药品监督管理局（NMPA）的新药临床试验申请（IND）受理通知书。
+2.2025年4月，塞力医疗集团专注于感染及危重症快速分子诊断、脑科学数字疗法为主研方向的AI诊疗技术研发中心（TAIDx Lab）已在上海正式部署完成。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>物理AI</t>
+          <t>创新药, AI医疗</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>物理AI</t>
+          <t>智能驾驶</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>9.494299999999999</v>
+        <v>-0.3744</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》，在2026世界物理AI大会暨宇树合作伙伴生态大会上，宇树科技创始人王兴兴表示，随着GPT-6的发布，目前物理AI已经看到被击穿的苗头，很可能最近1-2年或2-3年。</t>
+          <t>日前，一位不愿透露姓名的C-V2X领域从业者向记者透露，相关部门已经在推动车辆安装C-V2X（蜂窝车联网）的强标制定工作。相关工作组已经成立，有几十家单位已经参与进来了。</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>sz300296</t>
+          <t>sz002869</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>利亚德</t>
+          <t>金溢科技</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>7.32</v>
+        <v>20.04</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>9.989000000000001</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>物理AI|子公司利亚德（北京）演艺文化有限公司致力于将LED科技应用于文化创意领域，为文艺演出、电视综艺节目、会展及其他各类舞台活动提供基于LED技术的舞台视觉效果工程技术服务，以及相关舞台视效产品的研发、生产和销售。</t>
+          <t>智能驾驶+低空经济|1.公司是智慧交通领域领先的数智化解决方案及产品提供商，打造了完整的车、路、云产品体系,包括车载V2X系列产品、路端V2X边端系统集成产品、云端车路协同云平台和C-V2X车载HMI人机交互系统等。
+2.公司低空智联产品线深耕“高速+低空”特色垂直场景，依托自身在智能交通领域沉淀的融合感知、AI识别、车路通信核心技术，将机器视觉、物联网技术跨界迁移至无人机领域，打造“自动机场+无人机+AI”一体化智能巡检与监测解决方案，精准赋能交通、应急、工程、政务等多行业数字化、智能化升级。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>物理AI</t>
+          <t>智能驾驶, 低空经济</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>物理AI</t>
+          <t>固态电池</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>9.494299999999999</v>
+        <v>-0.7462</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》，在2026世界物理AI大会暨宇树合作伙伴生态大会上，宇树科技创始人王兴兴表示，随着GPT-6的发布，目前物理AI已经看到被击穿的苗头，很可能最近1-2年或2-3年。</t>
+          <t>工信部、国家发改委、交通运输部等七部门联合印发的《新型电池产业发展“十五五”规划》提出，到2030年，我国新型电池产业规模实现稳步增长，新体系电池研发取得重大进展，全固态电池初步实现规模化应用。</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>sz002421</t>
+          <t>sh603200</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>达实智能</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>3.43</v>
+        <v>50.41</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>9.9359</v>
+        <v>9.993499999999999</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>物理AI|达实智能将AI技术嵌入物联网平台，通过平台使AI具备对物理世界的感知与执行能力。平台V5版本基于判别式AI打造智慧冷源应用，V6版本实现了设备及能源诊断和AI视觉分析功能。V7版本首次接入大模型，诞生了基于生成式AI的智能体，V7.1版本迎来AI智能体2.0升级版本，为智慧园区打造了专属的超级智能体。</t>
+          <t>固态电池+液冷|1.公司生产的固态电解质粉体材料可以应用于锂离子固态电池，多形态固态电解质粉体材料（含油性、水性、浆料）年产50吨级产线主要采用的是氧化物技术路线，公司储备了硫化物、氯化物等固态电解质的其它固态电解质粉体技术路线。
+2.公司面向腾讯、华为、中国移动等重点客户数据中心提供循环水/空气蒸发冷却等专业服务。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>物理AI</t>
+          <t>固态电池, 液冷</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>物理AI</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>9.494299999999999</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>据《科创板日报》，在2026世界物理AI大会暨宇树合作伙伴生态大会上，宇树科技创始人王兴兴表示，随着GPT-6的发布，目前物理AI已经看到被击穿的苗头，很可能最近1-2年或2-3年。</t>
-        </is>
-      </c>
+        <v>-0.4457</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>sh603859</t>
+          <t>sh603021</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>能科科技</t>
+          <t xml:space="preserve">*ST华鹏 </t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>43.56</v>
+        <v>3.81</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>10</v>
+        <v>10.1156</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>物理AI|公司精准卡位具身智能“大脑”角色，构建起从“感知—决策—执行—评估”的物理AI全链条能力，成功打造可独立运行的“端侧单体大脑”，实现在工业及特种场景下的深度应用，并逐步建立本体小脑到应用大脑的中间层链接标准。</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>物理AI</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是国内日用玻璃行业的企业之一，主营业务为研发、生产和销售玻璃器皿产品和玻璃瓶罐。</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>物理AI</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>9.494299999999999</v>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>据《科创板日报》，在2026世界物理AI大会暨宇树合作伙伴生态大会上，宇树科技创始人王兴兴表示，随着GPT-6的发布，目前物理AI已经看到被击穿的苗头，很可能最近1-2年或2-3年。</t>
-        </is>
-      </c>
+        <v>-0.4457</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>sh603466</t>
+          <t>sh600476</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">风语筑  </t>
+          <t xml:space="preserve">*ST湘邮 </t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>14.69</v>
+        <v>10.37</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>10.0375</v>
+        <v>9.968200000000001</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>物理AI|公司投资松应科技，围绕物理AI仿真引擎开展技术合作；与松应科技共同设立控股子公司公司风应科技，聚焦物理AI仿真环境构建、合成数据生成及相关训练基础设施等方向开展业务。</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>物理AI</t>
-        </is>
-      </c>
+          <t>ST股 | 公司是邮政物流北斗设备的供应商及技术解决方案提供商，正在做末端无人配送方面的应用研究。</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>业绩超预期</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>2.2483</v>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>A股上市公司三季报披露进入加速期，绩优股获青睐。</t>
-        </is>
-      </c>
+        <v>-0.4457</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>sz002982</t>
+          <t>sz000639</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>湘佳股份</t>
+          <t>ST西王</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>13.28</v>
+        <v>1.78</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>10.0249</v>
+        <v>9.8765</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>业绩|湘佳股份公告称，第三季度营业收入为13.15亿元，同比增长15.48%；归属于上市公司股东的净利润为7597.44万元，同比增长360.44%。前三季度营业收入为36.31亿元，同比增长10.98%；归属于上市公司股东的净利润为6387.96万元，同比增长185.84%。</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>业绩</t>
-        </is>
-      </c>
+          <t>ST股 | 国内最大的玉米胚芽油生产基地，主要生产销售西王牌系列健康食用油。</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>业绩超预期</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>2.2483</v>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>A股上市公司三季报披露进入加速期，绩优股获青睐。</t>
-        </is>
-      </c>
+        <v>-0.4457</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>sz300584</t>
+          <t>sh600180</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>海辰药业</t>
+          <t xml:space="preserve">*ST瑞茂 </t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>32.08</v>
+        <v>1.23</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>20.015</v>
+        <v>9.821399999999999</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>业绩|公司2026年1-9月实现营业收入6.15亿元，同比增长30.49%；归母净利润6225.56万元，同比增长90.51%。报告期内，公司业绩增长主要受益于锂电池电解液添加剂业务量产后收入大幅增加，同时公司优化研发项目布局、缩减市场相关费用投入，盈利能力持续提升。</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>业绩</t>
-        </is>
-      </c>
+          <t>ST股 | 煤炭供应链业务是公司核心业务版块，业务区域已覆盖国内煤炭资源主产地和主要消费地。</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>业绩超预期</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>2.2483</v>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>A股上市公司三季报披露进入加速期，绩优股获青睐。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>sz001328</t>
+          <t>sh600838</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>登康口腔</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>32.51</v>
+        <v>12.1</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>10.0169</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>4天4板</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>业绩|公司2026年1-9月实现营业收入14.25亿元，同比增长16.05%；归母净利润约1.61亿元，同比增长18.32%。</t>
+          <t>零售|公司控股股东为上海九百（集团）有限公司。目前已经发展成为涉及洗涤化工产品生产销售及洗染服务、酒类产品批发等多种业态的综合性企业。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>业绩</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>业绩超预期</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>2.2483</v>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>A股上市公司三季报披露进入加速期，绩优股获青睐。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>sh603713</t>
+          <t>sh600094</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>密尔克卫</t>
+          <t xml:space="preserve">大名城  </t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>66.66</v>
+        <v>4.83</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+        <v>10.0228</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>业绩|公司2026年1-9月实现营业收入125.89亿元，同比增长17.98%；归母净利润约5.93亿元，同比增长12.96%。</t>
+          <t>房地产+算力|1.公司以房地产为主业，主要从事住宅地产和商业地产的开发，打造城市综合运营商是公司中长期发展目标。
+2.2024年9月13日公告，公司控股子公司名城数字基于算力业务发展需要，向智算公司采购先进计算技术服务，包括但不限于算力和存储服务。此次交易标志着公司在智算中心项目的首期投资将实现落地并投入运营。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>业绩</t>
+          <t>房地产, 算力</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>业绩超预期</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>2.2483</v>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>A股上市公司三季报披露进入加速期，绩优股获青睐。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>sz301101</t>
+          <t>sz301314</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>明月镜片</t>
+          <t>科瑞思</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>35.34</v>
+        <v>56.14</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>20</v>
+        <v>20.0086</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>业绩|公司2026年1-9月实现营业收入7.30亿元，同比增长16.54%；归母净利润约1.76亿元，同比增长18.29%。</t>
+          <t>并购重组|科瑞思公告称，拟通过发行股份及支付现金的方式购买李刚等7名交易对方持有的宏钢光电100%股份，并向不超过35名特定投资者发行股份募集配套资金。经申请，公司股票自10月26日起复牌。宏钢光电主要从事激光器、光通讯、混合集成电路、半导体功率器件等领域的封装壳体及高功率光纤激光器芯片热沉的研发、生产与销售。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>业绩</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>3.1121</v>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>sh603721</t>
+          <t>sh600558</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>中广天择</t>
+          <t xml:space="preserve">大西洋  </t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>21.77</v>
+        <v>5.56</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>10.0051</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>10.099</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧+数据要素|1.公司积极布局纪实IP、微短剧、AI漫剧、中长剧等多元内容赛道，构建多层次、差异化的内容供给与运营体系。在短剧及中长剧领域，公司以制作、投资与分账发行相结合的模式稳步推进项目落地，内容制作与市场运营能力持续提升，优质项目储备不断充实。
-2.控股的湖南马栏山天择微链科技有限公司全面推进的“中国V链”, 致力打造运营全域数字资产保护及交易平台，平台利用区块链技术，将权利人提交的版权内容进行上链存证，对资产的版权进行保护。</t>
+          <t>核电|公司已和国内三大核电公司（中核、国核、广核）充分合作，研发出如碳钢低合金钢、不锈钢、镍基等一系列焊接材料，部分产品用于可控核聚变相关部件的制造。</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>AI漫剧, 数据要素</t>
+          <t>核电</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>3.1121</v>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>sh688787</t>
+          <t>sz002795</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>海天瑞声</t>
+          <t>永和智控</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>141</v>
+        <v>6.9</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>20</v>
+        <v>10.0478</v>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>数据要素|‌海天瑞声深耕AI训练数据领域超过20年，已形成覆盖数据采集、处理、标注、治理到应用落地的完整能力体系，服务全球上千家科技企业与科研机构 。‌‌‌</t>
+          <t>剥离资产|公司近期披露系列公告，完成成都永和成等多家亏损医疗、新能源子公司股权及债权转让，彻底甩掉长期拖累业绩的非主业包袱，同时回笼部分运营资金，进一步聚焦自身流体智控核心主业，优化业务结构。</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>剥离资产</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>3.1121</v>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>sh603171</t>
+          <t>sh603657</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>税友股份</t>
+          <t>春光科技</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>48.29</v>
+        <v>33.88</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>10</v>
@@ -3043,134 +3012,128 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>数据要素|公司积极布局业财税大数据商业服务业务，探索财税数据要素的多场景应用、多主体复用，重点布局“数据要素×金融服务”“数据要素×商贸流通”等场景的新产品和新服务。公司基于高质量数据底座，利用数据、算法的结合，将数据及数据模型服务运用于交易撮合、风险评估等场景，以提高客户营销及服务场景的效率和准确性，并有效降低交易风险。</t>
+          <t>家电|公司主营业务为吸尘器零件、橡塑软管、塑料制品、小家电的研发、制造和销售及自营进出口业务。</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>家电</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>3.1121</v>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>国家数据集团有限公司在河北雄安新区成立，集团成立旨在推进数据资源开发利用、释放数据要素价值、服务人工智能发展、繁荣数据产业生态。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>920207.BJ</t>
+          <t>sz002578</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>众诚科技</t>
+          <t>闽发铝业</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>28.34</v>
+        <v>3.6</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>30</v>
+        <v>10.0917</v>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>数据要素|公司通过平台升级，实现数据集成管理、数据交换管理、实时计算存储、元数据管理、数据标准管理、数据质量管理、主数据管理、数据资产管理、数据安全管理、数据生命周期管理十大模块的融合，各模块可独立或任意组合使用，打通数据治理各个环节，可快速满足政府、企业用户各类不同的数据治理场景需求。</t>
+          <t>福建+铝|公司是国内行业中较早涉足工业型材领域的企业之一，主营业务和产品主要是建筑铝型材、工业铝型材和建筑铝模板的研发、生产、销售。</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>福建, 铝</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>金融科技</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>4.8231</v>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>业内人士认为，A股上市券商前三季度净利润有望在第三季度承压的情况下仍保持增长。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>sh601519</t>
+          <t>sz000635</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">大智慧  </t>
+          <t>英 力 特</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>9.25</v>
+        <v>8.02</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>9.988099999999999</v>
+        <v>10.0137</v>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>互联网金融|公司是国内领先的互联网金融信息服务提供商，主要业务聚焦在证券信息服务平台、大数据及数据工程服务和境外业务三大板块。</t>
+          <t>拟股权转让|英力特公告称，公司控股股东英力特集团拟通过公开征集受让方方式一次性整体协议转让其持有的公司1.55亿股无限售流通股份，占公司总股本的39.41%，转让价格不低于6.27元/股。若本次转让实施完成，公司控制权将发生变更。</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>互联网金融</t>
+          <t>拟股权转让</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>金融科技</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n">
-        <v>4.8231</v>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>业内人士认为，A股上市券商前三季度净利润有望在第三季度承压的情况下仍保持增长。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sz301428</t>
+          <t>sz300976</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>世纪恒通</t>
+          <t>达瑞电子</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>32.64</v>
+        <v>53.4</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>20</v>
@@ -3178,1211 +3141,98 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>金融科技|公司为保险及银行等金融机构、电信运营商、高速集团等大型企业客户提供整合后的车主信息服务资源，客户的车主用户可通过微信平台、小程序、APP、H5页面等享有车主信息服务，包括ETC办理、代驾、停车及汽车美容、保养、安全检测、年检代办等各项专享优惠及便捷服务。</t>
+          <t>并购重组|达瑞电子公告，公司此前约定以9560万元收购麦德坤持有的维斯德20%股权；2026年10月22日，公司与麦德坤正式签署剩余股权收购协议。交易完成后公司将持有维斯德100%股权，目前尚需履行工商变更等相关程序。</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>金融科技</t>
+          <t>并购重组</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>金融科技</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n">
-        <v>4.8231</v>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>业内人士认为，A股上市券商前三季度净利润有望在第三季度承压的情况下仍保持增长。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>sz300561</t>
+          <t>sh603955</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>汇金科技</t>
+          <t>大千生态</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>15.6</v>
+        <v>27.05</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>20</v>
+        <v>10.0041</v>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>金融科技+AI|1.公司是从事软件开发和系统集成信息技术服务的专业型企业，面向金融机构、政府部门、企事业单位提供一体化解决方案。
-2.公司人工智能技术在人脸识别、活体检测、语音处理、指静脉识别等方向有应用案例。</t>
+          <t>冰雪产业|2025年12月，旗下江苏大千文旅与柳叶湖旅游度假区正式签约。项目以“沉浸式体验、全年龄段适配”为核心，精心打造奇趣雪乡乐园、戏雪乐园、侏罗纪秘境、梦幻绿野仙踪等六大核心体验区，设置20多条滑道、恐龙主题展区、冰雪雕塑区及免费互动项目。</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>金融科技, AI</t>
+          <t>冰雪产业</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>2.7819</v>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>财政部等三部门发文明确，自2026年9月1日起至2028年12月31日，对钠离子电池、固态电池等免征消费税，定向扶持新技术路线。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>sz001301</t>
+          <t>sz001317</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>尚太科技</t>
+          <t>三羊马</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>45.71</v>
+        <v>53.68</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>10.012</v>
+        <v>10</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>固态电池|公司已获得多件与硅基负极材料等与固态电池相关的发明专利。</t>
+          <t>物流|公司是一家主要通过公铁联运方式为汽车行业和啤酒、饮料、洗涤用品等非汽车行业提供综合服务的第三方物流企业，建成以重庆为龙头，以柳州、西安、兰州、乌鲁木齐等为支点，串联“一带一路”沿线节点城市，横贯中西部地区，联系亚欧大陆的流通大通道。</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>2.7819</v>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>财政部等三部门发文明确，自2026年9月1日起至2028年12月31日，对钠离子电池、固态电池等免征消费税，定向扶持新技术路线。</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>sz002812</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>恩捷股份</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>46.92</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>10.0117</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>固态电池|公司已与北京卫蓝和天目先导成立了合资公司江苏三合，进行半固态电解质涂层隔膜及多种高端涂层隔膜的研发、生产。</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>2.7819</v>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>财政部等三部门发文明确，自2026年9月1日起至2028年12月31日，对钠离子电池、固态电池等免征消费税，定向扶持新技术路线。</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>sz001359</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>平安电工</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>PCB+固态电池|1.公司玻纤布产品主要分为工业级玻纤布和电子级玻纤布。其中电子级玻纤布可使基板具备优质的电气特性及机械强度，是主要用于印制电路覆铜板的绝缘增强材料。
-2.公司对固态电池行业的发展动态和趋势保持密切关注。云母是天然的高绝缘材料，耐高温、耐绝缘等特性可以在固态电池、人形机器人中有潜在的应用价值。</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>PCB, 固态电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>商业零售</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n">
-        <v>1.939</v>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>在10月22日国新办新闻发布会上，商务部市场运行和消费促进司司长杨沐表示，今年前三季度，服务零售额同比增长5%，比商品零售额高出4个百分点，预计未来一段时期，商品消费增速将保持平稳增长。</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>sh600838</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>上海九百</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>3天3板</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>零售|公司控股股东为上海九百（集团）有限公司。目前已经发展成为涉及洗涤化工产品生产销售及洗染服务、酒类产品批发等多种业态的综合性企业。</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>零售</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>商业零售</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n">
-        <v>1.939</v>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>在10月22日国新办新闻发布会上，商务部市场运行和消费促进司司长杨沐表示，今年前三季度，服务零售额同比增长5%，比商品零售额高出4个百分点，预计未来一段时期，商品消费增速将保持平稳增长。</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>sh600865</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>百大集团</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>11.04</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>9.9602</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>零售|公司主营业务为商品零售，主要业态为百货商场，旗下杭州百货大楼是公司最主要的营收和利润来源，是杭州市区域龙头百货商场之一。</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>零售</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>商业零售</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="n">
-        <v>1.939</v>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>在10月22日国新办新闻发布会上，商务部市场运行和消费促进司司长杨沐表示，今年前三季度，服务零售额同比增长5%，比商品零售额高出4个百分点，预计未来一段时期，商品消费增速将保持平稳增长。</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>sh600785</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>新华百货</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>12.56</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>9.9825</v>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>零售|公司是宁夏乃至西北地区较大的商业零售企业，主要从事商业零售、物流和商业物业出租业务，零售业务主要涉及百货商场、综合购物中心、超市连锁、电器及通信连锁。</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>零售</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>网络安全</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>3.5051</v>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>广泛应用于网站和网络应用开发的编程语言PHP被曝出存在严重网络安全漏洞，需要进行紧急安全更新，亚洲多国政府与企业当前正紧急排查并加固旗下网站。</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>sz300369</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>绿盟科技</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>19.9795</v>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>网络安全+AI|2024年公司推出了自主研发的“风云卫AI安全能力平台”，该平台融合大模型、小模型、知识图谱等核心能力，依托公司二十余年的网络安全研究积累与攻防对抗实践，构建了开放式PaaS架构，广泛适配于安全运营、检测响应、攻防实战等场景。</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>网络安全, AI</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>网络安全</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>3.5051</v>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>广泛应用于网站和网络应用开发的编程语言PHP被曝出存在严重网络安全漏洞，需要进行紧急安全更新，亚洲多国政府与企业当前正紧急排查并加固旗下网站。</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>sz002439</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>启明星辰</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>15.05</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>10.0146</v>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>网络安全+AI|1.公司是信息安全行业龙头，为政企用户提供网络安全软/硬件产品、安全管理平台、安全服务与解决方案。
-2.公司已完成了“安星”智能体与DeepSeek大模型的全面对接，并应用到安全运营、威胁检测、威胁情报、数据安全等全业务场景中，实现了安全智能化能力的再升级。</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>网络安全, AI</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>消费电子</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n">
-        <v>2.9914</v>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>机构研报指出，AI眼镜正处于由产品验证向快速放量过渡的关键阶段，科技巨头争相布局AI眼镜业务，预计该行业2025—2030年复合增速约60%。</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>sh603341</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>龙旗科技</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>44.14</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>9.9925</v>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>端侧AI|公司为全球头部消费电子品牌商和全球领先科技企业提供专业的智能产品综合服务，形成了涵盖智能手机、平板电脑、AI PC、AIoT产品及汽车电子等智能产品布局。</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>端侧AI</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>消费电子</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n">
-        <v>2.9914</v>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>机构研报指出，AI眼镜正处于由产品验证向快速放量过渡的关键阶段，科技巨头争相布局AI眼镜业务，预计该行业2025—2030年复合增速约60%。</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>sz002241</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>歌尔股份</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>9.995200000000001</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>端侧AI+机器人|1.公司在与AR和智能眼镜相关的光机模组领域内有广泛的技术布局，包括应用DLP，LCoS，Micro-OLED，Micro-LED等不同微显示技术的相关产品。
-2.公司的扬声器、传感器、光学器件、精密结构件等产品均可以应用于多种类的终端硬件设备中，公司在机器人相关业务领域内有所布局，并已在智能制造领域内广泛应用机器视觉、机器人等相关技术。</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>端侧AI, 机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>短剧</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n">
-        <v>2.906</v>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>国家广播电视总局印发《广播电视和网络视听“十五五”规划》。《规划》总体目标为到2030年，广电媒体全面挺进互联网主战场（包括“十五五”期间推出优秀电视剧（网络剧）100部；推出优秀微短剧500部。</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>sz002343</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>慈文传媒</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>10.89</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>短剧|公司已形成了以自有IP为核心资源，以影视IP内容投资、开发、制作及发行为核心业务，积极延伸拓展电影、网络电影、网络微短剧、互动剧、小程序短剧、IP线下衍生等相关品类的业务体系。</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>短剧</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>短剧</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="n">
-        <v>2.906</v>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>国家广播电视总局印发《广播电视和网络视听“十五五”规划》。《规划》总体目标为到2030年，广电媒体全面挺进互联网主战场（包括“十五五”期间推出优秀电视剧（网络剧）100部；推出优秀微短剧500部。</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>sz000156</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>华数传媒</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>9.9857</v>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>短剧|公司积极关注相关行业的发展机遇，探索结合公司主营业务的产业机会，将发挥公司牌照、渠道、平台等优势，整合上下游产业链资源，赋能微短剧精品内容创作，已尝试和部分短剧平台公司开展内容审核业务合作。</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>短剧</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>有色金属概念</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n">
-        <v>1.3079</v>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>三祥新材在投资者互动平台表示，公司锆系列产品价格均有不同幅度涨价，目前订单较为饱满。</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>sz001216</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>华瓷股份</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>28.12</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>10.0156</v>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>8天4板</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>氧化锆粉体|子公司江西金环旗下江西金瓷在氧化锆粉体研发领域历经多年持续投入并形成技术积淀，氧化锆粉体纯度最高可达99.995%，产品可适配新能源研磨、齿科陶瓷、MLCC等不同领域使用需求。</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>氧化锆粉体</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="n">
-        <v>0.5898</v>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
-      <c r="D73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>sh600187</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST国中 </t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>10.4762</v>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 1.国中水务2025年04月23日公告，终止重大资产重组事项。
-2.公司的主营业务为污水处理、自来水供应和环保工程技术服务，是具备全国范围内投资运营能力的水务环保企业。</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="n">
-        <v>0.5898</v>
-      </c>
-      <c r="C74" s="2" t="inlineStr"/>
-      <c r="D74" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>sh600745</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST闻泰 </t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>11.58</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>9.971499999999999</v>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 5月8日，*ST闻泰(600745)发布异动公告，前期公司子公司安世半导体以及安世半导体控股收到荷兰经济事务与气候政策部下达的部长令（Order）和阿姆斯特丹上诉法院企业法庭的裁决。截至目前，虽然上述部长令（Order）被宣布暂停，但企业法庭相关裁决依旧处于生效状态，公司对安世的控制权仍暂处于受限状态。</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr"/>
-      <c r="D75" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>sz002724</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>海洋王</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>9.991099999999999</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>6天6板</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>军工|公司是武器装备科研生产三级保密资格单位，设有专门的军品事业部负责军品的销售。</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>军工</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
-      <c r="D76" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>sz002474</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>榕基软件</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>10.0619</v>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>AI应用|公司以国内大模型为基座模型，归集高质量政务领域数据集，研发政务大模型，建立从数据治理、模型训练到场景落地的全栈AI能力。公司研发完成AI应用开发平台，提供推理引擎、模型管理、知识库管理等功能，支持可视化智能体编排服务。基于平台能力，公司发布了新一代政务智能办公解决方案，涵盖公文写作、公文纠错、政策摘要、流程协同、办公助手，语音转录、会议纪要生成以及知识引擎等智能化应用场景，并在福建、湖北等地的省市级党政机关单位取得试点应用突破。</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr"/>
-      <c r="D77" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>sz002945</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>华林证券</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>15.36</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>10.0287</v>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>券商|西藏地区唯一一家上市券商，主要通过总部以及下属分支机构从事财富管理、投资银行、资产管理以及自营业务等，通过全资子公司从事另类投资业务、私募股权投资业务。</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr"/>
-      <c r="D78" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>sh600094</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">大名城  </t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>10.0251</v>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>房地产+算力|1.公司以房地产为主业，主要从事住宅地产和商业地产的开发，打造城市综合运营商是公司中长期发展目标。
-2.2024年9月13日公告，公司控股子公司名城数字基于算力业务发展需要，向智算公司采购先进计算技术服务，包括但不限于算力和存储服务。此次交易标志着公司在智算中心项目的首期投资将实现落地并投入运营。</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>房地产, 算力</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr"/>
-      <c r="D79" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>sz000972</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>中基健康</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>10.0271</v>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>农业种植|公司依托新疆得天独厚的地域和自然优势，致力于发展番茄“红色产业”，产业规模居于前列，产品行销世界数十国家和地区，是全球主要食品企业长期、固定的原料供应商。</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>农业种植</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr"/>
-      <c r="D80" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>sz002322</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>理工能科</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>9.975899999999999</v>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>智能电网|公司是定额管理总站“定额电子版数据库”著作权的统一授权单位，并多次参与定额管理总站相关标准与规范的编制，电力工程造价工具软件获得定额管理总站重点推荐。凭借系统、高效的销售渠道和优质的售后服务，公司与两大电网、五大发电集团、两大辅业集团及其下属众多单位建立了良好的合作关系，并逐渐向电力系统外客户渗透，形成了优质的客户资源和庞大的用户群体。</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>智能电网</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr"/>
-      <c r="D81" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>sz002612</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>朗姿股份</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>16.93</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>10.0065</v>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>化妆品|公司参股的公司L&amp;P Cosmetics Co., Ltd.是韩国知名化妆品公司，该公司主要研发、生产和销售各类护肤品，旗下品牌包括“Mediheal”、“T.P.O”、“Mediental”、“Labocare”等，主打产品为Mediheal面膜。</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>化妆品</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr"/>
-      <c r="D82" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>sz002687</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>乔治白</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>9.934900000000001</v>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>纺织|公司主要从事“乔治白”“giuseppe”品牌的职业装生产和销售。</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>纺织</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr"/>
-      <c r="D83" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>sz002988</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>豪美新材</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>31.24</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>汽车零部件|公司专注于汽车零部件铝合金材料及部件研发和生产，包括电池托盘、防撞梁、副车架、减震支架、动力托架、电机部件等10余种产品。</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>汽车零部件</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr"/>
-      <c r="D84" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>sh600303</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>曙光股份</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>10.1754</v>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>汽车|公司是以整车、车桥及零部件为主营业务的跨地区的企业集团。</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>汽车</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr"/>
-      <c r="D85" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>sh603838</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>四通股份</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>10.0149</v>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>陶瓷|公司是一家集研发、设计、生产、销售于一体的新型家居生活陶瓷供应商，产品覆盖日用陶瓷、卫生陶瓷、艺术陶瓷、建筑装饰等全系列家居生活用瓷。</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>陶瓷</t>
+          <t>物流</t>
         </is>
       </c>
     </row>
@@ -4397,7 +3247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4424,31 +3274,31 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sh603278</t>
+          <t>sh600838</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>大业股份</t>
+          <t>上海九百</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz002724</t>
+          <t>sz002535</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>海洋王</t>
+          <t>林州重机</t>
         </is>
       </c>
     </row>
@@ -4458,72 +3308,72 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh600838</t>
+          <t>sh603089</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>正裕工业</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh603089</t>
+          <t>sh603028</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>正裕工业</t>
+          <t xml:space="preserve">赛福天  </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sh603528</t>
+          <t>sz301502</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>华阳智能</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz002535</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>林州重机</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sz003021</t>
+          <t>sh603528</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>兆威机电</t>
+          <t>多伦科技</t>
         </is>
       </c>
     </row>
@@ -4533,12 +3383,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sh603028</t>
+          <t>sz002931</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">赛福天  </t>
+          <t>锋龙股份</t>
         </is>
       </c>
     </row>
@@ -4548,12 +3398,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sz301502</t>
+          <t>sh605488</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>华阳智能</t>
+          <t>福莱新材</t>
         </is>
       </c>
     </row>
@@ -4563,12 +3413,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sz000700</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>模塑科技</t>
         </is>
       </c>
     </row>
@@ -4578,12 +3428,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>sh603280</t>
+          <t>sh600094</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>南方路机</t>
+          <t xml:space="preserve">大名城  </t>
         </is>
       </c>
     </row>
@@ -4593,12 +3443,57 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>sh603933</t>
+          <t>sz000810</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>睿能科技</t>
+          <t>创维数字</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>sh603901</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>永创智能</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>sz000559</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>万向钱潮</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>sh603337</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>杰克科技</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,20 +476,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="99" customWidth="1" min="3" max="3"/>
+    <col width="89" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="252" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="247" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,46 +556,45 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sz002535</t>
+          <t>sh603028</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>林州重机</t>
+          <t xml:space="preserve">赛福天  </t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3.33</v>
+        <v>10.33</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.901</v>
+        <v>10.0106</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>7天4板</t>
+          <t>4天4板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>军工+机器人|1.公司与多家大型军工集团建立了合作关系，并承接、交付了多批次的订单。
-2.公司曾于14年定增募资1.02亿元用于工业机器人产业化（一期）项目。</t>
+          <t>机器人|在工业机器人领域，公司凭借对钢丝绳在升降与传动系统中核心技术的深度研发与创新应用，成功突破了传统业务的边界，开辟了全新的市场空间。通过为仓储智能机器人企业深圳市海柔创新科技有限公司提供高性能的升降配件解决方案，公司实现了从传统制造业向高端智能装备领域的跨越式发展。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>军工, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -606,45 +605,46 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sh603089</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>正裕工业</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>13.08</v>
+        <v>16.01</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.0084</v>
+        <v>10.0344</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>4天4板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司布局机器人零部件赛道，致力于机器人用柔性触觉传感技术的研发、传感器的设计与制造、以及信号处理系统的开发与测试，已完成核心产品的技术攻关与样品研发。</t>
+          <t>军工+机器人|1.公司是湖北省军民融合企业，东风公司的军车轴承一直指定公司独家供应。
+2.公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>军工, 机器人</t>
         </is>
       </c>
     </row>
@@ -655,45 +655,46 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh603028</t>
+          <t>sh603528</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">赛福天  </t>
+          <t>多伦科技</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.953199999999999</v>
+        <v>10.0559</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>4天4板</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>机器人|在工业机器人领域，公司凭借对钢丝绳在升降与传动系统中核心技术的深度研发与创新应用，成功突破了传统业务的边界，开辟了全新的市场空间。通过为仓储智能机器人企业深圳市海柔创新科技有限公司提供高性能的升降配件解决方案，公司实现了从传统制造业向高端智能装备领域的跨越式发展。</t>
+          <t>智能驾驶+机器人|1.公司已开展多项人工智能驾考新技术研究，包括基于机器视觉的驾驶人注意力分配识别、基于机器视觉的道路环境目标识别、基于激光雷达的目标探测技术等。
+2.公司通过珠海星芯投资基金参与了众擎机器人科技有限公司Pre-A++轮融资，并持有其1.57%的股份。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>智能驾驶, 机器人</t>
         </is>
       </c>
     </row>
@@ -704,41 +705,40 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sh603528</t>
+          <t>sz002708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>光洋股份</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>8.949999999999999</v>
+        <v>17.22</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9.950900000000001</v>
+        <v>10.0319</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>机器人|1.公司已开展多项人工智能驾考新技术研究，包括基于机器视觉的驾驶人注意力分配识别、基于机器视觉的道路环境目标识别、基于激光雷达的目标探测技术等。
-2.公司通过珠海星芯投资基金参与了众擎机器人科技有限公司Pre-A++轮融资，并持有其1.57%的股份。</t>
+          <t>机器人|2024年12月2日公告，公司拟与安徽黄山高新技术开发区管理委员会签订《项目投资协议书》，在安徽省黄山高新区内拍取面积100亩土地使用权用于建设年产6000万套高端新能源汽车及机器人用精密零部件项目，以公司全资子公司黄山光洋传动科技有限公司为投资建设主体。本次项目投资总额预计为100,000万元。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -754,45 +754,45 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sz001331</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>胜通能源</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>14.55</v>
+        <v>38.52</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9.9773</v>
+        <v>9.994300000000001</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
+          <t>七腾机器人入主|胜通能源公告称，七腾机器人向公司除收购人及其一致行动人外的全体股东发出部分要约收购，预定收购股份数量42,336,000股，占公司总股本的15%，要约价格为13.28元/股。要约收购期限为2026年4月28日至2026年5月27日，最后三个交易日预受要约不可撤销。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>七腾机器人入主</t>
         </is>
       </c>
     </row>
@@ -803,40 +803,40 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sz301502</t>
+          <t>sh605333</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>华阳智能</t>
+          <t>沪光股份</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>77.76000000000001</v>
+        <v>19.91</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3天3板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司的无框电机可应用于机器人、协作机器人及高端医疗器械等领域。</t>
+          <t>机器人|2026年8月12日，公司与北京辉羲智能信息技术有限公司、全能具身智能科技（苏州）有限公司、灵巧科技（昆山）有限公司四方正式签署具身智能战略合作仪式，依托沪光在汽车线束制造及场景化机器人应用方面的深厚积淀，叠加合作伙伴在芯片设计、具身智能算法及灵巧操作系统等维度的顶尖能力，有望构建起“场景定义—芯片赋能—技术落地”的闭环生态，为具身智能在工业领域的大规模应用打造可复制的标杆范式。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -852,40 +852,40 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh603337</t>
+          <t>sh603370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>杰克科技</t>
+          <t>华新精科</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>43.19</v>
+        <v>30.81</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.0102</v>
+        <v>9.9964</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司在2024年年报中透露，公司高端产品研发取得里程碑进展，高端AI缝纫机原型样机成功落地，“杰克1号”人形机器人、无人模板机等“机器人+AI人工智能+缝制机械”多技术融合的智能高端产品初具雏形。</t>
+          <t>机器人|公司铁芯产品下游应用广阔，可应用于机器人关节等相关部位的电机。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -901,45 +901,46 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz000559</t>
+          <t>sz002249</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>万向钱潮</t>
+          <t>大洋电机</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>12.71</v>
+        <v>7.7</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.0433</v>
+        <v>10</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司在机器人领域主要布局精密轴承和丝杠，目前相关产品尚处于开发验证阶段。</t>
+          <t>机器人+稀土|1.公司前瞻技术研究院已设立前瞻技术研究项目--人形机器人电机项目，其中涉及包括无框力矩电机在内的多项研究。
+2.公司持有宁波科星材料科技有限公司51%的股份，宁波科星是一家专注于烧结钐钴、烧结钕铁硼永磁材料及产品研发和制造的高新技术企业，产品广泛应用于曳引机、汽车、电子信息、医疗、航空航天、国防等领域。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>机器人, 稀土</t>
         </is>
       </c>
     </row>
@@ -950,45 +951,42 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sz002931</t>
+          <t>sh603758</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>锋龙股份</t>
+          <t>秦安股份</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>42.37</v>
+        <v>10.73</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>9.9948</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0513</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>优必选入主|锋龙股份公告称，本次股份协议转让已完成，公司控股股东变更为优必选，实际控制人变更为周剑。根据中国证券登记结算有限责任公司于2026年3月12日出具的《证券过户登记确认书》，本次协议转让事项过户登记手续已办理完毕，过户日期为2026年3月11日，过户股数为6552.99万股，占公司股份总数的29.99%，股份性质为无限售流通股。</t>
+          <t>汽车+机器人|1.公司是国内具有一定规模水平的汽车发动机核心零部件专业生产企业，主要从事汽车发动机核心零部件——气缸体、气缸盖、曲轴、变速器箱体等产品的研发、生产与销售。
+2.参股墨现科技专注于触觉传感器领域，为各种应用场景提供高适应性柔性压力传感器解决方案。其研发的电子皮肤技术还在机器人灵巧手和机械臂上取得了显著进展，并逐渐拓展至机器人本体全身。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>优必选入主</t>
+          <t>汽车, 机器人</t>
         </is>
       </c>
     </row>
@@ -999,40 +997,36 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sz000700</t>
+          <t>sh601956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>模塑科技</t>
+          <t>东贝集团</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>13.07</v>
+        <v>5.54</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10.0168</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>9.9206</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>机器人|2025年12月16日公告，公司与国内某机器人企业签订零部件采购框架协议，并获得人形机器人外覆盖件小批量采购订单。</t>
+          <t>机器人|2025年4月17日公司在互动平台表示，公司转子压缩机具备量产能力，正在进行客户匹配性能测试。另外，公司在洗衣机电机、空调电机、机器人关节电机等领域均有相关技术研发储备。人形机器人关节电机目前还处于研发测试阶段。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1048,40 +1042,36 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sh603901</t>
+          <t>sz300539</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>永创智能</t>
+          <t>横河精密</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>10.63</v>
+        <v>19.68</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.0414</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司在通过自主研发图像识别、视觉检测工业机器人等技术集成于公司智能包装生产线系列产品，提高智能包装生产线的柔性化和智能化；同时公司进一步完善标准包装设备产品的模块化分解，缩短标准包装设备产品的研发设计周期。</t>
+          <t>机器人|公司齿轮箱/减速器类产品主要应用在智能扫地机器人等领域。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1097,36 +1087,36 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sz300916</t>
+          <t>sh603037</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>朗特智能</t>
+          <t>凯众股份</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>34.27</v>
+        <v>11.87</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>19.993</v>
+        <v>10.0093</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司在机器人领域主要专注于扫地机器人智能控制器、清洁机器人及服务型机器人的组装及代工等。</t>
+          <t>机器人|公司的聚氨酯材料具有高强度、高弹性、高耐磨、重量轻、易加工等优良特性，可以用于人形机器人的制造。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1142,42 +1132,41 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz002178</t>
+          <t>sz002823</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>延华智能</t>
+          <t>凯中精密</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>5.34</v>
+        <v>13.49</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.1031</v>
+        <v>10.0326</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>机器人+AI医疗|1.“建筑设施智能巡检机器人”为上海张江国家自主创新示范区专项发展资金重点项目，由子公司东方延华研发。
-2.在智慧医疗领域，公司研究开发了HIS系统、智能化电子病历系统、基于微服务的医院信息化集成平台，基于AI的临床辅助诊断系统、全流程医疗质量管理系统、智能决策分析系统、智能导诊系统、城市智慧救护车云服务平台、医疗质量信息管理平台、医院总值班信息系统平台、医护一体化平台等。</t>
+          <t>机器人|参股武汉数字化设计与制造创新中心有限公司的经营范围包括智能机器人的研发、智能机器人销售。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>机器人, AI医疗</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -1188,41 +1177,42 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sh688648</t>
+          <t>sz301682</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>中邮科技</t>
+          <t>宏明电子</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>34.66</v>
+        <v>102.1</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>20.0139</v>
+        <v>20.0047</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司及子公司拥有的已授权专利情况包括：一种双承载分拣机器人（实用新型）、一种基于智能机器人的自动分拣矩阵系统（实用新型）。</t>
+          <t>机器人+MLCC|1.公司间接供应的无框力矩电机产品，最终用于人形机器人关节中，目前已实现小批量应用配套。
+2.公司是国内少数从高品质电子材料（陶瓷瓷料和导电浆料）到电子元器件均具备研制能力的全产业链生产企业，核心产品为高可靠MLCC产品，拥有国内首条宇航级MLCC生产线。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>机器人, MLCC</t>
         </is>
       </c>
     </row>
@@ -1233,36 +1223,36 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.771</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz002708</t>
+          <t>sz301479</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>弘景光电</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>15.65</v>
+        <v>56.15</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>9.978899999999999</v>
+        <v>20.0043</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>机器人|2024年12月2日公告，公司拟与安徽黄山高新技术开发区管理委员会签订《项目投资协议书》，在安徽省黄山高新区内拍取面积100亩土地使用权用于建设年产6000万套高端新能源汽车及机器人用精密零部件项目，以公司全资子公司黄山光洋传动科技有限公司为投资建设主体。本次项目投资总额预计为100,000万元。</t>
+          <t>机器人|公司的光学镜头及摄像模组产品可用于人形机器人。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1274,316 +1264,332 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>商业零售</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>0.199</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>商务部流通发展司负责人表示，据国家统计局数据，1至9月，我国批发和零售业增加值11.1万亿元，同比增长4.4%，增速较上半年提高0.7个百分点，占GDP比重为10.4%。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sz001225</t>
+          <t>sh600838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>和泰机电</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>31.08</v>
+        <v>13.31</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.0177</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5天5板</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司通过持续实施自动化、智能化改造，更新迭代生产设备，在物料输送设备制造领域的生产工艺已相对成熟，应用了机器人自动焊接技术，机器人视觉识别自动上下料、自动装箱等技术。</t>
+          <t>零售|公司控股股东为上海九百（集团）有限公司。目前已经发展成为涉及洗涤化工产品生产销售及洗染服务、酒类产品批发等多种业态的综合性企业。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>商业零售</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>0.199</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>商务部流通发展司负责人表示，据国家统计局数据，1至9月，我国批发和零售业增加值11.1万亿元，同比增长4.4%，增速较上半年提高0.7个百分点，占GDP比重为10.4%。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sz001331</t>
+          <t>sh600785</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>胜通能源</t>
+          <t>新华百货</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>35.02</v>
+        <v>13.9</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.987400000000001</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+        <v>9.968399999999999</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>七腾机器人入主|胜通能源公告称，七腾机器人向公司除收购人及其一致行动人外的全体股东发出部分要约收购，预定收购股份数量42,336,000股，占公司总股本的15%，要约价格为13.28元/股。要约收购期限为2026年4月28日至2026年5月27日，最后三个交易日预受要约不可撤销。</t>
+          <t>零售|公司是宁夏乃至西北地区较大的商业零售企业，主要从事商业零售、物流和商业物业出租业务，零售业务主要涉及百货商场、综合购物中心、超市连锁、电器及通信连锁。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>七腾机器人入主</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>商业零售</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>0.199</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>商务部流通发展司负责人表示，据国家统计局数据，1至9月，我国批发和零售业增加值11.1万亿元，同比增长4.4%，增速较上半年提高0.7个百分点，占GDP比重为10.4%。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh603683</t>
+          <t>sh600828</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>晶华新材</t>
+          <t>茂业商业</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>17.16</v>
+        <v>4.47</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10</v>
+        <v>10.0985</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>机器人+固态电池|1.旗下子公司晶智感发布高自由度灵巧手全掌全触觉电子皮肤，该产品采用压阻式工艺，能为机器人的灵巧手提供触觉感知能力，可部署在手的各个区域。
-2.在新能源动力电池方面，针对新能源电池电芯、模组、PACK不同组件背胶要求特性，公司建立完善的产品类别，已成熟运用于软包电池、半固态电池。</t>
+          <t>零售|公司业务以商业零售为主，并辅以部分物业租赁和酒店业务，旗下实体零售门店数量总共22家，经营业态包括百货商场、购物中心、奥特莱斯及超市；商业零售主要经营模式仍为自营模式、联营模式和租赁模式，以联营模式为主。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>机器人, 固态电池</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>商业零售</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>0.199</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>商务部流通发展司负责人表示，据国家统计局数据，1至9月，我国批发和零售业增加值11.1万亿元，同比增长4.4%，增速较上半年提高0.7个百分点，占GDP比重为10.4%。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sh605333</t>
+          <t>sz002187</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>沪光股份</t>
+          <t>广百股份</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>18.1</v>
+        <v>5.92</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.0304</v>
+        <v>10.0372</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>机器人|2026年8月12日，公司与北京辉羲智能信息技术有限公司、全能具身智能科技（苏州）有限公司、灵巧科技（昆山）有限公司四方正式签署具身智能战略合作仪式，依托沪光在汽车线束制造及场景化机器人应用方面的深厚积淀，叠加合作伙伴在芯片设计、具身智能算法及灵巧操作系统等维度的顶尖能力，有望构建起“场景定义—芯片赋能—技术落地”的闭环生态，为具身智能在工业领域的大规模应用打造可复制的标杆范式。</t>
+          <t>零售|公司是广东省百货连锁龙头、广州市销售规模最大的百货零售企。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>商业零售</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>0.199</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>商务部流通发展司负责人表示，据国家统计局数据，1至9月，我国批发和零售业增加值11.1万亿元，同比增长4.4%，增速较上半年提高0.7个百分点，占GDP比重为10.4%。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh688386</t>
+          <t>sh601086</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>泛亚微透</t>
+          <t>国芳集团</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46.56</v>
+        <v>12.62</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>20</v>
+        <v>10.0262</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>机器人|在人形机器人方向，公司与柔性传感技术标杆企业苏州能斯达电子科技有限公司签署战略合作协议及委托开发协议，双方将聚焦机器人用ePTFE膜电子皮肤领域开展深度合作，携手打造技术协同、产业联动的创新生态，提升机器人用电子皮肤和关节等零部件性能，解决电子皮肤使用寿命、耐磨、抗压、防水透气等性能的技术瓶颈。</t>
+          <t>零售|公司从事以百货业为主，超市、电器为辅的连锁零售业务，是甘肃省内最大的连锁零售企业。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>零售</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.1342</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>国家发改委表示，正在研究制定扩大内需战略实施方案（2026—2030年），并将加快推动印发实施。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>sh688585</t>
+          <t>sz001219</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>上纬新材</t>
+          <t>青岛食品</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>151.57</v>
+        <v>14.98</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>19.9984</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+        <v>9.985300000000001</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>机器人|上纬新材消费级机器人启元Q1、启元T1双产品开启预订，用户可通过上纬启元官方小程序、天猫、抖音、B站官方店铺，以及线下体验活动参与预订，预计首批发货时间为今年9月。据了解，此前上纬新材与蓝思科技旗下蓝思智能机器人签约，落地首期万台级规模机器人产线合作；同时与卧龙电驱达成核心部件产线战略合作。</t>
+          <t>休闲食品+业绩|1.公司主要从事饼干与花生酱等休闲食品的研发、生产及销售，主要产品包括“青食”品牌钙奶饼干、“青食”品牌休闲饼干和“海友”品牌花生酱。
+2.公司2026年7-9月实现营业收入为1.57亿元，同比上升7.1%；归母净利润为3678万元，同比上升31.2%。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>休闲食品, 业绩</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>机器人概念</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-2.1342</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10月23日至25日，2026全球开发者先锋大会暨国际具身智能技能大赛在上海举行，智元组织110台远征A3全尺寸人形机器人同场群舞，创下最多人形机器人同时跳舞的吉尼斯世界纪录。</t>
+          <t>国家发改委表示，正在研究制定扩大内需战略实施方案（2026—2030年），并将加快推动印发实施。</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>sh603331</t>
+          <t>sz002820</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>百达精工</t>
+          <t>桂发祥</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>12.91</v>
+        <v>11.21</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9.9659</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
+        <v>10.0098</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司已布局人形机器人灵巧手指部关节模组核心零部件以及具身机器人手部关节与腿部关节的核心铝制结构件等具身智能机器人核心零部件。</t>
+          <t>休闲食品|公司是专业从事传统特色及其他休闲食品的研发、生产和销售的中华老字号企业，自产产品包括麻花、糕点、节令食品、天津风味方便食品等。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>休闲食品</t>
         </is>
       </c>
     </row>
@@ -1594,1645 +1600,890 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.7533</v>
+        <v>-2.1342</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
+          <t>国家发改委表示，正在研究制定扩大内需战略实施方案（2026—2030年），并将加快推动印发实施。</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>sz002696</t>
+          <t>sz001318</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>百洋股份</t>
+          <t>阳光乳业</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>11.28</v>
+        <v>13.31</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10.0488</v>
+        <v>10</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12天8板</t>
+          <t>2天2板</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>水产品+鱼粉|1.公司位于广西，水产品加工业务板块将着重研发以罗非鱼、生鱼、金鲳鱼、海鲈鱼为原料的内销产品。
-2.公司下辖鱼粉厂的合计年产量约为1-2万吨，鱼油年产量约为2000-4000吨。</t>
+          <t>乳制品|公司专注于乳制品及乳饮料的研发、生产和销售，并以低温乳制品、低温乳饮料为主打产品。公司针对儿童提高免疫力开发的“初乳” 产品。公司从事液态乳、含乳饮料等产品的研发、生产、销售。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>水产品, 鱼粉</t>
+          <t>乳制品</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>业绩超预期</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.7533</v>
+        <v>-3.3196</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
+          <t>部分机构策略展望研报认为，当前市场底部信号密集释放，进攻端关注三季报预期向好、产业趋势明确且基本面坚挺的超跌方向。</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sz002086</t>
+          <t>sz002011</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东方海洋</t>
+          <t>盾安环境</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>2.3</v>
+        <v>11.37</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>10.0478</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>9.9613</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>水产品+医药|1.公司主营业务为海洋水产品加工和海水养殖，其中海参养殖是公司海水养殖的传统主导业务。
-2.公司大健康事业部已布局免疫技术平台、质谱技术平台、分子技术平台及第三方医学检验实验室等四大平台。</t>
+          <t>业绩|公司2026年7-9月实现营业收入35.36亿元，同比增长18.12%；归母净利润2.61亿元，同比增长11.94%。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>水产品, 医药</t>
+          <t>业绩</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>业绩超预期</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.7533</v>
+        <v>-3.3196</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
+          <t>部分机构策略展望研报认为，当前市场底部信号密集释放，进攻端关注三季报预期向好、产业趋势明确且基本面坚挺的超跌方向。</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sz001219</t>
+          <t>sz300504</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>青岛食品</t>
+          <t>天邑股份</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>13.62</v>
+        <v>17.69</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10.0162</v>
+        <v>20.0136</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>休闲食品|公司主要从事饼干与花生酱等休闲食品的研发、生产及销售，主要产品包括“青食”品牌钙奶饼干、“青食”品牌休闲饼干和“海友”品牌花生酱。</t>
+          <t>业绩|公司2026年1-9月实现营业收入12.82亿元，同比增长30.40%；归母净利润0.98亿元，同比增长277.38%。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>休闲食品</t>
+          <t>业绩</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>业绩超预期</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.7533</v>
+        <v>-3.3196</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
+          <t>部分机构策略展望研报认为，当前市场底部信号密集释放，进攻端关注三季报预期向好、产业趋势明确且基本面坚挺的超跌方向。</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sh603719</t>
+          <t>sh603565</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>良品铺子</t>
+          <t>中谷物流</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>12.58</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>9.953199999999999</v>
+        <v>9.965</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>休闲食品|公司主营休闲食品，已形成覆盖肉类零食、坚果炒货、糖果糕点、果干果脯、素食山珍等多个品类、1000余种的产品组合。</t>
+          <t>业绩|中谷物流公告称，第三季度营业收入为29.18亿元，同比增长13.95%；归属于上市公司股东的净利润为8.45亿元，同比增长149.41%。前三季度营业收入为83.75亿元，同比增长6.04%；归属于上市公司股东的净利润为19.28亿元，同比增长36.70%。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>休闲食品</t>
+          <t>业绩</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>智能驾驶</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.7533</v>
+        <v>-2.8624</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
+          <t>大众中国发布消息称，大众汽车集团（中国）已在合肥正式获得L3级自动驾驶道路测试牌照，并已在合肥启动L3级技术的真实道路测试与数据采集。</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sz002820</t>
+          <t>sh603376</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>桂发祥</t>
+          <t>大明电子</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>10.19</v>
+        <v>26.3</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>10.0432</v>
+        <v>9.995800000000001</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>休闲食品|公司是专业从事传统特色及其他休闲食品的研发、生产和销售的中华老字号企业，自产产品包括麻花、糕点、节令食品、天津风味方便食品等。</t>
+          <t>智能驾驶|公司主要产品包括驾驶辅助系统、座舱中控系统、智能光电系统、门窗控制系统、座椅调节系统等。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>休闲食品</t>
+          <t>智能驾驶</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>智能驾驶</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.7533</v>
+        <v>-2.8624</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
+          <t>大众中国发布消息称，大众汽车集团（中国）已在合肥正式获得L3级自动驾驶道路测试牌照，并已在合肥启动L3级技术的真实道路测试与数据采集。</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>sz001318</t>
+          <t>sz002284</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>阳光乳业</t>
+          <t>亚太股份</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>12.1</v>
+        <v>9.67</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10</v>
+        <v>10.0114</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>乳制品|公司专注于乳制品及乳饮料的研发、生产和销售，并以低温乳制品、低温乳饮料为主打产品。公司针对儿童提高免疫力开发的“初乳” 产品。公司从事液态乳、含乳饮料等产品的研发、生产、销售。</t>
+          <t>智能驾驶|公司以汽车主动安全技术为基础，布局汽车智能网联产业和新能源产业，打造智能汽车环境感知+主动安全控制+移动互联的无人驾驶产业链。公司以成功开发并产业化的汽车防抱死制动系统ABS为基础，逐步实现各类汽车底盘电子制动系统产品的开发。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>乳制品</t>
+          <t>智能驾驶</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.7533</v>
+        <v>-3.6932</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>近日商务部消费促进司负责人介绍2026年前三季度我国消费市场情况。前三季度，商务部深入实施提振消费专项行动，出台一系列促消费政策措施，推动消费市场规模稳步扩大、居民消费结构持续优化。</t>
+          <t>据报道，Anthropic计划在11月16日当周进行IPO。Anthropic在IPO文件中表示，公司上半年营收163亿美元，去年同期为12亿美元。</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>sz000995</t>
+          <t>sz002093</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>皇台酒业</t>
+          <t>国脉科技</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>13.37</v>
+        <v>7.93</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>10.0412</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+        <v>9.9861</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>葡萄酒|西北风格的名优白酒。葡萄酒产品依靠河西走廊得天独厚的地理优势，酒体品质达到了国际标准。</t>
+          <t>数据要素+AI|1.参股公司国脉生物以全球领先、低成本的“群体基因型数据库”建库技术与数据分析能力，为各地市解决公共卫生问题，为居民提供精准健康管理服务，同时运用区块链、分布式存储等技术解决数据安全、确权、交易中的痛点，激励用户、研究机构共享数据与算法，进一步提高数据在生态中的使用效率。
+2.公司一直高度重视人工智能在我司业务中的应用价值，已与多家主流大模型服务商建立合作关系，并结合各家平台的技术优势，打造更适配社区与居家养老场景的AI agent。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>葡萄酒</t>
+          <t>数据要素, AI</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.5710999999999999</v>
+        <v>-3.6932</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>国联民生指出，国家数据集团有望推动公共数据由分散走向统筹，把数据资源优势转化为AI产业优势。具备数据要素运营、治理与安全能力的厂商有望充分受益。</t>
+          <t>据报道，Anthropic计划在11月16日当周进行IPO。Anthropic在IPO文件中表示，公司上半年营收163亿美元，去年同期为12亿美元。</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sh603138</t>
+          <t>sh600715</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>海量数据</t>
+          <t>文投控股</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>17</v>
+        <v>1.87</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10.0324</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>4天3板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>数据要素+AI应用|1.公司是国内主要的关系型数据库产品提供商，也是国内数据库基础软件产业发展的重要参与者和推动者。公司的企业级大数据平台提供全域数据资产管理功能，可以帮助客户采集和汇聚数据，经过治理后形成数据资产，为数字化应用提供支撑。该平台可实现全过程可视化，能快速开发数据类应用系统。
-2.公司发布的企业级大数据应用平台提供AI驱动的增强分析功能，如时序预测分析、关联分析、根因分析等，助力数据驱动决策。</t>
+          <t>短剧+AI|公司已针对短剧行业进行深入研究，并计划依托自身IP资源孵化优势，结合AIGC等工具的发展应用，探索文化内容与科技手段相融合的新型创作模式。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>数据要素, AI应用</t>
+          <t>短剧, AI</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
+          <t>ST股</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.5710999999999999</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>国联民生指出，国家数据集团有望推动公共数据由分散走向统筹，把数据资源优势转化为AI产业优势。具备数据要素运营、治理与安全能力的厂商有望充分受益。</t>
-        </is>
-      </c>
+        <v>-1.3577</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>sh600822</t>
+          <t>sh603843</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>上海物贸</t>
+          <t xml:space="preserve">*ST正平 </t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>4.97</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>9.976500000000001</v>
+        <v>9.9558</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>数据要素|旗下上海有色金属交易中心有限公司有研发的数据产品——有色金属现货指数查询，已在上海数据交易所备案并挂牌。</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>数据要素</t>
-        </is>
-      </c>
+          <t>ST股 | 2025年2月21日公司官微披露，旗下正平智算参加海东市绿色算力产业集中签约暨推介活动并签订算电协同产业园框架协议。</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>0.5710999999999999</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>国联民生指出，国家数据集团有望推动公共数据由分散走向统筹，把数据资源优势转化为AI产业优势。具备数据要素运营、治理与安全能力的厂商有望充分受益。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>sz002095</t>
+          <t>sz002724</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>生 意 宝</t>
+          <t>海洋王</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>16.48</v>
+        <v>13.09</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>10.0134</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>8天7板</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>大宗商品数据商|公司是大宗商品数据商，主要跟踪能源、化工、橡塑、有色、钢铁、纺织、建材和农副八大行业的大宗原材料现货价格，以及上期所，郑商所，大商所和国外期货市场的期货价格数据。同时，为产业用户提供大宗原材料撮合服务。通过10多年的积累，已形成了价格、均价、涨跌榜、指数等数据产品形式，并形成了完整的价格数据采集、加工、研究和发布体系。</t>
+          <t>军工|公司是武器装备科研生产三级保密资格单位，设有专门的军品事业部负责军品的销售。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>大宗商品数据商</t>
+          <t>军工</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>数据要素</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>0.5710999999999999</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>国联民生指出，国家数据集团有望推动公共数据由分散走向统筹，把数据资源优势转化为AI产业优势。具备数据要素运营、治理与安全能力的厂商有望充分受益。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sz002093</t>
+          <t>sz301314</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>国脉科技</t>
+          <t>科瑞思</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7.21</v>
+        <v>67.37</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10.0763</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+        <v>20.0036</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>数据要素+AI应用|1.参股公司国脉生物以全球领先、低成本的“群体基因型数据库”建库技术与数据分析能力，为各地市解决公共卫生问题，为居民提供精准健康管理服务，同时运用区块链、分布式存储等技术解决数据安全、确权、交易中的痛点，激励用户、研究机构共享数据与算法，进一步提高数据在生态中的使用效率。
-2.公司一直高度重视人工智能在我司业务中的应用价值，已与多家主流大模型服务商建立合作关系，并结合各家平台的技术优势，打造更适配社区与居家养老场景的AI agent。</t>
+          <t>并购重组+光通信|2026年10月12日公告，公司正筹划发行股份及支付现金购买资产并募集配套资金事项，拟购买深圳市宏钢光电封装技术股份有限公司100%股权。标的公司主营产品为光通讯管壳、激光器管壳、预置金锡热沉、混合集成电路管壳等。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>数据要素, AI应用</t>
+          <t>并购重组, 光通信</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>业绩超预期</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>-2.7035</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>部分机构策略展望研报认为，当前市场底部信号密集释放，进攻端关注三季报预期向好、产业趋势明确且基本面坚挺的超跌方向。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sh600826</t>
+          <t>sh600303</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>兰生股份</t>
+          <t>曙光股份</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>8.220000000000001</v>
+        <v>3.11</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>10.0402</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
+        <v>9.894</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>3天2板</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>业绩|公司2026年7-9月实现营业收入6.37亿元，同比增长35.14%；归母净利润1.4亿元，同比增长12.97%。</t>
+          <t>汽车整车|公司是以整车、车桥及零部件为主营业务的跨地区的企业集团。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>业绩</t>
+          <t>汽车整车</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>业绩超预期</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>-2.7035</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>部分机构策略展望研报认为，当前市场底部信号密集释放，进攻端关注三季报预期向好、产业趋势明确且基本面坚挺的超跌方向。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sh600980</t>
+          <t>sz000058</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>北矿科技</t>
+          <t>深 赛 格</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>18.95</v>
+        <v>7.87</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9.9826</v>
+        <v>10.0699</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>业绩|公司2026年1-9月实现营业收入10.30亿元，同比增长19.92%；归母净利润约1.09亿元，同比增长30.37%。</t>
+          <t>创投|公司拟与深创投集团合作发起设立“深圳市红土赛格智能产业投资基金（有限合伙）”。公司地处广东深圳，积极开展创新创客业务，赛格众创空间构建智能硬件创客交流平台与创新项目的孵化基地。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>业绩</t>
+          <t>创投</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>业绩超预期</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>-2.7035</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>部分机构策略展望研报认为，当前市场底部信号密集释放，进攻端关注三季报预期向好、产业趋势明确且基本面坚挺的超跌方向。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sz000411</t>
+          <t>sz001400</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>英特集团</t>
+          <t>江顺科技</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>10.52</v>
+        <v>80.28</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.0418</v>
+        <v>10.0027</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>业绩|公司2026年7-9月实现营业收入88.21亿元，同比增长5.84%；归母净利润1.05亿元，同比增长41.59%。</t>
+          <t>液冷+商业航天|1.子公司江宇科技主要从事用于服务器液冷相关的3D打印产品的研发工作，已有部分样品。
+2.公司产品铝型材挤压模具和铝型材挤压配套设备应用于航空航天领域。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>业绩</t>
+          <t>液冷, 商业航天</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>物理AI</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>0.4224000000000001</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>智元正式开源AGIBOT WORLD 2026第四期“具身推理”（Physical Reasoning）——首个真实场景Physical Agent数据集。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>sh605488</t>
+          <t>sh603813</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>福莱新材</t>
+          <t>原尚股份</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>41.97</v>
+        <v>24.2</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>10.0131</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>6天4板</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>物理AI|公司与浙江清华柔性电子技术研究院共建智能感知联合实验室，聚焦柔性电子皮肤与超宽域压力传感器研发；并与通智人工智能科技（北京）有限公司签署战略合作协议，推进“材料-感知-算法-终端”一体化的具身智能生态建设，强化触觉信号与AI大模型的深度融合。</t>
+          <t>物流|公司的主营业务为汽车整机厂及其供应商提供零部件干线运输、配送、仓储、品质检验、流通加工以及包装等全方位、一体化的综合物流服务,主要产品或服务为综合物流服务、物流设备销售、保险代理、商品贸易等。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>物理AI</t>
+          <t>物流</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>物理AI</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>0.4224000000000001</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>智元正式开源AGIBOT WORLD 2026第四期“具身推理”（Physical Reasoning）——首个真实场景Physical Agent数据集。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sz000810</t>
+          <t>sz002205</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>创维数字</t>
+          <t>国统股份</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>11.02</v>
+        <v>11.4</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
+        <v>10.0386</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>数据采集|公司的EGO数据采集设备面向具身智能与机器人训练场景，已于海内外市场形成销售。</t>
+          <t>建材|公司产品PCCP（预应力钢筒混凝土管）技术含量较高，规格齐全，公司积极推进产品结构及业务调整转型，通过PPP模式积极参与水务、地下综合管廊等市政基础设施的投资、建设、运营，培育新的利润增长点。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>数据采集</t>
+          <t>建材</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>0.1153</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>据市场研究机构Omdia预测，亚太及大洋洲地区的AI智能体软件市场规模将从2025年的7.82亿美元跃升至2030年的112亿美元，年复合增长率达94%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sh601900</t>
+          <t>sz000888</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>南方传媒</t>
+          <t>峨眉山Ａ</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>14.28</v>
+        <v>10.1</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10.0154</v>
+        <v>10.0218</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>传媒+AI应用|1.公司是广东省出版集团以主要经营性资产和业务发起设立的股份制公司。公司旗下拥有出版、印刷、发行、报刊、数字、投资等一体化完整产业链。
-2.公司可应用AI技术的数字教育产品主要为粤教翔云数字教材应用平台。</t>
+          <t>旅游+冰雪产业|1.峨眉山风景区是世界自然与文化双重遗产，国家5A级风景区。公司主要从事峨眉山风景区游山门票、客运索道、宾馆酒店服务以及其他相关旅游服务的经营。
+2.公司在互动平台表示，1998年，四川首个高山滑雪场在峨眉山雷洞坪诞生，峨眉山举办首届冰雪节，推出冰雪主题十大冬游项目，填补了四川冬游市场的空白。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>传媒, AI应用</t>
+          <t>旅游, 冰雪产业</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AI应用</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>0.1153</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>据市场研究机构Omdia预测，亚太及大洋洲地区的AI智能体软件市场规模将从2025年的7.82亿美元跃升至2030年的112亿美元，年复合增长率达94%。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>sz300949</t>
+          <t>sh601566</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>奥雅股份</t>
+          <t xml:space="preserve">九牧王  </t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>35.58</v>
+        <v>10.32</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>20</v>
+        <v>10.0213</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>短剧+AI应用|1.公司建立了专门的短视频团队、短剧制作团队以及宣传片制作团队，这些团队毕业于海外知名电影学院，拥有非常国际化的视野和背景。
-2.“AI+IP”双引擎赋能是公司的长期策略，项目已广泛应用AI工具重塑工作流，落地项目包括广州花都蓝莓基地项目、衢州南孔洛嘉森乐园、顺德北滘体育（儿童）乐园等项目。</t>
+          <t>福建+纺织|国内商务休闲男装品牌的领先企业、国内男裤行业的龙头。主要从事男士商务休闲品牌服饰的生产和销售,主要产品包括男裤、茄克、衬衫、T恤和西装等。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>短剧, AI应用</t>
+          <t>福建, 纺织</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>游戏</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>0.9217</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>万联证券认为，9月获批版号数量延续高位，进一步验证了版号供给常态化运行的稳定性。从年初至今，游戏版号审批节奏已逐步趋于平稳，行业供给端预期持续改善。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>sh603258</t>
+          <t>sz002623</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>电魂网络</t>
+          <t>亚玛顿</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>15.3</v>
+        <v>18.78</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>9.992800000000001</v>
+        <v>10.0176</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>游戏|公司为一家拥有自主研发能力、运营能力的专业化网络游戏公司，致力于自主研发运营精品化的网络游戏。</t>
+          <t>光伏+玻璃基板|1.国内光伏镀膜玻璃、大尺寸超薄光伏玻璃产品的先行及引领者，在行业内率先开发了更加轻量化、薄型化的1.6mm的光伏玻璃、BIPV美学、彩色镀膜玻璃、玻璃扩散板、一体化AG玻璃等具有核心竞争力的产品。
+2.2023年9月16日公司在官微透露，超高清玻璃基板产业项目占地800亩，由常州亚玛顿股份有限公司建设，主要建设年产5800万平方米的超高清玻璃基板生产基地。生产的超高清玻璃基板厚度为0.55毫米至1.1毫米，广泛应用于超高清电视、智能手机、电脑等智能电子产品显示屏制造。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>光伏, 玻璃基板</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>医药</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>据医药魔方统计，2026年1—9月中国创新药BD交易总额达1279.8亿美元，接近2025年全年水平；技术出口目录修订征求意见稿亦明确常见对外授权不受影响。</t>
-        </is>
-      </c>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>sh603716</t>
+          <t>sh600626</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>塞力医疗</t>
+          <t>申达股份</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>16.06</v>
+        <v>3.94</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>10</v>
+        <v>10.0559</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>创新药+AI医疗|1.公司战略投资的心血管领域长效治疗性疫苗的创新性研发公司——武汉华纪元生物技术开发有限公司，其自主研发国家1类生物创新药HJY-ATRQβ-001正式获得国家药品监督管理局（NMPA）的新药临床试验申请（IND）受理通知书。
-2.2025年4月，塞力医疗集团专注于感染及危重症快速分子诊断、脑科学数字疗法为主研方向的AI诊疗技术研发中心（TAIDx Lab）已在上海正式部署完成。</t>
+          <t>汽车零部件+纺织|公司是一家以进出口贸易、产业用纺织品研发与制造为主的多元化经营上市公司，主要业务包括以汽车内件及声学元件和纺织新材料业务为主的产业用纺织品业务、以及纺织品为主的外贸进出口和国内贸易业务。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>创新药, AI医疗</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>智能驾驶</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>-0.3744</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>日前，一位不愿透露姓名的C-V2X领域从业者向记者透露，相关部门已经在推动车辆安装C-V2X（蜂窝车联网）的强标制定工作。相关工作组已经成立，有几十家单位已经参与进来了。</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>sz002869</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>金溢科技</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>20.04</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>9.989000000000001</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>智能驾驶+低空经济|1.公司是智慧交通领域领先的数智化解决方案及产品提供商，打造了完整的车、路、云产品体系,包括车载V2X系列产品、路端V2X边端系统集成产品、云端车路协同云平台和C-V2X车载HMI人机交互系统等。
-2.公司低空智联产品线深耕“高速+低空”特色垂直场景，依托自身在智能交通领域沉淀的融合感知、AI识别、车路通信核心技术，将机器视觉、物联网技术跨界迁移至无人机领域，打造“自动机场+无人机+AI”一体化智能巡检与监测解决方案，精准赋能交通、应急、工程、政务等多行业数字化、智能化升级。</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>智能驾驶, 低空经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>固态电池</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>-0.7462</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>工信部、国家发改委、交通运输部等七部门联合印发的《新型电池产业发展“十五五”规划》提出，到2030年，我国新型电池产业规模实现稳步增长，新体系电池研发取得重大进展，全固态电池初步实现规模化应用。</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>sh603200</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>上海洗霸</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>50.41</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>9.993499999999999</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>固态电池+液冷|1.公司生产的固态电解质粉体材料可以应用于锂离子固态电池，多形态固态电解质粉体材料（含油性、水性、浆料）年产50吨级产线主要采用的是氧化物技术路线，公司储备了硫化物、氯化物等固态电解质的其它固态电解质粉体技术路线。
-2.公司面向腾讯、华为、中国移动等重点客户数据中心提供循环水/空气蒸发冷却等专业服务。</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>固态电池, 液冷</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>-0.4457</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>sh603021</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST华鹏 </t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>10.1156</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司是国内日用玻璃行业的企业之一，主营业务为研发、生产和销售玻璃器皿产品和玻璃瓶罐。</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>-0.4457</v>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>sh600476</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST湘邮 </t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>9.968200000000001</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 公司是邮政物流北斗设备的供应商及技术解决方案提供商，正在做末端无人配送方面的应用研究。</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>-0.4457</v>
-      </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>sz000639</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>ST西王</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>9.8765</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 国内最大的玉米胚芽油生产基地，主要生产销售西王牌系列健康食用油。</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>ST股</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>-0.4457</v>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>sh600180</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*ST瑞茂 </t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>9.821399999999999</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>ST股 | 煤炭供应链业务是公司核心业务版块，业务区域已覆盖国内煤炭资源主产地和主要消费地。</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>sh600838</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>上海九百</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>4天4板</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>零售|公司控股股东为上海九百（集团）有限公司。目前已经发展成为涉及洗涤化工产品生产销售及洗染服务、酒类产品批发等多种业态的综合性企业。</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>零售</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>sh600094</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">大名城  </t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>10.0228</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>房地产+算力|1.公司以房地产为主业，主要从事住宅地产和商业地产的开发，打造城市综合运营商是公司中长期发展目标。
-2.2024年9月13日公告，公司控股子公司名城数字基于算力业务发展需要，向智算公司采购先进计算技术服务，包括但不限于算力和存储服务。此次交易标志着公司在智算中心项目的首期投资将实现落地并投入运营。</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>房地产, 算力</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>sz301314</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>科瑞思</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>56.14</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>20.0086</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>并购重组|科瑞思公告称，拟通过发行股份及支付现金的方式购买李刚等7名交易对方持有的宏钢光电100%股份，并向不超过35名特定投资者发行股份募集配套资金。经申请，公司股票自10月26日起复牌。宏钢光电主要从事激光器、光通讯、混合集成电路、半导体功率器件等领域的封装壳体及高功率光纤激光器芯片热沉的研发、生产与销售。</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr"/>
-      <c r="D53" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>sh600558</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">大西洋  </t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>10.099</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>核电|公司已和国内三大核电公司（中核、国核、广核）充分合作，研发出如碳钢低合金钢、不锈钢、镍基等一系列焊接材料，部分产品用于可控核聚变相关部件的制造。</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>核电</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>sz002795</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>永和智控</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>10.0478</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>剥离资产|公司近期披露系列公告，完成成都永和成等多家亏损医疗、新能源子公司股权及债权转让，彻底甩掉长期拖累业绩的非主业包袱，同时回笼部分运营资金，进一步聚焦自身流体智控核心主业，优化业务结构。</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>剥离资产</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>sh603657</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>春光科技</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>33.88</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>家电|公司主营业务为吸尘器零件、橡塑软管、塑料制品、小家电的研发、制造和销售及自营进出口业务。</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>家电</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>sz002578</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>闽发铝业</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>10.0917</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>福建+铝|公司是国内行业中较早涉足工业型材领域的企业之一，主营业务和产品主要是建筑铝型材、工业铝型材和建筑铝模板的研发、生产、销售。</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>福建, 铝</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>sz000635</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>英 力 特</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>10.0137</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>拟股权转让|英力特公告称，公司控股股东英力特集团拟通过公开征集受让方方式一次性整体协议转让其持有的公司1.55亿股无限售流通股份，占公司总股本的39.41%，转让价格不低于6.27元/股。若本次转让实施完成，公司控制权将发生变更。</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>拟股权转让</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>sz300976</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>达瑞电子</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>并购重组|达瑞电子公告，公司此前约定以9560万元收购麦德坤持有的维斯德20%股权；2026年10月22日，公司与麦德坤正式签署剩余股权收购协议。交易完成后公司将持有维斯德100%股权，目前尚需履行工商变更等相关程序。</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>并购重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr"/>
-      <c r="D59" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>sh603955</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>大千生态</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>27.05</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>10.0041</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业|2025年12月，旗下江苏大千文旅与柳叶湖旅游度假区正式签约。项目以“沉浸式体验、全年龄段适配”为核心，精心打造奇趣雪乡乐园、戏雪乐园、侏罗纪秘境、梦幻绿野仙踪等六大核心体验区，设置20多条滑道、恐龙主题展区、冰雪雕塑区及免费互动项目。</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>冰雪产业</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>sz001317</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>三羊马</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>53.68</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>物流|公司是一家主要通过公铁联运方式为汽车行业和啤酒、饮料、洗涤用品等非汽车行业提供综合服务的第三方物流企业，建成以重庆为龙头，以柳州、西安、兰州、乌鲁木齐等为支点，串联“一带一路”沿线节点城市，横贯中西部地区，联系亚欧大陆的流通大通道。</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>物流</t>
+          <t>汽车零部件, 纺织</t>
         </is>
       </c>
     </row>
@@ -3247,7 +2498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3274,7 +2525,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -3289,91 +2540,91 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sz002535</t>
+          <t>sh603028</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>林州重机</t>
+          <t xml:space="preserve">赛福天  </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sh603089</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>正裕工业</t>
+          <t>襄阳轴承</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sh603028</t>
+          <t>sh603528</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">赛福天  </t>
+          <t>多伦科技</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sz301502</t>
+          <t>sz002708</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>华阳智能</t>
+          <t>光洋股份</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sh605333</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>沪光股份</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sh603528</t>
+          <t>sz002820</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>桂发祥</t>
         </is>
       </c>
     </row>
@@ -3383,12 +2634,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sz002931</t>
+          <t>sz301314</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>锋龙股份</t>
+          <t>科瑞思</t>
         </is>
       </c>
     </row>
@@ -3398,12 +2649,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sh605488</t>
+          <t>sz002093</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>福莱新材</t>
+          <t>国脉科技</t>
         </is>
       </c>
     </row>
@@ -3413,12 +2664,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sz000700</t>
+          <t>sz001318</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>模塑科技</t>
+          <t>阳光乳业</t>
         </is>
       </c>
     </row>
@@ -3428,12 +2679,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>sh600094</t>
+          <t>sz001219</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">大名城  </t>
+          <t>青岛食品</t>
         </is>
       </c>
     </row>
@@ -3443,57 +2694,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>sz000810</t>
+          <t>sz001331</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>创维数字</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>sh603901</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>永创智能</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>sz000559</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>万向钱潮</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>sh603337</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>杰克科技</t>
+          <t>胜通能源</t>
         </is>
       </c>
     </row>

--- a/stock_data1.xlsx
+++ b/stock_data1.xlsx
@@ -476,20 +476,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="89" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="106" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="247" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="254" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,45 +556,46 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>sh603028</t>
+          <t>sz000678</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">赛福天  </t>
+          <t>襄阳轴承</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>10.33</v>
+        <v>17.61</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.0106</v>
+        <v>9.9938</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>5天5板</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>机器人|在工业机器人领域，公司凭借对钢丝绳在升降与传动系统中核心技术的深度研发与创新应用，成功突破了传统业务的边界，开辟了全新的市场空间。通过为仓储智能机器人企业深圳市海柔创新科技有限公司提供高性能的升降配件解决方案，公司实现了从传统制造业向高端智能装备领域的跨越式发展。</t>
+          <t>军工+机器人|1.公司是湖北省军民融合企业，东风公司的军车轴承一直指定公司独家供应。
+2.公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>军工, 机器人</t>
         </is>
       </c>
     </row>
@@ -605,46 +606,45 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>sz000678</t>
+          <t>sz002708</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>襄阳轴承</t>
+          <t>光洋股份</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>16.01</v>
+        <v>18.94</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.0344</v>
+        <v>9.9884</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>3天3板</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>军工+机器人|1.公司是湖北省军民融合企业，东风公司的军车轴承一直指定公司独家供应。
-2.公司高效率、低振动、薄壁等轴承技术都可应用于机器人减速器轴承。</t>
+          <t>机器人|2024年12月2日公告，公司拟与安徽黄山高新技术开发区管理委员会签订《项目投资协议书》，在安徽省黄山高新区内拍取面积100亩土地使用权用于建设年产6000万套高端新能源汽车及机器人用精密零部件项目，以公司全资子公司黄山光洋传动科技有限公司为投资建设主体。本次项目投资总额预计为100,000万元。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>军工, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -655,46 +655,45 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>sh603528</t>
+          <t>sz000559</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>多伦科技</t>
+          <t>万向钱潮</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>9.85</v>
+        <v>13.18</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10.0559</v>
+        <v>10.0167</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4天4板</t>
+          <t>4天3板</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>智能驾驶+机器人|1.公司已开展多项人工智能驾考新技术研究，包括基于机器视觉的驾驶人注意力分配识别、基于机器视觉的道路环境目标识别、基于激光雷达的目标探测技术等。
-2.公司通过珠海星芯投资基金参与了众擎机器人科技有限公司Pre-A++轮融资，并持有其1.57%的股份。</t>
+          <t>机器人|公司在机器人领域主要布局精密轴承和丝杠，目前相关产品尚处于开发验证阶段。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>智能驾驶, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -705,31 +704,31 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>sz002708</t>
+          <t>sh601956</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>光洋股份</t>
+          <t>东贝集团</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>17.22</v>
+        <v>6.09</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10.0319</v>
+        <v>9.927800000000001</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -738,7 +737,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>机器人|2024年12月2日公告，公司拟与安徽黄山高新技术开发区管理委员会签订《项目投资协议书》，在安徽省黄山高新区内拍取面积100亩土地使用权用于建设年产6000万套高端新能源汽车及机器人用精密零部件项目，以公司全资子公司黄山光洋传动科技有限公司为投资建设主体。本次项目投资总额预计为100,000万元。</t>
+          <t>机器人|2025年4月17日公司在互动平台表示，公司转子压缩机具备量产能力，正在进行客户匹配性能测试。另外，公司在洗衣机电机、空调电机、机器人关节电机等领域均有相关技术研发储备。人形机器人关节电机目前还处于研发测试阶段。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -754,31 +753,31 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>sz001331</t>
+          <t>sh603037</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>胜通能源</t>
+          <t>凯众股份</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>38.52</v>
+        <v>13.06</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9.994300000000001</v>
+        <v>10.0253</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -787,12 +786,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>七腾机器人入主|胜通能源公告称，七腾机器人向公司除收购人及其一致行动人外的全体股东发出部分要约收购，预定收购股份数量42,336,000股，占公司总股本的15%，要约价格为13.28元/股。要约收购期限为2026年4月28日至2026年5月27日，最后三个交易日预受要约不可撤销。</t>
+          <t>机器人|公司的聚氨酯材料具有高强度、高弹性、高耐磨、重量轻、易加工等优良特性，可以用于人形机器人的制造。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>七腾机器人入主</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -803,40 +802,40 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sh605333</t>
+          <t>sh603081</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>沪光股份</t>
+          <t>大丰实业</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>19.91</v>
+        <v>11.31</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10</v>
+        <v>10.0195</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2天2板</t>
+          <t>4天2板</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>机器人|2026年8月12日，公司与北京辉羲智能信息技术有限公司、全能具身智能科技（苏州）有限公司、灵巧科技（昆山）有限公司四方正式签署具身智能战略合作仪式，依托沪光在汽车线束制造及场景化机器人应用方面的深厚积淀，叠加合作伙伴在芯片设计、具身智能算法及灵巧操作系统等维度的顶尖能力，有望构建起“场景定义—芯片赋能—技术落地”的闭环生态，为具身智能在工业领域的大规模应用打造可复制的标杆范式。</t>
+          <t>机器人|公司于2025年3月23日与智元机器人签订《战略合作协议》，双方拟共同投资设立合资公司（公司持股85%），聚焦多模态交互系统研发与智能终端场景化应用，打造"技术+场景"融合创新平台，构建基于语音、视觉、触觉、手势等多模态交互模型，研发出匹配文娱旅体商场景需求的具身智能产品并实现商业化落地。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -852,40 +851,36 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>sh603370</t>
+          <t>sh603006</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>华新精科</t>
+          <t>联明股份</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30.81</v>
+        <v>10.74</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.9964</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>10.041</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司铁芯产品下游应用广阔，可应用于机器人关节等相关部位的电机。</t>
+          <t>机器人|公司通过尚成一号产业基金间接参股逐际动力，逐际动力是一家具身智能机器人公司，聚焦打造全尺寸通用人形机器人，并衍生了包括双足机器人等创新产品。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -901,46 +896,41 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>sz002249</t>
+          <t>sh603897</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>大洋电机</t>
+          <t>长城科技</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>7.7</v>
+        <v>26.43</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4天2板</t>
-        </is>
-      </c>
+        <v>9.987500000000001</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>机器人+稀土|1.公司前瞻技术研究院已设立前瞻技术研究项目--人形机器人电机项目，其中涉及包括无框力矩电机在内的多项研究。
-2.公司持有宁波科星材料科技有限公司51%的股份，宁波科星是一家专注于烧结钐钴、烧结钕铁硼永磁材料及产品研发和制造的高新技术企业，产品广泛应用于曳引机、汽车、电子信息、医疗、航空航天、国防等领域。</t>
+          <t>机器人|公司电磁线产品的应用领域包括工业电机、家用电器、汽车电机、电动工具和低压电器，其中工业电机涵盖水泵电机、轮毂电机、吸尘器电机、微特电机、中小型电机等产品领域，家用电器主要包括空调压缩机和风扇电机等，汽车电机包括新能源汽车驱动电机在内的车用各式电机产品应用领域，低压电器分别为仪表仪器、以及应用于包括机器人应用领域等在内的低压线圈产品。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>机器人, 稀土</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -951,42 +941,41 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>sh603758</t>
+          <t>sz002164</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>秦安股份</t>
+          <t>宁波东力</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>10.73</v>
+        <v>16.9</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.0513</v>
+        <v>10.026</v>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>汽车+机器人|1.公司是国内具有一定规模水平的汽车发动机核心零部件专业生产企业，主要从事汽车发动机核心零部件——气缸体、气缸盖、曲轴、变速器箱体等产品的研发、生产与销售。
-2.参股墨现科技专注于触觉传感器领域，为各种应用场景提供高适应性柔性压力传感器解决方案。其研发的电子皮肤技术还在机器人灵巧手和机械臂上取得了显著进展，并逐渐拓展至机器人本体全身。</t>
+          <t>机器人|公司的产品包括行星减速器等，杭州湾电机、减速器部分车间已投入生产。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>汽车, 机器人</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -997,36 +986,36 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>sh601956</t>
+          <t>sz002526</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东贝集团</t>
+          <t>山东矿机</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>5.54</v>
+        <v>2.98</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9.9206</v>
+        <v>9.963099999999999</v>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>机器人|2025年4月17日公司在互动平台表示，公司转子压缩机具备量产能力，正在进行客户匹配性能测试。另外，公司在洗衣机电机、空调电机、机器人关节电机等领域均有相关技术研发储备。人形机器人关节电机目前还处于研发测试阶段。</t>
+          <t>机器人|公司具有高尖端的加工装备、成熟可靠的技术工艺以及优良的职工队伍，自行研制的机器人和自动化生产线，既可为现有产品提供加工服务又可承接外部定制任务，具有较强的装备优势，目前公司智能焊接机器人主要用于对结构件等部件进行焊接作业。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1042,41 +1031,42 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>sz300539</t>
+          <t>sh603667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>横河精密</t>
+          <t>五洲新春</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>19.68</v>
+        <v>49.98</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>20</v>
+        <v>9.991199999999999</v>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司齿轮箱/减速器类产品主要应用在智能扫地机器人等领域。</t>
+          <t>机器人+业绩|1.公司已经研发成功机器人全系列轴承产品，配套南高齿、纽氏达特、中大力德、大族谐波、来福谐波等机器人减速器企业。此外，公司发展以高端行星滚柱丝杠产品为切入点的各类丝杠产品，为直线执行器、旋转执行器和灵巧手提供部件或者成套产品。
+2.五洲新春公告称，第三季度营业收入为7.16亿元，同比下降6.59%；归属于上市公司股东的净利润为9.22亿元，同比增长3875.18%。前三季度营业收入为22.50亿元，同比下降15.45%；归属于上市公司股东的净利润为9.83亿元，同比增长898.01%。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>机器人, 业绩</t>
         </is>
       </c>
     </row>
@@ -1087,36 +1077,36 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>sh603037</t>
+          <t>sh600173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>凯众股份</t>
+          <t>卧龙新能</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>11.87</v>
+        <v>5.45</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10.0093</v>
+        <v>10.101</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司的聚氨酯材料具有高强度、高弹性、高耐磨、重量轻、易加工等优良特性，可以用于人形机器人的制造。</t>
+          <t>机器人|参股浙江龙能电力科技股份有限公司自主研发的PVRC-D1-2384-3P/4P光伏清扫机器人，于2025年6月在广西横县双胞胎光伏电站和安徽池州汇成光伏电站完成首批1期光伏清扫机器人安装调试。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1132,36 +1122,37 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>sz002823</t>
+          <t>sz003028</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>凯中精密</t>
+          <t>振邦智能</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>13.49</v>
+        <v>25.91</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.0326</v>
+        <v>10.0212</v>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>机器人|参股武汉数字化设计与制造创新中心有限公司的经营范围包括智能机器人的研发、智能机器人销售。</t>
+          <t xml:space="preserve">机器人|公司人形机器人领域主要在智能控制器、电子皮肤等技术方面有布局。
+</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1177,42 +1168,41 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>sz301682</t>
+          <t>sz301261</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>宏明电子</t>
+          <t>恒工精密</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>102.1</v>
+        <v>62.89</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>20.0047</v>
+        <v>19.9962</v>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>机器人+MLCC|1.公司间接供应的无框力矩电机产品，最终用于人形机器人关节中，目前已实现小批量应用配套。
-2.公司是国内少数从高品质电子材料（陶瓷瓷料和导电浆料）到电子元器件均具备研制能力的全产业链生产企业，核心产品为高可靠MLCC产品，拥有国内首条宇航级MLCC生产线。</t>
+          <t>机器人|公司为国内规模最大的连续铸铁生产企业，技术和工艺国内领先，连续球墨铸铁材料具有高刚度、高耐磨性、轻量化的特点，可应用于机器人减速器（RV/谐波）核心部件。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>机器人, MLCC</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
@@ -1223,36 +1213,36 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-2.771</v>
+        <v>3.5565</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>据《科创板日报》报道，字节跳动官网及招聘信息显示，其Seed Model团队更新一批机器人相关岗位，覆盖本体设计、灵巧手、减速机控制、仿真工程师、数据算法工程师等数十个方向。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sz301479</t>
+          <t>sh603219</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>弘景光电</t>
+          <t>富佳股份</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>56.15</v>
+        <v>13.21</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>20.0043</v>
+        <v>9.9917</v>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>机器人|公司的光学镜头及摄像模组产品可用于人形机器人。</t>
+          <t>机器人|子公司宁波益佳电子有限公司为乐聚机器人代工各类线路板。乐聚机器人是一家致力于高端智能人形机器人研发、制造和销售的高科技企业。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1264,1226 +1254,2619 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>商业零售</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.199</v>
+        <v>3.5565</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>商务部流通发展司负责人表示，据国家统计局数据，1至9月，我国批发和零售业增加值11.1万亿元，同比增长4.4%，增速较上半年提高0.7个百分点，占GDP比重为10.4%。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sh600838</t>
+          <t>sh605288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>凯迪股份</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>13.31</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5天5板</t>
-        </is>
-      </c>
+        <v>10.0084</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>零售|公司控股股东为上海九百（集团）有限公司。目前已经发展成为涉及洗涤化工产品生产销售及洗染服务、酒类产品批发等多种业态的综合性企业。</t>
+          <t>机器人|公司主要产品为线性驱动系统，可以应用在机器人上。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>商业零售</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.199</v>
+        <v>3.5565</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>商务部流通发展司负责人表示，据国家统计局数据，1至9月，我国批发和零售业增加值11.1万亿元，同比增长4.4%，增速较上半年提高0.7个百分点，占GDP比重为10.4%。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sh600785</t>
+          <t>sh603992</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>新华百货</t>
+          <t>松霖科技</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>13.9</v>
+        <v>22.67</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9.968399999999999</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3天2板</t>
-        </is>
-      </c>
+        <v>9.995099999999999</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>零售|公司是宁夏乃至西北地区较大的商业零售企业，主要从事商业零售、物流和商业物业出租业务，零售业务主要涉及百货商场、综合购物中心、超市连锁、电器及通信连锁。</t>
+          <t>机器人|旗下松霖机器人与达闼机器人签署了战略合作框架协议，共同探索人形机器人垂直场景应用、核心部件创新升级、机器人出海及其他创新领域的产业机会。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>商业零售</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.199</v>
+        <v>3.5565</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>商务部流通发展司负责人表示，据国家统计局数据，1至9月，我国批发和零售业增加值11.1万亿元，同比增长4.4%，增速较上半年提高0.7个百分点，占GDP比重为10.4%。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sh600828</t>
+          <t>sh603633</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>茂业商业</t>
+          <t>徕木股份</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4.47</v>
+        <v>6.36</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10.0985</v>
+        <v>10.0346</v>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>零售|公司业务以商业零售为主，并辅以部分物业租赁和酒店业务，旗下实体零售门店数量总共22家，经营业态包括百货商场、购物中心、奥特莱斯及超市；商业零售主要经营模式仍为自营模式、联营模式和租赁模式，以联营模式为主。</t>
+          <t>光模块壳体+机器人|1.公司在研项目包括800G光模块壳体相关产品。
+2公司是智元机器人的合格供应商，主要向智元公司销售精密电子连接器及线束类产品。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>光模块壳体, 机器人</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>商业零售</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.199</v>
+        <v>3.5565</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>商务部流通发展司负责人表示，据国家统计局数据，1至9月，我国批发和零售业增加值11.1万亿元，同比增长4.4%，增速较上半年提高0.7个百分点，占GDP比重为10.4%。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>sz002187</t>
+          <t>920896.BJ</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>广百股份</t>
+          <t>旺成科技</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>5.92</v>
+        <v>16.23</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>10.0372</v>
+        <v>29.944</v>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>零售|公司是广东省百货连锁龙头、广州市销售规模最大的百货零售企。</t>
+          <t>机器人|公司拥有瑞士莱斯豪尔的Rz260、Rz410蜗杆砂轮磨齿机等高端设备，通过“滚齿+磨齿”工艺，产品精度可达到ISO或德国标准DIN4级，能够满足工业机器人或者人形机器人的产品需求。</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>机器人</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>商业零售</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.199</v>
+        <v>3.5565</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>商务部流通发展司负责人表示，据国家统计局数据，1至9月，我国批发和零售业增加值11.1万亿元，同比增长4.4%，增速较上半年提高0.7个百分点，占GDP比重为10.4%。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>sh601086</t>
+          <t>sh603109</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>国芳集团</t>
+          <t>神驰机电</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>12.62</v>
+        <v>17.93</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.0262</v>
+        <v>10</v>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>零售|公司从事以百货业为主，超市、电器为辅的连锁零售业务，是甘肃省内最大的连锁零售企业。</t>
+          <t>机器人+发电机|1.2025年8月14日，神驰机电与七腾机器人正式达成深度战略合作关系，标志着神驰机电正式进军机器人领域。七腾机器人有限公司是一家集特种机器人设计、研发、生产、销售、服务为一体的高新技术企业，在应急安全领域处于头部地位。
+2.公司主要从事小型发电机、通用汽油机及终端类产品的研发、生产、销售。终端类产品包括发电机组、高压清洗机、水泵等产品。小型发电机、通用汽油机主要用于配套发电机组。发电机组作为备用电源为家庭、医院、银行、机场、宾馆、通信等领域应急发电。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>机器人, 发电机</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>机器人概念</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-2.1342</v>
+        <v>3.5565</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>国家发改委表示，正在研究制定扩大内需战略实施方案（2026—2030年），并将加快推动印发实施。</t>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>sz002265</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>建设工业</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>9.9895</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司在第十五届中国国际航空航天博览会轻武器展区展出的多功能足式机器人、小型室内清剿机器人、小型智能察打机器人、便携式无人飞行枪械系统、班组多旋翼察打无人机等。</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>3.5565</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>sh605566</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>福莱蒽特</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司通过参股双曲线智能（杭州）有限公司布局柔性触觉传感相关业务，合作方钛深科技具备柔性触觉传感核心技术。</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>3.5565</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>sh603418</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>友升股份</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>机器人|2026年9月3日公司在机构调研中表示，公司依托子公司上海奥拓睿智科技有限公司，全面推进智能割草机器人产品研发及后续产业化的准备，围绕三电、结构、软件、测试等领域完善专业人才梯队建设和项目团队建设，目前智能割草机器人项目尚处于产品研发、测试验证及市场导入阶段。</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>3.5565</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>sh688045</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必易微  </t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>19.9957</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>半导体+机器人|1.公司主营业务为电源管理芯片的设计和销售。目前公司在产的电源管理芯片规格型号700余款，产品广泛运用于LED照明、通用电源、家电及IoT领域。
+2.公司所布局的温度传感器、磁传感器、电流传感器等，可广泛应用于工业自动化、服务机器人等领域。</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>半导体, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>3.5565</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>sh603135</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>中重科技</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>10.0637</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司主要产品为智能装备及生产线。整个生产线通过中央控制室下达指令实现高度自动化的运行，该生产线中包含了智能打包机器人、智能标识机器人、拆辊机器人、码垛机器人等机器人。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>3.5565</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>sz002879</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>长缆科技</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>10.0074</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司的智能管道可视化机器人可以对管道内部的情况进行实时影像监测、缺陷记录、AI故障判断、数据库对比分析、视频回放、图像抓拍等，无需人员进入管内即可了解管道内部状况，为制定养护、修复方案提供重要依据，并可以对管道内部进行清理及简单修复，适用于电力管道、排水管道、供水管道、工业管道、燃气管道等多种场景。</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>3.5565</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>sz002889</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东方嘉盛</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>9.971499999999999</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>机器人|在AI报关领域，公司在进出口报关领域的AI智能报关系统平台、智能通关机器人等，在通关领域已成为众多世界500强企业的最优选择。</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>3.5565</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>sh603926</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>铁流股份</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>9.993599999999999</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司于2025年9月3日与长三角哈特机器人产业技术研究院签署框架协议，内容涉及机器人关键零部件设计、机电控复合参数匹配设计与拓扑配置优化设计；机器人高精高效零部件的设计与制造；多传感融合的高精度高频响的自适应力位混合控制技术研究；机器人关键零部件的多维性能测试与评估设备研制。</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>3.5565</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>sh603626</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>科森科技</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>机器人+折叠屏|1.公司不生产机器人产品，公司为某品牌家用机器人提供相关结构件。
+2.公司生产的折叠屏手机铰链已量产。</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>机器人, 折叠屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>3.5565</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>920220.BJ</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>朗信电气</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>机器人|公司已与行业知名客户配套研发人形机器人关节电机，已实现批量供货。</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>机器人概念</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>3.5565</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>小米技术公众号披露仿生灵巧手技术探索成果。小米披露，新仿生手经过多姿态抓握测试，抓握拟人度与抓握成功率较前代低自由度版本均有提升。</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>sz301525</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>儒竞科技</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>19.995</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>机器人|子公司儒竞自控专注发展工业伺服驱动及控制系统领域业务，主要产品为伺服驱动器，产品在工业机器人、电子制造、物流、包装机械、印刷、锂电新能源等细分行业已实现批量销售。</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>4.0247</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>10只PCB产业链上市公司集体发布三季报，其中南亚新材、金安国纪第三季度净利增长超10倍。</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>sh603226</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>菲林格尔</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>10.0227</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>PCB|2026年9月18日公告，公司拟以现金向覃早才、杨振宇购买其持有的南京克锐斯自动化科技有限公司51%股权，交易对价暂定为2.14亿元。标的公司主要从事PCB压合工序自动化设备的研发、生产及销售。</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>4.0247</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>10只PCB产业链上市公司集体发布三季报，其中南亚新材、金安国纪第三季度净利增长超10倍。</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>sz002636</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>金安国纪</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>10.0075</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>业绩+PCB|金安国纪公告称，第三季度营业收入为31.45亿元，同比增长161.88%；归属于上市公司股东的净利润为11.58亿元，同比增长1030.57%。前三季度营业收入为65.43亿元，同比增长101.25%；归属于上市公司股东的净利润为19.24亿元，同比增长1012.67%。业绩变动主要系本期覆铜板售价上涨以及销量增长所致。</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>业绩, PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>4.0247</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>10只PCB产业链上市公司集体发布三季报，其中南亚新材、金安国纪第三季度净利增长超10倍。</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>sz002741</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>光华科技</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>9.9946</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>PCB+半导体|1.PCB化学品系公司三大主要产品之一，并进一步向PCB制造湿法流程的完整化学品体系延伸，为下游客户PCB制造湿法流程化学品提供切实有效的整体解决方案。
+2.公司化学试剂产品包括分析与专用试剂，主要应用于分析测试、教学、科研开发以及新兴技术领域的专用化学品，其中超净高纯试剂化学试剂为集成电路（IC）和超大规模集成电路（VLSI）制造过程中的关键性基础化工材料之一。</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>PCB, 半导体</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>4.0247</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>10只PCB产业链上市公司集体发布三季报，其中南亚新材、金安国纪第三季度净利增长超10倍。</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>sh600601</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>方正科技</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>10.0213</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>PCB|公司提供包括PCB设计、制造、仿真和测试的一站式解决方案，产品主要包括HDI、多层板（2-56层）、软硬结合板和其它个性化定制PCB等，以通信类高多层及消费类HDI产品为主。</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>4.0247</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>10只PCB产业链上市公司集体发布三季报，其中南亚新材、金安国纪第三季度净利增长超10倍。</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>sh603920</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>世运电路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>9.9971</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>PCB+机器人|公司与北美人形机器人龙头企业开展联合研发，聚焦人形机器人核心控制模块、驱动系统等关键部位的PCB产品，已形成从定制化设计、快速打样到性能优化的全流程技术能力。</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>PCB, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>4.0247</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>10只PCB产业链上市公司集体发布三季报，其中南亚新材、金安国纪第三季度净利增长超10倍。</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>sz300806</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>斯迪克</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>43.92</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>PCB|公司生产的感光干膜主要应用于PCB制造过程中电路设计的图形转移。</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>2.8164</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>SpaceX三季度营收146亿美元，同比大增161%；净利润44亿美元，去年同期净亏损11亿美元；调整后EBITDA 88亿美元，同比大涨306%。</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>sz001400</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>江顺科技</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>88.31</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>10.0025</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>2天2板</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>3D打印+商业航天|1.子公司江宇科技主要从事用于服务器液冷相关的3D打印产品的研发工作，已有部分样品。
+2.公司产品铝型材挤压模具和铝型材挤压配套设备应用于航空航天领域。</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>3D打印, 商业航天</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2.8164</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>SpaceX三季度营收146亿美元，同比大增161%；净利润44亿美元，去年同期净亏损11亿美元；调整后EBITDA 88亿美元，同比大涨306%。</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>sz001296</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>长江材料</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>10.0054</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>3D打印+商业航天|公司生产的3D打印砂应用于3D打印砂型铸造，采购公司3D打印砂的客户中有航天领域的供应商。</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>3D打印, 商业航天</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>2.8164</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>SpaceX三季度营收146亿美元，同比大增161%；净利润44亿美元，去年同期净亏损11亿美元；调整后EBITDA 88亿美元，同比大涨306%。</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>sh603131</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>上海沪工</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>10.0152</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>商业航天+机器人|1.公司旗下航天华宇是航天装备制造平台，是我国多家航天总装单位的核心供应单位。同时，公司设立沪航卫星作为卫星业务平台，为商业卫星提供配套产品及服务。
+2.拥有机器人及自动化焊接(切割)成套设备，与全球最大机器人公司之一的FANUC结成合作伙伴。</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>商业航天, 机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>2.8164</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>SpaceX三季度营收146亿美元，同比大增161%；净利润44亿美元，去年同期净亏损11亿美元；调整后EBITDA 88亿美元，同比大涨306%。</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>sz001270</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>铖昌科技</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>9.995900000000001</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>商业航天|在卫星互联网方面，目前已经成功推出星载和地面用卫星互联网相控阵T/R芯片全套解决方案，公司研制的硅基毫米波模拟波束赋形芯片系列产品的性能优异，目前已与多家科研院所及优势企业开展合作。</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>2.8164</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>SpaceX三季度营收146亿美元，同比大增161%；净利润44亿美元，去年同期净亏损11亿美元；调整后EBITDA 88亿美元，同比大涨306%。</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>sh603680</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>今创集团</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>商业航天|公司成立常州今创航空航天产业投资有限公司，计划做商业航空航天产业链的布局。</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>2.5725</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>华福证券策略首席分析师周浦寒在接受记者采访时提到，已披露三季报的业绩盈利水平改善明显，A股上市公司盈利面持续修复，总量与结构同步向好。</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>sz001219</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>青岛食品</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>9.985300000000001</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="G44" s="2" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>10.0134</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>3天3板</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>休闲食品+业绩|1.公司主要从事饼干与花生酱等休闲食品的研发、生产及销售，主要产品包括“青食”品牌钙奶饼干、“青食”品牌休闲饼干和“海友”品牌花生酱。
 2.公司2026年7-9月实现营业收入为1.57亿元，同比上升7.1%；归母净利润为3678万元，同比上升31.2%。</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>休闲食品, 业绩</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>-2.1342</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>国家发改委表示，正在研究制定扩大内需战略实施方案（2026—2030年），并将加快推动印发实施。</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>2.5725</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>华福证券策略首席分析师周浦寒在接受记者采访时提到，已披露三季报的业绩盈利水平改善明显，A股上市公司盈利面持续修复，总量与结构同步向好。</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>sz301359</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>东南电子</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>业绩|公司2026年1-9月实现营业收入3.20亿元，同比增长32.29%；归母净利润3404.79万元，同比增长14.93%。报告期内，公司营业收入同比增长，主要系客户订单增加所致；经营活动产生的现金流量净额同比下降，主要系购买商品、接受劳务支付的现金增加所致。</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>2.5725</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>华福证券策略首席分析师周浦寒在接受记者采访时提到，已披露三季报的业绩盈利水平改善明显，A股上市公司盈利面持续修复，总量与结构同步向好。</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>sz300613</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>富瀚微</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>72.48</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>业绩+半导体|富瀚微公告称，第三季度营收为10.91亿元，同比增长141.10%；净利润为4.25亿元，同比增长620.99%。前三季度营收为25.54亿元，同比增长123.94%；净利润为7.75亿元，同比增长845.02%。业绩增长主要系产品销售数量与销售价格均实现提升所致。</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>业绩, 半导体</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>2.5725</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>华福证券策略首席分析师周浦寒在接受记者采访时提到，已披露三季报的业绩盈利水平改善明显，A股上市公司盈利面持续修复，总量与结构同步向好。</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>sh603868</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>飞科电器</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>9.9968</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>业绩|公司2026年1-9月实现营业收入30.66亿元，同比增长0.84%；归母净利润5.32亿元，同比增长16.40%。业绩变动方面，公司归属于上市公司股东的扣除非经常性损益的净利润同比增长，主要为本报告期销售收入增加；经营活动产生的现金流量净额同比下降，主要为本报告期内支付的采购款增加。</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>业绩超预期</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>2.5725</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>华福证券策略首席分析师周浦寒在接受记者采访时提到，已披露三季报的业绩盈利水平改善明显，A股上市公司盈利面持续修复，总量与结构同步向好。</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>sh600078</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>澄星股份</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>10.0467</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>业绩|澄星股份公告称，第三季度营收为14.52亿元，同比增长65.00%；净利润为1.47亿元，同比增长1471.96%。前三季度营收为35.90亿元，同比增长35.15%；净利润为2.65亿元，同比增长848.20%。</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1.9086</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>10月28日，Anthropic宣布，其生命科学团队已与百时美施贵宝、Generate Biomedicines等六家新药研发机构建立深度研究合作，并启动自主药物发现项目。</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>sz301080</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>百普赛斯</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>101.24</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>19.9953</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>CXO|公司是一家专业提供重组蛋白等关键生物试剂产品及技术服务的高新技术企业，主要产品及服务应用于肿瘤、自身免疫疾病、心血管病、传染病等疾病的药物早期发现及验证、药物筛选及优化、诊断试剂开发及优化、临床前实验及临床试验、药物生产过程及工艺控制（CMC）等研发及生产环节。</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>CXO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>1.9086</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>10月28日，Anthropic宣布，其生命科学团队已与百时美施贵宝、Generate Biomedicines等六家新药研发机构建立深度研究合作，并启动自主药物发现项目。</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>sh688137</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>近岸蛋白</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CXO+AI制药|1.公司CRO服务业务主要分为定制化技术服务和技术包转让，主要为生物领域相关科研院所、药企及疫苗生产企业提供研究用重组蛋白、抗体及mRNA等相关定制化服务，同时也可提供重组蛋白质大规模生产工艺开发及技术转移服务。
+2.公司创新性地将AI工具与自主研发的机器学习系统深度融合，提高了研发创新的效率，广泛应用于酶、抗体等蛋白质的创新设计、改造和表达，以及抗体亲和力和稳定性改造噬菌体库等技术领域。 </t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>CXO, AI制药</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>1.9086</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>10月28日，Anthropic宣布，其生命科学团队已与百时美施贵宝、Generate Biomedicines等六家新药研发机构建立深度研究合作，并启动自主药物发现项目。</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>sz002172</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>澳洋健康</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>9.9099</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>医疗服务|公司的医疗服务业务已形成医、康、养护联动发展模式，形成以澳洋医院总院为支撑，澳洋医院三兴分院、顺康医院、港城康复医院、优居壹佰护理院、张家港澳洋护理院联动发展。</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>医疗服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>1.9086</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>10月28日，Anthropic宣布，其生命科学团队已与百时美施贵宝、Generate Biomedicines等六家新药研发机构建立深度研究合作，并启动自主药物发现项目。</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>sz300006</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>莱美药业</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>19.9516</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>纳米炭抗癌|公司主要业务为医药制造，涵盖特色专科类（主要包括抗肿瘤药、消化系统药、肠外营养药）、抗感染类等，重点产品肿瘤淋巴示踪剂卡纳琳（纳米炭混悬注射液）由公司自研自产。</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>纳米炭抗癌</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>3.5184</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉创始人马斯克表示，当人工智能从处理信息走向物理现实时，载体机器人对内存的消耗将碾压地球上现有的所有计算设备。</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>sz002820</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>桂发祥</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>10.0098</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sz000670</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>盈方微</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>9.937899999999999</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>存储芯片+业绩|1.控股子公司熠存存储技术（上海）有限公司目前主营业务为：集成电路芯片设计及服务；数据处理和存储支持服务；计算机软硬件及辅助设备批发等。
+2.盈方微发布2026年第三季度报告称，公司2026年第三季度实现营业收入2,529,454,326.59元，同比增长66.90%；归属于上市公司股东的净利润为11,747,630.76元，同比增长206.33%。</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>存储芯片, 业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>3.5184</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉创始人马斯克表示，当人工智能从处理信息走向物理现实时，载体机器人对内存的消耗将碾压地球上现有的所有计算设备。</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>sz002943</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>宇晶股份</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>9.9869</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>半导体材料|公司的碳化硅切割、研磨、抛光设备主要用于加工单晶碳化硅抛光片，N型导电型碳化硅抛光片是制作功率芯片的核心材料，在新能源汽车和充电桩等产品上有广阔的应用前景。</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>半导体材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>芯片产业链</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>3.5184</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉创始人马斯克表示，当人工智能从处理信息走向物理现实时，载体机器人对内存的消耗将碾压地球上现有的所有计算设备。</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>sh603061</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金海通  </t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>260.15</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>芯片测试设备|公司是一家从事研发、生产并销售半导体芯片测试设备的高新技术企业，深耕集成电路测试分选机（Test handler）领域，其UPH（单位小时产出）最大可达到13500颗，可测试芯片尺寸范围可涵盖2*2mm~100*100mm。</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>芯片测试设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>文化传媒</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>2.3887</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>根据QuestMobile于2026年10月26日公布的数据，截至2026年8月，腾讯绿泡泡短剧小程序月活跃用户数已达1.43亿，成功突破亿级大关。10月首周周活跃用户达8968万，较9月首周提升44.1%。</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>sh600715</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>文投控股</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>10.1604</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>6天3板</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>短剧+AI|公司已针对短剧行业进行深入研究，并计划依托自身IP资源孵化优势，结合AIGC等工具的发展应用，探索文化内容与科技手段相融合的新型创作模式。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>短剧, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>文化传媒</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>2.3887</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>根据QuestMobile于2026年10月26日公布的数据，截至2026年8月，腾讯绿泡泡短剧小程序月活跃用户数已达1.43亿，成功突破亿级大关。10月首周周活跃用户达8968万，较9月首周提升44.1%。</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>sh603533</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>掌阅科技</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>10.0078</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>短剧+AI|1.公司已经搭建起专业的短剧生产运营体系。公司2025年度AI短剧业务收入预计不超过2025年度主营业务收入的1%。
+2.MiniMax与掌阅科技合作的对话式AI应用“阅爱聊”，能让文学作品中的角色来到现实，与用户展开一场“跨次元”对谈。</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>短剧, AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>文化传媒</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>2.3887</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>根据QuestMobile于2026年10月26日公布的数据，截至2026年8月，腾讯绿泡泡短剧小程序月活跃用户数已达1.43亿，成功突破亿级大关。10月首周周活跃用户达8968万，较9月首周提升44.1%。</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>sz300291</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>百纳千成</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>短剧|公司多格式影视业务主要包括电影、剧集、短视频、中短剧、视频影视游戏、超级短剧集。</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>短剧</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>2.9266</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>10月27日，上海市经济信息化委印发《上海市加快发展新一代智能制造行动方案》。《行动方案》提到，研制推广物理AI装备，研制具备自主感知和决策能力的机器人、检测装备等智能制造装备。</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>sh603337</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>杰克科技</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>10.0023</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>4天3板</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>物理AI|公司持续沉淀工业软件、产线仿真、项目现场实施能力，积累服装制造场景数据与标杆客户案例，为服装机器人业务场景落地储备技术、客户及工况数据。</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>2.9266</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>10月27日，上海市经济信息化委印发《上海市加快发展新一代智能制造行动方案》。《行动方案》提到，研制推广物理AI装备，研制具备自主感知和决策能力的机器人、检测装备等智能制造装备。</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>sz301488</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>豪恩汽电</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>97.87</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>19.9975</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>物理AI|公司与英伟达的合作为采购其芯片用于共同开发机器人大脑控制系统，涵盖英伟达Jetson Thor、Orin AGX、Orin NX 和Orin Nano全系列控制域，双方将共同突破机器人“大小脑”开发。</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>物理AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>PEEK材料</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>4.7261</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>具身智能机器人正加速从实验室走向量产，2025年全球人形机器人原型机发布超50款，国内PEEK材料需求指数级增长。</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>sz002915</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>中欣氟材</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>10.0275</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>PEEK|公司已构建一体化的PEEK核心原材料产业，已布局5000吨PEEK核心中间体的产能DFBP，并围绕DFBP布局有氟苯、4-氟苯甲酰氯、氢氟酸、萤石矿的一体化产业链。</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>PEEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>光通信</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>3.6175</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>高盛近期报告大幅上调全球光模块市场预测，预计2026年至2028年市场规模将分别达到677亿美元、1314亿美元和1485亿美元，较此前预测上调33%、81%和115%。</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>sz002975</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>博杰股份</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>85.12</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>10.0026</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>磷化铟|博杰股份公告称，公司拟使用自有资金1.83亿元通过股权收购方式取得联营公司珠海鼎泰芯源晶体有限公司控股权。交易完成后，公司持有鼎泰芯源股权由11.049%增至66.922%，合计控制92.190%表决权，鼎泰芯源将成为公司控股子公司。珠海鼎泰芯源晶体有限公司致力于以磷化铟（InP）、锑化镓（GaSb）为主的Ⅲ-Ⅴ族化合物半导体单晶及衬底材料的国产化事业，磷化铟衬底主要应用于光纤通信、光探测器、红外光学、高频毫米波通信等领域。</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>磷化铟</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>消费电子</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>3.3392</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>据Counterpoint预计，全球市场生成式AI手机渗透率将在2027年达到52%，端侧AI由高端卖点转为出厂标配。</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>sz002862</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>实丰文化</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>10.0143</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>端侧AI|公司在10月21日举行主题为"玩具之外"的发布会上首次公开面向办公场景的AI硬件新品DeskBuddy“桌面搭子”，并在同期举行的CTE中国玩具展暨潮玩展首次对外展出实体样机。</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>端侧AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>ST股</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>sz002816</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>*ST和科</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>9.9939</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>ST股 | 和科达半导体专注于半导体专用设备的研发、生产和销售，为半导体先进封装及前道制程的方案解决供应商。主要产品涵盖晶圆清洗设备、匀胶显影设备、无掩膜光刻机、微影光刻机和晶圆去胶机等。</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>sz002696</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>百洋股份</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>14天9板</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>水产品+鱼粉|1.公司位于广西，水产品加工业务板块将着重研发以罗非鱼、生鱼、金鲳鱼、海鲈鱼为原料的内销产品。
+2.公司下辖鱼粉厂的合计年产量约为1-2万吨，鱼油年产量约为2000-4000吨。</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>水产品, 鱼粉</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>sh600828</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>茂业商业</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>10.0671</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>2天2板</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>休闲食品|公司是专业从事传统特色及其他休闲食品的研发、生产和销售的中华老字号企业，自产产品包括麻花、糕点、节令食品、天津风味方便食品等。</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>休闲食品</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>食品饮料</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>-2.1342</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>国家发改委表示，正在研究制定扩大内需战略实施方案（2026—2030年），并将加快推动印发实施。</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>sz001318</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>阳光乳业</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="H24" s="2" t="n">
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>零售|公司业务以商业零售为主，并辅以部分物业租赁和酒店业务，旗下实体零售门店数量总共22家，经营业态包括百货商场、购物中心、奥特莱斯及超市；商业零售主要经营模式仍为自营模式、联营模式和租赁模式，以联营模式为主。</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>零售</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2天2板</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>乳制品|公司专注于乳制品及乳饮料的研发、生产和销售，并以低温乳制品、低温乳饮料为主打产品。公司针对儿童提高免疫力开发的“初乳” 产品。公司从事液态乳、含乳饮料等产品的研发、生